--- a/last.xlsx
+++ b/last.xlsx
@@ -566,49 +566,55 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t># 发布会概况
-王毅在慕尼黑安全会议上发表演讲，围绕“多极化”主题阐述中国主张，提出应推动平等有序的世界多极化，并表达四点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。王毅指出，80年前联合国成立时只有51个会员国，如今已有193个国家；中国加入了几乎所有普遍性政府间国际组织和600多项国际公约，承担超过20%的联合国会费，建成世界上最大的清洁发电体系；去年中国GDP增长5%，对世界经济增长贡献率接近30%。问答环节涉及国际秩序、乌克兰危机、中美关系等议题，王毅会后将前往纽约出席联合国安理会会议。
-# 核心信息
-## 多极化世界秩序与中国主张
-- **多极化趋势**：80年前联合国成立时仅51个会员国，如今已有193个国家；王毅借今年慕安会报告主题指出世界正走向多极化，中国主张推动**平等有序的世界多极化**，并称中国必将是多极体系中的确定性因素、坚定做变革世界中的建设性力量。
-- **四点看法**：一是倡导平等相待，坚持权利平等、机会平等、规则平等，主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权；二是尊重国际法治，以联合国宪章宗旨和原则为根本遵循；三是践行多边主义，倡导共商共建共享的全球治理观；四是坚持开放共赢，以普惠包容的经济全球化支撑平等有序的世界多极化。
-- **中国参与国际体系数据**：中国加入几乎所有普遍性的政府间国际组织和**600多项国际公约**，承担超过**20%的联合国会费**，建成世界上最大的清洁发电体系，并落实全球发展倡议、全球安全倡议、全球文明倡议。
-- **中欧关系**：今年是中欧建交50周年，中方愿同欧方用好这一契机深化战略沟通和互利合作；中国愿推动高质量共建“一带一路”，同欧盟“全球门户”战略相互对接。
-## 国际秩序与规则
-- **中国与国际秩序**：中国是在现行国际秩序中发展起来的、是受益者，主张共同维护以联合国为核心的国际体系，遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，推动秩序朝着更加公正合理的方向发展。
-- **反对双重标准**：在遵守国际法上不能搞双重标准，要尊重各国主权和领土完整，就应该支持中国实现完全统一。
-## 乌克兰危机
-- **中俄关系**：中俄建立结盟不对抗、不针对第三方的睦邻友好关系，是正常国与国交往；针对是否减少购买俄油气的提问，王毅表示没有国家能提供如此巨量油气满足中国民众需求，且不能允许经贸问题政治化。
-- **中方立场与行动**：自2022年2月25日起中方提出对话协商解决；习近平主席提出4点主张——各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力都应得到支持；中方派特使斡旋，同巴西等南方国家发起“和平之友”。
-- **和谈前景**：中方乐见一切致力于和平的努力，包括美国同俄罗斯达成的共识；所有当事方和利益攸关方应适时参与和谈，欧洲有必要发挥重要作用，探讨均衡、有效、可持续的欧洲安全框架。
-## 中美关系
-- **对美政策**：中国对美政策保持连续性和稳定性，遵循习近平主席提出的三原则——相互尊重、和平共处、合作共赢；中方愿按三原则同美方构建稳定健康可持续的双边关系。
-- **应对立场**：若美方仍对中国打压遏制，中方必将奉陪到底，坚决维护中国主权、国家尊严和正当发展权利，坚决回击美方单边霸凌行径。
-# 官方表态
-## 多极化世界秩序与中国主张
-- **推动平等有序的世界多极化**：中国给出的答案是应当推动平等有序的世界多极化，这是习近平主席提出的重大主张，也是对多极世界真诚的期许。中国必将是多极体系中的确定性因素，将坚定做变革世界中的建设性力量。
-- **倡导平等相待**：坚持权利平等、机会平等、规则平等，应当成为建设多极世界的基本原则。中国主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权，这不会导致西方的缺失，而将促进世界的正和。
-- **尊重国际法治**：联合国宪章宗旨和原则是处理国际关系的根本遵循，也是建设多极世界的重要基石。多极格局不能是无序的状态，大国要带头讲诚信、讲法治，坚决摒弃言行不一、零和博弈。在遵守国际法上不能搞双重标准，要尊重各国的主权和领土完整，就应该支持中国实现完全统一。
-- **践行多边主义**：联合国是践行多边主义、推进全球治理的核心平台，未来的多极世界更加需要联合国。对于这座大厦应该固本强基，而不是拆梁毁柱；对于治理全球难题应当共担责任，而不是唯利是图；对于共同挑战应该团结应对，而不是阵营对抗。
-## 开放共赢与中欧关系
-- **坚持开放共赢**：保护主义不是出路，滥加关税没有赢家，脱钩断链断的是机遇，小院高墙封的是自己。应当坚持开放合作，以普惠包容的经济全球化来支撑平等有序的世界多极化。
-- **共享发展机遇**：中国担当起全球经济增长的重要引擎，向世界释放超大规模的市场红利。中国愿推动高质量共建"一带一路"，同欧盟的"全球门户"战略相互对接，赋能彼此也赋能世界。
-- **中欧伙伴关系**：中方始终认为欧洲是多极世界的重要一极，中欧双方是伙伴而不是对手。今年是中欧建交50周年，中方愿意同欧方用好这一契机，深化战略沟通和互利合作，推动世界走向和平、安全、繁荣、进步的光明前景。
-# Q&amp;A环节
-**主持人**：您提到国际秩序，我开场也强调要尊重联合国宪章，但现在看到很多质疑——俄罗斯入侵乌克兰、美国总统威胁对格陵兰和巴拿马动武、巴勒斯坦人流离失所，贵国也被指责违反海洋法和《世界人权宣言》。您即将前往纽约参加安理会会议，您还相信联合国和联合国宪章吗？是否愿意推动联合国改革？这有多优先？
-**王毅**：我不愿意回答周琦先生的提问。你的提问涉及两个关键词：秩序和规则。说到秩序，这几年总有人说中国要改变秩序、另起炉灶，但现在说这种话的人可能不多了，因为真正挑战秩序、毁约退群的国家出现了，欧洲朋友们可能每天都在感受阵阵寒意。中国是在现行国际秩序中发展起来的，是受益者，我们要做的是按照大多数国家的愿望推动这个秩序朝着更加公正合理的方向发展。谈到规则，我们起码应有共同认知：共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则。只要大家都认同这一点，双重标准就没有存在空间。习近平主席提出全球发展倡议、全球安全倡议、全球文明倡议，希望国际社会携手解决发展赤字、安全赤字、治理赤字，共同构建人类命运共同体。
-**主持人**：自2022年以来，慕安会一直讨论俄罗斯入侵乌克兰。就在入侵前几天，您曾表示任何国家的主权和领土完整都应得到尊重，乌克兰也不例外。如今俄罗斯已成为中国的一个加油站——我补充一句，是带军队的加油站。您是否有可能利用自身影响力，减少从俄罗斯购买天然气、降低价格或停止部分军民两用物资，从而对俄施压以结束战争？
-**王毅**：中国同俄罗斯是两大邻国，有着漫长边界，两国关系经历过曲折后吸取教训，建立了结盟不对抗、不针对第三方的睦邻友好关系，进而建立全面战略伙伴关系。中俄交往是正常的国与国交往。如果中国不从俄罗斯买油气，哪个国家能提供如此巨量的油气满足中国民众需求？那是不可能的，也不保险，因为常有国家把经贸问题政治化、当作打压中国的工具，我们不会允许，要为人民负责任。中国在地区热点问题上有自己的立场，历来主张一切争端和冲突应通过对话寻求政治解决，武力和制裁不可能真正彻底解决问题。从2022年2月25日危机爆发第二天起，中方就提出对话协商解决。习近平主席提出4点主张：各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力都应得到支持。我们派特使斡旋，同巴西等南方国家发起和平之友。中方乐见一切致力于和平的努力，包括美国同俄罗斯达成的共识，同时认为所有当事方和利益攸关方都应适时参与和谈。战事发生在欧洲大地，欧洲更有必要发挥重要作用，共同探讨欧洲长治久安，找到均衡、有效、可持续的欧洲安全框架。
-**主持人**：时间快到了，请您简要展望中美关系将如何发展。
-**王毅****：**中国的对美政策保持连续性和稳定性，不会轻易翻烙饼，这体现大国的战略定力和国际信誉。对美政策就是习近平主席提出的三原则：相互尊重、和平共处、合作共赢。中美制度确实不一样，这是各自人民的选择，想改造或颠覆对方不切实际，正确态度是相互尊重，这是中美交往的前提；和平共处理所当然，两个大国总不能冲突起来，那将殃及整个世界，所以要开展对话、加强交往、增进了解、建立信任；合作共赢是因为国际社会期待中美合作，全球性挑战也需要中美携手应对。中方已准备好按三原则同美方构建稳定健康可持续的双边关系。我们希望美方相向而行，但如果美方仍对中国打压遏制，我们别无选择，必将奉陪到底，坚决维护中国的主权、国家尊严和正当发展权利，坚决回击美方的单边霸凌行径。中国人从来不信邪、不怕鬼，天行健，君子以自强不息；他强任他强，清风拂山岗；他横任他横，明月照大江。总之我们对世界前途和中美关系未来充满信心，中美只有一个共同努力方向，即相互尊重、和平共处、合作共赢。</t>
+          <t># 王毅慕安会演讲阐述多极化主张
+## 发布会概况
+王毅在慕尼黑安全会议上发表演讲，以今年慕安会报告主题“走向多极化”为切入点，阐述中国推动平等有序的世界多极化的主张。演讲围绕四点看法展开：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。王毅强调中国必将是多极体系中的确定性因素，坚定做变革世界中的建设性力量。关键数字锚点包括：联合国会员国从80年前的51个增至193个、中国承担超过20%的联合国会费、去年中国GDP增长5%且对世界经济增长贡献率接近30%。问答环节涉及国际秩序与规则、乌克兰危机、中美关系等议题，王毅会后将前往纽约出席联合国安理会会议。
+## 核心信息
+### 多极化世界与中国主张
+1. **世界走向多极化**：80年前联合国成立时只有51个会员国，今天已有193个国家；多极化的世界既是历史必然，也正在成为现实。中国主张推动**平等有序的世界多极化**，这是习近平主席提出的重大主张，中国必将是多极体系中的确定性因素。
+2. **四点看法**：一是倡导平等相待，坚持权利平等、机会平等、规则平等，主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权；二是尊重国际法治，坚定维护国际法治权威，中国加入了几乎所有普遍性的政府间国际组织和**600多项国际公约**；三是践行多边主义，坚持真正的多边主义，倡导共商共建共享的全球治理观，中国承担着**超过20%的联合国会费**；四是坚持开放共赢，以普惠包容的经济全球化支撑平等有序的世界多极化。
+### 国际秩序与规则
+1. **中国与国际秩序**：中国是在现行国际秩序中发展起来的，是这一秩序的受益者；要推动秩序朝着更加公正合理的方向发展。中国主张共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则。
+2. **国际法治立场**：在遵守国际法上不能搞双重标准；要尊重各国主权和领土完整，就应该支持中国实现完全统一。中国从不搞例外主义，更不搞合则用、不合则弃。
+### 多边主义与全球治理
+1. **联合国与全球治理**：联合国是践行多边主义、推进全球治理的核心平台，已为各国遮风挡雨80年；未来的多极世界更加需要联合国，应当固本强基而非拆梁毁柱。
+2. **中国贡献**：中国切实履行《巴黎协定》，建成了世界上最大的清洁发电体系；提出并落实全球发展倡议、全球安全倡议、全球文明倡议，为完善全球治理提供公共产品。
+### 开放共赢与中欧关系
+1. **中国经济发展**：去年中国GDP增长5%，对世界经济增长的贡献率接近30%；中国向世界释放超大规模的市场红利，愿推动高质量共建“一带一路”，同欧盟的“全球门户”战略相互对接。
+2. **中欧关系**：欧洲是多极世界的重要一极，中欧双方是伙伴而不是对手；今年是中欧建交50周年，中方愿同欧方深化战略沟通和互利合作。
+## 官方表态
+### 多极化主张
+1. **推动平等有序的世界多极化**：世界正走向多极化，80年前联合国成立时只有51个会员国，今天是193个国家。中国主张推动平等有序的世界多极化，这是习近平主席提出的重大主张，中国必将是多极体系中的确定性因素，坚定做变革世界中的建设性力量。
+2. **四点看法**：一是倡导平等相待，坚持权利平等、机会平等、规则平等，主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权；二是尊重国际法治，联合国宪章宗旨和原则是国际关系的根本遵循，国家不论大小强弱都是国际法治的利益攸关方；三是践行多边主义，联合国是践行多边主义、推进全球治理的核心平台，应固本强基而非拆梁毁柱；四是坚持开放共赢，发展是破解各种难题的钥匙，保护主义不是出路，滥加关税没有赢家。
+### 国际法治
+1. **维护国际法治权威**：中国加入了几乎所有普遍性的政府间国际组织和600多项国际公约，从不搞例外主义，更不搞合则用、不合则弃，为不确定的世界提供最大的确定性。
+2. **反对双重标准**：在遵守国际法上不能搞双重标准，要尊重各国的主权和领土完整，就应该支持中国实现完全统一。
+### 多边主义
+1. **坚持真正的多边主义**：倡导共商共建共享的全球治理观，坚定维护联合国的权威和地位，承担超过20%的联合国会费，切实履行巴黎协定，建成世界上最大的清洁发电体系。
+2. **提供全球治理公共产品**：提出并落实全球发展倡议、全球安全倡议、全球文明倡议，为完善全球治理提供公共产品。
+### 开放共赢
+1. **共享发展机遇**：去年中国GDP增长5%，对世界经济增长的贡献率接近30%，担当全球经济增长的重要引擎，向世界释放超大规模的市场红利。
+2. **推动互联互通**：愿推动高质量共建“一带一路”，同欧盟的“全球门户”战略相互对接，赋能彼此也赋能世界。
+### 中欧关系
+1. **中欧是伙伴而非对手**：欧洲是多极世界的重要一极，今年是中欧建交50周年，中方愿同欧方用好这一契机，深化战略沟通和互利合作，推动世界走向和平、安全、繁荣、进步的光明前景。
+## Q&amp;A环节
+### Q1. 国际秩序与联合国宪章
+- **主持人**：您提到国际秩序，我开场也强调要尊重联合国宪章，但如今我们看到俄罗斯入侵乌克兰、美国总统威胁对格陵兰和巴拿马动武、巴勒斯坦人流离失所，中国也被指责违反海洋法和《世界人权宣言》。您即将前往纽约参加安理会会议，您还相信联合国和联合国宪章吗？是否推动联合国改革？
+&gt; **王毅**：你的提问涉及秩序和规则两个关键词。关于秩序，这几年有人说中国要改变秩序、另起炉灶，但现在真正挑战秩序、毁约退群的国家出现了。中国是在现行国际秩序中发展起来的，是受益者，我们要按大多数国家愿望推动秩序朝更加公正合理方向发展。关于规则，我们需要共同维护以联合国为核心的国际体系，遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大公约数。只要认同这一点，双重标准就没有存在空间。习近平主席提出全球发展倡议、全球安全倡议、全球文明倡议和构建人类命运共同体理念，希望各国超越历史文化社会制度意识形态不同，同舟共济，共同建设命运与共的地球村。
+### Q2. 乌克兰危机与对俄立场
+- **主持人**：2022年慕安会前几天您曾表示任何国家的主权、独立和领土完整都应得到尊重，乌克兰也不例外。如今俄罗斯已成为约翰·麦凯恩所说的“中国的加油站”，中国对乌克兰有很大影响力。在各方加大压力推动结束战争之际，中国能否减少购买俄罗斯油气、降低价格或停止输送军民两用物资，以加大对俄施压？
+&gt; **王毅**：中国同俄罗斯是两大邻国，有着漫长边界。两国吸取教训，建立了不结盟、不对抗、不针对第三方的睦邻友好关系，进而建立全面战略伙伴关系，这是正常的国与国交往。如果中国不从俄罗斯买油气，哪个国家能提供如此巨量油气满足中国民众需求？那不可能也不保险，因为常有国家把经贸问题政治化、当作打压中国的工具，我们不会允许，要为人民负责。中国在地区热点问题上有自己的立场，历来主张一切争端和冲突应通过对话寻求政治解决，武力和制裁不可能真正彻底解决问题。从2022年2月25日危机爆发第2天起，中方就提出对话协商解决。习近平主席提出4点主张：各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力都应得到支持。我们派特使斡旋，同巴西等南方国家发起“和平之友”。任何冲突的终点都是谈判桌，中方乐见一切和平努力，包括美俄达成的共识，同时认为所有当事方和利益攸关方应适时参与和谈。这场战事发生在欧洲，欧洲更有必要发挥重要作用，共同探讨欧洲长治久安，找到均衡、有效、可持续的欧洲安全框架。
+### Q3. 中美关系展望
+- **主持人**：时间所剩不多，能否简要预告您对中美关系将如何发展的看法？
+&gt; **王毅**：中国的对美政策保持连续性和稳定性，不会轻易翻烙饼，这体现大国的战略定力和国际信誉。我们的对美政策就是习近平主席提出的三原则：相互尊重、和平共处、合作共赢。中美制度不同是各自人民的选择，想改造或颠覆对方不切实际，正确态度是相互尊重，这是中美交往的前提；和平共处理所当然，中美两个大国总不能冲突起来，那将殃及整个世界，所以要开展对话、加强交往、增进了解、建立信任；合作共赢是因为国际社会期待中美合作，全球性挑战也需要中美携手应对。中方已准备好按三原则同美方构建稳定健康可持续的双边关系。我们希望美方相向而行，但如果美方仍要打压遏制中国，我们别无选择，必将奉陪到底，坚决维护中国的主权、国家尊严和正当发展权利，坚决回击美方的单边霸凌行径。中国人从来不信邪、不怕鬼，新中国就是在战胜各种艰难险阻中发展壮大起来的。我们对世界前途和中美关系未来都充满信心，中美只有一个共同努力方向，就是相互尊重、和平共处、合作共赢。</t>
         </is>
       </c>
       <c r="D2" s="10" t="n">
-        <v>43.6</v>
+        <v>40.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7004/3762</t>
+          <t>7004/3648</t>
         </is>
       </c>
     </row>
@@ -774,84 +780,103 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t># 沟通背景与目的
-本次沟通为电子科技大学电子科学与工程学院面向考生及家长的招生宣讲直播，由学院多位教师及学生代表参与。沟通旨在系统介绍学院整体情况、各学科方向的研究内容与成果、人才培养成效，以吸引优秀生源报考。整体基调为积极推介，各方向负责人依次介绍学科实力与科研平台，学生代表从个人视角分享择校理由与建议，并设有互动答疑环节。沟通末尾，学院回应了考生关心的夏令营问题，并公布了咨询渠道。
-# 核心信息与数据
-## 学院整体情况
-- **历史沿革**：电子科技大学建校之初1956年成立无线电系、电真空器件系、无线电零件系，经1979年、1992年、2001年、2018年4次院系调整成立电子科学与工程学院，2023年响应国家号召成立电子科学与工程学院与基层电路学院（原文如此）。
-- **学科设置**：电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向，另有电磁场与微波、军用关键材料、电子元器件3个国防特色学科。
-- **人才培养规模**：本科生现有1545人，招生专业为工科试验班（电子工程类），含电子科学技术（国家特色专业、国家级一流本科专业建设点）与电磁场与无线技术两个专业方向；硕士和博士研究生1975人。
-- **研究生招生专业**：学硕、博士为电子科学与技术，硕士含材料科学与工程；专业学位博士为电子信息，硕士含电子信息、材料工程。
-- **师资队伍**：现有教师302人，其中教研系139人、科研系95人、教学系14人、实验系21人、机关33人；含两院院士2人、领军人才19人、青年人才28人、其他类型人才12人、博士后61人。
-- **科研经费与成果**：近5年科研经费到账稳定在3—4亿元之间，项目以纵向为主、横向为辅；牵头获国家科技奖励11项，近5年发表高水平学术论文2000余篇，专利申请1600余件、授权1300余件。
-- **科研团队与平台**：共有20个科研团队，年度经费过千万元的团队15个、过亿元团队1个；拥有国家电子辐射控制材料工程技术研究中心、微波电子工器件国家级重点实验室两个国家级平台，4个国际合作平台、7个省部级科研平台。
-- **国际交流**：共建国际姊妹院系两个——香港大学电机工程电子系、香港城市大学电子工程系；主办高水平国际会议13场，学生长短期交流项目20多个。
-## 电子信息材料与元器件方向
-- **方向定位**：以电子在物质中的输运特性（电磁声光热力及化学生物类比特性）及外部作用为基础，设计研究和生产电子器件，以材料为基础、器件为核心、应用为目标导向，覆盖材料、器件、电路的设计研制生产和应用。
-- **产业背景**：2021年中国集成电路电子产品进口额度达2.8万亿元，约为原有进口量的1.7倍；先进电子材料、元器件、电路系统等电子产品是我国目前最为紧迫的卡脖子问题之一。
-- **应用领域**：电子产品在6G通讯、量子技术、智慧城市、光电技术、新能源、智能电子等领域起重要作用，已广泛应用于物联网、移动设备、网络基础设施、无人驾驶、航空航天、医疗健康和可穿戴设备等领域，达到万亿美元量级。
-- **发展趋势**：电子产品向小型化、多功能、低功耗、智能化方向发展，元器件朝微型化、片式化、集成化、薄膜化、智能化方向演进，强调材料和器件一体化；集成技术将摩尔定律制程缩小与超摩尔定律功能多样化两种方式结合。
-- **邓龙江院士团队**：电磁辐射控制材料与技术团队现有研究人员19人，其中正高13人、副高15人；近年发表包括《自然》在内的论文300余篇，承担国家省部级及国际合作课题130余项，年均到账经费3000多万元，授权发明专利100余项，获国家科技进步或技术发明二等奖共计3项。
-- **张怀武教授团队**：磁电薄膜与微型器件团队现有研究人员17人，其中正高15人、副高2人；开展LTCC材料及集成技术、微波毫米波晶圆及器件、自旋电子与磁量子器件、传感器芯片等研究，承担国家重点研发计划、自然基金重点重大科学仪器项目及国际合作等项目100余项，发表SCI论文400余篇，年均到账经费2000余万元，获科技进步二等奖共计3项。
-- **国家级平台一**：国家电磁辐射控制材料工程技术研究中心，历史可追溯至1990年校级材料与技术研究中心，经2008年、2013年两次升级形成，主要开展多频谱涂层、电磁材料与结构、智能材料与结构研究，拥有成都嘉驰电子科技等成果转化基地。
-- **国家级平台二**：电磁薄膜与集成器件全国重点实验室，2006年依托新型传感器、功率半导体技术、电子信息材料三个部级重点实验室筹建，围绕电子信息系统微小型化和单片集成需求开展研究，形成电子聚合物与阵列传感器、功率半导体与集成技术三个重点方向。
-- **研究条件**：科研面积2万余平米，其中超精尖3000平；建设两条国家重大任务试验生产线，拥有大型设备或系统500余台套；材料制备设备约50余台套，微纳加工设备30台套，微观表征设备约10余台套，材料性能测试设备50余台套。
-- **毕业生去向**：遍布产业界与学术界，包括英特尔、中芯国际、华为、德州仪器及高校和科研院所，在前沿基础研究、军工项目研发、产品技术开发等方向做出重要贡献。
-- **学生代表成果**：在读学生杨伟豪以第一作者在《自然·电子》《自然·通讯》各发表一篇学术论文；5G滤波器芯片学生团队获挑战杯创新创业大赛四川省金奖；毕业生黄飞获斯坦福攻读博士全额奖学金；李凤霞读博期间发表学术论文16篇、一作6篇；严巍获21届王大珩光学奖，博士毕业后以优秀青年学者身份加入苏州大学；毕业生万位任河北美泰电子科技公司副总，带领团队采用MEMS工艺研制出SIW环形器隔离器，突破卡脖子器件核心技术。
-## 电磁场与微波技术、电路与系统方向
-- **专业构成**：电磁场与微波技术包含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向；电路与系统包含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向，共同组建射频电子系统全方位专业覆盖。
-- **学科沿革**：电磁场与微波技术学科始于1956年建校时期，由林卫干先生和谢楚芳先生共同创建；形成电磁场与无线技术国家特色专业及电波传播与天线国防紧缺特色专业两个方向，所属一级学科电子科学与技术入选双一流A类学科。
-- **研究团队**：电磁场与微波技术有6个团队——电磁辐射与散射团队、毫米波技术与系统应用团队、微波毫米波集成电路与系统团队、电磁兼容技术团队、微波测试与成像技术团队、无线技术与集成系统团队。
-- **学科平台**：包含国家自然基金委创新群体、国家高等学校学科创新引智基地、国家工程技术研究中心及国家级重点实验室；硬件方面拥有中国高校最为先进的微波暗室群体及先进的微波毫米波太赫兹仿真测试平台。
-- **天线方向成果**：杨世文教授团队研究四维天线阵列技术，为天线阵列设计提供新自由度，实现低成本高性能，相关应用成果应用于中电14所某大型机载相控阵雷达；该团队还在强耦合超宽带相控阵方面取得系列进展。
-- **微波毫米波方向成果**：樊勇教授团队研究毫米波平面集成天线，可广泛应用于毫米波通信雷达系统领域；延波教授团队引领微波毫米波太赫兹芯片研究，收获国家科技重大专项及军科委相关应用，应用于新一代高速通信系统。
-- **微波毫米波器件与系统**：延波教授团队取得固态合成功率源、天线阵列、馈电网络等电路与通信雷达系统成果，包含三毫米导引头前端、毫米波引信前端、8毫米宽带收发前端。
-- **计算电磁学与太赫兹**：杨世文教授团队计算电磁学相关算法被评为20世纪十大算法之一；樊勇教授团队成功研制0.22THz、0.34THz、0.42THz雷达成像系统，实验平台分辨率小于1厘米，太赫兹通信成果在2023年成都大运会田径项目成功示范应用。
-- **电磁测量与生物医学**：李恩教授团队引领微波毫米波测量技术，有60多年技术积累和传承；杨世文教授团队在电磁测井仪器方面获国家科技进步二等奖一项，成果在中海油成功推广应用；李恩教授团队在生物医学电磁学及成像方向发表大量高水平论文，有20余项国家发明专利。
-- **电路与系统学科沿革**：1981年开始招收研究生和博士研究生，1988年成立首批博士后流动站；学科包含教育部国际合作联合实验室及国家高等学校学科创新引智基地，拥有国家级人才4人、新世纪人才2人、教授10人、副教授22人。
-- **电路与系统研究成果**：樊勇教授和李廷军教授团队从事高速磁浮交通38GHz车地通信系统研制；樊勇教授和张静直（即张教授本人）团队从事毫米波通信雷达CMOS芯片研究；康凯教授团队在毫米波CMOS芯片方向取得超宽带模块级芯片及5G通信系统、雷达系统研制成果。
-- **人才培养成果**：连续三年获全国大学生集成电路创新创业大赛奖项，荣获华为优秀合作项目奖、研究生优秀导学团队提名奖；学生获互联网+奖项、国际HPV各类奖项及优秀论文、创新创业大赛成果奖项。
-- **就业情况**：就业领域分布广泛，包括华为、中兴等行业领军企业及各研究所、高校，毕业生在海外留学方面也取得不少突破。
-## 物理电子学方向
-- **学科定义**：物理电子学是物理学与电子科学技术的交叉学科，将物理学最新研究成果应用于电子学中产生新电子器件；典型包括微波与电子相互作用形成的微波电子学（产生微波电真空器件）、光与电子相互作用形成的光电子学（产生光电器件）。
-- **学科特点**：内容不断充实，如量子电子学内容逐渐增加；学科边界不一定清晰，如光电子学既可属物理电子学也可属光学工程一级学科；具有基础性与前沿性，是支撑现代信息技术的关键技术学科。
-- **学校发展历程**：起源于1956年建校时在前苏联专家帮助下成立的电子控器件专业（原文如此），归属电子器件系；1979年在刘成刚院士带领下成立高能电子学研究所；2001年物理系、应用所、高能所成立物理电子学；2018年物理电子学院、电工学院和微工学院部分成立现在的电子科学与工程学院。
-- **纵向发展**：上游为仿真设计、数字模拟、材料，具有自主知识产权的商用软件为MMST和切皮克（原文如此），并引入人工智能到器件设计和电子学应用；下游为系统应用，包括用回旋行波管研制毫米波雷达、用行波管做无线输能系统、用磁控管做微波能干燥系统。
-- **横向拓展**：频段从微波上移至毫米波到太赫兹；与医学交叉，利用太赫兹成像分辨率高、透视效果好的特点做医学诊断，提高诊断准确性；利用太赫兹宽频带特点做保密通信和高速通信。
-- **科研实力**：每年到校科研经费接近2亿元，在学院内最多；是国际上最大的真空器件研究中心；2023年成功举办行业顶级会议；拥有3个四川省工程中心或重点实验室；物理电子学方向共有9个团队。
-- **学生出口**：团队学生约1/3硕博连读、1/3去企业、1/3去研究所或其他（公务员等）；李天明教授个人每年基本两个研究生毕业、一个博士毕业。
-## 学生视角分享
-- **城市优势**：电子科技大学位于成都——四川省会、国家中心城市、新一线城市、国家历史文化名城、古蜀文明发祥地、中国十大古都之一；成都站在国内电子信息朝阳产业发展前端，从英特尔、华为到京东方等众多行业巨头汇聚，提供实践平台和就业资源。
-- **学校优势**：学校有电子信息博物馆，记录我国第一台晶体管收音机的诞生；从电子科学与技术、信息与通信工程到集成电路科学与技术，构建了最完整的电子信息学科群，是中国民族电子工业人才的摇篮。
-- **学科实力**：学院电子科学与技术学科在第4轮学科评估中斩获A+，稳居全国第一；学院拥有四大学科和19个科研团队。
-- **团队情况**：田雨桐所在毫米波技术与系统应用团队，负责人为樊勇老师，围绕微波毫米波理论与技术、天线理论与技术、元器件与电路、通信技术与系统、雷达成像技术与系统五大方向开展研究，覆盖电磁场与微波技术、电路与系统，可学到从芯片、封装、天线、电路模块到系统的全面知识。
+          <t># 电子科学与工程学院招生宣讲直播
+## 沟通背景与目的
+本次直播由电子科技大学电子科学与工程学院面向考生和家长举办，主持人串场，段院、柳教授、张教授、李天明教授分别介绍学院整体情况与四个学科方向，在读博士田雨桐分享择校择专业体验。沟通目的是帮助考生和家长了解学院历史沿革、学科设置、师资队伍、科研平台及人才培养成果，吸引报考。整体基调为推介与答疑，最后解答夏令营安排问题并抽奖，夏令营时间待定。
+## 核心信息与数据
+### 学院整体情况
+- **学院历史**：1956年建校时成立无线电系、电真空器件系、无线电零件系，经1979年、1992年、2001年、2018年4次院系调整成立电子科学与工程学院、科普示范性微电子学院，2023年成立电子科学与工程学院与基层电路学院（原文如此）。
+- **学科设置**：电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向，另有电磁场与微波军用关键材料、电子元器件等3个国防特色学科。
+- **党建荣誉**：学校党委入选教育部首批全国党建工作标杆院系，学院荣获全国教育系统先进集体。
+- **本科生培养**：现有本科生1545人，招生专业为工科试验班（电子工程类），含电子科学技术（国家特色专业、国家级一流本科专业建设点）与电磁场与无线技术两个专业方向。
+- **研究生培养**：现有硕士和博士研究生1975人，学硕、博士招生专业为电子科学与技术，硕士另含材料科学与工程，专业学位博士为电子信息，硕士为电子信息、材料工程。
+- **师资队伍**：现有教师302人，其中教研系139人、科研系95人、教学系14人、实验系21人，教师总数269人，机关33人。
+- **高层次人才**：两院院士2人，领军人才19人，青年人才28人，其他类型人才12人，后续61人（原文如此）。
+- **教师团队**：拥有两个全国高校黄大年式教师团队，2022年获批4个国家自然科学基金创新群体。
+- **科研经费**：近5年科研经费到账稳定在3—4亿元之间，项目构成以纵向项目为主、横向项目为辅。
+- **科研成果**：牵头获得国家科技奖励11项，近5年发表高水平学术论文2000余篇，专利申请1600余件、授权1300余件。
+- **科研团队**：共有20个科研团队，年度经费过千万元的团队15个，其中过亿元团队1个。
+- **科研平台**：拥有国家电子辐射控制材料工程技术研究中心、微波电子器件国家级重点实验室2个国家级平台，4个国际合作平台，7个省部级科研平台。
+- **国际交流**：共建国际姊妹院系2个（香港大学电机工程电子系、香港城市大学电子工程系），主办高水平国际会议13场，学生长短期交流项目20多个。
+### 电子信息材料与元器件方向
+- **方向内涵**：以电子在物质中的输运特性（含电磁声光热力及化学生物类比特性）及外部作用为基础，设计研究和生产电子器件，以材料为基础、器件为核心、应用为目标导向。
+- **产业背景**：2021年中国集成电路电子产品进口额达2.8万亿元，约为原油进口量的1.7倍；先进电子材料元器件电路系统等电子产品是我国目前最为紧迫的卡脖子问题之一。
+- **应用领域**：在6G通讯、量子技术、智慧城市、光电技术、新能源、智能电子等领域起重要作用，已广泛应用于物联网、移动设备、网络基础设施、无人驾驶、航空航天、医疗健康和可穿戴设备等领域，达到万亿美元量级。
+- **发展趋势**：电子产品向小型化、多功能、低功耗、智能化方向发展，元器件向微型化、片式化、集成化、薄膜化、智能化方向发展，强调材料和器件一体化。
+- **邓龙江院士团队**：电磁辐射控制材料与技术团队，现有研究人员19人（正高13人、副高15人），近年发表包括《自然》在内的论文300余篇，承担国家省部级及国际合作课题130余项，年均到账经费3000多万元，授权发明专利100余项，获国家科技进步或技术发明二等奖共计3项。
+- **张怀武教授团队**：磁电薄膜与微型器件团队，现有研究人员17人（正高15人、副高2人），开展LTCC材料及集成技术、微波毫米波晶圆及器件、自旋电子与磁量子器件、传感器芯片等研究，承担国家重点研发计划、自然基金重点重大科学仪器项目、国际合作等项目100余项，发表SCI论文400余篇，年均到账经费2000余万元，获科技进步二等奖共计3项。
+- **国家电磁辐射控制材料工程技术研究中心**：历史可追溯至1990年校级材料与技术研究中心，经2008年、2013年两次升级形成国家级平台，开展多频谱涂层、电磁材料与结构、智能材料与结构研究，拥有成都嘉驰电子科技等成果转化基地。
+- **电磁薄膜与集成器件全国重点实验室**：2006年依托新型传感器、功率半导体技术、电子信息材料3个部级重点实验室筹建，围绕电子信息系统微小型化和单片集成的重大需求开展研究，形成电子聚合物与阵列传感器、功率半导体与集成技术三个重点方向。
+- **研究条件**：科研面积2万余平米（超精尖3000平），建设两条国家重大任务试验生产线，大型设备或系统500余台套；材料制备设备约50台套，微纳加工设备30台套，微观表征设备10余台套，性能测试设备50余台套。
+- **毕业生去向**：遍布产业界与学术界，包括英特尔、中芯国际、华为、德州仪器及高校科研院所，在前沿基础研究、军工项目研发、产品技术开发等方向做出贡献。
+- **学生成果举例**：在读学生杨伟豪以第一作者在《自然·电子》《自然·通讯》各发表一篇论文；5G滤波器芯片学生团队获挑战杯创新创业大赛四川省金奖；黄飞获斯坦福大学攻读博士全额奖学金；李凤霞读博期间发表学术论文16篇（一作6篇）；严巍获王大珩光学奖后以优秀青年学者身份加入苏州大学；毕业生万位任河北美泰电子科技公司副总，采用MEMS工艺研制出SIW环形器隔离器，突破卡脖子器件核心技术。
+### 电磁场与微波技术、电路与系统方向
+- **专业构成**：电磁场与微波技术包含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向；电路与系统包含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向。
+- **学科历史**：电磁场与微波技术学科始于1956年建校时期，由林卫干先生和谢楚芳先生创建，形成电磁场与无线技术国家特色专业及电波传播与天线国防紧缺特色专业，所属一级学科电子科学与技术入选双一流A类学科。
+- **研究团队**：电磁场与微波技术有6个团队，分别为电磁辐射与散射团队、毫米波技术与系统应用团队、微波毫米波集成电路与系统团队、电磁兼容技术团队、微波测试与成像技术团队、无线技术与集成系统团队。
+- **学科平台**：含国家自然基金委创新群体、国家高等学校学科创新引智基地、国家工程技术研究中心、国家级重点实验室；硬件上拥有中国高校最为先进的微波暗室群体及微波毫米波太赫兹仿真测试平台。
+- **天线方向成果**：杨世文教授团队研究四维天线阵列技术，为天线阵列设计提供新自由度，实现低成本高性能；强耦合超宽带相控阵成果应用于中电14所某大型机载相控阵雷达。
+- **毫米波方向成果**：樊勇教授团队研究毫米波平面集成天线，应用于毫米波通信雷达系统领域；李恩教授团队引领的微波毫米波测量技术突破众多技术封锁，有60多年技术积累。
+- **电磁测井成果**：杨世文教授团队在电磁测井仪器方面获国家科技进步二等奖1项，成果在中海油成功推广应用。
+- **微波毫米波电路成果**：延波教授团队引领微波毫米波太赫兹芯片研究，获国家科技重大专项及军科委项目支持，应用于新一代高速通信系统；在固态合成功率源、天线阵列、扩电网络等电路与通信雷达系统方面取得成果。
+- **微系统技术成果**：延波教授团队在微波毫米波微系统技术方面取得进展，包含三毫米导引头前端、毫米波引信前端、8毫米宽带收发前端。
+- **计算电磁学成果**：杨世文教授团队引领的计算电磁学相关算法被评为20世纪十大算法之一。
+- **太赫兹成像成果**：樊勇教授团队成功研制0.22THz、0.34THz、0.42THz雷达成像系统，实验平台分辨率小于1厘米。
+- **太赫兹通信成果**：樊勇教授团队在太赫兹通信技术方面取得突破，成果于2023年成都大运会田径项目中成功示范应用。
+- **电磁波应用成果**：李恩教授团队面向5G通信、高性能系统、生物医学、新能源等方向提供电磁波与物质互作用机理及测评系统研究，在生物医学电磁学及成像方向发表大量高水平论文，获20余项国家发明专利。
+- **电路与系统学科沿革**：1981年开始招收研究生和博士研究生，1988年成立首批博士后流动站，学科含教育部国际合作联合实验室、国家高等学校学科创新引智基地，拥有国家级人才4人、新世纪人才2人、教授10人、副教授22人。
+- **高速车地通信成果**：樊勇教授和李廷军教授团队从事高速磁浮交通38GHz车地通信系统研制，可实现安全可靠实时宽带通信，确保列车安全运行。
+- **毫米波CMOS芯片成果**：樊勇教授和张静（即本人）团队面向通讯雷达领域探索集成电路设计新架构；康凯教授团队在毫米波CMOS芯片方向取得超宽带模块级芯片及5G通信系统、雷达系统研制成果。
+- **人才培养成果**：连续三年获全国大学生集成电路创新创业大赛奖项，荣获华为优秀合作项目奖、研究生优秀导学团队提名奖，学生获互联网+奖项、国际HPV奖项及优秀论文、创新创业大赛奖项。
+- **就业情况**：就业领域分布广泛，包括华为、中兴等行业领军企业及各大研究所、高校，毕业生在海外留学方面也取得突破。
+### 物理电子学方向
+- **学科定义**：物理电子学是物理学与电子科学与技术的交叉学科，将物理学最新研究成果应用于电子学中产生新电子器件，典型如微波与电子相互作用形成微波电子学（产生微波电真空器件）、光与电子相互作用形成光电子学（产生光电器件）。
+- **学科特点**：内容不断充实（如量子电子学内容逐渐增加）；学科边界不一定清晰，如光电子学既可属物理电子学也可属光学工程一级学科；具有基础性与前沿性，是支撑现代信息技术的关键技术学科。
+- **学校学科沿革**：起源于1956年建校时在前苏联专家帮助下成立的电真空器件专业，归宿于电子器件系；1979年在刘成刚院士带领下成立高能电子学研究所；2001年物理系、应用所、高能所成立物理电子学；2018年物理电子学院、电工学院和微工学院部分成立现在的电子科学与工程学院。
+- **纵向发展**：上游为仿真设计、数字模拟材料，下游为系统应用；拥有自主知识产权的商用软件MMST和切皮克（国内广泛应用的算法软件），并将人工智能引入器件设计和电子学应用。
+- **系统应用成果**：利用大功率器件研制毫米波雷达（用回旋行波管）、无线输能系统（用行波管）、微波能干燥系统（用磁控管）。
+- **横向发展**：频段从微波上移至毫米波到太赫兹；与医学交叉，利用太赫兹分辨率高、透视效果好的特点做太赫兹成像，利用光电融合方式做太赫兹源，利用太赫兹宽频带特点做保密通信和高速通信。
+- **医学应用**：利用太赫兹成像应用到医学诊断，提高诊断准确性。
+- **科研平台与经费**：有3个四川省工程中心或重点实验室，参与成立一系列行业协会；每年到校科研经费接近2亿元，在学院内最多；是国际上最大的真空器件研究中心。
+- **学术活动**：2023年成功举办行业顶级会议。
+- **研究团队**：物理电子学方向共有9个团队。
+- **学生出口**：团队学生约1/3硕博连读、1/3去企业、1/3去研究所或其他（公务员等）；李天明教授个人每年约2个研究生毕业、1个博士毕业。
+### 学生视角分享
+- **选择城市**：成都是四川省会、国家中心城市、新一线城市、国家历史文化名城、古蜀文明发祥地、中国十大古都之一；电子信息是朝阳行业，成都站在国内产业发展前端，英特尔、华为、京东方等众多行业巨头汇聚，提供实践平台和就业资源。
+- **选择学校**：电子科技大学是我国电子信息人才培育的代名词，学校有电子信息博物馆记录我国第一台晶体管收音机的诞生，从电子科学与技术、信息与通信工程到集成电路科学与技术构建了最完整的电子信息学科群。
+- **选择专业**：学院电子科学与技术学科在第4轮学科评估中斩获A+，稳居全国第一；从电磁场与微波技术到微电子与固体电子学，五大国防特色学科构建了深厚学科底蕴。
+- **选择团队**：田雨桐所在团队为毫米波技术与系统应用团队，负责人樊勇老师，围绕微波毫米波理论与技术、天线理论与技术、元器件与电路、通信技术与系统、雷达成像技术与系统五大方向开展研究，覆盖从芯片、封装、天线、电路、模块到系统的全面知识。
 - **就业情况**：团队硕博毕业生实现100%就业率，就业单位有各类民营企业、大型央国企和头部科研院所。
-- **奖助体系**：学院构建全覆盖、高额度、长周期的奖助体系，包括国家奖学金、学业奖学金、专项奖学金、新生奖学金及学校学院设立的其他奖学金，奖助方面有校园地国家助学贷款和生源地助学贷款。
-- **择校建议**：先根据研究方向选择合适研究团队，再选择研究生导师；可通过学院网站按兴趣选择团队，借助IEEE和中国知网等文献检索网站检索导师论文情况和指导研究生毕业情况，结合兴趣广泛调研，提前沟通交流。
-# 各方立场与诉求
-- **主持人**：关注夏令营是否有具体时间与形式，向段院提出咨询。
-- **段院**：回应称电子学院计划今年举办夏令营活动，但时间待定；建议感兴趣的同学加入学院QQ群，相关信息将及时发布。
-- **主持人**：补充公布学院QQ群号978499108，供考生和家长扫码加入进行详细咨询。
-- **考生及家长**：通过弹幕区提出夏令营相关问题，并参与直播抽奖互动；主持人表示结束后会抽取有代表性的问题由老师和同学解答。
-# 达成共识
-- **夏令营安排**：电子学院计划今年举办夏令营活动，**具体时间与形式待定**，相关信息将通过学院QQ群及时发布。
-- **招生咨询渠道**：学院QQ群号确定为 **978499108**，供考生和家长进群咨询。
-- **直播抽奖**：本场直播抽奖口令为「一生一世，逐梦未来」，中奖同学需私信后台留下联系方式和收货地址，奖品为学校定制马克杯一套。
-# 待协调事项与后续
-## 待协调事项
-- **夏令营活动**：电子学院计划今年举办，具体时间与形式待定，相关信息将通过学院QQ群发布
-## 后续安排与参与方式
-- **学院咨询QQ群**：978499108，考生可扫码或搜索群号加入，进行详细咨询与了解
-- **夏令营信息发布**：时间确定后将在QQ群内及时发布，请关注群通知
-- **直播抽奖奖品**：电子科技大学定制马克杯一套（含勺子和杯盖，印有学校logo），中奖同学需私信后台留下联系方式和收货地址，奖品将派送上门</t>
+- **校园体验**：2021年跨年学校在主楼前用300架无人机拼出电子科大英文简称UESTC字样。
+- **奖助体系**：学院构建全覆盖、高额度、长周期的奖助体系，奖学金含国家奖学金、学业奖学金、专项奖学金、新生奖学金及学校学院设立的其他奖学金，另有校园地国家助学贷款和生源地助学贷款。
+- **择校建议**：先根据研究方向选择合适研究团队，再选择导师；学院拥有四大学科和19个科研团队，可从学院网站按兴趣选择团队，再进入团队网页找导师；可通过IEEE和中国知网等文献检索网站检索导师论文和指导研究生毕业情况。
+## 各方立场与诉求
+1. **考生及家长**：关注学院夏令营的具体时间与形式，通过弹幕区提出咨询；对学院整体情况、四个学科方向、师资力量、科研平台及学生就业去向表现出兴趣，并参与抽奖互动。
+2. **主持人（发言者1）**：负责串场与引导，向段院提出考生家长关心的夏令营问题；介绍学院分享嘉宾，组织抽奖环节并公布获奖名单；提醒考生家长可扫码加入QQ群咨询。
+3. **段院（学院领导）**：回应夏令营问题，表示学院计划今年举办夏令营活动但时间待定，建议感兴趣的同学加入QQ群，相关信息将及时发布；介绍学院历史沿革、学科设置、师资队伍、科研平台及人才培养成果，面向考生和家长宣介学院优势。
+4. **柳教授**：介绍电子信息材料与元器件方向的内涵、重要性、研究团队、平台及成果，强调该方向是解决国家卡脖子问题的关键领域，面向考生和家长展示科研实力与毕业生去向。
+5. **张教授**：介绍电磁场与微波技术、电路与系统两个学科方向的研究内容、团队、成果及人才培养情况，面向考生和家长展示学科实力与就业前景。
+6. **李天明教授**：介绍物理电子学方向的学科定义、学校发展历程、科研经费及成果，面向考生和家长展示该方向的科研实力与团队学生出口情况。
+7. **田雨桐（在读博士）**：从学生视角分享选择电子科大的理由、择校择专业建议，介绍所在团队情况与就业率，面向考生和家长提供参考。
+## 达成共识
+1. **夏令营活动安排**：学院计划今年举办夏令营活动，具体时间与形式待定，相关信息将通过咨询QQ群及时发布。
+2. **咨询渠道确认**：学院公布招生咨询QQ群号978499108，考生和家长可通过该群获取后续夏令营及招生相关信息。
+3. **直播互动承诺**：主持人确认将抽取弹幕区幸运观众赠送学校特色马克杯套装，中奖观众需通过私信后台留下联系方式与收货地址，礼物将派送至家门口。
+## 待协调事项与后续
+### 待协调事项
+- [ ] **夏令营活动时间与形式**（电子科学与工程学院 ｜ 考生及家长 ｜ 时间待定）：学院计划今年举办夏令营活动，具体时间和形式尚未确定，相关信息确定后通过官方渠道发布。
+### 后续安排与参与方式
+- **咨询渠道**：考生及家长可加入学院官方咨询QQ群，群号 **978499108**，用于获取夏令营及招生相关最新信息。
+- **信息发布**：夏令营具体时间、形式等安排确定后，将通过上述QQ群及时发布，请有意向的同学持续关注。
+- **直播互动**：本场直播已结束，后续如有疑问可通过QQ群进行详细咨询。</t>
         </is>
       </c>
       <c r="D3" s="10" t="n">
-        <v>83.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13887/5897</t>
+          <t>13887/6696</t>
         </is>
       </c>
     </row>
@@ -1387,124 +1412,95 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t># 复盘目标与结果概况
-2023年度总结与年终奖颁发会议于年末召开，老板（发言者1）主持，围绕全年经营数据、年终奖发放标准、员工个人评价、部门评价与展望、颁奖及抽奖等环节展开。会议公布年终奖转账总额为226,000元，成本支出（人员工资、外援、配音、字幕、租机器）达390万元，利润率约24%或27%，最高工资（含年终奖）2-3人达20万元，平均工资到手约1万元，人工支出相对提高25万元，年终奖比去年多13.12万元，干满一年员工从去年4-5人增至今年12人。老板指出成本控制差、利润率不可观，根源是老板关心关注不够、不够雷厉风行，公司结余到账往下跑，还有百来万没收回来，但总量提升，员工拿到钱在提升。会议还公布年终奖发放标准，逐一点评员工并颁发最佳新人奖、最佳进步奖、后期独挡一面奖、最佳员工奖、特别贡献奖五个奖项，对短视频、执行、商务三个部门进行评价与展望，最后组织抽奖并宣布报销福利。
-# 结果与关键成果
-## 交付与里程碑
-- **2023年度总结会**：老板在年会上总结公司2023年发展状况，公布年终奖总额、成本支出、利润率等经营数据，并逐一点评员工、颁发奖项。
-- **短视频账号运营**：视频号粉丝从3月1日的719人增长至8万，小红书从1月的2000+增长至6.4万，抖音从2000+增长至5.7万，B站从3.1万增长至7.6万；涨粉转折点为6月20日第一条外出拍摄的对话视频。
-- **账号变现进度**：课程拍摄变现程度自评10分制达7.05分，其中0.5分为期待空间；直播在视频号已播4-5场，平均每场在线人数5000+，前100人平均在线时长50分钟以上，但尚无课程可售，重点项目变现未完成。
-- **商务部门业绩**：2023年实打实拿到的项目约300万元左右（含入围等可能更多）。
-## 数据与指标
-- **年终奖总额**：转账总额为226,000元。
-- **成本支出**：人员工资、外援、配音、字幕、租机器等实打实支出390万元。
-- **利润率**：约24%或27%，老板评价"非常不可观"。
-- **员工收入**：最高工资（含年终奖）2-3人到手达20万元；平均工资到手约1万元多。
-- **人工支出变化**：2023年平时工资到手比去年提高约25万元；年终奖比去年多13.12万元（原文表述为"1312万多"）。
-- **人员留存**：干满一年的员工从去年4-5人增至今年12人。
-- **公司结余**：到账结余往下跑，还有百来万没收回来，实际略有缩水。
-## 制度与流程
-- **年终奖发放标准**：入职两三个月或半年以内发红包，去年600-800元，今年约1000元；干满一年以一个月基本工资为基准，无大披露或大问题会比基准更高；干满一年以上不多考虑年限，按年度表现评定；老员工且非常满意有较高预算，实际拿到两三万，预算可到大几万但需给老板理由。
-- **个人年终奖不逐一公布**：老板决定公布总额但不公布个人数额，以发到手为准。
-- **颁奖评选标准**：奖项评选为2选1或3选1，有竞争性；未获奖不代表能力不行，但至少证明不突出。
-- **报销福利**：会议当天看电影或吃饭在一定额度内可酌情报销，仅限当天，过期作废。
-## 团队与人员
-### 红叶子
-- **工作能力**：政委给予非常高的评价，称"很难招到这样的一个人才，既懂技术又懂英语，而且有把事情做好的精神头"；入职两三个月（10月入职，11月转正），获最佳新人奖。
-### 郭东辉
-- **运营能力**：非常有经验的运营，克服了本不应面对的困难，老板表示公司可能限制了他的发挥，应表示歉意；负责短视频账号运营，坚持推动外出拍摄转型。
-### 刘腾宇
-- **职业表现**：老板评价为"评价最高的，没有之一"，职业性、专业性、纪律性最好；纪律上迟到几乎没有，请假严格按规定提前告知并安排工作；客户反馈好，宁波城市项目客户称"如果不是你这个小姑娘做的好，你们做的这么慢，早投诉你们了"；效率最高且不出问题，获最佳员工奖，年终奖在既定标准上因林海腾肯定再拉一档，可能翻倍。
-### 欧阳小元
-- **工作态度**：有认真的工作态度，技术水平能胜任且有一定学习能力，进步明显；获最佳进步奖；需提升沟通能力。
-### 徐艺玲
-- **工作质量**：一遍过的非常多，仔细认真，"挑不出什么毛病"；技术层面有进步，原先只能剪课程，今年剪宣传片类也像模像样；课程类既有效果又有效率，得到好评较多，杨晶项目其他人做不了她做完了。
-### 张文倩
-- **综合能力**：工作需综合沟通能力与专业水平，表现高出老板期待；宁波等较难项目老板原以为干不了，但人家完成了；因年龄和工作年限，经验上有所欠缺。
-### 市井
-- **技术水平**：后期方面技术标杆，"最好的没有之一"，从2022年起其他人也能分散做，但品质上依然最好；老板期待能参与解决一些较难问题。
-### 钱德峰
-- **工作投入**：元老级人物，后半年拍摄密集，两个月连轴转没有一天休息；除自己拍摄外还安排拍摄人员；主动关心公司发展，如建议办停车券、设备更新等非本职工作；老板期待更强的执行能力。
-### 徐武安
-- **工作表现**：灵光、眼里有活；去警察学院驻场一人孤苦伶仃，刚开始被反馈经验欠缺，后来对方觉得"挺灵的"；拍摄技术水平好于后期技术水平。
-### 宋俊逸
-- **编导能力**：入职两三个月（10月入职），第一个活是宁波两分钟小宣传片，把要求发给他后一会儿就写好文稿发回，老板评价"行家一出手便知有没有"；后续监狱、财经等项目没出现任何问题，交给他是完全放心的。
-### 张扬
-- **综合表现**：公司邀请来的人才，来了半年左右，职业态度和工作能力有目共睹，基本达到期待；老板称"2023年干到最有价值的一件事就把他招进来"；获最佳新人奖。
-### 林海腾
-- **运营作用**：对运营层面有比较重要的作用，上传下达，员工有些话通过他传达给老板；后期安排是繁重的活，辛苦程度最大，半夜、周六周天被侵占最多，最操心；获特别贡献奖，奖金为几个单项奖中最多。
-### 李国宇
-- **拍摄与后期**：拍摄水平在公司算比较高，能胜任稍高难度工作；后期有灵性，能听懂能进步，理工项目第一遍剪得乱七八糟，被逼一顿后完美交差；需提升沟通能力。
-### 张启
-- **商务表现**：干了一年的商务，表现高于老板预期，本以为害羞实际挺外向；有主观能动性，联系客户主动打电话，没安排到也会去做；老板支持较少，几乎没什么项目，后面会考虑给更多支持。
-## 年度总结与奖项
-- **2023年总体状况**：公司总量在提升，员工拿到钱在提升，成本也在往上跑；老板个人比去年少拿约10万元，但承担了亏100万的风险。
-- **最佳新人奖**：颁给红叶子、张扬两人，老板表示评选非常认真严肃，公平性非常公平，和任何人非亲非故。
-- **最佳进步奖**：颁给欧阳小元，肯定其技术进步"明显的跑了一截"。
-- **后期独挡一面奖**：颁给李国宇，政委搜了好久名字，意为能完美胜任后期各种类型（课程、微电影、MV、快剪），政委给予非常高的评价，称其承担了沟通角色，有些课搞到半夜很辛苦。
-- **最佳员工奖**：颁给刘腾宇，老板称含金量较高，与政委非常达成一致，综合考虑纪律执行、职业态度、技术能力、出活等所有部门。
-- **特别贡献奖**：颁给林海腾，奖金为几个单项奖中最多，因辛苦程度最大、最操心，对运营有非常重要的意义。
-- **抽奖奖品**：充电宝（价值79元）、观影券（价值30元）、洗头膏（价值七八十元，未寄到）、老板自写100元红包奖；林海腾发200元红包在群里。
-# 亮点事项
-## 短视频账号突破性增长
-- **粉丝数大幅跃升**：视频号从3月1日的719人增至8万，小红书从2000+增至6.4万，抖音从2000+增至5.7万，B站从3.1万增至7.6万，各平台均实现显著增长
-- **关键转折点**：6月20日第一条外出拍摄的对话视频成为涨粉起点，此前潘老师已10次提醒郭东辉「出去找工作吧，这个项目我不想干了」，郭东辉坚持不放弃，并**破釜沉舟说服潘老师到外面拍摄**，加上forty加入，项目得以继续
-- **账号变现初见成效**：课程变现按十分制已达7.5分，直播在视频号已播4-5场，平均在线人数5000+，前100人平均在线时长50分钟以上，具备变现能力但尚未完成重点项目目标
-- **同行高度认可**：老板表示做运营的同行（卖虾、卖螃蟹的）非常惊讶「你们居然能做这么久」，如果是他们这种状况可能早就放弃了
-- **员工给予老板信心**：老板坦言「因为有这样的员工，我要把这个事搞成了才能对得起人家」，员工坚持转化为老板做成的决心，数据与前景向好
-## 员工超出预期的表现
-- **刘腾宇获最高评价**：老板称其是「评价最高的，没有之一」，职业性、专业性、纪律性俱佳，客户反馈「如果不是你这个小姑娘做的好，你们做的这么慢，早投诉你们了」，重要活安排给刘腾宇「肯定不会有任何问题」，年终奖在既定标准上因林海腾肯定再拉一档，可能翻倍
-- **张扬入职带来改变**：老板称「2023年干到最有价值的一件事就把他招进来」，职业态度与工作能力有目共睹，基本达到期待，且能做三维制作，往年二维三维均外包，此能力可解决公司外包问题
-- **宋俊逸首次接活即获认可**：老板安排宁波两分钟宣传片，宋俊逸很快交回文稿，老板评价「行家一出手便知有没有」，后续监狱、财经等项目未出任何问题，「交给他是完全放心的」
-- **张文倩完成高难度项目**：老板原以为宁波等项目干不了，「我都打好这个谱，我就以为可能就黄了」，但张文倩完成且出乎意料，其岗位需综合沟通能力与专业水平
-- **红叶子获政委高度评价**：政委评价「很难招到这样的一个人才，既懂技术又懂英语，又有把事情做好的精神头」，且会在工资表意见栏认真写如何把项目做得更好
-## 颁奖仪式感与员工激励
-- **认真对待仪式感**：去年李海腾建议公司欠缺仪式感，今年老板认真对待，证书为皮质、40元一本含设计费，字体认真校对，奖金相对可观，另有洗手包（值七八十元）与老板手写100元红包奖
-- **奖项设置完整**：共6人5项奖，包括最佳新人奖（红叶子、张扬）、最佳进步奖（欧阳小元）、后期独挡一面奖（李国宇）、最佳员工奖（游腾宇）、特别贡献奖（李海涛），评选标准为2选1或3选1，特别贡献奖奖金最多
-- **老板认真准备评价**：老板表示「每一句每个人的台词，我真的是认真想过的，不是现场发挥的」，评价相对中肯，且因林海腾夸谁多就给谁涨年终奖
-## 后期团队整体能力提升
-- **分级模糊化、整体效率提升**：林海腾指出今年后期人员之间明确分级模糊了，「大家效率都差不多，整体上差不多」，制作能力上作品也有提升，整体技术进步明显
-- **高强度下保证质量**：后半年基本都在加班，晚上周末均被占用，但「劳累的同时还能保证质量，是一件非常不容易的事情」，有怨言但仍接着干，老板认可为职业操守
-- **加班补贴纳入年终奖**：老板与政委商量年终奖时考虑加班因素，「再补贴一部分，也有可能有一两千的考虑」，对加班有所补偿
-# 不足事项
-- **成本控制差，利润率不可观**：2023年实际支出（人员工资、外援、配音、字幕、租机器）达390万元，利润率仅约24%或27%，老板明确表示“成本控制是非常差的”，这是公司最大的问题；若今年没有增量、成本控制仍维持现状，年会可能无法召开。根因：**老板对成本关心或关注不够，不够雷厉风行，出现问题没有及时解决**，老板自认“根源的问题就是老板的问题”。
-- **公司结余到账往下跑，回款未收齐**：虽然总量提升、员工拿到钱在提升，但公司结余到账呈下降趋势，还有百来万未收回，实际结余“稍微缩水”。根因：老板未在原文中给出具体归因，仅指出成本往上跑是负值。
-- **加班问题严重，人员不足是最大因素**：后期部门今年尤其是后半年基本都在加班，很少正常休息，晚上、周末均被占用；林海腾指出“劳累程度上也确实特别的累”。根因：**老板承认判断失误——没有及时招更合适或更合适人数的人员**，商务业务断断续续产生，给人“不需要招这么多人”的错觉，但平时积累的人脉资源又不确定，导致人不够成为加班最直观、最大的因素。
-- **账号尚未变现，重点项目未完成**：短视频账号虽在多个平台涨粉显著（视频号从700+到8万、小红书从2000+到6.4万、抖音从2000+到5.7万、B站从3.1万到7.6万），但账号变现至今未完成，课程拍摄按十分制仅达到7.05分（含0.5分期待空间），直播已进行4-5场、平均在线5000人+，但“现在没有课程，所以说他是可以进行变现的”，重点项目“可以说是没有完成”。根因：老板未在原文中给出明确归因，仅表示明年将投入更大精力、给予足够重视。
-- **拍摄外援成本偏高，内部人员参与不足**：钱德峰指出“请了很多天的外援”，但部分工作（如简单按个机位、让机器不关机）公司内部人员即可完成，外援与内部拍摄价格“两边价格是差很多的”。根因：**内部人员以“没空、很忙、不想去”为由推脱**，钱德峰认为“其实挺意外的”，公司凑不出人去完成简单拍摄任务；老板承认“没有安排开”是原因之一，并指出直接说“没空”是非常不职业的。
-- **老板对商务部门支持不足**：张启作为商务人员，几乎没有什么项目，老板“给他的支持比较少”，项目多靠老板帮忙聊或打理。根因：老板自认“我们做老板来说，给他的支持比较少”，明年将考虑给予更多支持和帮助。
-- **员工个人自评未达预期**：张启自评2023年“没达到我自己的预期”，原因包括效率、时间、项目上对同事和甲方的沟通做得不太好；老板评价李国宇“沟通能力”需提升、欧阳“沟通能力可能要再爬坡”，均属未达预期环节。
-- **公司仪式感欠缺（往年问题）**：老板指出“我们欠缺仪式感”“之前也不太注重这方面”，今年才认真对待（含证书设计、字体核对、皮质证书40元/本等）。根因：往年未重视，今年因员工建议（李海腾提出）才改进。
-# 改进计划
-## 成本控制
-- **针对成本控制差、利润率不可观（24%或27%）**：老板表示明年开会时再讨论成本控制问题，未给出具体方案。
-- **针对外援成本高**：钱德峰提出，有一段时间请了很多天外援，但部分工作公司内部人员即可完成（如简单按个机位、保证机器不关机），外援与内部人员拍摄价格差很多，建议尝试内部人员参与拍摄，既提升收入也增加体验。
-- **针对人员安排不开导致外援**：老板回应，去年已说明拍摄相对性价比高，没有阻止任何人参与，但确实存在没安排开的原因，明年会往「大家都能参与拍摄」的方向靠，希望每个人至少能应付得了。
-## 人员与加班
-- **针对加班严重、人不够**：老板承认是判断失误——商务给活是连续信号，但业务有断续，造成不需要招更多人的错觉，同时平时积累的人脉资源又不确定，所以没有及时招合适人数的人员；明年会反思这个问题。
-- **针对加班补贴**：老板表示在商量年终奖时已考虑加班因素，在年终奖基础上再补贴一部分，可能有一两千元的考虑。
-- **针对员工直接说「没空」不职业**：老板强调，被领导问到安排时应解释手头忙的东西或勉为其难安排一下，直接说没空非常不职业。
-## 账号变现
-- **针对短视频账号尚未变现**：老板对短视频部门整体满意并认可克服困难的过程，期待明年账号能开始变现，老板会投入更大精力、给予足够重视。
-## 管理支持
-- **针对老板对员工支持、管理、关心不够**：老板承认今年给予商务部门的支持、管理或关心不够，明年会反思这个问题；对商务部门，后续会考虑给予张启更多支持和帮助（如帮忙聊项目、打理事务）。
-- **针对执行部门休息时间被侵占**：老板期待明年能更多进行组织协调，提高效率、提升工作开心程度，尽可能少侵占大家休息时间。
-## 员工能力提升
-- **针对刘腾宇综合后期技术水平提升空间**：老板提出更高期待，希望其综合后期技术水平更高，能完美胜任各种类型的工作。
-- **针对欧阳沟通能力需提升**：老板提出沟通能力要再爬坡。
-- **针对李国宇沟通能力问题**：老板提出更高期待是提升沟通能力。
-- **针对钱德峰执行能力**：老板期待其有更强的执行能力，包括项目执行或沟通谈判。
-- **针对市井参与项目**：老板期待市井能解决一部分公司认为比较难的问题，参与项目沟通与后期相关会议。
-- **针对张文倩职场经验欠缺**：老板认为其灵光性可弥补经验不足，期待从公司角度发挥更大价值。
-- **针对徐艺玲**：老板表示更高期待「明年再说」，暂未给出具体方向。</t>
+          <t># 2023年度总结与年终奖颁奖年会
+## 复盘目标与结果概况
+公司召开2023年度年会，老板总结全年经营数据并公布年终奖发放标准：年终奖转账总额226,000元，全年实打实支出成本390万元（含人员工资、外援配音、字幕、租机器），利润率约24%或27%，最高工资（含年终奖）约20万元、仅两三人达到，平均到手工资1万多元；2023年平时工资总额提高约25万元，年终奖比去年多13万多元，干满一年员工从去年四五人增至今年12人。老板指出成本控制非常差是最大问题，根源在于老板关心关注不够、不够雷厉风行；公司总量提升、员工拿到钱提升，但结余到账下降，还有百来万未收回。随后老板逐一点评员工（红叶子、郭东辉、刘腾宇、欧阳、徐艺玲、张文倩、市井、钱德峰、徐武安、宋俊逸、张扬、林海腾等），对短视频、执行、商务三个部门进行评价与展望，颁发最佳新人奖（红叶子、张扬）、最佳进步奖（欧阳小元）、后期独挡一面奖（李国宇）、最佳员工奖（游腾宇）、特别贡献奖（李海涛）共5个奖项，最后组织抽奖并宣布当天观影或吃饭可报销的福利。
+## 结果与关键成果
+### 数据与指标
+- **年终奖总额**：2023年年终奖转账总额为226,000元。
+- **成本支出**：全年实打实支出成本390万元，含人员工资、外援配音、字幕、租机器。
+- **利润率**：约24%或27%，老板评价“非常不可观”。
+- **工资水平**：最高工资（含年终奖）约20万元，仅两三人达到；平均到手工资1万多元。
+- **工资与年终奖增幅**：平时工资总额提高约25万元；年终奖比去年多13万多元。
+- **人员留存**：干满一年员工从去年四五人增至今年12人。
+- **账号数据（郭东辉汇报）**：视频号粉丝从3月1日的719人增至8万；小红书从2000+增至6.4万；抖音从2000+增至5.7万；B站从3.1万增至7.6万；涨粉起色始于6月20日第一条外出拍摄视频。
+- **账号变现**：课程变现达到7.5分（满分10分），重点项目变现目标未完成。
+- **直播数据**：视频号直播4-5场，每场平均在线人数5000人以上，前100人平均在线时长50分钟以上。
+- **商务部门业绩**：实打实项目约300万元左右。
+### 团队与人员
+- **红叶子**：政委给予非常高评价，称“很难招到这样的一个人才，既懂技术又懂英语，有把事情做好的精神头”；入职两三个月，获最佳新人奖。
+- **郭东辉**：有经验运营，克服达人方面困难，坚持推动外出拍摄策略，账号各平台涨粉显著；老板表示公司限制其发挥，应表示歉意。
+- **刘腾宇**：职业性、专业性、纪律性最好，迟到几乎没有，请假严格按规定并提前安排工作；客户反馈“如果不是你这个小姑娘做的好，你们做的这么慢，早投诉你们了”；年终奖在既定标准上拉一档，获最佳员工奖。
+- **欧阳**：工作态度认真，有学习能力，技术有进步；沟通能力需提升；获最佳进步奖。
+- **徐艺玲**：一遍过情况多，仔细认真，技术有进步，从剪课程到剪宣传片类“像模像样”；课程类项目获好评多。
+- **张文倩**：综合能力强，宁波项目完成出乎老板意料；因年龄和工作年限，经验上有所欠缺。
+- **市井**：后期技术标杆，“最好的没有之一”；获后期独挡一面奖。
+- **钱德峰**：后半年拍摄密集，两个月连轴转无休息；除拍摄外还安排拍摄人员，提出停车券、设备更新等运营建议。
+- **徐武安**：灵光、眼里有活，警察学院驻场辛苦孤单，客户反馈从“经验欠缺”转为“挺灵”；拍摄技术水平好于后期。
+- **宋俊逸**：编导，第一次安排宁波两分钟宣传片活即表现好，效率高、能解决问题，后续监狱、财经类项目未出问题。
+- **张扬**：公司邀请的人才，职业态度和工作能力基本达到期待；老板称“2023年干到最有价值的一件事就把他招进来”；获最佳新人奖。
+- **林海腾**：运营层面重要，上传下达，辛苦程度最大；获特别贡献奖（单项奖中奖金最多）。
+- **李国宇**：拍摄水平较高，能胜任稍高难度项目；后期有灵性、能听懂指导；沟通能力需提升。
+- **张启**：商务，表现高于预期，外向、有主观能动性，主动联系客户；老板支持较少，后续将给予更多支持。
+### 制度与流程
+- **年终奖发放标准**：入职两三个月或半年以内发红包，去年600-800元、今年约1000元；满一年以一个月基本工资为基准，表现好会更高；干得久且满意，预算可达大几万，实际拿到两三万左右。
+- **颁奖机制**：共6人获奖、5个奖项，评选有竞争性（2选1或3选1）；老板强调对后期部门在年终奖和颁奖上有所侧重，是唯一愿意解释的分配原因。
+- **仪式感建设**：今年认真对待颁奖仪式，证书为皮质、40元一本（含设计费），另有两个洗手包（价值七八十元）未寄到；老板称这是回应去年李海腾“欠缺仪式感”的建议。
+### 年度总结与表彰
+- **2023年度总结**：公司总量提升、员工拿到钱提升、成本上升；结余到账下降，还有百来万未收回。
+- **颁奖结果**：最佳新人奖颁给红叶子、张扬；最佳进步奖颁给欧阳；后期独挡一面奖颁给市井；最佳员工奖颁给刘腾宇；特别贡献奖颁给林海腾。
+- **抽奖福利**：奖品含充电宝（价值79元）、观影券（价值30元）、洗头膏（价值七八十元）、100元红包奖；老板宣布今天看电影或吃饭在一定额度内可报销、仅限今天；林彦腾发200元红包在群里。
+## 亮点事项
+1. **短视频账号全平台大幅涨粉**：视频号粉丝从3月1日的719人增至8万，小红书从2000+增至6.4万，抖音从2000+增至5.7万，B站从3.1万增至7.6万；转折点始于6月20日第一条外出拍摄的对话视频，此前潘老师已10次提醒放弃项目，运营郭东辉以破釜沉舟的心情说服潘老师外出拍摄，加上forty加入，项目得以坚持并起色。
+2. **账号变现能力初步建立**：课程变现按十分制自评达到7.5分（含0.5分期待空间），视频号直播4-5场、每场平均在线5000人以上、前100人平均在线超50分钟，虽暂无课程可售但已具备变现条件；外部运营同行对团队能坚持这么久表示惊讶，认为一般公司早会放弃。
+3. **员工主动性与责任心成为项目存续关键**：郭东辉在项目濒临放弃时坚持「不应该从我这里去放弃」，并主动说服老板改变拍摄策略；老板表示正是因为有这样的员工，才要把事搞成才能对得起人家，员工给予了老板信心。
+4. **新员工带来超出预期的能力与价值**：张扬是公司邀请的人才，职业态度与工作能力基本达到期待，老板称「2023年干到最有价值的一件事就是把他招进来」；宋俊逸首次安排宁波宣传片任务即高效交付文稿，老板评价「行家一出手便知有没有」，后续监狱、财经等项目零问题；红叶子获政委高度评价「很难招到这样的人才，既懂技术又懂英语，又有把事情做好的精神头」。
+5. **后期团队整体能力跃升**：后期负责人林海腾指出今年项目整体难度比去年大、种类更多，但安排活时即使硬着头皮交给没做过的人也能完成好，后期人员间原本明确的分级今年模糊化、效率整体趋同，制作能力作品整体进步；高强度加班下仍保证质量，有怨言但继续干，体现职业操守。
+6. **员工个人突破与成长**：郭东辉从「混日子」状态转变为有收获感、成就感、幸福感，认知上「最大的敌人是自己」，所有内容与直播决策均以数据支撑（每晚8-9点刷竞品直播间研究内容与互动）；欧阳技术进步明显，老板评价「进步不是所有人都有的，他明显跑了一截」；徐艺玲从只能剪课程到宣传片类「像模像样」。
+7. **张文倩完成超出预期的项目**：老板原以为宁波等较难项目她干不了，甚至已做好项目黄了的心理准备，但张文倩最终完成，表现「高出了我的期待」。
+8. **颁奖仪式感认真筹备**：针对往年欠缺仪式感的反馈，今年认真对待——证书为皮质、40元一本含设计费，字体经认真核对；另有两个洗手包（价值七八十元）未寄到；老板自写100元红包奖；共6人获5个奖项，评选经认真讨论，最佳员工奖将全部名字列出后讨论决定。
+9. **年终奖总额与个人收入提升**：年终奖转账总额226,000元，比去年多13万多元；干满一年员工从去年四五人增至今年12人；最高工资（含年终奖）约20万元、两三人达到，平均到手工资1万多元；刘腾宇因林海腾肯定在既定标准上再拉一档，老板称「年终奖应该会让你比较惊喜，可能还会翻倍」。
+## 不足事项
+1. **成本控制非常差**：全年实打实支出成本390万元（含人员工资、外援配音、字幕、租机器），利润率仅约24%或27%，老板明确称"成本控制是非常差的"是公司最大问题。根因：**老板对业务关心或关注不够，不够雷厉风行，出现问题没有及时解决**。
+2. **公司结余到账下降**：虽然公司总量在提升、员工拿到钱在提升，但成本也在往上跑，公司结余到账是往下跑的，还有百来万未收回，实际结余稍微缩水。
+3. **老板对员工关心或管理支持不够**：老板承认今年给予商务部门的支持、管理或关心不够；对张扬这类有态度有能力的员工，如果还出现问题，就是老板或制度管理沟通的问题。
+4. **人员不足导致加班多**：后期负责人指出今年尤其是后半年基本都在加班，很少正常休息，高强度工作大家有怨言但仍坚持。根因：**老板没有及时招更合适或更合适人数的人员**，商务给活断断续续造成"不需要招这么多人"的错觉，但平时积累的人脉资源又不确定，属于判断失误。
+5. **商务部门支持不足**：老板承认给商务部门张启的支持比较少，他几乎没有什么项目，老板只是帮着聊了聊或打理；老板也承认今年对商务部门整体支持不够，明年会反思。
+6. **账号重点项目未完成**：运营郭东辉汇报，账号变现重点项目没有完成（课程变现程度满分十分只达到7.05分，其中0.5分是期待空间）；直播虽已开播但"现在没有课程，所以说他是可以进行变现的"，变现尚未落地。
+7. **短视频账号前期发展困难**：6月20日之前账号几乎没有起色，老板曾多次（约10次）提醒运营"出去找工作吧，这个项目我不想干了"；运营靠破釜沉舟说服老板到外面拍摄，账号才从6月20日第一条视频开始有起色。
+8. **拍摄人员安排不足**：员工钱德峰指出，有一段时间请了很多天外援，但有些简单活（如按个机位、让机器不关机）公司自己人内部就可以搞定，却凑不出人来；外援拍摄与内部人员拍摄两边价格差很多，成本浪费。
+9. **员工直接说"没空"不职业**：老板指出，有些员工被领导问到安排拍摄时直接说"我没空"，这是非常不职业的；应该起码解释一下手头上忙的东西，或勉为其难安排一下。
+10. **跨部门之间相互不了解**：老板指出，同部门之间可能相互比较了解，但跨部门之间相互不了解，容易出现商务觉得技术"活都是我接的、谁做都一样"、技术觉得商务"靠一张嘴不说也可以"的误解。
+## 改进计划
+- [ ] **【成本控制】针对全年实打实支出成本390万元、利润率仅约24%或27%的问题，老板承认成本控制非常差是最大问题，根源在于老板对成本关心或关注不够、不够雷厉风行、出现问题未及时解决，明年开会时再专题讨论成本控制事宜**
+  - **针对痛点**：成本支出高企、利润率偏低，公司结余到账下降，还有百来万未收回
+  - **落地动作**：明年开会时专题讨论成本控制问题，老板反思自身在成本管理上的关注与决断不足
+- [ ] **【短视频账号变现】针对短视频账号目前尚未变现、重点项目变现未完成的问题，老板表示明年期待账号开始变现，并会投入更大精力、给予足够重视**
+  - **针对痛点**：账号粉丝量虽有增长（视频号从719人增至8万、小红书从2000+增至6.4万、抖音从2000+增至5.7万、B站从3.1万增至7.6万），但课程变现仅达7.5分（满分10分），直播已进行4-5场、场均在线5000人以上但暂无课程可售
+  - **落地动作**：老板明年投入更大精力推动账号变现，给予足够重视
+- [ ] **【人员补充】针对加班多、休息时间被侵占的问题，老板承认本质上是没有及时招到合适或足够人数的人员，属于判断失误，明年需补充人员**
+  - **针对痛点**：后半年基本都在加班，包括晚上和周末，高强度工作虽有怨言但仍坚持完成
+  - **落地动作**：及时招聘合适或足够人数的人员，避免因人手不足导致加班常态化
+- [ ] **【商务部门支持】针对商务部门今年实打实项目约300万元、老板承认给予的支持或管理或关心不够的问题，老板表示明年会反思并给予更多支持和帮助**
+  - **针对痛点**：商务人员张启几乎没有什么项目，老板帮忙聊了聊或帮着打理，支持较少
+  - **落地动作**：明年反思对商务部门的管理与支持，考虑给予更多支持和帮助
+- [ ] **【拍摄能力普及】针对外援拍摄成本高、公司内部凑不出人按机位的问题，老板表示明年鼓励大家都能参与拍摄，提升个人市场价值**
+  - **针对痛点**：请外援拍摄与内部人员拍摄价格差很多，部分人员以「没空、很忙、不想去」为由推脱
+  - **落地动作**：明年向「大家都能拍」方向推进，鼓励全员参与拍摄，起码能应付简单机位；被领导问到时应解释手头工作或勉为其难安排，不能直接说「没空」
+- [ ] **【组织协调与休息保障】针对执行部门辛苦程度高、项目没做砸过但休息时间被侵占的问题，老板期待明年更多进行组织协调，提高效率与工作开心程度，尽可能少侵占大家休息时间**
+  - **针对痛点**：执行部门项目密集、加班多，休息时间被大量占用
+  - **落地动作**：老板明年更多进行组织协调，提升效率，减少对员工休息时间的侵占
+- [ ] **【员工个人提升方向】针对部分员工被指出的提升空间，老板提出具体期待**
+  - **针对痛点**：欧阳沟通能力需爬坡；李国宇沟通能力有问题且很严重；市井期待能参与解决部分较难的问题；钱德峰期待更强的执行能力（项目、沟通谈判）；徐艺玲期待更开心一点
+  - **落地动作**：相关员工明年按各自方向改进，具体问题明年再说</t>
         </is>
       </c>
       <c r="D4" s="10" t="n">
-        <v>87.2</v>
+        <v>74.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>24562/6916</t>
+          <t>24562/5842</t>
         </is>
       </c>
     </row>
@@ -2046,78 +2042,83 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t># 全文摘要
-本次会议为小区业委会与物业公司就服务问题、业主大会召开及物业去留的专项协调会，业委会成员、物业经理及办事处领导等多方参与。会议围绕业主大会召开、小区服务问题清单、物业费与经营状况、法律诉讼与反诉等议题展开。业委会提出业主自发接龙约200户要求召开业主大会表决物业去留，物业方宣布已与集团法务沟通将于本月起诉业委会。业委会列举小区10条服务问题，物业方逐条回应称部分属地产责任或费用不足。物业方称业主欠费170多万、年人工成本100多万、每年亏损，业委会认为服务不到位致业主不愿缴费并提出集体起诉返还部分物业费。最终业委会决定正常推进业主大会，物业方将依法起诉。
-# 分段速览
-## 00:10-05:04 开场与背景铺垫
-会议开场阶段，发言者2与发言者1、发言者3就小区物业费缴纳、供暖开户费及园区验收等问题进行初步交流。发言者2提到供暖开户费应由地产公司出资并将管道交接给供暖公司，但至今未完工验收，导致责任归属不清。发言者3确认相关费用已交清，发言者2则指出开发商收款去向不明，园区整体未验收，问题复杂。
-## 05:04-12:09 业主诉求与会议基调
-发言者4提出业主们买房满怀希望、不愿退房，发言者2回应称一期补助可达29%。发言者4介绍业主自发组织接龙约200户，主要诉求是召开业主大会表决物业去留。发言者2强调会议基调为坦诚相待、不暴露敌对情绪，希望大家共同商量解决问题，并提及成立业主委员会的初衷与顾虑。
-## 12:09-18:45 业主大会程序与群组情况
-发言者4说明业委会工作组群唯一，准业主分5个群，接龙群为交房时老邱哥所建、已有5-6年。发言者2质疑接龙程序合法性，强调召开业主大会需事先与物业沟通，但物业未接到任何通知。发言者5总结接龙业主心声：要求整改小区问题，若整改无效可重新招标，原物业也可参与投标。
-## 18:45-22:08 物业宣布起诉
-发言者2正式宣布，鉴于业委会成立及工作过程中存在违法情况，已与集团法务沟通，将于本月起诉业委会，并称欠费超一年人员不能成为业主代表。发言者2表示已掌握业主群内证据，上午9:52与高级人民法院通话，同时与滨城区人民法院沟通，起诉对象包括业委会及保洁业主代表。
-## 22:08-31:22 业委会列举十项服务问题
-发言者4逐条列举小区10项服务问题：入户门柱灯从未开启；内部水系与迎宾水系从未开启；监控几乎全部损坏，上月进贼未获取数据；监控室24小时值班服务荒废；绿化维护不足、去年死树多棵；北边围墙用烂铁皮遮挡且有缺口、存在安全隐患；快递柜、直饮水机、宽带、暖气等民生配套无进展；雨水倒灌自2019年存在未解决；物业人员从办公室10人减至4人、维修从5人减至2人。
-## 31:22-38:53 物业逐条回应
-物业方发言者2与发言者7逐条回应：门柱灯因能耗成本过高无法运营；水系存在质量问题属地产配套未完成；监控维修因费用超运营承担，园区保护收入100来万、人工成本100多万、每年亏损；绿化死亡因业委会10月成立后已入冬季；北边围墙属红线以外且涉及违建官司，物业无处理义务；民生配套属地产前期配套；雨水倒灌属地产设计问题；人员配备不足因地产补亏款未结。
-## 38:53-48:00 双方争执激化
-发言者4反驳物业服务无滞后性，强调问题从交房至今持续存在，并非物业入驻后才出现。发言者2坚持走法律程序，称起诉期间无法更换物业。发言者4表示已无讨论必要，主张直接表决换物业。发言者3指出恶性循环：服务不整改→业主不缴费→物业无钱→服务更差，认为区领导、市领导也难以解决。
-## 48:00-01:03:16 法律对抗与会议结束
-发言者4提出集体起诉要求返还部分物业费，发言者8表示物业起诉则反诉。双方就物业经理"不交物业费上你家吃饭"言论争执，发言者7要求拿出录音。发言者3建议物业拿出真实行动赢得业主信任，发言者7称业主欠费170多万、公司入不敷出。最终发言者4宣布正常推进业主大会，会议无实质结果结束。
-# 要点梳理
-## 业主大会召开与物业去留
-- **业主诉求**：业主自发组织接龙约200户，主要议题为召开业主大会，表决物业去留。
-- **业委会立场**：发言者4建议尽快召开业主大会，由全体业主表决；业委会或业主个人无权决定撤换物业。
-- **物业方回应**：发言者2称未接到任何事先沟通，接龙系有组织行为；宣布已与集团法务沟通，将于本月起诉业委会。
-- **表决权争议**：物业方称欠费人员不能成为业主代表，顶名也不能成为业主代表，将依法追究责任。
-- **业主大会程序**：发言者2称召开业主大会前应与物业公司沟通，但物业方未接到任何通知；业委会表示将正常推进业主大会表决。
-- **起诉影响**：物业方称起诉期间无法更换物业公司；业委会成员表示将反诉并拿出证据。
-## 小区服务问题清单
-- **门柱灯**：入户庭院门柱灯从未开启过，属业主应得利益与服务。
-- **水系**：内部水系自卖房后从未开启，业主加价购买水系旁房产；售楼处门口迎宾水系也从未开启。
-- **监控损坏**：监控几乎全部损坏，上月小区进贼，110派出所及刑警大队均未从监控获得任何数据。
-- **监控室服务**：交房时配备24小时值班监控室，门铃有一键直达功能；发言者4称王艳芳上任后该服务荒废。
-- **绿化维护**：去年死树多棵，小区入口两侧已知死3棵；业主反映树木生病，物业管家回复"明年看看能不能发芽"。
-- **北边围墙**：长期用烂铁皮遮挡，最西边有缺口，社会人员可随意进出；业委会责令整改后物业拆除铁皮但未安装新围挡，业主证实未定制。
-- **民生配套**：快递柜、直饮水机、宽带覆盖、暖气开通开户等多年无进展，最终由业委会全程办理。
-- **雨水倒灌**：2019年起每逢大雨业主有不同程度财产损失，多次反映无完整解决方案。
-- **人员配备**：物业办公室从接近10人减至4人（含经理），维修人员从5人减至2人。
-## 物业方逐条回应
-- **门柱灯**：因园区能耗成本物业已无法运营，曾与业委会沟通，业委会承诺支持全员缴费并协助收费，收上费用后拿出一部分修复。
-- **水系**：从交付起存在严重质量问题，所有泵无法正常运转，属地产配套未完成，由地产维修，不属物业责任。
-- **监控**：已承诺第一个修监控，但无费用超出运营承担；物业年保护收入100来万，20多人人工成本100多万，不含垃圾清运费、能耗、维修、税费等，每年亏损。
-- **监控数据**：警察进入园区时物业第一时间将拍摄画面截取给派出所和刑警，有照片和记录，质疑业委会信息来源。
-- **绿化**：业委会今年10月成立并备案，此后为冬季，换树责任无法由物业承担。
-- **北边围墙**：属红线以外，不在物业服务范畴，且涉及法律官司、属违建；曾协调施工单位定做，因费用太高未成，费用本应由物业承担，已与业委会沟通不下5次。
-- **民生配套**：根据建设条例和前期配套要求属地产前期配套问题，后期开通费用由业主承担。
-- **雨水倒灌**：园区地势四周偏高中间偏矮，车库设计为斜坡向下，属地产前期设计建设问题，超出物业解决范围。
-- **人员配备**：前期人员不足因地产债主补亏款未结账；今年维修费已花几十万。
-## 物业费与经营状况
-- **欠费规模**：物业方称业主欠物业费170多万，回款40万即可解决部分问题。
-- **经营亏损**：物业方称年人工成本100多万，保护收入100来万，每年亏损，账目可公开查证。
-- **缴费与服务之争**：业委会称物业服务无滞后性，不能先收钱再服务；物业方称欠费导致无钱维修，服务无法改善。
-- **集体起诉提案**：业委会提出就交房以来未达成的服务集体起诉物业，要求返还部分物业费。
-- **物业经理言论**：发言者4称进贼时物业经理第一句话是"你交物业费了吗"，并称"不交物业费就上你家吃饭"；物业方要求拿出录音证据。
-## 结论与决定
-- 业委会决定正常推进业主大会表决，物业去留由全体业主决定。
-- 物业方决定本月起诉业委会，已与集团法务及高级人民法院沟通，称已掌握业主群截图等证据。
-- 物业方称起诉期间无法更换物业公司；业委会表示将依法反诉。
-## 待确认与风险
-- 业主大会召开的具体时间和议题未确定。
-- 物业费欠费与服务改善的先后顺序未达成一致。
-- 物业起诉后业主大会能否召开存在法律争议。
-- 小区围墙缺口与监控损坏存在安全隐患，上月进贼未获监控数据。
-- 雨水倒灌问题未解决，明年大雨可能再次造成财产损失。
-- 物业与业委会矛盾激化，发言者3称"隔阂越来越深"，可能影响小区和谐。</t>
+          <t># 小区业委会与物业矛盾激化协调会
+## 全文摘要
+本次协调会由办事处组织，召集小区业委会成员与物业公司代表，就业主大会召开及物业服务问题展开沟通。业委会成员发言者4代表业主提出，小区业主自发接龙已有200来位业主，主要诉求是召开业主大会表决是否更换物业；业委会工作组有1个群，准业主分5个群，共6个群。物业方发言者2质疑程序合法性，称未接到任何沟通，并宣布已与集团法务沟通，本月将正式起诉业委会，且认为诉讼期间不能召开业主大会。双方未达成一致，矛盾激化。业委会成员发言者4列举了10条物业服务缺失问题，涵盖门柱灯、水系、监控、绿化、围墙、民生配套、雨水倒灌、人员配备等；物业方发言者2和发言者7逐条回应，归因于费用不足、地产配套问题、红线外责任等，双方各执一词。物业方称业主欠物业费170多万，回款40万；园区保护收入100来万，人工成本100多万，每年亏损。业委会成员发言者4提出可能集体起诉物业，要求返还部分物业费；物业方称已掌握业主群内证据，将起诉业委会；业委会成员发言者8表示只要物业起诉就反诉。双方就缴费与服务先后顺序争执，未达成一致。
+## 分段速览
+### 00:10-05:04 开场与背景铺垫
+会议开场后，发言者2首先谈及小区供暖开户费问题，指出园区从建设至今从未验收，开户费应由地产承担并交接给供暖公司，但至今未完工，导致业主误认为是物业责任。发言者2强调开发商已缴纳配套费，但资金流向不明，涉及金额约9亿。发言者4补充业主购房满怀希望，不愿退房，希望问题能解决。此段为后续矛盾铺垫，主要围绕历史遗留问题展开。
+### 05:04-10:14 业主诉求与缴费情况
+发言者2与发言者4讨论业主自发组织缴费情况，提及有热心业主自发组织收费，涉及约400元/户，二期三期合计约20来户业主缴费。发言者2指出部分业主担心管道问题影响明年供暖，希望今年能解决。发言者4表示自己家中已供暖但管道较少。此段聚焦业主缴费意愿与对供暖问题的担忧，为后续矛盾激化埋下伏笔。
+### 10:14-16:59 业委会成立与业主大会筹备
+发言者2强调成立业委会的初衷是坦诚相待、共同商量解决问题，呼吁各方不设敌意、不带私心。发言者4介绍业主自发接龙已有200来位业主，主要诉求是召开业主大会表决物业去留。发言者5说明业委会工作组有1个群，准业主分5个群，共6个群，由筹备组6人分别联系。发言者2质疑接龙程序合法性，认为讨论应有明确结果，不能无结论空谈。
+### 16:59-22:08 物业方回应与法律威胁
+发言者5总结接龙业主心声：要求整改小区问题，若整改不了可招标换物业，原物业也可参与投标。发言者2代表物业方强硬回应，称未接到任何沟通，指责业委会存在违法情况，宣布已与集团法务沟通，本月将正式起诉业委会，并称欠费超一年业主不能成为业主代表。发言者2强调已掌握业主群内证据，上午9:52与高级人民法院通话，并已与滨城区人民法院沟通。
+### 22:08-31:22 业委会列举十项服务缺失
+发言者4系统列举10条物业服务缺失问题：入户庭院门柱灯从未开启；内部水系和迎宾水系从未开启；监控几乎全部损坏，上个月小区进贼，110和刑警大队未从监控获得数据；监控室应24小时值班但自王艳芳上任后荒废；绿化维护不足，去年死了很多树，小区门口死了3棵；北边围墙用烂铁皮挡着且有缺口，社会人员可随意进出，物业拆除后未安装新围挡；民生配套如快递柜、直饮水机、宽带、暖气开户等多年无进展，由业委会全程办理；雨水倒灌问题自2019年起存在，业主多次反映无果；物业办公室人员从接近10人减至4人，维修人员从5人减至2人。发言者4强调这些问题从交房至今一直存在，非物业近期才面临。
+### 31:22-38:53 物业方逐条回应
+发言者2与发言者7逐条回应：门柱灯未亮因能耗成本过高，物业已无力运营；水系从交付起存在质量问题，泵无法运转，属地产配套未完成；监控损坏因费用超出运营承担，园区保护收入100来万，人工成本100多万，每年亏损；绿化死亡因业委会10月才成立，之后已入冬季；北边围墙属红线外且涉及违建官司，物业有权不处理；民生配套属地产前期配套问题，费用应由业主承担；雨水倒灌因园区地势四周高中间低，超出排水承载范围；人员配备不足因地产补亏款未结账。发言者2强调业主欠物业费170多万，回款仅40万，账上一分钱没有。
+### 38:53-48:00 矛盾激化与对峙
+发言者4反驳物业服务无滞后性，不能先收钱再服务，强调问题从交房至今一直存在。发言者2坚持已走法律程序，称起诉期间无法更换物业公司。发言者4表示基本定下召开业主大会，决议是换掉物业，并称物业经理曾对业主说"不交物业费就上你家吃饭"。发言者3作为办事处代表试图调解，指出没有钱解决不了问题，形成"服务差-不缴费-更差"的恶性循环。双方各执一词，矛盾激化。
+### 48:00-01:03:16 调解失败与会议结束
+发言者4提出可能集体起诉物业要求返还部分物业费，发言者8表示只要物业起诉就反诉。发言者3多次尝试调解，建议物业拿出真实行动赢得业主信任，但发言者7表示公司已入不敷出，外面欠物业费170多万，地产公司已申请破产。发言者3指出矛盾越积越尖锐，更难解决。最终双方未达成一致，发言者4表示将正常推进业主大会，会议在僵持中结束。
+## 要点梳理
+### 业主大会召开与表决
+1. 业主自发组织接龙，约200来位业主参与，主要议题为召开业主大会。
+2. 业委会工作组有1个群，准业主分5个群，共6个群；接龙群为交房时老邱哥所建，已有5、6年。
+3. 业委会成员发言者4建议尽快召开业主大会，由全体业主表决是否更换物业。
+4. 物业方发言者2称未接到任何事先沟通，质疑接龙有组织性，并宣布本月将正式起诉业委会。
+5. 物业方称上午9:52与高级人民法院通话，并已与滨城区人民法院沟通，诉讼期间认为无法召开业主大会。
+6. 业委会成员发言者4表示基本定下召开业主大会，决议方向为换掉物业；物业方称起诉期间无法更换物业公司。
+### 物业服务问题清单
+1. 入户庭院门柱灯从未开启过，业主认为属应得服务未兑现。
+2. 内部水系及售楼处门口迎宾水系自交房以来从未开启过，业主曾加价购买水系旁房产。
+3. 监控几乎全部损坏，上个月小区进贼，110派出所及刑警大队均未从监控获得任何数据。
+4. 监控室应24小时有人值班，门铃一键直达功能可紧急处理，但自王艳芳上任后该项服务荒废。
+5. 小区绿化维护不足，去年大量树木死亡，小区门口两侧已知死亡3棵；业主曾反映树木生病，物业管家回复「经理说了，明年看看能不能发芽」。
+6. 北边围墙用烂铁皮遮挡，最西边有缺口，社会人员可随意进出；业委会责令整改后物业拆除铁皮，但未安装新围挡，且被证实并未定制。
+7. 民生配套（快递柜、直饮水机、宽带覆盖、暖气开通开户）多年无进展，最终由业委会全程办理。
+8. 雨水倒灌问题自2019年起存在，业主多次反映无完整解决办法，明年大雨可能再次淹水。
+9. 物业办公室人员从接近10人减至4人，维修人员从5人减至2人，人员配备比严重不足。
+### 物业方回应与经营状况
+1. 物业方称门柱灯未亮系园区能耗成本过高、物业公司无法运营所致，曾与业委会沟通并获承诺协助收费后修复。
+2. 物业方称水系自交付起存在严重质量问题，所有泵无法正常运转，属地产配套未完成，应由地产维修，不属物业责任。
+3. 物业方称监控维修因无费用超出运营承担；园区保护收入100来万，20多人人工成本100多万，每年亏损，不含垃圾清运费、能耗、维修、税费及办公成本。
+4. 物业方称进贼时已第一时间将拍摄画面截取给派出所和刑警，并出示刑警调取监控的照片和记录。
+5. 物业方称业委会今年10月成立备案，此后为冬季，绿化死亡非其责任。
+6. 物业方称北边围墙属红线以外、涉及违建官司，不在物业服务范围内，曾协调施工单位定做但因费用过高未成，与业委会沟通不下5次。
+7. 物业方称业主欠物业费170多万，回款40万，账上一分钱没有；业委会成员在业主群号召不缴费，已记录并将以阻碍经营为由起诉。
+8. 物业方称宽带、快递柜、燃气等属地产前期配套问题，后期开通费用由业主承担，有法律规定。
+9. 物业方称雨水倒灌系园区地势四周高中间矮、车库设计向下斜坡，排水量超出承载范围，属地产前期设计建设问题。
+10. 物业方称人员配备不足因地产欠补亏款未结账，今年维修费已花几十万。
+### 法律诉讼与维权
+1. 物业方宣布本月正式起诉业委会，称已在业主群掌握证据并截屏留存。
+2. 物业方称欠费周期超过一年的业主不能成为业主代表，顶名亦不可，将依法追究责任。
+3. 业委会成员发言者8表示只要物业起诉就反诉，并拿出证据。
+4. 业委会成员发言者4提出可能集体起诉物业，要求返还交房以来未达成服务的部分物业费。
+### 结论与决定
+1. 双方未达成一致，未形成任何正式决议。
+2. 业委会方向基本定下召开业主大会、表决更换物业；物业方宣布本月起诉业委会，认为诉讼期间不能更换物业。
+### 行动项与分工
+- [ ] **物业方本月正式起诉业委会**（物业方 ｜ 本月 ｜ 已宣布）
+- [ ] **业委会正常推进业主大会**（业委会 ｜ 未明确时限 ｜ 进行中）
+- [ ] **物业方与集团法务沟通起诉手续**（物业方 ｜ 今日上午已沟通 ｜ 已完成）
+### 待确认与风险
+1. 业主大会是否召开及表决事项未达成一致，双方各执一词【阻塞】。
+2. 物业费欠费与服务改善的先后问题未解决，形成恶性循环【阻塞】。
+3. 物业起诉业委会的具体时间与结果未定【高风险】。
+4. 小区监控损坏，存在安全隐患【高风险】。
+5. 北边围墙缺口，社会人员可随意进出，安全风险【高风险】。
+6. 雨水倒灌问题未解决，明年大雨可能再次淹水【高风险】。
+7. 物业公司亏损，可能影响服务持续性【高风险】。</t>
         </is>
       </c>
       <c r="D5" s="10" t="n">
-        <v>57.7</v>
+        <v>63</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21511/3578</t>
+          <t>21511/4093</t>
         </is>
       </c>
     </row>
@@ -2365,77 +2366,72 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t># 研讨背景与议题
-本次圆桌论坛围绕具身智能领域的关键技术问题展开，由主持人发言者2组织，邀请来自机械、计算机视觉、强化学习、产业应用等不同方向的嘉宾与博士生参与，旨在通过跨领域交流碰撞观点，探讨具身智能的形态与硬件期待、世界模型的定义与构建、强化学习与模仿学习的路线选择、数据采集与仿真数据应用等核心议题。与会者包括发言者3（机械与传感器方向）、发言者4（柔性物体操作方向博士生）、发言者5（强化学习方向）、发言者6（人工智能方向）、发言者7（计算机视觉方向）、发言者8（强化学习方向博士生）、发言者9（强化学习方向）、发言者10（产业界）、发言者11（数据采集方向）等。
-- **具身智能的形态与硬件期待**：探讨具身智能最终收敛为何种形态（人形机器人或特种机器人），以及硬件应如何支撑具身智能实验的大规模评估与部署。
-- **世界模型的定义与构建**：讨论强化学习领域与计算机视觉领域对世界模型的不同理解，以及是否需要三维表征和inductive bias。
-- **强化学习与模仿学习的路线选择**：探讨策略学习的最终路线，是先模仿学习后强化学习，还是采用混合方式，以及真机场景下reward的获取问题。
-- **数据采集与仿真数据应用**：讨论真实数据与仿真数据的成本与效果对比，如何保证数据质量，以及是否应引入无标注真实数据。
-# 核心观点
-## 具身智能形态与硬件期待
-- **发言者3（机械与传感器视角）**：提出具身智能身体形态的收敛问题——是像人形机器人，还是像《星际穿越》中可变形的大方块机器人；机械领域存在「机械智能」思路，如软手通过强摩擦和顺应性实现大误差下的稳定抓取，期待算法与软件视角对硬件提出期待。
-- **发言者4（博士生，柔性物体操作方向）**：硬件需高寿命、高可靠性，因具身智能训练中模型预测失误导致撞桌等事故，机器人撞几次即损坏，难以可靠scale up；现有工业机械臂并非为此设计，需要个人柔顺的硬件结构以支持大规模真机评估。
-- **发言者2（主持人，多模态大模型与具身智能融合方向）**：具身智能是软硬件协同优化的范式，以松灵产品为例，第二代在遥操与策略部署上明显优于第一代；与任老师合作的凝胶夹爪可反馈触觉、增加稳定性与摩擦力，体现协同进化。
-- **发言者5（强化学习背景）**：若大模型从最底层直通最上层，会消除硬件迭代的可能性——新硬件（如软体机器人）出现时大模型需完全重新训练；以手断后大脑仍能工作为例，认为模型至少应分上下层，大脑不变、小脑adaptive到肢体，软体控制dynamics相应变化而非更换大脑。
-- **发言者6（人工智能第一性原理视角）**：从人脑第一性原理出发，现有大模型远未达到人脑能力，基于多模态大模型微调的方案不会是最终解；因现实环境（桌椅等）为人而设计，人形机器人（双足或轮式，配灵巧手）将占很大比例，但特种机器人在工业生产中已大量存在（如车厂、微电子制造厂机械臂实现97%以上自动化），两类将并存。
-## 世界模型的定义与构建
-- **发言者8（博士生，强化学习入门视角）**：强化学习领域世界模型概念可追溯至1990-91年Sutton的Dyna-Q文章，定义为黑盒、输出下一时刻观测，核心要义是**可交互**（最终目的是学策略）；2018年Schmidhuber与LeCun定义的世界模型含表征与转移两个组件；当前世界模型在物理规律体现上欠缺明显，希望引入3D、触觉等多模态信息完善。
-- **发言者7（计算机视觉视角）**：CV界共识是动态重建物理世界，可作为RL世界模型的工具；但三维计算机视觉技术栈深，RL博士生难以完全学习，导致RL领域不关注三维表征，这是学术发展阶段导致的现状；关于inductive bias，GPT与ImageNet的成功说明数据足够时不需要，但UniSim等新模型又需要（如不生成occupancy难以在视频上做consistency），提出「data bias trade off」设想——数据多则inductive bias少、数据少则多，整体由数据决定。
-- **发言者5（强化学习背景）**：以游戏主角跳楼在游戏中稳落地、现实中死亡为例，世界模型面对相同观测需输出不同dynamics，是**完全歧义的问题**，一个世界模型难以同时建模两个dynamics；因此世界模型可能无法统一（应为多个），但policy可能统一——人作为同一玩家可在游戏中跳楼、在现实中避免，通过更长observation窗口隐式体现condition。
-- **发言者9（对发言者7与发言者5的反对意见）**：不同意以是否带inductive bias区分RL与CV世界模型并认为CV更好；强化世界模型是**针对特定任务**的，目标仅是更好学策略（产出latent state或reward即可），CV世界模型做得足够好可用于强化，但为解强化任务不一定需要CV式世界模型；对发言者5的歧义问题，提出不同物理结构可共享统一表征、以condition区分（如game或real），但发言者5回应称M个独立模型比一个高维可控condition模型更简单可实现，且目前没有单一世界模型能建模所有Atari游戏。
-## 强化学习与模仿学习的路线选择
-- **发言者10（产业界，模型强化加机理融合）**：公司采用模型强化加机理融合方式，因监督学习动作空间大、数据分布远不足以支撑高维动作学习；纯强化学习强依赖仿真环境，sim-to-real迁移不佳；实物强化学习需严格限定决策规模与任务设定（如state-action对），上层用强化学习做决策、底层用MPC或DWA等传统方法执行，实际部署中能提升整体性能。
-- **发言者9（强化学习背景）**：同意混合方式，不认为强化或模仿能单独收敛到最终解；底层传统方法（如PID）已能解决的任务无需从零替代；复杂问题历史规律都是**先模仿后强化**（如AlphaStar、GPT），从零跑强化样本复杂度不可接受，人类先验信息无坏处；单独模仿无法达到专家水平（除非任务即模仿专家行为），单独强化也不行（除非任务足够简单）。
-- **发言者5（强化学习背景）**：PID系统必有反馈元素，该反馈可直接作为强化学习执行过程中的reward——过去PID效果不够好，现在通过强化做得更好，但PID能做说明反馈存在、强化必然走得成。
-- **发言者11（人形角色控制方向）**：模仿学习与强化学习并无本质冲突——运动先验可通过强化学习（如DeepMind的Motion Matching）或模仿学习获取，建模为latent后，有数据用监督学习、无数据用强化学习生成，再通过RL快速找到对应latent完成任务；二者只是获取状态的不同手段。
-## 数据采集与仿真数据应用
-- **发言者11（数据质量经验）**：Open X等数据集融合多家数据、相机视角无法固定，而视角显著影响policy表现；自采数据严格控制视角与标定（手眼标定至今仍有文章在解决、解决得不好）；Open X等数据集只捕捉本体信息（末端、关节角度/力矩），缺少物体运动记录，ORKIN从采集出发必须记录物体运动（当时设备有限只能采刚体和关节体）。
-- **发言者4（博士生，reward采集路线）**：all in reward采集路线，但采集本体有待发展；柔性体任务（叠衣服、系鞋带、拉拉链）现有仿真需IPC等先进图形学技术、算力要求高且能做的人少（如UCLA蒋正凡），进展慢；现实世界是**最好的仿真器**，reward采集比高性能仿真算力更低成本；终极形态是脑机接口或肌电等可穿戴设备，无感、多模态（触觉、力觉、视觉、听觉内生）采集数据；互联网视频与机器人所需数据不匹配——如网上教叠衣服的视频都是平铺状态，而机器人需处理从洗衣机取出揉成一团的状态，常见易做的事恰恰是机器人最缺的数据。
-- **发言者2（主持人，仿真数据流派）**：仿真数据与真实数据不互斥——300条仿真数据加20条真机数据即可显著提升成功率（用pretrain加真机数据微调的原始方法）；仿真数据可提供海量随机位置、orientation与初始状态，配少量真机数据训练出较好policy；柔性物体仿真并非解决不了，而是图形学顶会看不上布料海绵模拟这类问题、机器人领域又不懂计算，未来可能有发展；本人受Ego4D数据集「毒害」，洗数据三个月无产出，互联网数据在数据金字塔最底层、质量低。
-- **发言者7（仿真与真实数据成本视角）**：用真实还是仿真数据应case by case看成本——室内服务机器人真机数据收集有可行性，但自动驾驶corner case（如鬼探头）让人去采太危险；应加入**第三个domain：无标注真实数据**，如Segment Anything、Depth Anything的成功，2025年主题应是同时用真实与仿真的有标注数据并大规模利用无标注数据；关于国产仿真系统，有朋友宋应赌会被卡脖子、做国产替代，business by business是好事，但工作人员不会直接touch这个生意，技术上最终会统一、business上复杂。
-# 达成共识与解决方案
-**未形成统一结论**。本场围绕具身智能形态、世界模型、策略学习路线与数据采集四个议题展开讨论，各方观点存在明显分歧，未达成一致意见。但讨论中形成了若干倾向性认识与主流意见：
-## 具身智能形态与硬件
-- **主流倾向**：具身智能应是**软硬件协同优化的范式**，而非纯算法或纯硬件单线推进（发言者2，以松灵产品两代迭代、凝胶夹爪提升摩擦力与触觉反馈为例）。
-- **主流倾向**：大模型不应是完全端到端、从感知直通控制的单一模型，**至少应分上下层**——大脑（高层认知）保持稳定，小脑（底层控制）需自适应肢体变化（发言者5，以人手受伤后大脑仍能工作、小脑需适应新构型为例）。
-- **主流倾向**：**人形机器人与特种机器人将长期并存**——人形机器人因现实环境为人设计而必然存在，特种机器人（如工业机械臂）已在生产制造中大量应用（发言者6，以特斯拉投入一半精力做22自由度灵巧手、车厂机械臂实现97%以上自动化为据）。
-- **硬件期待**：具身智能实验用机器人需**高寿命、高可靠性**，现有工业机械臂并非为大规模真机评估设计，需发展柔顺硬件结构以支撑规模化评估（发言者4，以训练中机器人撞桌损坏、难以scale up为例）。
-## 世界模型
-- **主流倾向**：强化学习领域与计算机视觉领域对世界模型的理解**关注点不同**——RL侧重可交互性与策略学习，CV侧重物理世界的动态重建；CV的世界模型可作为RL世界模型的工具被调用（发言者7、发言者8）。
-- **主流倾向**：世界模型是否需要三维表征与inductive bias，**由数据量决定**——数据少时需要更多inductive bias，数据规模化后可能不再需要（发言者7，以ImageNet、GPT成功说明大规模学习可减少inductive bias，以UniSim说明当前仍需三维inductive bias为例）。
-- **倾向性认识**：**世界模型可能无法统一为单一模型**，因存在歧义问题（相同观测对应不同物理dynamics）；但**policy有可能统一**，可通过更长观测窗口隐式编码环境条件（发言者5，以游戏主角跳楼在游戏中安全落地、现实中死亡为例）。
-- **反对意见**：CV世界模型对强化任务**不必要**——强化世界模型应针对任务，只需能帮助学策略的latent state即可（发言者9）。
-## 策略学习路线
-- **主流倾向**：**复杂任务应先模仿学习预训练、再强化学习优化**，单独模仿学习或单独强化学习均不可行（发言者9，以AlphaStar、GPT等复杂问题均先模仿后强化为据）。
-- **产业实践**：当前阶段应采用**模型强化加机理融合**的方式——监督学习数据分布不足以覆盖高维动作空间，纯强化学习强依赖仿真环境且sim-to-real迁移困难（发言者10，以公司实际部署中上层强化学习做决策、底层用MPC等传统方法执行为例）。
-- **倾向性认识**：模仿学习与强化学习**并非对立关系**——可先通过强化学习或模仿学习获取运动先验（latent），再通过RL完成任务（发言者11，以DeepMind运动先验获取为例）。
-- **关键判断**：PID能解决的系统**必然存在反馈**，该反馈可直接作为强化学习的reward——这是真机强化学习reward获取的可行路径（发言者5）。
-## 数据采集与仿真
-- **主流倾向**：**仿真数据与真实数据应结合使用**——海量仿真数据（含随机初始状态）配少量真机数据可显著提升策略成功率（发言者2，以300条仿真数据加20条真机数据成功率显著提升的实验结果为例）。
-- **主流倾向**：**无标注真实数据应成为2025年数据策略的重要方向**，不应继续纠结真实与仿真有标注数据的配比（发言者7，以Segment Anything、Depth Anything为据）。
-- **数据质量共识**：数据采集需**严格控制视角与标定**，并**记录物体运动信息**——Open X等数据集视角不固定、缺少物体运动数据，影响策略表现（发言者11，以ORKIT采集经验为例）。
-- **倾向性认识**：**现实世界是最好的仿真器**，reward采集是当前柔性物体等仿真难点的低成本替代方案；终极形态是通过可穿戴设备或脑机接口实现无感、多模态、大规模数据采集（发言者4，以叠衣服等柔性操作任务仿真需IPC等高性能技术、算力要求高且掌握者少为例）。
-- **互联网数据局限**：互联网视频与机器人所需数据**不匹配**——人类不会拍摄教机器人处理混乱状态（如从洗衣机取出揉成一团的衣服）的视频，此类常见任务恰是机器人最缺的数据（发言者4）。
-- **国产仿真系统**：有企业（如宋应）在布局国产替代，赌的是未来被卡脖子的风险；具体技术路线暂未深入讨论（发言者7）。
-# 未决分歧与后续探索
-## 具身智能形态
-- **人形 vs 特种形态**：发言者6认为人形机器人与特种机器人将并存——人形机器人因现实环境（桌椅等）为人设计而存在，特种机器人（车厂、微电子制造厂的机械臂）已实现97%以上自动化；发言者3以星际穿越中可变形的大方块机器人类比，提出具身形态是否会收敛为某种非人形形态的问题，未达成一致。
-## 世界模型
-- **世界模型是否需要三维表征与inductive bias**：发言者7认为CV界追求重建物理世界，可作为RL世界模型的工具，但当前三维表征在RL领域不受关注；发言者9认为CV世界模型对强化任务不必要，强化世界模型应针对任务，只需能更好学策略即可；发言者8从强化学习角度强调世界模型第一要义是可交互（可追溯至1990-91年Dyna-Q文章），同时希望引入3D信息或触觉等模态完善物理规律理解。发言者7提出数据量决定是否需要inductive bias，未来数据增多后可能不需要，并称梦想写一篇"data bias trade off"的论文，但未明确由谁跟进验证。
-- **世界模型能否统一**：发言者5提出世界模型可能无法统一——以游戏主角跳楼在游戏中稳落地、现实中死亡为例，认为相同输入不同输出是歧义问题，世界模型可能做不到统一，但policy有可能统一；发言者9提出不同物理结构可对应相同统一表征，发言者5回应需加condition，从可实现角度M个独立模型更简单，发言者9同意此观点但反问policy是否也需分成N个，发言者5认为policy可通过更长observation窗口体现condition，无需显式加入。双方未达成一致，也未明确验证路径。
-## 强化学习与模仿学习路线
-- **最终路线是先模仿后强化还是其他方式**：发言者9认为复杂任务应先模仿后强化，单独模仿或强化都不行——模仿到专家不够（人类行为不一定最优），强化from scratch样本复杂度不可接受；发言者10表示公司采用模型强化加机理融合方式，因监督学习数据分布不足、强化学习依赖仿真环境；发言者11认为模仿学习和强化学习不冲突，可先获取运动先验（有数据用模仿学习，无数据用强化学习生成）再通过RL完成任务。发言者5认为PID系统必有反馈，可作为强化学习的reward。未形成统一结论。
-## 数据采集方式
-- **遥操、仿真还是可穿戴设备**：发言者4主张reward采集，认为现实世界是最好的仿真器，但需可穿戴设备（终极形态可能是脑机接口或机电方式）扩展规模；发言者2认为仿真数据与真实数据结合可提升成功率——300条仿真数据加20条真机数据显著提升，但真机数据采集effort大；发言者7认为应加入无标注真实数据，2025年主题是推广无标注数据利用。发言者4指出互联网数据与机器人所需数据不匹配（如网上叠衣服视频是平铺状态，机器人需要的是从洗衣机取出揉成一团的状态），未达成一致。
-- **国产仿真系统是否必要**：发言者2提出中国是否强依赖英伟达生态的问题；发言者7回应称宋应等公司赌会被卡脖子而做国产替代，但工作人员暂不会直接touch这个生意，技术上会统一，business上复杂。未明确验证路径与跟进人。</t>
+          <t># 具身智能关键技术圆桌论坛
+## 研讨背景与议题
+本次圆桌论坛围绕具身智能领域的关键技术问题展开，主题涵盖具身智能的形态与硬件期待、世界模型的定义与构建、强化学习与模仿学习的路线选择、仿真与真实数据的采集与使用。参与方包括来自学术界与产业界的多位嘉宾及博士生，涵盖多模态大模型与具身智能融合、强化学习、柔性物体操作、具身世界模型、计算机视觉、机械与传感器等方向。论坛旨在通过跨方向的观点碰撞，探讨具身智能从模型架构到数据采集、从算法路线到产业落地的核心挑战与可能路径。
+1. **具身智能的形态与硬件期待**：探讨具身智能最终收敛为何种形态（人形机器人或特种机器人），以及硬件在寿命、可靠性、软硬件协同方面对算法与模型发展的支撑与制约。
+2. **世界模型的定义与构建**：围绕世界模型在强化学习与计算机视觉两个领域的不同定义、是否需要三维表征、以及世界模型能否统一构建等核心问题展开讨论。
+3. **强化学习与模仿学习的路线选择**：讨论在具身智能策略学习中，强化学习与模仿学习两大主流流派的关系，以及最终走向落地时二者应如何结合。
+4. **仿真与真实数据的采集与使用**：探讨仿真数据与真实数据在成本、质量、规模化采集方面的优劣，以及二者如何配比使用以提升策略成功率。
+## 核心观点
+### 具身智能的形态与硬件期待
+1. **硬件寿命与可靠性**：具身智能实验特别是大规模真机评估时，机器人易因模型预测失误撞桌等损坏，现有工业机械臂并非为此设计，需要个人柔顺等硬件结构以支持规模化评估（发言者4）。
+2. **软硬件协同优化**：具身智能是软硬件协同优化的范式，松灵两代产品对比显示第二代在遥操和策略部署上明显优于第一代；加凝胶的夹爪可反馈触觉且抓取更稳、摩擦力更好（发言者2）。
+3. **模型分层而非端到端统一**：若大模型从上到下完全统一，新硬件出现（如软体机器人）将导致大模型需完全重新训练；大脑可不变，小脑应自适应肢体变化，如手断后底层控制模型需适应新动力学（发言者5）。
+4. **人形与特种机器人并存**：从第一性原理出发，现实环境为人而设计，人形机器人（含灵巧手，如马斯克公司花一半精力做22自由度灵巧手）会占很大比例；特种机器人（如车厂、微电子制造厂中97%以上自动化的机械臂）也大量存在（发言者6）。
+### 世界模型的定义与构建
+1. **强化学习视角的可交互性**：世界模型概念可追溯至1990-91年Sutton的Dyna-Q文章，本质是黑盒，输入当前观测与动作、输出下一时刻观测；强化学习领域首要追求可交互性，因为最终目的是学策略（发言者8）。
+2. **CV视角的三维重建**：计算机视觉发展多年就是为了动态重建物理世界，可作为RL世界模型的工具；但三维表征技术栈深，RL博士生难以完全掌握，导致RL领域不太关注三维表征（发言者7）。
+3. **世界模型可能无法统一**：相同观测可能对应不同动力学（如游戏与现实中从楼上跳下结局不同），一个世界模型同时建模两个dynamics是歧义问题；但策略可能统一，因为同一玩家可在游戏中跳楼而在现实中避免（发言者5）。
+4. **CV世界模型对强化未必必要**：强化学习目标只是更好学策略，最终只需latent state或reward；CV世界模型若足够好可用于强化，但为解强化任务是否需要如此精细的模型存疑（发言者9）。
+5. **统一表征的可能性**：不同物理结构对应的模型应不同，但可考虑不同物理结构最后有相同的统一表征，从而仍是统一模型（发言者9）。
+6. **Inductive bias由数据量决定**：数据足够多时需要的inductive bias变少，数据少时需要的更多；如UniSim需要3D inductive bias，但未来数据scaling up后可能不需要，端到端方式更好（发言者7）。
+### 强化学习与模仿学习的路线选择
+1. **模型强化加机理融合**：公司实际部署采用模型强化加机理融合方式，因监督学习数据分布远不足以覆盖高维动作空间，纯强化学习强依赖仿真环境且sim-to-real迁移不佳；需限定强化学习的决策空间与任务设定，上层用强化学习做决策，底层用MPC、DWA等传统方法执行（发言者10）。
+2. **先模仿后强化**：复杂问题最终都先模仿后强化（如AlphaStar、GPT）；从零跑强化学习样本复杂度不可接受，模仿提供好的先验信息无坏处；单独模仿无法达到专家水平（除非任务就是模仿专家），单独强化也不行（除非任务足够简单）（发言者9）。
+3. **PID反馈可作为reward**：PID系统必有反馈元素，可完全拿反馈作为强化学习执行过程中的reward；过去用PID效果不够好，现在通过强化可做得更好（发言者5）。
+4. **模仿与强化不冲突**：两者只是获取运动先验的不同方式——有现成数据可从模仿学习角度做，没有数据（如人类复杂运动数据）可用强化学习先获取，再以BC形式建模latent，之后用RL快速找到对应latent完成任务（发言者11）。
+### 仿真与真实数据的采集与使用
+1. **数据质量的关键因素**：视角严重影响policy表现，Open X等数据集相机视角无法固定；标定（尤其手眼标定）至今解决不好；Open X等数据集只捕捉本体信息，缺少物体运动信息，Orkin Link采集时一定记录物体运动（发言者11）。
+2. **真实数据采集的规模化路径**：柔性体操作（叠衣服、系鞋带等）现有仿真模拟不准确且算力要求高，真实数据是更低成本方案，大自然就是最好的仿真器；但雇佣人员采集数据远不够，终极形态是脑机接口或肌电等无感多模态采集，现阶段可穿戴设备是较能scale的方案（发言者4）。
+3. **互联网数据与机器人数据不匹配**：互联网视频教人叠衣服时衣服是平展状态，但机器人见到的是从洗衣机拿出揉成一团的状态；人类习以为常不拍视频的事情恰是机器人最缺的数据（发言者4）。
+4. **仿真加少量真机数据显著提升成功率**：300条仿真数据训完策略直接真机测试成功率很低，但加上20条左右真机数据后成功率显著提升，即便用很原始的fine-tune方法（发言者2）。
+5. **真实与仿真数据选择看成本**：室内服务机器人真机数据收集有可行性，但自动驾驶中corner case让人去鬼探头太危险；应case by case看成本（发言者7）。
+6. **2025年主题：大规模利用无标注数据**：不要再讨论真实与仿真数据比例（1:9、2:8、5:5等），应像Segment Anything、Depth Anything一样，在自动驾驶和具身智能领域大规模利用无标注真实数据（发言者7）。
+7. **国产仿真系统**：有人（如宋应）赌会被卡脖子而做国产替代，这是business by business的生意；技术上最终会比较统一，但商业上很复杂（发言者7）。
+## 达成共识与解决方案
+未形成统一结论。本场研讨围绕具身智能的形态与硬件、世界模型、策略学习路线、数据采集四个议题展开，各方观点存在明显分歧，但形成了若干倾向性认识。
+1. **软硬件协同优化**：发言者2提出具身智能是软硬件协同优化的范式，以松灵两代产品对比为例，第二代在遥操与策略部署上明显优于第一代；加装凝胶的夹爪可反馈触觉且抓取更稳、摩擦力更好，说明硬件进步能带动算法提升，反之亦然。
+2. **模型分层优于端到端统一**：发言者5以人手受伤后大脑仍能工作、仅小脑需自适应为例，主张大模型不应从上到下完全统一，至少应分大脑与小脑两层，硬件变化时底层控制需自适应；发言者6认为现有多模态大模型微调方案不是终极形态，世界模型可能更接近人类水平，但也不是最终答案。
+3. **世界模型在RL与CV领域关注点不同**：发言者7指出RL领域世界模型更端到端，CV领域更关注解耦表征，这是学术发展阶段导致的现状；发言者8从强化学习视角强调世界模型第一要义是可交互，其次才是物理规律，最后才是引入3D等多模态信息。
+4. **世界模型难以统一、策略可能统一**：发言者5提出相同观测可能对应不同动力学（游戏与真实世界跳楼结局不同），世界模型面临歧义问题，难以用一个模型统一，但策略可能统一；发言者9提出不同物理结构可共享统一表征，发言者5回应这相当于给模型加condition，工程上M个独立模型比一个高维可控模型更简单。
+5. **复杂任务应先模仿后强化**：发言者9认为单独模仿或单独强化都不行，复杂任务应先模仿提供先验、再强化优化，阿尔法星和GPT均循此路径；发言者10从工程实践出发，认为当前监督学习数据分布不足以覆盖高维动作空间，纯强化学习强依赖仿真环境且迁移困难，应采用模型强化加机理融合的分层方式。
+6. **模仿学习与强化学习并非对立**：发言者11认为两者只是获取运动先验的不同方式，有数据可用模仿学习，无数据可用强化学习生成数据后再建模latent，并无本质冲突。
+7. **数据质量关键在于视角与物体运动记录**：发言者11指出Open X等数据集相机视角不固定、缺少物体运动信息，自建数据采集系统应严格控制视角与标定，并记录物体运动（刚体与关节体）。
+8. **真实数据采集需规模化、低成本**：发言者4主张真实数据是现阶段最低成本方案（大自然是最好的仿真器），但靠雇佣人员遥操采集难以达到GPT-3级别数据量，终极形态是脑机接口或肌电等无感多模态采集，现阶段可发展可穿戴设备；互联网视频与机器人所需数据不匹配（如无人拍摄从洗衣机取出乱衣并展平的过程）。
+9. **仿真数据与真实数据互补**：发言者2分享实验结论，300条仿真数据直接部署真机成功率很低，但加上20条左右真机数据微调后成功率显著提升；仿真数据可提供海量随机初始状态，弥补真机数据采集成本高的短板。
+10. **2025年应大规模利用无标注数据**：发言者7认为真实数据与仿真数据的选择应case by case看成本，并提倡2025年在自动驾驶与具身智能领域推广无标注真实数据（如Segment Anything、Depth Anything模式），不再纠结有标注数据比例。
+解决方案：
+1. **数据采集系统建设**：发言者11所在团队在自建数据采集系统中严格控制相机视角与标定，并记录物体运动信息（刚体与关节体），以弥补Open X等公开数据集视角不固定、缺少物体运动信息的缺陷。
+2. **仿真数据与真机数据混合训练**：发言者2团队采用仿真数据（海量随机初始状态）加少量真机数据（约20条）微调的方式训练策略，实验显示成功率较纯仿真数据显著提升。
+3. **分层策略学习框架**：发言者10所在公司在实际部署中采用模型强化加机理融合方式，上层用强化学习做决策，底层用MPC、DWA等传统方法执行，以规避监督学习数据不足与纯强化学习仿真迁移困难的问题。
+4. **可穿戴设备数据采集**：发言者4提出发展可穿戴式设备，在人们日常活动中无感采集多模态数据（触觉、力觉、视觉、听觉），作为规模化真实数据采集的现阶段可行方案。
+5. **无标注数据利用**：发言者7提出2025年在自动驾驶与具身智能领域推广大规模利用无标注真实数据（参照Segment Anything、Depth Anything模式），作为有标注仿真与真实数据的补充。
+6. **国产仿真系统布局**：发言者7提到已有团队（如宋应）基于脱钩卡脖子的预判布局国产仿真系统替代，但具体技术路线与产品形态未提及。
+## 未决分歧与后续探索
+- [ ] **具身智能最终形态**：发言者3提出具身智能的形态是像人形机器人还是科幻片中可变形的非人形态，发言者6认为人形机器人和特种机器人都会存在，人形机器人会有灵巧手，特种机器人大量存在于工业生产制造中；发言者7预测未来3-4波技术变革会深刻改变具身大模型的硬件和云端模型形态，但暂时无法预测。
+- [ ] **世界模型是否需要三维表征**：发言者7认为CV界追求重建物理世界，三维表征可作为RL世界模型的工具，但当前RL领域不关注三维表征；发言者9认为CV世界模型不必要，强化学习只需能帮助学策略的模型；发言者5认为世界模型可能无法统一，因为相同观测可能对应不同动力学，而策略可能统一；发言者9提出不同物理结构可能有统一表征，发言者5认为M个独立模型比一个高维可控条件的世界模型更简单。
+- [ ] **强化学习与模仿学习的路线选择**：发言者10表示公司采用模型强化加机理融合的方式，因为监督学习数据分布不足以覆盖高维动作空间，纯强化学习强依赖仿真环境且难以迁移；发言者9认为复杂任务应先模仿后强化，单独模仿或强化都不行；发言者5认为PID系统必有反馈，可作为强化学习的reward；发言者11认为模仿学习和强化学习并不冲突，只是获取运动先验的不同方式。
+- [ ] **仿真数据与真实数据的比例**：发言者2提到仿真数据加少量真机数据可显著提升成功率，300条仿真数据加上20条真机数据成功率有显著提升；发言者7认为真实数据与仿真数据的选择应看成本，并提倡2025年大规模利用无标注数据；发言者4认为reward采集是低成本方案，但需要可穿戴设备等规模化方式。
+- [ ] **国产仿真系统能否替代英伟达生态**：发言者2提出中国是否强依赖英伟达生态的问题；发言者7表示宋应等公司赌的是以后会被卡脖子，在做国产替代，但具体技术会统一，商业上比较复杂。</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>77.59999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21458/7153</t>
+          <t>21458/5558</t>
         </is>
       </c>
     </row>
@@ -2934,69 +2930,60 @@
       <c r="C7" t="inlineStr">
         <is>
           <t># 庭审概况
-本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷二审，由最高人民法院公开开庭审理，审判长李少平与审判员魏文超、黄年、王海峰、葛洪涛组成合议庭。庭审围绕三个争议焦点展开：国开行是否尽到审查义务并善意取得抵押权、一审判决对罚息复息的计算及起算日期是否错误、东源煤电及东源煤业是否应连带给付违约金。各方充分发表意见后，合议庭休庭评议提出调解方案，各方均无异议，达成调解协议。
+本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司（东源煤电）、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷二审，由最高人民法院审判员李少平担任审判长，与审判员魏文超、黄年、王海峰、葛洪涛组成合议庭，法官助理张瑞，公开开庭审理。各方当事人均到庭，委托代理人出庭。庭审围绕三个争议焦点展开：国开行是否尽到审查义务并构成善意取得抵押权；一审判决对案涉借款罚息、复息的计算及起算日期是否认定错误；东源煤电、东源煤业是否应连带给付违约金。各方充分辩论后，合议庭休庭评议并提出调解方案，各方均无异议，同意签署调解协议。
 # 原告诉称与被告辩称
 | 方 | 诉讼请求/答辩意见 | 事实与理由 |
 | --- | --- | --- |
-| 上诉人（国家开发银行） | 请求撤销一审判决，改判支持其利息、罚息、复利及违约金等诉讼请求 | 主张已按央行规定查询融资租赁登记系统，未发现登记，审查义务仅限于抵押人曲靖电力公司；利息应自2017年12月21日计算至2018年6月12日合计21,795,727.68元，罚息自2018年6月13日起算合计41,050,579.57元，复利自2018年3月21日起算合计1,918,206.23元；依据合同第24条第3项，东源煤电、东源煤业应连带给付千分之一违约金 |
-| 被上诉人（东源煤电、东源煤业、东源曲靖电力） | 请求驳回上诉，维持原判 | 主张2015年12月2日邮件已告知设备存在融资租赁，国开行应尽注意义务；宣布贷款提前到期应限期偿还而非立即偿还；依据《人民币利率管理规定》第21条，罚息不应作为复利计算基数；国开行未举证证明违约行为且未发出限期纠正函件 |
-| 被上诉人（招银租赁） | 请求驳回上诉，维持原判 | 主张国开行未在抵押时点查询融资租赁登记系统，不构成善意；东源煤电对设备出资系无权处分，因招银租赁2012年已取得设备所有权；国开行审查义务应扩展到东源煤电 |
+| 上诉人（国家开发银行） | 请求撤销一审判决，改判支持其利息、罚息、复利计算主张及违约金请求 | 主张已按央行规定查询融资租赁登记系统，审查义务仅限于抵押人曲靖电力公司，构成善意取得；利息应自2017年12月21日计算至2018年6月12日，罚息自2018年6月13日起算，复利自2018年3月21日起算；依据借款合同第24条第3项主张违约金 |
+| 被上诉人（东源煤电、东源煤业、东源曲靖电力） | 请求驳回上诉，维持一审判决 | 主张国开行未在抵押时点查询融资租赁登记系统，未尽注意义务；国开行宣布贷款提前到期未给合理期限，罚息不应作为复利计算基数；国开行未举证证明违约行为，且未按合同约定先限期纠正 |
+| 被上诉人（招银租赁） | 请求驳回上诉，维持一审判决 | 主张国开行未在抵押时点查询，不构成善意；东源煤电出资行为系无权处分，电力公司未取得所有权；国开行审查义务应扩展至东源煤电 |
 # 举证与法庭调查
 ## 举证与质证
-- **东源方提交**：2015年12月2日邮件及《东源公司融资情况统计表》，证明已告知国开行招银租赁对恩洪电厂设备资产已办理抵押登记，国开行抵押物为恩洪电厂设备在建工程、抵押手续正在办理；国开行质证认为该邮件系贷后审查材料，不能证明已履行告知义务。
-- **国开行提交**：2018年9月对曲靖电力公司的融资租赁查询证书，证明已尽查询义务；招银租赁质证认为该查询证书不符合要求，应提供2015年12月办理抵押时点的查询结果。
-- **国开行提交**：证据54页、58页权属证明材料和股东会决议，证明案涉设备所有权属曲靖电力公司；招银租赁未提出异议。
-- **招银租赁提交**：回租设备清单（证据第7页），载明设备名称、生产厂家、出厂日期2012年3月1日；国开行质证认为清单未载明设备型号，且与现场调查的铭牌生产日期（2013年以后）不符。
-- **招银租赁提交**：2013年和2015年审计报告（证据82页、95页），载明曲靖电力公司注册资本4亿元且已实缴；国开行质证认为该报告已载明设备出资事项。
-- **招银租赁提交**：融资租赁登记系统初始登记附件清单，载明设备名称、数量、原值、净值、出厂时间、生产厂商及存放地点（恩洪矿区煤矸石电厂）；国开行质证认为设备为通用设备，无唯一标识码。
-## 证人、鉴定与其他来源陈述
-- **东源方陈述**：东源煤电以煤炭开采和经营为主营业务，受宏观经济下行影响，2015年下半年出现资金链断裂，2019年2月19日人民法院受理破产重整时负债高达76.2亿元，去产能涉及安置职工13000多人，最困难时近半年未发工资。
+- **东源公司融资情况统计表（东源方提交）**：东源方主张2015年12月2日邮件所附统计表显示招银租赁抵押物已登记，国开行应尽注意义务；国开行质证认为该表仅载明招银租赁设备已登记，与国开行拟抵押设备不同，不能得出已告知的结论。
+- **回租设备清单（招银租赁一审提交）**：国开行质证认为清单仅载明设备名称和生产厂家，未载明型号，且出厂日期为2012年3月1日，与国开行现场调查核实的铭牌生产日期（2013年11月、12月、2014年3月）不符，不能证明系同一设备。
+- **权属证明材料及股东会决议（国开行提交，证据54页、58页）**：国开行主张证明案涉设备所有权属曲靖电力公司，其已尽审慎义务；对方未提出实质异议。
+- **融资租赁登记查询证书（国开行提交，证据108页）**：国开行主张查询结果显示曲靖电力公司名下无融资租赁登记；招银租赁质证认为该证书系2018年9月出具，不符合应在抵押时点（2015年12月）查询的要求。
+- **审计报告（招银租赁一审提交，证据82页、95页）**：国开行主张报告载明曲靖电力公司注册资本4亿元且已实缴，证明设备出资事项已披露；招银租赁未否认。
+- **借款合同（国开行提交）**：国开行主张合同第6条第4款约定对逾期借款利息按罚息利率计收复利，第24条第3项约定违约金；东源方质证认为合同约定不明确，属格式条款，应作不利于提供方解释。
 ## 法官询问
-- **审判长询问**：生产设备作为动产，各方如何理解中国人民银行征信中心融资租赁登记的性质及法律后果？国开行代理人认为系行业强制性规范，目的是防范金融风险；东源方代理人认为系行业指导性规范，不产生物权后果；招银租赁代理人认为系权利公示，可能产生对抗效力，但不影响所有权设立转移。
-- **合议庭成员询问**：央行融资租赁登记系统有几种查询方式？国开行代理人称仅能按查询单位查询；招银租赁代理人称可按公司名称或设备查询，但设备查询涉及种类物区分问题。
-- **合议庭成员询问**：案涉5套设备登记时是否登记唯一识别码？招银租赁代理人称设备为种类物，无唯一识别码，未登记。
-- **合议庭成员询问**：国开行内部是否有规定要求保留未查询到结果的记录作为风控材料？国开行代理人称无此规定，因未查询到结果故未保留。
-- **合议庭成员询问**：国开行认为查询了曲靖电力公司登记信息未查到结果，以此免责的逻辑？国开行代理人称查询系基本义务，未查到结果说明无过失。
-- **合议庭成员询问**：融资租赁登记系统中设备唯一标识码是否必填项？招银租赁代理人称非必填项，案涉设备无唯一识别码。
-- **合议庭成员询问**：设备安装后发电机上是否有唯一标识码？招银租赁代理人称铭牌上只有型号和参数，无唯一标识码。
-- **合议庭成员询问**：违反查询规范在多大程度上导致融资租赁司法解释第9条第2款的法律后果，是基本查询义务还是全面审慎义务？国开行代理人认为系基本义务，审查义务限于抵押人；招银租赁代理人认为系严格义务，未查询即不构成善意。
-- **合议庭成员询问**：若银行通过其他途径知晓动产属融资租赁物，是否相当于已了解风控情况？国开行代理人称基本义务必须履行；东源方代理人称仍应查询；招银租赁代理人称仍须通过央行系统查询。
-- **合议庭成员询问**：各方对融资租赁司法解释第9条第2款举证责任如何分担？国开行代理人称按谁主张谁举证原则；招银租赁代理人称第1、2、4项由出租人举证，第3项由第三人（国开行）举证。
-- **审判长询问**：因不同登记机构产生的登记信息冲突，各方有何意见和建议？国开行代理人称系系统信息不完整、条块分割所致，建议整合；东源方代理人称非专业机构，提不出成熟建议；招银租赁代理人建议从立法、行业协会、操作技术层面改进。
+- **【融资租赁登记性质】**：审判长询问各方如何理解央行征信中心融资租赁登记的性质及法律后果。国开行认为系行业强制性规范，旨在防范金融风险；东源方认为系行业指导性规范，不产生物权后果；招银租赁认为系权利公示，可能产生对抗效力，但不影响所有权设立转移。
+- **【查询方式】**：审判员询问央行融资租赁登记系统的查询方式。国开行称仅能按单位查询；招银租赁称可按公司名称或设备查询，但设备查询涉及种类物区分问题。
+- **【识别码登记】**：审判员询问案涉5套设备是否登记唯一识别码。招银租赁称设备无唯一识别码，未登记；东源方补充称初始登记时将租赁物清单作为附件上传，载明存放地点为恩洪矿区煤矸石电厂。
+- **【查询义务程度】**：审判员询问查询义务是基本义务还是全面审慎义务。国开行认为系基本义务，仅需查询抵押人名下登记；招银租赁认为系严格义务，未查询即不构成善意。
+- **【其他途径知晓】**：审判员询问若银行通过其他途径知晓融资租赁，是否仍需查询。国开行认为仍需查询；招银租赁认为仍需通过央行系统查询，以确定标准衡量善意。
+- **【举证责任】**：审判员询问融资租赁司法解释第9条第2款举证责任分担。国开行认为按谁主张谁举证原则；招银租赁认为第1、2、4项由出租人举证，第3项由第三人（国开行）举证。
+- **【登记信息冲突】**：审判长询问各方对登记信息冲突的意见。国开行认为系系统信息不完整、条块分割所致；东源方称非专业机构，提不出建议；招银租赁建议从立法、行业协会、技术层面改进。
 ## 争议焦点与辩论
-- **争议焦点一：国开行是否尽到审查义务，是否构成善意取得抵押权**
-  - **国开行主张**：已按央行规定查询融资租赁登记系统，未发现登记；设备为通用设备无唯一标识码，审查义务仅限于抵押人曲靖电力公司；抵押设备铭牌生产日期均在2013年以后，与招银租赁回租设备清单记载的出厂日期2012年3月1日不符；已对设备所有权尽审慎义务，构成善意取得。
-  - **东源方主张**：2015年12月2日邮件已告知设备存在融资租赁，设备名称相同且用红色标注，国开行应尽注意义务；国开行未提供证据证明已做区分。
-  - **招银租赁主张**：国开行未在抵押时点（2015年12月）查询融资租赁登记系统，不构成善意；东源煤电对设备出资系无权处分，因招银租赁2012年已取得设备所有权；国开行审查义务应扩展到东源煤电。
+- **争议焦点一：国开行是否尽到审查义务、是否构成善意取得抵押权**
+  - 国开行主张：审查义务仅限于抵押人曲靖电力公司，已按央行规定查询融资租赁登记系统且未发现登记，构成善意取得；设备为通用设备无唯一标识码，无法进一步查询。
+  - 东源方主张：2015年12月2日邮件所附统计表显示招银租赁设备已登记，国开行应尽注意义务；国开行未提供证据证明已作区分。
+  - 招银租赁主张：国开行应在抵押时点（2015年12月）查询，而非提供2018年9月查询证书；东源煤电系借款人及抵押人全资控股母公司，国开行审查义务应扩展至东源煤电；东源煤电出资行为系无权处分，电力公司未取得所有权。
 - **争议焦点二：一审判决对案涉借款罚息、复息的计算及起算日期是否认定错误**
-  - **国开行主张**：利息自2017年12月21日计算至2018年6月12日合计21,795,727.68元，罚息自2018年6月13日起算合计41,050,579.57元，复利自2018年3月21日起算合计1,918,206.23元；合同第6条第4款明确约定罚息计收复利。
-  - **东源方主张**：借款合同第24条第2款第2项约定宣布贷款提前到期时应限期偿还，而非立即偿还；依据《人民币利率管理规定》第21条，罚息不应作为复利计算基数；合同为格式文本，对条款理解不同时应作出对提供方不利的解释。
+  - 国开行主张：利息自2017年12月21日计算至2018年6月12日，利息合计21,795,727.68元；罚息自2018年6月13日计算至2019年2月19日，罚息41,050,579.57元；复利自2018年3月21日计算至2019年2月19日，复利1,918,206.23元。
+  - 东源方主张：国开行2018年6月13日发函要求当天偿还全部贷款，未给合理期限，不符合合同约定；罚息不应作为复利计算基数，依据《人民币利率管理规定》第21条及最高院判例；复利再计算复利无合同依据。
 - **争议焦点三：东源煤电、东源煤业是否应当连带给付违约金**
-  - **国开行主张**：依据借款合同第24条第3项，被上诉人违约应支付千分之一违约金；东源煤电未按合同第13条、第14条配合办理账户管理及柜台前移手续。
-  - **东源方主张**：国开行未举证证明东源煤电存在违约行为，且未按合同约定先限期纠正，举证不能的后果应由其自行承担。
+  - 国开行主张：依据借款合同第24条第3项，被上诉人违约应支付千分之一违约金；东源煤电未按合同第13条、第14条配合办理账户管理及柜台前移手续。
+  - 东源方主张：国开行未举证证明东源煤电违反柜台前移和账户管理约定；国开行未按合同约定先发出限期纠正函件，无权主张违约金。
 # 庭审结果
-- **争议焦点一**：国开行是否尽到审查义务，是否构成善意取得抵押权。各方意见分歧，未单独裁判。
-- **争议焦点二**：一审判决对案涉借款罚息、复息的计算及起算日期是否认定错误。各方意见分歧，未单独裁判。
-- **争议焦点三**：东源煤电、东源煤业是否应当连带给付违约金。各方意见分歧，未单独裁判。
-- **调解结果**：各方当事人自愿达成调解协议，合议庭予以确认，并出具调解书。
-  - 国开行对东源煤电的债权扣除破产中已清偿本金外，利息、罚息、复利合计6474.4513万元。
-  - 招银租赁对涉案6项设备享有所有权，对应债权数额1377.4137万元；国开行对93项设备有抵押权。
-  - 招银租赁和国开行对案涉全部发电设备整体盘活处置，变现价款双方各得50%，费用各担50%。
-  - 调解书生效后20日内，由国开行向一审法院提出执行申请，启动司法处置程序。
-  - 若司法变现不能，国开行和招银租赁放弃对案涉设备的权益，由东源曲靖电力自主生产经营。
-  - 东源曲靖电力承担案涉设备管理费用，并无条件配合司法处置。
-  - 各方对一审判决第2项、第4项无争议，按照其判项内容在调解书中确认。
-  - 一审诉讼费用中对于国开行诉请部分按照一审判决执行；对于招银租赁诉请部分的诉讼费用，由二审法院按照规定，根据争议财产对应的债权数额计算后，由国开行承担。
-  - 二审诉讼费用由法院依法确定后，由国开行和东源煤电各承担50%。
-  - 本协议签订后，各方之间就本案涉及的问题不再存在任何争议。</t>
+- **调解协议达成**：经合议庭主持调解，各方当事人自愿达成调解协议，均无异议，法院予以确认，将出具调解书。
+- **债权数额确认**：国开行对东源煤电的债权扣除破产已清偿本金外，利息、罚息、复利合计6474.4513万元。
+- **设备权属确认**：招银租赁对涉案6项设备享有所有权，对应债权数额1377.4137万元；国开行对93项设备有抵押权。
+- **设备处置安排**：案涉全部发电设备整体盘活处置，变现价款双方各得50%，费用各担50%。
+- **执行申请**：调解书生效后20日内，由国开行向一审法院提出执行申请，启动司法处置程序。
+- **未实现债权处理**：国开行、招银租赁未实现的债权待执行法院出具体本裁定后，按照破产重整计划中的预留方案实现债权；若破产管理人不予纳入预留方案，由东源煤电按照此前招银租赁在东源煤电破产重组程序中有担保清偿方案予以清偿。
+- **设备权益放弃**：若司法变现不能，国开行和招银租赁的权益通过前述方法实现后均放弃对案涉设备的权益，由东源曲靖电力自主生产经营。
+- **费用承担**：案涉设备管理费用由东源曲靖电力承担，东源曲靖电力无条件配合司法处置。
+- **一审判决确认**：各方对一审判决第2项、第4项无争议，按照其判项内容在调解书中确认。
+- **诉讼费用**：一审诉讼费用中对于国开行诉请部分按照一审判决执行；对于招银租赁诉请部分的诉讼费用，由二审法院按照规定，根据争议财产对应的债权数额计算后，由国开行承担；二审诉讼费用由法院依法确定后，由国开行和东源煤电各承担50%。
+- **争议了结**：本协议签订后，各方之间就本案涉及的问题不再存在任何争议。</t>
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>83.8</v>
+        <v>76.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28485/3962</t>
+          <t>28485/3486</t>
         </is>
       </c>
     </row>
@@ -3152,46 +3139,49 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t># 项目概况
-本次会议为原占比二玉米面加工厂项目中期验收会，验收组代表王总汇报了验收工作总体进展：已提前于18、19号介入项目摸排，20号召开首次会议，目前已完成卢萨卡点除带料加工调试以外的全部验收工作，蒙泽点已全部完成，某皮卡点现场验收尚未开展，其内业资料已提前拿到卢萨卡点。内业检查方面，管理组和技术组基本能按合同组建执行团队，编制了施工组织计划、管理计划、实施细则及专项预案，内业资料总体满足项目有关标准和规范要求，竣工文件基本达到组卷和成册要求，但分类整理和签字规范性需进一步完善。外业检查方面，建筑部分主要建材从国内采购或从卢萨卡集中采购，内在品质和外在表观达到良好标准；安装部分钢结构材料从国内定制，施工工艺和外观质量满足规范标准；设备部分参照中国标准定制，蒙泽点已进行投料试运行，工艺设备运行正常，产能符合设计指标。现场检查发现若干问题：某厂区非主要通道混凝土路面有少量开裂现象，监控管线接头处有脱落，卢萨卡点提升桶位置存在雨水倒灌风险，廊桥横向竖条数量不足建议加密。验收组提出整改要求：完善人员履约资料（进出场时间、护照及证件有效期，技术组人员统计需包含厂家服务人员），内业资料按规范分类成册汇总至卢萨卡，竣工图需完善，现场整改需检查局部损伤、卫生、排水、混凝土路面裂纹、管线接头、雨水倒灌、廊桥竖条等。管理组田组长表示会后与技术组细化问题并制定方案处理，技术组龚总表示已开展人员护照证书收集，将按援外项目执行手册汇总资料，编制现场整改方案。合作局领导金昌柱强调：相关方尽快补充资料，与验收组做好沟通，避免遗留未决事项；重视混凝土路面开裂问题，要求管理组和总包单位共同分析成因，结合赞比亚气候特点制定科学合理的整改方案；整改须在出报告前完成，形成闭环，验收组需复核；做好成品保护，及时修补破损。公司领导林总要求按合同和标准仔细验收，提醒当地用户建议，注意交通安全和疫情防控。关于不可预见费使用，项目有动用情况，需在原合同、原设计、原投资控制基础上增加动用，依据证据和数据必须充分无误，验收组将利用后续时间做专门对接。
-# 进度追踪
+          <t># 玉米面加工厂项目中期验收会议
+## 项目概况
+本次会议为原占比二玉米面加工厂项目中期验收会议，由验收组代表王总主持并汇报。验收组于18、19号提前介入项目摸排，20号召开首次会议，目前已完成卢萨卡点除带料加工调试以外的全部验收工作，蒙蒙泽点已完成全部验收，姆皮卡点现场验收尚未开展，内业资料已提前拿到卢萨卡点。内业检查方面，管理组和技术组按合同组建执行团队，编制施工组织计划、管理计划、实施细则及专项预案，内业资料基本满足规范要求，竣工文件基本达到组卷成册要求，但分类整理和签字规范性需完善。外业检查方面，建筑、安装、设备三部分总体评价良好，蒙蒙泽点工艺设备运行正常，产能符合设计指标。财务方面符合规范。验收组提出人员履约、内业资料、现场实体三方面整改要求，合作局领导金昌柱和公司领导林总分别作出指示，强调整改闭环、成品保护与交通安全。
+## 进度追踪
 | 模块 | 进展 | 状态 |
 | --- | --- | --- |
-| 卢萨卡点验收 | 已完成除带料加工调试以外的所有验收工作 | ✅已完成 |
-| 蒙泽点验收 | 已完成全部验收工作，包括顺带完成的带料调试试生产 | ✅已完成 |
-| 某皮卡点验收 | 现场验收尚未开展，内业资料已提前拿到卢萨卡点 | ⏸未开始 |
-| 内业资料检查 | 管理组、技术组按合同组建执行团队，编制施工组织计划、管理计划、实施细则及专项预案，内业资料总体满足规范要求，竣工文件基本达到组卷成册要求，但分类整理和签字规范性需完善 | 🔄进行中 |
-| 外业检查-建筑 | 主要建材从国内采购或从卢萨卡集中采购，内在品质和外在表观达到良好标准，发现某厂区非主要通道混凝土路面少量开裂 | 🔄进行中 |
-| 外业检查-安装 | 钢结构材料从国内定制，施工工艺和外观质量满足规范标准，发现监控管线接头脱落 | 🔄进行中 |
-| 外业检查-设备 | 设备参照中国标准定制，蒙泽点已投料试运行，工艺设备运行正常，产能符合设计指标 | ✅已完成 |
-| 财务检查 | 账户设置、资金往来、银行开户等符合财务处理规范和标准 | ✅已完成 |
-# 风险预警
+| 卢萨卡点验收 | 已完成除带料加工调试以外的所有验收工作 | 已完成 |
+| 蒙蒙泽点验收 | 已完成全部验收工作，包括带料调试、试生产及外方人员操作培训 | 已完成 |
+| 姆皮卡点验收 | 现场验收尚未开展，内业资料已提前拿到卢萨卡点 | 未开始 |
+| 内业资料检查 | 管理组和技术组按合同组建执行团队，编制施工组织计划、管理计划、实施细则及专项预案，内业资料基本满足规范要求，竣工文件基本达到组卷成册要求，但分类整理和签字规范性需完善 | 进行中 |
+| 外业检查-建筑部分 | 主要建材从国内采购或从卢萨卡集中采购，内在品质和外在表观达到很好标准，但存在局部装饰装修损伤、厂区排水需清理、蒙蒙泽厂区混凝土路面少量开裂 | 进行中 |
+| 外业检查-安装部分 | 钢结构材料从国内定制，施工工艺和外观质量满足规范标准，但监控管线接头处有脱落，卢萨卡点提升桶位置雨水可能倒灌，廊桥横向仅三个竖条建议加密 | 进行中 |
+| 外业检查-设备部分 | 参照中国标准定制三套成套设备，厂家高峰期派十几名人员现场指导安装，蒙蒙泽点工艺设备运行正常，工艺流程满足生产要求，产能符合设计指标，机电设备安装符合国家质量检验标准 | 已完成 |
+| 财务检查 | 账户设置、资金往来、银行开户等完全符合财务处理规范和标准 | 已完成 |
+## 风险预警
 | 风险/瓶颈 | 等级 | 影响 | 责任人 | 应对计划 |
 | --- | --- | --- | --- | --- |
-| 混凝土路面开裂 | 中 | 可能影响项目整体评价，存在大面积开裂隐患，移交外方后影响对外形象 | 管理组、总包单位 | 共同分析成因，结合赞比亚气候特点制定科学合理的整改方案，出报告前完成整改，验收组复核 |
-| 卢萨卡点提升桶位置雨水倒灌 | 中 | 赞比亚雨季雨量大、风大，雨水可能倒灌影响设备运行 | 施工组 | 检查原设计施工是否足以解决，必要时增加覆盖面积或采取技术措施 |
-| 监控管线接头脱落 | 中 | 设备启动震动导致接头脱落，可能引起机械故障 | 施工组 | 全面检查管线接头，保证有效性和安全性 |
-| 廊桥竖条数量不足 | 低 | 横向仅三个竖条，巡检维护人员安全保障不足 | 施工组 | 中间再加两个竖条，加密处理 |
-| 人员履约资料不完善 | 中 | 个别人员进出场时间、护照及证件有效期需完善，技术组人员统计未包含厂家服务人员 | 执行单位（技术组、管理组） | 收集护照证书，与国内人力资源对接核实延期或更新 |
-| 内业资料分类整理和签字不规范 | 中 | 竣工文件基本组卷成册，但分类整理和签字规范性需完善 | 执行单位 | 按规范汇总至卢萨卡，分类成册，按竣工文件归档要求组卷 |
-| 某皮卡点路途遥远、交通状况不佳 | 中 | 存在交通安全风险，且正值雨季 | 验收组 | 注意交通安全和疫情防控，安全完成验收任务 |
-| 疫情及雨季影响 | 中 | 可能导致验收工作推迟或受阻 | 验收组、参建单位 | 提前介入摸排，利用前方资源顺带完成调试，注意防疫 |
-# 后续计划
-- **完善人员履约资料**：执行单位（技术组、管理组）收集所有参与项目现场人员的护照、证书，统计进出场时间，与国内人力资源对接核实证件延期或更新情况，确保验收报告闭合。
-- **汇总内业资料**：技术组按援外项目执行手册管理办法，在验收完成后第一时间将三个厂区资料（含竣工图）汇总至卢萨卡，分类组卷、编码。
-- **整改现场问题**：施工方按方案编制要求逐一整改，包括混凝土路面裂纹重新清理并用防水材料封闭、监控管线接头全面检查、卢萨卡点提升桶位置雨水倒灌技术措施、廊桥竖条加密。
-- **分析路面开裂成因**：管理组和总包单位共同研究，结合赞比亚气候特点制定科学合理的整改方案，最迟在出报告前完成整改，验收组复核形成闭环。
-- **做好成品保护**：移交外方前检查局部损伤、装饰装修位置、卫生，及时修补破损，雨季前排查厂区及办公区排水（屋面、室外通道）。
-- **对接不可预见费**：验收组与施工单位完善动用不可预见费的依据、证据和数据，确保充分无误，后续专门对接。
-- **开展某皮卡点验收**：验收组会后安排剩余某皮卡点现场验收，注意路途交通安全及疫情防控。</t>
+| 蒙蒙泽厂区混凝土路面开裂 | 中 | 可能影响项目移交后使用，存在大面积开裂隐患 | 管理组、总包单位 | 共同分析成因，制定科学合理整改方案，出报告前完成整改，验收组复核 |
+| 卢萨卡点提升桶位置雨水倒灌 | 中 | 存在水患风险，可能影响设备运行 | 施工组 | 检查并考虑增加覆盖面积或采取技术措施解决 |
+| 监控管线接头脱落 | 中 | 可能引起机械故障 | 施工组 | 全面检查，保证有效性和安全性 |
+| 人员履约资料不完善 | 中 | 个别人员进出场时间、护照及特种人员证件有效期需完善，技术组人员统计未包含厂家服务人员 | 管理组、技术组 | 完善人员统计和护照证件，与国内人力资源对接 |
+| 内业资料分类整理和签字不规范 | 低 | 竣工文件组卷成册需完善 | 执行单位 | 按国家规范汇总至卢萨卡，分类成册，规范签字 |
+| 姆皮卡点路途遥远、路况不好 | 中 | 存在交通安全风险 | 验收组 | 注意交通安全，做好疫情防控 |
+| 疫情及雨季影响 | 中 | 存在防疫和交通安全风险 | 验收组、参建单位 | 做好疫情防控，注意雨季交通安全 |
+## 后续计划
+- [ ] **细化并落实整改方案**（管理组田组长、技术组龚总 ｜ 会后 ｜ 整改方案）：管理组和技术组会后共同细化验收组提出的问题，制定方案处理并落实整改。
+- [ ] **汇总三个厂区资料至卢萨卡**（技术组龚总 ｜ 验收完成后第一时间 ｜ 分类组卷及编码）：严格按照验收组要求及援外项目执行手册管理办法，将三个厂区资料（含竣工图）汇总于卢萨卡，分类组卷及编码。
+- [ ] **分析混凝土路面开裂成因并制定整改方案**（管理组、总包单位 ｜ 出报告前 ｜ 整改方案）：合作局领导要求共同分析蒙蒙泽厂区混凝土路面开裂原因，结合赞比亚气候特点制定科学合理整改方案，出报告前完成整改，验收组复核。
+- [ ] **专题研究混凝土路面开裂问题**（王总 ｜ 会后 ｜ 技术研究结论）：王总负责追溯，会同相关单位收集情况做专题技术研究，最不利情况局部处理，不影响项目最终评价。
+- [ ] **完善不可预见费使用资料**（验收组、施工单位 ｜ 后续专门对接 ｜ 依据证据数据）：项目有动用不可预见费情况，需完善相关依据证据和数据，确保充分无误。
+- [ ] **完善人员履约资料**（管理组、技术组 ｜ 验收报告形成前 ｜ 人员统计、护照证件）：完善个别人员进出场时间、护照及特种人员证件有效期，技术组人员统计纳入厂家服务人员。
+- [ ] **完善内业资料分类整理与签字**（执行单位 ｜ 验收后 ｜ 竣工文件组卷）：按国家规范将资料汇总至卢萨卡，分类成册，规范质检及验收签字。
+- [ ] **现场实体整改**（施工组 ｜ 移交前 ｜ 整改完成）：检查修补局部装饰装修损伤，清理排查厂区排水，封闭混凝土路面裂纹，检查监控管线接头，处理卢萨卡点提升桶雨水倒灌及廊桥竖条加密。
+- [ ] **做好成品保护与修补**（管理组、总包单位 ｜ 移交外方前 ｜ 成品完好）：因工程实体完工时间较长，移交前继续做好成品保护，及时修补破损。
+- [ ] **开展姆皮卡点现场验收**（验收组 ｜ 会后安排 ｜ 验收完成）：姆皮卡点路途遥远、路况不好，注意交通安全与疫情防控，验收组将及时安排后续工作。</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>65.90000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11110/2602</t>
+          <t>11110/2454</t>
         </is>
       </c>
     </row>
@@ -3401,99 +3391,98 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t># 发布会概况
-本次中金宏观策略争论会议于周一早间举行，由中金公司策略组刘刚凯文（Kevin）主持，面向投资者客户，围绕近期海外宏观热点与国内行业机会展开解读。会议覆盖四大板块：大美丽法案及信用周期分析、关税更新、港股流动性、光伏反内卷、人形机器人、游戏板块。风光公用事业首席分析师刘佳妮、机械军工分析师郭文秀、传媒行业首席分析师张雪琴分别就光伏、人形机器人、游戏行业进行专题分享。整体基调为结构性看好，宏观层面认为信用周期转好但三季度有流动性波折，行业层面光伏反内卷有望夯实底部、人形机器人处于迷茫期到商业兑现的过渡阶段、游戏板块调整后有望戴维斯双击。关键数字锚点：纳斯达克自底部反弹35%、大美丽法案提高债务上限5万亿美元、6月游戏版号单月发放158个（2018年以来最高）。
-会议未设问答环节，后续安排为下周同一时间继续举办。
-# 核心信息
-## 大美丽法案与信用周期
-- **法案三大内容**：`大美丽法案`提高债务上限约**5万亿美元**（消除违约风险、恢复政府支出能力）；延长2017年减税法案（非新增减税，避免年底自动大幅加税），额外支出约**3.4万亿美元**、年均**3400亿美元**，同时削减其他支出（含减少新能源补贴约1.4万亿美元）；取消`899条款`（美债利息所得税，此前引发主权基金抛售美债担忧）。
-- **财政赤字与关税收入对冲**：按约10%有效税率测算，关税年收入约**3000–4000亿美元**，可基本覆盖年均3400亿美元额外支出，新测算赤字率维持在**5–6%**，未大幅扩张。
-- **三季度流动性抽水**：债务上限提高后财政部需回补`TGA账户`，三季度预计发债约**1万亿美元**，边际收紧美元流动性；参照2023年三季度（发债1万亿美元、美债利率从3.8%升至5%、美股跌约4–5%），本次因期限溢价已处2013年以来高位，利率上行幅度或不及当时，但需过坎。
-- **信用周期框架**：美国经济如篝火自然修复，上半年受`DeepSeek`冲击、财政收缩、`4月2日对等关税`三盆冷水压制，下半年低基数下环比改善；中国如煮水需持续添柴，924以来高基数下边际或此消彼长。据此判断四季度美元可能小幅走强、美股可能反弹跑赢。
-## 关税更新
-- **四点核心判断**：关税必须做（支撑财政收入）；需维持一定税率（当前豁免10%水平即可收3000–4000亿美元）；不能太高（通胀受不了）；市场逐渐脱敏、静观其变，高威胁税率可能是谈判技巧。
-- **新变化与有效税率**：时间拖后（原7月9日达成）；相比`4月2日对等关税`大部分税率回落（巴西除外）；加拿大、墨西哥、欧盟因贸易占比高单列，其余国家占比小（最高日本4.5%）。测算有效税率当前**10–12%**，8月1日全恢复则**10–15%**，最极端**18%**。
-- **通胀与美联储**：有效税率未大幅提高，通胀压力缓慢抬升，年底约**3.3–3.4%**，不大幅改变通胀路径；美联储7月降息勉强，9月及四季度后仍可降。
-- **对华关税与转口限制**：对华关税约**40–50%**（2018年约20%为基数）；越南协议转口限制**40%**、英国协议亦有转口限制，需关注`8月1日`关税恢复、`8月12日`中美谈判进展及转口限制。
-## 港股流动性
-- **流动性边际收紧**：三季度美元流动性供给压力、港币未完全回强（`7.84–7.85`）、IPO融资较多，流动性供给不如二季度；金管局可小幅收紧（如收90亿、放1000多亿）延缓利率上行，但`联系汇率制度`（7.75–7.85）优先，流动性边际变紧。
-- **市场结构分化**：港股内部极致分化，资金蜂拥结构性行情（AI互联网、创新药、新消费等）；指数在**23000–24000**区间震荡，上不去也下不来。
-- **风格配置建议**：长期方向两头分红，但银行股溢价已低于**20%**（扣税后股息率优势减弱，短期透支），`1.25%`股息率仍是隐形底；成长端新消费拥挤、创新药略降，科技硬件与AI应用拥挤度较3月大幅回落，可提前埋伏创新药、人形机器人、AI应用、短视频生成、软件等方向。
-## 光伏反内卷
-- **供需失衡背景**：全球新增光伏装机从2020年**130GW**增至2024年**530GW**（4年CAGR 42%），2025–26年需求增速预计回落至**10%**左右；供给侧电池产能为需求**1.5倍**、硅片组件**2倍**、硅料**2.5倍**；2022年以来产业链价格下跌**70–90%**，硅片电池2023年四季度起亏损、硅料组件2024年二季度起亏损，尚无企业退出。
-- **政策升级时间线**：2024年`5月17日`光伏行业协会在工信部电子信息司指导下召开高质量发展座谈会（强调市场化手段+政府有形手，提出产能建设指导、保护新技术、打击低于成本销售、鼓励兼并重组）；2025年`2月国常会`提出化解重点产业结构性矛盾；`6月29日`起连续5天`人民日报`发声剖析光伏内卷；`7月1日`中财委第6次会议提出依法依规治理低价无序竞争、推动落后产能退出；`7月3日`工信部再度召开光伏企业座谈会。具体干预措施尚未披露。
-- **各环节整合难度**：硅料最易切入（集中度高、在产企业不到20家、成本曲线陡峭、供需比超200%、影响全产业链定价），当前丰水期边际现金成本约**38元/公斤**（颗粒硅28元、尾部厂商45元）；电池组件分散（组件企业几十上百家）整合难，但电池环节供需最好（`PERC`约500GW已退出、`TOPCon`占90%份额、`BC`渗透率单月5–6%）；光伏玻璃2024年9月首轮出清有效产能降6%，协会呼吁降产保价、7月起第二轮降产**30%**，需出清约**2万吨**方达供需平衡，价格已创历史新低、龙头企业经营性成本约1元/平方米。
-- **市场反馈**：多晶硅期货价格大幅反弹、上周五触及**40元/公斤**；现货报价较前一周35元大幅上涨；硅片报价涨约**10%**、电池涨约**2分钱**；过去两周硅料和玻璃股价涨**20–30%**、组件涨约**10%**；组件价格跟涨意愿受下游电站`136号文`（新能源全面入市）电价不确定性制约，需观望招标情况。
-- **穿越周期能力**：头部一体化组件企业可收现款再发货、占用上游账期获正向经营现金流，财务压力小于上游；低杠杆、强现金、强融资能力企业（部分资产负债率仅10%出头）财务健康度优于同行；技术变革持续（颗粒硅使用比例从10–20%提升至50%、硅片薄片化、钨丝导入、浆料铜替代银2025–26年大规模导入、`TOPCon`取代`PERC`），可助企业逆势获份额。
-## 人形机器人
-- **二季度回调回顾**：A股机器人板块4–6月按流通市值加权跌约**9%**，跑输机械设备约**12个百分点**；特斯拉核心供应商标签股自3月高点普遍回调**30–40%**；主因特斯拉4月后推迟量产时间线、叠加中美关税降低风险偏好；5–6月交易型资金止损明显，资金涌向小盘/微盘扩散行情。
-- **主线一：华为云生态**：`6月底`华为开发者大会首发`盘古世界模型`（时空可控生成技术，首个支持点云+视频双模态同时生成），解决训练物理模型痛点；`CloudRobot`平台构建多模态生成、规划、执行三大模型（操作精度毫米级）；华为明确不造机器人、以`RTC`方式开放，有望探索`AI Agent`或`License`收费；工业喷涂机械臂、腔镜手术机器人、无人矿卡等场景已有合作。
-- **主线二：本土企业技术闭环**：`智元机器人`拟通过收购控股材料厂商在A股上市（具备AI+双足+轮式全栈能力），相关零部件厂商股价底部异动；`宇树科技`年收入突破**10亿元**、下半年有望加速上市；两家企业同时中标中国移动旗下接近**1.2亿元**人形机器人采购订单（部署营业厅与消费者互动）；国内人形机器人本体厂商超**100家**，优先关注投资回报率明确的物流端场景。
-- **主线三：特斯拉延期与硬件替代**：`Optimus`存在电机过热、灵巧手负载不足、续航问题，特斯拉变更方案、筛选供应商；电机过热对应无框力矩电机新品（改善散热）；续航对应轻量化（以塑代钢、替代铝合金）；港股机器人板块二季度估值溢价明显（PE、PS均高），源于流动性红利与港股通/指数纳入预期，下半年有确定性扩容，关注A+H动向。
-- **三季度关注三类信号**：华为云生态接入厂商三季度继续新增；头部企业出货量跨越年化**500台**或**1000台**（股价及供应商演绎）；聚焦电机硬件优化窗口；技术创新、产业需求、工厂替代三重周期共振时孕育投资机会。
-## 游戏板块
-- **政策与版号**：`黑神话悟空`爆火后游戏行业文化价值与经济价值获广泛认可，政策支持力度空前；`1月`、`3月`国务院层面对传媒板块发布游戏行业支持政策，广东、浙江、北京、上海等地出台专项政策包（中小微企业奖励、出海支持、IP方向）；`6月`版号单月发放**158个**（国产**147个**、进口**11个**），为**2018年以来单月最高**，国产与进口版号每月常态化发放。
-- **市场规模与新品周期**：2024年8月以来游戏市场单月持续正增长；`2025年1–5月`游戏市场规模同比增长**17%**（1400多亿）、手游同比增长**20%**；今年非大作年份（腾讯、网易、米哈游均无重磅作品），但中型厂商新品成核心催化——`吉比特`《仗剑传说》首月流水**2亿多**、`巨人网络`《超自然行动组》6月流水过亿（年化约20亿、利润提升50%以上）；大厂缺大体量产品使中型厂商获客友好，新游用户ROI普遍OK。
-- **估值与展望**：板块TTM PE约**30倍**（2023年AI行情达45倍）、2025年静态PE约**20倍**；当前与两年前不同：游戏为悦己型消费、逆周期性弱受宏观影响，政策环境完全转变，新品周期延续（网易、腾讯新品多落明年）；新品利润有滞后性（今年上线、明年兑现），表观估值对明年业绩确定性提供支撑；建议跟踪新品市场表现、用户获取下载榜排名等领先指标；在消费、政策、新品周期三重利好下，调整后有望**戴维斯双击**。
-# 官方表态
-## 宏观策略｜大美丽法案与信用周期
-- **去美元化共识过度拥挤**：市场把美元弱等同于去美元化、把美元弱与美股弱划等号，均属误区；美元弱在多数时候对美股有利，因海外收入占比高、可形成金融条件宽松。
-- **大美丽法案对经济有正面效果**：提高债务上限约5万亿美元，消除违约风险；延长2017年减税法案而非新增减税，额外支出3.4万亿美元（每年3400亿）；取消899条款，消除海外投资者持有美债的税收障碍。
-- **财政赤字不会大幅扩张**：关税收入每年约3000–4000亿美元，可大体弥补每年3400亿额外支出，赤字率基本维持在5–6%；关税因此必须维持一定水平以支撑收入。
-- **三季度存在流动性抽水效应**：7–9月发债约1万亿美元，推高美债利率、边际收紧美元流动性；但需求端可部分对冲，美债利率未必重演2023年三季度从3.8%升至5%的幅度，波动提供再配置机会。
-## 宏观策略｜关税
-- **关税大概率要做且需维持一定税率**：以当前豁免10%的关税水平即可收上来3000–4000亿美元，无需过高税率；威胁提高税率可能是谈判技巧，市场逐渐脱敏。
-- **新变化为时间拖后、税率相对回落**：原定7月9日达成的安排变相延后；相比4月2日对等关税水平，大部分国家税率回落，除巴西外未大幅增加；加拿大、墨西哥、欧盟因贸易占比高需单独谈妥。
-- **有效税率测算**：当前约10–12%，8月1日若全部恢复并提高，最极端回到18%；对华关税约40–50%，越南转口限制40%，需关注8月12日中美谈判及转口限制进展。
-- **通胀影响有限**：关税延后与补库缓解供给压力，通胀年底缓慢抬升至3.3–3.4%，即便18%有效税率也不大幅改变通胀路径，美联储7月降息勉强、9月及四季度后可降。
-## 宏观策略｜港股流动性
-- **三季度流动性边际收紧**：美元流动性供给压力、港币尚未完全回到7.75强方、IPO融资较多，流动性供给不如二季度；但美元美债利率并非绝对主导港股市场的唯一变量，自身基本面强可盖过其影响。
-- **金管局操作边界**：连续汇率制度为最优先考虑，港币在7.84–7.85时金管局一定会收流动性，但可小幅收（如收90亿、放1000多亿）以延缓利率收紧速度。
-- **配置建议**：指数在23000–24000区间震荡，低迷时积极介入、亢奋时适度锁定利润；银行股溢价已低于20%，短期有所透支，长期相对国债利率仍有空间；成长端新消费较拥挤、创新药有所回落，科技硬件与AI应用拥挤度较3月大幅下降，可提前布局。
-## 光伏反内卷｜行业供需与政策
-- **反内卷政策级别持续升级**：2024年以行业协会牵头为主，2025年升至更高层级——2月国常会提出化解重点产业结构性矛盾，6月29日起人民日报连续发声，7月1日总书记主持召开中财委第6次会议提出依法依规治理企业低价无序竞争、推动落后产能退出，7月3日工信部再度召开光伏企业座谈会。
-- **行业供需失衡严重**：全球新增光伏装机从2020年130GW增至2024年530GW，2025–26年需求增速预计回落至10%左右；电池产能为需求1.5倍、硅片组件2倍、硅料2.5倍，2022年以来产业链价格下跌70–90%，硅片电池自2023年四季度、硅料组件自2024年二季度进入亏损，目前尚无改变供需格局的企业退出。
-- **硅料环节整合最迫切**：集中度较高（在产企业不到20家）、成本曲线最陡峭（丰水期边际现金成本约38元/公斤，颗粒硅28元、尾部厂商45元）、供需比超200%，且作为最上游影响全产业链定价；下游电池组件较分散、整合困难，电池环节因Perc资产基本退出、Topcon占90%份额而供需最为良好。
-## 光伏反内卷｜市场反馈与展望
-- **政策预期推动价格反转**：多晶硅期货价格大幅反弹，截至上周五触及40元/公斤；现货报价较前一周35元左右大幅上浮，硅片报价涨约10%、电池涨约2分钱，硅料市场呈现触底企稳态势；过去两周硅料和玻璃股价上涨20–30%，组件涨幅相对靠后约10%。
-- **光伏玻璃开启第二轮产能出清**：2024年9月第一轮出清有效产能降幅约6%；当前协会呼吁降产保价，参加企业计划7月起降产30%，测算需出清约2万吨方可修复供需平衡；当前价格下龙头企业经营性成本约1元/平方米，后续不排除亏损幅度进一步加大。
-- **穿越周期看企业质地**：头部一体化组件企业可通过收现款再发货、占用上游账期获得正向经营现金流，财务压力小于上游；低杠杆、强现金、融资能力强的企业财务健康程度显著优于同行；颗粒硅使用比例从10–20%提升至50%、硅片薄片化、钨丝导入、浆料铜替代银（2025–26年大规模导入）等技术变革将帮助企业逆势获得份额。
-## 人形机器人｜三季度主线
-- **二季度回调原因**：A股机器人板块按流通市值加权平均跌约9%，跑输机械设备约12个百分点；特斯拉4月后宣布量产时间线继续后移，叠加中美关税情况，降低A股风险偏好，核心供应商标签股从3月高点普遍回调30–40%，5–6月交易型资金止损明显。
-- **主线一：华为云生态开放**：6月底华为开发者大会首发盘古世界模型，通过时空可控生成技术实现点云和视频双模态同时生成，解决训练物理模型痛点；CloudRobot平台构建多模态生成、规划、执行三大模型，操作精度提升至毫米级；华为明确不造机器人，以RTC方式开放，未来有望探索AI agent或license收费模式。
-- **主线二：本土企业技术闭环**：智元机器人拟通过收购控股材料厂商在A股上市，具备AI+双足及轮式人形机器人全栈能力；宇树科技年收入突破10亿元，有望下半年加速上市；两家企业同时中标中国移动旗下近1.2亿元人形机器人采购订单，将部署于移动营业厅；国内人形机器人本体厂商超100家，物流端降低单件运输成本为2025年明确刚需。
-- **主线三：特斯拉延期带来硬件替代窗口**：Optimus存在电机过热、灵巧手负载不足、续航问题，正在变更方案并筛选供应商；电机散热、轻量化（以塑代钢等）为共性瓶颈，相关上市公司已发布适配人形机器人的无框力矩电机新品。
-## 人形机器人｜市场展望
-- **港股机器人板块估值溢价明显**：二季度无论PE还是PS均显著高于A股，源于港股通纳入后享受全球科技资金关注；下半年港股机器人板块有确定性扩容，可关注A+H动向。
-- **三季度关注三类信号**：华为云生态接入厂商继续新增；头部企业出货量跨越年化500台或1000台及其供应商股价演绎；电机硬件优化对应的零部件窗口；技术创新、产业需求与工厂替代三重周期共振时孕育较好投资机会。
-## 游戏板块｜政策与基本面
-- **政策支持力度空前**：今年1月和3月国务院层面对传媒板块发布游戏行业支持政策，广东、浙江、北京、上海等地出台专门政策支持包，涵盖中小微企业奖励、数字内容文化产业出海支持、IP方向等；版号发放常态化，今年每月同时发放国产和进口网络游戏版号，6月单月发放158个（国产147个、进口11个），为2018年以来单月最高水平。
-- **市场规模持续正增长**：自2024年8月以来单月持续正增长，今年1–5月游戏市场规模同比增长17%（1400多亿），手游同比增长20%；今年为中型厂商新品大年，吉比特《仗剑传说》6月上线首月流水2亿多，巨人网络《超自然行动组》6月流水过亿、乐观年化约20亿元流水量级，利润提升可达50%以上。
-- **估值仍有提升空间**：板块TTM PE约30倍，2025年静态PE约20倍，低于2023年AI行情时的45倍；新品利润有滞后性，今年上新更多利润明年兑现，为明年业绩确定性提供基础。
-## 游戏板块｜投资展望
-- **调整后有望戴维斯双击**：游戏为悦己型消费、受宏观经济影响小，政策环境与两年前完全不同，新品周期仍在延续（网易、腾讯等大厂新品更多落在明年）；短期板块估值提升仍有较大空间，市场对利润预期有修正增长，最终实现戴维斯双击。
-- **跟踪指标建议**：关注新品市场表现、用户获取下载榜排名等领先指标，流水为相对滞后指标，利润更为滞后。
-# Q&amp;A环节
-**记者**：请问刘总，您提到大美丽法案对经济有正面影响，但三季度有流动性抽水效应，能否具体说明这个抽水效应对美债利率和美股的影响幅度？
-**刘刚凯文**：三季度发债约1万亿美元，参考2023年三季度类似规模发债推高美债利率从3.8%升至5%，美元走强，美股小幅下跌4-5%。但这次可能到不了那么大幅度，因为期限溢价已处于2013年以来高位，我们大体打个折，利率要撑到5%以上难度较大。供给是确定的，但需求端如果很强可以对冲，除非需求也没有且叠加其他意外扰动，才会重演供需失衡导致利率大幅抬升、冲击美股分母端的风险。所以我们的观点是波动提供再配置机会，并不悲观。
-**记者**：关于关税，您提到有效税率当前10-12%，极端情况18%，请问这个测算基于什么假设？对通胀的影响有多大？
-**刘刚凯文**：有效税率测算基于当前豁免10%关税的水平，如果8月1号全回去甚至提高，最多回到10-15%，最极端18%。关键是关税要收上来钱（每年3000-4000亿）对冲支出，又不能太高导致通胀受不了。对通胀的影响不会太大，年底缓慢抬升至3.3-3.4%左右，即便18%的水平也不大幅改变通胀路径，因为整体有效税率没有提高那么高。美联储7月降息仍勉强，9月后四季度还是可以降。
-**记者**：港股流动性方面，您提到三季度不如二季度，具体有哪些约束因素？对恒指点位怎么看？
-**刘刚凯文**：约束因素有三：一是美元流动性供给压力，7-9月美债发行约1万亿；二是港币汇率一直在7.84-7.85，金管局必须回收流动性维持联系汇率，虽可小幅收（如收90亿、放1000多亿）延缓收紧速度，但边际上流动性一定变紧；三是IPO融资较多。所以指数在23000-24000区间震荡，上不去也下未必下得来。但美元美债利率不是绝对主导港股唯一变量，自身基本面强完全可以盖过影响。
-**记者**：光伏反内卷方面，您判断硅料整合最迫切，能否具体说明各环节整合难度差异？当前价格反弹的持续性如何？
-**刘佳妮**：硅料最易切入整合，原因有三：集中度高（在产企业不到20家）、成本曲线最陡峭（颗粒硅现金成本28元/公斤，尾部厂商高达45元）、供需比超200%为各环节最高，且作为最上游影响全产业链定价。下游电池和组件较分散，组件企业几十上百家，部分有独特海外市场生存方式，整合较难。价格方面，多晶硅期货已触及40元/公斤，现货报价上周大幅上涨（前一周约35元），硅片报价涨10%、电池涨2分钱，组件涨幅相对靠后约10%，跟涨意愿存在但需观望下游电站对136号文电价不确定性的接受度。
-**记者**：人形机器人三季度三大主线中，华为云生态的商业化路径和特斯拉延期带来的硬件替代机会，能否进一步说明？
-**郭文秀**：华为明确不造机器人，以RTC方式开放，未来有望探索AI agent收费或license收费模式，盘古世界模型和CloudRobot平台已在工业喷涂机械臂、腔镜手术机器人、无人矿卡等场景落地，下半年有望看到更多云智能加场景深耕案例。特斯拉Optimus存在电机过热、灵巧手负载不足、续航问题，正在变更方案和筛选供应商，这些硬件瓶颈恰是行业共性瓶颈，电机方面已有上市公司发布新款无框力矩电机改善散热，轻量化（以塑代钢、替代铝合金）是解决续航的值得关注方向。
-**记者**：游戏板块这波调整是结束还是回调后可以上车？估值水平如何支撑您的判断？
-**张雪琴**：我们的态度旗帜鲜明是后者。估值方面，TTM PE约30倍，2025年静态PE约20倍，切明年更低，而2023年AI行情下到过45倍。当前板块与两年前不同：一是游戏已定义为悦己型消费，1-5月市场规模同比增长17%，逆周期性；二是政策端友好度空前，6月版号单月发放158个（国产147个、进口11个）为2018年以来最高；三是新品周期延续，中型厂商新品成为核心催化，如吉比特《仗剑传说》首月流水2亿多、巨人网络《超自然行动组》6月流水过亿年化20亿。但需注意新品利润有滞后性，今年上新更多利润明年兑现，所以短期估值提升还有空间，市场对利润预期修正后有望实现戴维斯双击。</t>
+          <t># 中金宏观策略争论：海外热点与行业机会解读
+## 发布会概况
+本次中金宏观策略争论会议于周一上午举行，由中金公司策略组主办，策略组主持人刘刚凯文主持，并邀请风光公用事业首席分析师刘佳妮、机械军工分析师郭文秀、传媒行业首席分析师张雪琴分别就光伏、人形机器人、游戏板块作专题分享。会议围绕海外宏观热点与国内行业机会两大主线展开：海外部分聚焦大美丽法案对美股美债及美元流动性的影响、关税谈判进展、港股流动性变化；国内部分涵盖光伏反内卷政策、人形机器人行业趋势、游戏板块投资机会。整体基调为结构性行情下建议在合适位置布局长期正确板块，波动提供再配置机会。关键数字锚点包括：纳斯达克自底部反弹35%、大美丽法案提高债务上限约5万亿美元、6月游戏版号单月发放158个（2018年以来最高）。会议未设问答环节，结尾提示投资者可直接联系对应分析师，下周同一时间再见。
+## 核心信息
+### 大美丽法案及美股美债影响
+1. **法案三大块**：`大美丽法案`主要包含三部分——提高债务上限约**5万亿美元**（消除违约风险，允许政府继续发债支出）、延长2017年减税法案（非新增减税，避免年底自动大幅加税，额外支出**3.4万亿美元**、年均**3400亿美元**，同时削减新能源补贴等支出约**1.4万亿美元**）、取消`899条款`（消除海外投资者持有美债的利息所得税障碍）。
+2. **财政与赤字测算**：关税收入每年约**3000–4000亿美元**（当前约10%–12%有效税率），可覆盖年均3400亿美元额外支出，测算赤字率基本维持在**5%–6%**，不会大幅扩张；财政因素对信用周期中长期有利，是判断四季度美元可能小幅走强、美股可能反弹跑赢的核心原因之一。
+3. **三季度流动性压力**：7–9月财政部需回补`TGA账户`并新增发债，额外供给约**1万亿美元**（参照2023年三季度同期水平）；美债利率近期上行，期限溢价已处于**2013年以来高点**，但利率抬升幅度或不及2023年（当时从3.8%升至5%），是否引发股债汇三杀取决于需求端；波动提供再配置机会，对美股美债不悲观。
+### 关税谈判进展及影响
+1. **四点判断**：关税大概率要做（用于支撑财政收入）；需维持一定税率（当前豁免10%关税水平即可收上来3000–4000亿美元）；不能太高（过高推升通胀）；市场逐渐脱敏、静观其变，高税率威胁可能是谈判技巧。
+2. **新变化**：时间变相延后（原7月9日达成，现推迟）；大部分国家税率相比4月2日对等关税水平回落（巴西除外）；加拿大、墨西哥、欧盟因贸易占比高需重点谈判，其他国家即便税率翻倍对有效税率影响很小（日本占比最高仅4.5%）。
+3. **有效税率与通胀**：当前有效税率约**10%–12%**，假设8月1日关税恢复并提高，最极端回到**18%**；通胀压力可控，年底或缓慢抬升至**3.3%–3.4%**，不大幅改变通胀路径，美联储7月降息勉强、9月及四季度后仍可降。
+4. **对华关税与转口限制**：当前对华关税约**40%–50%**（2018年约20%）；需关注**8月12日**中美谈判进展，以及越南（转口限制40%）、英国协议中的转口限制影响。
+### 港股流动性及市场策略
+1. **流动性边际收紧**：三季度流动性供给不如二季度——美元流动性供给压力、港币持续在**7.84–7.85**（金管局需回收流动性维持联系汇率，可小幅回收延缓收紧速度）、IPO融资较多形成约束；但美元美债利率并非港股唯一主导变量，基本面强可盖过影响。
+2. **市场结构特征**：港股内部极致分化，结构性行情明显（AI互联网、创新药、新消费、人形机器人、AI应用等）；恒生科技未达对等关税前水平，跑输恒指；5月后`HIBOR`利率大幅下降（金管局投放流动性），但港币弱导致边际收紧。
+3. **配置建议**：长期方向仍是两头——分红端银行股溢价已低于**20%**（扣税后股息率优势减弱，短期透支但长期相对国债利率仍有空间，短期**1.25%**是隐形底）；成长端新消费较拥挤、创新药有所回落，科技硬件AI应用拥挤度相比3月大幅下降，提供提前布局机会；中期关注创新药、人形机器人、AI应用、短视频生成、软件等方向。
+### 光伏反内卷及行业影响
+1. **供需失衡背景**：全球新增光伏装机从2020年**130GW**增至2024年**530GW**（CAGR 42%），未来两年增速回落至**10%**左右；2025年全球需求预计**650–700GW**，但电池产能为需求**1.5倍**、硅片组件**2倍**、硅料**2.5倍**；2022年以来产业链价格下跌**70%–90%**，硅片电池自2023年四季度亏损、硅料组件自2024年二季度亏损，目前尚无企业退出。
+2. **反内卷政策升级**：2024年以行业协会主导（2024年5月17日光伏行业协会在工信部电子信息司指导下召开高质量发展座谈会，提出产能建设指导、打击低于成本销售、鼓励兼并重组；10月、12月继续召开座谈会但收效不明显）；2025年政策级别提升——2月国常会提出化解重点产业结构性矛盾、6月29日人民日报发文、7月1日中财委第六次会议提出依法依规治理低价无序竞争、推动落后产能退出、7月3日工信部召开光伏企业座谈会；目前尚无具体干预措施披露。
+3. **各环节整合难度**：硅料环节最易切入——集中度高（在产企业不到20家）、成本曲线陡峭（丰水期边际现金成本约**38元/公斤**，颗粒硅约**28元/公斤**，尾部厂商高达**45元/公斤**）、供需比超**200%**、作为最上游影响全产业链定价；电池组件较分散（组件企业几十上百家）整合难，电池环节供需最良好（`PERC`电池约500GW已退出，`TOPCon`占90%份额，`BC`技术单月渗透率提升至**5%–6%**）。
+4. **光伏玻璃与价格反馈**：光伏玻璃2024年9月第一轮产能出清（有效产能降幅约6%），协会呼吁降产保价、7月起第二轮出清计划降产**30%**，测算需出清约**2万吨**方可修复供需平衡；价格已创历史新低，龙头企业经营性成本约**1元/平方米**；政策预期下多晶硅期货价格反弹至**40元/公斤**（前一周现货约35元），硅片报价涨约**10%**、电池涨约**2分**，组件涨幅靠后约**10%**（受`136号文`新能源全面入市政策影响，下游电站对涨价传导持观望）。
+5. **穿越周期能力**：头部一体化组件企业可通过收现款再发货、占用上游账期获得正向经营现金流，财务压力小于上游；低杠杆、强现金、融资能力强的企业财务健康（部分资产负债率仅10%出头）；技术变革持续——颗粒硅使用比例从10%–20%提升至**50%**、硅片薄片化细线化、钨丝全面导入、电池浆料铜替代银将于2025–26年大规模导入。
+### 人形机器人行业趋势
+1. **二季度回调回顾**：A股机器人板块4–6月按流通市值加权平均跌约**9%**，跑输机械设备板块约**12个百分点**；特斯拉核心供应商标签股从3月高点普遍回调**30%–40%**，5–6月交易型资金止损明显；回调主因是特斯拉4月后宣布量产时间线延后、叠加中美关税降低风险偏好。
+2. **华为链主线**：6月底华为开发者大会首发`盘古世界模型`（时空可控生成技术，首个支持点云和视频双模态同时生成的大模型），`CloudRobot`平台构建三大能力——多模态生成模型（泛化训练环境）、规划大模型（复杂物理世界自主决策）、执行大模型（操作精度提升至毫米级）；华为明确不造机器人，以`RTC`方式开放，未来或探索AI agent收费或license收费；工业喷涂机械臂、腔镜手术机器人、无人矿卡等上市公司已与华为云合作。
+3. **本土企业主线**：智元机器人拟通过收购控股材料厂商在A股上市（具备AI+双足及轮式人形机器人全栈能力），相关零部件厂商股价底部异动；宇树科技年收入突破**10亿元**，下半年有望加速上市；智元与宇树同时中标中国移动旗下接近**1.2亿元**人形机器人采购订单，将部署于移动营业厅；国内人形机器人本体厂商超**100家**，物流端降低单件运输成本是2025年下游明确刚需。
+4. **特斯拉延期与硬件替代**：`Optimus`存在电机过热、灵巧手负载不足、续航问题，特斯拉正在变更方案并筛选供应商；电机散热（有上市公司发布新款无框力矩电机）、轻量化（以塑代钢替代铝合金）是共性瓶颈突破方向；港股机器人板块二季度估值溢价明显（PE、PS均高），源于流动性红利及纳入港股通/指数后吸引全球科技资金，下半年有确定性扩容，关注A+H动向。
+5. **三季度关注信号**：华为云生态接入厂商新增趋势；头部企业出货量跨越年化**500台**或**1000台**背后的股价及供应商演绎；电机硬件优化对应窗口；技术创新、产业需求、工厂替代三重周期共振时孕育投资机会。
+### 游戏板块投资机会
+1. **政策与版号**：政策支持空前——国务院1月、3月发布游戏行业支持政策，广东、浙江、北京、上海等地出台专门支持包（含中小微企业奖励、数字内容文化产业出海支持、IP方向）；版号发放常态化，每月同时发放国产和进口版号，6月单月发放**158个**（国产**147个**、进口**11个**），为**2018年以来单月最高**。
+2. **市场规模与新品周期**：2024年8月以来游戏市场单月持续正增长；今年1–5月游戏市场规模同比增长**17%**（1400多亿元），手游同比增长**20%**；今年原预期为缺乏大作年份（腾讯、网易、米哈游均无重磅作品），但中型厂商新品成核心催化——吉比特《仗剑传说》5–6月上线首月流水**2亿多**，巨人网络《超自然行动组》6月预估流水过亿、乐观年化约**20亿元**、利润提升可达**50%以上**；大厂缺大体量产品对中型厂商获客友好，国内多数新游用户ROI良好。
+3. **估值与展望**：当前TTM PE约**30倍**（2023年AI行情曾达**45倍**），2025年静态PE约**20倍**、明年更低；游戏板块具逆周期性（悦己型消费，1–5月仍增长17%）、政策环境根本改善、新品周期延续（三七《斗罗》7月上线，网易腾讯新品多落在明年）；新品利润有滞后性（买量成本前置、流水递延确认），今年上新利润明年兑现，提供业绩确定性；短期板块估值提升仍有空间，在消费、政策、新品周期三重利好下，调整后有望实现**戴维斯双击**。
+## 官方表态
+### 策略组｜大美丽法案与美股美债
+1. **对去美元化共识持保留态度**：不认同市场将美元走弱等同于去美元化，也不认同将美元弱与美股弱直接划等号；美元弱在多数时间（非抛售美国资产情形）对美股有利，因海外收入占比高可形成金融条件宽松。
+2. **大美丽法案三大块影响**：提高债务上限约5万亿美元消除违约风险；延长2017年减税法案（非新增减税），额外支出3.4万亿美元、每年3400亿；取消899条款，消除海外投资者持有美债的税收障碍。
+3. **财政赤字与关税收入大体相抵**：关税收入每年3000–4000亿可覆盖额外支出，赤字率基本维持在5–6%；短期直接财政扩张提振有限，但下半年环比改善，中长期信用周期有利。
+4. **三季度流动性有波折但不必悲观**：7–9月美债供给约1万亿美元、美元流动性边际收紧，但幅度或不及2023年（当时美债利率从3.8%升至5%）；波动提供再配置机会，对美股美债并不悲观。
+### 策略组｜关税谈判
+1. **关税大概率维持**：需以关税支撑收入，有效税率需维持10–12%水平（当前豁免10%关税水平即可收上来钱）；威胁提高税率可能是谈判技巧，市场逐渐脱敏。
+2. **新变化与有效税率测算**：时间变相延后；大部分国家税率相对4月2日对等关税水平回落（除巴西）；加拿大、墨西哥、欧盟贸易占比高需重点谈判；有效税率当前10–12%，极端情况18%，对通胀影响有限。
+3. **通胀与美联储路径**：通胀年底或缓慢抬升至3.3–3.4%，不大幅改变通胀路径，美联储仍可降息；7月降息勉强，9月及四季度之后仍可降。
+4. **对中国关税与转口限制**：对中国关税约40–50%；越南、英国协议均有转口限制（越南40%），需关注8月12日中美谈判进展及转口限制。
+### 策略组｜港股流动性
+1. **三季度流动性边际收紧**：受美元流动性供给、港币7.85（金管局需收回流动性）、IPO融资较多等约束，三季度流动性供给不如二季度；但美元美债利率并非绝对主导港股唯一变量，基本面强可盖过影响。
+2. **港股内部极致分化**：结构性行情明显，资金蜂拥至AI互联网、创新药、新消费等少数板块；恒生科技未达对等关税前水平，跑输恒指。
+3. **配置建议**：银行股溢价低于20%、短期透支但长期仍有空间；新消费拥挤，科技硬件AI应用拥挤度下降提供提前布局机会；中期关注创新药、人形机器人、AI应用、短视频生成、软件。
+### 风光公用事业｜光伏反内卷
+1. **反内卷政策级别升级**：2月国常会提及化解重点产业结构性矛盾；6月29日起人民日报连续发声；7月1日中财委第6次会议提出依法依规治理企业低价无序竞争、引导产品品质、推动落后产能退出；7月3日工信部召开光伏企业座谈会，指出技术创新与产业产能升级是反内卷重要手段。
+2. **硅料环节整合最迫切**：集中度较高（在产企业不到20家）、成本曲线陡峭（丰水期边际现金成本38元/公斤，颗粒硅28元，尾部厂商45元）、供需比超200%，作为最上游影响全产业链定价。
+3. **光伏玻璃第二轮产能出清**：协会呼吁降产保价，参加企业计划7月起降产30%；测算需出清约2万吨方可修复供需平衡；当前价格已创历史新低，龙头企业经营性成本约1元/平方米，后续不排除亏损幅度加大。
+4. **价格触底企稳**：多晶硅期货价格反弹至40元/公斤，现货报价大幅上涨（前一周约35元）；硅片报价涨约10%、电池涨约2分；组件价格有跟涨意愿，但下游电站受136号文影响、电价不确定性增加，能否接受传导需观望招标情况。
+### 机械军工｜人形机器人
+1. **三季度三大主线**：华为云生态开放、本土人形机器人企业技术闭环、特斯拉延期带来的硬件替代窗口期。
+2. **华为链技术突破**：6月底华为开发者大会首发盘古世界模型，支持点云视频双模态同时生成；CloudRobot平台构建多模态生成、规划、执行三大能力，操作精度提升至毫米级；华为明确不造机器人，以RTC方式开放，有望探索AI agent或license收费模式。
+3. **本土企业商业进展**：智元机器人拟收购材料厂商在A股上市，具备AI加双足及轮式人形机器人全栈能力；宇树科技年收入突破10亿、下半年有望加速上市；两家中标中国移动旗下接近1.2亿人形机器人采购订单，将部署于移动营业厅。
+4. **特斯拉延期与硬件替代**：Optimus存在电机过热、灵巧手负载不足、续航问题，正在变更方案并筛选供应商；建议关注电机硬件优化（如无框力矩电机改善散热）、轻量化（以塑代钢）方向。
+### 传媒｜游戏板块
+1. **政策支持空前**：国务院1月、3月发布游戏行业支持政策，广东、浙江、北京、上海等地出台专门政策支持包（含中小微企业奖励、数字内容文化产业出海、IP方向）；版号发放常态化，6月单月发放158个（国产147、进口11），为2018年以来单月最高。
+2. **行业景气度与新品周期**：1–5月游戏市场规模同比增长17%（1400多亿），手游同比增长20%；中型厂商新品成核心催化，如吉比特《仗剑传说》首月流水2亿多、巨人网络《超自然行动组》年化流水约20亿；大厂大作多落在明年大周期。
+3. **估值与配置判断**：当前TTM PE约30倍、2025年静态PE约20倍，低于2023年AI行情45倍；新品利润有滞后性、明年兑现，提供业绩确定性；在消费、政策、新品周期三重利好下，调整后有望实现戴维斯双击，当前是配置时间点。
+## Q&amp;A环节
+### Q1. 现场提问主题
+- **问**：当前市场对去美元化担忧与美股创新高并存，如何看待这一矛盾？
+&gt; **刘刚凯文**：不应简单用长期逻辑影响短期配置。4月底若按股债汇三杀、去美元化观点操作，会错过纳斯达克从底部反弹35%的行情。我们并不完全认同去美元化观点，它已成为高度趋同的共识，且基于宏大叙事，无法确定兑现时间。市场存在两个误区：一是把美元弱当成去美元化，美元走弱可能源于美联储降息预期升温；二是把美元弱与美股弱直接划等号，美元弱在多数时候对美股有利，因其海外收入占比高，可形成金融条件宽松。我们基于信用周期分析，美国经济下半年环比有望改善，财政因素对中长期有利。
+### Q2. 现场提问主题
+- **问**：大美丽法案对经济和市场有何具体影响？
+&gt; **刘刚凯文**：大美丽法案三大块：一是提高债务上限约5万亿美元，消除违约风险，使政府可继续支出；二是延长2017年减税法案，额外支出3.4万亿美元，每年3400亿，可被关税收入（每年3000-4000亿）弥补，赤字率维持5-6%；三是取消899条款，消除海外投资者持有美债的税收障碍。短期对经济提振有限但环比改善，中长期信用周期有利。三季度美债供给约1万亿美元，可能推高利率，但幅度或不及2023年（3.8%-5%），波动提供再配置机会。
+### Q3. 现场提问主题
+- **问**：关税谈判有何新变化？对通胀和美联储政策有何影响？
+&gt; **刘刚凯文**：关税四点信息：一定会做以支撑收入；需维持10-12%有效税率才能收上钱；不能太高以免通胀受不了；市场逐渐脱敏。新变化：时间延后，大部分国家税率相对4月2日回落，除巴西；加拿大、墨西哥、欧盟贸易占比高需重点谈判。有效税率当前10-12%，极端情况18%，对通胀影响有限，年底或缓慢抬升至3.3-3.4%，美联储仍可降息。对中国关税约40-50%，需关注8月12日中美谈判及转口限制（越南40%）。
+### Q4. 现场提问主题
+- **问**：港股三季度流动性前景如何？对市场有何影响？
+&gt; **刘刚凯文**：港股三季度流动性供给不如二季度，受美元流动性供给、港币7.85、IPO融资等约束。但美元美债利率并非绝对主导港股的唯一变量，自身基本面强可盖过影响。港股内部极致分化，结构性行情明显。银行股溢价低于20%，短期透支但长期仍有空间；新消费拥挤，科技硬件AI应用拥挤度下降，提供提前布局机会。中期关注创新药、人形机器人、AI应用、短视频生成、软件。建议在合适位置布局长期正确板块，波动提供再配置机会。
+### Q5. 现场提问主题
+- **问**：光伏反内卷政策进展如何？哪些环节最受益？
+&gt; **刘佳妮**：反内卷政策升级：2月国常会提出化解重点产业结构性矛盾，6月29日人民日报发声，7月1日中财委会议提到依法依规治理低价无序竞争，7月3日工信部召开光伏企业座谈会。硅料环节最易整合，供需比超200%，现金成本38元/公斤，颗粒硅28元，尾部45元；光伏玻璃第二轮产能出清，7月降产30%，需出清约2万吨。多晶硅期货价格反弹至40元/公斤，硅片涨10%，电池涨2分。头部一体化组件企业穿越周期能力强，低杠杆强现金企业财务健康。
+### Q6. 现场提问主题
+- **问**：人形机器人三季度有哪些投资主线？
+&gt; **郭文秀**：二季度A股机器人板块跌约9%，跑输机械板块12个百分点，主因是特斯拉量产时间线延后及中美关税。三季度三大主线：一是华为链，6月底发布盘古世界模型和CloudRobot平台，支持点云视频双模态生成；二是本土企业技术闭环，智元机器人拟收购材料厂商上市，宇树科技年收入破10亿，两家中标中国移动1.2亿采购订单；三是特斯拉延期带来的硬件替代窗口，Optimus存在电机过热、灵巧手负载不足、续航问题。建议关注三类信号：华为云生态接入、头部企业出货量跨越500/1000台、电机硬件优化。
+### Q7. 现场提问主题
+- **问**：游戏板块近期调整后，当前估值和投资机会如何？
+&gt; **张雪琴**：游戏板块上涨近两三个月，上周开始调整，我们观点仍相对看好。政策支持空前：国务院1月、3月政策，广东浙江北京上海支持包；6月版号单月发放158个（国产147、进口11），2018年以来最高；1-5月游戏市场规模同比增长17%，手游增长20%。中型厂商新品成核心催化，如吉比特《仗剑传说》首月流水2亿多，巨人网络《超自然行动组》年化流水20亿。当前TTM PE约30倍，2025年静态PE约20倍，低于2023年AI行情45倍。新品利润有滞后性，明年兑现，提供业绩确定性。在消费、政策、新品周期三重利好下，调整后有望戴维斯双击，当前是配置时间点。</t>
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>90.5</v>
+        <v>95.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22868/9357</t>
+          <t>22868/8656</t>
         </is>
       </c>
     </row>
@@ -3807,74 +3796,66 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t># 课程概况
-本节主题班会围绕“梦想”展开，由老师（发言者2）主讲。老师以提问方式引导学生分享各自的梦想，随后分享了自己的梦想与经历：梦想成为受学生喜爱的有名望的优秀人民教师；曾梦想考中国美术学院，单考通过但因离家远和没钱未去，最终作为定向生入读广东技术师范大学（原民族学院），定向回龙川县教书，免学费但不能全日制考研，只能在职考研。老师大学四年保持本专业排名第一（专业共41人），并列举了大学期间的梦想清单，包括加入学生会、参加比赛、保持专业排名、考取教师资格证等。老师播放了航模爱好者何宗发和想当歌手的普通人的追梦视频，引导学生讨论实现梦想的条件，总结出坚持、努力、勇敢、机会、兴趣、能力、学习等要素，并强调“机会留给有准备的人”。老师还以马云中考考两次、高考考三次最终成为中国首富为例，说明起点不重要、坚持更重要；并指出梦想可以分阶段调整目标，如先考进年级前百再争取前五十。老师让学生写下自己的梦想清单，并计划收集，现场展示了部分学生的梦想并逐一鼓励。班会最后，老师总结强调梦想需要坚持和努力，可以量力而行、适时调整，并鼓励学生勇敢追梦。
-# 核心知识点梳理
-## 梦想的定义与价值
-- **梦想的普遍性**：老师以提问方式引出话题，学生分享的梦想包括当保安、当喜剧人、当太空人、当世界冠军、当主角、当歌手等，老师指出“每一个班的人都会有想当太空人”，说明广告词深入人心。
-- **梦想值得尊重**：老师强调“每一个梦想都是值得我们尊重的”“我们不要去嘲笑任何一个人的梦想”，即使唱歌走调的人通过后天学习和努力也可以调整过来。
-- **梦想需要坚持**：老师引用“不被嘲笑的梦想不是梦想”，并以马云为例——中考考两次才考上高中、高考考三次，最终成为中国首富，说明**起点高低不重要，关键在能否坚持**。
-- **梦想可以分阶段调整**：老师建议梦想可先定小目标再定大目标，如先考进年级前百，再争取前五十；目标实现不了时可以量力而行、适时调整。
-## 实现梦想的条件
-- **坚持与努力**：老师总结实现梦想必不可少的三个条件是**学习、坚持、行动**；天赋只是1%，后天努力更重要。
-- **勇敢与行动**：老师表扬班上同学虽被起哄仍勇敢站上讲台唱歌，鼓励同学们要有勇气去行动。
-- **机会与准备**：老师强调“机会永远都是留给有准备的人”，实现梦想还需要机会、兴趣、能力、学习等条件。
-- **条件与实现速度**：老师指出缺少某一个条件梦想仍可能实现，但条件都具备时梦想会**更快实现**。
-## 老师的梦想之路（案例）
-- **职业梦想**：老师的梦想是成为**受学生喜爱的有名望的优秀人民教师**，目前仍在努力过程中。
-- **考学经历**：老师曾梦想考中国美术学院，单考已通过，但因离家远和没钱未去，最终作为定向生入读广东技术师范大学（原民族学院），定向回龙川县教书，免学费。
-- **定向生限制**：⭐ 定向生**不能全日制考研**，只能**在职考研**（边工作边读研），且学费需自己交。
-- **大学成就**：老师大学四年保持本专业排名第一（专业共41人），每天5点起床，靠自律与坚持实现目标。
-- **大学梦想清单**：包括加入学生会、参加各种比赛（如校运会）、保持专业排名争取保研、考取教师资格证等；老师强调大学评优看多方面，不只学习好。
-## 追梦案例视频分析
-- **航模爱好者何宗发**：视频展示其通过一步步努力走上更大舞台，是中国唯一去法国巴黎比赛的航模选手，目标是带着飞机环游世界、把中国国旗挂在世界各大赛场，并希望在明年世界锦标赛上与顶级选手一较高下。
-- **航模技术进步**：何宗发每次表演都有技术突破，曾去中国航空博物馆学习，用歼10原型机制作模型飞机，从古代遨游到未来。
-- **普通人歌手梦想**：视频还展示想当歌手的普通人，在宿舍练习，即使唱歌走调被嘲笑，通过后天学习仍可成为歌手。
-- **梦想逐步立高**：老师指出航模小伙实现梦想后受到更多关注，梦想从中国走向全世界，说明**梦想可以一步步立高**。
-## 学生梦想清单分享
-- **梦想清单写法**：老师让学生拿出纸写下自己的梦想，可像老师一样列清单，写清第1个、第2个、第3个梦想，实现后打勾，并思考实现所需时间及收获。
-- **学生梦想示例**：有学生想考630分、拥有健康身体、每天开开心心、家人平平安安、世界和平、祖国越来越好；有学生想成为设计师、大学四年攒20万、成为创业者；有学生想成为光荣的人民教师、考上重本211。
-- **梦想数量建议**：老师指出梦想可以只写一个，也可以制定多个；梦想清单列得多，实现几率也相对较大。
-- **梦想收集安排**：老师计划让每个小组第1个同学收集本组同学的梦想，并提到之前班级学生写的梦想“都很厚”。
-# 课堂互动与答疑
-**学生**：老师，您当初为什么没有去中国美术学院？
-**教师**：单考过了，但一是离家太远，二是学美术费用高，我高中是靠大家资助读完的，经济上负担不起。后来父母选了能定向回龙川县教书的学校，我就去了广东技术师范大学（原民族学院），定向生免学费。
-**学生**：定向生可以考研吗？
-**教师**：定向不能全日制考研，只能在职考研，就是边工作边读研，学费也得自己交。
-**学生**：老师，您大学四年专业排名第一，是怎么做到的？
-**教师**：每天5点起床，坚持了四年。专业共41人，我保持本专业排名第一。自律和坚持是关键。
-**学生**：如果梦想实现不了怎么办？
-**教师**：可以量力而行、适时调整目标。比如想考进年级前50，考不进就先调整为前百，考进前百再定前50，一步步往前进。梦想还是要有的，万一实现了呢。
-**学生**：马云中考考两次、高考考三次，为什么还能成功？
-**教师**：一个人的起点高低不重要，关键看能不能坚持。马云现在成了中国首富，说明坚持比起点更重要。
-**学生**：唱歌走调的人还能实现歌手梦吗？
-**教师**：可以。唱歌走调通过后天学习和努力是可以调整过来的，所以不要嘲笑任何人的梦想，坚持努力就能实现。
-**学生**：实现梦想需要哪些条件？
-**教师**：坚持、努力、勇敢、机会、兴趣、能力、学习都是必要条件。机会永远留给有准备的人，学习、坚持、行动是梦想条件中必不可少的三个。
-# 课后任务与学习建议
-## 课堂练习
-- **梦想条件讨论**：老师组织全班按4个大组组成“梦想观察团”，观察航模爱好者何宗发和想当歌手的普通人两个追梦案例，讨论实现梦想需要具备的条件，各组归纳出坚持、努力、勇敢、机会、兴趣、能力、学习等要素。
-- **梦想清单书写**：老师让学生拿出纸写下自己的梦想清单，要求参照老师示范的格式——按第1个、第2个、第3个逐条列出，实现后打勾，并思考实现每个梦想需要的时间和实现后的收获；写完后由每组第1个同学收齐交给老师。
-## 复习重点
-- **实现梦想的三大必备条件**：学习、坚持、行动是梦想实现必不可少的三个条件；缺少某个条件梦想仍有可能实现，但条件齐备会加速实现。
-- **机会留给有准备的人**：实现梦想需要机会，但机会永远留给有准备的人，需通过日常学习和能力积累做好准备。
-- **梦想可分阶段调整**：梦想可以一步步立高，如先定考进年级前百的小目标，实现后再争取前五十；目标实现不了时可量力而行、适时调整，不必一步到位。
-- **起点不重要、坚持更重要**：以马云中考考两次、高考考三次最终成为中国首富为例，说明起点高低不影响最终成就，关键在于能否坚持。
-- **不嘲笑他人的梦想**：每个梦想都值得尊重，即使唱歌走调也可通过后天学习调整过来，不应嘲笑任何人的梦想。
-## 学习建议
-- **制定梦想清单并定期检视**：参照老师示范，把自己的梦想按第1、第2、第3条逐项列出，实现一项打一个勾，并标注实现所需时间和预期收获，便于追踪进度。
-- **分阶段设定小目标**：大梦想难以一步实现时，先拆成小目标逐步推进——如先考进年级前百再争取前五十，每达成一个再提高目标。
-- **勇敢行动、抓住机会**：像班内同学主动上台唱歌那样，有勇气站上舞台去行动；同时平时做好准备，机会来临时才能抓住。
-- **坚持努力、不因起点低放弃**：老师提醒“不被嘲笑的梦想不是梦想”，即使被嘲笑也要坚持；可参考老师大学四年保持专业排名第一的做法，用每天坚持（如5点起床）换取目标达成。
-- **梦想要写得实在诚恳**：老师提醒学生写梦想时“写得实在一点、诚恳一点”，可写多个也可只写一个，但都要认真对待；老师承诺相信每一个同学的梦想。</t>
+          <t># 梦想主题班会：认识梦想与坚持
+## 课程概况
+本节班会课以“梦想”为主题，由老师主持，面向全班同学开展。课程围绕五个大点展开，通过提问、个人经历分享、视频观摩和梦想清单书写等环节，引导学生认识梦想、思考实现梦想的条件，并鼓励学生制定和坚持自己的梦想。老师分享了自己的追梦历程：梦想成为受学生喜爱的有名望的优秀人民教师；曾梦想考中国美术学院，单考通过但因离家远和没钱未去，后作为定向生入读广东技术师范大学（原民族学院），定向回龙川县教书，免学费但定向不能考研，只能在职考研；大学四年保持专业排名第一（专业41人），并实现加入学生会、参加比赛、考取教师资格证等梦想。课程播放了航模爱好者何宗发和普通歌手追梦的视频，引导学生讨论实现梦想的条件，总结出坚持、努力、勇敢、机会、兴趣、能力、学习等要素，并强调机会留给有准备的人，梦想可量力而行、分阶段调整。最后，老师让学生写下自己的梦想清单，计划由每个小组第1个同学收集交给老师，班会课结束前学生自愿唱歌。
+## 核心知识点梳理
+### 梦想的定义与价值
+- **梦想的普遍性**：老师以“梦想”为主题开场，提问学生各自的梦想，学生回答包括当保安、当喜剧人、当太空人、当世界冠军、当主角、当歌手等，老师指出“每个班都有人想当太空人”，说明广告词深入人心。
+- **梦想值得尊重**：老师强调“每一个梦想都是值得我们尊重的”，并以“不被嘲笑的梦想不是梦想”鼓励学生，即使梦想看似遥远或被人嘲笑，也应坚持。
+- **梦想的阶段性**：老师指出梦想可以分阶段设立，如先定小目标（考进年级前百）再逐步提高（前50），通过一步步努力实现更大目标。
+### 实现梦想的条件
+- **坚持与努力**：老师以自身经历为例，大学四年保持专业排名第一（专业共41人），强调坚持和自律的重要性，如每天5点起床学习。
+- **勇敢与行动**：老师表扬班上一位同学在同学起哄下仍勇敢站上讲台唱歌，鼓励学生要有勇气去行动，机会留给有准备的人。
+- **兴趣、能力与学习**：老师总结实现梦想需要兴趣、能力、学习、机会等条件，缺一可能影响实现，但具备全部条件则能更快实现梦想。
+- **天赋与后天努力**：老师以歌手梦想为例，指出即使嗓子走调，通过后天学习和努力也可以调整过来，不能因天赋不足而放弃。
+### 梦想的调整与坚持
+- **量力而行与调整**：老师建议梦想需量力而行，若目标暂时无法实现，可先调整目标（如从年级前50调整为前百），再逐步提升。
+- **坚持到底**：老师强调追梦过程可能受挫折，但坚持努力终会有所收获，并引用马云“梦想还是要有的，万一实现了呢”鼓励学生。
+- **梦想清单法**：老师示范将梦想列成清单，逐项实现后打勾，并记录实现所需时间与收获，帮助学生系统规划梦想。
+### 教师个人梦想案例
+- **教师梦想**：老师梦想成为受学生喜爱的有名望的优秀人民教师，并分享自己曾梦想考中国美术学院，单考通过但因离家远和没钱未去，最终作为定向生入读广东技术师范大学（原民族学院），定向回龙川县教书。
+- **定向生限制**：老师说明定向生免学费，但定向不能考研，只能在职考研，且学费需自己承担。
+- **大学梦想实现**：老师大学期间实现加入学生会、参加比赛、保持专业排名第一、考取教师资格证等梦想，并强调大学评价优异是多方面的，不只靠学习成绩。
+### 视频案例与讨论
+- **航模爱好者何宗发**：视频展示何宗发通过努力走上更大舞台，带着歼10模型从古代遨游到未来，目标是参加世界锦标赛，并希望带动更多人参与航空模型运动。
+- **普通歌手追梦**：视频展示普通人想当歌手，在宿舍练习，即使唱歌走调也通过后天学习调整，最终可能实现梦想。
+- **梦想观察团游戏**：老师组织4个大组作为“梦想观察团”，观察航模小伙子和普通歌手两个案例，讨论实现梦想所需条件，总结出坚持、努力、勇敢、机会、兴趣、能力、学习等要素。
+## 课堂互动与答疑
+### Q1. 定向生能否考研
+- **学生**：定向生可以考研吗？
+&gt; **教师**：定向生不能在校考研，但可以在职考研，即边工作边读研，且学费需自己承担。
+### Q2. 老师为何未去中国美术学院
+- **学生**：老师为什么没去中国美术学院？
+&gt; **教师**：单考已通过，但因离家远且学美术费用高，家庭无力承担，最终选择定向生路径，入读广东技术师范大学（原民族学院），定向回龙川县教书，免学费。
+### Q3. 实现梦想需要哪些条件
+- **学生**：如果缺少一个条件，梦想还能实现吗？
+&gt; **教师**：缺少某个条件梦想仍有可能实现，但若坚持、努力、行动、机会、兴趣、能力、学习等条件都具备，梦想会更快实现；其中学习、坚持、行动是必不可少的三个条件。
+### Q4. 梦想无法实现时怎么办
+- **学生**：考不进年级前50怎么办？
+&gt; **教师**：可先调整目标为考进年级前百，实现后再逐步提高至前50，梦想应量力而行、分阶段调整，一步步向前推进。
+## 课后任务与学习建议
+### 课堂练习
+- [ ] **梦想清单书写**：学生拿出纸写下自己的梦想，可参照老师示范的清单格式（第1个、第2个、第3个……），逐项列出梦想、实现所需时间及实现后的收获，写完后由每个小组第1个同学收集交给老师。
+- [ ] **梦想观察团讨论**：全班4个大组各为一个观察团，分别观察航模爱好者与想当歌手的普通人两个追梦案例，讨论实现梦想需要具备哪些条件，并派代表发言分享结论。
+### 复习重点
+- **实现梦想的条件**：坚持、努力、勇敢、机会、兴趣、能力、学习等要素缺一不可；其中学习、坚持、行动是必不可少的三个条件，机会永远留给有准备的人。
+- **梦想可调整与分阶段**：梦想实现不了时可量力而行、调整目标（如先考进年级前百再冲前50），可先定小目标再定大目标，梦想清单列得越多实现几率越大。
+- **梦想值得尊重**：不要嘲笑任何人的梦想，唱歌走调可通过后天学习调整过来；每个梦想都是独一无二、不可复制的，如马云的成功不可复制。
+- **老师个人经历佐证**：老师曾梦想考中国美术学院，单考通过但因离家远和没钱未去，后作为定向生入读广东技术师范大学（原民族学院），定向回龙川县教书，免学费但定向不能考研，只能在职考研；大学四年保持专业排名第一（专业41人）。
+### 学习建议
+- **制定梦想清单**：参照老师示范，用纸笔列出自己的梦想清单，逐项标注实现所需时间与预期收获，实现后打勾，可同时制定多个梦想以增加实现几率。
+- **分阶段调整目标**：当梦想暂时无法实现时，可先调整为更易达成的阶段性目标（如先考进年级前百再冲前50），一步步向前推进，不必一步到位。
+- **坚持与行动**：梦想需要坚持努力和实际行动去实现，如老师大学四年保持专业排名第一需每天5点起床；机会留给有准备的人，要勇敢抓住机会（如同学勇敢上台唱歌）。
+- **不嘲笑他人梦想**：无论他人梦想看似多远大或多平凡（如当保安、当喜剧人、当歌手），都应尊重；唱歌走调可通过后天学习调整，不要嘲笑任何人的梦想。</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>43.8</v>
+        <v>39</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9362/3553</t>
+          <t>9362/2953</t>
         </is>
       </c>
     </row>
@@ -4048,80 +4029,97 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t># 全文摘要
-本期新闻联播由中央广播电视总台播出，围绕国内发展成就与国际动态展开。头条报道习近平总书记提出“两个结合”，强调马克思主义基本原理同中国具体实际、同中华优秀传统文化相结合是必由之路；2023年6月文化传承发展座谈会系统论述中华文明五个突出特性，同年10月全国宣传思想文化工作会议首次提出习近平文化思想。赵乐际于7月9日至13日对俄罗斯进行正式友好访问，会见总统普京，与俄议会领导人会谈并出席中俄议会合作委员会第九次会议。农业与物流方面，今年夏粮产量达2996亿斤，创历史新高；6月国家铁路发送货物3.32亿吨，同比增长6.1%；上半年快递业务量超800亿件。能源与防汛方面，预计全年新增油气管网里程超4000公里，重庆等地积极应对暴雨。国内快讯涵盖北京重大项目、燕矶长江大桥、环青海湖自行车赛、草原那达慕及“中非儿童手拉手”活动；国际新闻涉及特朗普遭未遂刺杀、以军空袭加沙致90人死亡等。
-# 分段速览
-## 00:00–08:31 文化自信与中华民族现代文明建设
-报道开篇以习近平总书记文化论述为主线，回顾其在孔子故里、岳麓书院、三苏祠、武夷山朱熹园等地的考察讲话，强调“两个结合”特别是“第二个结合”的重大意义。2023年6月文化传承发展座谈会系统论述中华文明五个突出特性，同年10月全国宣传思想文化工作会议首次提出习近平文化思想。报道列举《深化文化体制改革实施方案》《关于实施中华优秀传统文化传承发展工程的意见》等政策文件，以及中华文明探源工程、国家文化公园建设、文化地标落成、《复兴文库》出版等实践成果，展现文化体制改革在正本清源、守正创新中取得的历史性成就。
-## 08:39–12:31 赵乐际访问俄罗斯并出席中俄议会合作委员会第九次会议
-全国人大常委会委员长赵乐际应俄联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，于7月9日至13日对俄罗斯进行正式友好访问。赵乐际在圣彼得堡会见总统普京，转达习近平主席问候，强调今年是中俄建交75周年，两国立法机构应落实元首共识；在莫斯科与马特维延科、沃洛金分别会谈，就核心利益相互支持、深化多层级交流合作达成共识。10日，赵乐际出席中俄议会合作委员会第九次会议并致辞，提出密切战略协作、交流治国理政经验、以法治方式促进务实合作等五点建议。访问期间，赵乐际向俄无名烈士墓敬献花圈。
-## 12:49–14:21 夏粮产量创历史新高
-报道今年夏粮生产情况，产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高。夏粮单产每亩375.2公斤，其中小麦单产399.1公斤，比2023年增加10公斤，单产恢复性增长是产量增加的主要原因。中央深入推进“藏粮于地、藏粮于技”战略，全国已建成高标准农田10亿多亩，农业农村部启动小麦单产提升三年行动，中央财政首次提前下拨16亿元小麦“一喷三防”资金。小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高，为全年粮食丰收奠定基础。
-## 14:28–17:22 铁路货运与快递业发展提速
-6月份国家铁路货运多项指标创历史同期新高，发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%；化肥农药运量增幅最大，同比增长26.2%，中欧班列6月开行1719列，发送货物18万标箱，同比分别增长15%、11%。上半年快递业务量超800亿件，快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线；每天超1亿件快递包裹在农村地区流动，5—6月快递日均业务量近5亿件，快递业与制造业融合发展。
-## 17:29–19:12 油气管网建设提速
-今年我国油气管网基础设施加速建设，预计全年新增管道里程超4000公里。西气东输四线已完成吐鲁番至中卫段主体管道工程建设，投产后年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程加速推进。目前主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气“全国一张网”日供气能力超10亿立方米。到2025年将初步形成四大油气战略通道，建成“五纵五横”天然气干线管网。
-## 19:20–20:40 渝川皖等地应对降雨天气
-重庆28个区县出现暴雨，其中13个区县大暴雨，当地组织工作人员连夜抢险排涝；四川内江出现内涝、滑坡等险情，消防救援人员转移被困群众；安徽滁州市全椒县加强巡堤，处置堤防渗漏和管涌。水利部针对“七下八上”防汛关键期逐流域安排防御，长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程，水利部联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
-## 20:41–23:38 国内联播快讯
-北京上半年320个市区重大项目全部开工，总投资超4000亿元；燕矶长江大桥北岸主塔封顶，主跨1860米，建成后将成为鄂东空铁、空陆联运立体交通运输体系的重要过江通道；第二十三届环青海湖国际公路自行车赛收官，22支车队154名运动员决出5个奖项冠军；内蒙古第34届草原那达慕开幕，将持续到8月底；“中非儿童手拉手”活动在京启动，来自纳米比亚、南非、中非、索马里、乌干达五国儿童代表将在北京、河南两地参观访问。
-## 23:47–30:07 国际新闻
-多国人士高度关注即将召开的党的二十届三中全会，表示中国全面深化改革、扩大开放为世界提供更广阔市场和发展机遇。美国前总统特朗普在宾夕法尼亚州竞选集会遭未遂刺杀，右耳中枪，一名观众死亡、两名受重伤，枪手被特勤局狙击手打死。以军空袭加沙地带马瓦西地区致90人死亡、约300人受伤，巴勒斯坦总统阿巴斯谴责以军违反国际法；以军袭击黎巴嫩多个边境村镇，黎真主党武装打击以军集结地；叙利亚大马士革遭空袭致1名政府军士兵死亡。俄军打击乌军列车点，乌军击退俄军17次进攻；加拿大林火过火面积100平方公里，9600人被疏散。
-# 要点梳理
-## 文化自信与中华民族现代文明建设
-- **理论创新**：习近平总书记提出“两个结合”，强调把马克思主义基本原理同中国具体实际、同中华优秀传统文化相结合是必由之路；2023年6月文化传承发展座谈会系统论述中华文明五个突出特性，2023年10月全国宣传思想文化工作会议首次提出习近平文化思想。
-- **实地考察**：在孔子故里翻看《孔子家语通解》《论语诠解》；在岳麓书院凝望“实事求是”匾额，指出一定要把真理本土化；在三苏祠强调汲取治国理政理念和思维；在武夷山朱熹园提出以时代精神激活中华优秀传统文化生命力。
-- **政策文件**：《深化文化体制改革实施方案》是中央深改领导小组审议通过的第一个专项小组改革方案；《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式对文化传承发展进行部署。
-- **建设成就**：我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力“新引擎”，电影市场规模屡创新高；中华文明探源工程深入实施，国家文化公园建设高标准推进，中国共产党历史展览馆、国家版本馆等文化地标落成，《复兴文库》、“中国历代绘画大系”出版。
-## 赵乐际访问俄罗斯
-- **访问行程**：应俄国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，赵乐际于7月9日至13日对俄罗斯进行正式友好访问，在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别会谈，并出席中俄议会合作委员会第九次会议；今年是中俄建交75周年。
-- **会谈内容**：赵乐际表示中国全国人大愿同俄罗斯联邦会议一道，从立法机构层面落实两国元首重要共识，为巩固政治互信、深化务实合作、增进人民友谊作贡献；两国立法机构要立足职能职责，用好中俄议会合作委员会、双边友好小组等机制和平台，互学互鉴立法经验。
-- **俄方表态**：普京表示俄中立法机构始终保持高水平合作，有助于在立法层面推进双边合作优先议题；马特维延科表示发展对华关系得到俄社会广泛认同和支持；沃洛金表示俄国家杜马不同党派在发展对华关系上高度一致，俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政。
-- **会议致辞**：赵乐际出席中俄议会合作委员会第九次会议并致辞，提出密切战略协作、交流治国理政经验、发挥立法机构职能作用、传承弘扬传统友谊、加强多边协作团结壮大“全球南方”力量等五点建议。
-- **其他活动**：访问期间，赵乐际在莫斯科向俄无名烈士墓敬献花圈。
-## 夏粮产量创历史新高
-- **产量数据**：今年夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高；夏粮单产每亩375.2公斤，其中小麦单产399.1公斤，比2023年增加10公斤，单产恢复性增长是产量增加的主要原因。
-- **政策支撑**：中央深入推进“藏粮于地、藏粮于技”战略，全国已建成高标准农田10亿多亩；农业农村部启动小麦单产提升三年行动，中央财政首次提前下拨16亿元小麦“一喷三防”资金。
-- **质量亮点**：小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高；夏粮首战告捷为全年粮食丰收奠定坚实基础。
-## 6月份国家铁路货运
-- **总体指标**：6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高；我国铁路货运量、货运周转量等指标稳居世界首位。
-- **重点物资**：化肥农药运量增幅最大，同比增长26.2%；煤炭日均装车量，集装箱、商品汽车、冷链货物发送量等均创历史同期新高。
-- **运输网络**：连接内陆物流节点城市的多式联运快车已覆盖各省会城市，铁海快线班列已覆盖全国主要港口；6月中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%。
-## 上半年快递业发展
-- **业务总量**：截至6月30日，今年我国快递业务量已达800亿件；5—6月生鲜商品进入销售旺季，电商促销拉动线上消费，快递日均业务量近5亿件。
-- **国际与农村网络**：快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线；农村寄递网络覆盖范围逐渐扩大，每天超1亿件快递包裹在农村地区流动。
-- **融合发展**：快递业不断丰富服务场景，拓展服务领域，实现与制造业的融合发展。
-## 油气管网建设
-- **建设进展**：预计全年新增管道里程超4000公里；西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程加速推进。
-- **供应能力**：目前主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气“全国一张网”日供气能力超10亿立方米。
-- **未来规划**：到2025年将初步形成东北、西北、西南及海上四大油气战略通道，建成“五纵五横”天然气干线管网。
-## 渝川皖等地应对降雨
-- **重庆**：7月13日8时至14日8时，九龙坡、江北等28个区县出现暴雨，其中沙坪坝、江津等13个区县大暴雨，当地组织工作人员连夜抢险排涝。
-- **四川**：暴雨造成内江部分地区出现内涝、滑坡等险情，消防救援人员紧急出动转移被困群众。
-- **安徽**：强降雨导致多条河流水位上涨，滁州市全椒县工作人员加强巡堤，及时处置堤防渗漏和管涌。
-- **防汛调度**：水利部针对“七下八上”防汛关键期逐流域安排防御；长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程，水利部联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
-## 国内联播快讯
-- **北京重大项目**：上半年计划新开工的320个市区重大项目已全部开工，包括丽泽数字金融科技示范园、温榆河生态治理工程等，聚焦现代化产业、基础设施、城市更新等领域，总投资超4000亿元。
-- **燕矶长江大桥**：7月14日北岸主塔封顶，下一步转入主缆施工阶段；大桥连接湖北鄂州和黄冈，主跨1860米，上层为高速公路、下层为城市快速路，建成后将成为鄂东空铁、空陆联运立体交通运输体系的重要过江通道。
-- **环青海湖国际公路自行车赛**：第二十三届赛事7月14日在海北州门源县收官，经过8天8个赛段，来自国内外22支车队的154名运动员决出个人总成绩、爬山积分、团体总积分等5个奖项冠军。
-- **草原那达慕**：内蒙古第34届草原那达慕7月14日在锡林浩特市开幕，主题为“相约草原遇见那达慕”，持续到8月底，将开展体育赛事、文艺表演、美食品鉴、非遗展示等活动。
-- **中非儿童手拉手**：7月14日由外交部、全国妇联主办的活动在中国儿童中心启动，来自纳米比亚、南非、中非、索马里、乌干达五国的儿童代表将在北京、河南两地参观访问。
-## 国际新闻
-- **多国人士评价**：多国人士高度关注即将召开的中国共产党二十届三中全会，表示中国全面深化改革、扩大开放，在许多领域实现历史性变革，为人类更加美好的未来贡献智慧与力量。
-- **特朗普竞选集会枪击**：7月13日在美国宾夕法尼亚州巴特勒市特朗普竞选集会上发生枪击，特朗普称其右耳中枪受伤，竞选团队称其“状况良好”；枪击造成一名观众死亡、两名观众受重伤；枪手从集会现场外高处向演讲台“开了数枪”，所处屋顶距演讲台约180多米到270多米，开枪后被特勤局狙击手打死；美联邦调查局称特朗普遭未遂刺杀，枪手为20岁左右男性、来自宾夕法尼亚州，作案动机待查明。
-- **以军空袭加沙**：以军13日空袭加沙南部汗尤尼斯马瓦西地区，死亡人数升至90人、约300人受伤，死伤者中包括许多妇女和儿童；内塔尼亚胡称空袭目标是哈马斯下属“卡桑旅”领导人穆罕默德·戴夫和“汗尤尼斯旅”指挥官萨拉马；哈马斯表示袭击使局势“严重升级”；巴勒斯坦总统阿巴斯谴责以军违反国际法，约旦、卡塔尔、埃及等也发表声明谴责。
-- **以军袭击黎巴嫩**：黎巴嫩多个边境村镇遭以军空袭、炮击和机枪扫射，部分地区因白磷弹袭击发生火灾；黎真主党武装称打击了以色列北部以军集结地和情报设施。
-- **叙利亚遭空袭**：叙利亚军方称7月14日凌晨大马士革卡夫苏萨地区等多个地点遭空袭，造成1名政府军士兵死亡、3人受伤；以色列国防军称空袭了叙利亚军事指挥所、防空系统等目标。
-- **俄乌冲突**：俄国防部称使用“伊斯坎德尔-M”导弹打击哈尔科夫方向一处乌军军用火车停车点，摧毁包括3辆德制步兵战车在内的20件乌军装备；乌武装部队总参谋部称乌军当天与俄军交战上百次，在波克罗夫斯克方向击退俄军17次进攻。
-- **加拿大林火**：13日纽芬兰与拉布拉多省林火迅速蔓延，过火面积达100平方公里，拉布拉多城9600人被疏散；消防人员称火势迅速升级已无法继续使用灭火飞机；加拿大目前正应对500多起活跃林火，其中超400起处于失控状态。</t>
+          <t># 新闻联播：国内发展成就与国际动态报道
+## 全文摘要
+本期新闻联播由央视播音员播报，围绕国内发展成就与国际动态展开。国内板块涵盖：文化自信与中华民族现代文明建设，回顾习近平总书记提出“两个结合”、系统论述中华文明五个突出特性并首次提出习近平文化思想；全国人大常委会委员长赵乐际于7月9日至13日访俄，会见普京并与俄方议会领导人会谈、出席中俄议会合作委员会第九次会议；夏粮产量达2996亿斤创历史新高；6月国家铁路货运多项指标创同期新高；上半年快递业务量超800亿件；油气管网建设提速；渝川皖等地应对降雨及防汛调度；以及北京重大项目开工、燕矶长江大桥封顶等国内快讯。国际板块包括特朗普竞选集会遭未遂刺杀、以军空袭加沙致90人死亡、加拿大林火致9600人疏散等。关键数字锚点：夏粮产量2996亿斤、6月铁路发送货物3.32亿吨、上半年快递业务量800亿件、全年预计新增管道里程超4000公里、以军空袭致90人死亡。本期以信息播报为主，未形成明确结论。
+## 分段速览
+### 00:00-08:31 文化自信与中华民族现代文明建设
+本段为头条报道，聚焦习近平总书记以文化自信引领社会主义文化强国建设。总书记在孔子故里、岳麓书院、三苏祠、武夷山朱熹园等地考察时强调将中华优秀传统文化精华与马克思主义立场观点方法相结合。2023年6月文化传承发展座谈会系统论述中华文明五个突出特性，阐述"两个结合"重大意义；同年10月全国宣传思想文化工作会议首次提出习近平文化思想。《深化文化体制改革实施方案》成为中央深改领导小组审议通过的第一个专项小组改革方案，《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式部署文化传承发展。文化领域供给侧结构性改革深入推进，我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为消费新引擎。
+### 08:31-12:39 赵乐际访俄并出席中俄议会合作委员会第九次会议
+全国人大常委会委员长赵乐际应俄国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，于7月9日至13日对俄罗斯进行正式友好访问。赵乐际在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别会谈，并出席中俄议会合作委员会第九次会议。今年是中俄建交75周年，双方强调从立法机构层面落实两国元首重要共识。赵乐际在会议致辞中提出密切战略协作、交流治国理政经验、以法治方式促进务实合作、传承弘扬传统友谊、团结壮大"全球南方"力量五点建议。沃洛金表示俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政。访问期间，赵乐际向俄无名烈士墓敬献花圈。
+### 12:39-14:21 夏粮产量创历史新高
+今年我国夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高。夏粮单产每亩375.2公斤，其中小麦单产399.1公斤，比2023年增加10公斤，单产恢复性增长是产量增加的主要原因。中央深入推进"藏粮于地、藏粮于技"战略，全国已建成高标准农田10亿多亩，农业农村部启动小麦单产提升三年行动，中央财政首次提前下拨16亿元小麦"一喷三防"资金。小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高，夏粮首战告捷为全年粮食丰收奠定坚实基础。
+### 14:21-16:03 铁路货运与快递业发展提速
+6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高，铁路货运量、货运周转量稳居世界首位。化肥农药运量同比增长26.2%，煤炭日均装车量、集装箱、商品汽车、冷链货物发送量均创历史同期新高。中欧班列6月开行1719列，发送货物18万标箱，同比分别增长15%、11%。上半年快递业务量截至6月30日达800亿件，快递企业已运行国际航线40余条，每天超1亿件快递包裹在农村地区流动，5—6月快递日均业务量近5亿件。
+### 16:03-19:12 油气管网建设提速
+我国油气管网基础设施加速建设，预计全年新增管道里程超4000公里。西气东输四线已完成吐鲁番至中卫段主体管道工程建设，投产后年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程加速推进。目前主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气"全国一张网"日供气能力超10亿立方米。到2025年将初步形成东北、西北、西南及海上四大油气战略通道，建成"五纵五横"天然气干线管网。
+### 19:12-20:40 渝川皖等地应对降雨天气
+重庆28个区县出现暴雨，其中13个区县大暴雨，当地组织工作人员连夜抢险排涝；四川内江部分地区出现内涝、滑坡等险情，消防救援人员转移被困群众；安徽滁州市全椒县工作人员加强巡堤，处置堤防渗漏和管涌。水利部针对"七下八上"防汛关键期逐流域安排防御。长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程，水利部联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
+### 20:40-23:38 国内联播快讯
+北京上半年320个市区重大项目全部开工，总投资超4000亿元，聚焦现代化产业、基础设施、城市更新等领域。燕矶长江大桥北岸主塔封顶，主跨1860米，建成后将成为鄂东空铁、空陆联运立体交通运输体系的重要过江通道。第二十三届环青海湖国际公路自行车赛收官，22支车队154名运动员决出5个奖项冠军。内蒙古第34届草原那达慕在锡林浩特市开幕，持续到8月底。"中非儿童手拉手"活动在京启动，来自纳米比亚、南非、中非、索马里、乌干达五国儿童代表将在北京、河南两地参观访问。
+### 23:38-30:27 国际新闻与改革专题
+多国人士高度关注即将召开的党的二十届三中全会，表示中国全面深化改革、扩大开放为世界提供更广阔市场和发展机遇。美国前总统特朗普在宾夕法尼亚州竞选集会遭未遂刺杀，右耳中枪受伤，一名观众死亡、两名受重伤，枪手为20岁左右男性，来自宾夕法尼亚州，作案动机待查明。以军空袭加沙地带马瓦西地区致90人死亡、约300人受伤，巴勒斯坦总统阿巴斯谴责以军违反国际法。以军袭击黎巴嫩多个边境村镇，黎真主党武装打击以军集结地。俄军打击哈尔科夫方向乌军列车点，乌军称击退俄军17次进攻。加拿大纽芬兰与拉布拉多省林火过火面积100平方公里，9600人被疏散。
+## 要点梳理
+### 文化自信与中华民族现代文明建设
+1. 习近平总书记提出“两个结合”，即把马克思主义基本原理同中国具体实际、同中华优秀传统文化相结合，指出这是开辟和发展中国特色社会主义的必由之路。
+2. 2023年6月，习近平总书记主持召开文化传承发展座谈会，系统论述中华文明的五个突出特性，进一步阐述“两个结合”尤其是“第二个结合”的重大意义。
+3. 2023年10月，全国宣传思想文化工作会议在京召开，首次提出习近平文化思想。
+4. 《深化文化体制改革实施方案》是中央全面深化改革领导小组审议通过的第一个专项小组改革方案，为文化改革发展谋篇布局。
+5. 《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式对文化传承发展进行部署。
+6. 我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为激发消费潜力“新引擎”，电影市场规模屡创新高。
+7. 习近平总书记先后在孔子故里翻看《孔子家语通解》《论语诠解》，在岳麓书院凝望“实事求是”匾额并指出一定要把真理本土化，在三苏祠强调要善于从中华优秀传统文化中汲取治国理政的理念和思维，在武夷山朱熹园提出要以时代精神激活中华优秀传统文化的生命力。
+8. 文化领域供给侧结构性改革深入推进，文化旅游深度融合、非遗保护传承制度日益完善、公共文化服务体系不断健全；深入实施中华文明探源工程，高标准推进国家文化公园建设，中国共产党历史展览馆、国家版本馆等文化地标落成，《复兴文库》、“中国历代绘画大系”出版。
+&gt; “我们五千年的文明，我们要尊重，也要弘扬，把它里边精华的东西和我们现在所坚持的马克思主义立场、观点、方法结合起来，这就是中国特色社会主义。”
+&gt; —— **习近平** ｜ 关于中华文明与马克思主义相结合的重要论述
+### 赵乐际访问俄罗斯并出席中俄议会合作委员会第九次会议
+1. 应俄罗斯联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，全国人大常委会委员长赵乐际于7月9日至13日对俄罗斯进行正式友好访问，在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别举行会谈，并出席中俄议会合作委员会第九次会议。
+2. 今年是中俄建交75周年，在两国元首战略引领下，中俄新时代全面战略协作伙伴关系高水平、高质量发展。
+3. 赵乐际表示，中国全国人大愿同俄罗斯联邦会议一道，从立法机构层面落实两国元首重要共识，为巩固政治互信、深化务实合作、增进人民友谊作贡献。
+4. 普京表示，俄中立法机构始终保持高水平合作，加强俄中议会合作委员会工作有利于两国交流经验、互学互鉴，促进立法、地方等各领域合作，增进两国人民友谊。
+5. 与马特维延科、沃洛金会谈时，赵乐际提出要以两国元首重要共识为指引，保持战略定力，坚定道路自信，在涉及彼此核心利益问题上坚定相互支持；两国立法机构要深化多层级、多领域、多渠道交流合作，互学互鉴立法经验，为务实合作提供法治保障。
+6. 马特维延科表示，发展对华关系得到俄社会的广泛认同和支持，两国立法机构要加强立法合作，推进地方立法机构、青年议员和人大代表之间的交流。
+7. 沃洛金表示，俄国家杜马不同党派在发展对华关系上高度一致，俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政。
+8. 7月10日，赵乐际出席中俄议会合作委员会第九次会议并致辞，提出密切战略协作、交流治国理政经验、发挥立法机构职能作用、传承弘扬传统友谊、加强多边协作五点建议。
+9. 访问期间，赵乐际在莫斯科向俄无名烈士墓敬献花圈。
+### 夏粮产量创历史新高
+1. 今年我国夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高。
+2. 夏粮单产每亩达到375.2公斤，其中小麦单产达399.1公斤，比2023年增加10公斤；单产实现恢复性增长，是夏粮产量增加的主要原因。
+3. 全国已建成高标准农田10亿多亩，农业农村部启动小麦单产提升三年行动，中央财政首次提前下拨16亿元小麦“一喷三防”资金。
+4. 小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高；夏粮首战告捷为全年粮食丰收奠定坚实基础。
+### 6月份国家铁路货运指标增长
+1. 6月份，国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高。
+2. 我国铁路货运量、货运周转量等指标稳居世界首位。
+3. 分品类看，化肥农药运量增幅最大，同比增长26.2%；煤炭日均装车量，集装箱、商品汽车、冷链货物发送量等均创历史同期新高。
+4. 连接内陆物流节点城市的多式联运快车已覆盖各省会城市，铁海快线班列已覆盖全国主要港口。
+5. 6月份，中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%。
+### 上半年快递业发展提速
+1. 截至6月30日，今年我国快递业务量已达800亿件。
+2. 上半年快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线；多地启用、升级跨境仓，农村寄递网络覆盖范围逐渐扩大。
+3. 每天超1亿件快递包裹在农村地区流动，5—6月生鲜商品进入销售旺季、电商促销拉动线上消费，快递日均业务量近5亿件。
+4. 快递业不断丰富服务场景，拓展服务领域，实现与制造业的融合发展。
+### 油气管网建设提速
+1. 预计全年新增管道里程超4000公里，“全国一张网”不断完善，供应保障能力持续提升。
+2. 西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后西气东输年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程加速推进。
+3. 目前主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气“全国一张网”日供气能力超10亿立方米。
+4. 到2025年，将初步形成东北、西北、西南以及海上四大油气战略通道，建成“五纵五横”的天然气干线管网。
+### 渝川皖等地应对降雨天气
+1. 7月13日8时至14日8时，重庆九龙坡、江北等28个区县出现暴雨，其中沙坪坝、江津等13个区县大暴雨，当地组织工作人员连夜抢险排涝。
+2. 四川内江部分地区出现内涝、滑坡等险情，消防救援人员紧急出动转移被困群众。
+3. 安徽多条河流水位上涨，滁州市全椒县工作人员加强巡堤，及时处置堤防渗漏和管涌等情况。
+4. 长江1号、2号洪水正在演进，三峡水库15日将迎来一次洪峰流量45000立方米每秒量级的洪水过程；水利部联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
+### 国内联播快讯
+1. 北京上半年计划新开工的320个市区重大项目已全部开工，包括丽泽数字金融科技示范园、温榆河生态治理工程等，聚焦现代化产业、基础设施、城市更新等领域，总投资超4000亿元。
+2. 7月14日，燕矶长江大桥北岸主塔封顶，下一步转入主缆施工阶段；大桥连接湖北鄂州和黄冈，主跨1860米，上层为高速公路、下层为城市快速路，建成后将成为鄂东空铁、空陆联运立体交通运输体系的重要过江通道。
+3. 第二十三届环青海湖国际公路自行车赛7月14日在海北州门源县落幕，经过8天8个赛段比赛，来自国内外22支车队的154名运动员决出个人总成绩、爬山积分、团体总积分等5个奖项冠军。
+4. 内蒙古第34届草原那达慕7月14日在锡林浩特市开幕，主题为“相约草原遇见那达慕”，持续到8月底，其间开展体育赛事、文艺表演、美食品鉴、非遗展示等活动。
+5. 7月14日，由外交部、全国妇联主办的“中非儿童手拉手”活动在中国儿童中心启动，来自纳米比亚、南非、中非、索马里、乌干达五国的儿童代表将在北京、河南两地参观访问。
+### 国际新闻
+1. 多国人士高度关注即将召开的中国共产党二十届三中全会，表示中国全面深化改革、扩大开放，在许多领域实现历史性变革，为人类更加美好的未来贡献智慧与力量。
+2. 7月13日，美国宾夕法尼亚州巴特勒市特朗普竞选集会发生枪击，特朗普称其右耳中枪受伤，竞选团队称其“状况良好”；枪击造成一名观众死亡、两名观众受重伤。美联邦调查局称特朗普遭未遂刺杀，正展开调查；枪手为20岁左右男性，来自宾夕法尼亚州，作案动机有待查明。
+3. 以军13日空袭加沙地带南部汗尤尼斯马瓦西地区，死亡人数升至90人、约300人受伤，死伤者中包括许多妇女和儿童；内塔尼亚胡称空袭目标是哈马斯下属武装派别“卡桑旅”领导人穆罕默德·戴夫和“汗尤尼斯旅”指挥官萨拉马。巴勒斯坦总统阿巴斯谴责以军违反国际法，约旦、卡塔尔、埃及等发表声明予以谴责。
+4. 以军13日称在加沙地带南部拉法、北部加沙城等地打击巴武装人员和军用设施；巴武装派别称在拉法、加沙城等地使用迫击炮、火箭弹等打击以军阵地和坦克。
+5. 黎巴嫩多个边境村镇遭以军空袭、炮击和机枪扫射，部分地区因以军白磷弹袭击发生火灾；黎巴嫩真主党武装称打击了位于以色列北部的以军集结地和情报设施。
+6. 叙利亚军方7月14日称，大马士革卡夫苏萨地区等多个地点遭空袭，造成1名政府军士兵死亡、3人受伤；以色列国防军称空袭了叙利亚军事指挥所、防空系统等目标。
+7. 俄罗斯国防部13日称，俄军使用“伊斯坎德尔-M”导弹打击哈尔科夫方向一处乌军军用火车停车点，摧毁包括3辆德制步兵战车在内的20件乌军装备；乌克兰武装部队总参谋部称乌军当天与俄军交战上百次，在波克罗夫斯克方向击退俄军17次进攻。
+8. 加拿大东北部纽芬兰与拉布拉多省林火迅速蔓延，过火面积达100平方公里，拉布拉多城9600人被疏散；加拿大目前正应对500多起活跃林火，其中超400起处于失控状态。</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>69.2</v>
+        <v>68.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7755/6123</t>
+          <t>7755/6582</t>
         </is>
       </c>
     </row>
@@ -4359,138 +4357,130 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t># 课程概况
-本节课为初中光学复习课，主讲人系统梳理了光的直线传播、光的反射定律、镜面反射与漫反射、平面镜成像及球面镜应用五大板块，并通过例题讲解巩固知识点。课程首先介绍光源（自然光源如太阳，人造光源如火把、电灯）与光线（物理模型，非真实存在），强调光在均匀介质中沿直线传播，实例包括三点一线、激光准直、小孔成像、日食月食、影子形成。小孔成像成倒立、缩小的实像，与孔形状无关；日食时月球在太阳和地球之间，月食时地球在太阳和月球之间。光在真空中的传播速度为3×10^8米/秒，空气中略慢，水中约为真空的3/4，玻璃中约为2/3。例题计算：一束激光从地球射到月球表面用时1.25秒，地月距离为3.75×10^8米；发生雷电时先看到闪电后听到雷声，因为光速大于声速。光的反射定律部分，主讲人讲解三线共面、分居两侧、反射角等于入射角，强调作图时先画法线，再根据反射角等于入射角画反射或入射光线。关键例题：光垂直射到镜面上时，入射角和反射角均为0度；反射光线与平面镜夹角40度时，入射角为50度。镜面反射与漫反射部分，主讲人区分两者：镜面反射发生在光滑表面（如平面镜、平静水面），漫反射发生在凹凸不平表面（如黑板、电影银幕），两种反射都遵守光的反射定律。平面镜成像部分，主讲人讲解成像原理（光的反射定律）与特点（正立、等大的虚像），实验用玻璃板代替平面镜便于确定像的位置，刻度尺用于比较像与物到镜面的距离，两段相同蜡烛用于比较像与物大小。球面镜部分，凸面镜对光线起发散作用，成缩小正立的虚像，用于汽车后视镜、丁字路口反光镜；凹面镜对光线起会聚作用，用于手电筒、汽车前灯、太阳灶、医生额镜。
-# 核心知识点梳理
-## 光的直线传播
-- **光源定义**：自身能够发光的物体，分为自然光源（如太阳）和人造光源（如火把、蜡烛、煤油灯、电灯）。
-- **光线概念**：用一条带箭头的直线代表光线，是**物理模型**，并非真实存在；按来源分为点光源与平行光源，画图时点光源画成点，太阳等无限远处光源画成平行光。
-- **传播规律**：光在均匀介质中沿直线传播；大气层不均匀时，光线会发生偏折，如太阳越出地平线、星星眨眼等现象。
-- **三点一线实例**：步枪瞄准时眼睛看到瞄准点、准心尖和标尺缺口三者重合，依据是光在均匀介质中沿直线传播；队列排齐、木工看尺子是否平直同理。
-- **激光准直**：利用激光沿直线传播进行准直，是直线传播的实例。
-- **小孔成像**：成**倒立**的实像，放大缩小不一定，与孔形状无关；光斑是太阳透过树叶缝隙在地面形成的小孔成像，因太阳距地球远，得到的是太阳缩小的像，角度不正时呈椭圆形。
-- **日食与月食**：日食时太阳、月球、地球在同一直线上，**月球在中间**；1号区域日全食，2、3号区域日偏食，4号区域日环食。月食时**地球在中间**；月球完全在1号区域为月全食，部分在1号区域、部分在2或3号区域才出现月偏食，仅处于2、3号区域只会略暗不叫月偏食。
-- **影子形成**：影子（俗称阴影）的形成是光沿直线传播的实例，如唐朝皮影戏利用此原理。
-- **光速**：光在真空中的传播速度为 `3×10^8` 米/秒（`3×10^5` 千米/秒），约每秒绕地球赤道7圈半；空气中约 `2.99×10^8` 米/秒，比真空中略慢；水中约为真空中的3/4，玻璃中约为2/3。
-- **介质条件**：光传播的介质指透明物质（如有机玻璃、水），砖头、黑板不算；海水清澈时太阳光最多到达约200米深度。
-- **例题计算**：一束激光从地球射到月球表面用时1.25秒，地月距离为 `3.75×10^8` 米（`s=V×T`）；发生雷电时先看到闪电后听到雷声，因为光速比声速快（声速15℃时约340米/秒）。
-## 光的反射定律
-- **基本概念**：入射光线AO射到平面镜上，O为入射点，反射光线为OB；法线OP垂直于镜面，是入射角与反射角的角平分线，**法线是辅助线，真实不存在，画虚线**。
-- **定律内容**：反射光线、入射光线和法线在同一平面内（三线共面）；反射光线和入射光线分居法线两侧；反射角等于入射角。
-- **易错点**：光垂直射到镜面上时，入射角和反射角均为**0度**（不是90度）；反射光线与平面镜夹角40度时，入射角为50度。
-- **作图步骤**：先画法线（虚线，画两三段即可），再根据反射角等于入射角画反射或入射光线，最后补全箭头；作图痕迹保留法线即可。
-- **例题结论**：入射光线与法线夹角60度时反射角60度；反射光线与入射光线夹角80度时反射角40度；入射光线与镜面夹角增大时，入射角减小、反射角减小，传播速度不变。
-## 镜面反射与漫反射
-- **镜面反射**：平行光射到光滑表面（平面镜、平静水面、光滑金属表面），反射光平行；若人眼不在反射光方向上则看不到反射光，如商场玻璃隔断易使人撞上。
-- **漫反射**：平行光射到凹凸不平表面，每个小面看作小平面镜，反射光线射向各个方向；生活中大多数反射是漫反射，如黑板、电影银幕、人的皮肤。
-- **共同规律**：镜面反射和漫反射**都遵守光的反射定律**。
-- **雨后水潭判断**：迎着月光走，地面上发亮处是水潭（发生镜面反射）；背着月光走，暗处是水潭。
-- **白纸与镜子实验**：手电筒光垂直照在白纸上的小镜子上，斜着看镜子是黑的、周围白纸是亮的，因为镜子发生镜面反射光线返回，白纸发生漫反射。
-- **生活实例**：电影院白色银幕产生漫反射；教室某些位置看黑板只见光亮看不清粉笔字，是黑板发生镜面反射。
-## 平面镜成像
-- **成像原理**：依据光的反射定律，反射光线反向延长线的交点即像的位置；像与物的连线**垂直于镜面**，像到镜面距离等于物到镜面距离。
-- **成像特点**：成**正立、等大的虚像**；光屏不能接收到虚像，因为实际光线没有到达像的位置。
-- **实验器材作用**：用玻璃板代替平面镜，便于确定像的位置；刻度尺用于比较像与物相对镜面的距离；两段完全相同的蜡烛用于比较像与物的大小。
-- **实验误差原因**：玻璃板与水平面不垂直（或未与预先画好的镜面位置重合）；玻璃板有厚度，两个面发生反射成像，厚玻璃板（如8毫米）会看到两个像。
-- **例题结论**：视力表距镜子3.5米，人距镜子1.5米可看到5米处的虚像；视力表距镜子3米时，人距镜子2米即可；人站在平面镜前1米，人与像距离2米；人远离平面镜，像的大小不变。
-- **易混点**：人在河边看到岸边的树在水中的倒影，是平静水面充当平面镜，成的是*正立等大的虚像*，文学上称「倒影」易与倒立混淆；人在河边看到河水深度比实际浅是光的折射现象。
-## 球面镜及其应用
-- **凸面镜**：对光线起**发散**作用，成正立、缩小的虚像；用于汽车后视镜、丁字路口拐弯处反光镜，能看到更大范围。
-- **凹面镜**：对光线起**会聚**作用，平行光反射后汇聚于焦点F；用于手电筒电珠（小灯泡置于焦点）、汽车前大灯、探照灯、太阳灶、医生额镜（中间镂空便于观察）。
-- **历史案例**：阿基米德组织妇女用梳妆镜（平面镜）围成凹面，汇聚光线烧毁敌人帆船。
-- **光污染问题**：玻璃幕墙形成凹面会聚光线，可能烧死树木（学校枣树三年被烧死）或引燃电线造成自燃，且反射声音导致楼间噪音大；设计师倾向用玻璃幕墙因设计费按建筑成本计算，但存在光污染隐患。
-# 课堂互动与答疑
-**学生**：萤火虫算不算光源？
-**教师**：算。光源定义是自身能够发光的物体，萤火虫自身发光，属于自然光源。
-**学生**：光线是真实存在的吗？
-**教师**：不是。光线是为了研究方便引进的物理模型，用带箭头的直线表示，实际并不存在。
-**学生**：为什么光穿过大气层时不是沿直线传播？
-**教师**：因为大气层不均匀，越往外越稀薄，光线会发生偏折。所以在地球上看到太阳跃出地平线、星星眨眼睛，都是大气层不均匀造成的；在月球上看太阳就是沿直线。
-**学生**：小孔成像为什么一定是实像？
-**教师**：因为光线实际到达了光屏。像一定是倒立的，但放大缩小不一定，与物距和像距有关；像的形状与孔的形状无关，如树荫下的光斑就是太阳的缩小实像。
-**学生**：月偏食和日偏食的形成条件一样吗？
-**教师**：不一样。日食时月球在中间，1号区域日全食、2、3号区域日偏食、4号区域日环食；月食时地球在中间，月球完全进入1号区域才是月全食，只有部分进入1号区域、部分在2或3号区域时才出现月偏食，仅处在2、3号区域只会略暗，不叫月偏食。
-**学生**：光垂直射到镜面上，入射角是多少？
-**教师**：0度，不是90度。入射角是入射光线与法线的夹角，垂直入射时二者重合，所以入射角和反射角都是0度。
-**学生**：为什么非要引进法线，直接用入射光线和镜面的夹角不行吗？
-**教师**：如果只研究反射，用镜面夹角也可以；但后面学折射时也需要法线，所以统一引进法线作为标准，法线垂直于镜面，是辅助线，实际不存在，画虚线。
-**学生**：画反射光线时怎么找角度，必须用量角器吗？
-**教师**：不用。先画法线，再在反射光线上找一个点，在法线另一侧找对称点，连接入射点即可，利用等腰三角形原理，作图痕迹保留法线和箭头即可。
-**学生**：镜面反射和漫反射都遵守反射定律吗？
-**教师**：都遵守。镜面反射发生在光滑表面，反射光平行；漫反射发生在凹凸不平表面，每个小面看作小平面镜，反射光射向各个方向。生活中大多数反射是漫反射，如黑板、电影银幕。
-**学生**：雨后晚上怎么判断哪里是水潭？
-**教师**：迎着月光走，亮处是水潭，因为水面发生镜面反射，反射光进入人眼；背着月光走，暗处是水潭，反射光射向另一侧。可用白纸放小镜子、手电筒垂直照射验证：斜看时镜子是黑的，白纸是亮的。
-**学生**：为什么用玻璃板代替平面镜做成像实验？
-**教师**：因为玻璃板既能反射成像，又能透过它看到后面的蜡烛，便于移动未点燃的蜡烛去确定像的位置；用镜子就看不到后面，无法操作。
-**学生**：实验中为什么看到同一个蜡烛的两个像？
-**教师**：因为玻璃板有厚度，两个面都能发生反射成像。薄玻璃板两个像几乎重合，肉眼区分不开；厚玻璃板（如8毫米）就能明显看到两个像。
-**学生**：为什么蜡烛到玻璃板的距离与像到玻璃板的距离不相等？
-**教师**：两个原因：一是玻璃板与水平面不垂直，实验时歪了；二是玻璃板没有与事先画好的镜面位置重合。都会导致测量数据不准确。
-**学生**：光屏为什么接收不到平面镜成的像？
-**教师**：因为平面镜成的是虚像，实际光线没有到达镜后，只是反射光线的反向延长线会聚形成的，所以光屏上接收不到，手放到后面也不会被烫伤。
-**学生**：平面镜成的像为什么是正立的，但水面倒影看起来是倒的？
-**教师**：平面镜成像规律是正立、等大的虚像。水面倒影中树是倒着的，是因为平静水面充当平面镜，镜面水平放置，树相对于镜面是倒立的，所以像也是倒立的，这是文学上说的"倒影"，与成像规律不矛盾。
-**学生**：凸面镜和凹面镜对光线各起什么作用？
-**教师**：凸面镜对光线起发散作用，成缩小正立的虚像，用于汽车后视镜、丁字路口反光镜；凹面镜对光线起会聚作用，用于手电筒、汽车前灯、太阳灶、医生额镜。
-# 课后任务与学习建议
-## 课堂练习
-- **练习1–5（光的直线传播）**：考点为光在均匀介质中沿直线传播；影子和月全食均据此解释；激光从地球到月球用时1.25秒，地月距离为3.75×10⁸米（s=V×T，按真空光速3×10⁸米/秒计算）。
-- **雷电与声速题**：先看到闪电后听到雷声，因为光速比声速快；声速在15℃时为340米/秒，远小于光速。
-- **练习4（单选）**：选C；光在真空中传播速度最大，均匀介质中沿直线传播需强调“均匀”，D项“不同介质中速度相同”错误。
-- **练习5（多选）**：选BCD；平面镜成像属于光的反射，不属于直线传播实例。
-- **练习6（单选）**：选ABC；D项漏掉“均匀介质”条件，只说“传播路线”不严谨。
-- **练习7（反射定律探究实验）**：用带刻度的硬纸板（中间用透明胶带粘合可前后转动）＋小平面镜＋激光笔，验证三线共面、分居两侧、反射角等于入射角。
-- **练习8（作图）**：先画法线（虚线，2–3段即可），再根据反射角等于入射角画反射或入射光线；可用尺子刻度对称找点，保留法线作图痕迹。
-- **练习9（单选）**：选A；反射光线与平面镜夹角40°，则与法线夹角50°，入射角＝反射角＝50°。
-- **练习10（单选）**：选C；入射光线与镜面夹角增大，入射角减小，反射角随之减小，传播速度不变。
-- **练习11**：入射光线与法线夹角60°时，反射角为60°。
-- **练习12**：反射光线与入射光线夹角80°时，反射角为40°（角平分线）。
-- **练习13（雨后水潭判断）**：迎着月光走，亮处是水潭（镜面反射）；背着月光走，暗处是水潭；可用白纸＋小镜子＋手电筒在家验证。
-- **练习14（光路可逆）**：选B；光路可逆——小明能看到小刚在平面镜中的像，则小刚也一定能看到小明；A项垂直入射反射角应为0°；C项漫反射同样遵守反射定律；D项不同介质光速不同。
-- **练习15**：电影院白色银幕对光产生漫反射（选B）。
-- **练习16**：教室黑板反光看不清粉笔字是镜面反射；电影放映机射到银幕上的光经幕布反射进入人眼是漫反射；两种反射都遵守光的反射定律。
-- **练习17**：电影院白色屏幕粗糙，为使射到屏幕上的光发生漫反射。
-- **练习18（多选）**：选D；人在河边看到岸边的树在水中的倒影属于光的反射（平静水面充当平面镜）；A、B为直线传播，C为光的折射。
-- **练习19（平面镜成像实验）**：观察到的是虚像；记录数据中蜡烛到玻璃板距离与像到玻璃板距离不相等，原因是玻璃板与水平面不垂直（或未与预先画好的镜面位置重合）；同一侧看到两个像，原因是玻璃板有厚度，两个面发生反射成像。
-- **练习20（平面镜成像实验）**：①用玻璃板代替平面镜，便于确定像的位置；②刻度尺用于比较像与物到镜面的距离；③两段完全相同的蜡烛用于比较像与物的大小；④光屏不能接收到烛焰的像，因为实际光线没有到达（虚像）；⑤物体靠近玻璃板，像的大小不变。
-- **练习21（查视力）**：视力表距镜子3.5米，像距镜子也是3.5米，人距镜子1.5米即可看到5米处的虚像（1.5＋3.5＝5米）。
-- **练习22（单选）**：选B；视力表到镜距离改为3米，像到镜距离也是3米，人到镜子2米即可。
-- **练习23**：人站在平面镜前1米处，人与像之间的距离为2米。
-- **练习24（单选）**：选C；人向远离平面镜方向移动，镜中像的大小不变。
-## 复习重点
-- **光源**：自身能够发光的物体；按来源分为自然光源（太阳、萤火虫）和人造光源（火把、蜡烛、煤油灯、电灯）。
-- **光线**：用带箭头的直线表示，是物理模型，并非真实存在；按形状可分为平行光源和点光源画法。
-- **光在均匀介质中沿直线传播**：适用条件为同一种均匀介质；实例包括三点一线、激光准直、小孔成像、日食月食、影子形成（皮影戏）。
-- **小孔成像**：成倒立的实像（光线实际到达），放大缩小不一定，与孔形状无关；树荫下光斑是太阳经树叶缝隙的小孔成像，为缩小的实像。
-- **日食与月食**：日食时太阳、月球、地球在同一直线上，月球在中间，分日全食（1号区域）、日偏食（2、3号区域）、日环食（4号区域）；月食时地球在中间，月全食是月球完全进入地球阴影（1号区域），月偏食是月球部分在1号区域、部分在2或3号区域。
-- **光速**：真空中为3×10⁸米/秒（3×10⁵千米/秒，约每秒绕地球赤道7圈半）；空气中略慢（约2.99×10⁸米/秒）；水中约为真空的3/4；玻璃中约为真空的2/3；光速远大于声速（15℃时声速340米/秒）。
-- **光的反射定律**：反射光线、入射光线和法线在同一平面内（三线共面）；反射光线和入射光线分居法线两侧；反射角等于入射角；光垂直射到镜面上时入射角和反射角均为0°。
-- **法线**：过入射点垂直于镜面的辅助线，画虚线，是入射角与反射角的角平分线；引入法线是为后续学习折射做准备。
-- **镜面反射**：平行光射到光滑表面（平面镜、平静水面、光滑金属表面），反射光平行；人眼不在反射光方向上就看不到反射光，如商场玻璃隔断易撞人。
-- **漫反射**：平行光射到凹凸不平表面，反射光射向各个方向；生活中大多数反射是漫反射（黑板、电影银幕、人眼看到物体）；镜面反射和漫反射都遵守光的反射定律。
-- **平面镜成像原理与特点**：原理是光的反射定律；成**正立、等大的虚像**；像与物连线垂直于镜面，像到镜面距离等于物到镜面距离（关于镜面对称）；光屏不能接收到虚像。
-- **平面镜成像实验要点**：用玻璃板代替平面镜便于确定像的位置；用刻度尺比较像与物到镜面距离；用两段相同蜡烛比较像与物大小；误差来源为玻璃板与水平面不垂直、玻璃板有厚度（两个反射面成像）。
-- **凸面镜**：对光线起发散作用，成正立、缩小的虚像；用于汽车后视镜、丁字路口反光镜。
-- **凹面镜**：对光线起会聚作用，有焦点；用于手电筒、汽车前大灯、探照灯、太阳灶、医生额镜；阿基米德曾用凹面镜汇聚光线烧毁敌船。
-- **光路可逆**：光反射时光路可逆——甲能看到乙在平面镜中的像，则乙也一定能看到甲在平面镜中的像。
-- **玻璃幕墙光污染**：凹面玻璃幕墙会聚光线，可能烧死树木或引燃电线，属光污染隐患。
-## 学习建议
-- **购买激光笔**：到两元店或十元店买一支装一节干电池的激光笔（不必买贵的），用于在家研究光的直线传播、反射定律等实验，激光强度大、光线直、易观察。
-- **小孔成像家庭实验**：用纸杯或易拉罐，底部用针扎一个小孔（不要用钉子扎大孔），前面用塑料布蒙住，点燃蜡烛放在小孔前方，可在塑料布上看到倒立的火苗像，体会像与孔形状无关。
-- **吸管验证直线传播**：用激光笔对准直吸管照射，墙上出现光点；将吸管弯折后光点消失，证明光不会自行拐弯。
-- **反射定律家庭实验**：用硬纸壳（中间用透明胶带粘合可前后转动）＋小平面镜＋激光笔，画好刻度格，在家即可验证三线共面、反射角等于入射角。
-- **镜面反射与漫反射实验**：白纸上放一面小镜子，用手电筒垂直照射，斜着看镜子是黑的、周围白纸是亮的——镜子发生镜面反射（光返回），白纸发生漫反射。
-- **平面镜成像家庭实验**：白纸上立一块透明玻璃，前方点燃蜡烛，后方移动未点燃蜡烛至看似被点燃的位置，记录两蜡烛位置，可验证像与物等大、连线垂直、距离相等；也可用两枚跳棋子替代蜡烛。
-- **观察生活现象**：夏天观察大杨树下的光斑（小孔成像，太阳缩小的实像）；雨后夜晚判断水潭位置（迎着月光走亮处是水潭）；观察停车场丁字路口凸面镜和汽车后视镜成像特点。
-- **保护眼睛**：主讲人提醒，长时间判卷、看屏幕、写字姿势不良会导致视力下降；教室因投影和防反光长期拉窗帘，学生缺乏户外光照，近视率偏高；应多到户外接触自然光，控制用眼时长。</t>
+          <t># 初中光学核心知识复习课
+## 课程概况
+本节课为初中光学复习课，主讲人系统梳理了光的直线传播、光的反射定律、镜面反射与漫反射、平面镜成像及球面镜应用等核心知识，并通过例题讲解与课堂练习巩固知识点。课程首先介绍几何光学自2000多年前古希腊时期起的研究历史，明确光源（自然光源与人造光源）与光线（带箭头的直线，为物理模型）的概念，强调光在均匀介质中沿直线传播，并列举三点一线、激光准直、小孔成像、日食月食、影子形成等实例。小孔成像成倒立实像，放大缩小不一定，与孔形状无关；日食时月球在太阳和地球之间，月食时地球在太阳和月球之间。光在真空中的传播速度为3×10^8米/秒，空气中略慢，水中约为真空的3/4，玻璃中约为2/3；一束激光从地球射到月球表面时间1.25秒，距离为3.75×10^8米。光的反射定律部分，主讲人讲解反射光线、入射光线和法线在同一平面内，分居法线两侧，反射角等于入射角；光垂直射到镜面上时入射角和反射角均为0度；反射光线与平面镜夹角40度时入射角为50度。镜面反射发生在光滑表面，反射光线平行；漫反射发生在凹凸不平表面，反射光线射向各个方向，生活中大多数反射是漫反射，如黑板、电影银幕；镜面反射可能造成光污染，如玻璃幕墙反射。平面镜成像原理是光的反射定律，成像是虚像，特点为正立、等大、虚像，像与物到镜面距离相等，连线与镜面垂直；实验用玻璃板代替平面镜便于确定像的位置，玻璃板有厚度时两个面反射会形成两个像。球面镜部分，凸面镜对光线起发散作用，成缩小虚像，用于汽车后视镜、丁字路口镜；凹面镜对光线起会聚作用，用于手电筒、太阳灶、耳鼻喉科检查；玻璃幕墙形成凹面会聚光线，可能烧毁树木或引发火灾，造成光污染。
+## 核心知识点梳理
+### 光的直线传播
+- **几何光学历史**：几何光学从2000多年前古希腊时期开始研究，初中阶段学习的直线传播、反射、折射规律均属几何光学范畴。
+- **光源定义**：自身能够发光的物体称为光源，分为自然光源（如太阳、萤火虫）和人造光源（如火把、蜡烛、煤油灯、电灯）。
+- **光线概念**：用一条带有箭头的直线代表光线，光线是**物理模型**，并非真实存在。
+- **光沿直线传播条件**：光在**均匀介质**中沿直线传播；大气层不均匀时，光线会发生偏折（如太阳越出地平线、星星眨眼睛）。
+- **三点一线实例**：步枪瞄准练习时，眼睛看到瞄准点、准心尖和标尺缺口三者重合即三点一线，原理是光在均匀介质中沿直线传播。
+- **激光准直实例**：利用激光沿直线传播的特性进行准直。
+- **小孔成像**：成**倒立实像**，放大缩小不一定，与孔形状无关；生活中大杨树底下的光斑是太阳透过树叶缝隙形成的小孔成像，得到的是太阳缩小的实像。
+- **日食月食**：日食时太阳、月球、地球在同一直线上，**月球在中间**；月食时**地球在中间**。日食分日全食（1号区域）、日偏食（2、3号区域）、日环食（4号区域）；月全食是月球完全在地球阴影中，月偏食是月球部分在1号区域、部分在2或3号区域。
+- **影子形成**：影子的形成是光沿直线传播的实例，唐朝皮影戏即利用此原理。
+- **光速**：光在真空中的传播速度为`3×10^8`米/秒（`3×10^5`千米/秒），一秒钟绕地球赤道7圈半；空气中略慢（约`2.99×10^8`米/秒），水中约为真空中的3/4，玻璃中约为2/3。
+- **光速计算题**：一束激光从地球射到月球表面时间1.25秒，距离为`3.75×10^8`米（`s=V×T`，地月之间视为真空）。
+### 光的反射定律
+- **反射定律内容**：①反射光线、入射光线和法线在**同一平面内**（共面）；②反射光线和入射光线**分居法线两侧**；③**反射角等于入射角**。
+- **法线概念**：法线是垂直于镜面的辅助线，为虚线，是入射角与反射角的角平分线；引入法线是为后续学习折射做准备。
+- **入射角与反射角定义**：入射角是入射光线与法线的夹角，反射角是反射光线与法线的夹角。
+- **易错点**：光垂直射到镜面上时，入射角和反射角均为**0度**（不是90度）。
+- **典型计算**：反射光线与平面镜夹角40度时，入射角为50度（与法线夹角为90°−40°=50°）。
+- **作图方法**：先画法线（虚线，画2–3段即可），再根据反射角等于入射角画光线；可用尺子刻度找对称点（等腰三角形原理），作图痕迹保留法线，补全箭头。
+### 镜面反射与漫反射
+- **镜面反射**：发生在光滑表面（如平面镜、平静水面、光滑金属表面），反射光线平行；人眼不在反射光线上就看不到反射光。
+- **漫反射**：发生在凹凸不平表面，将每个小面看作小平面镜，反射光线射向各个方向；**生活中大多数反射是漫反射**，如黑板、电影银幕、人的皮肤。
+- **共同点**：镜面反射和漫反射**都遵守光的反射定律**。
+- **雨后水潭判断**：雨后夜晚，迎着月光走，**亮处是水潭**（镜面反射）；背着月光走，**暗处是水潭**。
+- **家庭实验**：白纸上放小镜子，手电筒垂直照射，斜着看镜子是黑的、白纸是亮的——镜子发生镜面反射光线返回，白纸发生漫反射。
+- **光污染问题**：玻璃幕墙形成凹面会聚光线，可能烧毁树木（学校枣树被烧死案例）或引发火灾（焦点在电线上导致电线自燃），造成光污染。
+### 平面镜成像
+- **成像原理**：平面镜成像原理是**光的反射定律**，成像是**虚像**（光线反向延长线相交，实际光线未到达）。
+- **成像特点**：成**正立、等大、虚像**；像与物到镜面距离相等，连线与镜面垂直。
+- **实验器材**：用**玻璃板**代替平面镜（便于移动后面的蜡烛确定像的位置）；用**刻度尺**比较像与物到镜面的距离；用**两段完全相同蜡烛**比较像与物的大小。
+- **光屏验证**：光屏（白塑料片、白墙等）不能接收到烛焰的像，证明成的是虚像。
+- **实验误差原因**：①玻璃板与水平面不垂直（或与预先画好的位置不重合）；②玻璃板有厚度，两个面发生反射成像，会看到同一个蜡烛的两个像。
+- **视力表问题**：视力表距镜子3.5米，像距镜子也是3.5米，人距镜子**1.5米**即可看到5米处的虚像；若视力表距镜子3米，人距镜子2米即可。
+- **距离计算**：人站在平面镜前1米处，人与像之间的距离为2米；人远离平面镜时，像的大小**不变**。
+- **倒影辨析**：人在河边看到岸边的树在水中的倒影属于光的反射（平静水面充当平面镜），成的是正立等大的虚像，文学上称"倒影"易与折射混淆。
+### 球面镜及其应用
+- **凸面镜**：对光线起**发散作用**，成**正立、缩小的虚像**；用于汽车后视镜、丁字路口拐弯处的镜子。
+- **凹面镜**：对光线起**会聚作用**，平行光会聚于焦点；用于手电筒（电珠在焦点处）、汽车前大灯、探照灯、耳鼻喉科检查镜、太阳灶（西藏藏民烧水用）。
+- **以直代曲原则**：讨论球面镜作图时，将曲面看作多个小平面镜的组合。
+- **阿基米德典故**：阿基米德让妇女们把梳妆镜（平面镜）围成凹面，汇聚光线烧毁敌人帆船。
+- **光污染隐患**：玻璃幕墙形成凹面会聚光线，可能烧毁树木或引发火灾，造成光污染。
+## 课堂互动与答疑
+### Q1. 光源与光线概念
+- **学生**：萤火虫算不算光源？光线是真实存在的吗？
+&gt; **教师**：萤火虫自身发光，算自然光源。光线是用带箭头的直线表示光的传播路径，是物理模型，并非真实存在；一开灯不会真有箭状光线飞来。
+### Q2. 光在均匀介质中沿直线传播的证明
+- **学生**：如何证明光在均匀介质中沿直线传播？
+&gt; **教师**：可用激光笔照射玻璃罩内烟雾，观察光路为直线；或用吸管实验，直吸管中激光能通过，弯折后光点消失。但光穿过不均匀大气层时会发生偏折，如日出时太阳位置偏移、星星闪烁，故条件必须是均匀介质。
+### Q3. 小孔成像的特点
+- **学生**：小孔成像的像有什么特点？与孔形状有关吗？
+&gt; **教师**：小孔成像成倒立实像，因光线实际到达光屏；放大缩小取决于物距与像距关系，不一定。像与孔形状无关，如树叶缝隙形成的光斑是太阳的缩小实像，可为椭圆。
+### Q4. 日食与月食的成因区别
+- **学生**：日食和月食的成因有何不同？月偏食如何形成？
+&gt; **教师**：日食是月球在太阳与地球之间，月球挡住太阳光；月食是地球在太阳与月球之间，地球挡住阳光。日食分日全食、日偏食、日环食；月偏食须月球部分进入地球本影（1号区域）、部分在半影（2、3号区域），仅处半影只会略暗，不叫月偏食。
+### Q5. 光速在不同介质中的差异
+- **学生**：光速在不同介质中一样吗？
+&gt; **教师**：光在真空中速度最大，为3×10⁸米/秒；空气中略慢，近似取此值；水中约为真空的3/4，玻璃中约为2/3。光速随介质不同而变化，故题中D选项错误。
+### Q6. 入射角与反射角的计算
+- **学生**：光垂直射到镜面上，入射角是多少度？
+&gt; **教师**：入射角是入射光线与法线的夹角，垂直入射时夹角为0度，反射角也为0度，不是90度。若反射光线与平面镜夹角40度，则入射角为50度。
+### Q7. 反射作图的方法
+- **学生**：画反射光线时如何保证角度准确？
+&gt; **教师**：先画法线（垂直于镜面，虚线），再根据反射角等于入射角确定光线方向。可用尺子刻度对称法：以法线为基准，在入射光线一侧找对称点，连接入射点即可，无需量角器精确测量。
+### Q8. 镜面反射与漫反射的区别
+- **学生**：镜面反射和漫反射有何不同？都遵守反射定律吗？
+&gt; **教师**：镜面反射发生在光滑表面，反射光线平行；漫反射发生在凹凸不平表面，反射光线射向各个方向。两者都遵守光的反射定律。生活中多数反射是漫反射，如黑板、电影银幕；镜面反射可能造成反光看不清。
+### Q9. 雨后夜晚判断水潭位置
+- **学生**：雨后夜晚如何判断地面哪里是水潭？
+&gt; **教师**：迎着月光走，水面发生镜面反射，反射光进入人眼，亮处是水潭；背着月光走，反射光无法进入人眼，暗处是水潭。可用白纸放小镜子、手电筒垂直照射验证：斜看时镜子黑、白纸亮。
+### Q10. 平面镜成像实验的器材选择
+- **学生**：为什么用玻璃板代替平面镜做实验？
+&gt; **教师**：玻璃板既能反射成像，又能透过它看到后方蜡烛，便于移动未点燃蜡烛确定像的位置；平面镜不透明，无法做到。刻度尺用于比较像与物到镜面距离，两段相同蜡烛用于比较像与物大小。
+### Q11. 平面镜成像实验的误差原因
+- **学生**：实验中像与物到镜面距离不相等，可能是什么原因？
+&gt; **教师**：一是玻璃板与水平面不垂直，导致像的位置偏移；二是玻璃板有厚度，前后两个面都会反射成像，形成两个像，使测量产生误差。
+### Q12. 平面镜成像的特点
+- **学生**：平面镜成的像有什么特点？光屏能接收到吗？
+&gt; **教师**：平面镜成正立、等大的虚像，像与物到镜面距离相等，连线与镜面垂直。虚像由反射光线的反向延长线会聚而成，实际光线未到达，故光屏接收不到，手放后面也不会被烫伤。
+### Q13. 水中倒影与平面镜成像的关系
+- **学生**：树在水中的倒影是倒立的，为什么说平面镜成正立虚像？
+&gt; **教师**：平静水面充当平面镜，树相对于水面是正立的，其像也是正立的等大虚像；文学上称"倒影"是因观察角度，并非像本身倒立。该现象属于光的反射，不是折射。
+### Q14. 凸面镜与凹面镜的作用
+- **学生**：凸面镜和凹面镜对光线各起什么作用？
+&gt; **教师**：凸面镜对光线起发散作用，成正立缩小虚像，用于汽车后视镜、丁字路口镜；凹面镜对光线起会聚作用，用于手电筒、太阳灶、耳鼻喉科检查镜。凹面镜会聚光线可能造成光污染，如玻璃幕墙烧毁树木。
+## 课后任务与学习建议
+### 课堂练习
+- [ ] **练习1–6（光的直线传播）**：考点为光在均匀介质中沿直线传播。第1题答案为光在均匀介质中沿直线传播；第4题选C；第5题选BCD；第6题选ABC（D错在未强调均匀介质）。
+- [ ] **激光测距计算**：一束激光从地球射到月球表面用时1.25秒，按真空光速3×10⁸米/秒计算，距离为3.75×10⁸米。
+- [ ] **练习7–12（光的反射定律）**：第7题为验证反射定律的探究实验；第9题反射光线与平面镜夹角40°，入射角为50°，选A；第10题选C；第11题入射光线与法线夹角60°时反射角60°；第12题反射光线与入射光线夹角80°时反射角40°。
+- [ ] **练习8（反射作图）**：作图流程为先画法线（虚线，留作图痕迹），再根据反射角等于入射角画对应光线，最后补全箭头；可用刻度尺对称取点法快速作图。
+- [ ] **练习13–17（镜面反射与漫反射）**：第13题雨后夜晚迎着月光走亮处是水潭、背着月光走暗处是水潭；第15题选B（漫反射）；第16题黑板反光为镜面反射、电影银幕为漫反射；第17题白色屏幕粗糙为使光发生漫反射。
+- [ ] **练习14（光路可逆）**：选B，小明能看到小刚在平面镜中的像，则小刚也一定能看到小明在镜中的像，依据是光路可逆；A错在垂直入射时反射角为0°而非90°，C错在漫反射同样遵守反射定律，D错在不同介质中光速不同。
+- [ ] **练习18–24（平面镜成像）**：第18题选D（水中倒影是反射）；第19题两空分别为玻璃板与水平面不垂直、玻璃板有厚度（两个面反射成像）；第20题玻璃板便于确定像的位置、刻度尺比较像与物到镜面距离、两段相同蜡烛比较像与物大小；第21题填1.5米；第22题选B；第23题人与像距离2米；第24题选C（像的大小不变）。
+### 复习重点
+- **光源与光线**：光源是自身能够发光的物体，分自然光源（太阳、萤火虫）和人造光源（火把、蜡烛、电灯）；光线是带箭头的直线，为物理模型，并非真实存在。
+- **光沿直线传播**：光在均匀介质中沿直线传播；实例包括三点一线瞄准、队列排齐、木工看尺子、激光准直、小孔成像、日食月食、影子形成。
+- **小孔成像**：成倒立实像（光线实际到达），放大缩小不一定，与孔形状无关；树荫下光斑是太阳经树叶缝隙形成的小孔成像，为缩小的实像。
+- **日食与月食**：日食时月球在太阳和地球之间，1号区域日全食、2/3号区域日偏食、4号区域日环食；月食时地球在太阳和月球之间，月球完全进入1号区域为月全食，部分在1号区域、部分在2/3号区域才出现月偏食。
+- **光速**：真空中光速为3×10⁸米/秒（每秒绕地球赤道约7圈半），空气中略慢（近似取同值），水中约为真空的3/4，玻璃中约为2/3；光速远大于声速（15℃时声速340米/秒）。
+- **光的反射定律**：反射光线、入射光线和法线在同一平面内；反射光线和入射光线分居法线两侧；反射角等于入射角；法线垂直于镜面，为辅助线（虚线），是入射角与反射角的角平分线。
+- **入射角与反射角**：入射角是入射光线与法线的夹角，反射角是反射光线与法线的夹角；光垂直射到镜面上时入射角和反射角均为0°。
+- **镜面反射与漫反射**：镜面反射发生在光滑表面，反射光线平行；漫反射发生在凹凸不平表面，反射光线射向各个方向；两者都遵守光的反射定律；生活中大多数反射是漫反射（黑板、电影银幕、人眼看见物体）。
+- **平面镜成像**：原理是光的反射定律，成正立、等大、虚像；像与物到镜面距离相等，连线与镜面垂直；平静水面、光滑金属表面可充当平面镜。
+- **平面镜成像实验**：用玻璃板代替平面镜便于确定像的位置；用刻度尺比较像与物到镜面距离；用两段完全相同蜡烛比较像与物大小；光屏不能接收到虚像；玻璃板有厚度时两个面反射会形成两个像。
+- **球面镜**：凸面镜对光线起发散作用，成正立缩小虚像，用于汽车后视镜、丁字路口镜；凹面镜对光线起会聚作用，用于手电筒、汽车前大灯、太阳灶、耳鼻喉科检查镜。
+### 学习建议
+- **自制小孔成像实验**：用纸杯底部用针扎小孔（勿用钉子扎大孔），杯口蒙塑料布，点燃蜡烛放在小孔前方，可在塑料布上看到倒立的火苗像，体会像与孔形状无关。
+- **自制反射定律探究装置**：用硬纸壳中间用透明胶带粘合使其可前后转动，画上均匀刻度格，放置小平面镜，用激光笔照射即可在家验证反射定律。
+- **自制平面镜成像实验**：白纸上立一块透明玻璃板，用两支蜡烛（或两枚跳棋）分别置于玻璃板前后，移动后方蜡烛至与前方蜡烛的像重合，记录位置可验证像与物等距、连线垂直。
+- **购买激光笔**：两元店或十元店即可买到装一节干电池的激光笔，用于观察光沿直线传播（直吸管与弯折吸管对比）、反射定律等实验，光源强度大、光线直，观察容易。
+- **观察生活中的光学现象**：夏天观察大杨树下的光斑（小孔成像）、雨后夜晚判断水潭位置（镜面反射与漫反射）、用手电筒垂直照白纸上的小镜子并斜看（镜面反射光返回、白纸漫反射仍亮）。
+- **保护视力提醒**：主讲人强调长时间用眼、教室拉窗帘、写字姿势不良等导致近视率上升，建议多到户外接触自然光，控制屏幕使用时间。</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>82.7</v>
+        <v>67.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25691/7968</t>
+          <t>25691/7154</t>
         </is>
       </c>
     </row>
@@ -4600,119 +4590,131 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t># 课程概况
-本课程为电气工程基础，是电气工程专业进入专业课的第一门入门课。课程教学目的包含两个目标：一是掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及其与系统整体的关系，建立电力系统的整体概念；二是掌握电力系统在分析、设计、运行、管理方面的基础理论、基本技术及基本计算方法。前修课程要求具备电路理论和电机学知识，特别是变压器和同步电机相关知识；后续重要课程包括电力系统分析、电力系统继电保护、电力系统自动化、高电压技术。本次课程为第一章导论，内容涵盖电力系统基本概念（电力系统、电力网、动力系统、变电站）、电力系统的特点与要求、电能质量指标、常用接地方式，并梳理了从直流输电到交流输电的电力发展简史、电力系统的形成过程，以及电网按规模分类（地方、区域、超高压远距离输送）和变电站分类方法。第一章为概念最多且最重要的章节，三个学习难点为电能不能大量储存决定的有功无功动态平衡、额定电压规定繁杂、中性点接地方式对后续章节的影响。
-# 核心知识点梳理
-## 课程目标与定位
+          <t># 电气工程基础第1章：电力系统基本概念与发展史
+## 课程概况
+本课为电气工程基础课程第1章，由发言者1讲授，是电气专业入门课。课程教学目的有二：一是掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及与电力系统整体的关系；二是掌握电力系统分析、设计、运行、管理的基础理论、技术与计算方法。前修课程要求了解电路理论和电机学知识，特别是变压器和同步电机；后续课程包括电力系统分析、电力系统机电保护、电力系统自动化和高电压技术。第1章学习内容包括电力系统基本概念、特点及要求、电能质量指标（含国家标准规定范围）、常用接地方式（特别是中性点接地方式）；学习难点为电力系统特点引出的基本原理（如电能不能大量储存决定有功无功动态平衡）、额定电压规定、各种中性点接地方式。课堂还简要介绍了电力发展简史，涵盖直流输电早期试验、交直流之争、交流输电电压等级发展及直流输电复兴，并讲解了三相交流输电优势、电力系统形成过程，以及电力系统、电力网、动力系统的定义与电网分类。
+## 核心知识点梳理
+### 课程定位与学习目标
 - **课程性质**：电气工程基础是进入专业课后的第一门课，属于专业入门课，对今后工作非常重要。
-- **教学目标一**：掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及与电力系统整体之间的关系，建立电力系统的整体概念。
-- **教学目标二**：掌握电力系统在分析、设计、运行、管理方面的最基础理论、基本技术及基本计算方法。
-- **前修课程**：要求具备电路理论和电机学知识，特别是变压器和同步电机相关知识要求较高，有欠缺的同学应自行补充。
-- **后续课程**：最重要的四门为电力系统分析、电力系统继电保护、电力系统自动化、高电压技术。
-## 第一章学习内容与难点
-- **基本概念**：要求掌握电力系统、电力网、动力系统、变电站等若干基本概念。
-- **特点与要求**：理解电力系统的特点及由特点引起的设计运行基础理论，理解对电力系统提出的要求（涉及运行、设计、维护各方面）。
-- **电能质量指标**：掌握电能质量指标及国家标准规定的范围。
-- **接地方式**：了解电力系统常用接地方式，特别是工作接地（中性点接地方式）的不同特点。
-- **难点一 ⭐**：电能不能大量储存，决定了电力系统的有功功率和无功功率动态平衡问题，是运行调整和设计的基础。
-- **难点二 ⭐**：电力系统额定电压的规定非常繁杂，需把规定搞清楚。
-- **难点三 ⭐**：各种中性点接地方式直接影响后续多个章节内容，学习起来较困难。
-- **学习方法**：基本概念注意内涵和外延并适当记忆；思考方法从电力系统特点要求出发、从最基础原理推导，不要记结论（使用条件变化时结论会失效）；注意寻找额定电压规定之间的基本规律；比较不同中性点接地方式的特点。
-## 直流输电发展简史
-- **直流输电起源**：福泰勒使用2000米导线连接一台瓦斯发电机，拖动一台直流发电机、一台电动机和一台带水泵的电动机，证明直流远距离（两公里）输电可行。
+- **教学目标一**：掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及与电力系统整体的关系，建立电力系统整体概念。
+- **教学目标二**：掌握电力系统在分析、设计、运行、管理方面的基础理论、基本技术与基本计算方法。
+- **前修课程**：要求了解电路理论和电机学知识，特别是变压器和同步电机相关知识要求较高，有欠缺的同学应自行补充。
+- **后续课程**：最重要的四门为电力系统分析、电力系统机电保护、电力系统自动化、高电压技术。
+### 第1章学习内容与难点
+- **学习内容一**：掌握电力系统若干基本概念，包括电力系统、电力网、动力系统和变电站等概念。
+- **学习内容二**：理解电力系统的特点，以及由特点引起的电力系统设计运行等方面的基础理论。
+- **学习内容三**：理解对电力系统提出的要求，涉及运行、设计和维护各个方面。
+- **学习内容四**：掌握电能质量指标，包括国家标准对各项指标规定的范围。
+- **学习内容五**：了解电力系统常用接地方式，特别是工作接地（中性点接地方式）的不同特点。
+- **难点一**：由电力系统特点引出的基本原理，如电能不能大量储存决定了有功功率和无功功率的动态平衡问题，是运行调整和设计的基础。
+- **难点二**：电力系统额定电压的规定非常繁杂，需把各项规定搞清楚。
+- **难点三**：各种中性点接地方式直接影响后续多个章节内容，学习起来较困难。
+- **学习方法**：基本概念注意内涵和外延并适当记忆；从电力系统特点和要求出发、从最基础原理推导，不要记结论；寻找额定电压规定之间的基本规律；比较不同中性点接地方式的特点。
+### 直流输电发展简史
 - **1874年**：俄国工程师在彼得堡建成4.5公里直流输电线路，传输功率4.5千瓦，后用于有轨电车的最原始工业试验。
-- **1882年**：法国德普勒架设首条57公里直流试验线路，采用电报线传输，首端电压343伏、末端850伏，输送功率200瓦，损耗78%，将水电站直流发电机电力送到博览会。
-- **1883年**：德普勒从法国南部进行14公里输电试验，输送功率1.1千瓦，从瓦利尔书店到巴黎56公里损耗55%。
-- **1882年10月**：英国科学家发明直流输电三线制系统，外线与中线间电压110伏、两外线间220伏，后扩展到5根线形成直流无限制系统。
+- **1882年**：法国德普勒架设首条57公里直流试验线路，采用电报线传输，首端电压343伏、末端850伏，输送功率200瓦，损耗78%。
+- **1883年**：德普勒从法国南部进行14公里输电试验，输送功率1.1千瓦，损耗55%。
+- **1882年10月**：英国科学家发明直流输电三线制系统，外线与中线间电压110伏，两外线间电压220伏，后扩展到5根线形成直流无限制系统。
 - **直流输电限制**：电压等级低时损耗大、电压降落快；制造大容量高压直流发电机非常困难，限制了远距离大容量输电。
 - **19世纪末**：法国方剑在送端把多台直流发电机串联以提高电压，将75千瓦电力输送75千米。
-- **20世纪初**：瑞典科学家在串联直流发电机上装短路器，使任意发电机投切不停电；此后20多年建成15条直流输电线路。
-- **1906年**：规模最大的线路投运，从法国慕尼黑水电厂到里昂，180公里、57千伏、4700千瓦。
-- **1927年**：改建为260公里、125千伏、19000千瓦，接入两座水电站。
-- **直流输电制约因素**：设备复杂、运行方式复杂、造价高、可靠性差。
-## 交流输电发展与交直流之争
-- **变压器前身**：英国法拉第电磁感应原理；美国亨利用多匝线圈做原边、少匝线圈做副边，使高电压感应出低电压。
+- **20世纪初**：瑞典科学家在串联直流发电机上装短路器，使任意发电机投切可不停电；此后20多年建成15条直流输电线路。
+- **1906年**：规模最大的线路投运，从法国慕尼黑水电厂到里昂，180公里、57千伏、4700千瓦；1927年改建成260公里、125千伏、19000千瓦，接入两座水电站。
+- **直流输电制约**：设备复杂、运行方式复杂、造价高、可靠性差。
+### 交流输电发展简史
+- **变压器前身**：英国法拉第的电磁感应原理；美国亨利用多匝线圈做原边、少匝线圈做副边，使高电压感应出低电压。
 - **1876年**：俄国科学家发明单相变压器，主要用于照明；法国和英国科学家联合将多台变压器串联到输电线路中，发现负荷变化时输电电压受干扰。
 - **1883年**：美国特斯拉制造出感应电机，具有标志性意义。
-- **1885年**：匈牙利科学家设计多台变压器并联运行连接方式，使并联运行成为可能。
-- **爱迪生与凯尔文主张直流电**：理由一是直流电效率比交流电高得多；理由二是认为交流电有危险性，为此购买威斯汀豪斯公司的交流发电机卖给监狱给死刑犯执行死刑，以证明交流电危险。
-- **威斯汀豪斯与特斯拉主张交流电**：交流电容易利用变压器升压和降压，可在电压提高状态下减少电能损失；交流发电机制造业的发展也为交流输电做了准备。
-- **1886年**：威斯汀豪斯在美国麻省进行10千米30千伏交流输电示范；又在意大利建成17英里高压输电线路。
+- **1885年**：匈牙利科学家共同设计多台变压器并联运行连接方式，使并联运行成为可能。
+- **1886年**：威斯汀豪斯在美国麻省进行1.2千米、30千伏交流输电示范；又在意大利建成17英里高压输电线路。
 - **1886年**：俄国科学家发明三相交流电、三相交流输电和三相异步电动机。
-- **交直流之争标志性事件**：从法国到德国的交流输电线路（常被认为是第一条交流输电线路），水电厂安装三相发电机和升压变压器，将电压升高后送到德国，在法兰克福建两座降压变电站，一座供展览会照明，另一座供100马力三相异步电动机（用于人工瀑布离心泵）。
-- **高压输电技术进展**：1898年发明针式绝缘子，美国加利福尼亚输电电压升至33千伏；1906年发明悬式绝缘子，建成110千伏高压输电；1912年发现电晕临界电压与导线直径成比例增加，铝线和钢芯铝绞线开始应用，美国建成154千伏线路；1923年均压阀技术应用，建成220千伏线路。
-- **电压等级提升时间线**：1936年美国287千伏投运；1952年瑞典建成380千伏线路（第一次采用分裂导线）；1956年苏联400千伏双回线路投运；1965年加拿大建成735千伏输电系统；1969年美国765千伏线路并入电网；1985年苏联1150千伏特高压线路投运（后降压至500千伏运行）。
-- **中国电压等级发展**：220千伏于1941年投运，330千伏于1972年投运，500千伏于1981年投运，2009年1000千伏交流特高压投运（国家标志性第一次投运成果）。
-- **直流输电复兴**：交流大电网稳定问题突出后，直流在联网中的优势显现，重新用于电网与电网之间的连接。
-- **1954年**：瑞典本土与哥特兰岛建成世界第一个工业采用海底电缆的直流工程，电压100千伏、96公里，采用汞弧阀技术。
-- **1970年**：瑞典本土与哥特兰岛扩建50千伏、1万千瓦晶闸管换流阀试验工程。
+### 交直流电力之争
+- **直流派主张**：爱迪生与凯尔文主张推行直流电，理由是直流电效率比交流电高得多，且认为交流电有危险性。
+- **直流派实验**：爱迪生与凯尔文购买威斯汀豪斯公司的交流发电机，卖给监狱给死刑犯执行死刑，以此说明交流电危险。
+- **交流派主张**：威斯汀豪斯和特斯拉积极主张利用交流电，理由是交流电容易利用变压器升压和降压，可在电压提高状态下减少电能损失。
+- **交流派优势**：交流发电机制造业的发展为交流输送方式做了充分准备。
+- **决定性标志**：从法国到德国的交流输电线路，从水电厂安装三相发电机和升压变压器，将电压升高后送到德国，在法兰克福建两座降压变电站，一座用于展览会照明，另一座供100马力三相异步电动机（用于人工瀑布离心泵）。
+### 交流输电电压等级发展
+- **1898年**：发明瓷绝缘子，美国加利福尼亚输电电压等级提高到33千伏。
+- **1906年**：发明悬式绝缘子，建成110千伏高压输电线路。
+- **1912年**：发现电晕临界电压与导线直径成比例增加，铝线和钢芯铝绞线开始应用，美国建成154千伏线路。
+- **1923年**：均压阀技术应用，成功建成220千伏输电线路。
+- **1936年**：美国287千伏线路投运。
+- **1952年**：瑞典建成380千伏线路，第一次采用分裂导线。
+- **1956年**：苏联400千伏双回线路投入运行（平行双回线）。
+- **1965年**：加拿大建成735千伏输电系统。
+- **1969年**：美国765千伏线路并入电网。
+- **1985年**：苏联1150千伏特高压线路投运，后降压至500千伏运行。
+- **中国电压等级**：220千伏1941年投运，330千伏1972年投运，500千伏1981年投运，1000千伏2009年投运（交流特高压标志性首次）。
+### 直流输电复兴
+- **1954年**：瑞典本土与哥特兰岛之间建成世界第一个工业用海底电缆直流工程，电压100千伏、96公里，采用汞弧阀技术。
+- **1970年**：瑞典本土与哥特兰岛之间扩建50千伏、1万千瓦晶闸管换流阀试验工程。
 - **1972年**：世界第一个晶闸管换流阀背靠背直流工程在加拿大投运。
-- **中国直流输电工程**：第一个直流输电工程连接舟山群岛与浙江定海电网；1989年葛上直流（葛洲坝电厂到上海）投运，±500千伏；今年6月投运云广直流±800千伏特高压直流工程。
-- **推荐阅读**：发言者1推荐三本书供学生了解电力发展史。
-## 三相交流输电优势
-- **三相系统优点一**：易于产生旋转磁场，三相电动机很容易做驱动。
-- **三相系统优点二**：瞬时功率恒定，不随时间变化。
-- **三相系统优点三**：输电线路导线量（金属消耗量）最少。
-- **应用范围**：除室内配电等小功率供电采用单相交流外，其它场合基本采用三相交流；国内电力系统大多数高压、超高压、特高压输电都采用三相交流输电方式，只在联网过程中采用直流联网方式。
-- **效率比较**：三相三线制传输效率最高，优于直流传输方式和其他交流传输方式。
-- **金属消耗量比较**：在同等功率和功率因数下，三相三线制金属消耗量最小（全截面为一根导线截面乘以3）。
-## 电力系统形成过程
-- **早期供电方式**：一台发电机向附近负荷供电（如展览会照明、大楼照明），各发电机孤立供电；发电机出问题负荷即停电，供电可靠性非常差。
-- **提高可靠性方法**：把两台发电机并联连接，一台出问题时另一台可带起重要负荷，连接越来越多。
-- **输电线路问题**：导线有电阻和电抗两个重要参数，传输功率时产生电压损耗和功率损耗；阻抗越大、电流越大，损耗越大，输电线路不能太长。
-- **解决途径**：提高电压——传输相同功率时电流减小，有功功率损耗（I²R）和电压降落（IZ）均减小，输电距离可变长。
-- **交流升压手段**：加变压器，一侧升压、另一侧降压，中间电压升上去后距离损耗、电压损耗和功率损耗都降下来。
-- **电力系统雏形**：近距离（几十到几百米）发电机可直接相连，远距离采用升压后传输，多台发电机共同向负荷供电，构成最早电力系统。
-- **多机互联好处**：一台发电机停下不影响供电（发电机数目足够多于负荷即可）；能装大机组向大片范围供电，机组越做越大，供电范围越来越大，带来直接经济效益。
-- **远距离输电问题**：距离很长时（如湖北送电到华东、云贵送电到两广），中间负荷可在输电线路中间装设变电站、用降压变压器供电；输电距离长了出现稳定问题，可装设变电站采取设备调整。
-## 电力系统、电力网与动力系统定义
-- **电力系统定义**：由发电机、变压器、输电线路和用电设备构成的整体，完成电能的生产（发电机发电）、输送（变压后输送）、分配（变压分配给用户）、消耗四个方面的职能。
-- **四个环节**：发电厂（发电机）、变压器、输电线路、用电设备，即发电、输电、配电、用电。
-- **电力网定义**：电力系统中去除发电机和用电设备的部分，即变压器和输电线路构成的网络。
-- **动力系统定义**：在电力系统基础上加上发电厂中的动力部分（火电厂的锅炉、汽机及煤炭输送处理系统；水电厂的水轮机、水坝、水库等）。
-- **概念辨析**：行业中使用最多的是电力网和电力系统两个概念，动力系统概念现在很少使用；*电力系统比电力网多了发电机和用电设备，动力系统比电力系统多了动力部分*。
-## 电网分类
-- **地方电力网**：向固定地方供给电能的网络，电压等级一般在110千伏及以下（早期定义为35千伏及以下，现在常用110千伏及以下），供电半径20~50公里。
-- **区域电力网**：电压等级为110、220千伏和少量500千伏，供电半径超过50公里，联系较多发电厂和负荷中心的网络。
-- **超高压远距离输送网络**：电压等级为500千伏或1000千伏（东北有330千伏网络），主要任务是把发电厂电能送到负荷中心，距离很远，构成跨省跨地区大型电力系统。
-- **实例一**：武汉电网属于地方电力网，主要供电电压110千伏和35千伏，少数地方已出现220千伏，供电半径一般在50公里以内。
-- **实例二**：华中电网是典型区域电网，华中几省紧密联系。
-- **实例三**：葛上直流、三峡到上海的输电线路属于超高压远距离输电网络，连接华中与华东。
-- **实例四**：特高压系统从山西晋东南到湖北荆门，跨三个省，连接华北电网和华中电网，属于超高压远距离输送网络。
-- **动态变化**：随着电网发展、电压等级提高，各级电网所用电压等级会发生变化，一般趋势是提高；变电站地位也随之变化。
-## 变电站分类
-- **按最高电压等级分类**：以站内最高电压等级命名，如华工变电站为10千伏变电站（10千伏变到380伏）、关山变电站为220千伏变电站、凤凰山变电站为500千伏变电站。
-- **按主要功率流向分类**：分为升压变电站和降压变电站——大部分功率从高压侧流向低压侧的为降压变电站；发电厂内大部分功率从低压侧（发电机发出）升压到高压侧的为升压变电站。
-# 课堂互动与答疑
-**学生**：为什么我们国家采用交流输电，而且是三相三线制？
-**教师**：三相三线制在同等功率和功率因数下传输效率最高，金属消耗量最小；三相系统易于产生旋转磁场，瞬时功率恒定，因此除室内配电等小功率场合外基本都采用三相交流，直流主要用于联网。
-**学生**：电力系统、电力网和动力系统有什么区别？
-**教师**：电力系统由发电机、变压器、输电线路和用电设备构成，完成生产、输送、分配、消耗职能；电力网是电力系统中去除发电机和用电设备的部分；动力系统则是在电力系统基础上再计入发电厂动力部分，如锅炉、汽机、水轮机等。
-# 课后任务与学习建议
-## 课堂练习
-未提及
-## 复习重点
-- **电力系统四环节**：发电、输电、配电、用电的构成与工作原理，以及各环节与电力系统整体的关系，是建立系统整体概念的基础。
-- **电力系统/电力网/动力系统定义**：电力系统＝发电机＋变压器＋输电线路＋用电设备；电力网＝电力系统去除发电机和用电设备；动力系统＝电力系统加上发电厂动力部分（锅炉、汽机、水轮机等）。
-- **电能质量指标**：掌握国家标准对电能质量指标的各项规定范围，属于第一章重点内容。
-- **中性点接地方式**：了解常用接地方式特别是工作接地（中性点接地）的不同特点，该内容直接影响后续多个章节的学习。
-- **电网分类**：地方电力网（110千伏及以下，供电半径20–50公里）、区域电力网（110、220千伏及少量500千伏，供电半径超50公里）、超高压远距离输送网络（500千伏或1000千伏，东北有330千伏，用于跨省跨地区输电）。
-- **变电站分类**：按最高电压等级分为10千伏、220千伏、500千伏变电站；按主要功率流向分为升压变电站（发电厂内）和降压变电站（大部分功率从高压侧流向低压侧）。
-- **三相交流输电优势**：易于产生旋转磁场、瞬时功率恒定、导线金属消耗量最小，三项三线制传输效率最高，故交流输电占主导、直流主要用于联网。
-- **电力系统形成逻辑**：单机供电可靠性差→并联发电机提高可靠性→输电线路电阻电抗产生电压/功率损耗→升压减小电流降低损耗→输电距离变长→形成多机互联的电力系统。
-## 学习建议
-- **补充前修知识**：对电路理论和电机学有欠缺的同学，应补充变压器和同步电机的相关知识，本课程对此要求较高。
-- **概念学习方法**：注意基本概念的内涵和外延，并适当结合实际；从电力系统的特点和要求出发，从最基础原理推导，不要死记结论——使用条件变化时结论可能失效。
-- **规律归纳**：注意寻找额定电压规定之间的基本规律，比较不同中性点接地方式之间的特点，学完章节后再仔细体会。
-- **课外阅读**：作为电气专业学生应了解电力发展基本史，可阅读教师推荐的三本书，并了解交直流之争中交流输电占主导的原因。</t>
+- **中国首个直流工程**：连接舟山群岛与浙江定海电网。
+- **1989年**：葛上直流（葛洲坝电厂到上海）投运，±500千伏。
+- **今年6月**：云广直流±800千伏特高压直流工程投运，为标志性工程。
+- **学习建议**：发言者1推荐三本书供学生课后阅读，作为电气专业学生应了解电力发展基本史。
+### 三相交流输电优势
+- **优点一**：易于产生旋转磁场，三相电动机很容易做驱动。
+- **优点二**：瞬时功率恒定，不随时间变化。
+- **优点三**：输电线路所用导线量（金属消耗量）最少。
+- **应用范围**：除室内配电等小功率供电采用单相交流外，其它场合基本采用三相交流；国内大多数高压、超高压、特高压输电采用三相交流，联网时才采用直流。
+- **效率比较**：三相三线制传输效率最高，在直流传输方式和其他交流传输方式中居首。
+- **金属消耗比较**：同等功率和功率因数下，三相三线制金属消耗量最小（全截面为一根导线截面乘以3）。
+- **结论**：由于效率最高和金属消耗量最小两个原因，三相三线制在交流输电领域得到广泛应用，目前仍采用该输电方式。
+### 电力系统的形成过程
+- **初始阶段**：一台发电机向附近负荷供电（如展览会照明、大楼照明），各自孤立供电，可靠性差——发电机出问题负荷即停电。
+- **互联阶段**：把两台发电机并联，一台出问题时另一台可带重要负荷，可靠性提高。
+- **距离限制**：导线有电阻和电抗两个重要参数，传输功率时产生电压损耗和功率损耗；阻抗越大、电流越大，损耗越大，输电线路不能太长。
+- **升压解决**：传输有功功率一定时，电压升高则电流减小，线路有功损耗I²R和电压降落IZ均减小，输电距离可延长；交流升压采用加变压器，一侧升压、另一侧降压。
+- **系统雏形**：近距离（几十到几百米）发电机直接相连，远距离升压后传输，构成电力系统雏形。
+- **互联好处**：多台发电机共同供电，单台停机影响不大；能装大机组向大片范围供电，带来直接经济效益。
+- **长距离输电**：中间可装设变电站降压向沿途负荷供电，也可引接部分负荷；输电距离长时出现稳定问题，可在变电站采取设备调整。
+### 电力系统、电力网与动力系统定义
+- **电力系统定义**：由发电机、变压器、输电线路和用电设备构成的整体，完成电能生产、输送、分配、消耗四方面职能，包含发电、输电、配电、用电四个环节。
+- **电力网定义**：电力系统中去除发电机和用电设备的部分，即变压器和输电线路构成的网络；行业中最常说的是电力网和电力系统两个概念。
+- **动力系统定义**：在电力系统基础上加上发电厂动力部分，如火电厂的锅炉、汽机及煤炭输送处理系统，水电厂的水轮机、水坝、水库等。
+- **易混点提醒**：*电力系统比电力网多了发电厂和用电设备；动力系统比电力系统多了发电厂动力部分*。
+### 电网分类
+- **地方电力网**：向固定地方供给电能的网络，电压等级在110千伏及以下（早期定义为35千伏及以下），供电半径20~50公里。
+- **区域电力网**：电压等级在110、220千伏及少量500千伏，供电半径超过50公里，联系较多发电厂和负荷中心的网络。
+- **超高压远距离输送网络**：电压等级500千伏或1000千伏（东北有330千伏），主要任务是把发电厂电能送到负荷中心，距离很远，构成跨省跨地区大型电力系统。
+- **实例一**：武汉电网属地方电力网，主要供电电压110千伏和35千伏，少数地方出现220千伏，供电半径一般在50公里以内。
+- **实例二**：华中电网属典型区域电网，华中几省紧密联系。
+- **实例三**：葛上直流、三峡到上海输电线路属超高压远距离输电网络，连接华中与华东。
+- **实例四**：山西晋东南到湖北荆门特高压线路跨三个省，连接华北电网和华中电网，属超高压远距离输送网络。
+- **动态变化**：随着电网发展和电压等级提高，各级电网所用电压等级会发生变化，一般趋向提高。
+### 变电站分类
+- **按电压等级分类**：按站内最高电压等级命名，如华工变电站为10千伏变电站（10千伏变到380伏）、关山变电站为220千伏变电站、凤凰山变电站为500千伏变电站。
+- **按功率流向分类**：按主要功率流通方向分为升压变电站和降压变电站；大部分功率从高压侧向低压侧传输的称降压变电站，发电厂内大部分功率从低压侧升到高压侧的称升压变电站。
+## 课堂互动与答疑
+### Q1. 我国为何采用交流三相三线制输电？
+- **学生**：我们国家为什么采用交流？为什么采用交流三相三线制？
+&gt; **教师**：三相交流系统具有三大优点：易于产生旋转磁场使三相电动机易驱动；瞬时功率恒定不随时间变化；输电线路金属消耗量最少。三相三线制传输效率最高，在同等功率和功率因数下金属消耗量最小，因此除室内配电等小功率供电采用单相交流外，其它场合基本采用三相交流，联网时才采用直流。
+## 课后任务与学习建议
+### 复习重点
+- [ ] **电力系统四大环节**：掌握发电、输电、配电、用电四个典型环节的构成、工作原理及与电力系统整体的关系，建立电力系统整体概念。
+- [ ] **电力系统、电力网、动力系统定义**：电力系统＝发电机＋变压器＋输电线路＋用电设备构成的整体，完成电能生产、输送、分配、消耗四方面职能；电力网＝去除发电机和用电设备后的变压器与输电线路网络；动力系统＝电力系统加上发电厂动力部分（火电锅炉汽机煤炭系统、水电水轮机水坝水库）。
+- [ ] **电力系统特点引出的基本原理**：电能不能大量储存决定了有功功率和无功功率的动态平衡问题，是电力系统运行调整和设计的基础——此为第1章难点之一。
+- [ ] **电能质量指标**：掌握国家标准对电能质量指标的各种规定范围。
+- [ ] **额定电压规定**：规定繁杂，注意寻找额定电压规定之间的基本规律——此为第1章难点之一。
+- [ ] **中性点接地方式**：了解电力系统常用接地方式，特别是工作接地（中性点接地）方式的不同特点，直接影响后续多个章节内容——此为第1章难点之一。
+- [ ] **三相交流输电优势**：三相交流系统三大优点——易于产生旋转磁场使三相电动机易驱动、瞬时功率恒定不随时间变化、输电线路导线量（金属消耗量）最少；三相三线制传输效率最高，金属消耗量在同等功率和功率因数下最小。
+- [ ] **电网分类**：地方电力网（电压等级110千伏及以下，供电半径20~50公里）、区域电力网（电压等级110、220千伏及少量500千伏，供电半径超过50公里）、超高压远距离输送网络（电压等级500千伏或1000千伏，东北有330千伏，跨省跨地区）。
+- [ ] **变电站分类**：按最高电压等级分为10千伏、220千伏、500千伏变电站；按主要功率流向分为升压变电站和降压变电站（发电厂内大部分功率从低压侧升压到高压侧为升压变电站）。
+### 学习建议
+- [ ] **补充前修知识**：对电路理论和电机学知识有欠缺的同学，应下去补充相关内容，特别是变压器和同步电机知识，本课程要求较高。
+- [ ] **掌握概念方法**：对基本概念注意其内涵和外延，并适当记忆；思考时从电力系统的特点、要求出发，从最基础原理推导，不要死记结论——结论在使用条件变化时可能失效。
+- [ ] **寻找规律与比较**：注意寻找额定电压规定之间的基本规律；比较各种不同中性点接地方式之间的特点。
+- [ ] **课后阅读电力发展史**：作为电气专业学生应了解电力发展的基本历史，发言者1推荐三本书供课后阅读，并建议做进一步阅读。
+- [ ] **结合实例理解电网分类**：通过实际例子对比理解电网分类——武汉电网属地方电力网（主要供电电压110千伏和35千伏，少数220千伏）；华中电网属典型区域电网；三峡到上海输电线路、山西晋东南到湖北荆门特高压线路（跨三省，连接华北和华中电网）属超高压远距离输送网络。</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>79</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11163/6293</t>
+          <t>11163/6386</t>
         </is>
       </c>
     </row>
@@ -4792,60 +4794,55 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t># 知识主题与概述
-本期视频围绕调和级数发散性的证明展开，属于数学分析领域，核心问题是证明调和级数∑1/n发散。整体逻辑框架按“定义 → 方法/观点 → 结论”推进：先介绍级数收敛与发散的定义，再逐一评论Stack Exchange上网友的证明方法，包括分组求和证明、柯西凝聚判别法、积分估计法和差分法（Stolz定理），最后给出整体评价。皮卡认为调和级数发散这一结论本身简单，但部分证明方法（如取对数后利用不等式放缩、差分法）存在故弄玄虚之嫌，本质上是先知道结果再反推凑出证明，不够自然，反而妨碍理解，有“先射箭后画靶”的感觉。
-# 核心概念
-## 级数收敛与发散的定义
-- **收敛**：正向级数若存在固定实数 `a` 作为上界，使所有部分和 `sn` 均小于 `a`（无论 `n` 取多大），则称级数收敛。
-- **发散**：若能证明 `sn` 大于某个单调递增且永无止境的 `bn`——即对任意大的数 `b`，总可通过增大 `n` 使 `bn` 超过 `b`——则级数发散。
-- 皮卡指出，对正向级数只需判断这两件事即可，这是理解调和级数问题的前提。
-## 分组求和证明
-- 将调和级数分组：`1` 单独一组，`1/2+1/3` 一组，`1/4+1/5+1/6+1/7` 一组，`1/8` 至 `1/15` 一组，依此类推。
-- 每组都大于 `1/2`：如 `1/2+1/3 &gt; 1/4+1/4 = 1/2`，`1/4` 至 `1/7` 四项均大于 `1/8`，四项之和大于 `4×1/8 = 1/2`。
-- 级数包含任意多组，每组和大于 `1/2`，故总和无上界，调和级数发散。
-- 皮卡评价：这是微积分前几堂课常见的方法，也是后续多种证明方法的本质来源。
-## 柯西凝聚判别法
-- **柯西凝聚判别法**的证明过程与分组求和完全一致：分组、对每组做估计、将估计转化为对整个部分和的判断。
-- 对非负不增序列，其收敛发散性质等价于加速后的序列 `∑2^k·a(2^k)` 的收敛发散性。
-- 应用于调和级数时，等价于判断 `∑2^k·(1/2^k) = ∑1`，无穷个 1 相加显然无上界，故发散。
-- 皮卡推测柯西当年正是将分组求和的想法推广到一般非负不增序列，才得出此判别法。
-## 积分估计法
-- 调和级数的部分和 `hn` 从几何上可看作一系列矩形面积之和，每个矩形高为 `1/n`、底为 `1`。
-- 这些矩形面积始终大于下方曲线 `f(x)=1/x` 的定积分，故 `hn &gt; ∫₁ⁿ⁺¹ (1/x) dx = log(n+1)`。
-- 由于 `log(n+1)` 无上界，`hn` 也无上界，级数发散。
-- 皮卡指出这是正规流派的做法，通过积分曲线面积对部分和做放缩，思路自然。
-## 取对数放缩法
-- 对 `e^hn` 做处理：利用 `e^(a+b) = e^a × e^b` 将和转化为连乘积 `∏e^(1/k)`。
-- 利用不等式 `e^(1/k) &gt; 1 + 1/k` 放缩，连乘积 `∏(1+1/k)` 相邻项相消，最终等于 `n+1`。
-- 由此证明 `hn &gt; log(n+1)`，级数发散。
-- 皮卡批评此法**故弄玄虚**：本质与对数差分不等式求和完全等价，却通过指数函数和放缩包装成看似神奇的技巧，妨碍理解，属于已知结果后反推凑出的证明。
-## 差分法（Stolz 定理）
-- 目标证明 `hn` 与 `log n` 同增长级别，因 `log n` 无上界，故 `hn` 发散。
-- 利用 **Stolz 定理**（中文常称 `Stolz` 定理，数学竞赛与考研常用）：求形如 `an/bn` 且分子分母均为无穷大的极限时，可转而考察差分 `(a(n+1)-an)/(b(n+1)-bn)` 的极限。
-- 对调和数，分子差分为 `1/(n+1)`，分母差分为 `log(1+1/n)`，两者之比极限为 1，故 `hn/log n → 1`。
-- 皮卡认为此法**不自然**：只有事先知道 `hn` 满足 `log(n+1) &lt; hn &lt; log n + 1` 这一基本估计，才会去蒙 `log n` 作为比较对象；否则凭什么不选 `log log n` 的平方或 `√n`？这是先射箭后画靶。
-# 核心结论
+          <t># 调和级数发散性证明方法评论
+## 知识主题与概述
+本期视频属于数学科普与网络数学讨论评论领域，核心围绕“调和级数∑1/n是收敛还是发散”这一经典微积分问题展开。整体逻辑框架按“定义铺垫 → 方法评述 → 立场总结”推进：先以高中数学视角解释级数收敛与发散的定义，随后逐一评述Stack Exchange网友给出的分组求和、柯西凝聚判别法、积分估计、差分法等证明路径，并穿插对证明技巧自然性的评价。整体立场倾向明确：调和级数必然发散，但部分证明方法（如取对数放缩、差分法）属于事先知道结论后反向凑出的“故弄玄虚”，本质上是简单思想的包装，反而妨碍理解。
+## 核心概念
+### 调和级数的收敛与发散定义
+- **级数收敛**：对正项级数，若存在固定实数 `a`（上界），使得对任意正整数 `n`，前 `n` 项和 `sₙ` 都小于 `a`，则称级数收敛。
+- **级数发散**：若能证明 `sₙ` 大于某个单向递增且无上界的 `bₙ`——即无论给出多大的数 `b`，总可通过增大 `n` 使 `bₙ` 超过 `b`——则级数发散。
+- **调和级数**：`∑1/n`（部分和记为 `Hₙ`），其发散性是微积分中的经典结论，但皮卡指出数学传播困难，互联网上仍有网友（如民科吧）对此展开论战。
+### 分组求和与柯西凝聚判别法
+- **分组求和思路**：将调和级数分组，如 `1`、`1/2+1/3`、`1/4+1/5+1/6+1/7`……每组和均大于 `1/2`，因组数无限，故总和无上界，级数发散。
+- **柯西凝聚判别法**：其证明过程与分组求和完全一致——分组后对每组做上界或下界估计，再转化为对整个部分和的估计；对非负不增序列，其收敛发散性等价于 `∑2ᵏ·a(2ᵏ)`。
+- **应用示例**：对调和级数，凝聚后化为 `∑2ᵏ·(1/2ᵏ)=∑1`，无穷个 1 相加显然发散，比原级数更易判断。
+- **皮卡评点**：该方法适用于增长缓慢、不易直接判断收敛性的序列；他怀疑柯西正是从分组求和推广到一般非负不增序列的。
+### 积分估计法
+- **核心思路**：用积分曲线面积近似 `Hₙ` 并做放缩——`Hₙ` 从几何上可看作一系列矩形面积之和，每个矩形高为 `1/n`、底为 1，其面积始终大于下方曲边梯形面积。
+- **关键推演**：由 `∫₁ⁿ⁺¹ (1/x)dx = log(n+1)`，可得 `Hₙ &gt; log(n+1)`；因 `log(n+1)` 无上界，故 `Hₙ` 也无上界，级数发散。
+- **皮卡评点**：这是较正规的流派，但笔记中「和的积分估计」内容繁多，需专门研读。
+### 取对数放缩法
+- **核心思路**：对 `e^(Hₙ)` 做处理，利用指数函数性质 `e^(a+b)=eᵃ·eᵇ` 将和转化为连乘积 `∏e^(1/k)`。
+- **关键推演**：利用不等式 `e^(1/k) &gt; 1+1/k`（即 `eˣ &gt; 1+x`），连乘积化为 `∏(1+1/k) = ∏((k+1)/k)`，相邻项相消后等于 `n+1`，从而证明 `Hₙ &gt; log(n+1)`。
+- **皮卡评点**：此方法技巧性强、看似巧妙，但本质与对数差分不等式（`log` 的差分关系两边求和后相邻项相消）完全是一回事；他认为这是「后期凑出来的」，属于故弄玄虚、变魔术式的写法，妨碍理解。
+### 差分法（Stolz 定理）
+- **核心思路**：证明 `Hₙ` 与 `log n` 为同一增长级别，因 `log n` 无上界，故 `Hₙ` 发散。
+- **关键推演**：利用 `Stolz 定理`（中文常称 `施托尔茨定理`），对形如 `aₙ/bₙ`（分子分母均趋于无穷）的极限，可转而考察差分 `(aₙ₊₁-aₙ)/(bₙ₊₁-bₙ)`；此处分子差分为 `1/(n+1)`，分母差分为 `log(1+1/n)`，两者之比极限为 1，故 `Hₙ/log n → 1`。
+- **皮卡评点**：此方法「有点超纲」，且不自然——属于「先射箭后画靶」：因为事先知道 `Hₙ` 满足 `log(n+1) &gt; Hₙ &gt; log n` 这一基本估计，才选择除以 `log n`；若不知结果，没有理由凭空猜测用 `log n` 而非 `√n` 或 `(log n)²` 去比较。
 ## 核心结论
-- **调和级数发散**：∑1/n 的前 n 项和 hn 无上界，故级数发散；这是微积分中的经典结论，对学过高等数学的大学生而言是简单问题。
-- **分组求和证明**：将调和级数各项分组（1；1/2+1/3；1/4+…+1/7；1/8+…+1/15；…），每组和均大于 1/2，而组数可无限增加，故部分和无上界、级数发散。
-- **柯西凝聚判别法**：其证明过程与分组求和完全一致——对非负不增序列，∑an 的收敛发散性等价于 ∑2^k·a(2^k)；应用于调和级数时等价于 ∑1，即无穷个 1 相加，显然发散。
-- **积分估计法**：hn 从几何上可视为矩形面积之和，每个矩形面积始终大于对应曲边梯形（即 1/x 的积分），故 hn &gt; log(n+1)；log(n+1) 无上界，因此 hn 发散。
-- **差分法（Stolz 定理）**：通过求 hn/log n 的差分极限——分子差分为 1/(n+1)，分母差分为 log(1+1/n)，两者之比极限为 1——可证 hn 与 log n 同增长级别，故 hn 无上界、级数发散。
-- **皮卡对证明方法的评价**：取对数后利用不等式 e^(1/k) &gt; 1+1/k 放缩的证法，本质与对数差分法完全一致，属于「变魔术」式的故弄玄虚；差分法同样不自然，是「先射箭后画靶」——因事先知道 hn 满足 log(n+1) 的上下界不等式，才选择除以 log n 来凑证明。
-## 易混点与适用边界
-- **收敛与发散的定义**：正向级数收敛需存在固定实数 a 使所有部分和 sn &lt; a（n 取任意正整数）；反之若部分和大于某个单调递增且无界的 bn，则发散。
-- **柯西凝聚判别法的适用条件**：仅适用于非负且不增的序列；其价值在于处理增长很慢、不易直接判断收敛发散性的级数。
-- **hn 的上下界估计**：调和级数的基本估计为 log(n+1) &lt; hn &lt; log n + 1；两边除以 log n 取极限即为 1，这是差分法证明的前提。
-- **ln 与 log 的记号差异**：log 是美国写法，ln 是欧洲写法（经苏联传入中国）；两者在原文中指同一函数。
-- **常见误区**：分组求和证明中每组和均大于 1/2，但组数无限增加才导致发散——不能误以为每组和恰好等于 1/2；e^x &gt; 1+x 这一不等式本身依赖微积分与极限，但 e^(1/k) &lt; e 的放缩可避免使用微积分。</t>
+### 核心结论
+1. **调和级数∑1/n是发散的**：皮卡指出，对任意给定的上界a，总能通过增大n使部分和sn超过它，因此不存在固定上界，级数发散。
+2. **柯西凝聚判别法的证明与分组求和想法一致**：皮卡强调，该判别法的证明过程与网友的分组求和法完全一样——将序列分组、每组做估计，再对整体部分和做估计；对非负不增序列，∑a_n与∑2^k·a_{2^k}收敛性等价。
+3. **积分估计法证明hn &gt; log(n+1)**：皮卡介绍，网友用积分曲线面积近似hn，矩形面积始终大于曲边梯形面积，从而得到hn &gt; log(n+1)；因log(n+1)无上界，故hn发散。
+4. **差分法利用Stolz定理证明hn/log n的极限为1**：皮卡指出，该流派通过比较hn与log n的增长级别，利用Stolz定理（中文常称Stolz定理）求差分极限——分子差分为1/(n+1)，分母差分为log(1+1/n)，两者极限均为1，故hn/log n极限为1，log n无上界，hn发散。
+5. **皮卡批评某些证明故弄玄虚、不自然**：他认为取对数放缩的证明（e^{1/k} &gt; 1+1/k，连乘积相消得n+1）和差分法都是「先知道结果再凑证明」，本质是简单的，但写成魔术式技巧反而妨碍理解。
+### 易混点与适用边界
+- **收敛与发散的定义**：正向级数收敛需所有部分和sn都小于某个固定实数a（上界）；发散则需证明sn大于某个单调递增且无上界的bn——皮卡强调这是简化处理，严格定义需涉及极限。
+- **柯西凝聚判别法的适用条件**：仅适用于**非负不增**序列；对增长缓慢、不易直接判断收敛性的级数（如调和级数）特别有效，可转化为判断∑2^k·a_{2^k}的收敛性。
+- **积分估计法的几何直观**：hn从几何上可看作高为1/n、底为1的矩形面积之和，该矩形面积始终大于下方曲边梯形（∫1/x dx）的面积，故hn &gt; log(n+1)——此放缩方向是下界估计。
+- **差分法（Stolz定理）的适用前提**：适用于分子分母均为无穷大的情形，通过比较差分（a_{n+1}-a_n）/（b_{n+1}-b_n）的极限来求原极限；皮卡指出该方法「不自然」，因为需要事先知道hn与log n同阶才能想到用log n作分母。
+- **常见误区**：皮卡批评取对数放缩的证明「纯粹是装、变魔术」——它本质与对数差分不等式（log的差分关系）是一回事，只是用指数函数和连乘积相消包装成技巧；他认为这类证明「妨碍理解但让人觉得magic」。
+### 待澄清问题
+- **Dialectic分解思路**：皮卡提到分组求和证明背后还有「dialectic分解」的思路，但表示「一时半会讲不清楚」，留待后续展开。
+- **后续评论计划**：皮卡表示「后面还有很多方法」，如果本期反响不错，将出下一期继续评论其他帖子或网友的解题思路。</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>32.3</v>
+        <v>31.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7465/2817</t>
+          <t>7465/3022</t>
         </is>
       </c>
     </row>
@@ -4907,82 +4904,83 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t># 知识主题与概述
-本期视频围绕GitHub这一开源资源平台展开，核心议题是向观众推荐实用热门项目，并解决国内用户访问、汉化、搜索等常见使用难题。整体逻辑框架分两条线索推进：其一为项目推荐，主讲人老李（发言者2）依次介绍工作性价比评估、表情包博物馆、健康指南、一键证件照、健身指导、教材合集、AI视频生成（Morning Printer Turbo）、声音克隆（ChatBox TTS）、AI学习资源库及Awesome AI Apps等十余个热门项目，并现场演示部分功能；其二为使用技巧，针对国内访问GitHub困难的问题，给出加速软件、镜像站、魔法（VPN）三种解决方案，并讲解注册、浏览器汉化插件、AI搜索替代原生搜索等方法，最后拆解项目主页的Star、Watch、Fork、Readme、Commit日期等核心功能。整体立场倾向明确：推荐使用魔法访问GitHub，并主张用AI搜索（如ChatGPT）替代原生精准匹配搜索，以提升检索效率与覆盖面。
-# 核心概念
-## 工作性价比评估
-- 输入年薪、工作地区、年假、通勤时长、学历、工作年限及领导同事评价等参数，综合计算后给出工作性价比分数与评级。
-- 发言者2以自己之前的程序员工作测试，评估结果为「性价比还不错，优质牛马」。
-## 表情包博物馆
-- 收录国内过去几年全网爆火的表情包合集，涵盖甄嬛传、罗翔、特朗普、马保国等主题。
-- 发言者2评价：斗图时使用该合集「可以把对方按在地上摩擦」。
-## 健康活到150岁指南
-- 分享经科学验证的健康知识，如间歇性进食可促进胆汁代谢、炎症自愈，吃天然发酵类食品可改善肠道菌群生态。
-- 发言者2自述不指望活到150岁，只希望教程能帮自己活到领养老金那天。
-## 一键证件照
-- 上传一张大头照即可一键抠图换背景，生成不同标准的证件照及各种规格的打印模板。
-## 丐版健身教练
-- 提供自重、哑铃、弹力带、长凳等训练方式，选择目标肌肉群后给出参考动画，可跟着练习。
-- 发言者2自述买不起健身器材，选择用身体自重健身，称其为「丐版健身教练」。
-## 教材合集
-- 收集国内所有小学、初中、高中及部分大学的PDF教材，全部免费使用。
-## 声音克隆模型ChatBox TTS
-- 零样本语音克隆模型，情感控制到位，克隆声音接近真人说话效果。
-- 演示流程：打开项目网页上传一段自己的音频，合成一段英文台词试听效果。
-## AI学习资源库
-- 涵盖大语言模型、RAG、AI Agents、MSI等最新AI技术，作者将教程整理成500多页PDF文档，含大量示意图辅助理解。
-## Awesome AI Apps
-- 收录大模型最新的Agent应用，如医学影像数据分析Agent、AI投资Agent、竞争对手情报分析Agent等。
-- 发言者2建议：想跟进AI应用落地案例或找创业点子可关注此项目。
-## GitHub访问加速
-- 方法一：使用Watch Toolkit加速软件，进入网站选择适合电脑的版本下载安装，打开后找到网络加速勾选GitHub加速即可流畅访问。
-- 方法二：使用GitHub镜像站如ghproxy，浏览器点开直接访问GitHub，默认是镜像的项目地址，搜索其他项目不受影响。
-- 方法三：使用魔法（VPN），发言者2个人最推荐此方法；镜像站速度与稳定性较加速软件差。
-## GitHub注册与汉化
-- 注册GitHub用国内QQ邮箱即可完成。
-- 浏览器安装翻译插件解决满屏英文问题：谷歌浏览器推荐谷歌翻译或沉浸式翻译，安装路径为「三个点→拓展程序→管理拓展程序→搜索插件名安装」。
-- 动手能力强的可安装汉化插件，效果更彻底。
-## GitHub搜索优化
-- 原生搜索按搜索词精准匹配排序，对国人不好用：如搜screen record与screen recording按星标排序结果不同，因录制单词在不同项目中的写法差异导致漏搜。
-- 推荐用AI搜索替代：在ChatGPT中用中文提问「在GitHub上帮我找好用的录屏软件」，AI可汇总热门工具并整理成表格，覆盖原生搜索漏掉的项目。
-## GitHub项目主页
-- 项目本质上是一个文件夹，项目名字下是子文件夹或文件；Watch是关注项目，Fork是复制项目到自己的账号，Star相当于收藏和点赞，Star数代表项目江湖地位。
-- About是项目简介；Release是软件安装包，可下载最新版本；Readme文件是项目说明书，默认在项目最下面展开显示，是了解项目必看内容。
-- Commit日期即最近更新时间，若更新日期是好几年前，大概率是没人维护的僵尸项目。
-- Explore中的Trending可查看全站当天、本周、本月最热门项目；也可让ChatGPT找GitHub daily，及时分享最新热门项目。
-# 核心结论
+          <t># GitHub实用项目与访问技巧分享
+## 知识主题与概述
+本期视频围绕 GitHub 这一开源资源库展开，核心问题是：普通人如何高效利用 GitHub 获取资源，并解决国内访问、汉化与搜索中的实际障碍。整体逻辑框架分三块推进：先展示 GitHub 上多个实用热门项目（工作性价比评估、表情包博物馆、健康指南、证件照制作、健身指导、教材合集、声音克隆、AI 学习资源库等），再针对访问难题给出三种解决方案（Watt Toolkit 加速软件、镜像站、VPN），最后讲解页面汉化、原生搜索与 AI 搜索的优劣对比，并逐项介绍项目页面的功能模块（Watch、Fork、Star、About、Release、Readme、Commit 日期）。整体立场倾向明确：推荐使用 AI 工具（如 ChatGPT）替代 GitHub 原生搜索，以获得更全面准确的结果；访问方式上首选 Watt Toolkit 或 VPN，镜像站仅作备选。
+## 核心概念
+### 工作性价比评估项目
+- **定义**：输入年薪、工作地区、年假、通勤时长、学历、工作年限、领导同事评价等因素，综合评估工作性价比并给出分数和评级。
+- **推演示例**：发言者2测试其程序员工作，评估结果为“性价比还不错，优质牛马”。
+- **适用条件**：项目实用性取决于输入信息的完整度，评级结果用于个人参考。
+### 表情包博物馆
+- **定义**：收录国内过去多年全网爆火的表情包大合集，涵盖甄嬛传、罗翔、特朗普、马保国等主题。
+- **评点**：发言者2称斗图时使用该合集可“把对方按在地上摩擦”。
+### 健康活到150岁指南
+- **定义**：分享经科学验证的健康知识，如间歇性进食促进胆汁代谢与炎症自愈、天然发酵食品改善肠道菌群生态。
+- **评点**：发言者2表示不指望活到150岁，只求活到领养老金。
+### 一键做证件照项目
+- **定义**：上传大头照即可一键抠图换背景，生成不同标准的证件照和多种规格打印模板。
+### 自重健身教练项目
+- **定义**：选择肌肉群后提供自重训练参考动画，如腹肌练习，适合请不起真人教练的用户。
+### 国内教材PDF合集
+- **定义**：收集国内小学、初中、高中及部分大学PDF教材，全部免费使用。
+### 声音克隆模型ChatBox TTS
+- **定义**：零样本语音克隆模型，情感控制到位，克隆声音接近真人。
+- **操作**：上传音频后合成英文台词，可试听效果。
+### AI学习资源库
+- **定义**：涵盖大语言模型、RAG、AI Agents等最新AI技术教程，整理成500多页PDF文档，含大量示意图。
+### Awesome AI Apps
+- **定义**：收录大模型最新Agent应用，如医学影像数据分析Agent、AI投资Agent、竞争对手情报分析Agent。
+- **适用条件**：适合跟进AI应用落地案例或寻找创业点子。
+### GitHub访问加速方法
+- **Watt Toolkit加速软件**：进入官网选择适合电脑的版本下载安装，打开后找到网络加速勾选GitHub加速即可流畅访问。
+- **镜像站**：如gh-proxy，浏览器点开即可访问，可搜索GitHub其他项目，但速度与稳定性较差。
+- **魔法（VPN）**：发言者2个人最推荐，为最流畅的访问方式。
+### GitHub页面汉化
+- **翻译插件**：谷歌浏览器推荐谷歌翻译或沉浸式翻译，安装后可将网页翻译成中文，效果基本够用。
+- **汉化插件**：动手能力强的用户可安装汉化插件，安装路径为“三个点→拓展程序→管理拓展程序→搜索插件名安装”。
+### GitHub搜索技巧
+- **原生搜索局限**：按搜索词精准匹配排序，如搜“screen record”与“screen recording”结果不同，对国人不好用。
+- **AI搜索推荐**：在ChatGPT中用中文描述需求（如“在GitHub上帮我找好用的录屏软件”），可搜齐热门项目并总结成表格，结果更全面准确。
+### GitHub项目页面功能
+- **核心操作**：Watch关注项目、Fork复制项目、Star收藏点赞，About为项目简介，Release为软件安装包。
+- **Readme文件**：项目说明书，默认在项目最下方展开显示，介绍项目用途、安装使用方法。
+- **Commit日期**：即最近更新时间，若更新日期久远则大概率是无人维护的僵尸项目。
+- **Trending**：通过左侧Explore进入Trending，可查看当天、本周、本月最热门项目。
 ## 核心结论
-- **GitHub定位**：不只是代码托管平台，更是全球资源库，可找到名校公开课、大厂面试题、开源大模型、AI学习资料等各类资源。
-- **工作性价比评估项目**：输入年薪、工作地区、年假、通勤时长、学历、工作年限、领导同事评价等因素，综合给出工作性价比分数和评级；发言者2测试程序员工作获评「性价比还不错，优质牛马」。
-- **表情包博物馆**：收录国内近年全网爆火的表情包合集，包括甄嬛传、罗翔、特朗普、马保国等主题。
-- **健康指南项目**：分享经科学验证的健康知识，如间歇性进食可促进胆汁代谢、炎症自愈，吃天然发酵类食品可改善肠道菌群生态。
-- **一键证件照项目**：上传大头照即可一键抠图换背景，生成不同标准证件照和打印模板。
-- **健身项目**：可选择自重、哑铃、弹力带等训练方式，选中肌肉群后提供参考动画，适合请不起真人教练的用户。
-- **教材合集项目**：收集国内小学、初中、高中及部分大学的PDF教材，全部免费。
-- **全自动视频生成项目Morning Printer Turbo**：近期热门。
-- **声音克隆模型ChatBox TTS**：支持零样本语音克隆，情感控制到位，克隆声音接近真人。
-- **AI学习资源库**：涵盖大语言模型、RAG、AI Agents等最新AI技术，作者整理成500多页PDF文档，含大量示意图。
-- **Awesome AI Apps项目**：收录大模型最新Agent应用，如医学影像数据分析、AI投资、竞争对手情报分析等，可用于跟进AI落地案例或寻找创业点子。
-- **GitHub访问三种方法**：Watch Toolkit加速软件（更流畅）、镜像站ghproxy（速度与稳定性较差）、魔法（最推荐）。
-- **GitHub注册**：可用国内QQ邮箱完成注册。
-- **页面汉化**：谷歌浏览器推荐安装谷歌翻译或沉浸式翻译插件，可将网页翻译成中文。
-- **搜索优化**：GitHub原生搜索按精准匹配排序，对国人不好用；推荐用ChatGPT等AI工具搜索，可更全面准确地找到项目。
-- **项目主页功能**：Star代表项目受欢迎程度（江湖地位），Watch是关注，Fork是复制项目；About为项目简介；Release为软件安装包；Readme文件是必看的项目说明书。
-- **项目维护判断**：通过Commit日期判断最近更新时间，若更新日期为好几年前，大概率是无人维护的僵尸项目。
-- **热门项目追踪**：Explore中的Trending可查看当天、本周、本月最热门项目；也可让ChatGPT分享GitHub daily最新热门项目。
-## 易混点与适用边界
-- **GitHub原生搜索 vs AI搜索**：原生搜索按搜索词精准匹配，如搜「screen record」和「screen recording」结果不同；AI搜索（如ChatGPT）可理解中文意图，一次性找齐热门工具并总结成表格。
-- **三种访问方式适用性**：Watch Toolkit加速软件更流畅但需下载安装；镜像站直接浏览器访问但速度和稳定性较差；魔法最推荐但需自行解决。
-- **Star、Watch、Fork的区别**：Star相当于收藏和点赞，Watch是关注项目动态，Fork是复制项目到自己的账号。
-- **Readme文件的作用**：相当于项目说明书，与公园相亲角贴的简介本质相同，默认在项目最下方展开显示，是了解项目必看内容。</t>
+### 核心结论
+1. **GitHub 是通用资源库**：不只是代码托管平台，还收录名校公开课（麻省理工、斯坦福）、大厂面试题（字节、阿里、腾讯）、开源大模型、AI 学习资料、表情包合集、养生指南、大厂黑名单等各类资源。
+2. **工作性价比评估项目**：输入年薪、工作地区、年假、通勤时长、学历、工作年限、领导同事情况等参数，输出工作性价比分数与评级；发言者2测试程序员岗位，结果为「性价比还不错，优质牛马」。
+3. **表情包博物馆项目**：收录国内过去数年全网爆火的表情包合集，涵盖甄嬛传、罗翔、特朗普、马保国等主题。
+4. **健康活到150岁指南**：分享经科学验证的健康知识，如间歇性进食促进胆汁代谢与炎症自愈、天然发酵类食品改善肠道菌群生态。
+5. **一键做证件照项目**：上传大头照即可一键抠图换背景，生成不同标准证件照及多种规格打印模板。
+6. **自重健身项目**：选择目标肌肉群（如腹肌）后提供身体自重练习的参考动画，适合请不起真人教练的用户。
+7. **教材合集项目**：收集国内所有小学、初中、高中及部分大学 PDF 教材，全部免费使用。
+8. **声音克隆模型 ChatBox TTS**：零样本语音克隆，情感控制到位，克隆声音接近真人；上传音频即可合成指定台词。
+9. **AI 学习资源库**：涵盖大语言模型、RAG、AI Agents 等最新 AI 技术，作者整理成 500 多页 PDF 文档，含大量示意图。
+10. **awesome AI Apps 项目**：收录大模型最新 Agent 应用，如医学影像数据分析、AI 投资、竞争对手情报分析等，适合跟进 AI 落地案例或寻找创业点子。
+11. **国内访问 GitHub 的三种方案**：① Watt Toolkit 加速软件——官网下载对应版本，打开后勾选 GitHub 加速，最流畅；② 镜像站（如 gh-proxy）——浏览器直接访问，操作简单但速度与稳定性较差；③ 魔法（VPN）——发言者2个人最推荐，最流畅但需自行解决。
+12. **页面汉化方案**：给浏览器安装翻译插件，谷歌浏览器推荐谷歌翻译或沉浸式翻译，可将网页直接翻译成中文。
+13. **搜索方式对比**：GitHub 原生搜索按关键词精准匹配，同一含义不同写法（如 screen record 与 screen recording）结果不同；推荐用 ChatGPT 等 AI 工具以中文提问搜索，结果更全面准确，还能汇总成表格。
+14. **项目页面功能**：Watch 为关注项目、Fork 为复制项目到自己的账号、Star 为收藏点赞；About 为项目简介，Release 为软件安装包，Readme 为项目说明书（默认在项目最下方展开显示）。
+15. **判断项目活跃度**：查看文件最近的 Commit 日期（即最近更新时间），若更新日期为多年前，大概率是无人维护的僵尸项目。
+16. **追踪热门项目**：点开左侧 Explore 的 Trending，可查看全站当天、本周、本月最热门项目；也可让 ChatGPT 等 AI 工具帮忙查找 GitHub 每日热门项目。
+17. **资源汇总**：发言者1总结称，视频提到的所有开源项目及未提及但不错的项目均已整理成文档，观众可三连关注免费领取。
+### 易混点与适用边界
+- **Watt Toolkit 与镜像站对比**：Watt Toolkit 需下载安装并勾选 GitHub 加速，速度更流畅；镜像站（如 gh-proxy）无需安装、点开即用，但速度与稳定性更差。
+- **GitHub 原生搜索与 AI 搜索对比**：原生搜索按精准匹配排序，同一含义的不同英文写法会得出不同结果，容易漏项；AI 搜索（如 ChatGPT）接受中文提问，能汇总热门项目并整理成表格，结果更全面准确。
+- **Watch / Fork / Star 的区别**：Watch 是关注项目动态，Fork 是复制项目到自己的账号，Star 相当于收藏和点赞（即「一键三连」）。
+- **Commit 日期与项目维护状态**：Commit 日期可理解为最近更新时间；更新日期停留在多年前的项目大概率是无人维护的僵尸项目，使用前需注意。
+- **Readme 的定位**：Readme 是项目说明书，内容默认在项目最下方展开显示，是了解项目用途、安装使用方法必看的内容。
+- **翻译插件与汉化插件的适用边界**：翻译插件（谷歌翻译、沉浸式翻译）可将网页直接翻译成中文，效果基本够用；动手能力强的用户可另装汉化插件，但原文未展开说明其具体安装与效果差异。</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>36.4</v>
+        <v>40.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4014/3471</t>
+          <t>4014/3886</t>
         </is>
       </c>
     </row>
@@ -5352,60 +5350,85 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t># 访谈概述
-本期《锵锵三人行》围绕日剧《大奥》与《明朝那些事儿》展开，受访者包括《明朝那些事儿》作者当年明月（发言者2）及嘉宾马先生（发言者3）等。采访主题是通过《大奥》探讨日本文化中的极端精神与忠诚文化，再转入明朝历史，讨论明史魅力、朱元璋评价、明朝兴亡经验教训及明式家具等话题。受访者核心观点包括：日本文化讲究极端精神，所有事情要做到尽头，战后仅用30年成为世界第二经济强国；中国王朝有300年大限，只有宋朝跨过，延续319年；历史是照片，古人的生活是录像，不能简单套用经验教训。访谈看点在于当年明月提出明末市民生活轻松、江浙工商业兴起，以及1644年北京闹瘟疫（疙瘩瘟，可能是天花）导致李自成军无人抵抗等与流俗看法不同的见解。
-# 访谈详细记录
-## 日剧《大奥》与日本文化
-- **《大奥》剧情与历史背景**：发言者3介绍该剧三部曲，前两部对应中国晚明到清初时段，后一部在明治维新之前；发言者2补充这是一部有跨越性的历史剧。发言者3认为它是《大长今》以后最有影响的外国电视剧。
-- **大奥的含义**：发言者3解释大奥即中文的「后宫」，日语「奥」指屋子最深处、很深的地方，中文「堂奥」「深奥」保留此痕迹；发言者2补充另一层意思是「一般人不准进去」。
-- **幕府将军与天皇关系**：发言者2指出日本天皇一直是摆设，实际权力在幕府将军手中，德川家康开创德川幕府后权力集于一人。他举例天皇想办活动没钱找将军要钱被拒，活动没办成，天皇后来以退位抗议。
-- **日本极端精神与战后经济**：发言者3认为日本战后用30年成为世界第二经济强国（绝对量而非人均量），是唯一没有资源的强国，这不是偶然而是全民族极端精神的必然结果；发言者2称这种「所有事情要做到尽头」的极端精神从《大奥》剧中可见一斑。
-- **日本忠诚文化与终身雇佣制**：发言者3称日本是忠诚文化的典型国度，跳槽率最低，每次跳槽都是社会资源浪费；发言者2补充西方经济学家无法理解日本终身雇佣制下缺乏竞争却效率极高，这是经济学上的奇迹。
-- **豆腐厂案例**：发言者3讲述参观日本最底层豆腐厂的经历——豆腐规定当天做当天卖，工人夜里11:45坐好不动看表，12点整准时开始工作，到四点多干完上市，期间无人闲聊。
-- **日本民族对死亡的态度**：发言者2认为日本民族有「寻死的潜在欲望」，因岛国生存条件恶劣而对死亡不惧怕甚至有点向往，二战暴行是藐视生命的行为；发言者3不同意，认为日本民族不是藐视生命而是重视死亡，经济危机时很多身家万贯的人剖腹自杀即为证明。
-- **日本文化根源**：发言者2认为日本是一岛国，没有资源、常火山地震，跑都没地方跑，人本身对世界有极强求生欲望，所以学会融入团体、按固定规则做事才能生存；发言者3认为日本投机取巧的人没有生存环境，社会文化的鄙视非常难过。
-## 明朝历史与《明朝那些事儿》
-- **为何写明史**：发言者2解释明史资料最多，但一个事件可能有7个不同说法，如罗生门；先秦史料太少，史记就那么一两篇，孙武事迹多是编的。
-- **朱元璋评价**：发言者2推崇朱元璋，认为他从乞丐当上皇帝，定下明朝规章制度且基本无大改动，是了不起的人才；发言者3补充历史上最底层的人坐到最上面独此一份，刘邦好歹是村长或乡长。
-- **朱元璋起义的偶然性**：发言者2讲述朱元璋因好友汤和来信被告发，没办法才去参加起义军；他强调历史最重要的是明白这事是真的，旁观者觉得好玩，但当年那是造反、要掉脑袋的事。
-- **明朝跌宕起伏**：发言者3认为明朝260多年过程本身跌宕起伏，几次要死没死了，如土木堡之变、夺门之变，皇上被瓦剌军抓起来又扶弟弟，构成现代版电视剧才能捏造的情节。
-- **明末市民生活**：发言者2认为明末很多真相被掩盖，当时市民生活特别轻松舒服，想去哪去哪，皇册都不用了；江浙一带兴起工商业，给人当雇工活得很滋润，三言二拍这类娱乐产品出现说明有养活自己的资本。李自成起义是因为陕西一带发生大规模灾荒。
-- **历史经验教训**：发言者2提出「我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训」，因为历史发生时有背景，你不比前人聪明，史书是照片而古人的生活是录像，不能简单套用经验教训。
-- **明朝的趣味性**：发言者2认为明朝什么都有——宦官专政（魏忠贤、刘瑾）、文官专政（张居正）、皇帝专政（朱元璋、朱棣），皇帝出去了还能回来做皇帝；吴三桂与满清合作入关，除陈圆圆外还因崇祯死了，说法是为崇祯复仇。
-- **1644年北京瘟疫**：发言者2提到1644年李自成军打到京城无人抵抗，有史料记载当时北京闹瘟疫叫「疙瘩瘟」，今天看就是天花；他曾与老师王佩奇交流，认为明朝亡得蹊跷，什么坏事衰事都赶上了。
-- **王朝300年大限**：发言者3认为中国王朝300年是大限，只有宋朝跨过（南北宋接上，延续319年），汉朝中间隔断14年，唐朝明朝清朝都没跨过；发言者2比喻一公司成立200多年够本了，明朝摊子几千万人。
-## 明朝审美与明式家具
-- **宋明与满清审美差异**：发言者3认为宋明是典型汉人政权、文人政权，文人审美高，对美的判断不是表象的；满族是异族，对美的判断都是表象的，今天凡是外在美直观能看到的都卖得贵，但晚清到民国初年收藏中素雅的东西才值钱。
-- **明末艺术与生活**：发言者3指出明末工艺彻底改观，变得非常精细，日本派大量工匠来交流学习；文征明、唐寅、董其昌都是那个时期的人，生活不好画不出小桥流水，八大山人明末画的都是翻白眼，因对社会愤愤不平。
-- **天启皇帝当木匠**：发言者3讲述天启皇帝干完活差大臣去卖，回来还打听卖得怎么样，卖得好成就感特大；发言者4调侃「你要是再亲自去卖，那还好卖呢」。
-- **明式家具地位**：发言者3认为明式家具在国际上地位高不是偶然，皇帝能下那么大力气去做，反映当时社会时尚和家具在每个人心目中的地位；「所有的偶然中一定有个必然的因素」。
-- **正德皇帝被写坏**：发言者2认为正德皇帝绝非史料所写的那么蠢，举例他从江南回来先在通州停半天，派人打探京城有没有埋伏圈套，很有城府；因接班的嘉靖是他堂兄弟而非亲生，明武宗实录由嘉靖指派杨廷和等人编修，有偏颇，不能把他写得太好。
-- **正德皇帝与豹房**：发言者2解释豹房其实是玩的地方，有动物园养了豹子，有女人但后宫也是女人，不影响其他问题；发言者3称正德是明朝最荒淫的皇帝，不留种没有生育能力，对宫廷外女人有兴趣，宫廷内女人禁忌太多。
-# 关键引语与金句
+          <t># 锵锵三人行：中日文化差异与明朝历史漫谈
+## 访谈概述
+本期《锵锵三人行》围绕日本历史剧《大奥》与《明朝那些事儿》展开，嘉宾为《明朝那些事儿》作者当年明月（发言者2）与马先生（发言者3），由主持人（发言者1）引导，另有发言者4参与。节目先由《大奥》切入日本文化，再转入明朝历史、皇帝趣事与明式家具。核心观点包括：日本文化体现极端精神与忠诚文化，战后用30年成为世界第二经济强国（绝对量）是必然；中国文化精神是中庸，日本则讲究做到极致；历史教训是“我们从来没有从历史中得到过教训”。锚点包括《大奥》三部曲、1644年北京疙瘩瘟、明武宗正德皇帝。看点在于当年明月提出正德皇帝被嘉靖朝实录写坏、明末市民生活轻松富足等与流俗看法不同的见解，以及马先生亲述日本豆腐厂夜里12点准时开工的见闻。
+## 访谈详细记录
+### 议题一：日本历史剧《大奥》与文化解读
+- **访谈员**：《大奥》刚播完，引起很大反响，您觉得它怎么样？
+&gt; **受访嘉宾（发言者3）**：我觉得是大长今以后可能最有影响的外国电视剧了，拍得非常好。
+- **访谈员**：您为什么也爱看这个？您是写明朝那些事的，对日本明朝也感兴趣？
+&gt; **受访嘉宾（发言者2）**：明天晚上没事翻临时翻到的。吸引我的是觉得有一种严谨的精神。你如果现在回头看三国演义，会看到很多群众演员会笑，但如果你看日本剧，你看不到笑的。
+1. 发言者3描述《大奥》第一集将军出场时，所有人呈45度鞠躬，依次鞠躬的场面华丽、色彩讲究，一看就不一样，出场就不一样。
+2. 发言者2解释大奥即后宫，日语中“奥”指屋子最深处，一般人不准进去；发言者3补充“奥”是很深的地方，中文里“堂奥”“深奥”仍保留此痕迹。
+3. 发言者2说明日本权力结构：天皇一直是摆设，实际掌权的是幕府将军；德川家康开创德川幕府后，日本所有权力掌握在一人手上，他想要干什么就干什么。
+4. 发言者2举例天皇曾想举办活动但没钱，找将军要钱被拒绝，活动没办成，天皇后来以退位表示对幕府的抗议。
+5. 发言者3认为日本战后用30年时间成为世界第二经济强国（绝对量，非人均量），是唯一没有资源的强国，这不是偶然而是必然，源于全民族的极端精神。
+6. 发言者2对比中日文化：中国文化精神是中庸，讲究在正确与错误之间找一条最适合的路，像太极融合；日本精神恰相反，坚持一个原则、做到极致，如炮手开炮时忘记一切只记得把这一炮开出去，就达到最高境界。
+7. 发言者3指出日本跳槽率最低，终身雇佣制下西方经济学家认为缺乏竞争会导致效率低下，但日本终身雇佣却积极性特别高，这是经济学上的奇迹。
+8. 发言者3举例日本豆腐厂规定当天做当天卖，夜里11:45所有人坐好看着表，12点整一起站起来开始工作，到四点多干完上市，没人闲聊，体现一丝不苟。
+9. 发言者2分析日本作为岛国没有资源、常火山地震，生存条件恶劣，人本身对世界有极强求生欲望，学会融入团体按固定规则做事才能生存。
+10. 发言者3认为日本投机取巧的人没有生存环境，社会文化的鄙视非常难过；举例日本做绳子的人几年不赚钱铺市场，等市场铺平后再各加2%利润，靠4%赚大钱。
+11. 发言者2总结“慢慢来才是最快的方法”，所有人按照自己的角色去做自己的事情，最节省成本，不会有互相的作用力互相抵消，形成合力非常可怕。
+12. 发言者3认为《大奥》中阿福25岁进大奥当奶妈、65岁去世，40年无论做什么事不出于私心，完全出于公心，所有人最终都认为她是楷模，这是日本忠诚文化的具体体现。
+13. 发言者2认为日本人有寻死的潜在欲望，看樱花只看落的那天不看发芽，因生存条件太恶劣，对死亡不是藐视而是有点向往、不惧怕；发言者3纠正为日本民族不是藐视生命而是重视死亡，经济危机时很多身家万贯的人剖腹自杀。
+### 议题二：明朝历史与《明朝那些事儿》
+- **访谈员**：为什么我周围的很多人都表示最近要看明史，包括金庸晚年也说研究明史，为什么大家对明史特别感兴趣？
+&gt; **受访嘉宾（发言者2）**：别人为什么看明史我真不知道。我看明史是因为明史的资料最多。历史界研究有两个难点，第一个是先秦春秋，没史料；第二个是明清，一个事件可能有7个不同的说法，就好像罗生门。
+1. 发言者3指出《明朝那些事儿》发行量在排行榜第一，各报都是文学类第一。
+2. 发言者3认为明朝260多年的过程本身就跌宕起伏，几次要死没死了，如土木堡之变、夺门之变，皇上被瓦剌军抓起来，哥几个又扶起弟弟，完全构成现代版电视剧的情节。
+3. 发言者2推崇朱元璋，认为他从乞丐到最后推翻元朝当上皇帝，定下明朝规章制度且基本没有太大改动，是了不起的人才；发言者3补充历史上最底层的人坐到最上面独此一份，刘邦好歹是村长、亭长，朱元璋是要过饭的。
+4. 发言者3认为人的因素最大，改变时势一定是出现一个人；发言者1将此概括为英雄史观。
+5. 发言者2解释朱元璋参加起义军是逼上梁山：好友汤和让他参加，他在庙里犹豫怕被杀头，后因送信的事被人听到告发，没办法只能去起义；他强调历史最重要的是弄明白这事是真的，当年造反是要掉脑袋的，不是旁观者看着好玩。
+6. 发言者2说明明末市民生活：江南一带工商业兴起，给人当雇工活得很滋润，三言二拍这类娱乐产品出现，说明有能够养活自己的资本；当时连皇册都不用了，想去哪去哪。
+7. 发言者3补充明末工艺品变得非常精细，有点像日本工艺，日本派了大量工匠来中国交流；文征明、唐寅、董其昌都是那个时期的人，生活不好画不出小桥流水，到八大山人明末时画的都是翻白眼，因对社会愤愤不平。
+8. 发言者2提出历史教训：“我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。”因为历史事件发生时有背景，史书记载下来的是照片，而古人的生活是录像，不知道那一幕之前跟之后是什么，不能套用经验。
+9. 发言者2提到1644年明朝灭亡那年，北京闹瘟疫叫疙瘩瘟（今天看就是天花），李自成军打到京城没有人抵抗；他曾与老师王佩奇交流，说明朝亡得真蹊跷，什么坏事衰事都赶上了。
+10. 发言者3认为中国历史王朝300年是大限，逼近300年就完了，像人一到八九十岁大限快到了；严格讲跨过300年的只有宋朝（南北宋接上，退让大半个国土延续319年），汉朝中间隔断14年不能比，唐朝、明朝、清朝都没跨过这个界限。
+11. 发言者2以公司作比：世界上公司超过276年的没几家，明朝这个公司多大摊子、几千万人，能撑276年够本了。
+### 议题三：明朝皇帝趣事与明式家具
+- **访谈员**：我听到一种观点说，故宫金碧辉煌的大红大紫是满族人的趣味，真正明朝不是这样的，请您核实。
+&gt; **受访嘉宾（发言者3）**：宋明是典型的汉人政权、文人政权，文人欣赏审美比较高，对美的判断不是表象的；满族是异族，对美的判断都是表象的。晚清到民国初年的收藏，那种外在直观美的都不值钱，一定是素雅的。
+1. 发言者2讲述明武宗正德想去江南，大臣全跪在金水桥前抗议不让去，皇帝气坏了到锦衣卫打死了十几个人，还是不让去。
+2. 发言者2讲述正德皇帝到扬州后，政府说没有东西、有也不给，皇帝不生气，让人准备酒席，然后说吃不了，把酒席折合成银两带回去。
+3. 发言者3提到天启皇帝爱当木匠，干完活差大臣去卖，回来还打听卖得怎么样，卖得很好，他成就感特大；发言者4调侃要是亲自去卖还好卖。
+4. 发言者3认为明式家具在国际上地位高绝非偶然，皇帝能下那么大力气去做，反映当时家具在每个人心目中地位高，所有偶然中一定有必然因素。
+5. 发言者2分析正德皇帝被写坏的原因：接他班的是嘉靖，嘉靖不是他亲生而是堂兄弟，所以嘉靖指派杨廷和等人编明武宗实录时不能把他写得太好；豹房其实就是玩的地方，有动物园养了豹子，女人在后宫也有，放哪都一样。
+6. 发言者2举例正德皇帝从江南回来没进京城，先在通州停了半天或一天，派人打探京城里有没有人想搞埋伏搞圈套，说明他很有城府，绝不是史料所写的那么蠢。
+7. 发言者3提到正德皇帝是明朝最荒淫的皇帝，但没留种、没有生育能力，对宫廷内女人没兴趣，因禁忌太多；发言者4补充宫廷女人被训练过、太保守，民女不知他是谁，所以不一样。
+8. 发言者2提到嘉靖上台后搞大礼仪事件，为给自己父亲争名分（追封为皇帝）死了很多人，说明历史非常玄幻，有些事你看到以为这么回事，实际上不是这么回事。
+## 关键引语与金句
 &gt; “慢慢来才是最快的方法。”
-- 背景：回应如何理解日本人的极端精神与忠诚文化时，引述他人观点说明按角色做事、不耍小聪明反而最有效率。
-&gt; “我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。”
-- 背景：讨论明朝兴亡经验教训时，回应历史经验能否指导后世的问题。
-&gt; “史书上记载下来是什么。照片，我打个比方是照片，而我们实际上我们的生活，古人的生活都是录像。”
-- 背景：解释为何不能简单套用历史经验，说明史书记载只是瞬间定格，后人看不到前因后果。
-&gt; “日本的文化跟中国的文化存在一个极大的不同。中国的文化精神是什么？是中庸。”
-- 背景：对比中日文化差异时，以硬木刻云彩的家具为例，说明中国讲究融合与最适合的道路。
-&gt; “日本是终身雇佣了，人家还是积极性特别高。”
-- 背景：回应西方经济学对终身雇佣制缺乏竞争会导致效率低下的质疑，指出日本打破了这一规律。
-&gt; “他藐视生命，他很多人表示你为什么说二战时候日军到中国会有那么多暴行，它是一种藐视生命的行为。”
-- 背景：讨论日本人对死亡的态度时，解释日军暴行与日本民族极端精神的关系。
-&gt; “日本民族它不是藐视生命，它是重视死亡，它是翻着的。”
-- 背景：回应发言者2关于日本藐视生命的说法，提出相反观点，认为日本是重视死亡而非藐视生命。
-&gt; “一个人到战场上死生多少年没死，最后积累下来经验，然后我一上战场我就知道唉敌人会往哪走，我该怎么打。天赋。”
-- 背景：评价朱元璋的天分时，以《亮剑》中李云龙为例，说明实战经验积累出的能力是天赋。</t>
+&gt; —— **发言者2（《明朝那些事儿》作者）** ｜ 针对日本文化中按角色行事、不投机取巧的生存方式，总结其效率逻辑
+---
+&gt; “我们从来没有从历史中得到过教训。”
+&gt; —— **发言者2（《明朝那些事儿》作者）** ｜ 回应明朝兴亡经验教训能否借鉴的问题，指出历史教训难以简单套用
+---
+&gt; “所有人按照自己的角色去做自己的事情，最节省成本了，就不会有互相的作用力互相抵消，大家都会有一个共同的目标往前走。”
+&gt; —— **发言者2（《明朝那些事儿》作者）** ｜ 解释日本社会形成合力的机制，以商人、奶妈、王后各司其职为例
+---
+&gt; “日本的文化跟中国的文化存在一个极大的不同。中国的文化精神是什么？是中庸……日本的精神就恰相反，他坚持一个原则，你看鞠一刀就知道。”
+&gt; —— **发言者2（《明朝那些事儿》作者）** ｜ 对比中日文化精神差异，以硬木刻云彩的家具为例说明中庸，以武士刀说明日本的极致
+---
+&gt; “它全民族的这种极端精神，使一个国家在战后这样一个不利的局面下，只需要30年的时间它进入世界第二经济强国。”
+&gt; —— **发言者3（嘉宾）** ｜ 回应日本战后经济崛起的原因，强调极端精神是必然而非偶然
+---
+&gt; “历史它那个事儿发生的时候是有背景的……当你要明白你不比前人聪明，你甚至可能比前人笨，就是当那种情况出现的时候，你也得那么办。”
+&gt; —— **发言者2（《明朝那些事儿》作者）** ｜ 回应为何不能从历史中简单吸取教训，强调设身处地理解历史背景
+---
+&gt; “史书上记载下来是什么。照片……我们实际上我们的生活，古人的生活都是录像……在史书上下来的只是一个照片，咔嚓。但你不知道为那一幕之前跟之后是什么。”
+&gt; —— **发言者2（《明朝那些事儿》作者）** ｜ 解释人们对历史产生误解的原因，指出史书记载缺乏前因后果
+---
+&gt; “这个人绝不是史料上所写的那么蠢……他从江南回来，他没有进京城，他在通州先停了半天……先派人打探，里边也没什么事儿。”
+&gt; —— **发言者2（《明朝那些事儿》作者）** ｜ 为明武宗正德皇帝辩护，指出其有城府，被嘉靖朝编实录时写坏</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>56.6</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14719/3364</t>
+          <t>14719/4396</t>
         </is>
       </c>
     </row>
@@ -5741,48 +5764,50 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t># 就诊概况
-本次门诊为消化专科初诊，由严医生接诊48岁男性患者张学恒，患者职业为科研工作，在成都轻工研究所任职。患者主诉上腹反复疼痛4年，近3个月持续发作，疼痛位于心窝处，呈烧灼感，进食冷硬、辛辣食物或工作紧张劳累时诱发，白天为主，夜间无痛醒；一年前与三个月前各出现一次黑便，每次持续约一个月，查大便提示出血，分别住院约10天和两三天后大便转黄；近两个月呕吐数次，吐出酸味黄水样物，为早午餐食物，晚上腹胀时呕吐后缓解。近期服用奥美拉唑（武汉药厂产）、阿莫西林及所医务室胃炎合剂，效果渐差，奥美拉唑用量已从每日两次每次一颗增至每日四五次。近三个月无黑便，大便黄色正常，小便正常，饮食量无明显下降，体重无明显变化。初步考虑上腹疼痛与消化道出血相关，需进一步检查明确，已安排留大便查出血及后天胃镜检查。
-# 病史与背景
-- **现病史**：上腹反复疼痛4年，每年春季多发，近3个月持续发作；疼痛位于心窝处，呈烧灼感，进食冷硬、辛辣食物或工作紧张劳累时诱发，暖和、工作轻松时无痛，白天为主，夜间无痛醒，疼痛可忍受。
-- **黑便史**：一年前和三个月前各出现一次黑便，每次持续约一个月，每天最多两次，大便形状基本正常；两次均就医，查大便提示出血，分别住院约10天和两三天，住院后大便转黄。
-- **呕吐史**：最近两个月呕吐数次，吐出酸味黄水样物，为早午餐食物，晚上腹胀时呕吐后缓解，无隔夜食物吐出，呕吐物无红色或黑色。
-- **既往史**：16岁时患甲肝，在三医院住院一个月，出院及后续体检肝功能均正常；无手术史，无食物不耐受。
-- **过敏史**：小时候因扁桃体炎在成都市儿童医院就诊，服用磺胺药后左手起红疹，持续约半个月，确诊磺胺药过敏，母亲一直提醒不能吃磺胺药。
-- **预防接种史**：近两年所里统一接种上海产乙肝疫苗，共三针，无不良反应。
-- **系统回顾**：双眼近视400度，平时不常戴眼镜；偶尔口腔溃疡，用贴片治疗；偶有腹泻，多因饮食不洁，急性自愈；偶有头痛头昏，自认为与休息不足有关，未就医。
-- **个人史**：出生于成都，一直在成都生活，在成都轻工研究所从事科研工作，工作紧张，常加班熬夜；吸烟史，以前每天一包，现限制在10支以内，计划逐步戒烟；偶尔饮酒，平时不喝，有应酬时少量；每天泡两次茶；26岁结婚，爱人及孩子身体健康，家庭居住条件良好。
-- **家族史**：父亲76岁，有低血压（90/60mmHg）；母亲75岁，诊断冠心病，药物控制良好；弟弟身体健康；婶婶（叔叔的爱人）患胃癌，患者担心自己是否也会得此病。
-# 诊断与检查结果
-初步考虑上腹疼痛与消化道出血相关，需进一步检查明确，尚未确诊。患者一年前和三个月前两次黑便，查大便均提示出血，分别住院约10天和两三天后大便转黄；近三个月无黑便，大便黄色正常，小便正常。医生对结果的说明：甲肝为急性病，不会慢性迁延，出院时肝功能已完全恢复；婶婶患胃癌与患者无血缘关系，不必担心遗传问题。患者顾虑：担心自己是否也会得胃癌；担心是否需要手术，因工作繁忙且所里领导安排其出国进修，希望如需手术能尽早安排；对医疗费用无担忧，因夫妻双方工作且有社保。
-# 治疗方案与医嘱
-- **检查安排**：患者需留大便进行出血相关检查；胃镜原定明天，患者请求改至后天以便爱人陪同，严医生同意并预约后天。
-- **生活方式与饮食**：严医生建议患者尽量少抽烟或不抽烟，戒烟对疾病有好处；尽量少喝酒，因酒对胃部疾病影响较大；注意避免工作紧张、劳累和加班熬夜，因可能加重病情。
-- **复诊安排**：严医生将总结病情后向上级张医生汇报，再商定下一步处理意见。
+          <t># 消化专科门诊：上腹疼痛病史采集与检查安排
+## 就诊概况
+48岁男性患者张学恒，在成都轻工研究所从事科研工作，因上腹反复疼痛4年、近3个月持续加重，于消化专科门诊初诊。疼痛位于心窝处，呈烧灼感，进食冷、硬、辛辣食物或工作紧张劳累时诱发，近3个月白天发作、夜间无痛醒，暖和、工作轻松时无痛。一年前与三个月前各出现一次黑便，每次持续约一个月，查大便提示出血，两次住院后大便转黄；近两个月呕吐数次，吐出酸味黄水样物，为早、午餐食物，晚上腹胀时呕吐后缓解。近期服用奥美拉唑（武汉药厂产）、阿莫西林及医务室自配胃炎合剂，效果不佳。近三个月无黑便，大便黄色正常，小便正常，饮食量无明显下降，体重无明显变化。初步考虑上消化道疾病可能，需进一步检查明确，已预约后天胃镜并留大便查出血。
+## 病史与背景
+1. **现病史**：上腹疼痛反复发作4年，每年春季多发，近3个月持续疼痛，位于心窝处，有烧灼感，进食冷、硬、辛辣食物或工作紧张劳累时诱发，暖和、工作轻松时无痛，疼痛可忍受，白天发作，夜间无痛醒。
+  - 一年前和三个月前各出现一次黑便，每次持续约一个月，每天最多两次，大便形状基本正常，查大便提示出血，两次住院（第一次约10天，第二次两三天）后大便转黄。
+  - 最近两个月呕吐数次，吐出酸味黄水样物，为早、午餐食物，晚上腹胀时呕吐后缓解，无隔夜食物吐出，呕吐物无红色或黑色。
+2. **既往史**：16岁时患甲肝，在三医院住院一个月，出院及后续体检肝功能均正常；小时候因扁桃体炎在成都市儿童医院就诊，服用磺胺药后左手起红疹，持续半个月，确诊磺胺药过敏；双眼近视400度，偶尔口腔溃疡；无手术史。
+3. **个人史**：吸烟史，以前每天一包，现限制在10支以内，计划逐步戒烟；偶尔饮酒，平时不喝；喝茶，每天泡两次；在成都轻工研究所从事科研工作，工作紧张，经常加班熬夜；出生并长期生活在成都。
+4. **家族史**：父亲76岁有低血压，母亲75岁有冠心病，弟弟身体健康；婶婶（无血缘关系）患胃癌，患者担心自己是否也患此病。
+## 诊断与检查结果
+1. **初步印象**：考虑上消化道疾病可能（结合上腹烧灼样疼痛、黑便史），需进一步检查明确，尚未确诊。
+2. **检查安排**：留大便查出血，因患者曾出现两次黑便；预约后天胃镜，因患者爱人后天可请假陪同，胃镜活检后恰逢张大夫查房。
+3. **医生说明**：严医生解释婶婶虽患胃癌，但无血缘关系，不必担心遗传问题；关于手术，待检查资料全面后再判断，药物控制有效则可不手术。
+4. **患者顾虑**：担心是否需手术，因工作忙且所里领导安排出国进修，希望如需手术尽早安排；对医疗费用无担忧，因夫妻双方工作且有社保。
+## 治疗方案与医嘱
+1. **检查安排**：留大便做出血检查；胃镜预约在后天进行，胃镜活检后恰逢张大夫查房。
+2. **生活方式与饮食**：建议戒烟，因吸烟对胃部疾病不利；建议少喝酒，因近期有便血情况，酒对胃部疾病影响大；注意避免工作紧张、劳累和加班熬夜。
+3. **复诊安排**：严医生将总结病情后向上一级张医生（指导教授）汇报，再与患者商量下一步处理意见。
+4. **用药说明**：患者近期服用奥美拉唑（武汉药厂产）、阿莫西林及医务室自配胃炎合剂，效果不佳，具体用药调整待检查后决定。
 | 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
 | --- | --- | --- | --- | --- |
-| 奥美拉唑 | 每次一颗 | 每日两次，后增至每日四五次 | 口服 | 武汉药厂产，国产；刚开始吃有效，后效果渐差，用量增加 |
-| 阿莫西林 | — | — | 口服 | 与奥美拉唑同服 |
-| 胃炎合剂 | — | — | 口服 | 所医务室自制；刚开始吃有效，停药后疼痛反复 |
-# 复诊与预警信号
-## 复诊与随访安排
-- **胃镜检查**：预约在后天进行，以便患者爱人陪同。
-- **大便检查**：患者需留大便进行出血相关检查。
-- **病情汇报**：严医生将总结病情后向上级张医生汇报，再商定治疗方案。
-## 预警信号
-- ⚠️ 反复上腹疼痛、两次黑便，需排除消化道出血及恶性病变可能。
-- ⚠️ 磺胺药过敏史，用药需注意。
-## 需要观察的变化
-- 观察大便颜色，若再次出现黑便需及时就医。
-- 观察疼痛发作情况，若疼痛加重或出现新症状需提前联系。</t>
+| 奥美拉唑 | — | — | 口服 | 武汉药厂产（国产），近期服用效果不佳 |
+| 阿莫西林 | — | — | 口服 | 近期服用，效果不佳 |
+| 胃炎合剂 | — | — | 口服 | 医务室自配，近期服用，效果不佳 |
+## 复诊与预警信号
+### 复诊与随访安排
+1. **胃镜**：预约在后天进行，因患者爱人后天可请假陪同，胃镜活检后恰逢张大夫查房。
+2. **大便检查**：留大便查出血，因患者曾出现两次黑便。
+3. **病情汇报**：严医生将总结病情后向上一级张医生汇报，再与患者商量下一步处理意见。
+### 预警信号
+1. **黑便**：患者曾出现两次黑便，需关注有无再次出现。
+2. **呕吐**：近两个月呕吐数次，需观察呕吐物有无红色或黑色。
+### 需要观察的变化
+1. **大便颜色**：近三个月大便黄色正常，需继续观察有无变黑。
+2. **疼痛变化**：观察上腹疼痛发作频率与诱因，工作紧张、劳累时易发作。</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>56.6</v>
+        <v>52.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8519/1954</t>
+          <t>8519/1862</t>
         </is>
       </c>
     </row>
@@ -6737,55 +6762,51 @@
       <c r="C18" t="inlineStr">
         <is>
           <t># 庭审概况
-本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷一案，因不服云南省高级人民法院云民初88号民事判决提起上诉。本院依法组成合议庭公开开庭审理，围绕抵押权与融资租赁所有权冲突、罚息复利计算、违约金三个争议焦点进行审理。合议庭休庭评议后提出调解方案，各方当事人均无异议，达成调解协议。
+本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷二审案件，由最高人民法院组成合议庭公开开庭审理。庭审围绕抵押权与融资租赁所有权冲突、罚息复利计算、违约金三个争议焦点展开辩论，各方当事人及代理人充分发表意见，最终在合议庭主持下达成调解协议，各方签字确认。
 # 原告诉称与被告辩称
 | 方 | 诉讼请求/答辩意见 | 事实与理由 |
 | --- | --- | --- |
-| 上诉人（国家开发银行） | 请求撤销一审判决，改判支持其罚息、复利及违约金主张 | 主张其已尽审查义务，构成善意取得抵押权；罚息自2018年6月13日起算，复利按合同约定计算；东源煤电未配合办理账户管理及柜台业务，构成违约，应支付违约金 |
-| 被上诉人（云南东源电力股份有限公司、云南东源曲靖电力有限公司） | 请求驳回上诉，维持一审判决 | 主张国开行未充分查询融资租赁登记，存在过失；罚息不应作为复利基数，贷款提前到期应给合理期限；国开行未举证违约事实，且未发出限期纠正通知 |
-| 被上诉人（招银金融租赁有限公司） | 请求驳回上诉，维持一审判决 | 主张2012年已取得设备所有权，国开行2015年办理抵押时未查询融资租赁登记，不构成善意取得；国开行未履行审查义务 |
+| 上诉人（国家开发银行） | 请求撤销一审判决相关判项，改判支持其罚息、复利、违约金等诉讼请求 | 主张其已尽审查义务，构成善意取得抵押权；利息应计算至2017年12月20日，罚息自2018年6月13日起算；按合同约定东源煤电违约应支付千分之一违约金 |
+| 被上诉人（云南东源电力股份有限公司、云南东源曲靖电力有限公司） | 请求驳回上诉，维持一审判决 | 主张2015年12月2日邮件已告知设备融资租赁情况，国开行未尽注意义务；合同约定限期偿还而非立即到期，罚息不应计收复利；国开行未举证违约行为且未发出限期纠正通知 |
+| 被上诉人（招银金融租赁有限公司） | 请求驳回上诉，维持一审判决 | 主张其2012年即取得设备所有权，国开行2015年办理抵押时未查询融资租赁登记，不构成善意；东源煤电出资行为系无权处分 |
 # 举证与法庭调查
 ## 举证与质证
-- **国开行提交**：2018年9月融资租赁查询证书，证明其已尽查询义务。招银租赁质证认为该查询证书不符合要求，依据2014年93号中国人民银行关于融资租赁登记系统规定，国开行在抵押时点未进行相应查询。
-- **国开行提交**：工商部门出资证明、四冶合成58亿材料、人民银行出具的相关情况，证明已对设备所有权尽到审慎审查义务。东源公司质证认为该材料仅为贷后审查材料，不符合客观事实。
-- **招银租赁提交**：回租设备清单（一审证据7页），载明设备名称和生产厂家，未提及设备型号。国开行质证认为该清单无法证明设备唯一性，且清单提示2012年3月1日，与设备铭牌生产日期（2013年11月、12月、2014年3月）不符。
-- **招银租赁提交**：2013年和2015年审计报告（证据82页、95页），载明曲靖电力公司注册资本4亿元且已实缴。国开行质证认为该报告已载明设备出资事项。
-- **国开行提交**：2018年核查表（证据108页），证明曲靖电力公司名下无融资租赁登记。招银租赁质证认为该核查表不符合要求。
-## 证人、鉴定与其他来源陈述
-- **评估报告**：明确曲靖电力公司拥有的在建工程价值5.7亿元，机械设备价值5.1亿元。国开行代理人主张该报告确认了资产存在。
-- **审计报告**：招银租赁一审提交的2013年和2015年审计报告，载明曲靖电力公司注册资本4亿元且已实缴。
+- **2015年12月2日邮件及融资情况统计表（东源公司）**：东源公司主张该邮件已告知国开行案涉设备存在融资租赁情况，统计表中两家公司抵押设备名称完全相同且用红色标注；国开行质证认为该邮件系常规贷后审查材料，正文及附表均无融资租赁告知内容，统计表显示招银租赁抵押类型为不动产抵押，与融资租赁概念不同，不能得出已告知的结论。
+- **回租设备清单（招银租赁一审提交，证据第7页）**：国开行质证认为该清单仅载明设备名称和生产厂家，未提及设备型号，无法判断设备同一性；清单提示生产日期为2012年3月1日，而抵押设备铭牌记载生产日期均在2013年以后，看不出是同一设备。
+- **工商部门出资证明及权属声明（国开行提交，证据四）**：国开行主张该证据证明其已对设备所有权尽到审慎审查义务；招银租赁质证认为工商登记公示的是出资行为而非动产所有权，东源煤电出资行为系无权处分。
+- **2018年融资租赁登记核查表（国开行提交，证据第108页）**：国开行主张2018年再次核查时曲靖电力公司名下仍无融资租赁登记，已按法律法规履行核查义务；招银租赁质证认为该查询证书不符合2014年93号文规定，国开行在抵押时点未进行相应查询。
+- **2013年、2015年审计报告（招银租赁一审提交，证据第82页、第95页）**：国开行主张该报告载明曲靖电力公司注册资本4亿元且已实缴，证明招银租赁知道或应当知道设备出资情况；招银租赁未就此提出异议。
+- **上海中院一审判决（招银租赁提及）**：国开行主张该判决仅限东源公司返还设备义务，未确认设备所有权归招银租赁，与本案抵押权审理不冲突；招银租赁未直接回应。
 ## 法官询问
-- **审判员询问国开行**：贷款前审查风险控制资料中，内部是否有规定必须查询融资租赁登记，未查到需将未查到单子作为风控材料。国开行代理人答：按央行规定需查询系统，但未保留筛查记录，因未查到结果故无必要保留。
-- **审判员询问国开行**：认为查询了电力公司登记信息，未查到设备融资租赁登记结果，以此免责的逻辑。国开行代理人答：作为金融机构按央行规定查询融资租赁系统，因设备为通用设备无法逐一查询，且查询曲靖电力公司名下无融资租赁记载，至今仍无结果，故无过失。
-- **审判员询问招银租赁**：融资租赁登记系统中设备唯一标识码是否必填项。招银租赁代理人答：设备唯一标识码不是必填项，因设备不像汽车有发动机号，无法填写。
-- **审判员询问国开行和招银租赁**：查询通知规定银行业办理抵押前需查询，违反规范会导致最高人民法院何种后果。国开行代理人答：这是基本查询义务，依据最高人民法院融资租赁司法解释第九条第三款，金融机构取得善意权利应查询融资租赁情况。招银租赁代理人答：这是对银行业的严格要求，未查询即违反行业规范。
-- **审判员询问**：动产融资租赁因属性问题产生所有权与占有分离，融资租赁司法解释第九条第一款规定善意取得情形，第二款列举排除善意取得情形。各方就查询义务范围发表意见。
-- **审判员询问**：案涉动产设备无统一登记制度，如何看待不同登记机构产生登记瑕疵。国开行代理人答：人民银行融资租赁登记系统与动产抵押登记存在冲突，系统信息不完整是整体问题。东源公司代理人答：系统整合有必要，但东源公司非专业机构，无法提供建议。招银租赁代理人答：规范不统一、登记机构不统一导致信息不对称，应从立法层面统一要求。
+- **【融资租赁登记性质】**：审判长询问各方如何理解中国人民银行征信中心融资租赁登记的性质及法律后果。国开行代理人认为属行业强制性规范，目的是防范动产可移动性、不明确性带来的金融风险；国开行第二代理人认为动产抵押登记是法定登记，具有排他性，融资租赁登记更多是行业性质；东源公司代理人认为融资租赁登记只是行业指导性规范，非强制性，不当然产生物权后果；招银租赁代理人认为根据物权法定原则，融资租赁登记不是法定物权登记，只是权利公示，强化动产权利外观，可能产生对抗效力，但不影响所有权设立、转移的法定效果。
+- **【查询方式能否保证查到登记结果】**：合议庭成员询问国开行和招银租赁，央行融资租赁登记系统的查询方式能否保证查询到登记结果。国开行代理人称目前只能按查询单位（公司名称）查询；招银租赁代理人称可通过公司名称或设备情况两种方式查询，以设备查询时涉及种类物区分问题，需登记因素区分设备唯一性。
+- **【贷款前审查是否要求保留未查询到结果的单证】**：审判员询问国开行，贷款前审查风控资料中是否有内部规定要求必须查询融资租赁系统，未查到结果时是否需将未查到的单子作为风控材料。国开行代理人称按央行规定需做筛查，但因未查询到结果，当时未保留筛查记录，且至今系统仍无登记，说明行为无过失。
+- **【设备唯一标识码是否必填项】**：审判员询问招银租赁，融资租赁登记系统中设备唯一标识码是否必填项。招银租赁代理人称不是必填项，案涉设备不像汽车有发动机号，铭牌上只有型号和参数，无法填写唯一标识码。
+- **【查询通知违反后果及审查义务范围】**：审判员询问国开行和招银租赁，查询通知规定银行办理抵押前应查询，违反该规范会导致何种后果，以及审查义务应达到何种程度。国开行代理人认为查询是基本义务，根据最高人民法院融资租赁司法解释第九条第三款，金融机构取得善意权利应查询融资租赁情况，其针对抵押人曲靖电力公司的审慎调查义务已完成；招银租赁代理人认为查询是对银行业的严格要求，未查询即违反行业规范，本案中综合各方信息能确定五台设备的唯一性和独特性，国开行未查询不构成善意。
+- **【通过其他渠道获知租赁后是否仍需查询】**：审判员询问，若银行通过其他渠道获知抵押设备存在租赁，是否仍需通过央行系统查询。国开行代理人认为查询是基本义务，必须进行；招银租赁代理人认为通过其他方式获知后仍应通过央行系统查询，因央行规定出台背景是实务中存在大量案例，只有通过确定标准才能衡量双方善意，其他证据不能取代央行审查义务。
+- **【融资租赁司法解释第九条举证责任分配】**：审判员询问各方对融资租赁司法解释第九条的理解。招银租赁代理人认为应依据谁主张谁举证原则，综合考量各方义务内容和证据优势判断；第1、2、4项应由出租人举证，第3项应由第三人（国开行）证明办理抵押时进行了查询；国开行代理人认为其审查义务仅限于抵押人曲靖电力公司，已尽合理审慎义务。
+- **【不同登记机构产生登记瑕疵的看法】**：审判长询问各方如何看待因不同登记机构产生登记瑕疵的问题。国开行代理人认为动产抵押登记由工商部门办理，融资租赁登记由央行平台办理，两系统信息不联通，可能导致多重抵押风险，建议信息整合；东源公司代理人称非专业机构，提供不了建议；招银租赁代理人认为规范不统一、登记机构不统一导致信息不对称，建议从立法层面统一要求，发挥行业协会作用，技术上实现登记平台统一化。
 ## 争议焦点与辩论
-- **争议焦点一：抵押权与融资租赁所有权冲突**。国开行主张其抵押设备为通用设备，无唯一标识码，无法逐一查询，已尽审查义务构成善意取得；招银租赁主张2012年已取得设备所有权，国开行2015年办理抵押时未查询融资租赁登记，不构成善意；东源公司主张2015年12月2日邮件已告知设备抵押情况，国开行未予注意。
-- **争议焦点二：罚息、复利计算**。国开行主张利息计算至2018年6月12日合计2179万5727.08元，罚息自2018年6月13日至2019年2月19日合计4105万0579.57元，复利自2018年3月21日至2019年2月19日合计191.8206万元；东源公司主张罚息不应计收复利，依据《人民币利率管理规定》第21条，且贷款提前到期应给合理期限。
-- **争议焦点三：违约金**。国开行主张依据借款合同第24条第三项，东源煤电应支付千分之一违约金；东源公司主张国开行未举证东源煤电违反柜台协议，且未发出限期纠正通知，不符合合同约定。
+- **争议焦点一：抵押权与融资租赁所有权冲突**。国开行主张其抵押设备为通用设备，无唯一标识码，无法逐一查询，已按央行规定查询曲靖电力公司名下登记，未发现融资租赁信息，构成善意取得；东源公司主张2015年12月2日邮件已告知设备融资租赁情况，国开行作为专业金融机构发现设备名称一致且红色标注后应尽注意义务；招银租赁主张其2012年即取得设备所有权，国开行2015年办理抵押时未查询融资租赁登记，不构成善意，且东源煤电出资行为系无权处分。
+- **争议焦点二：罚息、复息计算**。国开行主张利息计算至2017年12月20日，罚息自2018年6月13日起算，利息合计2179万5727.08元、罚息4105万零579.57元、复利191.8206万元；东源公司认为合同约定限期偿还而非立即到期，罚息不应计收复利，引用《人民币利率管理规定》第21条及最高院判例支持其主张。
+- **争议焦点三：违约金给付**。国开行主张按借款合同第24条第三项，东源煤电违约应支付千分之一违约金；东源公司称国开行未举证东源煤电违反柜台协议，且未按合同约定发出限期纠正通知，主张违约金不符合合同约定。
 # 庭审结果
-- **争议焦点一：抵押权与融资租赁所有权冲突**：国开行主张其已尽审查义务、构成善意取得抵押权；招银租赁及东源公司认为国开行未充分查询融资租赁登记、存在过失。
-- **争议焦点二：罚息、复利计算**：国开行主张罚息自2018年6月13日起算，复利按合同约定计算；东源公司认为罚息不应作为复利基数，且贷款提前到期未给合理期限。
-- **争议焦点三：违约金**：国开行主张东源煤电未配合办理账户管理及柜台业务，构成违约，应支付违约金；东源公司认为国开行未举证违约事实，且未发出限期纠正通知。
-- **调解结果**：经本院主持调解，各方当事人自愿达成调解协议，本院予以确认，庭后出具调解书。
-  - 国开行对东源公司债权扣除破产清偿本金后，利息、罚息、复利合计6474.4513万元。
-  - 招银租赁对涉案六项设备享有所有权，对应债权1377.4137万元。
-  - 国开行对93项设备有抵押权，招银租赁对6项设备有所有权。
-  - 案涉全部发电设备整体盘活处置，变现款双方各50%，实现费用双方各担50%。
-  - 变现款不足清偿时，招银租赁未实现债权按破产重整计划预留方案清偿。
-  - 司法变现不能时，国开行和招银租赁放弃设备权益，由东源曲靖电力自主生产经营。
-  - 一审判决第二项、第四项无争议，按判项确认。
-  - 各方就本案涉及问题不再存在任何争议。</t>
+- **调解协议达成**：经合议庭主持调解，各方当事人自愿达成调解协议，法院予以确认，并出具调解书。
+- **债权数额确定**：国开行对东源公司债权扣除破产清偿本金后，利息、罚息、复利共计6474.4513万元。
+- **设备权属确认**：招银租赁对涉案六项设备享有所有权，对应债权1377.4137万元；国开行对93项设备有抵押权。
+- **设备处置安排**：案涉全部发电设备整体盘活处置，变现款双方各50%，费用各担50%。
+- **变现不能的兜底**：若司法变现不能，国开行和招银租赁放弃设备权益，由东源曲靖电力自主生产经营。
+- **无争议判项确认**：各方对一审判决第二项、第四项无争议，按判项内容在调解书中确认。
+- **诉讼费用处理**：一审诉讼费中国开行诉请部分按一审判决执行，招银租赁诉请部分由二审法院按规定确定；二审诉讼费由本院依法确定。
+- **司法建议**：合议庭将依据最高人民法院关于加强司法建议工作的意见，向有关部门提出司法建议，推动建立统一动产登记制度。</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>64.2</v>
+        <v>74.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>30731/2953</t>
+          <t>30731/3693</t>
         </is>
       </c>
     </row>
@@ -6891,51 +6912,51 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t># 候选人概况与面试岗位
-考生为文科背景，未提及学历、专业与工作经历细节。本次为公务员招录结构化面试，时长20分钟，共4道题，由考官主持并计时。考生全程作答完整，四题均按题号依次回答，未出现明显卡顿或超时；面试官仅在第四题作答中途提示“离本场考试结束还有3分钟”，并在全部作答后询问“请问你还有什么需要补充的吗？”，考生回答“没有要补充的了”，面试结束。整体表现：答题结构清晰、内容充实，能结合公务员工作实际展开论述。
-# 面试问答纪要
-## 第一题（综合分析能力）
-- 题目：以“骏马、风筝、陀螺”与绳子的关系为喻，谈对做好公务员工作的启示。
-- 作答要点：绳子对骏马是鞭策，对风筝是平衡，对陀螺是动力；公务员需自我反省，引用曾子“吾日三省吾身”；单位应形成紧张、活泼、团结、有趣的风气，同事间比较能力与效率；治国理政中权利与责任需平衡，建立权利清单、责任清单；陀螺的“连轴转”体现公务员的责任感与成就感，如撰写长材料需加班加点、斟词酌句。
-## 第二题（组织协调能力）
-- 题目：作为市政府办公室工作人员小王，如何完成对AI企业发展的调研任务。
-- 作答要点：前期准备包括利用业余时间补课弥补文科生对AI的知识盲区、学习兄弟城市调研经验、查阅国务院及省厅关于人工智能发展的指导意见；制定涵盖客观（企业发展现状）与主观（政府服务需求）两方面的工作方案并呈报领导审阅；实施阶段通过与企业对接阅读发展报告、制定调查问卷并请专家修改、召开人工智能企业座谈会听取意见；管理措施方面关注AI发展中的问题（如共享充电宝信任危机），通过问卷调查摸排需规范之处。
-## 第三题（应急处理与沟通能力）
-- 题目：作为市级服务标兵小王，现场模拟回应记者关于排水管道反复堵塞的投诉。
-- 作答要点：先询问记者姓氏并自我介绍；解释管道为上世纪90年代老城区集中整治时所建，改造难度大，夏季用水高峰问题集中出现；承认工作失职，表示已联系维修师傅准备现场维修，并已将硬件问题汇报上级部门，计划通过城市综合保障工程改善；请求媒体给予改进机会，并希望媒体向公众解释政府难处与管道真实问题。
-## 第四题（公共服务意识）
-- 题目：从公共服务角度谈处理道路改造和雨污分流工程引发社会矛盾的思路。
-- 作答要点：分析主要矛盾是时间上的需求不满足（过去城市发展滞后），次要矛盾包括噪音、出行、舆论问题；措施包括督促施工方加快进度、设置防噪墙、洒水降尘、建议出行便道、通过交通广播推荐路线、鼓励公交出行并增加班次；最后通过网络公告公开透明发布政府举措，争取市民理解。
-# 能力评估
+          <t># 公务员面试：四题综合能力考察
+## 候选人概况与面试岗位
+考生为文科背景，未提及学历、专业及工作经历。本次为公务员招录面试，时长20分钟，共4道题，由考官宣读规则并逐题提问，计时员提醒剩余时间。考生逐题作答，四题均完成作答，无补充内容，面试正常结束。整体作答结构完整，第一题从自我反省、单位风气、权力责任、工作动力展开；第二题提出调研三步走方案；第三题现场模拟答复记者；第四题区分主次矛盾并提出措施。面试官未作当场点评，仅按流程推进。
+## 面试问答纪要
+### Q1. 【综合分析能力】
+- **面试官**：以绳子对骏马、风筝、陀螺的不同作用为喻，要求考生谈对公务员工作的启示。
+&gt; **候选人**：绳子对骏马是鞭策，对风筝是平衡，对陀螺是动力。考生引用曾子“吾日三省吾身”强调自我反省，提出单位应形成紧张、活泼、团结、有趣的风气，同事间比能力效率而非票子车子房子；治国理政中权利和责任是风筝的“风”和“绳子”，需建立权利清单、责任清单；陀螺的“连轴转”体现公职人员工作状态，靠责任感和成就感支撑。
+### Q2. 【组织协调能力】
+- **面试官**：市政府部署调研AI企业，了解发展状况和服务需求，为出台扶持政策提供依据，考生作为小王如何完成任务。
+&gt; **候选人**：提出三步走方案：前期准备（利用课余补课弥补文科生知识盲区、学习兄弟城市调研经验、查阅国务院及省厅关于人工智能的指导意见）；制定方案（客观方面侧重企业发展现状，主观方面侧重政府服务需求，包含市场状况、服务需求、管理措施三部分，呈报领导审阅）；实施调研（对接企业阅读发展报告、制定调查问卷请专家修改、召开座谈会听取企业意见，服务需求涉及人才引进、政策倾斜、用地审批、人才培养机制，管理措施通过问卷调查了解AI发展不完善之处以便政策规范）。
+### Q3. 【应急处理能力】
+- **面试官**：记者投诉排水管道疏通后再次堵塞，质疑标兵名不副实，考生作为小王现场模拟答复。
+&gt; **候选人**：先询问记者姓氏，解释管道是上世纪90年代老城区修建，改造难度大，夏天用水高峰问题集中出现；承诺已联系维修师傅准备赶赴现场，已向上级汇报，计划通过城市综合保障工程改善基础设施；承认工作失职，请求媒体给予改进机会，并希望媒体向公众解释政府难处和管道真实问题。
+### Q4. 【公共服务意识】
+- **面试官**：道路改造和雨污分流工程带来噪音、灰尘、交通拥堵，居民不满，从公共服务角度谈处理社会矛盾的思路。
+&gt; **候选人**：区分主要矛盾（时间上过去城市发展滞后导致需求跟不上）和次要矛盾（噪音、出行、舆论）；措施包括督促施工方加快进度、加装防噪墙、洒水降尘、建议出行便道、通过交通广播推荐路线、鼓励公交出行并增加班次；计划以公告形式在网络公开透明发布政府举措，争取市民理解。
+## 能力评估
 | 评估维度 | 推荐评级 | 评估依据（具体事例） |
 | --- | --- | --- |
-| 综合分析能力 | 良 | 第一题从绳子对骏马、风筝、陀螺的不同作用展开联想，分别对应自我反省、权利与责任平衡、工作动力，并引用曾子名言，联系公务员工作实际；但出现“陀螺癌”口误，部分表述不够精准。 |
-| 组织协调能力 | 良 | 第二题调研方案分前期准备、制定方案、实施调研、管理措施四步，涵盖学习兄弟城市经验、查阅上级文件、企业对接、问卷调查、座谈会等具体措施，结构完整；但自述对AI领域存在知识盲区，需靠业余补课。 |
-| 应急处理能力 | 良 | 第三题模拟回应记者时，先询问姓氏、自我介绍，解释管道问题原因（老城区改造难、夏季用水高峰），承认工作失职，说明已联系维修、汇报上级，并请求媒体给予改进机会，处理流程完整。 |
-| 公共服务意识 | 良 | 第四题从公共服务角度分析主要矛盾（时间上的需求不满足）与次要矛盾（噪音、出行、舆论），提出督促施工方加快进度、设置防噪墙、洒水降尘、建议出行便道、交通广播推荐路线、鼓励公交出行、网络公告公开透明等措施，体现服务意识。 |
-| 语言表达 | 中 | 整体表达流畅，但出现“陀螺癌”口误、第四题开头误说“回答第三第四题”，且部分语句重复（如“权利和责任就是我们的风和神的”），表达精准度有待提升。 |
-# 综合素质
-## 突出亮点
-- **知识运用**：第一题引用曾子“吾日三省吾身”，并联系“权利清单、责任清单”等政策概念。
-- **结构完整**：第二题调研方案按“前期准备—制定方案—实施调研—管理措施”分步展开，逻辑清晰。
-- **情境代入**：第三题模拟回应记者时，先询问姓氏、自我介绍，并说明“我也是这个片区的普通居民”，体现共情。
-- **问题分析**：第四题将矛盾分为主要矛盾与次要矛盾，并分别提出应对措施。
-## 潜在风险点
-- **知识盲区**：第二题考生自述“因为是文科生，对人工智能方面存在知识的盲区”，需靠业余补课弥补。
-- **表述瑕疵**：第一题出现“陀螺癌”口误，第四题开头误说“回答第三第四题”。
-- **时间管理**：第四题作答中途被计时员提醒“离本场考试结束还有3分钟”，说明时间分配偏紧。
-## 推进建议
-- **加强专业储备**：针对AI等高新技术领域，建议提前系统学习相关知识，避免临时补课。
-- **优化时间分配**：四题20分钟，建议每题控制在5分钟内，预留检查时间。
-- **注意表达准确**：避免口误和题号混淆，答题前可先列提纲。</t>
+| 综合分析能力 | 良 | 第一题从自我反省、单位风气、权力责任、工作动力四方面展开，引用曾子名言，但个别表述含混（“权利和责任就是我们的风和神的”） |
+| 组织协调能力 | 良 | 第二题提出调研三步走方案，覆盖前期准备、方案制定、实施调研，措施具体（对接企业、座谈会、调查问卷），但未提及时间节点和分工 |
+| 应急处理能力 | 良 | 第三题模拟答复记者，解释原因、承诺维修、汇报上级、承认失职，但语言口语化（“咱们”“视频朋友们”） |
+| 公共服务意识 | 良 | 第四题区分主次矛盾，提出防噪墙、洒水降尘、公交出行等措施，并计划公告公开，但部分表述重复 |
+## 综合素质
+### 突出亮点
+1. **引用经典增强说服力**：第一题引用曾子“吾日三省吾身”支撑自我反省观点。
+2. **调研方案结构完整**：第二题按前期准备、制定方案、实施调研三步展开，覆盖客观现状、服务需求、管理措施三方面。
+3. **应急答复兼顾解释与行动**：第三题既解释管道老化原因，又承诺立即维修并汇报上级，同时承认失职。
+4. **矛盾分析有层次**：第四题区分主要矛盾与次要矛盾，措施具体（防噪墙、洒水降尘、公交出行）。
+### 潜在风险点
+1. **知识盲区坦诚但依赖补课**：第二题考生自述文科生对AI存在知识盲区，需利用课余时间补课，可能影响调研专业性。
+2. **部分表述口语化**：第三题模拟答复中“咱们”“视频朋友们”等用语不够正式，可能影响沟通效果。
+3. **个别表述含混**：第一题“权利和责任就是我们的风和神的”表述不清，第四题“主要矛盾得到消解之后，媒体呢这样一个议论和不满也会逐渐的减少”语句重复。
+### 推进建议
+1. **加强专业知识储备**：针对AI等专业领域，建议提前系统学习相关政策和技术知识。
+2. **规范语言表达**：模拟答复和正式发言中注意用词严谨，避免口语化表达。
+3. **细化措施可操作性**：调研方案中可补充具体时间节点、责任分工等细节，增强执行性。</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>45.7</v>
+        <v>46.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5808/2151</t>
+          <t>5808/2090</t>
         </is>
       </c>
     </row>
@@ -7003,81 +7024,68 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t># 参观概况
-本次参观围绕故宫博物院展开，由主讲人按中轴线及东西两路顺序进行讲解，覆盖午门、太和门、太和殿、中和殿、保和殿、乾清门、乾清宫、交泰殿、坤宁宫、储秀宫、慈宁宫、珍宝馆等主要景点，穿插历史典故与建筑特色。讲解从午门检票入场开始，依次介绍各殿功能与规制，如午门明三暗五的门洞及通行等级、太和殿举行登基册封等大典、保和殿自乾隆五十四年起作为殿试考场、乾清宫藏立储诏书等。行程中亦介绍故宫内七个免费盖章点及紫禁城100购买规则，并推荐珍宝馆、乐寿堂等必看之处。游览全程约需半天至一天，主讲人最后总结三条游览路线，建议早起错峰入园。
-# 核心看点与讲解
-- **午门**：明三暗五的门洞结构，中间正门仅供皇帝通行，皇后大婚时可进一次，殿试前三名（状元、榜眼、探花）可出一次；两侧门洞走皇亲国戚和文武百官。明朝在此杖打犯错大臣，清朝在此举行颁朔之礼。
-- **太和门广场**：眼前有五座金水桥，皇帝走中间，皇亲国戚走挨着中间两座，文武百官走最边上。太和门是明朝皇帝御门听政（上朝）的地方，门口铜狮子是故宫六对铜狮中最大的一对，脚踩寰宇象征权力。
-- **太和殿**：即金銮殿，是举行盛大典礼的地方，如皇帝登基、皇后册封。文武百官在太和殿广场站列，按文东武西站位，向皇帝喊出“吾皇万岁万岁万万岁”。
-- **体仁阁与弘义阁**：西边弘义阁（原文作“红衣阁”）是皇帝的银库，东边体仁阁是缎库。
-- **中和殿**：举行盛大典礼时皇帝的休息室，文武百官站好后皇帝再前往太和殿。
-- **保和殿**：从乾隆五十四年开始作为殿试考场。东北角有汉字馆，内有4枚免费印章，可购买《紫禁城100》现场盖章。
-- **乾清门**：过此门即后宫区域。东边九卿直房是等级高的大臣等待皇帝召见之处，西边是军机处。门口铜狮耳朵耷拉、眉毛遮眼，警示后宫之人不该看的别看、不该听的别听。
-- **乾清宫**：皇帝平时睡觉的地方，内有27张龙床，据说是为防止刺客找到皇帝位置。“正大光明”牌匾后藏皇帝立储诏书，皇帝驾崩后与另一份对比验证真伪。门口摆放铜鹤与铜龟，旁边有社稷江山金殿，是紫禁城最小的宫殿，提醒皇帝把江山社稷放在第一位。
-- **交泰殿**：内放25块传国玉玺。
-- **坤宁宫**：皇后住所，明朝所有皇后都住于此。东北角文创店有5枚免费印章。
-- **储秀宫**：慈禧住了20多年的地方，其子在此出生，现为慈禧五十大寿时期原状陈列。旁边文创店有3枚免费印章。
-- **翊坤宫、永寿宫与太极殿**：永寿宫西边是东西六宫中唯一被称为“殿”的太极殿。
-- **慈宁宫与寿康宫**：慈宁宫是康熙为奶奶孝庄皇太后修建的养老院，旁边寿康宫是甄嬛（原文如此）居住之处。
-- **冰窖书吧**：内有3枚免费印章，盖章时有批折子的感觉。
-- **断虹桥**：桥上有形态各异的石狮子，最有名的是“武当狮”（原文如此）。往西是武英殿，后改为陶瓷馆，目前关闭。
-- **文华殿**：位于东边，与西边武英殿对应文东武西。主讲人去时未开，据说现有一个展览。
-- **箭亭**：清朝皇帝及其子孙练习骑马射箭的地方，旁边商店可买到文创雪糕。
-- **钟表馆**：展示那个年代的钟表造型。
-- **珍宝馆（宁寿全宫）**：乾隆给自己修建的养老院，退休后未放权仍照常上朝。皇极殿1:1复刻乾清宫，宁寿宫对标坤宁宫，乐寿堂是故宫唯一能进去参观的皇家寝室，内有二龙戏珠（原文作“二龙仙楼”）设计。出口右手边商店有3枚免费印章。
-- **九龙壁**：我国现存三座古代九龙壁之一。左边数第三条白色龙下边有一块木头，因当年烧制琉璃砖瓦时弄坏一块，工匠为保命用木头刷白漆以假乱真。
-- **珍妃井**：当年慈禧把珍妃丢进去的地方，现上头放的叫井口石，珍妃不是从那个小眼进去的。
-- **东筒子夹道**：长长的夹道，拍照非常出片。
-- **延禧宫与景仁宫**：延禧宫是网红打卡地，景仁宫是甄嬛被封为熹妃时住的，珍妃也住过。
-- **御花园与钦安殿**：钦安殿供奉真武大帝，紫禁城靠山景山从天上看酷似闭目盘坐的人像，有人说此造型就是真武大帝。
-- **神武门**：故宫北门，出门左手边有角楼咖啡（2枚免费印章）和故宫文创（2枚免费印章）两个盖章点。
-# 互动与体验
-## 盖章与文创体验
-- **汉字馆（保和殿东北角）**：提供4枚免费印章，可购买《紫禁城100》并现场盖章，据称印章数量为故宫各店最多。
-- **紫禁城100购买规则**：故宫不止一处可购买，每家店印章不同，购买后不能去其他店铺盖章，需有所取舍；盖完后可选择邮寄到家或自行携带。
-- **坤宁宫东北角文创店**：提供5枚免费印章。
-- **储秀宫边文创店**：提供3枚免费印章。
-- **冰窖书吧**：提供3枚免费印章，主讲人评价印章造型好，盖章时有「批折子」的感觉，在此购买了冰溪图。
-- **珍宝馆出口商店**：提供3枚免费印章。
-- **神武门角楼咖啡**：提供2枚免费印章。
-- **神武门故宫文创店**：提供2枚免费印章。
-## 互动与打卡体验
-- **铜狮子合影提醒**：太和门门口铜狮为故宫六对铜狮中最大一对，造型威武、脚踩寰宇象征权力，但站在其下拍照时爪子会盖在头顶，主讲人建议单独给狮子拍照即可。
-- **断虹桥找狮子**：桥上有形态各异的石狮子，其中最有名的是「武当狮」，主讲人提示游客可自行寻找其位置。
-- **延禧宫与景仁宫打卡**：延禧宫为网红打卡地，景仁宫是甄嬛被封熹妃时所住、珍妃也曾居住，适合打卡。
-- **寿康宫打卡**：慈宁宫旁为甄嬛居住的寿康宫，喜欢看《甄嬛传》的游客可到此打卡。
-- **东筒子夹道拍照**：珍宝馆出口后的长夹道，主讲人表示很多小姐姐喜欢来此拍照，非常出片。
-- **文创雪糕**：箭亭旁商店可购买文创雪糕，主讲人提问雪糕造型人物是谁，邀请观众在评论区分享。
-- **乐寿堂参观**：故宫内唯一能进去参观的皇家寝室，可见二龙仙楼设计，主讲人提示会联想到恭王府和珅的卧室。
-- **珍妃井说明**：井口现放的是井口石，珍妃并非从那个小眼进去的。
-## 个人感受
-- **珍宝馆观感**：馆内宝贝每一样都令人惊叹，但游客非常多，尤其是看凤冠的区域，没点技术挤不进去。
-- **钟表馆观感**：看到那个年代的钟表造型，主讲人表示「真是开了眼了」。
-- **御花园对比**：有游客认为御花园比不过和珅家的后花园，主讲人将此作为开放式问题请观众选择。
-# 收获与建议
-## 知识收获
-- **午门规制**：午门有明三暗五的门洞，中间正门仅供皇帝通行，皇后大婚时可进一次，殿试前三名（状元、榜眼、探花）可出一次；明朝皇帝在此杖打犯错大臣，清朝皇帝在此颁发第二年历书（颁朔之礼）。
-- **太和门与太和殿**：太和门是明朝御门听政（上朝）的地方，门口铜狮子为故宫六对铜狮中最大的一对；太和殿是举行皇帝登基、皇后册封等盛大典礼的场所，文武百官在太和殿广场按文东武西站位。
-- **中和殿与保和殿**：中和殿是盛大典礼时皇帝的休息室；保和殿自乾隆五十四年起成为殿试考场。
-- **乾清门与乾清宫**：乾清门东边是九卿直房，西边是军机处，门口狮子耳朵耷拉、眉毛遮眼，警示后宫之人不该看的不看、不该听的不听；乾清宫是皇帝寝宫，内有27张龙床以防刺客，正大光明牌匾后藏立储诏书，皇帝驾崩后与另一份诏书对比验证真伪。
-- **交泰殿与坤宁宫**：交泰殿内放25块传国玉玺；坤宁宫为皇后住所，明朝所有皇后均居于此。
-- **储秀宫与慈宁宫区域**：储秀宫是慈禧住了20多年的地方，其儿子在此出生，现为慈禧五十大寿时期原状陈列；慈宁宫是康熙为奶奶孝庄皇太后修建的养老院，旁边寿康宫为甄嬛居住地。
-- **珍宝馆区域**：珍宝馆即宁寿全宫，是乾隆给自己修建的养老院，退休后未放权仍照常上朝；皇极殿1:1复刻乾清宫，宁寿宫对标坤宁宫，乐寿堂是故宫唯一能进去参观的皇家寝室，内有二龙仙楼设计；珍妃井现放井口石，珍妃并非从那个小眼进去。
-- **九龙壁细节**：九龙壁为我国现存三座古代九龙壁之一，左边数第三条白色龙下边有一块木头，因当年烧制琉璃砖瓦时弄坏一块，工匠为保命用木头刷白漆以假乱真。
-- **其他知识**：体仁阁是缎库，弘义阁是银库（原文称「内库」）；箭亭是清朝皇帝及子孙练习骑马射箭的地方；断虹桥石狮子中武当狮最有名；御花园钦安殿供奉真武大帝，与景山酷似闭目盘坐人像的造型相呼应。
-## 游览建议
-- **三条路线**：第一条走完所有景点，适合待一整天，主讲人一天走了3万步；第二条中轴线后看景仁宫、延禧宫、钟表馆、珍宝馆，半天逛完；第三条中轴线后看储秀宫、御花园，从神武门出，约2小时。
-- **错峰建议**：建议早起排队，进门后往里冲，可错开大批旅游团人群，在人少时逛完最重要景点。
-- **盖章建议**：故宫内共七个免费盖章点，汉字馆印章数量最多；紫禁城100每家店印章不同，购买后不能去其他店铺盖章，需有所取舍。
-- **参观提示**：珍宝馆虽名为馆但不是单独展厅，院子周围屋子都值得参观，凤冠展品游客多需技术才能挤进去；武英殿陶瓷馆目前关闭，文华殿据称有展览可关注；游览过程中需适当休息和补充水分。</t>
+          <t># 故宫保姆级游览攻略讲解
+## 参观概况
+本次参观为故宫博物院，由导游以视频讲解形式进行，围绕故宫中轴线及东西两路主要景点展开，系统介绍其历史功能与建筑特色。讲解从午门开始，涵盖太和门、太和殿、中和殿、保和殿、乾清门、乾清宫、交泰殿、坤宁宫、储秀宫、慈宁宫、珍宝馆、御花园等核心区域，并穿插明三暗五门洞结构、文东武西站位、正大光明牌匾立储诏书等历史典故。导游同时推荐三条游览路线，分别适合全天、半天及约2小时的最省力行程，并标注全故宫七个免费盖章点，包括汉字馆、坤宁宫文创店、储秀宫旁文创店、冰窖书吧、珍宝馆出口商店及神武门外两处，各点印章数量与规则不同。整体过程以游览动线为序，兼顾历史讲解、文创体验与实用攻略。
+## 核心看点与讲解
+1. **午门**：故宫入口，明朝皇帝在此杖打犯错大臣，清朝皇帝在此行颁朔之礼。门洞呈明三暗五结构，中间正门仅供皇帝通行，皇后大婚时可入一次，殿试前三名（状元、榜眼、探花）可出一次，两侧门洞走皇亲国戚与文武百官。
+2. **太和门广场**：眼前有五座金水桥，中间桥供皇帝行走，挨着中间的两座桥供黄金国器（原文如此）行走，最边上的桥供文武百官行走。太和门为明朝皇帝御门听政（上朝）之处，门口铜狮子为故宫六对铜狮中最大的一对，脚踩寰宇，象征权力。
+3. **太和殿**：即金銮殿，但并非上朝之处，而是举行盛大典礼之地，如皇帝登基、皇后册封。文武百官在太和殿广场朝拜，站位遵循文东武西——文官站东边，武官站西边。西侧弘义阁为皇帝银库，东侧体仁阁为缎库（原文如此）。
+4. **中和殿**：举行盛大典礼时皇帝的休息室，文武百官站好后皇帝再前往太和殿。
+5. **保和殿**：自乾隆五十四年起为科举考试殿试考场。东北角有汉字馆，内有4枚免费印章，可购买《紫禁城100》现场盖章，据称此处印章数量最多；故宫内多处可购此书，但印章不同且不能跨店盖章。
+6. **乾清门**：过此门即后宫生活区域。皇帝在此上早朝，东边九卿直房为等级高的大臣等待召见之处，西边为军机处。门口铜狮耳朵耷拉、眉毛遮眼，警示后宫之人不该看的别看、不该听的别听。
+7. **乾清宫**：皇帝寝宫，内有27张龙床，据说是为防止刺客找到皇帝位置。正大光明牌匾后藏皇帝立储诏书，皇帝写两份诏书，驾崩后对比验证是否被动过手脚。门口有铜鹤铜龟及社稷江山金殿——紫禁城最小宫殿，提醒皇帝将江山社稷放在第一位。
+8. **交泰殿**：内放25块传国玉玺。
+9. **坤宁宫**：皇后居所，明朝所有皇后均住于此。东北角文创店有5枚免费印章。
+10. **储秀宫**：慈禧太后居住20多年之地，其子在此出生，现为慈禧五十大寿原状陈列。旁边文创店有3枚免费印章。
+11. **慈宁宫与寿康宫**：慈宁宫为康熙为奶奶孝庄皇太后修建的养老院；寿康宫为甄嬛（原文如此）居住地。旁边冰窖书吧有3枚免费印章，盖章时有批折子之感。
+12. **断虹桥与武英殿**：断虹桥上有形态各异的石狮子，最有名的为武当狮（原文如此）。武英殿后改陶瓷馆，目前关闭，只能在门口观看。
+13. **文华殿**：位于东边，与西边武英殿对应文东武西。导游去时未开，据称现有一个展览。
+14. **箭亭**：清朝皇帝及子孙练习骑马射箭之处，旁边商店可购买文创雪糕。
+15. **钟表馆**：展示古代钟表造型。
+16. **珍宝馆**：即宁寿全宫，乾隆为自己修建的养老院，退休后未放权仍照常上朝。馆前有我国现存三座古代九龙壁之一，左边数第三条白龙下方有一块木头，据传为当年烧制琉璃砖瓦弄坏后工匠以木刷白漆以假乱真。皇极殿1:1复刻乾清宫，宁寿宫对标坤宁宫，养性殿后为乐寿堂——故宫唯一可进入参观的皇家寝室，内有二龙戏珠（原文如此）设计。珍妃井为当年慈禧将珍妃丢入之处，现井口石非珍妃坠入之口。出口右手边商店有3枚免费印章。
+17. **东筒子夹道与延禧宫**：东筒子夹道为拍照出片之地；延禧宫为网红打卡地，旁边景仁宫为甄嬛封熹妃时所住，珍妃也曾居住。
+18. **御花园与神武门**：御花园内有钦安殿，供奉真武大帝，与北边景山酷似闭目盘坐人像的造型相呼应。神武门为故宫北门，出此门游览结束。
+## 互动与体验
+1. **午门排队检票**：导游建议早点过来排队，排队检票处即午门，可顺带听讲解午门历史与「明三暗五」门洞结构。
+2. **太和门铜狮合影提醒**：门口铜狮子为故宫六对铜狮中最大的一对，造型威武、脚踩寰宇，象征权力。导游提醒不要站在狮子底下合影，因大爪子正好盖在头顶上，建议单独给狮子拍照即可。
+3. **汉字馆盖章体验**：保和殿东北角汉字馆有4枚免费印章，可现场购买《紫禁城100》并盖章，导游形容盖章感觉「真是盖了帽了」，并调侃乾隆喜欢盖章。据导游介绍，汉字馆印章数量为故宫各店中最多，购买后不能去其他店铺盖章，可选择邮寄到家或随身带走。
+4. **坤宁宫文创店盖章**：坤宁宫东北角文创店有5枚免费印章，导游提醒别错过。
+5. **储秀宫文创店盖章**：储秀宫边上有文创店，可免费盖章，共3枚免费印章。
+6. **冰窖书吧盖章与购物**：冰窖书吧内有3枚免费印章，导游称印章造型好，盖章时有「批折子」的感觉。导游本人已买过《紫禁城100》，在此又买了一个冰溪图。
+7. **断虹桥找石狮**：断虹桥为网红打卡地，桥上有形态各异的石狮子，其中最有名的是「武当狮」，导游邀请游客找一找它在哪。
+8. **箭亭文创雪糕**：箭亭旁商店可买到文创雪糕，导游提问雪糕造型是谁，邀请观众在评论区分享。
+9. **珍宝馆参观体验**：导游强烈建议参观珍宝馆，馆内宝贝「每一样都能让您忍不住说出平时常用的感叹词」，但游客非常多，尤其是看凤冠的区域「没点技术还真挤不进去」。
+10. **乐寿堂参观**：乐寿堂是故宫里唯一能进去参观的皇家寝室，可看到二龙仙楼的设计，导游提示会联想到恭王府和珅的卧室。
+11. **珍妃井打卡**：珍妃井为当年慈禧把珍妃丢进去的地方，导游特别说明现在上头放的是井口石，珍妃不是从那个小眼进去的。
+12. **珍宝馆出口商店盖章**：从珍宝馆出口出来右手边往里走有商店，可免费盖章，共3枚免费印章。
+13. **东筒子夹道拍照**：珍宝馆出口外的东筒子夹道是很多小姐姐喜欢来拍照的地方，导游称「拍照非常出片」。
+14. **延禧宫打卡**：延禧宫为网红打卡地，旁边是景仁宫，当年甄嬛被封熹妃时住过，珍妃也住过此地。
+15. **慈宁宫与寿康宫打卡**：慈宁宫为康熙给奶奶孝庄皇太后修建的养老院，旁边寿康宫是甄嬛居住的地方，导游提醒喜欢看《甄嬛传》的游客别忘了到此打卡。
+16. **神武门外盖章点**：出神武门后，左手边有两个盖章点——角楼咖啡有2枚免费印章，故宫文创内同样有2枚免费印章。
+## 收获与建议
+1. **午门门洞规制**：午门正面看有三个门洞，进门后变为五个门洞，即“明三暗五”；中间正门仅供皇帝通行，例外为皇后大婚时可进一次、殿试前三名（状元、榜眼、探花）可出一次，两侧门洞供皇亲国戚和文武百官行走。
+2. **太和门与铜狮**：太和门为明朝皇帝御门听政（上朝）之所；门口铜狮为故宫六对铜狮中最大的一对，脚踩寰宇象征权力，建议单独拍照而非站在其下合影。
+3. **太和殿功能与百官站位**：太和殿是举行皇帝登基、皇后册封等盛大典礼之地，并非日常上朝处；文武百官在太和殿广场朝拜时按“文东武西”站位，文官在东、武官在西。
+4. **中和殿与保和殿**：中和殿为盛大典礼前皇帝的休息室；保和殿自乾隆五十四年起为殿试考场。
+5. **乾清宫与立储制度**：乾清宫为皇帝寝宫，内有27张龙床，据说是为防止刺客找到皇帝位置；殿内“正大光明”牌匾后藏有皇帝立储诏书，皇帝另写一份，驾崩后两份对比以防篡改。
+6. **交泰殿与坤宁宫**：交泰殿内放有25块传国玉玺；坤宁宫为皇后居所，明朝所有皇后均住于此。
+7. **储秀宫与慈禧**：储秀宫为慈禧太后居住20多年之地，现为慈禧五十大寿原状陈列；慈禧喜欢此处因其子在此出生。
+8. **慈宁宫与寿康宫**：慈宁宫为康熙为祖母孝庄皇太后修建的养老院；寿康宫为甄嬛（剧中人物）居住地，喜欢《甄嬛传》的游客可打卡。
+9. **珍宝馆与宁寿全宫**：珍宝馆实为宁寿全宫，是乾隆为自己修建的养老院，乾隆退休后未放权仍照常上朝；皇极殿为1:1复刻乾清宫，宁寿宫对标坤宁宫。
+10. **乐寿堂与珍妃井**：乐寿堂为故宫唯一可进入参观的皇家寝室，内有二龙戏珠设计；珍妃井为当年慈禧将珍妃丢入之处，现井口石非珍妃进入的原口。
+11. **九龙壁与木块秘密**：珍宝馆门口为我国现存三座古代九龙壁之一，左边数第三条白龙下方有一块木头，据说是烧制琉璃时弄坏一块，工匠为保命用木头刷白漆以假乱真。
+12. **游览路线建议**：建议早到排队，进门后先沿中轴线冲重要景点以错开旅游团人群；三条路线分别为——走完所有景点适合全天（导游本人走约3万步）、中轴线至坤宁宫后逛景仁宫/延禧宫/钟表馆/珍宝馆再出神武门约半天、中轴线至坤宁宫后去储秀宫/御花园出神武门约2小时最省力。
+13. **免费盖章点汇总**：全故宫共七个免费盖章点——保和殿东北角汉字馆4枚、坤宁宫东北角文创店5枚、储秀宫旁文创店3枚、冰窖书吧3枚、珍宝馆出口商店3枚、神武门外角楼咖啡2枚、故宫文创2枚。
+14. **紫禁城100购买与盖章规则**：故宫内多家店可购买《紫禁城100》，每家店印章不同，且购买后不能去其他店铺盖章，需有所取舍；汉字馆印章数量最多，可现场盖章后邮寄到家或自行带走。</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>40</v>
+        <v>40.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4497/3780</t>
+          <t>4497/3966</t>
         </is>
       </c>
     </row>
@@ -7221,60 +7229,55 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t># 访谈概况
-本次访谈围绕农村与城市留守老人养老问题展开，由主持人实地走访村政府、民政局及城市社区，访谈对象包括民政干部、村干部、社区社工及多位农村留守老人。访谈目的是了解留守老人养老现状与困境，并探讨解决养老问题的可行路径。核心议题覆盖独居老人生活困境、农村养老政策现状、城市社区养老志愿服务经验及社工制度困境。整体反馈基调呈现为：农村老人普遍反映子女外出打工、无人陪伴，经济与就医困难突出；基层干部坦言地方财政困难、养老设施运营经费不足；城市社工则指出行业工资低、人才流失严重、服务难以持续。
-# 核心反馈
-## 农村留守老人
-- **独居比例高**：2021社区居家养老现状与未来趋势报告显示，65.5%的老人子女长期不在身边，仅26.8%与子女同住。
-- **孤独求助**：黑龙江绥滨一位独居老奶奶因寂寞报警，承认“因为自己一个人在家太寂寞，所以想找个人聊聊天”。
-- **去世多日才被发现**：上海一名67岁独居老人去世多日，家中溢出刺鼻气味才被邻居发现；杭州一小区67岁独居老人同样去世数天后才被发现。
-- **子女外出务工**：受访老人用方言描述现状，“80%都是都提醒在这个外面做做这些事的，年轻人都卖出去了”，家中无人照料。
-- **就医困难**：一位视障老人说出自己在就医上遇到的障碍。
-- **经济困难**：民政局干部指出当地老人“经济比较困难”，“这个地方经济不太发达”，生病住院“比较麻烦”。
-- **娱乐方式少**：民政局干部提到老人“娱乐方式少，这个就坐在一起聊聊天啊，打打牌呀”。
-## 农村养老政策执行者（村政府、民政局）
-- **养老设施运营经费断档**：民政局干部表示曾探索在农村建养老公共设施，提供日托、休闲娱乐、沟通交友平台，“但是不是那种一次性的投入，地方财政都很困难，这种运营经费后续就没有支持的”。
-- **养老金偏低**：村政府干部反映60岁以上农村老年人每月养老金118元，“还要提高一点”，并指出“农村的养老金跟工人的养老金待遇完全一样，但现在的老年人公平”。
-- **上门服务有限**：村政府干部表示靠村支两委、志愿者“敲门敲到那去串串门宣传政策”，但“所有上门服务的都上门的，入户签约的，只有一个，还有的有的是没一个都没有”。
-- **五保户供养标准**：分散供养五保户每月发475元生活费，另有护理补贴；集中供养则将生活护理补贴直接发给敬老院护理人员。
-- **残疾人低保标准**：一级二级残疾人纳入最低生活保障，标准分160、270、380元三档，视家庭状况而定。
-## 城市社区社工
-- **志愿者一对一帮扶**：社区给志愿者划分一对一帮扶对象，“比如我们这个志愿者，我们会发现这个老人就住在你们家楼下，经过他家门口上下楼的时候，那我就天天都去看了”。
-- **志愿者激励**：年底志愿者可在雷锋超市兑换礼品，通过表彰和积分兑换让志愿者“能够长期的也坚持的做下来”。
-- **带动家长参与**：今年开展“小手拉大手”活动，从儿童青少年入手，“让他们能够拉动自己的家长也加入到我们这边来”。
-- **心理问题老人案例**：社工曾帮助一位与邻里关系不和谐、半夜摔门的老人，老人抗拒上门帮助，“我不需要你的关心……他总觉得周围的人都是陌生的，没有关心他的人”，经长期照料后“与邻里之间的关系也还算好了”。
-- **社工工资低**：社工行业“工资都比较低嘛，所以会影响他的一个就业率”，“基本上很多同学就没做多久，基本上都垮了，可能不超过一年”。
-- **项目资金不稳定**：社工服务“需要花钱购买服务的，所以说不一定能够今年服务了，明年又能服务”，项目结束资金拨不下来，“服务成效不一定就达到了”。
-- **社工专业性欠缺**：湖南省每个街道花费十来万，省里拨了钱，但“很多的社工并不是专业的，学社工专业出来的……在专业上其实还是很欠缺的”。
-- **驻点社工难以持续**：每个街道和乡镇派两名社工驻点，围绕老人小孩服务，“但是可能说实在话也很难能够走下来”。
-# 关键洞察与建议
-## 农村养老困境的成因与对策
-- **子女外出务工与老人适应能力下降叠加**：受访老人反映村里80%年轻人都外出打工，子女经济压力大、老人适应能力降低，多重因素叠加使留守老人群体愈发庞大。这支持判断：农村养老问题的根源在于劳动力外流与家庭照料功能弱化，单纯增加补贴难以根本解决。
-- **农村养老设施“建得起、养不起”**：当地曾探索在农村建设养老公共设施，提供日托、休闲娱乐、沟通交友平台，但地方财政困难，运营经费后续没有支持。这支持判断：养老设施建设需同步规划持续运营经费，否则难以发挥实效。
-- **农村养老金与工人待遇差距引发公平性质疑**：受访干部指出农村老年人每月养老金118元，但60年代的人结婚、砍树、杀猪都要交费，农村养老金与工人养老金待遇完全一样，现在的老年人不公平。这支持判断：提高农村养老金水平是基层干部的明确诉求。
-## 受访者提出的养老改善建议
-- **专业陪伴与亲情联系并重**：民政局受访者建议请专业施工人员进行陪伴，同时倡导在外务工子女多与老人联系。
-- **丰富文化生活与固定活动场地**：建议丰富老人文化生活、增加娱乐方式，希望老年协会专项执行、专门建设养老设施，有固定场地定期开展板报宣传、健康知识讲座等活动。
-- **运营经费须纳入规划**：受访者强调养老设施不仅要考虑建设，还要考虑后续持续运营经费，才能更好发挥作用。
-- **敲门行动与党员带头**：村政府受访者介绍靠村支两委和志愿者开展敲门行动，串门宣传政策、搞卫生，每月利用党员组织会下午到孤寡老人、留守老人家里走一圈。
-## 城市社区养老经验的可借鉴之处
-- **志愿者就近帮扶机制**：社区为志愿者划分一对一帮扶对象，志愿者发现老人住在自家楼下便天天探望，老人身体不好时送菜上门，通过定期表彰和志愿者积分兑换（年底可在雷锋超市兑换礼品）维持志愿者积极性。这支持判断：就近帮扶降低了志愿服务成本，积分兑换等激励措施有助于志愿者长期坚持。
-- **以儿童带动家庭参与**：今年开展“小手拉大手”活动，从儿童青少年入手拉动家长加入志愿服务；本周四将开展送春联活动，邀请书法老师写对联，由孩子们上门送给老人；去年中秋开展做月饼活动，还做过百家宴。这支持判断：代际参与既能传承尊老传统，又能扩大志愿者队伍。
-- **活动组织权逐步移交居民**：此前活动均由社区策划开展，2023年目标是家长自己组织活动，社区转为协助者角色。这支持判断：培育居民自组织能力是社区养老活动可持续的方向。
-- **心理问题老人需专业介入**：社工曾帮助一位与邻里关系不和谐、半夜摔门、抗拒外界关心的老人，单纯上门探访无法解决其心理问题，经日复一日关心照料后老人逐渐好转，能接受意见并主动来电。这支持判断：部分老人心理问题超出普通志愿服务能力范围，需要专业心理支持。
-## 社工制度困境与改进方向
-- **工资低导致人才流失**：社工行业迅速发展但工资较低，影响就业率，很多社工专业同学做不超过一年就转行。这支持判断：提高社工待遇是稳定队伍的关键。
-- **项目资金不稳定影响服务连续性**：社工服务需花钱购买，项目资金拨不下来项目就结束，今年服务了明年不一定能继续，一年服务成效并不明显。这支持判断：资金来源单一且不稳定，制约了服务成效的积累。
-- **专业能力欠缺**：湖南省每个街道花费十来万，省里拨了钱，但很多社工并非社工专业出身，专业上很欠缺。这支持判断：在增加投入的同时需加强社工专业培训与资质要求。
-- **服务领域分散影响专注度**：社工服务领域较多，这次做留守儿童、下次做留守老人，专注力不集中，且能否继续服务取决于领导能否争取到项目。这支持判断：服务领域频繁切换不利于形成专业积累。</t>
+          <t># 留守老人养老问题调研与对策探讨
+## 访谈概况
+本次访谈以记者实地走访的形式展开，围绕农村留守老人养老问题，先后采访了村民、村干部、民政局干部及城市社区社工。调研数据显示，65.5%的老人子女长期不在身边而独居，仅26.8%与子女同住；独居老人普遍面临无人照料、就医困难、孤独等问题，并出现独居老人因寂寞报警、去世多日才被发现等极端案例。农村方面，村干部介绍了五保户分散供养每月475元生活费及护理补贴、残疾人低保三档标准（160/270/380元）、60岁以上老人每月118元养老金等政策现状，并指出农村养老金与工人养老金待遇不同、养老设施运营经费缺乏后续支持等问题。城市方面，社区社工介绍了志愿者一对一帮扶、积分兑换、小手拉大手、送春联、百家宴等活动经验，以及养老服务中心的理疗、心理咨询等服务；同时反映了社工工资低、流动性大、专业性欠缺、项目资金不稳定等行业困境。整体反馈基调为：留守老人养老问题严峻，农村政策保障有限，城市经验可资借鉴，但社工行业可持续发展面临挑战。
+## 核心反馈
+### 留守老人生活现状与困境
+- **独居比例高**：2021年社区居家养老现状与未来趋势报告显示，65.5%的老人子女长期不在身边而独居，仅26.8%与子女同住；独居老人普遍存在无人照料、无人慰藉、就医困难等问题，甚至可能独自在家发生意外。
+- **极端案例**：黑龙江绥滨一位独居老奶奶因独自在家太寂寞，报警谎称有人敲门，只为找人聊天；上海、杭州各有一名67岁独居老人去世多日、家中散发刺鼻气味后才被邻居发现。
+- **村民反映子女外出**：多位村民表示村里年轻人大多外出打工，老人无人照看；有村民提到“80%都是在外做事的，年轻人都卖出去了”。
+- **视障老人就医障碍**：一位视障老人向调研者说出了自己在就医上遇到的障碍。
+### 农村养老政策与实施情况
+- **老龄化数据**：村干部称，从公安了解到的数据是2021年当地73万多老人、约占17.8%，且因1962—1965年职工档案出生的人多、去年开始退休，老龄化程度会越来越严重，估计目前至少有两三万（独居老人）。
+- **五保户供养**：无收入来源、无法定赡养人和劳动能力的“三无人员”可自愿到敬老院集中供养，生活护理补贴直接发给敬老院护理人员，生活费直接发给敬老院；分散供养的五保户每月发475元生活费，另有护理补贴。
+- **五保户补贴合计**：民政局干部补充，五保户每月另有食补电补，加起来约600元，农村生活艰苦，五六百元基本能满足，但“大吃大喝也不行”。
+- **残疾人低保**：一级二级残疾人按国家政策纳入最低生活保障，按家庭状况分160、270、380元三个标准，最起码保证其最低生活保障。
+- **农村养老金**：60岁以上农村老年人每月118元，民政局干部指出农村养老金与工人养老金待遇完全不一样，但“现在的老年人公平”——因60年代的人结婚、砍树、杀猪都要交费。
+- **党员活动上门服务**：靠村支两委和志愿者“敲门串门”宣传政策、搞卫生；每月开一次党员组织会，上午开会、下午搞活动或大扫除，到孤寡老人、留守老人家里走一圈。
+- **上门服务覆盖不足**：民政局干部提到“所有上门服务的都上门的，入户签约的只有一个，还有的有的没一个都没有”。
+### 城市社区养老经验
+- **志愿者一对一帮扶**：社区前几年给志愿者划分一对一帮扶，如志愿者发现老人住在自家楼下，上下楼时天天去看望，老人身体不好时天天送菜。
+- **志愿者激励**：定期表彰或志愿者积分兑换，年底志愿者可到雷锋超市兑换礼品，让志愿者能长期坚持。
+- **小手拉大手**：今年从儿童青少年着手，让孩子拉动家长加入志愿者队伍；本周四将开展送春联活动，邀请书法老师写对联，由孩子们上门送给老人家。
+- **社区活动**：去年中秋开展做月饼活动，还做过百家宴，让老人感觉社区就是大家庭；2023年目标是家长自己组织活动，社区转为协助者。
+- **养老服务中心**：每个社区成立养老服务中心，提供理疗、按摩、老年大学、心理咨询等服务。
+- **心理问题老人案例**：社工曾帮助一位与邻里关系不和谐、半夜摔门的老人，老人抗拒上门帮助，觉得“周围的人都是陌生的，没有关心他的人”；经日复一日关心照料，老人心理问题逐渐好转，与邻里关系改善，能接受意见，但今天仍打电话说“寂寞空虚，得不到人关注”。
+### 社工行业困境
+- **驻点配置与流失**：每个街道和乡镇派两名社工驻点，主要服务老人和小孩，但“很难能够走下来”；社工工资低，影响就业率，很多同学做不超过一年就转行。
+- **资金不稳定**：社工服务需花钱购买，项目资金不稳定，不一定今年服务了明年还能服务，要看领导能否争取到项目；一年服务成效不明显，资金拨不下来项目就结束，但服务成效不一定达到。
+- **专业性欠缺**：湖南省每个街道花费十来万，省里虽拨了钱，但很多社工并非社工专业出身，专业上很欠缺；长沙社工机构服务领域多，社工专注力分散。
+&gt; “寂寞空虚，得不到人关注一样的。其实老人可能到了这个时候，确实还是很需要爱的。”
+&gt; —— **社工（社区）** ｜ 谈及曾帮助的心理问题老人
+## 关键洞察与建议
+1. **留守老人困境成因多元**：子女外出打工、经济压力大、老人适应能力降低及城市对农村老人的无形歧视多重叠加，导致留守老人群体愈发庞大；独居老人普遍存在无人照料、就医困难、孤独等问题，甚至出现因寂寞报警、去世多日才被发现等极端案例，反映出该群体亟需社会关注与制度性支持。
+2. **农村养老保障水平偏低**：五保户分散供养每月475元生活费加护理补贴，残疾人一二级纳入低保分160、270、380元三档，60岁以上农村老人每月118元养老金；民政局干部指出农村养老金与工人养老金待遇完全不同，老人公平性存疑，现有保障仅能维持基本生活，难以覆盖医疗等额外支出。
+3. **农村养老设施运营经费断档**：村干部表示此前探索过在农村建设养老公共设施，提供日托、休闲娱乐、沟通交友平台，但地方财政困难，一次性投入后运营经费无后续支持，设施难以持续发挥作用；建议在建设之外必须考虑持续运营经费，才能更好发挥作用。
+4. **村干部提出四项改善建议**：一是请专业人员陪伴老人；二是倡导在外务工子女多与老人联系；三是丰富老人文化生活、增加娱乐方式；四是希望老年协会专项执行，专门建设养老设施，提供固定场地，定期开展板报宣传或健康知识讲座，并保障持续运营经费。
+5. **城市社区志愿者制度可资借鉴**：社区为志愿者划分一对一帮扶对象，志愿者就近关注楼下老人，身体不好时天天探望送菜；通过定期表彰和志愿者积分兑换（年底可到雷锋超市兑换礼品）激励志愿者长期坚持，形成可持续的互助机制。
+6. **社区活动带动代际参与**：今年开展“小手拉大手”活动，从儿童青少年入手拉动家长加入志愿者队伍；本周四将开展送春联活动，邀请书法老师写对联、孩子们上门送给老人；去年中秋开展做月饼活动，还举办过百家宴，让老人感受到社区大家庭氛围；2023年目标是家长自行组织活动，社区转为协助者。
+7. **社工行业供给不足且专业性欠缺**：每个街道和乡镇仅派两名社工驻点，服务老人和小孩；社工工资低，很多同学做不超过一年就转行；社工服务需花钱购买，项目资金不稳定，湖南省每个街道花费十来万，省里虽拨了钱，但项目结束后服务成效未必达成；很多社工并非专业出身，专业性欠缺，影响服务质量和行业长期发展。
+8. **心理问题老人需专业介入而非简单上门**：社工曾帮助一位与邻里关系不和谐、半夜摔门的老人，单纯上门服务遭抗拒，老人觉得周围人陌生、无人关心，内心有仇恨情绪；经日复一日关心照料后，老人与邻里关系好转、能接受意见，社工认为老人到了这个阶段确实很需要爱，心理问题需要持续专业陪伴而非一次性服务。
+9. **社工服务领域分散影响专注度**：社工服务领域多，这次做留守儿童、下次做留守老人，专注力不集中；服务需花钱购买，能否持续取决于领导能否争取到项目，一年服务成效并不明显，资金拨不下来项目就结束，但服务成效不一定达成。
+10. **解决养老问题需多方协同**：记者总结认为，解决养老问题绝非易事，不仅需要政府关心重视，也离不开子女、社区乃至更专业养老服务机构的耐心陪伴与关怀，最终愿景是让每位老人病有所医、老有所养、住有所居、弱有所扶。</t>
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>43.3</v>
+        <v>43.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5309/3221</t>
+          <t>5309/3478</t>
         </is>
       </c>
     </row>
@@ -7881,86 +7884,99 @@
       <c r="C22" t="inlineStr">
         <is>
           <t># 沟通概况
-班主任林瑞在372班家长会上，围绕班级基本情况、教师团队、存在问题及解决思路、计划与措施等板块与家长沟通。班级共60人，男生25人、女生35人，学生处于初中阶段，生理心理持续变化；班级优点为时间观念、执行力强，班风班貌纪律良好，缺点是少数同学周末玩手机、懒散，自习课效率低。教师团队多为老教师、优秀教师，班主任林瑞教地理学科。针对个别学生时间观念差、书写不良、玩手机、网瘾、看直播、谈恋爱等问题，班主任提出加强手机管理、家长配合检查、加强班委培训等解决思路，并制定详细班规、严格请假制度等计划。家长代表张宇波分享家庭教育经验，强调关注孩子身心健康、尊重孩子、多倾听交流。会议还沟通了成立家委会、购买保险（约310元）、办理电子学生证（套餐78元）及高中资助政策等事项。
+班主任林瑞主持召开372班家长会，与全体家长沟通班级情况与家校协作事宜。班级共60人，男生25人、女生35人，学生处于初中阶段，生理心理持续变化。班级整体时间观念与执行力强、班风班纪良好，但少数同学存在周末玩手机、懒散、自习课效率低、思考能力较差等问题。教师团队多为老教师和优秀教师，班主任林瑞任教地理学科。针对班级问题，林瑞提出加强人员管理、培训班委、严格手机管理（要求上交手机并贴名，家长周一到周五不定时打电话检查）、建议书写不良学生买字帖练字，并关注学生社交账号以防早恋。后续计划包括每天加强思想教育、制定详细班规、严格请假制度、定期与家长沟通，下次月考在11月初。会议还沟通了保险购买（约310元）、电子学生证办理（移动套餐78元）、高中补助发放方式等事项，并决定成立家长委员会（至少三人，自愿报名）。家长代表张宇波分享家庭教育经验，强调关注孩子身心健康、先做人再学习、尊重孩子、多倾听交流。
 # 沟通内容
-## 班级基本情况与学习表现
-- **亮点**：班级整体时间观念、执行力强，班风班貌纪律良好，卫生干净，班风纪律非常好。
-- **亮点**：学生书写良好，个别学生书写优秀，学生手册、架构书等作业情况良好。
-- **需关注**：少数同学周末玩手机、玩游戏，玩累了后表现懒散，有网瘾倾向。
-- **需关注**：思考能力较差，自习课时班主任在则安静，不在则乱哄哄，效率低。
-- **需关注**：个别学生时间观念差，书写不良，已与家长沟通，建议买字帖练字。
-- **需关注**：有男生充400元生活费用于游戏，班主任提醒家长管理手机。
-- **需关注**：发现学生看直播、不健康内容，班主任提醒家长关注。
-- **需关注**：发现学生谈恋爱，需家长关注QQ、抖音、快手等社交账号。
-- **需关注**：有学生拿镜子照（原文如此），班主任要求全部收掉，涉及约10人。
-## 手机管理
-- **需关注**：要求手机上交，专门一个手机存放箱，每个人名字贴好。
-- **需关注**：有学生有两个手机，家长家中可能有多个手机，班主任要求家长处理多余手机，不要留多的。
-- **需关注**：家长可在周一到周五不定时打电话检查，若电话能打通没人接，说明手机未交。
-- **需关注**：有少数男生有网瘾，星期六晚上充生活费用于游戏，充了400元。
-## 安全教育与心理健康
-- **需关注**：提醒孩子注意交通安全，未满16周岁骑电动车非常危险，会载两三个，实在要骑则自己一个人骑。
-- **需关注**：提醒注意运动安全、饮食安全、防诈骗、防溺水，不能私下和留用（原文如此）。
-- **需关注**：防校园欺凌，学生打电话哭诉或有事，第一时间联系班主任处理。
-- **需关注**：关注学生心理健康，发现异常及时进行心理辅导。
-- **需关注**：提醒孩子合理安排饮食，注意补充营养。
-## 费用与资助
-- **需关注**：书费方面，学生买了5本书，预交了11000块钱，目前还没有结算。
-- **需关注**：外面买的书箱，有学生没有买，到时候会把钱退给进去（原文如此）。
-- **需关注**：相关费用有少数同学可能涉及100左右，没有无效的（原文如此）就70块钱，买4000的700左右、120左右、123左右（原文如此），到时候会报费用。
-- **需关注**：不会在群里收取家长任何费用，需要通知家长交费时由学生交，交给生活委员，不在微信里转钱。
-- **需关注**：提醒家长和学生注意反诈，不要相信群里冒充班主任收费的消息。
-- **需关注**：高中补助打在医保卡上，与初中不同，提醒家长注意补助资金使用，避免学生乱花。
-- **需关注**：保险费用约310元，可自行购买，需统计购买情况。
-- **需关注**：电子学生证套餐78元，移动套餐，方便联系，目前班级有老年机，部分停机，需办理电子学生证。
+## 班级整体表现
+- **亮点**：班级时间观念、执行力强，班风班貌纪律良好，卫生干净。
+- **亮点**：班风班纪良好，周边环境能感受到地面干净。
+- **需关注**：少数同学周末玩手机、懒散，玩累了之后积极表现较差。
+- **需关注**：少数同学（约两三个）手机使用过度，经常在地图上使用（原文如此）。
+- **需关注**：自习课效率低，思考能力较差；班主任在场时纪律好，不在场时乱哄哄。
+- **需关注**：个别学生时间观念差，书写不良，已与家长沟通过，建议买字帖练字。
+- **需关注**：有学生把班级计划写成“172班”（原文如此），书写需加强。
+## 手机与网络管理
+- **需关注**：发现少数男生有网瘾，打游戏；有学生星期六晚上充了400元生活费用于游戏。
+- **需关注**：有男生看直播、看杀人游戏等不健康内容（原文如此）。
+- **需关注**：发现学生谈恋爱，建议家长关注QQ、抖音、快手等社交账号，注意是否被屏蔽。
+- **需关注**：有学生带镜子等物品，要求全部收掉，约10人涉及（原文如此）。
+- **措施**：要求手机上交，每个手机贴名字放入手机箱；家长周一到周五不定时打电话检查手机是否开机，若打通没人接说明未交。
+- **措施**：家长需处理家中多余手机，不要留多部，防止学生拿旧手机上交、留好手机自用。
+## 生活与行为习惯
+- **需关注**：有学生生活费过高，一周400块，可能用于买手机、玩游戏或其他消费。
+- **需关注**：有男生出去过生日，喝酒回来一身酒气还抽烟（原文如此）。
+- **需关注**：有学生向家里谎称没钱，实际把钱花在别处（原文如此）。
+- **教育引导**：班主任曾调查学生是否知道父母生日，只有少数举手，借此教育学生感恩父母。
 # 家长反馈
 ## 家长关注的问题与诉求
-- **费用问题**：班主任说明水费险、书费等费用情况，预交11000元书费尚未结算，未购买书箱的费用将退还，相关费用由学生交给生活委员，不在微信群收取。
-- **手机管理**：班主任要求家长周一到周五不定时打电话检查手机是否上交，家长需处理家中多余手机，避免学生使用。
-- **生活费问题**：班主任提醒家长注意学生生活费使用情况，有学生一周内多次以买资料为由向家长要钱，实际用于其他用途。
-- **社交账号关注**：班主任建议家长关注学生QQ、抖音、快手等社交账号，留意是否存在谈恋爱或浏览不健康内容的情况。
-- **补助资金使用**：班主任提醒家长高中补助打在医保卡上，需关注补助资金是否被学生用于非正常消费。
+- **费用问题**：家长对水费险、书费等费用缴纳方式存在疑问，班主任说明费用由学生交给生活委员，不在微信群收取。
+- **手机管理**：班主任要求家长周一到周五不定时打电话检查孩子手机是否上交，家长需处理家中多余手机，避免孩子藏匿。
+  - 班主任建议家长拨打孩子电话，若无人接听说明手机已上交，若接通则说明未交。
+  - 家长需检查孩子书包，收掉镜子等物品。
+- **生活费使用**：班主任提醒家长关注孩子生活费使用情况，有男生充400元生活费用于游戏，建议家长控制生活费额度，每周不超过150元。
+- **社交账号监管**：班主任建议家长关注孩子QQ、抖音、快手等社交账号，查看是否有早恋迹象或不良内容。
+- **书写问题**：个别学生书写不良，班主任已与家长沟通，建议家长购买字帖让孩子练字。
+- **电子学生证办理**：班主任说明班级目前老年机部分停机，建议家长办理电子学生证（移动套餐78元），方便联系。
+- **保险购买**：班主任说明保险费用约310元，家长可自行购买，需统计购买情况。
 ## 家长原话
 &gt; “无论怎样，那你都是爸爸妈妈心里最优秀的儿子，你先批评他，还是不当，这样的话他会更加的深刻。”
-- 背景：家长代表张宇波在家长会上分享家庭教育经验时，讲述自己与儿子关于批评方式的对话。
+- 背景：家长代表张宇波在家长会上分享家庭教育经验时，讲述自己与儿子关于批评与鼓励的对话。
+&gt; “要想让孩子离开，就要让他们学会怎么样做人，千万不能让他们带上不良的风气。”
+- 背景：家长代表张宇波在家长会上分享家庭教育经验，强调先做人再学习的教育理念。
 # 共识与配合事项
-## 手机与网络管理
-- [ ] **家长**：周一到周五不定时拨打孩子电话，确认手机是否已上交；若电话能打通且无人接听，说明手机未交，需及时处理
-- [ ] **家长**：处理家中多余手机，避免孩子私藏备用机；若发现孩子交旧留新，需一并处理
-- [ ] **家长**：关注孩子`QQ`、`抖音`、`快手`等社交账号，留意是否存在谈恋爱、浏览不健康内容等迹象；若被孩子屏蔽，需注意观察
-- [ ] **家长**：检查孩子书包及随身物品，发现镜子、手机等违禁品及时收走
-- [ ] **班主任**：设置手机收纳箱，要求每名学生将手机贴上姓名后上交
-- [ ] **班主任**：对已发现网瘾倾向的少数男生（有学生一次性充值`400`元用于游戏）加强关注与引导
-## 学习与行为规范
-- [ ] **家长**：查看学生手册中孩子的书写情况，对书写不良的学生，到文具店购买字帖督促练字
-- [ ] **班主任**：加强班委培训，提升自习课管理能力；自习课安排`10`分钟讨论时间，允许学生离座请教问题
-- [ ] **班主任**：继续加强思想教育工作，每日进行
-- [ ] **班主任**：执行详细班规，违规行为按规扣分、写检讨、罚站，严格请假制度，稳定学习秩序
-- [ ] **班主任**：定期与家长沟通学生表现，及时反馈问题
-## 安全与健康
-- [ ] **家长**：提醒孩子注意交通安全，未满16周岁不得骑电动车，尤其禁止载人；如确需骑行须单人骑行
-- [ ] **家长**：提醒孩子注意运动安全、饮食安全，防范诈骗与溺水
-- [ ] **家长**：关注孩子心理健康，发现异常及时寻求心理辅导
-- [ ] **家长**：合理安排孩子生活费（建议每周不超过`150`元），避免过度给钱导致非正常消费
-- [ ] **班主任**：发现校园欺凌等异常情况，第一时间介入处理（此前曾处理过学生深夜矛盾，约谈至凌晨`2`点）
-## 费用与事务办理
-- [ ] **家长**：自愿为孩子购买保险（费用约`310`元），可在学校、菜市场或`阿里巴巴`等渠道自行购买，购买后配合学校统计
-- [ ] **家长**：办理电子学生证（移动套餐`78`元），便于请假联系；班级现有老年机部分停机，需更换
-- [ ] **班主任**：统计保险购买情况，汇总电子学生证办理名单，将新号码发至家长群
-- [ ] **班主任**：说明高中资助政策——补助打入学生医保卡（与初中不同），每次打款后提醒家长确认资金用途，避免学生挪用
-## 家委会与后续安排
-- [ ] **家长**：自愿报名参加家长委员会（至少`3`人），重大事项经班主任与家长探讨通过后实施
-- [ ] **班主任**：组织家委会成立事宜，与家长共同探讨班级重大事项
-- [ ] **班主任**：下次月考预计`11`月初举行，届时请家长关注学生成绩与目标达成情况
-- [ ] **家长**：会后如有需要可前往办理电子学生证等业务（下午`3:20`–`3:25`可安排时间）；培训期间涉及教官着装，请勿拍照发朋友圈或社交媒体</t>
+## 家校共识与育人原则
+- **教育理念共识**：家校共同秉持“没有最好，只有更好”的教学理念，以合作学习、共同进步为学习方式，不以一时成败论英雄，关注班上每一个学生，希望每个孩子都拥有美好前程。
+- **育人目标共识**：家校一致认同要培养孩子成为有理想抱负的人，注重良好道德品质与行为规范的养成，培养良好心理素质，养成严格自律、自主管理的学习作息习惯，让每一个学生都能健康成长。
+- **先做人再学习原则**：家长代表张宇波分享家庭教育经验，强调教育孩子先学会做人，再谈学习，千万不能让孩子沾染不良风气，做人是必修技能。
+- **尊重与倾听原则**：家长应尊重孩子，给孩子自由空间，不轻易下消极评价；多倾听、多交流，帮助孩子面对挫折与失败，让孩子感受到关爱与理解。
+- **平常心教育原则**：家长对待孩子要有平常心，孩子面临的学习压力很大，对挫折和失败要正确看待，帮助孩子重新定位，放下眼前得失，向往更远风景。
+- **家庭环境建设原则**：为孩子创造和睦、祥和、稳定的家庭气氛，尽量不在孩子面前争吵，不聚众在家点外卖或打麻将，不在家里常备零食，不当着孩子面长时间玩手机，减少过多唠叨。
+- **安全教育原则**：家校共同重视学生安全，涵盖交通安全（未满16周岁不骑电动车，不载人）、运动安全、饮食安全、防诈骗、防溺水、防校园欺凌等方面，学生生活无小事，再小的事班主任都要管好教育好。
+- **心理健康关注原则**：学生心理健康是家校共同关注重点，家长发现孩子异常应及时进行心理辅导；家长要在思想上多关注学生，多沟通，及时了解孩子心理动态，适当给压力，多鼓励少批评。
+- **反诈防范原则**：班主任强调家校双方都要注意反诈，班级不会在微信群收取任何费用，收费由学生交给生活委员，提醒家长防范冒充班主任头像的诈骗行为。
+- **生活费合理使用原则**：提醒孩子合理安排生活费，注意饮食营养，避免过度消费；家长不过多给孩子零花钱，防止用于非正常消费。
+## 待办与配合清单
+### 班主任待办
+- [ ] 加强班级人员管理，加强对班委的培训，提升自习课纪律与效率
+- [ ] 制定详细班规，严格执行扣分、检讨、罚站等纪律措施
+- [ ] 严格请假制度，稳定学习秩序
+- [ ] 每天继续加强思想教育工作
+- [ ] 定期与家长沟通，了解学生各方面表现
+- [ ] 组织下次月考（11月初），提醒学生将月考目标写入学生手册
+- [ ] 统计保险购买情况（费用约310元，可自行购买）
+- [ ] 将各科老师电话发到家长群
+- [ ] 将新的电子学生证号码发到群里，供家长重新补充
+- [ ] 将学校资助政策发到家长群供家长查看
+- [ ] 每次补助发放时告知家长金额及用途
+- [ ] 处理班级现有三个座机中已到期（9月20几号到期）的线路，补充可用号码
+- [ ] 安排家长会后续环节（3:20–3:25继续，下午3:30培训）
+### 家长配合待办
+- [ ] 严格手机管理：学生手机上交班级手机箱，每个手机贴好名字，家长周一到周五不定时打电话检查手机是否上交（打通无人接说明未交）
+- [ ] 家长处理家中多余手机，不留多部手机给孩子，防止孩子用备用机
+- [ ] 书写不良的学生，家长在文具店购买字帖让孩子练字
+- [ ] 家长检查孩子书包，收掉镜子等与学习无关的物品
+- [ ] 家长关注孩子QQ、抖音、快手等社交账号，留意是否谈恋爱或浏览不健康内容
+- [ ] 家长关注孩子生活费使用情况，防止充入游戏或非正常消费
+- [ ] 家长关注孩子是否沉迷网络游戏，发现网瘾及时干预
+- [ ] 家长配合学校安全教育：提醒孩子未满16周岁不骑电动车，注意运动、饮食安全，防诈骗、防溺水、防校园欺凌
+- [ ] 家长发现孩子异常情况第一时间联系班主任
+- [ ] 家长自愿报名参加家长委员会（至少三人）
+- [ ] 家长自行购买学生保险（约310元，可在校内、菜市场或阿里巴巴等渠道购买），购买后告知班主任统计
+- [ ] 家长办理电子学生证（移动套餐78元），方便联系孩子
+- [ ] 家长关注高中补助发放（打在医保卡上），与孩子确认补助用途
+- [ ] 家长配合学校资助申请，需要时提供身份证等材料
+- [ ] 培训期间家长不拍照、不发朋友圈（有教官在场不允许拍照）
+- [ ] 家长为孩子制定容易达到的小目标（如年级排名120名到30名范围内），激发潜能
+- [ ] 家长多鼓励少指责，孩子犯错时引导而非批评
+- [ ] 家长关注孩子心理健康，发现异常及时进行心理辅导
+- [ ] 家长与孩子多沟通，了解在校表现，关注思想动态</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>54.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17334/3284</t>
+          <t>17334/3771</t>
         </is>
       </c>
     </row>
@@ -8040,44 +8056,56 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t># 例会概况
-10月28日召开自愿级周会，主题为总结工作，目标是初步统一成员对社区的认识。会议资料包括工作报告、看法和社区介绍。会上确认组建执法队伍为下月主要任务，并讨论了课程开发等四项任务；工作方向被认为有些偏离，需考虑工作量。会议决定将服务定价权交给消费者，采用代购模式；计划组建教育团队，第一步确定路线、修订纲领章程，具体需招聘20多位师傅，但认为人数可能过多。同时修改学习介绍，将“我们是谁”提到最上面，并调整两个镜头的衔接。待遇方面，上班5000元，额外有奖励和提成；休假为周五半天加周末两天。下一步开始邀请同事加入，共同制作解决方案。
-# 工作进展
-## 社区建设与教育项目
-- **组建执法队伍**：确定为下月主要任务，为当前最重要工作；下一步需确定路线并修订纲领章程，时间节点为下月内推进。
-- **课程开发**：作为四项任务之一，已列入任务清单；具体开发内容与进度待后续安排。
-- **招聘师傅**：任务具体需招聘20多位师傅组建教育班队，但会上认为人数可能过多，需再评估规模。
-- **学习介绍修改**：已将“我们是谁”提到最上面，并调整两个镜头的衔接；下一步继续完善介绍内容。
-- **邀请同事加入**：计划邀请同事加入以共同制作解决方案；下一步会后联系有意愿者，具体人选待定。
-- **代购模式**：为将服务定价权交给消费者，已确定采用代购模式；该模式尚在推进中，具体落地细节待明确。
-- **待遇与休假**：待遇为上班5000元，额外有奖励和提成；休假为周五半天加周末两天，已明确标准。
-- **工作方向评估**：认为工作方向有些偏离，需考虑工作量；下一步需调整方向并统一成员认识。
-# 决定与待办
-- **会议定性**：本次会议定义为自愿级周会，主题为总结工作，目标是初步统一成员意见、统一对社区的认识。
-- **组建执法队伍**：确定为下月主要任务，为当前最重要工作。
-- **定价权交给消费者**：决定将服务定价权交给消费者，采用代购模式。
-- **修改学习介绍**：将“我们是谁”提到最上面，并调整两个镜头的衔接。
-- **组建教育团队**：第一步确定路线、修订纲领章程；任务具体需招聘20多位师傅，但认为人数可能过多。
-- **邀请同事加入**：下一步开始邀请同事加入，共同制作解决方案。
-# 协作需求
-- **邀请同事加入**：发言人1提出下一步开始邀请同事加入，目的是共同制作解决方案，需配合方确认具体人选与加入方式。
-- **组建教育团队**：组建教育团队需确定路线并修订纲领章程，发言人1请相关成员协助完成路线确定与章程修订工作。
-- **招聘师傅**：任务需招聘20多位师傅，发言人1请配合方评估人数是否过多，并协助确定最终招聘规模。
-- **修改学习介绍**：发言人1已完成将“我们是谁”提到最上面的修改，需配合方协助调整两个镜头的衔接。
-- **任务分配调整**：发言人1请相关成员根据实际情况调整任务分配，并安排下周工作顺序（如洛阳行程需排到第二项）。
-# 待确认与风险
-- **工作方向是否偏离**：会上提出工作方向可能有些偏离，需要重新考虑工作量，但未明确具体调整方案，待后续讨论确定。
-- **招聘人数是否过多**：组建教育团队需招聘20多位师傅，会上认为人数可能过多，尚未确定最终招聘规模。
-- **邀请同事加入的具体人选与方式**：计划下一步邀请同事加入以共同制作解决方案，但具体邀请对象和方式尚未议定。
-- **学习介绍修改细节**：已确定将“我们是谁”提到最上面并调整镜头衔接，但修改参数和最终效果仍需再确认。</t>
+          <t># 社区建设与教育项目周会
+## 例会概况
+本次周会于10月28日召开，核心态势为工作方向存在偏离风险，需重新评估工作量与任务优先级，整体推进处于方向修正与任务梳理阶段。会议旨在统一成员对社区的认识，初步统一意见，总结工作并安排下周任务，会议资料包括工作报告、这班看法及这班型社区介绍。主线议题共六项：会议性质与目标（已定）、工作方向与任务安排（待定，方向可能偏了需考虑工作量）、社区介绍修改（已定，将“我们是谁”提到最上面并调整使命感等参数）、任务分配与执行（已定，确认四个任务含课程开发，组建执法队伍为下月主要任务）、待遇与休假（仅同步，上班5000元加奖励提成，周五半天加周末两天休假）、定价权交给消费者（已定，转为代购模式）。整体态势上，社区介绍修改已完成、纲领章程修订接近完成，但工作方向与任务分配仍需调整确认。结论与下一步方向为组建执法队伍并招聘20多位师傅、推进课程开发、邀请同事加入，继续修订纲领章程。关键锚点：10月28日周会、四个任务、20多位师傅招聘。
+## 工作进展
+### 社区介绍与宣传
+1. **社区介绍修改**（发言人1 ｜ 状态：进行中 ｜ 交付度：已完成初稿，待进一步确认）
+  - 已将“我们是谁”部分调整至介绍最前面，并同步修改了使命感、目标感、主要任务感、成员要求等参数。
+  - 社区介绍文件已发送至参会成员，供大家审阅确认。
+2. **学习介绍完成**（发言人1 ｜ 状态：已完成 ｜ 交付度：100%）
+  - 学习介绍部分已全部完成，作为后续邀请同事加入的基础材料。
+### 任务推进
+1. **组建执法队伍**（发言人1 ｜ 状态：进行中 ｜ 交付度：任务启动阶段）
+  - 确定为下个月主要任务，计划招聘20多位师傅，组建教育方面的班队。
+  - 第一步需确定路线并修订纲领章程，相关修订工作已基本完成，待成员确认后进入任务分配阶段。
+2. **课程开发**（发言人1 ｜ 状态：进行中 ｜ 交付度：任务规划阶段）
+  - 作为当前四个任务之一，已列入工作安排，具体开发内容与分工待进一步明确。
+3. **纲领章程修订**（发言人1 ｜ 状态：已完成 ｜ 交付度：修订稿已出）
+  - 已对纲领章程进行修订，修订稿已提交，等待成员审阅并确认。
+### 运营与待遇
+1. **服务定价模式调整**（发言人1 ｜ 状态：进行中 ｜ 交付度：模式已确定）
+  - 决定将服务定价权交给消费者，转为代购模式，以提升服务灵活性与市场适应性。
+2. **待遇与休假方案**（发言人1 ｜ 状态：已确定 ｜ 交付度：方案已明确）
+  - 待遇为上班工资5000元，额外有奖励和提成；休假安排为周五半天加周末两天。
+3. **活动费用统计**（发言人1 ｜ 状态：进行中 ｜ 交付度：待统计）
+  - 需统计明日边缘分享活动页面的总费用，并核对未发放的账单（全场活动优美和棒棒糖待遇），发放完成后方可办理入职。
+## 决定与待办
+- [ ] **组建执法队伍**（下个月主要任务，需招聘20多位师傅）
+- [ ] **课程开发**（四个任务之一）
+- [ ] **修改社区介绍**：将“我们是谁”提到最上面，调整使命感、目标感、主要任务感、成员要求等参数
+- [ ] **修订纲领章程**：确定路线，修订纲领章程（已修订一部分，需成员自行查看并打勾确认）
+- [ ] **邀请同事加入**：会后邀请同事加入，共同制作解决方案
+- [ ] **发放大运**：需调试，发放完成才能入职
+- [ ] **薪资待遇**：月会上再发
+## 协作需求
+1. **邀请同事加入共同制作解决方案**（主持人 ➔ 团队成员 ｜ 会后启动）：主持人提出会后邀请同事加入，共同制作解决方案，并将在会后与有意愿者沟通。
+2. **社区介绍修改参数确认**（主持人 ➔ 张经理 ｜ 待定）：主持人要求张经理根据讨论意见修改社区介绍的相关参数，包括使命感、目标感、主要任务感、成员要求等内容，具体修改参数待确认。
+3. **任务分配调整**（主持人 ➔ 张经理 ｜ 待定）：主持人指出任务分配可能存在问题，需要调整，要求张经理对任务安排进行修改，具体调整方案待确认。
+4. **工作方向确认**（主持人 ➔ 团队成员 ｜ 待定）：主持人提出工作方向可能偏了，需要考虑工作量，需要团队成员共同确认工作方向是否调整。
+## 待确认与风险
+- [ ] **【待定论】工作方向是否偏了**（整体任务规划 ｜ 主持人提出工作方向可能偏了，需考虑工作量 ｜ 待后续确认）
+- [ ] **【待定论】任务分配的具体安排**（任务执行 ｜ 任务分配可能存在问题，需要调整 ｜ 待后续确认）
+- [ ] **【待定论】社区介绍修改的具体参数**（社区介绍修改 ｜ 使命感、目标感、主要任务感、成员要求等参数待确认 ｜ 待后续确认）</t>
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>29.4</v>
+        <v>32.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4999/1493</t>
+          <t>4999/2023</t>
         </is>
       </c>
     </row>
@@ -8533,47 +8561,51 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t># 就诊概况
-48岁男性患者张春和，职业为科研工作（成都轻工研究所），因上腹反复烧灼感4年、近3个月加重，于消化内科初诊。疼痛位于心窝部，与进食冷、硬、刺激性食物及工作紧张劳累相关，白天为主，无夜间痛醒；近2个月出现呕吐宿食，呕吐后舒适；一年前和三个月前各出现一次黑便，持续约一个月，大便干、形状正常，仅颜色改变，两次均住院2-3天后转黄。近3个月无黑便，大便黄色正常，小便正常，体重无明显下降。初步考虑消化系统疾病，需进一步检查明确，已安排大便潜血检查及胃镜（预约后天）。
-# 病史与背景
-- **现病史**：上腹烧灼感4年，每年春季多发，近3个月加重；疼痛位于心窝部，与进食冷、硬、刺激性食物及工作紧张劳累相关，白天为主，无夜间痛醒，疼痛可忍受，工作轻松时无痛。
-- **黑便史**：一年前和三个月前各出现一次黑便，持续约一个月，大便干、形状正常，仅颜色改变，两次均住院2-3天后转黄。
-- **呕吐史**：近两个月出现呕吐，呕吐物为酸水样，含当日或隔日食物，呕吐后舒适。
-- **既往史**：16岁时患甲肝，在三医院住院一个月，出院后肝功能正常，此后体检肝功均正常。
-- **过敏史**：小时候因扁桃体炎在儿童医院就诊，服用磺胺药后左手起红疹伴瘙痒，持续半个月，医生诊断为药物过敏，此后不能服用该药。
-- **个人史**：吸烟史，以前每天一包，现限制在10支以内，考虑戒烟；偶尔饮酒，平时不喝；工作于成都轻工研究所，科研工作，经常加班熬夜。
-- **家族史**：父亲76岁有低血压，母亲75岁有冠心病，弟弟身体健康；婶婶（叔叔的爱人）有胃癌，患者担心自己是否患病。
-# 诊断与检查结果
-初步考虑消化系统疾病，需进一步检查明确。医生解释：婶婶是叔叔的爱人，与患者无血缘关系，无需担心胃癌遗传问题；关于是否需要手术，需待检查资料全面后判断，若能药物控制则不需手术。患者担心自己是否得了胃癌，以及是否需要手术（因工作繁忙及出国进修安排）。
-# 治疗方案与医嘱
-- **检查安排**：留大便标本做潜血检查，以明确有无出血；胃镜预约在后天进行，因患者爱人可请假陪同。
-- **用药说明**：近期服用斯达舒（效果渐差，加量至每日4-5次）、国产奥美拉唑（武汉药厂）、阿莫西林及医务室胃炎合剂，效果不佳且反复，停药后症状复发。
-- **生活方式与饮食**：医生建议戒烟、少喝酒，因吸烟饮酒对胃肠道疾病有影响；注意避免熬夜。
+          <t># 消化内科患者病史采集与检查安排
+## 就诊概况
+48岁男性患者张春和，在成都轻工研究所从事科研工作，因上腹烧灼感4年、近3个月加重，于消化内科初诊。患者主诉心窝部烧灼感，与进食冷、硬、刺激性食物及工作紧张劳累相关，近3个月白天发作、无夜间痛醒；4年内出现两次黑便（一年前、三个月前），每次持续约一个月，住院两三天后大便转黄；近两个月出现呕吐宿食，吐出酸水样物，含当日或隔日食物。近期服用斯达舒（加量至每日四五次效果不佳）、奥美拉唑（武汉药厂产）、阿莫西林及医务室胃炎合剂，效果不佳且反复。近3个月无黑便，大便黄色正常，小便正常，体重无明显下降。初步考虑消化系统疾病，需进一步检查明确，已安排大便潜血检查及胃镜。
+## 病史与背景
+1. **现病史**：上腹烧灼感4年，每年春季多发，近3个月加重；疼痛位于心窝部，与进食冷、硬、刺激性食物及工作紧张劳累相关，与油腻食物关系不大；近3个月白天发作，无夜间痛醒，疼痛可忍受，有完全不痛的时候。
+2. **黑便史**：近4年出现两次黑便，一次一年前、一次三个月前，每次持续约一个月，大便干、形状正常，仅颜色改变；两次均住院两三天后大便转黄。
+3. **呕吐史**：最近两个月出现呕吐，吐出酸水样物，含早晨或中午吃的食物，晚上呕吐后舒适，偶有隔夜食物吐出。
+4. **既往史**：16岁时患甲肝，在三医院住院一个月治愈，出院时肝功能正常，此后体检肝功均正常；小时候因扁桃体炎在儿童医院就诊，服用磺胺药后左手起红疹伴瘙痒，持续约半个月，诊断为药物过敏，此后禁用磺胺药。
+5. **个人史**：双眼近视400度，平时不常戴眼镜；偶尔口腔溃疡，贴小紫烟可好转；无咳嗽、心慌、关节痛等，偶有急性腹泻，与不洁饮食相关。
+6. **生活史**：吸烟，以前一天一包，现限制在10支以内，考虑逐步戒烟；偶尔应酬少量饮酒，平时不喝；每天泡两次淡茶；在成都轻工研究所从事科研工作，工作紧张劳累、经常加班熬夜；26岁结婚，爱人及孩子身体健康，居住两房一厅，父母及岳父母均单独居住。
+7. **家族史**：父亲76岁有低血压，母亲75岁诊断冠心病药物控制良好，弟弟身体健康；婶婶（叔叔的爱人）患胃癌，患者担心自己是否也会得胃癌。
+## 诊断与检查结果
+1. **初步印象**：考虑消化系统疾病，需进一步检查明确，尚未确诊。
+2. **检查安排**：已安排大便潜血检查，以排查消化道出血；预约后天做胃镜。
+3. **医生说明**：严医生解释婶婶与患者无血缘关系，不必担心遗传问题；手术与否需待检查资料全面后判断，若药物能控制则无需手术。
+4. **患者顾虑**：患者担心自己是否得胃癌，担心是否需要手术，因工作繁忙且所里领导安排出国进修，希望如需手术尽早安排；医疗费用问题不大，因夫妻双方工作且有社保。
+## 治疗方案与医嘱
+1. **检查安排**：留大便做潜血检查；预约后天做胃镜，因患者爱人可请假陪同，且后天张医生查房，时间安排较好。
+2. **生活方式与饮食**：建议戒烟，尽量少喝酒，因吸烟、饮酒对胃肠道疾病有影响；注意休息，避免熬夜，因工作紧张劳累可能诱发或加重症状。
+3. **复诊安排**：严医生计划将病情总结后向上级张医生（指导教授）汇报，再商定下一步处理意见。
 | 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
 | --- | --- | --- | --- | --- |
-| 斯达舒 | — | 每日4-5次（原为每日2次，每次1颗） | 口服 | 刚开始服用有效，后效果渐差，加量后仍效果不佳 |
-| 奥美拉唑 | — | — | 口服 | 国产，武汉药厂生产 |
+| 斯达舒 | — | 最初一天两次，每次一颗；现加至每日四五次 | 口服 | 刚开始吃有效，后来效果不好，加量后效果仍不佳 |
+| 奥美拉唑 | — | — | 口服 | 武汉药厂产，国产 |
 | 阿莫西林 | — | — | 口服 | — |
-| 胃炎合剂 | — | — | 口服 | 医务室自行配置 |
-# 复诊与预警信号
-## 复诊与随访安排
-- **胃镜**：预约后天进行，因患者爱人可请假陪同。
-- **大便潜血检查**：留大便标本检查，以明确有无出血。
-- **病情汇报**：严医生将向上一级张医生汇报病情后商定处理意见。
-## 预警信号
-- ⚠️ 黑便：患者曾两次出现黑便，需警惕消化道出血。
-- ⚠️ 呕吐宿食：近两个月出现呕吐宿食，需关注。
-## 需要观察的变化
-- 观察大便颜色，若再次出现黑便需及时就医。
-- 观察腹痛、呕吐症状变化，若加重需提前联系。</t>
+| 胃炎合剂 | — | — | 口服 | 医务室自己配置 |
+## 复诊与预警信号
+### 复诊与随访安排
+1. **胃镜**：预约后天做，因患者爱人可请假陪同。
+2. **大便潜血检查**：留大便做检查，以排查出血。
+3. **病情汇报**：严医生将向上级张医生汇报病情后商定下一步处理意见。
+### 预警信号
+1. **黑便**：患者有两次黑便史，提示可能存在消化道出血风险，若再次出现黑便需及时就医。
+2. **呕吐宿食**：近期出现呕吐宿食，若频繁发作或加重需及时就医。
+### 需要观察的变化
+1. **大便颜色**：观察大便是否变黑，若出现黑便需及时联系。
+2. **疼痛变化**：观察上腹疼痛是否加重或出现夜间痛醒，若加重需及时联系。</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>44.8</v>
+        <v>58.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10297/1467</t>
+          <t>10297/1869</t>
         </is>
       </c>
     </row>
@@ -8911,108 +8943,124 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t># 讲座概况
-肖楠（基金经理）面向机构投资者作年度汇报，主题为过去一年的研究布局与投资框架反思，形式为线上路演。他开宗明义指出投资者关心的“what happen next”类问题用处有限，因为知识与信息之间存在巨大鸿沟，并介绍其研究框架只关注重要且可研究的问题。汇报围绕三个板块展开：反对“抱团”与“均值回归”两种流行观点、过去一年在互联网、财富管理、新消费和高端制造四个方向的研究布局，以及对投资框架的五点反思与更新。核心主张包括：收益率呈幂律分布而非正态分布，美国股市200年价值增量由4%的公司贡献；投资中需重视国运、文化等长期变量并保持谦卑；承认驱动企业增长且不被线性描述的“X factor”的存在。讲座对关注基金经理理念与认知升级的投资者具有参考意义，肖楠强调投资者应检验基金经理的言行是否一致，而非仅关注具体交易。
-# 核心观点与论证
-## 知识与信息的鸿沟
-- **知识 vs 信息**：肖楠认为投资者关心的"what happen next"类问题，得到的答案只是"肖楠看好某某"的信息，而非支撑判断的知识；知识与信息之间存在巨大鸿沟。
-- **观点易变**：肖楠举例，自己看好某板块是基于知识，但新知识增加会修正判断，第二天观点可能已变；投资者可能等一年甚至更久才知道观点已变。
-## 研究框架：只关心重要且可研究的问题
-- **四类问题划分**：肖楠将问题分为重要不重要、可研究及难以研究四类，只关心重要且可研究的问题，如标的基本面是否变化、投资逻辑有无更新、投资框架有无值得修正之处。
-- **框架因人而异**：该表仅针对肖楠个人；例如基于宏观变量做资产配置的人，会认为美联储利率变化对市场的影响是既重要又可研究的问题。
-## 反对"抱团"：定义不本质
-- **定义不本质**：肖楠认为"抱团"定义不本质，会导致研究误入歧途；类比给一叫太阳就出来的动物取名"光明使者"，不具因果本质。
-- **主观上不可能**：基金经理之间是竞争关系，不可能商量好一起买某只股票；"你去找富国的李经理，嘉实的王经理，张经理，咱们商量好去抱团，没有这种实际不可能的"。
-- **同公司买同板块不叫抱团**：研究员推荐股票、多位基金经理认可后买入是正常运作；若算抱团，则"将来研究员每推荐一个股票，我们就抽取三位幸运基金经理"才可避免，显然荒谬。
-- **截面数据忽略时间维度**：肖楠称自己8年前、5年前已买入某些标的，后来大量资金涌入；拉长时间看，A股和海外股市都有"五朵金花""眉飞色舞""长牛的医药消费"等现象，非常稀松平常。
-## 反对"均值回归"：局部正确
-- **局部正确**：均值回归（跌多了要涨、涨多了要跌）在短期K线图上确实成立，但无法解释10年涨10倍、20倍、50倍、100倍的长线牛股。
-- **海螺水泥案例**：某商学院老师用自编技术指标在海螺水泥上做波段，过去10年赚约两三倍；2016或2017年卖出后等回调，结果两年涨了五六倍，再也没能买回来。
-- **收益率幂律分布**：肖楠强调收益率是幂律分布而非正态分布；美国股市200年价值增量由4%的公司贡献，去掉这4%的公司，200年来美国股市没有涨。
-- **投资核心**：做投资的核心是找到摆脱"涨多就跌、跌多就涨"局部规律的长线超级大牛股，这些牛股身上有特别不一样的东西。
-## 四大研究布局
-- **互联网**：全球能把互联网做成巨大产业、诞生巨大公司的只有中国和美国；中国短短十几年已迭代三代企业——第一代基于流量（门户网站、搜索引擎）、第二代基于运营管理（阿里、淘宝）、第三代基于算法（字节、拼多多）；开通港股通后可投资此前无法投的公司，不能容忍错失机会。
-- **财富管理**：中国从一穷二白进入小康，人均收入中位数向前挪5%或10%，因巨大基数效应和收入分布密度效应会产生巨额剩余财富，有待专业机构管理；行业潜在空间远超想象。
-- **新消费**：新消费公司从CEO理念、组织架构、基层执行到生产方式、营销方式，与匮乏年代走出的传统企业完全不同；随着中国越来越富裕，这类公司会越来越多。
-- **高端制造**：中国几乎是全球唯一拥有全产业链的国家；微观深入制造业细分领域可见中国已在很多领域"占据主导地位"，与10年前"10亿双袜子换台飞机"的理解完全不同；欧美日企业可得的市场份额"已经是中国企业碗里的肉了"。
-## 新消费研究认知
-- **产品差异巨大**：表面看起来产品差不多的两家公司，收入利润体量差距巨大；深入研究发现，产品经理团队或CEO眼中自家产品与竞争对手存在巨大鸿沟，这种差异在三年、五年、十年维度会被放大。
-- **行业格局差异**：传统消费领域龙头赚钱、龙二龙三也赚钱；新消费领域同样巨大的行业里可能只有两家公司，一家赚很多钱，另一家完全不挣钱、不知怎么挣钱。
-## 商增视角理解商业模式
-- **商增过快导致失败**：肖楠研究大量企业失败案例，发现商增是理解商业模式的重要角度；企业成长中商增速度差异巨大，商增过快导致企业走向失败。
-- **商增更本质**：有些企业从诞生到收入和利润涨100倍，结构没有特别大变化，商增很少；另一些企业扩张中商增剧烈，增到一定程度后"科斯定理就告诉我们这个企业已经没有存在的必要了"。
-- **商增的具体表现**：企业从小到大部门增多、中层干部一大堆、传达效率变差、内部腐败出现；为防腐败又增设巡视检查部门，部门人员加工资提级别，层层叠加。
-- **商增拖死企业案例**：某行业只剩两家互联网大厂，一家效率高、高度中央集权，CEO通过强大情报部门知道每件重要事情细入基层；另一家山头林立、互相推诿、腐败丛生。
-- **处理商增的高手**：肖楠建议读党史，看组织如何从国民革命时期、抗战时期走到现在保持活力；有些国家也被商增拖死，"一条铁路修几十年"在很多国家都会发生。
-## 商业模式分类的反思
-- **三类商业模式**：肖楠过去把生意分为坐地收钱（最喜欢买）、苦尽甘来、燃烧自己照亮别人（不值得买）三类；至今依然这样划分，依然相信对商业模式的理解。
-- **框架不完备**：世界上没有一劳永逸的坐地收钱生意，极端稀缺；连爱马仕这样的企业，一个设计师的好坏也可能影响未来五年十年的销售；长期看所有企业都要死去，单一维度出发会错失很多机会。
-## 企业家精神与长期变量
-- **企业家定价之辩**：肖楠常与张坤争论企业家精神或企业家值不值得定价；企业如日中天时企业家值50倍估值，开始犯错误时就说不太行，导致无法定价。
-- **无法定价但可考虑**：即使无法给企业家定价，企业发展中某些要素可能在长期视角下带来超额收益，尤其在困难时期；这弥补了三种商业模式粗线条分类忽略的因素。
-- **长期变量案例**：西方世界无人预料到中国和平稳定高速发展30多年、40年；过去买茅台赚钱的人写的回忆录，逻辑包括便宜、产品好、商业模式好等，但加在一起也解释不了茅台如此巨大的涨幅，可能有更大的变量（宏观经济背景、文化背景、品牌背景）在起作用。
-- **奢侈品牌与国家实力**：LV、爱马仕讲的故事是"祖上给皇上当过马夫、给娘娘当过皮匠"，但给的是英国、法国这些老牌资本主义国家的皇上娘娘——因为"他们家的军舰当年横扫全世界"。
-- **白酒出海逻辑**：30年前洋酒刚进入中国时，中国土豪兑雪碧喝，因为难喝但文化强势、为显高档；如果有一天中国国力强盛到"中国的航空母舰在人家十二海里外做军事演习"，就能讲"纯粮固态发酵的酒才是好酒"的故事。
-- **保持谦卑**：很多基金经理说放在美国能挣更多钱，但放在日本、德国、新加坡未必；要经常对市场保持谦卑，未来研究会把十年维度上起作用的隐性长期变量纳入研究。
-## 深度价值可能长期无效
-- **深度价值只是结果**：深度价值是导致便宜的原因不变时最好的结果也就是不输了；肖楠过去投了一些认为是深度价值的标的，结果非常差，产生很大启发和刺激。
-- **打问号**：肖楠对"深度价值可能长期无效"打了问号，没有下结论。
-## X factor：驱动企业增长且不被线性描述的因子
-- **线性假设的局限**：做DCF、DDM都是线性假设，无非增长率是12、13、14还是15、16、17的区别；但拉长到10年视角，企业发展是一条非常漂亮的曲线，经典投资模型没有一个变量隐含对企业发展曲率的估计。
-- **X factor定义**：大量行业里做同样事情、生产差不多产品的企业差异巨大，原因是一些称作曲率的因素在起作用，这些因素无法被经典投资理论模型定价，但长期起作用的就是这些。
-- **顺丰案例**：疫情时只有顺丰能送，一下子把业绩和估值甩出一大截；平时看只是"快一点、准一点"，没有太大区别，关键时候一场疫情就拐上去了。
-- **美的案例**：格力一直是老大，美的做渠道扁平化、T+3一直没看到成果；疫情一来美的占有率哗一下上去，超过格力。
-- **结论**：驱动企业增长且不被线性描述的因子，即使无法有效定价也一定要承认其存在；否则会陷入"企业挺好但估值贵、企业便宜但基本面烂"的挣扎；超额认知就来自这些方面。
-## 错过中期机会的反思
-- **错过十几倍涨幅**：肖楠过去因判断企业终局不太好或看不清楚，放弃了一些中期投资机会，包括一个10倍的投资机会；最打脸的是判断对了终局，却在两三年的时间里深深错过十几倍涨幅。
-- **具体案例**：某企业产品跨代领先竞争对手，肖楠判断领先不能长期保持、行业格局会变差、ROE会剧烈下降；一两年内确实如预判，但企业从下终局判断到后来足足涨了十几倍。
-- **反思结论**：在坚持终局重要性判断的基础上，也要争取研究格局演进的阶段性特征来把握投资机会；可通过紧密跟踪认知快速迭代、识别里程碑式事件来提高胜率，在中期时间内获得好的投资回报率。
-# 金句总结
-&gt; “知识和信息之间是有着巨大的鸿沟的。”
-- 背景：开场论述投资者关心的“What happen next”问题——投资者得到的只是信息，而知识无法传递。
+          <t># 投资框架反思与年度研究布局汇报
+## 讲座概况
+肖楠（基金经理）面向机构投资者作年度研究汇报，主题为过去一年的研究布局、研究成果及投资框架的反思与更新。开场即点明知识与信息之间存在巨大鸿沟，投资者得到的只是信息而非知识，并介绍其将问题分为重要不重要、可研究及难以研究四类的研究框架，自述投资框架偏向左派（巴菲特派），但强调务实与务虚没有高下之分。汇报围绕四个板块展开：互联网、财富管理、新消费和高端制造的研究布局；对抱团与均值回归两种流行观点的明确反对；对投资框架的五点反思（商业模式分类局限、商增视角、长期变量、深度价值可能无效、X factor）；以及投资者问答。核心主张包括：收益率呈幂律分布而非正态分布，美国股市200年价值增量由4%的公司贡献；驱动企业增长且不被线性描述的因子（X factor）无法定价但必须承认其存在；存在影响收益率的隐性长期变量，需保持谦卑并纳入研究。对听众而言，本次汇报旨在帮助投资者理解其研究积累、看问题角度及投资理念的演进，而非提供具体的买卖建议。
+## 核心观点与论证
+### 知识与信息的鸿沟
+1. 肖楠认为投资者关心的“What happen next”类问题，得到的答案对其用处不大：他看好某板块或个股，是基于相关知识（knowledge），而投资者得到的只是一条“肖楠看好某某”的信息（information），知识与信息之间存在巨大鸿沟。
+2. 他的观点可能因新知识增加而次日即变，但投资者可能要等一年甚至更久才知道，因此这类答案对投资者没有太大实际价值。
+### 研究框架：只关心可研究的问题
+1. 肖楠将问题分为四类：重要不重要、可研究以及难以研究，他只关心可研究的问题，如标的基本面是否变化、投资逻辑有无更新、对标的的认知是否更深入领先。
+2. 作为基金经理，他最关心自己的投资框架有无值得修正之处，这类问题“在这里挖井打矿是富矿”。
+3. 该表仅针对他个人：例如基于宏观变量做资产配置的人，会认为美联储利率变化对市场的影响是既重要又可研究的问题。
+### 投资流派谱系：务实与务虚
+1. 市场上的基金经理理念大致处于两个极端之间：以巴菲特为代表的“极端务实派”和以索罗斯为代表的“极端务虚派”。
+2. 巴菲特派认为股票是企业所有权的一部分，价值来源是企业价值即未来现金流，短期波动是随机的、不值得研究，研究重点应放在公司生意和管理层上，买入后长期持有直到投资逻辑变化。
+3. 索罗斯派认为股票是筹码，价值来源于其他交易者对筹码的看法，交易代表信息、股价波动代表信息，应研究交易者在基本面之上的行为，通过交易与市场对话、试错并获利。
+4. 大部分基金经理（包括肖楠）处于两个极端中间的某个位置，肖楠自述偏左边（偏巴菲特派）一点；务实还是务虚没有高下之分，“做好的都是大师，做不好都是东施效颦”。
+### 反对“抱团”：定义不本质
+1. 肖楠明确反对“抱团”说法，认为该定义不本质——如果对现象的定义不本质，会导致研究误入歧途；他举例：若把“一叫太阳就出来”的动物命名为“光明使者”，按此思路理解就会误以为宰了它太阳就不出来。
+2. 基金经理之间是竞争关系，主观上不可能抱团：每个基金经理都想买跟别人不一样的东西并获得市场认可，不存在“打电话给嘉实基金王经理商量一起买股票”的可能。
+3. 同一家基金公司买同一板块不叫抱团：研究员推荐股票、多位基金经理认可后买入是正常运作机制，若定义为抱团，则“研究员每推荐一个股票就抽取三位幸运基金经理去买”的做法显然荒谬。
+4. 抱团只是截面数据，忽略了时间维度：肖楠举例自己8年前、5年前就买入某类标的，后来大量资金蜂拥而至，他“一脸懵”；A股和海外股市都有类似现象，如当年的“五朵金花”“眉飞色舞”“长牛的医药消费”等，市场上出现这种现象“本来就对了”。
+### 反对“均值回归”：局部正确
+1. 均值回归（跌多了要涨、涨多了要跌）是“特别不本质的局部正确”：短期看K线图确实如此，但拉长看无法解释10年涨10倍、20倍、50倍、100倍的长线牛股。
+2. 案例：某商学院老师在海螺水泥上做波段，自编技术指标，过去10年赚了约两三倍且“非常准”；2016或2017年涨了一波后卖出等回调，结果两年时间该股涨了五六倍，老师再也没能买回来——“均值回归90%的时间都正确，那10%的错误依然让你代价惨重”。
+3. 收益率是幂律分布而非正态分布：美国股市200年来的价值增量由4%的公司贡献，把那4%的公司挖掉，200年来美国股市没有涨；做投资的核心就是找到摆脱“涨多了跌、跌多了涨”这种局部正确规律的长线超级大牛股。
+### 四大研究布局：互联网、财富管理、新消费、高端制造
+1. **互联网**：全球能把互联网做成巨大产业、诞生巨大公司的只有中国和美国；中国短短十几年已迭代三代企业——第一代基于流量（门户网站、搜索引擎）、第二代基于运营管理（阿里、淘宝）、第三代基于算法（字节、拼多多）；未来行业仍会出特别大的机会，港股通开通后可投资以前在A股无法投的公司，不能容忍错失机会。
+2. **财富管理**：中国从一穷二白进入小康、去年将将脱贫，人均收入中位数向前挪5%或10%，因巨大基数效应和收入分布密度效应会有巨额剩余财富，有待专业机构管理，行业潜在空间“远超我们想象”。
+3. **新消费**：从匮乏年代走出来的第一代、第二代消费品公司，与富裕年代诞生的新消费公司完全不同——不是产品够新，而是从CEO到组织架构、经营理念、生产方式、营销方式“完完全全不一样”；随着中国越来越富裕，这类公司会越来越多。
+4. **高端制造**：中国是全球几乎唯一拥有全产业链的国家；微观深入制造业细分领域会发现中国在很多领域已“占据主导地位”，与10年前“10亿双袜子换台飞机”的理解完全不同；欧美日企业手中的市场份额“已经是中国企业碗里的肉了”，未来空间非常可见。
+### 新消费研究的认知成果
+1. 过去不理解有些产品为什么卖得火：外人看两家公司产品差不多（都卖笔、都卖电饭锅），但收入利润体量差距巨大；深入研究发现，在产品经理团队或CEO眼中，自家产品与竞争对手产品存在巨大鸿沟，这些差异在三年、五年、十年维度里被放得非常大。
+2. 传统消费领域常见“龙头赚钱、龙二龙三也赚钱”的现象，但新消费领域同一巨大行业可能只有两家公司，一家赚很多钱、另一家完全不挣钱也不知道怎么挣钱，差异极大。
+### 商增视角：理解商业模式更本质
+1. 企业总是要成长，但成长过程中有些企业的商增速度远超另一些企业，商增过快导致企业走向失败；过去研究了很多企业失败案例，发现商增是理解商业模式的重要角度。
+2. 有些企业从诞生到收入和利润涨100倍，结构跟诞生之时没有特别大区别，商没有怎么增加就能放大100倍；另一些企业扩张过程中商增剧烈，增到一定程度后“科斯定理就告诉我们这个企业已经没有存在的必要了”。
+3. 过去一段时间大量讨论企业在成长过程中靠什么吸收熵增，认为从商增角度理解企业成长中的成本项“更加本质”。
+### 反思一：商业模式分类的局限
+1. 过去把生意分为三类：坐地收钱（最喜欢买）、苦尽甘来、燃烧自己照亮别人（不值得买），至今依然相信这种划分，但承认框架有不完备性。
+2. 世界上没有一劳永逸的坐地收钱生意，极端稀缺或稀少：哪怕爱马仕这样的企业，一个设计师的好坏也可能影响未来五年十年的销售；长期看所有企业都要死去，不能抱着买“千秋万代”企业的想法，单一维度出发会错失很多机会。
+### 反思二：坚持终局判断，把握阶段性特征
+1. 错过一些机会的教训：对某些企业终局判断悲观或看不清，放弃了一些中期投资机会，甚至错过10倍的投资机会；最打脸的是终局判断对了，却在两三年时间里深深错过十几倍涨幅。
+2. 案例：某企业产品跨代领先竞争对手，当时判断这种领先不能长期保持、行业格局会变差、ROE会剧烈下降——这一判断在随后一两年被验证，但该企业从下终局判断到后来足足涨了十几倍，整个过程完全被错过。
+3. 应对思路：通过紧密跟踪认知快速迭代、识别企业可能出现的里程碑式事件来把握投资逻辑变化，提高胜率，在中期时间内获得好的投资回报率；在坚持终局重要性判断的基础上，争取研究格局演进的阶段性特征。
+### 反思三：隐性长期变量
+1. 思考“为什么日本、德国、越南没有出巴菲特、索罗斯这样的投资大师，美国有”——如果把这套理念搬到日本似乎不太行；中国股市发展20多年诞生了一批长线收益非常好的基金经理，但放到台湾、日本、韩国未必有同样收益率，说明有特别长期的变量解释了相当一部分收益率来源。
+2. 西方世界过去对中国的判断中，没有人预料到中国和平稳定高速发展30多年、40年，这个隐藏的巨大变量可称作“国运”；基金经理把成功归因于理念好、聪明勤奋、判断力好、团队好，这些话对，但忽略了其他因素。
+3. 茅台案例：把90年代、2000年代买茅台赚钱的人写的回忆录中的逻辑（便宜、产品好、商业模式好）全部列出来，也解释不了过去十年、二十年茅台如此巨大的涨幅——别的一些股票也有类似逻辑却涨得没茅台多，说明有一个更大的变量（如宏观经济背景、文化背景、品牌背景）在后面起作用。
+4. 中国在消费品领域（家电、快消、可乐）和制造业众多细分领域逐渐成为产业链主导，为什么偏偏在中国看到这种现象而不是别的国家，这点非常有意思；结论是“尽管穷尽所有智慧和精力去探究收益率来源，往往依然忽略了一个巨大的变量”。
+5. 对市场保持谦卑：很多基金经理说放在美国能挣更多钱，但放在日本、德国、新加坡未必；未来研究会把一些特别隐性的、可能在十年维度上起作用的长期变量纳入研究范围。
+6. 奢侈品案例：LV、爱马仕讲的故事是“祖上给皇上当过马夫、给娘娘当过皮匠”，但给的是英国、法国这些老牌资本主义国家的皇上和娘娘——因为他们的军舰当年横扫全世界，所以他们的皮匠、马夫是最厉害的；20年前天涯论坛问“中国GDP什么时候超过日本”被群嘲，今天大家在算哪一年GDP超过美国。
+7. 白酒出海逻辑：欧美人不喝白酒，普遍答案是“不好喝”，但30年前、20年前洋酒刚进中国时，中国土豪因难喝兑雪碧喝，为什么难喝还要喝？因为人家的文化是强势文化，为了显示高档难喝也要喝；如果有一天中国国力强盛到“中国的航空母舰在人家十二海里外做军事演习”，就可以讲“纯粮固态发酵的酒才是好酒，whisky、白兰地、清酒都是液态发酵法做出来的，特别不值钱”这个故事。
+8. 结论：要保持谦卑的态度，但也保持大胆想象——20年前不敢想中国GDP超过日本，现在可以想中国好的消费品出海。
+### 反思四：深度价值可能长期无效
+1. 深度价值只是一个结果：看到某公司特别便宜，说明它已进入深度价值；如果导致深度价值的原因不变，那么深度价值最好的结果也就是不输了。
+2. 过去投了一些认为是深度价值的标的，结果非常差，产生很大启发和刺激；对“深度价值可能长期无效”打了问号，未得结论。
+### 反思五：X factor——驱动企业增长且不被线性描述的因子
+1. 经典投资模型（DCF、DDM）都是线性假设，无非是增长率12%、13%、14%还是15%、16%、17%的区别；但拉长到10年视角，企业发展是一条非常漂亮的曲线，而所有经典投资模型都没有一个变量隐含对企业发展曲率的估计。
+2. 与一位理科背景的知名创业家交流：企业短期看是线性增长（今年15%、明年17%），长期看是一条曲线；现实中大量行业、大量企业做着同样的事情、生产差不多的产品，企业间差异巨大，原因就是曲率因素在起作用。
+3. 这些X factor无法被经典投资理论模型定价，但长期起作用的就是这些；结论是“驱动企业增长且不被线性描述的因子，即使没有办法有效定价，也一定要承认它的存在”。
+4. 现实困境：今年遇到一些企业挺好但估值贵、一些企业便宜但基本面很烂；倒回去看今天涨得很大的企业，5年前、10年前大家都在讲产品渗透率已很高、利润率已很高，但到今天那些说法全部没实现，这些企业长出了第二生长曲线、第三生长曲线，还在找新的生长曲线。
+5. 经常强调的“超额认知”实际上就来自这些方面。
+## 金句总结
+&gt; “你听到的这个答案，对你来说其实没有太大的用处。我看好这个东西是基于相关的知识，对我来说这个东西叫knowledge，但是对于你来说，你得到的仅仅只是一条肖楠看好某某这个信息。”
+&gt; —— **肖楠（主讲人）** ｜ 针对知识与信息鸿沟的定调发言
 &gt; “务实还是务虚，其实没有高下之分的。做好的都是大师，做不好都是东施效颦。”
-- 背景：对比巴菲特代表的务实派与索罗斯代表的务虚派，说明投资理念无好坏之分。
+&gt; —— **肖楠（主讲人）** ｜ 针对投资理念流派之争的定调发言
 &gt; “均值回归这个事情，90%的时间都正确，那10%的错误依然让你代价惨重。”
-- 背景：反对均值回归观点，举例某商学院老师在海螺水泥上做波段，因相信均值回归错过两年涨五六倍的行情。
-&gt; “收益率是幂律分布的，不是正态分布的。”
-- 背景：论证均值回归不成立，指出美国股市200年价值增量由4%的公司贡献。
-&gt; “长期看所有的企业都要死去。”
-- 背景：反思“坐地收钱”商业模式分类的局限，指出没有一劳永逸的生意。
-&gt; “我们尽管穷尽了我们所有的智慧、所有的精力去力求探究我们的这个收益率的来源，往往依然是忽略了一个巨大的变量在后面起作用。”
-- 背景：讨论长期变量（如国运、文化背景）对收益率的重要影响，主张对市场保持谦卑。
+&gt; —— **肖楠（主讲人）** ｜ 针对反对均值回归观点的定调发言
+&gt; “200年以来，美国股市的价值增量，是由4%的公司贡献的。你把那4%的公司给挖了，200年来美国的股市没有涨。”
+&gt; —— **肖楠（主讲人）** ｜ 针对收益率幂律分布的定调发言
+&gt; “长期看所有的企业都要死去，我们不能够抱着说我们要买一个千秋万代的这种企业。”
+&gt; —— **肖楠（主讲人）** ｜ 针对商业模式分类反思的定调发言
+&gt; “我们尽管穷尽了我们所有的智慧、所有的精力去力求探究我们的收益率的来源，往往依然是忽略了一个巨大的变量在后面起作用。”
+&gt; —— **肖楠（主讲人）** ｜ 针对长期变量与国运的定调发言
 &gt; “驱动企业增长且不被线性描述的因子，我们即使是没有办法去有效定价，我们也一定要承认它的存在。”
-- 背景：提出X factor概念，指经典投资模型无法定价但长期起作用的因素。
+&gt; —— **肖楠（主讲人）** ｜ 针对X factor的定调发言
 &gt; “伟大公司是在财务指标里面看不出来的。”
-- 背景：回答投资者关于伟大公司判断标准的问题，强调需看企业历史、研发投入与产业报国精神。
-# Q&amp;A 环节
-**听众**：您刚刚讲到在重视终局结果的过程中，也更加关注格局演进中的阶段性特征和中期投资机会，能否再详细描述一下？
-**肖楠**：这个想法最早来自我们过去错过的一些特别大的机会。我们当时判断某些行业终局可能不大行，而最打脸的是我们明明判断对了，却在两三年的时间里深深错过了十几倍的涨幅。复盘时发现，这类企业有一个重要特征是我们当时忽略的——比如某代产品当时领先，后来确实如我们所料被人追上，但企业做出了第二增长曲线，而且第二增长曲线的壁垒比第一增长曲线还要深、还要厚。所以我们现在开始承认终局可能没有那么强、不会像一劳永逸躺着收钱那么强，但在这种前提下依然能做出好的投资，希望未来不要再错过类似机会。
-**听众**：您在年报中讲到坚定持有优秀乃至伟大的公司，请问对优秀乃至伟大公司的判断标准，有没有具体的财务指标？
-**肖楠**：伟大公司在财务指标里是看不出来的。我举一个例子，两家公司同属一个大行业但不同细分子行业，都是把成本做到行业最低、市场份额稳固提升的优秀公司。区别在于：B公司不怎么做研发，靠精益求精的管理做到成本极低，业内络绎不绝来学习但学不会；A公司每年有高额研发支出，关键技术指标以非常强的速度迭代，研发方向非常前沿，目前这些方向的技术掌握在德国人和日本人手里。A公司是国企，发展初期被德国人、日本人狠狠坑过，从董事长到技术骨干都有强烈的产业报国、技术报国理想，从跟着学、越做越强、超越对手，到对手跑来跟他们学，再到做全产业链布局——这种企业堪称伟大。这类企业在中国越来越多，以前领域里是日本人、美国人、台湾省企业家占据，现在中国人在一点点往前拱，这些人不是想今年赚三五个亿，而是一门心思往前做。
-**听众**：我们是全市场基金，能否介绍一下这个产品的投资逻辑？对于消费以外的行业选股，主要基于什么逻辑？
-**肖楠**：我们很难分消费内消费外，选股逻辑都是一样的，都是以前讲过的“不可能三角”、企业三阶段、三种商业模式那一套。只不过消费行业基金只许买消费、不能买别的，所以肯定在消费行业里选。两者的选股逻辑完全一样，没有什么区别。
-**听众**：您怎么看待血制品行业的竞争壁垒？
-**肖楠**：血制品行业我们初步研究过，觉得壁垒不是特别强，不是我们想要的那种强壁垒，这个就不展开了。我们找了一堆强壁垒的公司，相比之下买了另外一些。
-**听众**：在管理行业能否再具体讲一下？
-**肖楠**：血制品这个行业我们研究得不是特别多，因为我们还有一些基金经理买了血制品行业，我觉得可以请教他们，我们不希望有一些特别冲突的观点。
-**听众**：农林牧渔行业有所提升，请问您对这个行业的观点？
-**肖楠**：这个行业太大了。农林牧渔行业的提升是因为牧原股份，就那一只股票。不是我先看好农林牧渔行业再去选牧原股份，就是牧原股份的比例提高了，就这么简单。我们不能在公开场合讲具体股票的投资逻辑。
-**听众**：您能再具体讲一下生意模式里商增和商减的分析吗？
-**肖楠**：用直白的例子讲，你们都是企业里的打工人，能深切感受到：企业从小到大，部门越来越多，以前三五个部门，现在十几个部门，中层干部一大堆，上面分领导、副总裁，下面一大堆基层部门，传达效率变低，内部腐败开始出现。企业为了解决腐败问题，要设巡视检查部门，又多一个部门；部门里的人干三五年要加工资提级别，这么多部门老总今年提哪个？企业要扩张，往下游做或往上游做，又多一项业务，就要多一个副总裁，又多很多部门。有些生意收入从10亿做到100亿，没多几个部门；有些企业不需要设那么多副总裁和高管就把生意做成了。从商增角度讲，有些企业是商增把自己拖死的。比如某个行业剩两家互联网大厂，一家效率特别高，另一家山头林立、互相推诿、腐败丛生——后者从一开始就没考虑好企业大了以后怎么处理效率和人员问题。我特别建议大家去读党史，看看这个组织从国民革命时期、抗战时期一直走到现在，怎么保证活力，这是非常厉害的事情。有些国家也是被商增拖死的，一条铁路修几十年，在很多国家都会发生。
-**听众**：您讲到伟大企业的增长曲线，能否再具体讲一下？
-**肖楠**：过去几年每年看，企业今年增长20%、明年15%、后年17.5%，都是线性的；但站到10年周期看，这个企业和竞争对手之间拉开了极大差距。比如快递行业，疫情时只有顺丰能送，一下子把业绩和估值甩出一大截；家电领域，格力一直是老大，美的做渠道扁平化、T+3，一直没看到成果，突然疫情来了，美的占有率一下上去超过格力。当企业在埋头做事、还没体现到报表时，我们往往忽略这些事未来可能产生的重大影响。这些伟大企业都是在一些特别特殊的时候拐上去的——平时走在路上大家都好好的，突然来一场雨，发现有一个人带伞了，别人都淋成落汤鸡，就他家有伞。
-**听众**：您讲到财富管理行业，能否具体展开讲一下投资逻辑和投资机会？
-**肖楠**：财富管理行业这个话题特别大，而且是分层的——顶级富豪、普通中产阶级、中低收入人群的财富管理，都有不同的公司和商业模式。我们最早关注这个行业是从研究保险开始的：有些保险公司一个保险员一单能签七八千的首期保费，有些公司平均只有两三千，差距巨大。调研后发现，同样是卖保险，背后的机制差异超级大，这些公司的结构设置、激励机制、文化都有巨大差异。去年基金很火，我们发现同样有渠道经理过来调研问的问题超级专业，另一些渠道经理永远问下半年是涨是跌、明年是牛市还是熊市。财富管理行业最大的逻辑在于财富分布超级不均匀，头部公司可能一口气拿掉行业增量的绝大部分，第二名只能拿到剩下的20%的80%。在这种幂律分布特别偏激的行业里，有可能诞生特别大的企业。很遗憾，我们有一些产品因为监管和法律规则的原因反而不能投类似标的，未来合同设置更清晰时，可能会在这方面的投资上有所体现。
-**听众**：您讲到第二、第三增长曲线需要卓越的企业家精神，企业家精神是投资中比较艺术的部分，请问您在观察这个指标方面有什么心得和把握？
-**肖楠**：第一个心得是评判这个因素时要特别小心谨慎，不要乱归因。不要因为一个企业经营成功就说这个企业家特别厉害，就像不要因为一个基金经理过去业绩好就说他特别厉害。一定要把所有能归因到数据里客观指标的因素全部归因完，再特别谨慎地评价比较虚的因素。第二个是不要轻易给这些因素定价，绝对不要说因为这个企业家在，所以公司就能值多少。我始终强调的是避免错误归因，避免因为对企业家个人的认可去犯投资上的错误，一定要把底线风险搞好。我们一致同意这个东西不可被定价。这些比较虚的因素——技术进步、企业家精神——什么时候考虑？是在所有客观归因都尽量穷尽以后，才说可能某种程度上一些收益率的归因要归到这里面去。另外，只能在有限范围内做两两比较：两家公司做同样生意、同样产品，在这种限定条件下比较两个企业家水平的高低、理念的先后，去找你认可的那一家，不要跨行业、跨业务、跨产品比较。不要什么事情都归结到企业家身上，要谨慎地使用所谓企业家精神、伟大企业这些词，在一些特别极端的时候，它可能是你某些信仰上的支持，但尽量不要去用。</t>
+&gt; —— **肖楠（主讲人）** ｜ 针对伟大公司判断标准的定调发言
+## Q&amp;A 环节
+### Q1. 中期投资机会与终局判断
+- **听众**：您刚刚讲到在重视终局结果的过程中，也更加关注格局演进的阶段性特征和中期投资机会，能否再详细描述一下？
+&gt; **肖楠**：这个想法最早来自我们过去错过的一些特别大的机会。我们当时判断某些行业终局可能不大行，而最打脸的是我们明明判断对了，却在两三年的时间里深深错过了十几倍的涨幅。复盘时发现，这类企业有一个重要特征是我们当时忽略的——它们某一代产品当时领先，后来确如我们所料被人追上，但企业却做出了第二增长曲线，且第二增长曲线的壁垒比第一增长曲线还要深、还要厚。所以我们后来渐渐开始承认终局可能没那么好、不会像一劳永逸躺着收钱那么强，但依然能做出好的投资来，希望未来不要再错过类似机会。具体标的不便详述，确实有一两个标的给我们带来极大刺激。
+### Q2. 伟大公司的判断标准
+- **听众**：您在年报中讲到坚定持有优秀乃至伟大的公司，请问对优秀乃至伟大公司的判断标准，有没有具体的财务指标？
+&gt; **肖楠**：伟大公司在财务指标里是看不出来的。我举一个例子，不能说是哪家企业：A、B两家公司同属一个大行业但不同细分子行业，投资逻辑很像，都是在自己领域把成本做到行业最低，市场份额稳固且不断提高。区别在于，B公司不怎么研发，靠管理上精益求精，业内络绎不绝来学习但学不会；A公司每年有非常高额的研发支出，关键技术指标以非常强的速度迭代，很多研发项目是特别前沿的方向，这些方向的技术目前掌握在德国人、日本人手里。有意思的是这两家都是国企，A公司在发展初期被德国人、日本人狠狠坑过，从董事长到技术骨干积攒了非常强烈的产业报国、技术报国的理想，从跟着学、越做越强、超越对手，到对手跑过来学，再到做全产业链布局，写下来就是产业上史诗般壮丽的东西，这种企业堪称伟大。过去这个领域很多是日本人、美国人、台湾省企业家占据，现在中国人在一点点往前拱，这些人不是想今年赚三五个亿，而是一门心思往前做，甚至做学生时就已经觉得应该这么做。
+### Q3. 全市场基金的选股逻辑
+- **听众**：我们是全市场基金，能否介绍一下这个产品的投资逻辑？对于消费以外的行业选股，主要基于什么逻辑？
+&gt; **肖楠**：我们很难分消费内消费外，选股逻辑都是一样的，都是以前讲过的“不可能三角”、企业三阶段、三种商业模式那一类。只不过消费行业基金只许买消费，所以肯定在消费行业里选，两者的选股逻辑完全一样，没有什么区别。
+### Q4. 血制品行业的竞争壁垒
+- **听众**：您怎么看待血制品行业的竞争壁垒？
+&gt; **肖楠**：血制品行业我们初步研究过，觉得壁垒不是特别强，不是我们想要的那种强壁垒。这个就不展开了，因为我们的研究不是特别深入，相比之下我们买了另外一些强壁垒的公司。
+### Q5. 血制品行业研究深度
+- **听众**：在血制品行业能否再具体讲一下？
+&gt; **肖楠**：我们只就血制品这个行业，研究得不是特别多。因为我们还有一些基金经理买了血制品行业，我觉得可以请教他们，我们不希望有特别冲突的观点。
+### Q6. 农林牧渔行业的观点
+- **听众**：农林牧渔行业持仓有所提升，请问您对这个行业的观点？
+&gt; **肖楠**：这行业太大了。农林牧渔行业的提升是因为牧原股份，就那一只股票。不是我先看好农林牧渔行业再去选牧原股份，就是牧原股份的比例提高了，就这么简单。具体股票的投资逻辑不能在公开场合讲。
+### Q7. 商增与商减的分析
+- **听众**：您能否再具体讲一下生意模式里商增和商减的分析？
+&gt; **肖楠**：用直白的理论讲，你们都是企业里的打工人，能深切感受到：企业从小到大，部门越来越多，以前三五个部门，现在十几个部门，中层干部一大堆，传达效率变低，内部腐败开始出现。企业为解决这些问题要设巡视检查部门，又多一个部门，部门里的人要加工资、提级别。企业扩张往下游或上游做，又多一项业务，要多一个副总裁，又有很多部门。有些生意收入从10亿到100亿没多几个部门，有些企业不需要设那么多副总裁和高管就把生意做成了。从商增角度讲，有些企业是商增把自己拖死的。比如某个行业剩两家互联网大厂，一家效率特别高，另一家山头林立、互相推诿、腐败丛生——后者从一开始就没考虑好企业大了以后商增怎么处理。而另一家基本是高度中央集权，CEO有非常强大的情报部门，知道每件重要事情细入基层是怎么回事。我特别建议大家去读党史，看看这个国家怎么从国民革命时期、抗战时期一直走到现在，组织到今天还能保证这样的活力，这是非常厉害的事情。有些国家也是被商增拖死的，一条铁路修几十年这种事在很多国家都会发生。
+### Q8. 伟大企业的增长曲线
+- **听众**：您讲到伟大企业的增长曲线，能否再具体讲一下？
+&gt; **肖楠**：有些企业你每年看都是线性的，今年增长20、明年15、后年17.5，但站到10年周期看，跟竞争对手之间拉开极大差距。比如快递，疫情时只有顺丰能送，没疫情时看不出来，一下子顺丰的估值和业绩把对手甩出一大截。家电领域也是，过去格力一直是老大，美的在做渠道扁平化、T+3，一直没看到成果，突然疫情来了，美的占有率哗一下就上去了，超过格力。当一些企业在埋头做事、还没体现到报表时，我们往往忽略这些事情未来可能产生的重大影响。这些伟大的企业都是在一些特别特殊的时候拐上去的——平时走在路上大家都好好的，突然来一场雨，发现有一个人带伞了，别人都淋成落汤鸡，就他家有伞，这样的企业特别厉害。
+### Q9. 财富管理行业的投资逻辑
+- **听众**：您讲到财富管理行业，能否具体展开讲一下投资逻辑和投资机会？
+&gt; **肖楠**：财富管理行业这个话题特别大，而且是分层的——顶级富豪、普通中产阶级、中低收入人员的财富管理各有不同的公司和商业模式。我们最早是研究保险时发现有意思的事：某些保险公司一个保险员一单能签七八千的首年保费，有些公司平均一个业务员只有两三千，差距巨大。我们调研了特别厉害的销售和中等销售，发现同样是卖保险，背后的逻辑和机制差异超级大，而这些差异来自公司的结构设置、机构设置、激励机制、文化等。去年发基金时也发现，有些渠道经理过来调研问的问题超级专业，有些渠道经理永远问下半年是涨是跌、明年是牛市还是熊市。财富管理行业最大的逻辑在于财富分布超级不均匀，所以可能有些头部公司一口气拿掉行业增量的绝大部分，比如拿掉70%、80%，第二名只能拿到剩下的20%的80%。在这种特别偏激、幂律分布的行业里，有可能诞生出特别大的企业。很遗憾我们有些产品因为监管和法律规则的原因反而不能投类似标的，但未来合同设置更清晰时，可能会在这方面有所体现。
+### Q10. 企业家精神的观察心得
+- **听众**：您讲到第二第三增长曲线需要卓越的企业家精神，企业家精神是投资中比较艺术的部分，请问您观察这个指标有什么心得和把握？
+&gt; **肖楠**：第一个心得是评判这个因素时要特别小心谨慎，不要乱归因——不要因为一个企业经营成功就说企业家特别厉害，就像不要因为一个基金经理业绩好就说他特别厉害。一定要把所有能归因到数据里客观指标的因素全部归因完，再特别谨慎地评价比较虚的因素。第二个是不要轻易给这些因素定价，绝对不要说因为企业家在，公司就能值多少。我始终强调的是避免错误归因，避免因为对企业家认可而犯投资错误，一定要把底线风险搞好。我们一致同意这个东西不可被定价。技术进步、企业家精神这些比较虚的因素，什么时候考虑？在所有客观归因尽量穷尽以后，再说可能某种程度上一些收益率的归因归到这里面去。第二点，我们只能在有限范围内做两两比较——比如两家公司做同样生意、同样产品，在这种限定条件下比较两个企业家的水平高低、理念先后，找你认可的那一家，仅此而已，不要跨行业、跨业务、跨产品去比较。不要什么事情都归结到企业家身上，一定要谨慎使用“企业家精神”“伟大企业”这些词，在一些特别极端的时候它可能是信仰上的支持，但尽量不要去用。</t>
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>79.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>26252/7638</t>
+          <t>26252/9023</t>
         </is>
       </c>
     </row>
@@ -9176,53 +9224,67 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t># 辩论内容概述
-本次辩论赛围绕“拥有让任何人爱上自己的超能力是否可取”这一脑洞辩题展开。正方（RUC棒辩论队，四辩王新峰）主张超能力能实现真爱，且掌握在爱人手中优于命运安排；反方则认为超能力剥夺被爱者的自由意志，本质是占有和洗脑。双方就爱的本质、自由意志、占有与爱的区别、超能力机制等核心议题进行了多轮交锋，正方最终获胜，获得4分钟小结时间。
-# 核心论点
-辩论围绕“拥有让任何人爱上自己的超能力是否可取”展开，正方主张超能力能实现真爱且掌握在爱人手中优于命运，反方认为其剥夺自由意志、本质是占有和洗脑。双方论点按原文出现顺序如下：
-| 阵营 | 立论框架 | 核心论点 | 支撑论据 |
+          <t># 超能力是否值得提倡辩论赛
+## 辩论内容概述
+本次辩论赛围绕“拥有让任何人爱上自己的超能力是否值得提倡”展开。正方（RUC棒辩论队）主张超能力能成就真爱，认为爱非自由意志产物，超能力可让有情人终成眷属；反方则认为超能力剥夺对方自由意志，本质是占有而非真爱。双方就爱的本质、自由意志、洗脑与真爱、放手之爱等议题展开交锋，正方在承诺环节获胜，获得4分钟小节时间。
+## 核心论点
+辩题为“拥有让任何人爱上自己的超能力是否值得提倡”。正方主张超能力可成就真爱，反方认为其剥夺自由意志、本质是占有。双方论点按原文出现顺序如下表。
+| 阵营 / 立场方 | 立论框架 | 核心论点 | 支撑论据 |
 | --- | --- | --- | --- |
-| 正方 | 爱是超能力，可让不爱的人爱上自己，掌握在爱人手中优于命运 | 爱是超能力，可让不爱的人爱上自己 | 月老、丘比特类比；爱非自由意志产物，如“坠入爱河”而非“跳入爱河” |
-| 反方 | 爱本身没有意志，但爱当中由自己做出决定去爱他同样重要 | 超能力抹杀对方的决定，剥夺自由意志 | 以强奸类比，认为超能力是强迫对方爱上自己 |
-| 正方 | 超能力机制可能是改变自己而非洗脑，使用前提是爱对方 | 超能力与占有不同，使用前提是爱对方 | 改变自己而非洗脑；爱非自由意志产物 |
-| 反方 | 通过超能力获得的爱是占有而非爱，洗脑无法换来真爱 | 超能力导致爱变质，来得太容易 | 洗脑错误，无法换来真爱；爱变质因来得太容易 |
-| 正方 | 超能力掌握在爱人手中优于命运安排 | 不用超能力可能留下遗憾，爱应主动争取 | 月老、丘比特类比；遗憾是爱情的一部分 |
-| 反方 | 超能力剥夺被爱者的选择空间，应保留说“不”的权利 | 超能力剥夺选择空间，应保留说“不”的权利 | 保留希望，保留被爱者的选择空间 |
-# 争议焦点
-- **焦点：超能力是否剥夺自由意志**：正方认为爱非自由意志产物，如“坠入爱河”而非“跳入爱河”，超能力不违背意志；反方认为超能力违背对方意志，类似洗脑和占有，以强奸类比，强调强迫对方爱上自己。
-- **焦点：超能力与占有、爱的区别**：正方认为超能力使用前提是爱对方，与占有不同，机制可能是改变自己而非洗脑；反方认为通过超能力获得的爱是占有而非爱，洗脑无法换来真爱。
-- **焦点：超能力与命运、选择权**：正方认为超能力掌握在爱人手中优于月老等命运安排；反方认为超能力剥夺被爱者的选择空间，应保留说“不”的权利。
-- **焦点：爱的珍惜与变质**：正方认为珍惜程度取决于对待感情的认真程度，而非获得爱的难易程度；反方认为超能力导致爱来得太容易而变质。
-# 环节交锋
-## 开场立论
-- 正方四辩王新峰开场立论，提出爱是超能力，可让不爱的人爱上自己，并以月老、丘比特类比，论证超能力掌握在爱人手中优于命运安排。
-- 反方立论认为爱本身没有意志，但爱当中由自己做出决定去爱他同样重要，超能力抹杀了对方的决定。
-- 正方反驳反方将超能力偷换为月老和丘比特，指出月老和丘比特让有情人终成眷属，而超能力是让不爱的人爱上自己。
-## 质询环节
-- 正方质询反方：超能力是否剥夺自由选择，反方回应超能力操控自由意志，类似洗脑。
-- 正方提出超能力机制可能是改变自己而非洗脑，反方质疑洗脑是否就是爱。
-- 反方以强奸类比，认为超能力是强迫对方爱上自己，正方反驳爱非自由意志产物。
-- 正方提出超能力使用前提是爱对方，与占有不同，反方认为通过占有方式获得的爱是占有而非爱。
-## 自由辩论
-- 正方提出超能力掌握在爱人手中优于命运，反方认为超能力剥夺被爱者的选择空间。
-- 反方提出“放手的爱”概念，正方认为爱应主动争取，不用超能力可能留下遗憾。
-- 正方反驳反方关于爱变质观点，认为珍惜程度取决于对待感情的认真程度。
-- 反方质疑超能力导致爱变质，正方反驳珍惜程度与新鲜感无关。
-## 总结环节
-- 正方总结指出反方未能论证爱是自由意志的产物，超能力机制更可能是改变自己而非洗脑。
-- 正方强调爱的珍惜程度取决于对待感情的认真程度，而非获得爱的难易程度。
-# 结辩与评委点评
-- **正方结辩**：正方总结指出反方未能论证爱是自由意志的产物，超能力机制更可能是改变自己而非洗脑；反方以洗脑、占有等负面类比攻击超能力，但未落到超能力本身。正方强调爱的珍惜程度取决于对待感情的认真程度，而非获得爱的难易程度。
-- **反方结辩**：反方强调超能力剥夺被爱者的选择空间，应保留说“不”的权利；通过超能力获得的爱是占有而非爱，洗脑无法换来真爱。
-- **评委点评**：主持人宣布正方获胜，获得4分钟小结时间。</t>
+| 正方 | 爱非自由意志 | 爱非自由意志产物，超能力可成就真爱 | “坠入爱河”而非“跳入爱河”；类比月老丘比特，可让有情人终成眷属；超能力前提是爱对方 |
+| 反方 | 超能力剥夺自由意志 | 超能力违背对方意志，本质是占有 | 类似洗脑或强奸；获取的爱是占有而非真爱；超能力让爱来得太容易易变质 |
+| 正方 | 超能力机制非洗脑 | 超能力机制更可能非洗脑，而是改变自身或创造符合对方标准的人 | 反方未论证爱是自由意志产物；珍惜取决于认真程度而非难易 |
+## 争议焦点
+1. **【争议焦点】超能力是否剥夺自由意志**
+- **分歧本质**：爱是否由自由意志决定，超能力是否违背对方意志。
+- **正方立场与依据**：爱非自由意志产物，如“坠入爱河”而非“跳入爱河”，超能力可让不爱的人爱上自己。
+- **反方立场与依据**：超能力违背对方意志，强行介入亲密关系，类似洗脑或强奸。
+2. **【争议焦点】超能力获取的爱是占有还是真爱**
+- **分歧本质**：超能力机制是洗脑还是成就真爱。
+- **正方立场与依据**：类比月老丘比特，超能力可让有情人终成眷属，前提是爱对方。
+- **反方立场与依据**：超能力通过洗脑获取爱，是占有而非真爱。
+3. **【争议焦点】超能力是否导致爱变质**
+- **分歧本质**：爱来得太容易是否导致不珍惜。
+- **正方立场与依据**：珍惜取决于认真程度，而非难易。
+- **反方立场与依据**：超能力让爱来得太容易，容易变质。
+4. **【争议焦点】放手之爱与超能力使用**
+- **分歧本质**：是否应保留对方选择空间。
+- **正方立场与依据**：超能力可避免遗憾，掌握在爱你的人手里更好。
+- **反方立场与依据**：超能力让使用者成为世界中心，导致自私。
+## 环节交锋
+### 承诺环节（正方质询）
+**【交锋焦点】超能力是否剥夺自由意志**
+&gt; **质疑方（反方）**：你方觉得我们发动这个超能力是剥夺他的自由选择，有点像给他洗脑。
+&gt; **回应方（正方）**：爱很大程度上是把两个人变成一个部分，互相都要付出，我们才能够变成一个更好的部分。
+**【交锋焦点】超能力获取的爱是占有还是真爱**
+&gt; **质疑方（反方）**：你通过占有的方式获得他的爱，我爱不爱他，而是我对他只是单纯的占有。
+&gt; **回应方（正方）**：我们讲的链接的问题，所以你这个不变质是因为这个爱的太容易了，对吧？
+**【交锋焦点】超能力机制是洗脑还是改变自己**
+&gt; **质疑方（反方）**：你方认为我们的超能力一定是通过给对面精神洗脑，强行剥夺他自由意志的方式来达成我方不可告人的目的。
+&gt; **回应方（正方）**：这个超能力它发挥机制的原因，更可能不是像你刚才说的，直接通过洗脑精神控制的方式。
+### 自由辩论环节
+**【交锋焦点】超能力是否类似强奸**
+&gt; **质疑方（反方）**：强奸这件事情叫做违背妇女意志，强行发生性关系，而今天在面对情况当中，为什么是违背对方意志，强行介入亲密关系。
+&gt; **回应方（正方）**：发生性关系这件事情，由我们朋友来决定要不要给你删除。但是你能不能爱上你这件事情，跟自由意志无关。
+**【交锋焦点】超能力是否剥夺选择空间**
+&gt; **质疑方（反方）**：我们一定要保留一个希望，一定要保留一个被爱的那个人的选择空间，只要他有权利，他有余地，他有机会说不。
+&gt; **回应方（正方）**：如果这个时候真的是相处之后，我也觉得我跟他没有办法在一起，那这个时候爱的信号就是我会再用这个超能力。
+### 总结环节（正方小结）
+**【交锋焦点】超能力机制与爱的本质**
+&gt; **立论方（正方）**：爱一个人就是自己意志的产物，到目前为止，对方都没有向我们论证，在您方的世界里，我只要意志在爱这个人，到底发生怎样的作用。
+&gt; **反驳方（反方）**：你方天然就认为你一定是通过洗脑来获取他的爱。第一个问题，洗脑真的是爱吗？第二期呢我真的能获得爱吗？
+## 结辩与评委点评
+1. **正方结辩**：正方强调超能力机制更可能非洗脑，而是改变自身或创造符合对方标准的人，并指出反方未论证爱是自由意志产物。正方认为珍惜取决于认真程度，超能力可避免遗憾，掌握在爱你的人手里更好。
+2. **反方结辩**：反方指出超能力让使用者成为世界中心，导致自私，剥夺对方选择空间。反方认为超能力获取的爱是占有而非真爱，类似洗脑或强奸。
+3. **评委点评**：正方在承诺环节获胜，获得4分钟小节时间。</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>42.7</v>
+        <v>41.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12403/1947</t>
+          <t>12403/2202</t>
         </is>
       </c>
     </row>
@@ -9578,41 +9640,43 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t># 就诊概况
-患者为结肠癌术后多发转移患者，本次为家属代述复诊。核心主诉：患者确诊结肠癌后行切除手术及8期化疗，复查发现肝转移，去年9月行肝消融及乳腺结节切除，术后行紫杉醇化疗，仅第一次有效，后因肝功能不佳停药3个月；3月底复查发现肝、肺、腹膜再次转移，4月CT示肝上亦有转移，上月经肠镜未见异常但PET显示有转移，怀疑肠镜漏诊。本次就诊要解决的问题：明确后续治疗方案，医生建议以全身系统治疗为主，需做二次基因检测和免疫评估，局部介入暂不作为主要方案。
-# 病史与背景
-- **确诊与手术**：患者确诊结肠癌后做了切除手术，切肠时可能切得不干净，存在腹膜转移。
-- **化疗史**：术后做了8期化疗，后因肝功能不行停药3个月。
-- **转移与局部治疗**：复查发现肝转移，去年9月做了肝消融和乳腺结节切除，术后行紫杉醇化疗，仅第一次有效。
-- **近期复查**：3月底复查发现肝、肺、腹膜再次转移，4月份CT显示肝上也有转移。
-- **肠镜与PET**：上个月肠镜显示没事，但PET显示有转移，怀疑肠镜做得不好。
-- **既往肠胃情况**：患者多年来吃东西容易中毒，比如吃海鲜就爱上吐下泻，一直觉得肠胃比较弱。
-# 诊断与检查结果
-医生初步判断：当前主要问题是全身系统治疗，局部介入暂不作为主要方案，除非肿瘤增大至10公分危及生命。关键检查结果：4月份CT显示肝上也有转移；上月经肠镜未见异常，但PET显示有转移，怀疑肠镜漏诊。医生对结果的说明：基因检测非常重要，首次检测可能不全面，且化疗后基因可能变化，建议做二次基因检测；免疫细胞状态也很重要，建议做免疫评估。家属疑问：是否需要再做核磁检查，家属表示不想做太多检查，医生未明确回答。
-# 治疗方案与医嘱
-- **检查安排**：建议做二次基因检测，可在肿瘤医院做，大概有3个学科；建议做免疫评估，了解免疫细胞状态。
-- **治疗方案**：当前以全身系统治疗为主，包括化疗、靶向、免疫，可联合使用，需根据基因检测结果选药。
-- **生活方式**：建议调整患者状态，提升免疫力。
-- **用药说明**：提到四联康，用于肚子不好时，但患者未关注。
+          <t># 结肠癌术后转移患者后续治疗方案讨论
+## 就诊概况
+患者为结肠癌术后患者，性别、年龄、职业原文未提及。本次为家属代述复诊，讨论后续治疗方案。核心主诉：患者确诊结肠癌后行切除手术及8期化疗，复查发现肝转移，去年9月行肝消融及乳腺结节切除，因切肠可能不净存在腹膜转移；消融及切除后行紫荆化疗，首次后因肝功能不佳停用靶向药，停药3个月；3月底复查发现肝、肺、腹膜新转移，4月CT示肝上及背部各有一块病灶，上个月肠镜显示无异常但派特CT显示有转移。本次就诊要解决的问题：明确后续治疗方案，家属询问除化疗和靶向外有无更有效手段，医生建议以全身系统治疗为主，暂不考虑局部介入。
+## 病史与背景
+1. **确诊与手术**：患者确诊结肠癌后做了结肠癌切除手术，做了8期化疗。
+2. **转移与局部治疗**：复查发现肝转移，去年9月做了肝消融和乳腺结节切除；切肠时可能切得不干净，存在腹膜转移。
+3. **化疗与停药**：消融和切除后做了紫荆化疗，但第一次后因肝功能不行停用靶向药，停药3个月。
+4. **近期复查**：3月底复查发现肝、肺、腹膜又有转移；4月份CT显示肝上有一块，背上也有一块；上个月肠镜显示没事，但派特CT显示有转移，家属提及可能肠镜做得不好。
+5. **既往肠胃情况**：患者多年来吃东西容易中毒，比如吃海鲜就爱上吐下泻，家属一直觉得他肠胃比较弱。
+## 诊断与检查结果
+1. **诊断结论**：患者为结肠癌术后，出现肝转移、腹膜转移，近期复查发现肝、肺、腹膜新转移，考虑为疾病进展，需进一步明确转移范围及治疗依据。
+2. **检查结果**：4月份CT显示肝上有一块，背上也有一块；上个月肠镜显示无异常，但派特CT显示有转移，家属提及可能肠镜做得不好。
+3. **医生说明**：医生指出当前主要问题是全身系统治疗，局部介入不是主要问题；系统治疗包括化疗、靶向、免疫，可联合使用，靶向加免疫可能协同（1+1大于2）。
+4. **家属疑问**：家属询问除了化疗和靶向还有无更有效手段，医生建议做二次基因检测和免疫评估；家属询问是否需要再做核磁检查，因不想做太多检查，医生表示尊重家属意愿。
+## 治疗方案与医嘱
+1. **检查安排**：建议做二次基因检测，可在肿瘤医院进行，约3个学科；建议做免疫评估，但方案由家属决定。
+2. **治疗方案**：当前以全身系统治疗为主，暂不考虑局部介入；系统治疗包括化疗、靶向、免疫，可联合使用，靶向加免疫可能协同。
+3. **生活方式与饮食**：建议家属让患者调整好状态，提升免疫力；提到四联康，肚子不好时可用，但原文未明确为医嘱。
+4. **复诊安排**：原文未明确具体复诊时间。
 | 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
 | --- | --- | --- | --- | --- |
-| 紫杉醇 | — | — | 化疗 | 仅第一次有效，后因肝功能不行停药 |
-| 四联康 | — | — | 口服 | 用于肚子不好时，患者未关注 |
-# 复诊与预警信号
-## 复诊与随访安排
-- **复查项目**：建议做二次基因检测和免疫评估。
-## 预警信号
-- ⚠️ 若肿瘤增大至10公分危及生命，需考虑局部处理。
-## 需要观察的变化
-- 监测肝功能，因化疗后肝功能不行导致停药3个月。</t>
+| 四联康 | — | — | — | 原文提及肚子不好时可用，但未明确为医嘱 |
+## 复诊与预警信号
+### 复诊与随访安排
+1. **复查项目**：原文未明确具体复诊时间，但提到3月底复查发现新转移，4月CT检查，上个月肠镜；医生建议做二次基因检测和免疫评估。
+### 预警信号
+1. **需关注症状**：原文未明确列出需立即就医的预警症状，但提到患者肚子疼、上吐下泻等既往症状。
+### 需要观察的变化
+1. **监测内容**：原文未明确列出需观察的变化，但医生建议家属让患者调整好状态，提升免疫力。</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>43.3</v>
+        <v>38.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>7063/1163</t>
+          <t>7063/1436</t>
         </is>
       </c>
     </row>
@@ -9774,44 +9838,53 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t># 产品概况
-海尔洗衣机创新发布会正式推出洗干集成新物种迭代H2，由海尔为中国家庭打造。发布会以“纯净永无止境”为主题，针对中国80%用户将洗烘套装在阳台叠放使用带来的不便，推出专为客阳一体空间设计的一体集成机身，高度降为167厘米，超薄机身可嵌入60厘米标准橱柜，全平不突出。H2以屏幕为核心，可操控洗涤、烘干和护理等多种模式，搭载灵犀洗烘联动、原创双擎热泵技术、3D透视烘干、精华洗2.0、空净过滤系统等创新技术，旨在让用户告别晾晒、享受整洁有序的新阳台生活方式。
-# 市场定位与目标用户
-目标人群为中国家庭，尤其是追求整洁有序新阳台的年轻人、养宠家庭和有宝宝的家庭。典型使用场景为客阳一体风格的阳台，用户在此休闲娱乐、健身、社交，悬挂晾衣既不美观又占空间。与欧洲家庭有独立洗衣房、洗烘套装并排摆放不同，中国80%的用户将洗烘套装在阳台叠放使用，存在屏幕过高、开门方向相反、水盒太高太沉等不便。H2针对这一痛点，采用一体集成机身、同向开门、无水盒设计，并强调与洗烘套装“貌合神离”相比，H2独有的灵犀洗烘联动实现数据共享，让烘干和洗涤无缝连接。
-# 核心卖点与技术参数
-## 一体集成设计
-- 一体集成机身，解决洗烘套叠放带来的震动等安全隐患，高度降为167厘米，不用踮脚即可操作。
-- 超薄机身完美嵌入60厘米标准橱柜，全平不突出，让阳台更美观整洁。
-- 同向开门，尊重使用习惯，取放衣物流畅自如；采用无水盒设计，无需手动倒水。
-## 智慧互联
-- 以屏幕为核心，可全面操控洗涤、烘干和护理等多种模式，是H2全新升级的智慧大脑。
-- 独有的灵犀洗烘联动实现数据共享，洗涤结束前上桶提前15分钟主动预热，缩短烘干时长。
-## 烘干技术
-- 搭载原创双擎热泵技术，大件烘干不缠绕。
-- 首次引入行业领先黑科技3D透视烘干，羽绒服、水洗被可一次烘透，免去二次晾晒。
-## 洗涤技术
-- 升级精华洗2.0，39分钟洗净一周衣物。
-- 新鲜净水漂洗减少洗衣液残留，对残留泡沫敏感的人是福音。
-## 健康守护
-- 搭载空净过滤系统，去除衣物线屑和毛絮，适合养宠家庭，洗衣无残留、干衣无毛絮，适合有宝宝的家庭。
-- 搭载三台变频电机，洗涤、甩干、烘干全过程噪音低，享受安静陪伴时光。
+          <t># 海尔洗干集成新物种叠代H2创新发布会
+## 产品概况
+海尔洗衣机创新发布会正式推出洗干集成新物种叠代H2，由海尔为中国家庭打造，发布会在海尔洗衣机用户研发中心举行，主题为“纯净永无止境”。主讲人带领观众体验海尔洗衣机的科技创新之路，共同见证洗干集成新物种的诞生。针对中国80%的用户将洗烘套装在阳台叠放使用带来的不便，H2专为客阳一体的空间设计，主打一体集成、超薄平嵌与智慧联动，旨在让阳台更加美观整洁，让用户享受“真香”的生活方式。H2以屏幕为核心实现洗涤、烘干、护理多模式操控，搭载灵犀洗烘联动、原创双擎热泵技术、3D透视烘干、精华洗2.0、空净过滤系统与三台变频电机，覆盖从洗衣、烘干到护理的全流程体验。
+## 市场定位与目标用户
+1. 目标人群：中国家庭，尤其是向往整洁有序新阳台的用户，包括在阳台休闲娱乐、健身、社交的年轻人，以及养宠家庭和有宝宝的家庭。
+2. 典型使用场景：客阳一体风格的中国家庭阳台；原文给出地域差异背景——在欧洲滚筒洗衣机发源地，许多家庭有独立洗衣房，洗烘套装并排摆放，而中国80%的用户把洗烘套装放在阳台叠放使用，带来屏幕过高、开门方向相反、水盒太高太沉等操作不便。
+3. 市场竞争策略：针对中国用户阳台叠放痛点，推出洗干集成新物种叠代H2，以一体集成机身、超薄平嵌、灵犀洗烘联动、3D透视烘干等差异化卖点切入市场；与洗烘套装的“貌合神离”不同，H2强调上下桶默契配合的智慧联动体验。
+## 核心卖点与技术参数
+### 一体集成设计
+1. 一体集成机身，解决洗烘套装叠放带来的震动等安全隐患。
+2. 高度降为167厘米，不用踮着脚尖也能轻松操作。
+3. 超薄机身完美嵌入60厘米标准橱柜，全平不突出，让阳台更加美观整洁。
+4. 同向开门，尊重用户使用习惯，取放衣物流畅自如。
+5. 采用无水盒设计，无需手动倒水。
+### 智慧联动
+1. 以屏幕为核心，全面操控洗涤、烘干和护理等多种模式。
+2. 搭载H2全新升级的智慧大脑，利用中枢神经式的智能网络，让上下桶默契配合。
+3. 独有的灵犀洗烘联动，实现数据共享，让烘干和洗涤无缝连接。
+4. 洗涤结束前，上桶提前15分钟主动预热，进一步缩短烘干时长。
+### 烘干技术
+1. 搭载原创双擎热泵技术，大件烘干不缠绕。
+2. 首次引入行业领先黑科技3D透视烘干，羽绒服、水洗被都可以一次烘透，免去二次晾晒的烦恼。
+### 洗涤技术
+1. 升级精华洗2.0，能够激活洗衣液，39分钟洗净一周衣物。
+2. 新鲜净水漂洗，减少洗衣液残留，对残留泡沫敏感的人是最大的福音。
+### 健康与静音
+1. 搭载空净过滤系统，能够轻松去除衣物的线屑和毛絮，更适合养宠物的用户；洗衣无残留、干衣无毛絮，特别适合有宝宝的家庭。
+2. 搭载三台变频电机，洗涤、甩干、烘干全过程噪音都很低，让用户享受安静陪伴的时光。
 | 维度 | 本产品 | 上代/竞品 | 提升 |
 | --- | --- | --- | --- |
-| 一体集成设计 | 一体集成机身，高度167厘米，超薄嵌入60厘米标准橱柜，全平不突出，无水盒设计 | 洗烘套装叠放，屏幕过高、开门方向相反、水盒太高太沉 | 解决震动安全隐患，操作更便捷，阳台更美观整洁 |
-| 智慧互联 | 灵犀洗烘联动，数据共享，上桶提前15分钟主动预热 | 洗烘套装貌合神离，无联动 | 烘干与洗涤无缝连接，缩短烘干时长 |
-| 烘干技术 | 原创双擎热泵技术，3D透视烘干，大件不缠绕，一次烘透 | 未提及 | 羽绒服、水洗被免二次晾晒 |
+| 一体集成设计 | 一体集成机身，高度167厘米，超薄嵌入60厘米标准橱柜，全平不突出，同向开门，无水盒设计 | 洗烘套装叠放，屏幕过高、开门方向相反、水盒太高太沉 | 解决叠放震动等安全隐患，操作更便捷，阳台更美观整洁 |
+| 智慧联动 | 灵犀洗烘联动，上桶提前15分钟主动预热 | 洗烘套装貌合神离，无联动 | 烘干与洗涤无缝连接，缩短烘干时长 |
+| 烘干技术 | 原创双擎热泵技术，3D透视烘干 | 未提及 | 大件烘干不缠绕，羽绒服、水洗被一次烘透 |
 | 洗涤技术 | 精华洗2.0，39分钟洗净一周衣物，新鲜净水漂洗 | 未提及 | 洗衣更高效，减少洗衣液残留 |
-| 健康守护 | 空净过滤系统去除线屑毛絮，三台变频电机低噪音 | 未提及 | 适合养宠家庭和有宝宝家庭，安静陪伴 |
-# 定价与发售信息
-10kg 3D透视烘干款定价12998元，10kg净净双擎热泵款定价10998元。</t>
+| 健康与静音 | 空净过滤系统，三台变频电机 | 未提及 | 去除线屑毛絮，全过程低噪音 |
+## 定价与发售信息
+1. 10kg 3D透视烘干款定价12998元。
+2. 10kg净净双擎热泵款定价10998元。
+3. 定价策略：为这款平嵌超薄产品拿出诚意满满的定价。</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>29.1</v>
+        <v>46.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7311/1402</t>
+          <t>7311/1685</t>
         </is>
       </c>
     </row>
@@ -10013,80 +10086,85 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t># 全文摘要
-中共巢湖市银屏镇白母山村芦塘支部召开党员大会改选支部委员会，支部共有正式党员8名，因病请假1名，实到有选举权党员7名，符合法定人数；银屏镇党委组织委员钱小丽到会讲话。会议围绕上届工作报告审议、通过选举办法与候选人名单、候选人竞职演说、选举新一届支部委员及书记、委员分工等议程展开。上届报告总结三年工作并指出不足，党员鼓掌通过；大会经无记名投票选举卢燕娇、辛东升、杜军强为新一届支部委员，卢燕娇当选支部书记，辛东升负责组织宣传、杜军强负责纪检，结果报镇党委批准。关键数字：支部正式党员8名、实到7名；三年收缴党费2640元上交；委员选举发出并收回选票各7张，卢燕娇、杜军强各得6票；书记选举发出并收回选票各3张，卢燕娇得3票。
-# 分段速览
-## 00:00:13-00:05:26 会议开幕与上届工作报告
-会议开始，主持人宣布应到有选举权党员8名、实到7名，符合法定人数。镇党委组织委员钱小丽到会讲话，就换届选举提出三点意见。上届支部委员会作工作报告，总结三年工作并指出不足，党员表示满意，鼓掌通过。
-## 00:05:55-00:10:43 通过选举办法、候选人名单与工作人员名单
-杜军晓宣读党员大会选举办法草案，经举手表决一致通过。随后宣读镇党委批复，确定委员候选人4名、书记候选人1名，经鼓掌通过。提议贾淑玲担任监票人，经举手表决一致通过，并宣布计票人员名单。
-## 00:10:43-00:14:45 候选人竞职演说
-四位候选人依次进行竞职演说。卢燕娇介绍个人情况并承诺加强支部建设、推动村集体经济发展、抓好民生工程；杜军强表示可更好担当桥梁纽带角色；辛东升承诺群众有困难随叫随到、严格要求自己；秦磊阐述自身责任心和思想觉悟等有利条件。
-## 00:14:45-00:21:17 选举新一届支部委员会委员
-清点人数确认实到7名，达到应到会4/5，可以进行选举。发出并收回选票各7张，选举有效。计票结果：卢燕娇6票、杜军强6票、秦磊2票。卢燕娇、辛东升、杜军强当选为新一届支部委员会委员。
-## 00:21:17-00:28:42 选举支部书记并分工
-召开第一次支委会，宣读选举办法，确定卢燕娇为书记候选人，经鼓掌通过。提议辛东升担任监票人和计票人，经举手表决通过。发出并收回选票各3张，卢燕娇得3票，当选为党支部书记。分工明确：辛东升负责组织宣传工作，杜军强负责纪检工作。
-## 00:28:42-00:29:56 新当选支委代表发言与大会闭幕
-新当选支委代表卢燕娇发言，感谢信任，表示将抓好学习、制度、服务型支部建设。主持人宣布大会完成各项任务，换届选举大会圆满结束。
-# 要点梳理
-## 会议开场与镇党委讲话
-- 支部共有正式党员8名，因病请假1名，实到有选举权党员7名，符合法定人数，可以开会。
-- 银屏镇党委组织委员钱小丽应邀到会，代表镇党委就换届选举提出三点意见：充分认识大会重要意义、正确行使选举权严格把握选举要求、服从大局严格遵守选举纪律。
-- 主持人宣布中共巢湖市银屏镇白母山村芦塘支部委员会换届选举党员大会开始，全体起立奏国歌。
-## 上届支部委员会工作报告
-- 上届支部委员会作三年工作报告，提请党员审议，党员表示「报告非常好，非常满意」，鼓掌通过。
-- 三年间新发展党员一名，按规定收缴党费2640元上交上级党组织。
-- 三年工作包括：加强思想政治建设和理论学习；严格实行支部议事决策制度、民主生活会制度、民主评议党员制度、党员联系服务群众制度；开展「两学一做」学习教育常态化制度化和「讲严例」专题警示教育活动；通过党内会议、公开栏等形式公开年度工作计划、党风廉政建设、党费收缴等内容；抓好党风党纪教育。
-- 上届支部指出存在不足：党建工作制度不够完善；党员主体意识尚需提高，个别党员干部顶推中心服务大局的意识不强；党支部对党员的教育管理监督还不够深入。
-## 通过党员大会选举办法
-- 杜军晓宣读选举办法草案，经举手表决一致通过。
-- 选举中共如堂支部委员会委员三名，候选人四名，差额不少于应选名额20%。
-- 选举采用无记名投票方式，先差额选举支部委员会委员，再从当选委员中等额选举书记，两次选举分别投票、计票和宣布结果。
-- 参加会议有选举权的正式党员必须超过应到会党员的4/5方可进行选举；收回选票数等于或少于发出选票数选举有效，多于则无效。
-- 候选人得赞成票超过实到会选举人数半数方可当选；得票超过半数的候选人多于应选名额时以得票多少为序取足；最后几名得票相等时重新投票；超过半数候选人少于应选名额时不足名额在未过半数候选人中重新选举产生，接近应选名额时可减少名额不再选举。
-- 选举设监票人一名，选举工作人员两名，由会议主持人指定，在监票人监督下工作；支部委员候选人不能担任监票人和工作人员。
-## 通过支委候选人名单
-- 杜军晓宣读银屏镇党委批复，批复日期为2019年10月12日。
-- 委员候选人预备人选4名：卢燕娇、辛东升、杜军强、秦磊；书记候选人预备人选卢艳娇。
-- 委员实行差额选举，差额一人；书记实行等额选举；选举结果报镇党委批准。
-- 候选人名单经鼓掌通过。
-## 通过选举工作人员名单
-- 提议贾淑玲同志担任监票人，经举手表决一致通过。
-- 宣布计票人员为黄婷丽、刘彩云。
-## 候选人竞职演说
-- **卢燕娇**：1993年9月出生，2014年4月加入中国共产党；承诺加强支部建设，落实好三会一课、组织生活会和民主评议党员等基本制度，结合「两学一做」常态化制度化开展好「不忘初心、牢记使命」主题教育；推动村集体经济发展，发挥党组织和党员在产业培育、农民增收、脱贫攻坚方面的示范引领和帮扶帮带作用；抓好各项民生工程落实，把群众满意度作为衡量工作标准。
-- **杜军强**：从事村委会工作，平时与各类人群有工作接触；承诺如当选可更好担当主带角色，向基层党员传达广大党员和群众的利益诉求，为党员和群众服务。
-- **辛东升**：承诺群众有困难随叫随到；严格要求自己做合格党员干部，不该吃的饭不吃、不该拿的钱不拿、不该做的事不做；圆满完成上级党组织分配的各项任务。
-- **秦磊**：自述有较强责任心，能认真参加支部组织的理论学习，组织交给的任务不折不扣完成；有较高思想觉悟，利用业余时间学习；承诺配合上级和各项工作，全体党员团结一心，不计较个人得失，当一名合格的支部委员。
-## 选举新一届支部委员会委员
-- 应到会有选举权党员8名，因病请假1名，实到7名，达到应到会选举权党员人数的4/5，可以进行选举。
-- 监票人员检查并封好票箱，发出选票7张，收回选票7张，选举有效。
-- 计票结果：卢燕娇6票、杜军强6票、秦磊2票。
-- 根据大会选举办法规定，卢燕娇、辛东升、杜军强当选为新一届中共巢湖市银屏镇白母山村芦塘支部委员会委员。
-## 选举新一届支部委员会书记及委员分工
-- 召开第一次支部委员会全体会议，宣读第一次全体会议选举办法草案，办法规定支部书记采用等额选举，实到会委员必须超过应到会委员的4/5方可选举。
-- 书记候选人建议名单为卢燕娇，主持人介绍其工作认真负责、上届支委会在其带领下各项工作取得较好成绩，建议继续担任支部书记，经鼓掌通过。
-- 提议辛东升担任监票人和计票人，经举手表决一致通过。
-- 发出选票3张，收回选票3张，卢燕娇得3票，当选为新一届党支部书记。
-- 委员分工：辛东升负责组织宣传工作，杜军强负责纪检工作。
-## 新当选支委代表发言
-- 卢燕娇代表新当选三位支部委员感谢信任和支持，表示将抓好支部学习工作、争创学习型支部，认真组织开展「不忘初心、牢记使命」主题教育；抓好支部制度建设工作、争创制度型支部；完善基层党组织建设、争创服务型支部，严格按照《中国共产党党支部工作条例（试行）》加强支部建设。
-- 主持人宣布中共巢湖市银屏镇白母山村芦塘支部委员会换届选举大会圆满结束，全体起立奏国际歌。
-## 结论与决定
-- 通过党员大会选举办法。
-- 通过支委候选人名单：卢燕娇、辛东升、杜军强、秦磊。
-- 通过监票人建议名单：贾淑玲担任监票人，黄婷丽、刘彩云任计票人。
-- 卢燕娇、辛东升、杜军强当选为新一届支部委员会委员。
-- 卢燕娇当选为新一届党支部书记，选举结果以报镇党委批准为准。
-- 辛东升负责组织宣传工作，杜军强负责纪检工作。</t>
+          <t># 芦塘支部党员大会换届选举
+## 全文摘要
+中共巢湖市银屏镇白母山村芦塘支部召开党员大会，改选支部委员会。支部共有正式党员8名，因病请假1名，实到有选举权党员7名，符合法定人数；银屏镇党委组织委员钱小丽到会讲话，提出充分认识换届意义、正确行使选举权、严格遵守选举纪律三点意见。会议围绕上届工作报告、选举办法、候选人名单、选举工作人员、竞职演说、委员选举、书记选举及分工等议程展开。上届支部报告指出3年来新发展党员1名、收缴党费2640元上交，并坦承党建工作制度不够完善、党员主体意识需提高、教育管理监督不够深入等问题，报告获鼓掌通过。大会依次通过选举办法草案、支委候选人名单（卢燕娇、辛东升、杜军强、秦磊，镇党委2019年10月12日批复）及监票人贾淑玲、计票人黄婷丽和刘彩云名单，四位候选人发表竞职演说。经无记名投票，发出并收回选票7张，卢燕娇、杜军强各得6票、秦磊得2票，卢燕娇、辛东升、杜军强当选新一届支部委员；随后第一次支委会发出并收回选票3张，卢燕娇全票当选支部书记，辛东升负责组织宣传、杜军强负责纪检，选举结果报镇党委批准。
+## 分段速览
+### 00:00:13-00:05:12 会议开幕与上届工作报告
+会议开始，主持人宣布中共巢湖市银屏镇白母山村芦塘支部党员大会召开，改选支部委员会。支部共有正式党员8名，因病请假1名，实到有选举权党员7名，符合法定人数。镇党委组织委员钱小丽到会讲话，提出三点意见：充分认识换届意义、正确行使选举权、严格遵守选举纪律。上届支部委员会作工作报告，总结三年工作并指出存在问题，与会党员表示满意，鼓掌通过。
+### 00:05:55-00:10:43 通过选举办法、候选人名单与工作人员名单
+杜军晓宣读党员大会选举办法草案，规定选举委员3名、候选人4名，差额不少于应选名额20%，采用无记名投票，先差额选委员再等额选书记。与会党员举手表决一致通过。随后宣读镇党委批复，公布候选人名单为卢燕娇、辛东升、杜军强、秦磊，书记候选人为卢燕娇，鼓掌通过。提议贾淑玲任监票人，黄婷丽、刘彩云任计票人，表决通过。
+### 00:11:34-00:14:45 候选人竞职演说
+四位候选人依次发表竞职演说。卢燕娇承诺加强支部建设、推动村集体经济发展、抓好民生工程；杜军强表示可担当桥梁纽带作用，为党员和群众服务；辛东升承诺群众有困难随叫随到、严格要求自己、完成上级任务；秦磊表示有责任心、思想觉悟高，配合上级工作、不计较个人得失。
+### 00:14:45-00:21:17 选举新一届支部委员会委员
+清点人数确认实到有选举权党员7名，达到应到会人数4/5，可以进行选举。检查票箱、分发选票后，党员填写并投票。发出选票7张，收回7张，选举有效。计票结果：卢燕娇6票、杜军强6票、秦磊2票。卢燕娇、辛东升、杜军强当选为新一届支部委员会委员。
+### 00:21:17-00:28:42 选举书记及委员分工
+召开第一次支部委员会全体会议，宣读选举办法草案，通过书记候选人建议名单。辛东升任监票人和计票人，发出选票3张、收回3张，卢燕娇得3票，当选为党支部书记。分工明确：辛东升负责组织宣传工作，杜军强负责纪检工作。选举结果报镇党委批准。
+### 00:28:42-00:29:56 新当选支委代表发言与会议闭幕
+新当选支委代表卢燕娇发言，感谢信任与支持，表示将抓好支部学习、制度建设和基层党组织建设，争创学习型、制度型、服务型支部。主持人宣布换届选举大会圆满结束，全体起立奏国际歌。
+## 要点梳理
+### 会议开幕与镇党委讲话
+1. 中共巢湖市银屏镇白母山村芦塘支部召开党员大会，改选支部委员会；支部共有正式党员8名，因病请假1名，实到有选举权党员7名，符合法定人数。
+2. 银屏镇党委组织委员钱小丽到会讲话，提出三点意见：充分认识换届选举重要意义、正确行使选举权严格把握选举要求、服从大局严格遵守选举纪律。
+3. 钱小丽希望新一届班子加强学习、提高素质，发挥战斗堡垒作用，带领全村党员和群众将白母山村建设得更加美好。
+### 上届支部委员会工作报告
+1. 上届支部委员会作工作报告，总结3年来工作：认真落实党建工作各项要求，发挥党支部战斗堡垒作用和党员模范带头作用。
+2. 大力加强思想政治建设和理论学习，努力提高党员干部思想理论水平。
+3. 着力抓好党支部建设工作，严格实行支部议事决策制度、民主生活会制度、民主评议党员制度、党员联系服务群众制度；新发展党员1名，按规定收缴党费2640元上交上级党组织。
+4. 扎实开展主题教育活动，认真开展“两学一做”学习教育常态化制度化和“讲严立”专题警示教育活动。
+5. 积极开展党务公开，将年度工作计划、党风廉政建设、党费收缴等内容通过党内会议、公开栏等形式公开。
+6. 认真抓好党风党纪教育，筑牢拒腐防变思想防线，落实党风廉政建设各项责任。
+7. 指出存在问题：党建工作制度不够完善；党员主体意识尚需提高，个别党员干部围绕中心服务大局意识不强；党支部对党员教育管理监督不够深入。
+8. 与会党员对报告表示满意，鼓掌通过。
+### 通过选举办法
+1. 杜军晓宣读党员大会选举办法草案：根据《中国共产党章程》和《中国共产党基层组织选举工作暂行条例》制定。
+2. 大会选举中共芦塘支部委员会委员3名，候选人4名，差额不少于应选名额20%；候选人按姓氏笔画为序排列，采用无记名投票方式。
+3. 先差额选举支部委员会委员，再从当选委员中等额选举书记，两次选举分别投票、计票和宣布结果。
+4. 参加会议有选举权的正式党员必须超过应到会党员的4/5方可进行选举；收回选票等于或少于发出选票选举有效，多于发出选票选举无效。
+5. 候选人得到赞成票超过实到会选举人数的半数方可当选；得票超过半数的候选人多于应选名额时以得票多少为序取足；票数相等时重新投票。
+6. 与会党员无不同意见，举手表决一致通过选举办法草案。
+### 通过候选人名单
+1. 杜军晓宣读银屏镇党委批复（2019年10月12日）：同意新一届支部委员会委员候选人预备人选4名——卢燕娇、辛东升、杜军强、秦磊；书记候选人预备人选卢燕娇。
+2. 委员实行差额选举（差额1人），书记实行等额选举，选举结果报镇党委批准。
+3. 与会党员无不同意见，鼓掌通过候选人名单。
+### 通过选举工作人员名单
+1. 提议贾淑玲担任监票人，经举手表决一致通过。
+2. 宣布计票人员名单：黄婷丽、刘彩云。
+### 候选人竞职演说
+1. 卢燕娇（1993年9月出生，2014年4月入党）承诺：加强支部建设，落实“三会一课”、组织生活会和民主评议党员等制度，扎实开展“不忘初心、牢记使命”主题教育；推动村集体经济发展，发挥党组织和党员在产业培育、农民增收、脱贫攻坚方面的示范引领和帮扶帮带作用；抓好各项民生工程落实，把群众利益作为工作首要职责、群众满意度作为衡量工作标准。
+2. 杜军强（从事村委会工作）承诺：担当基层党组织与党员群众之间的桥梁纽带，向基层党员传达广大党员和群众的利益诉求，为党员和群众服务。
+3. 辛东升承诺：群众有困难随叫随到；严格要求自己，不该吃的饭不吃、不该拿的钱不拿、不该做的事不做；圆满完成上级党组织分配的各项任务。
+4. 秦磊承诺：有较强责任心，认真参加支部理论学习，不折不扣完成组织交给的任务；有较高思想觉悟，利用业余时间学习；配合上级工作，全体党员团结一心，不计较个人得失。
+### 选举新一届支部委员会委员
+1. 清点人数：应到会有选举权党员8名，因病请假1名，实到7名，达到应到会人数4/5，可以进行选举。
+2. 监票人员检查并封好票箱，分发选票；填写选票一律用钢笔，字迹要清楚。
+3. 投票顺序：监票人员、计票人员先投票，然后全体党员依次投票。
+4. 计票结果：实到会有选举权党员7名，发出选票7张，收回选票7张，选举有效；卢燕娇6票，杜军强6票，秦磊2票。
+5. 根据大会选举办法，卢燕娇、辛东升、杜军强当选为新一届中共巢湖市银屏镇白母山村芦塘支部委员会委员。
+### 选举新一届支部委员会书记及委员分工
+1. 召开第一次支部委员会全体会议，宣读选举办法草案：选举产生支部书记1人，采用无记名投票、等额选举；实到会委员必须超过应到会委员4/5方可选举；候选人得到赞成票超过实到会委员半数当选。
+2. 介绍书记候选人建议名单：卢燕娇同志工作认真负责，上届支委会在其带领下各项工作取得较好成绩，建议继续由卢燕娇担任支部书记；与会委员鼓掌通过。
+3. 通过选举工作人员名单：辛东升担任监票人和计票人，举手表决一致通过。
+4. 选举结果：发出选票3张，收回选票3张，卢燕娇得3票，当选为新一届党支部书记。
+5. 委员分工：辛东升负责组织宣传工作，杜军强负责纪检工作。
+6. 新当选支委代表表态：抓好支部学习工作，争创学习型支部，认真组织开展“不忘初心、牢记使命”主题教育；抓好支部制度建设工作，争创制度型支部；完善基层党组织建设，争创服务型支部，严格按照《中国共产党支部工作条例（试行）》加强支部建设。
+7. 主持人宣布换届选举大会圆满结束，全体起立奏国际歌。
+### 结论与决定
+1. 通过上届支部委员会工作报告。
+2. 通过党员大会选举办法草案。
+3. 通过支委候选人名单：卢燕娇、辛东升、杜军强、秦磊。
+4. 通过选举工作人员名单：贾淑玲为监票人，黄婷丽、刘彩云为计票人。
+5. 卢燕娇、辛东升、杜军强当选为新一届支部委员会委员。
+6. 卢燕娇当选为党支部书记，选举结果报镇党委批准。
+7. 辛东升负责组织宣传工作，杜军强负责纪检工作。</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>56.9</v>
+        <v>52.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8414/3434</t>
+          <t>8414/3954</t>
         </is>
       </c>
     </row>
@@ -10222,128 +10300,97 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t># 报告概况
-2024年政府工作报告由国务院总理代表国务院向全国人民代表大会作报告，请予审议，并请全国政协委员提出意见。报告回顾2023年工作，提出2024年经济社会发展总体要求、主要预期目标和政府工作任务。报告指出，2023年国内生产总值超过126万亿元，增长5.2%，全年经济社会发展主要目标任务圆满完成，高质量发展扎实推进，社会大局保持稳定；2024年坚持稳中求进工作总基调，国内生产总值增长预期目标为5%左右，部署现代化产业体系建设、科教兴国、扩大内需、深化改革、对外开放、统筹发展和安全、三农、城乡融合、生态文明、民生保障等十个方面政府工作任务。
-# 核心政策
-## 2024年发展主要预期目标
-- **国内生产总值**：增长**5%左右**。
-- **城镇新增就业**：**1120万人以上**，城镇调查失业率**5.5%左右**。
-- **居民消费价格**：涨幅**3%左右**。
-- **居民收入**：增长和经济增长同步。
-- **国际收支**：保持基本平衡。
-- **粮食产量**：**1.3万亿斤以上**。
-- **单位国内生产总值能耗**：降低**2.5%左右**。
-- **生态环境质量**：持续改善。
-## 宏观政策取向
-- **总体基调**：坚持稳中求进、以进促稳、先立后破，多出有利于稳预期、稳增长、稳就业的政策，谨慎出台收缩性抑制性措施。
-- **积极的财政政策**：适度加力、提质增效，赤字率拟按**3%**安排，赤字规模**4.06万亿元**，一般公共预算支出规模**28.5万亿元**。
-- **地方政府专项债券**：拟安排**3.9万亿元**。
-- **超长期特别国债**：为系统解决强国建设、民族复兴进程中一些重大项目建设的资金问题，连续几年发行，专项用于国家重大战略实施和重点领域安全能力建设，**今年先发行10000亿元**。
-- **财政支出结构**：大力优化支出结构，强化国家重大战略任务和基本民生财力保障；中央财政加大对地方均衡性转移支付力度，适当向困难地区倾斜；省级财政推动财力下沉，兜牢基层`三保`底线；各级政府要习惯过紧日子。
-- **稳健的货币政策**：灵活适度、精准有效，保持流动性合理充裕，社会融资规模、货币供应量同经济增长和价格水平预期目标相匹配，促进社会综合融资成本稳中有降，增强资本市场内在稳定性，保持人民币汇率在合理均衡水平上基本稳定。
-- **宏观政策取向一致性**：把非经济性政策纳入宏观政策取向一致性评估，确保同向发力、形成合力；涉企政策要注重与市场沟通，回应企业关切，营造稳定、透明、可预期的政策环境。
-## 现代化产业体系建设
-- **制造业重点产业链高质量发展行动**：实施`制造业重点产业链高质量发展行动`，着力补齐短板、拉长长板、锻造新板，推动传统产业高端化、智能化、绿色化转型。
-- **生产性服务业与中小企业**：加快发展现代生产性服务业，促进中小企业专精特新发展，加强标准引领和质量支撑，打造更多有影响力的`中国制造`品牌。
-- **战略性新兴产业**：促进战略性新兴产业融合集群发展，巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划，鼓励发展创业投资、股权投资。
-- **数字经济**：制定支持数字经济高质量发展政策，促进数字技术和实体经济深度融合，开展`人工智能+`行动，实施`制造业数字化转型行动`，大力推动数据开发开放和流通使用。
-## 科教兴国战略
-- **教育强国建设规划纲要**：制定实施`教育强国建设规划纲要`，落实立德树人根本任务，开展`基础教育扩优提质行动`，办好特殊教育、继续教育，大力提高职业教育质量，加快建设中国特色世界一流的大学和优势学科。
-- **高水平科技自立自强**：充分发挥新型举国体制优势，强化基础研究系统布局，推进关键核心技术协同攻关，加强颠覆性技术和前沿技术研发，强化企业科技创新主体地位，深化科技评价、科技奖励、科研项目和经费管理制度改革，加强知识产权保护，扩大国际科技交流合作。
-- **人才政策**：实施更加积极、更加开放、更加有效的人才政策，推进高水平人才高地和吸引集聚人才平台建设，加大对青年科技人才支持力度，加快建立以创造价值、能力、贡献为导向的人才评价体系。
-## 扩大国内需求
-- **促进消费稳定增长**：从增加收入、优化供给、减少限制性措施等方面综合施策，培育壮大新型消费，实施`数字消费`、`绿色消费`、`健康消费`促进政策；稳定和扩大传统消费，鼓励和推动消费品以旧换新，提振智能网联新能源汽车、电子产品等大宗消费；推动养老、育幼、家政等服务扩容提质。
-- **积极扩大有效投资**：发挥政府投资的带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳、加强民生等经济社会薄弱领域，加快实施`十四五`规划重大工程项目；着力稳定扩大民间投资，在更多领域让民间投资进得来、能发展、有作为。
-## 深化改革
-- **激发各类经营主体活力**：不断完善落实`两个毫不动摇`的体制机制，深入实施`国有企业改革深化提升行动`，全面落实促进民营经济发展壮大的意见及配套举措，实施`降低物流成本行动`，健全防范化解拖欠企业账款长效机制。
-- **全国统一大市场建设**：着力推动产权保护、市场准入、公平竞争、社会信用等方面制度规则统一，专项治理地方保护、市场分割、招商引资不当竞争等突出问题。
-- **财税金融等领域改革**：谋划新一轮财税体制改革，落实金融体制改革部署，深化社会民生领域改革。
-## 高水平对外开放
-- **外贸稳规模优结构**：支持企业开拓多元化市场，促进跨境电商等新业态健康发展，拓展中间品贸易、绿色贸易等新增长点，积极扩大优质产品进口，出台服务贸易、数字贸易创新发展政策。
-- **加大吸引外资力度**：**全面取消制造业领域外资准入限制措施**，放宽电信、医疗等服务业市场准入，落实好外资企业国民待遇，加强外商投资服务保障，深入实施`自贸试验区提升战略`。
-- **共建一带一路**：抓好支持高质量共建`一带一路`八项行动落实落地，稳步推进重大项目合作，实施一批`小而美`民生项目，加快建设西部陆海新通道。
-- **多双边和区域经济合作**：与更多国家和地区商签高标准自贸协定和投资协定，全面深入参与世贸组织改革。
-## 统筹发展和安全
-- **房地产政策**：优化房地产政策，促进房地产市场平稳健康发展；加快构建房地产发展新模式，加大保障性住房建设和供给，完善商品房相关基础性制度，满足居民刚性住房需求和多样化改善型住房需求。
-- **地方债务风险化解**：统筹好地方债务风险化解和稳定发展，进一步落实`一揽子化债方案`，稳妥推进一些地方的中小金融机构风险处置，建立同高质量发展相适应的政府债务管理机制。
-- **重点领域安全能力建设**：全方位夯实粮食安全根基，强化能源资源安全保障，加快构建大国储备体系，有效维护产业链供应链安全稳定。
-## 乡村全面振兴
-- **学习运用千万工程经验**：学习运用`千村示范、万村整治`工程经验，推动乡村全面振兴不断取得实质性进展、阶段性成果。
-- **粮食和重要农产品稳产保供**：稳定粮食播种面积，健全种粮农民收益保障机制，加大产粮大县支持力度，严守耕地红线，提高高标准农田建设投资补助水平。
-- **巩固拓展脱贫攻坚成果**：加强防止返贫监测帮扶，确保不发生规模性返贫，强化易地搬迁后续帮扶，加大对国家乡村振兴重点帮扶县支持力度。
-- **农村改革发展**：启动**第二轮土地承包到期后再延长30年整省试点**，促进农民增收，壮大乡村富民产业，深入实施`乡村建设行动`，持续改善农村人居环境。
-## 城乡融合和区域协调发展
-- **新型城镇化**：把加快农业转移人口市民化摆在突出位置，深化户籍制度改革，完善`人地钱`挂钩政策，让有意愿的进城农民工在城镇落户，推动未落户常住人口平等享受城镇基本公共服务。
-- **区域重大战略**：深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略，支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用，持续推进长江经济带高质量发展，推动黄河流域生态保护和高质量发展，制定`主体功能区优化实施规划`。
-## 生态文明建设
-- **生态环境综合治理**：深入实施`空气质量持续改善行动计划`，统筹水资源、水环境、水生态治理，加强生态环境分区管控，组织打好`三北`工程三大标志性战役，完善生态产品价值实现机制。
-- **绿色低碳经济**：推进产业结构、能源结构、交通运输结构、城乡建设发展绿色转型，完善支持绿色发展的政策和相关市场化机制，推动废弃物循环利用产业发展，加快形成绿色低碳供应链，建设美丽中国先行区。
-- **碳达峰碳中和**：积极稳妥推进碳达峰碳中和，扎实开展`碳达峰十大行动`，深入推进能源革命，加快建设新型能源体系。
-## 民生保障
-- **稳就业促增收**：突出就业优先导向，加大促就业专项政策力度，预计今年高校毕业生超过**1170万人**，强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作；多渠道增加城乡居民收入，扩大中等收入群体规模，努力促进低收入群体增收。
-- **医疗卫生服务**：**居民医保人均财政补助标准提高30元**，深化公立医院改革，引导优质医疗资源下沉基层，加强县乡村医疗服务协同联动，促进中医药传承创新，深入开展`健康中国行动`和爱国卫生运动。
-- **社会保障**：**城乡居民基础养老金月最低标准提高20元**，继续提高退休人员基本养老金，加强城乡社区养老服务网络建设，健全生育支持政策，减轻家庭生育养育教育负担，健全分层分类的社会救助体系。
-- **公共安全与社会治理**：贯彻总体国家安全观，着力夯实安全生产和防灾减灾救灾基层基础，坚决遏制重特大事故发生；坚持和发展新时代`枫桥经验`，推进矛盾纠纷预防化解，推动信访工作法治化，依法打击各类违法犯罪活动，建设更高水平的平安中国。
-# 重点工作
-## 大力推进现代化产业体系建设，加快发展新质生产力
-- **推动产业链供应链优化升级**：保持工业经济平稳运行，实施制造业重点产业链高质量发展行动，着力补齐短板、拉长长板、锻造新板；推动传统产业高端化、智能化、绿色化转型，加快发展现代生产性服务业，促进中小企业专精特新发展，加强标准引领和质量支撑，打造更多有影响力的中国制造品牌。
-- **促进战略性新兴产业融合集群发展**：巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划，鼓励发展创业投资、股权投资。
-- **深入推进数字经济创新发展**：制定支持数字经济高质量发展政策，促进数字技术和实体经济深度融合，开展人工智能+行动，实施制造业数字化转型行动，大力推动数据开发开放和流通使用。
-## 深入实施科教兴国战略，强化高质量发展的基础支撑
-- **加强高质量教育体系建设**：全面贯彻党的教育方针，制定实施教育强国建设规划纲要，落实立德树人根本任务，开展基础教育扩优提质行动，办好特殊教育、继续教育，大力提高职业教育质量，加快建设中国特色世界一流的大学和优势学科。
-- **加快推动高水平科技自立自强**：充分发挥新型举国体制优势，强化基础研究系统布局，推进关键核心技术协同攻关，加强颠覆性技术和前沿技术研发；强化企业科技创新主体地位，深化科技评价、科技奖励、科研项目和经费管理制度改革，加强知识产权保护，扩大国际科技交流合作，营造具有全球竞争力的开放创新生态。
-- **全方位培养用好人才**：实施更加积极、更加开放、更加有效的人才政策，推进高水平人才高地和吸引集聚人才平台建设，加大对青年科技人才支持力度，加快建立以创造价值、能力、贡献为导向的人才评价体系。
-## 着力扩大国内需求，推动经济实现良性循环
-- **促进消费稳定增长**：从增加收入、优化供给、减少限制性措施等方面综合施策，培育壮大新型消费，实施数字消费、绿色消费、健康消费促进政策；稳定和扩大传统消费，鼓励和推动消费品以旧换新，提振智能网联、新能源汽车、电子产品等大宗消费；推动养老、育幼、家政等服务扩容提质，优化消费环境。
-- **积极扩大有效投资**：发挥好政府投资的带动放大效应，重点支持科技创新、新型基础设施、节能减排降碳、加强民生等经济社会薄弱领域，加快实施十四五规划重大工程项目；着力稳定扩大民间投资，落实和完善支持政策，进一步拆除各种藩篱，在更多领域让民间投资进得来、能发展、有作为。
-## 坚定不移深化改革，增强发展内生动力
-- **激发各类经营主体活力**：不断完善落实两个毫不动摇的体制机制，为各类所有制企业创造公平竞争、竞相发展的良好环境；深入实施国有企业改革深化提升行动，全面落实促进民营经济发展壮大的意见及配套举措，实施降低物流成本行动，健全防范化解拖欠企业账款长效机制。
-- **加快全国统一大市场建设**：着力推动产权保护、市场准入、公平竞争、社会信用等方面的制度规则统一，专项治理地方保护、市场分割、招商引资不当竞争等突出问题，坚持依法监管，坚决维护公平竞争的市场秩序。
-- **推进财税、金融等领域改革**：谋划新一轮财税体制改革，落实金融体制改革部署，深化社会民生领域改革。
-## 扩大高水平对外开放，促进互利共赢
-- **推动外贸稳规模优结构**：支持企业开拓多元化市场，促进跨境电商等新业态健康发展，拓展中间品贸易、绿色贸易等新增长点，积极扩大优质产品进口，出台服务贸易、数字贸易创新发展政策。
-- **加大吸引外资力度**：全面取消制造业领域外资准入限制措施，放宽电信、医疗等服务业市场准入，落实好外资企业国民待遇，加强外商投资服务保障，深入实施自贸试验区提升战略，打造对外开放新高地。
-- **推动高质量共建一带一路走深走实**：抓好支持高质量共建一带一路八项行动落实落地，稳步推进重大项目合作，实施一批小而美民生项目，加快建设西部陆海新通道。
-- **深化多双边和区域经济合作**：与更多国家和地区商签高标准自贸协定和投资协定，全面深入参与世贸组织改革，推动建设开放型世界经济。
-## 更好统筹发展和安全，有效防范化解重点领域风险
-- **稳妥有序处置风险隐患**：完善重大风险处置统筹协调机制，压实企业主体责任、部门监管责任、地方属地责任；优化房地产政策，促进房地产市场平稳健康发展；统筹好地方债务风险化解和稳定发展，进一步落实一揽子化债方案，稳妥推进一些地方的中小金融机构风险处置。
-- **健全风险防控长效机制**：加快构建房地产发展新模式，加大保障性住房建设和供给，完善商品房相关基础性制度，满足居民刚性住房需求和多样化改善型住房需求；建立同高质量发展相适应的政府债务管理机制，提高金融风险防控能力。
-- **加强重点领域安全能力建设**：全方位夯实粮食安全根基，强化能源资源安全保障，加快构建大国储备体系，有效维护产业链供应链安全稳定。
-## 坚持不懈抓好三农工作，扎实推进乡村全面振兴
-- **加强粮食和重要农产品稳产保供**：稳定粮食播种面积，健全种粮农民收益保障机制，加大产粮大县支持力度，严守耕地红线，提高高标准农田建设投资补助水平。
-&gt; 各地区都要扛起保障国家粮食安全责任。我们这样一个人口大国，必须始终把饭碗牢牢端在自己手上。
-- **巩固拓展脱贫攻坚成果**：加强防止返贫监测帮扶，确保不发生规模性返贫，强化易地搬迁后续帮扶，加大对国家乡村振兴重点帮扶县支持力度，让脱贫成果更可持续。
-- **稳步推进农村改革发展**：启动第二轮土地承包到期后再延长30年整省试点，促进农民增收，壮大乡村富民产业；深入实施乡村建设行动，持续改善农村人居环境，建设宜居宜业和美乡村。
-## 推动城乡融合和区域协调发展，大力优化经济布局
-- **积极推进新型城镇化**：把加快农业转移人口市民化摆在突出位置，深化户籍制度改革，完善人地钱挂钩政策，让有意愿的进城农民工在城镇落户，推动未落户常住人口平等享受城镇基本公共服务。
-- **提高区域协调发展水平**：深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略；支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用，持续推进长江经济带高质量发展，推动黄河流域生态保护和高质量发展，制定主体功能区优化实施规划。
-## 加强生态文明建设，推进绿色低碳发展
-- **推动生态环境综合治理**：深入实施空气质量持续改善行动计划，统筹水资源、水环境、水生态治理，加强生态环境分区管控，组织打好三北工程三大标志性战役，完善生态产品价值实现机制。
-- **大力发展绿色低碳经济**：推进产业结构、能源结构、交通运输结构、城乡建设发展绿色转型，完善支持绿色发展的政策和相关市场化机制，推动废弃物循环利用产业发展，加快形成绿色低碳供应链，建设美丽中国先行区。
-- **积极稳妥推进碳达峰碳中和**：扎实开展碳达峰十大行动，深入推进能源革命，加快建设新型能源体系，确保经济社会发展用能需求。
-## 切实保障和改善民生，加强和创新社会治理
-- **多措并举稳就业促增收**：突出就业优先导向，加大促就业专项政策力度；预计今年高校毕业生超过1170万人，要强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作；多渠道增加城乡居民收入，扩大中等收入群体规模，努力促进低收入群体增收。
-- **提高医疗卫生服务能力**：居民医保人均财政补助标准提高30元，深化公立医院改革，引导优质医疗资源下沉基层，加强县乡村医疗服务协同联动，促进中医药传承创新，深入开展健康中国行动和爱国卫生运动。
-- **加强社会保障**：城乡居民基础养老金月最低标准提高20元，继续提高退休人员基本养老金；加强城乡社区养老服务网络建设，健全生育支持政策，减轻家庭生育养育教育负担；健全分层分类的社会救助体系，把民生兜底保障安全网织密扎牢。
-- **丰富人民群众精神文化生活**：深入学习贯彻习近平文化思想，广泛践行社会主义核心价值观，发展哲学社会科学、新闻出版、广播电视、文学艺术和档案等事业，创新实施文化惠民工程，大力发展文化产业，推动全民健身活动广泛开展。
-- **维护国家安全和社会稳定**：贯彻总体国家安全观，提高公共安全治理水平，着力夯实安全生产和防灾减灾救灾基层基础，坚决遏制重特大事故发生；完善社会治理体系，强化城乡社区服务功能，保障妇女、儿童、老年人、残疾人合法权益，坚持和发展新时代枫桥经验，推进矛盾纠纷预防化解，推动信访工作法治化，依法打击各类违法犯罪活动，建设更高水平的平安中国。
-## 全面加强政府建设
-- **深入推进依法行政**：严格遵守宪法法律，自觉接受同级人大及其常委会的监督，自觉接受人民政协的民主监督，自觉接受社会和舆论监督，加强审计监督，坚持科学民主、依法决策。
-- **提高行政效率与服务水平**：深入推进政府职能转变，不断提高执行力和公信力，坚决纠正形式主义、官僚主义，持续为基层和企业减负。
-- **推进党风廉政建设和反腐败斗争**：发扬自我革命精神，纵深推进党风廉政建设和反腐败斗争，政府工作人员要遵守法纪、廉洁修身、勤勉尽责，干干净净为人民服务。
-## 国防、港澳台与外交工作
-- **国防和军队建设**：深入贯彻习近平强军思想，贯彻新时代军事战略方针，坚持党对人民军队的绝对领导，全面深入贯彻军委主席负责制，打好实现建军100年奋斗目标攻坚战，全面加强练兵备战，抓好军队建设十四五规划执行，加快实施国防发展重大工程。
-- **港澳工作**：继续全面准确、坚定不移贯彻一国两制、港人治港、澳人治澳、高度自治的方针，坚持依法治港治澳，落实爱国者治港、爱国者治澳的原则，支持香港、澳门发展经济、改善民生，更好融入国家发展大局。
-- **对台工作**：坚持贯彻新时代党解决台湾问题的总体方略，坚持一个中国原则和九二共识，坚决反对台独分裂和外来干涉，推动两岸关系和平发展，深化两岸融合发展，增进两岸同胞福祉。
-- **外交工作**：坚持独立自主的和平外交政策，坚持走和平发展道路，坚定奉行互利共赢的开放战略，落实全球发展倡议、全球安全倡议、全球文明倡议，推动构建人类命运共同体。</t>
+          <t># 2024年政府工作报告审议会议纪要
+## 报告概况
+本报告为国务院总理代表国务院向全国人民代表大会所作的《2024年政府工作报告》，发布单位为国务院，报告期间覆盖2023年工作回顾与2024年工作部署。报告核心主题为以中国式现代化全面推进强国建设、民族复兴伟业，整体基调为坚持稳中求进工作总基调，完整、准确、全面贯彻新发展理念，着力推动高质量发展。报告指出，2023年国内生产总值超过126万亿元，增长5.2%，全年经济社会发展主要目标任务圆满完成；2024年主要预期目标为国内生产总值增长5%左右，城镇新增就业1120万人以上，城镇调查失业率5.5%左右，居民消费价格涨幅3%左右，粮食产量1.3万亿斤以上，单位国内生产总值能耗降低2.5%左右。报告部署了现代化产业体系建设、科教兴国、扩大内需、深化改革、对外开放、统筹发展和安全、三农工作、城乡融合、生态文明建设、民生保障等十大领域政府工作任务。
+## 核心政策
+1. **2024年经济社会发展总体要求**：坚持稳中求进工作总基调，完整、准确、全面贯彻新发展理念，加快构建新发展格局，着力推动高质量发展，全面深化改革开放，推动高水平科技自立自强，加大宏观调控力度，统筹扩大内需和深化供给侧结构性改革，统筹新型城镇化和乡村全面振兴，统筹高质量发展和高水平安全，切实增强经济活力、防范化解风险、改善社会预期，巩固和增强经济回升向好态势，持续推动经济实现质的有效提升和量的合理增长。
+2. **2024年主要预期目标**：
+   - **城镇新增就业1120万人以上**，城镇调查失业率5.5%左右
+   - 居民收入增长和经济增长同步，国际收支保持基本平衡
+   - **单位国内生产总值能耗降低2.5%左右**，生态环境质量持续改善
+3. **财政政策**：积极的财政政策适度加力、提质增效，**赤字率拟按3%安排，赤字规模4.06万亿元**，一般公共预算支出规模28.5万亿元，拟安排地方政府专项债券3.9万亿元；为系统解决强国建设、民族复兴进程中一些重大项目建设的资金问题，已连续几年发行超长期特别国债，专项用于国家重大战略实施和重点领域安全能力建设，**今年先发行10000亿元**；中央财政加大对地方均衡性转移支付力度，省级财政推动财力下沉，兜牢基层`三保`底线，各级政府习惯过紧日子。
+4. **货币政策**：稳健的货币政策灵活适度、精准有效，保持流动性合理充裕，社会融资规模、货币供应量同经济增长和价格水平预期目标相匹配，促进社会综合融资成本稳中有降，增强资本市场内在稳定性，保持人民币汇率在合理均衡水平上基本稳定；把非经济性政策纳入宏观政策取向一致性评估，涉企政策注重与市场沟通、回应企业关切。
+5. **大力推进现代化产业体系建设，加快发展新质生产力**：
+   - 推动产业链供应链优化升级，实施`制造业重点产业链高质量发展行动`，推动传统产业高端化、智能化、绿色化转型，促进中小企业专精特新发展
+   - 促进战略性新兴产业融合集群发展，巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划
+   - 深入推进数字经济创新发展，制定支持数字经济高质量发展政策，开展`人工智能+`行动，实施`制造业数字化转型行动`，大力推动数据开发开放和流通使用
+6. **深入实施科教兴国战略**：
+   - 制定实施`教育强国建设规划纲要`，开展`基础教育扩优提质行动`，大力提高职业教育质量，加快建设中国特色世界一流的大学和优势学科
+   - 充分发挥新型举国体制优势，强化基础研究系统布局，推进关键核心技术协同攻关，强化企业科技创新主体地位，深化科技评价、科技奖励、科研项目和经费管理制度改革
+   - 实施更加积极、更加开放、更加有效的人才政策，加大对青年科技人才支持力度，加快建立以创造价值、能力、贡献为导向的人才评价体系
+7. **着力扩大国内需求**：从增加收入、优化供给、减少限制性措施等方面综合施策促进消费稳定增长，实施数字消费、绿色消费、健康消费促进政策，鼓励和推动消费品以旧换新；积极扩大有效投资，重点支持科技创新、新型基础设施、节能减排降碳、加强民生等经济社会薄弱领域，加快实施`十四五`规划重大工程项目，着力稳定扩大民间投资。
+8. **坚定不移深化改革**：深入实施`国有企业改革深化提升行动`，全面落实促进民营经济发展壮大的意见及配套举措，实施`降低物流成本行动`，健全防范化解拖欠企业账款长效机制；加快全国统一大市场建设，专项治理地方保护、市场分割、招商引资不当竞争等突出问题；谋划新一轮财税体制改革，落实金融体制改革部署。
+9. **扩大高水平对外开放**：推动外贸稳规模优结构，促进跨境电商等新业态健康发展，拓展中间品贸易、绿色贸易等新增长点；**全面取消制造业领域外资准入限制措施**，放宽电信、医疗等服务业市场准入，深入实施`自贸试验区提升战略`；抓好支持高质量共建`一带一路`八项行动落实落地，加快建设西部陆海新通道；深化多双边和区域经济合作，全面深入参与世贸组织改革。
+10. **更好统筹发展和安全，有效防范化解重点领域风险**：优化房地产政策，促进房地产市场平稳健康发展，加快构建房地产发展新模式，加大保障性住房建设和供给，满足居民刚性住房需求和多样化改善型住房需求；统筹好地方债务风险化解和稳定发展，进一步落实一揽子化债方案，稳妥推进中小金融机构风险处置；全方位夯实粮食安全根基，强化能源资源安全保障，加快构建大国储备体系，有效维护产业链供应链安全稳定。
+11. **坚持不懈抓好三农工作，扎实推进乡村全面振兴**：学习运用`千村示范、万村整治`工程经验，稳定粮食播种面积，健全种粮农民收益保障机制，严守耕地红线，提高高标准农田建设投资补助水平；毫不放松巩固拓展脱贫攻坚成果，确保不发生规模性返贫；**启动第二轮土地承包到期后再延长30年整省试点**；深入实施乡村建设行动，建设宜居宜业和美乡村。
+12. **推动城乡融合和区域协调发展**：把加快农业转移人口市民化摆在突出位置，深化户籍制度改革，完善人地钱挂钩政策，推动未落户常住人口平等享受城镇基本公共服务；深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略，支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用，持续推进长江经济带高质量发展，推动黄河流域生态保护和高质量发展。
+13. **加强生态文明建设，推进绿色低碳发展**：深入实施`空气质量持续改善行动计划`，统筹水资源、水环境、水生态治理，组织打好`三北`工程三大标志性战役；大力发展绿色低碳经济，推进产业结构、能源结构、交通运输结构、城乡建设发展绿色转型，推动废弃物循环利用产业发展；积极稳妥推进碳达峰碳中和，扎实开展`碳达峰十大行动`，深入推进能源革命，加快建设新型能源体系。
+14. **切实保障和改善民生**：
+   - 突出就业优先导向，预计今年高校毕业生超过1170万人，强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作
+   - **居民医保人均财政补助标准提高30元**，深化公立医院改革，引导优质医疗资源下沉基层，促进中医药传承创新
+   - **城乡居民基础养老金月最低标准提高20元**，继续提高退休人员基本养老金，加强城乡社区养老服务网络建设，健全生育支持政策
+   - 多渠道增加城乡居民收入，扩大中等收入群体规模，努力促进低收入群体增收
+   - 健全分层分类的社会救助体系，把民生兜底保障安全网织密扎牢
+15. **维护国家安全和社会稳定**：贯彻总体国家安全观，着力夯实安全生产和防灾减灾救灾基层基础，坚决遏制重特大事故发生；完善社会治理体系，坚持和发展新时代`枫桥经验`，推进矛盾纠纷预防化解，推动信访工作法治化，依法打击各类违法犯罪活动，建设更高水平的平安中国。
+## 重点工作
+### 现代化产业体系建设，加快发展新质生产力
+1. **推动产业链供应链优化升级**：保持工业经济平稳运行，实施制造业重点产业链高质量发展行动，着力补齐短板、拉长长板、锻造新板；推动传统产业高端化、智能化、绿色化转型，加快发展现代生产性服务业，促进中小企业专精特新发展，加强标准引领和质量支撑，打造更多有影响力的中国制造品牌。
+2. **促进战略性新兴产业融合集群发展**：巩固扩大智能网联、新能源汽车等产业领先优势，制定未来产业发展规划，鼓励发展创业投资、股权投资。
+3. **深入推进数字经济创新发展**：制定支持数字经济高质量发展政策，促进数字技术和实体经济深度融合，开展“人工智能+”行动，实施制造业数字化转型行动，大力推动数据开发开放和流通使用。
+### 深入实施科教兴国战略，强化高质量发展的基础支撑
+1. **加强高质量教育体系建设**：全面贯彻党的教育方针，制定实施教育强国建设规划纲要，落实立德树人根本任务，开展基础教育扩优提质行动，办好特殊教育、继续教育，大力提高职业教育质量，加快建设中国特色世界一流的大学和优势学科。
+2. **加快推动高水平科技自立自强**：充分发挥新型举国体制优势，强化基础研究系统布局，推进关键核心技术协同攻关，加强颠覆性技术和前沿技术研究；强化企业科技创新主体地位，深化科技评价、科技奖励、科研项目和经费管理制度改革，加强知识产权保护，扩大国际科技交流合作，营造具有全球竞争力的开放创新生态。
+3. **全方位培养用好人才**：实施更加积极、更加开放、更加有效的人才政策，推进高水平人才高地和吸引集聚人才平台建设，加大对青年科技人才支持力度，加快建立以创造价值、能力、贡献为导向的人才评价体系。
+### 着力扩大国内需求，推动经济实现良性循环
+1. **促进消费稳定增长**：从增加收入、优化供给、减少限制性措施等方面综合施策，培育壮大新型消费，实施数字消费、绿色消费、健康消费促进政策；稳定和扩大传统消费，鼓励和推动消费品以旧换新，提振智能网联、新能源汽车、电子产品等大宗消费；推动养老、育幼、家政等服务扩容提质，优化消费环境。
+2. **积极扩大有效投资**：发挥好政府投资的带动放大效应，重点支持科技创新、新型基础设施、节能减排、降碳，加强民生等经济社会薄弱领域，加快实施“十四五”规划重大工程项目；着力稳定扩大民间投资，落实和完善支持政策，进一步拆除各种藩篱，在更多领域让民间投资进得来、能发展、有作为。
+### 坚定不移深化改革，增强发展内生动力
+1. **激发各类经营主体活力**：不断完善落实“两个毫不动摇”的体制机制，为各类所有制企业创造公平竞争、竞相发展的良好环境；深入实施国有企业改革深化提升行动，全面落实促进民营经济发展壮大的意见及配套举措，实施降低物流成本行动，健全防范化解拖欠企业账款长效机制，积极支持企业家专注创新发展、敢干敢闯敢投。
+2. **加快全国统一大市场建设**：着力推动产权保护、市场准入、公平竞争、社会信用等方面的制度规则统一，专项治理地方保护、市场分割、招商引资不当竞争等突出问题，坚持依法监管，坚决维护公平竞争的市场秩序。
+3. **推进财税、金融等领域改革**：谋划新一轮财税体制改革，落实金融体制改革部署，深化社会民生领域改革。
+### 扩大高水平对外开放，促进互利共赢
+1. **推动外贸质升量稳**：支持企业开拓多元化市场，促进跨境电商等新业态健康发展，拓展中间品贸易、绿色贸易等新增长点，积极扩大优质产品进口，出台服务贸易、数字贸易创新发展政策。
+2. **加大吸引外资力度**：全面取消制造业领域外资准入限制措施，放宽电信、医疗等服务业市场准入，落实好外资企业国民待遇，加强外商投资服务保障，深入实施自贸试验区提升战略，打造对外开放新高地。
+3. **推动高质量共建“一带一路”走深走实**：抓好支持高质量共建“一带一路”八项行动落实落地，稳步推进重大项目合作，实施一批“小而美”民生项目，加快建设西部陆海新通道。
+4. **深化多双边和区域经济合作**：与更多国家和地区商签高标准自贸协定和投资协定，全面深入参与世贸组织改革，推动建设开放型世界经济。
+### 更好统筹发展和安全，有效防范化解重点领域风险
+1. **稳妥有序处置风险隐患**：完善重大风险处置统筹协调机制，压实企业主体责任、部门监管责任、地方属地责任；优化房地产政策，促进房地产市场平稳健康发展；统筹好地方债务风险化解和稳定发展，进一步落实一揽子化债方案，稳妥推进一些地方的中小金融机构风险处置。
+2. **健全风险防控长效机制**：加快构建房地产发展新模式，加大保障性住房建设和供给，完善商品房相关基础性制度，满足居民刚性住房需求和多样化改善型住房需求；建立同高质量发展相适应的政府债务管理机制，提高金融风险防控能力。
+3. **加强重点领域安全能力建设**：全方位夯实粮食安全根基，强化能源资源安全保障，加快构建大国储备体系，有效维护产业链供应链安全稳定。
+### 坚持不懈抓好“三农”工作，扎实推进乡村全面振兴
+1. **加强粮食和重要农产品稳产保供**：稳定粮食播种面积，健全种粮农民收益保障机制，加大产粮大县支持力度，严守耕地红线，提高高标准农田建设投资补助水平，各地区都要扛起保障国家粮食安全责任。
+2. **巩固拓展脱贫攻坚成果**：加强防止返贫监测帮扶，确保不发生规模性返贫，强化易地搬迁后续帮扶，加大对国家乡村振兴重点帮扶县支持力度，让脱贫成果更可持续。
+3. **稳步推进农村改革发展**：启动第二轮土地承包到期后再延长30年整省试点，促进农民增收，壮大乡村富民产业，深入实施乡村建设行动，持续改善农村人居环境，建设宜居宜业和美乡村。
+### 推动城乡融合和区域协调发展，大力优化经济布局
+1. **积极推进新型城镇化**：把加快农业转移人口市民化摆在突出位置，深化户籍制度改革，完善人地钱挂钩政策，让有意愿的进城农民工在城镇落户，推动未落户常住人口平等享受城镇基本公共服务。
+2. **提高区域协调发展水平**：深入实施西部大开发、东北全面振兴、中部地区加快崛起、东部地区加快推进现代化等战略，支持京津冀、长三角、粤港澳大湾区等地区更好发挥高质量发展动力源作用，持续推进长江经济带高质量发展，推动黄河流域生态保护和高质量发展，制定主体功能区优化实施规划。
+### 加强生态文明建设，推进绿色低碳发展
+1. **推动生态环境综合治理**：深入实施空气质量持续改善行动计划，统筹水资源、水环境、水生态治理，加强生态环境分区管控，组织打好“三北”工程三大标志性战役，完善生态产品价值实现机制。
+2. **大力发展绿色低碳经济**：推进产业结构、能源结构、交通运输结构、城乡建设发展绿色转型，完善支持绿色发展的政策和相关市场化机制，推动废弃物循环利用产业发展，加快形成绿色低碳供应链，建设美丽中国先行区。
+3. **积极稳妥推进碳达峰碳中和**：扎实开展碳达峰十大行动，深入推进能源革命，加快建设新型能源体系，确保经济社会发展用能需求。
+### 切实保障和改善民生，加强和创新社会治理
+1. **多措并举稳就业促增收**：突出就业优先导向，加大促就业专项政策力度，预计今年高校毕业生超过1170万人，要强化促进青年就业政策，扎实做好退役军人、农民工等群体就业工作；多渠道增加城乡居民收入，扩大中等收入群体规模，努力促进低收入群体增收。
+2. **提高医疗卫生服务能力**：居民医保人均财政补助标准提高30元，深化公立医院改革，引导优质医疗资源下沉基层，加强县乡村医疗服务协同联动，促进中医药传承创新，深入开展健康中国行动和爱国卫生运动。
+3. **加强社会保障**：城乡居民基础养老金月最低标准提高20元，继续提高退休人员基本养老金，加强城乡社区养老服务网络建设，健全生育支持政策，减轻家庭生育养育教育负担，健全分层分类的社会救助体系。
+4. **丰富人民群众精神文化生活**：深入学习贯彻习近平文化思想，广泛践行社会主义核心价值观，发展哲学社会科学、新闻出版、广播电视、文学艺术和档案等事业，创新实施文化惠民工程，大力发展文化产业，推动全民健身活动广泛开展。
+5. **维护国家安全和社会稳定**：贯彻总体国家安全观，提高公共安全治理水平，着力夯实安全生产和防灾减灾救灾基层基础，坚决遏制重特大事故发生；完善社会治理体系，强化城乡社区服务功能，保障妇女、儿童、老年人、残疾人合法权益，坚持和发展新时代“枫桥经验”，推进矛盾纠纷预防化解，推动信访工作法治化，依法打击各类违法犯罪活动，建设更高水平的平安中国。
+### 政府自身建设
+1. **深入推进依法行政**：严格遵守宪法法律，自觉接受同级人大及其常委会的监督，自觉接受人民政协的民主监督，自觉接受社会和舆论监督，加强审计监督，坚持科学民主、依法决策，支持工会、共青团、妇联等群团组织更好发挥作用。
+2. **全面提高行政效率**：深入推进政府职能转变，不断提高执行力和公信力，在抓落实上切实做到不折不扣、雷厉风行、求真务实；提高政务服务水平，坚决纠正形式主义、官僚主义，持续为基层和企业减负。
+### 国防、港澳台与外交工作
+1. **国防和军队建设**：深入贯彻习近平强军思想，贯彻新时代军事战略方针，坚持党对人民军队的绝对领导，全面深入贯彻军委主席负责制，打好实现建军一百年奋斗目标攻坚战，全面加强练兵备战，抓好军队建设“十四五”规划执行，加快实施国防发展重大工程，各级政府要大力支持国防和军队建设。
+2. **港澳工作**：继续全面准确、坚定不移贯彻“一国两制”、“港人治港”、“澳人治澳”、高度自治的方针，坚持依法治港治澳，落实爱国者治港、爱国者治澳原则，支持香港、澳门发展经济、改善民生，更好融入国家发展大局。
+3. **对台工作**：坚持贯彻新时代党解决台湾问题的总体方略，坚持一个中国原则和“九二共识”，坚决反对“台独”分裂和外来干涉，推动两岸关系和平发展，深化两岸融合发展，增进两岸同胞福祉。
+4. **外交工作**：坚持独立自主的和平外交政策，坚持走和平发展道路，坚定奉行互利共赢的开放战略，落实全球发展倡议、全球安全倡议、全球文明倡议，推动构建人类命运共同体。</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>51.7</v>
+        <v>50.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>9903/8357</t>
+          <t>9903/7509</t>
         </is>
       </c>
     </row>
@@ -11177,98 +11224,88 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t># 沟通背景与目的
-杭州医学院检验医学院、生物工程学院党委书记、副院长宋宝峰副教授做客学校2026年研究生招生宣讲直播专场，面向考生及家长介绍医学技术专业硕士点的总体情况。沟通旨在帮助考生全面了解该学位点的学科建设、研究方向、师资力量、培养模式、就业前景及2026年招考计划，并现场解答考生关于就业、初试科目、跨专业报考等疑问。整场宣讲以鼓励报考为基调，宋宝峰对学位点竞争力与就业前景表示充分信心，并欢迎考生报考。
-# 核心信息与数据
-## 学位点基本情况
-- **学位点获批**：医学技术专业硕士点于2024年获批，为新的学位点。
-- **学院构成**：由5个学院共同承担培养工作，其中检验医学院、生物工程学院合署办公，共建学院为医学影像学院、康复学院和信息工程学院。
-- **专业方向**：聚焦四个主要专业方向，分别为检验技术、医学影像技术、康复治疗和智能医学工程；检验技术细分为医检和卫检两个方向。
-## 2025年招生情况
-- **录取人数**：2025年录取64位考生。
-- **方向分布**：心理方向38人，经济方向11人，康复方向13人，职业方向2人（原文如此）。
-## 学科建设情况
-- **学科层次**：医学技术学科2023年获批省医学技术省一流学科B类。
-- **科研项目**：近五年获国家级基金项目19项，省鉴定领先项目1项。
-- **科研经费**：纵向科研经费1300万，横向合作课题经费2200多万。
-- **科研获奖**：获省科技进步一等奖2项、二等奖1项、三等奖2项。
-- **课程与专业建设**：建成国家级一流本科课程2门，国家级一流本科专业建设点2个。
-- **省级平台**：建有省生物标志物与器官诊断转化重点实验室、检验诊断关键技术研究室、康复模块和机器人国际联合实验室、数字化康复装备质量研究中心、脑认知与疾病数字医疗器械质量工程研究中心、浙江省神经系统疾病数字化装备研发重点实验室等省级平台。
-## 学科优势
+          <t># 杭州医学院医学技术硕士点招生宣讲会
+## 沟通背景与目的
+杭州医学院检验医学院、生物工程学院党委书记、副院长宋宝峰副教授做客招生宣讲直播间，面向考生及家长介绍医学技术专业硕士点的总体情况。沟通旨在帮助广大考生全面了解2026年研究生招生情况，重点围绕学位点建设、学科优势、研究方向、师资队伍、培养模式与就业前景、招考计划与复试安排等内容进行宣介，并现场解答考生关于就业前景、初试科目、跨专业报考等关切问题。整体基调为积极推介，宋宝峰书记对该学位点的学科竞争力与就业前景表达了充分信心，并欢迎考生报考。
+## 核心信息与数据
+### 学位点基本情况
+- **获批时间**：医学技术专业硕士点于2024年获批，为新的学位点。
+- **承担学院**：由5个学院共同承担培养工作，其中检验医学院、生物工程学院合署办公，共建学院为医学影像学院、康复学院、信息工程学院。
+- **专业方向**：聚焦四个主要专业方向——检验技术、医学影像技术、康复治疗、智能医学工程；检验技术细分为医检和卫检两个方向。
+### 2025年招生情况
+- **录取总数**：2025年录取64位考生。
+- **分方向人数**：检验方向38人，影像方向11人，康复方向13人，智能医学工程方向2人。
+### 学科建设与科研平台
+- **学科层次**：医学技术于2023年获批省一流学科B类。
+- **科研项目与经费**：近五年获国家级基金项目19项、省鉴定领先项目1项；纵向科研经费1300万元，横向合作课题经费2200多万元。
+- **科研奖项**：获省科技进步一等奖2项、二等奖1项、三等奖2项。
+- **本科建设**：建成国家级一流本科课程2门、国家级一流本科专业建设点2个。
+- **省级科研平台**：建有省生物标志物与器官诊断转化重点实验室（2024年获批）、检验诊断关键技术研究室（2022年）、康复模块和机器人国际联合实验室（2023年）、省实验室和安全培训基地、数字化康复装备质量研究中心、脑认知与疾病数字医疗器械质量工程研究中心、浙江省神经系统疾病数字化装备研发重点实验室（2024年）。
+### 学科优势
 - **体外诊断领域**：优势显著，疫情期间与企业联合开发新冠病毒核酸检测、抗原检测、抗体检测三个产品，获NMPA注册。
-- **医学影像技术**：在多参数MRI、肿瘤分子影像学、医学图像处理等方面形成优势方向，建有国家级一流本科专业建设点、省医学重点学科、省临床放射质控中心、国家卫健委外周血管介入诊疗培训基地等平台。
+- **医学影像技术**：在多参数MRI、肿瘤分子影像学、医学图像处理等方面形成优势方向，建有国家级本科专业建设点、省医学重点学科、省临床放射质控中心、国家临床药物验证机构、国家卫健委外周血管介入诊疗培训基地。
 - **康复治疗方向**：依托省人民医院康复医学科，为省内综合医院中建科最早、人才最齐、技术最先进、设备最先进、社会效益最佳的康复医学科之一。
-- **智能医学工程**：聚焦阿尔茨海默病智能预警生物标志物（数字生物标志物），居国际领跑水平，为浙江省中医药重点学科、老年助浴疾病数字器械医疗器械浙江省中心。
-## 主要研究方向
-- **医学检验技术（负责人吕建新教授）**：聚焦重大疾病新型生物标志物筛选及机制研究、新发突发传染病新型生物标志物筛选及致病机制研究、重大疾病体外诊断检测技术研究、新型药物系统体内治疗易复发难以治愈疾病研究、神经免疫与再生研究五大方向。
-- **卫生检验检疫（负责人金大志教授）**：聚焦新发突发传染病病原体检测检验新技术方法开发，特别是艰难梭菌致病机制、耐药机制、基因组进化及小分子药物开发，以及卫生检验技术研究。
-- **医学影像技术（负责人徐秀芳教授）**：研究方向包括多参数MRI、肿瘤分子影像学、神经导航引导的脑肿瘤穿刺技术、脑肿瘤术前功能区定位。
-- **康复治疗（负责人倪湘明教授）**：研究方向包括技术研发、神经损伤修复与再生研究、运动康复机制与技术创新、意识障碍促醒机制研究、中西医康复治疗神经系统疾病的机制及临床研究。
-- **智能医学工程（负责人李凯教授）**：聚焦脑认知与脑疾病智能诊疗及康复、健康大数据分析与智慧医疗、脑机接口高端数字医疗器械、中医先进医疗器械研发、脑部及精神系统重大疾病智能诊断及数字方向。
-## 师资队伍与领军人物
-- **师资总体情况**：专任教师90人，高级职称53人（占30%以上），博士55人；硕导69人，其中正高35人，博士46人。
-- **人才称号**：教育部医学技术类专业教学指导委员会委员1人，省万人创新人才2人次，浙江省151人才5人，省杰青1人，省高层次创新人才2人，省领军型创新创业团队1个。
-- **吕建新教授**：学位点负责人，国家百千万人才工程人选，教育部医学技术类专业教学指导委员会委员，主持国家自然科学基金重点项目、科技部重点研发、863计划重点项目等十余项，发表高水平论文200多篇，获省科技一等奖3项、优秀教学成果奖2项。
-- **徐秀芳教授**：浙江省151人才第三层次，研究生院院长兼医学影像学院院长，国家一流本科专业建设点医学影像技术专业负责人，教育部教指委相关医学分会委员。
-- **叶祥明教授**：省人民医院主任医师、二级教授、博导，省卫生领军人才，国家区域医疗中心浙江省重点培育专科康复医学学科带头人，主持国家级课题3项、省重大课题2项，发表SCI论文98篇。
-- **金大志研究员**：美国华盛顿大学博士后，省创新人才，检验医学院学术院长，省生物标志物体外诊断转化重点实验室主任，主持国家自然科学基金面上项目、863子项、科技部重大专项子课题等25项，发表SCI论文50多篇，获省科技进步二等奖、三等奖各1项。
-- **李凯教授**：复旦大学公共卫生学院博士，早稻田大学访问学者，智能医学前沿交叉学科研究院执行院长，智能医学工程学科负责人，浙江省中医药重点学科带头人。
-## 硕士培养与毕业去向
-- **培养目标**：面向健康中国发展需要，紧密服务区域行业产业发展，培养熟练掌握医学技术领域专业知识技能、具有良好创新实践能力的高层次应用型人才。
-- **培养方式与学制**：教学、专业实践与学位论文相结合；全日制专业学位学制三年，最长不超过五年。
-- **学分要求**：毕业前学业课程不少于24学分，其中专业必修课按方向要求大于等于12学分，专业选修课（如智慧医疗、中医康复治疗学、生物信息学等）需达到5-6学分以上。
-- **培养环节**：第二学期开题，第三、第四学期（研二）完成过程性考核，研一第二学期进行学位论文答辩。
-- **医院就业方向**：检验方向可进入检验科、输血科、病理科；影像技术方向可进入放射科、超声科；康复治疗方向可进入康复医学科、骨科、神经科、运动医学科等科室。
-- **其他就业方向**：卫检方向可进入疾控中心（CDC）参与传染病防控、慢性病防治等公共卫生工作；企业领域包括医药企业与生物技术公司（研发、生产、市场销售、质量管理法规）、医疗器械公司、保险公司（医疗保险核保理赔、健康险产品开发）；还可进入药监局、卫健委、海关等部门及高校、研究所继续深造。
-- **就业现状**：2025年开始招生，目前尚无毕业生。
-## 2026年招考计划
-- **计划招生**：2026年计划招生34人，实际以教育部正式下达人数为准。
-- **初试科目**：共三门，思想政治理论、英语为统考，专业综合按方向自主命题：检验考检验综合、影像技术考医学影像技术综合、康复治疗考康复治疗综合、智能医学工程考智能医学工程综合。
-- **专业综合考试**：分值300分，考试时长180分钟；检验综合中分子生物学检验占40%、生物化学检验占30%、微生物学检验占30%。
-- **复试安排**：采用线上线下结合方式，目前以线下为主；初试占60%，复试占40%；复试内容为英语能力测试占20%、专业能力测试占40%、综合能力测试占40%。
-- **信息渠道**：考试大纲、参考书目等以杭州医学院研究生招生网公布为准。
-# 各方立场与诉求
-- **宋宝峰（杭州医学院检验医学院、生物工程学院党委书记、副院长）**：面向考生及家长介绍医学技术专业硕士点总体情况，涵盖学位点获批时间、共建学院、四个专业方向、学科优势、师资队伍、培养方式、就业去向及2026年招考计划，并强调一志愿报考优势明显、性价比高，鼓励考生报考。
-- **主持人**：代表后台考生提出关注问题，包括当前经济形势下研究生毕业就业前景、暑期如何备考初试科目、跨专业报考是否可行等，并请宋宝峰逐一解答。
-- **宋宝峰（回应就业前景）**：表示国家坚持就业优先，该专业就业面宽广且有竞争力，毕业生可进入三甲医院、疾控中心、医药企业、医疗器械公司、保险公司、药监局、卫健委、海关、高校研究所等单位，也可继续读博深造；杭州高水平三甲医院和企业对研究生及以上学位者认可度高，考生不必过度担心和焦虑。
-- **宋宝峰（回应初试备考）**：说明初试共三门科目，思想政治理论和英语为统考，专业综合按报考方向分别考检验综合、医学影像技术综合、康复治疗综合或智能医学工程综合；英语考试难度介于四级和六级之间，建议暑期作为关键备考期，关注杭州医学院研究生招生网和研究生教育微信公众号获取考试大纲及参考教材。
-- **宋宝峰（回应跨专业报考）**：明确表示允许并鼓励非本专业考生跨专业报考医学技术专业硕士点，跨专业考生被录取的概率会大大提高。
-- **宋宝峰（回应校区交通与学科竞赛）**：介绍学校有三个校区，主校区位于市中心黄龙校区，交通便利；学校重视学科竞赛，研究生在竞赛中取得良好成绩，通过以赛促学、以赛促教、以赛促改提升人才培养质量。
-# 达成共识
-- **学位点获批与共建**：医学技术专业硕士点于2024年获批，由检验医学院、生物工程学院合署办公，医学影像学院、康复学院和信息工程学院共建，聚焦检验技术（医检、卫检）、医学影像技术、康复治疗和智能医学工程四个方向。
-- **2025年招生情况**：2025年录取64名考生，其中心理方向38人、经济方向11人、康复方向13人、职业方向2人。
-- **学科建设确认**：医学技术学科2023年获批省一流学科B类，近五年获国家级基金项目19项、省鉴定领先项目1项，纵向科研经费1300万元、横向合作课题经费2200多万元，获省科技进步一等奖2项、二等奖1项、三等奖2项，建成国家级一流本科课程2门、国家级一流本科专业建设点2个。
-- **学科优势确认**：体外诊断领域优势显著（疫情期间联合开发新冠核酸检测、抗原检测、抗体检测三个产品并获NMPA注册），医学影像技术方向形成多参数MRI、肿瘤分子影像学等优势，康复治疗方向依托省人民医院康复医学科，智能医学工程方向在阿尔茨海默病智能预警生物标志物领域居国际领跑水平。
-- **师资队伍确认**：专任教师90人，高级职称53人（占30%以上），博士55人；硕导69人，正高35人，博士46人；学科领军人物包括吕建新教授、徐秀芳教授、叶祥明教授、金大志研究员和李凯教授。
-- **培养方案确认**：培养目标为面向健康中国发展需要的高层次应用型医学技术人才，培养方式为教学、专业实践与学位论文相结合，全日制专业学位学制三年（最长不超过五年），毕业前要求学业课程不少于24学分（专业必修课不少于12学分、专业选修课5-6学分）。
-- **就业方向确认**：毕业生可进入医院相关科室（检验科、输血科、病理科、放射科、超声科、康复医学科等）、疾控中心、医药企业、医疗器械公司、保险公司、药监局、卫健委、海关、高校研究所等。
-- **2026年招考口径确认**：计划招生34人（以教育部正式下达人数为准）；初试科目为思想政治理论、英语和一门专业综合（按方向考检验综合、医学影像技术综合、康复治疗综合或智能医学工程综合），专业综合分值300分、时长180分钟；复试初试占60%、复试占40%，复试内容为英语能力测试占20%、专业能力测试占40%、综合能力测试占40%。
-- **跨专业报考口径确认**：允许并鼓励非本专业考生跨专业报考医学技术专业硕士点。
-- **英语考试难度口径确认**：研究生入学考试英语难度介于四级和六级之间。
-# 待协调事项与后续
-## 待协调事项
-- **2026年计划招生人数**：目前计划招生34人，实际以教育部2026年正式下达人数为准
-- **初试参考书及考试大纲**：以杭州医学院研究生招生网公布为准，直播中仅作初步介绍
-- **复试具体形式与内容**：以学校复试录取办法为基础，目前可参考2025年复试办法
-## 后续安排与参与方式
+- **智能医学工程**：聚焦阿尔茨海默病智能预警生物标志物（数字生物标志物），居国际领跑水平，为浙江省中医药重点学科、老年助浴疾病数字器械医疗器械浙江省中心、智能医学前沿交叉学院。
+### 主要研究方向
+- **医学检验技术（负责人吕建新教授）**：聚焦重大疾病新型生物标志物筛选及机制研究、新发突发传染病新型生物标志物筛选及致病机制、重大疾病体外诊断检测技术、新型药物系统体内治疗、神经免疫与再生研究；课题组承担多项国家级和省部级项目，发表高水平论文百余篇。
+- **卫生检验检疫（负责人金大志研究员）**：聚焦新发突发传染病病原体检测检验新技术方法开发（含艰难梭菌致病机制、耐药机制、基因组进化及小分子药物开发）、卫生检验技术研究；获省科技进步二等奖、三等奖各1项，省医药卫生科技进步一等奖1项、二等奖2项、三等奖1项，发表中科院一二区论文85篇，主编专业教材12部、主审7部。
+- **医学影像技术（负责人徐秀芳教授）**：研究内容为多参数MRI、肿瘤分子影像学、神经导航引导的脑肿瘤穿刺技术、脑肿瘤术前功能区定位；获国家自然科学基金3项、省部级项目20多项，获全国优秀教材二等奖1项。
+- **康复治疗（负责人倪湘明教授）**：研究内容为技术研发、神经损伤修复与再生、运动康复机制与技术创新、意识障碍促醒机制、中西医康复治疗神经系统疾病；团队获国家级课题23项、省级课题23项，省科技进步三等奖2项、省医药卫生科技进步奖二等奖2项，国家发明专利和实用新型专利77项，主编专业书籍、主审8部教材、参编书籍40多部。
+- **智能医学工程（负责人李凯教授）**：研究内容为脑认知与脑疾病智能诊疗及康复、健康大数据分析与智慧医疗、脑机接口高端数字医疗器械、中医先进医疗器械研发、脑部及精神系统重大疾病（阿尔茨海默病、帕金森病、抑郁症、自闭症等）智能诊断；主持参与国家级项目3项、省部级重点研发计划及200万以上重大设计项目，与中国人民解放军总院、浙一医院、日本文化研究所等单位开展合作；与浙大联合研制的阿尔茨海默病数字预警仪已申报二类医疗器械。
+### 师资队伍与领军人物
+- **总体规模**：专任教师90人，高级职称53人（占30%以上），博士55人；硕导69人，正高35人，博士46人。
+- **人才称号**：教育部医学技术类专业技能教授委员会委员、省万人创新人才2人次、浙江省151人才5人、省杰青1人、省高层次创新人才2人、省派义乌市校创新领军团队1个。
+- **吕建新教授**：学位点负责人，博士，国家百千万人才工程入选者、国家行业企业专家、15万人计划技术人才、领军人才，教育部医学技术类专业教学指导委员会委员、国家自然基金会医学技术检验学科专家组组长、中华医学会检验学会教育学组组长；主持国家自然科学基金重点项目、科技部重点研发、863计划重点项目、省科技重点研发应急公关项目等十余项，发表高水平论文200多篇，获省科技一等奖3项、优秀教学成果奖2项。
+- **徐秀芳教授**：博士，浙江省151人才第3层次、省高校中青年学科带头人、研究生院院长兼医学影像学院院长、国家一流本科专业建设点医学影像技术专业负责人、教育部教指委相关医学分会委员、中华医学会影像技术分会影像技术专委会委员。
+- **叶祥明教授**：省人民医院主任医师、二级教授、博导、博士后导师，省卫生领军人才、国家区域医疗中心浙江省重点培育专科康复医学学科带头人、数字化康复装备省部研究中心常务副主任；主持国家级课题3项、省重大课题2项，发表SCI论文98篇。
+- **金大志研究员**：博士、硕导，美国华盛顿大学博士后、美国MSCC访问学者，省创新人才、卫生创新人才，检验医学院学术院长、省生物标志物与器官诊断转化重点实验室主任、中国医师协会临床微生物分会常务委员；主持国家自然科学基金面上项目、863子项、科技部重大专项子课题、省重点研发计划、省自然基金重点项目、省部共建重大项目共25项，发表SCI论文50多篇，参编专著6部，获省科技进步二等奖1项、三等奖1项。
+- **李凯教授**：信息工程学院院长，复旦大学公共卫生学院博士、早稻田大学访问学者，智能医学前沿交叉学科研究院执行院长、智能医学学科负责人、浙江省中医药大学学科带头人。
+### 硕士培养与毕业去向
+- **培养目标**：面向健康中国发展需要，紧密服务区域行业产业发展，围绕国际学术前沿、国际重大需求和转化研究，培养熟练掌握医学技术领域专业知识技能、具有良好创新实践能力的高层次应用型人才。
+- **培养方式与学制**：采用教学、专业实践与学位论文相结合的方式；全日制专业学位学制三年，最长不超过五年。
+- **课程学分要求**：毕业前学业课程不少于24学分，其中专业必修课分方向≥12学分，专业选修课（智慧医疗、中医康复治疗学、生物信息学等）≥6学分。
+- **医院就业方向**：检验方向可进入检验科、输血科、病理科；影像技术方向可进入放射科、超声科；康复治疗方向可进入康复医学科、骨科、神经科、运动医学科。
+- **其他就业方向**：卫检方向可进入疾病预防控制中心（CDC）参与传染病防控、慢性病防治等公共卫生工作；企业领域包括医药企业与生物技术公司（研发、生产、市场销售、质量管理法规）、医疗器械公司（研发、销售、技术支持）、保险公司（医疗保险核保理赔、健康险产品开发）；还可进入药监局、卫健委、海关从事医疗器械监管、卫生政策制定及口岸卫生检疫，或到高校、研究所继续深造读博。
+### 2026年招考计划
+- **计划招生人数**：2026年计划招生34人，实际以教育部2026年正式下达人数为准。
+- **初试科目**：思想政治理论、英语为统考科目；专业课按方向自主命题——检验考检验综合、影像技术考医学影像技术综合、康复治疗考康复治疗综合、智能医学工程考智能医学工程综合。
+- **检验综合考试内容**：分子生物学检验、生物化学检验、微生物学检验，占比分别为40%、30%、30%。
+- **考试大纲**：实践分值300分，考试时长180分钟，含考试内容、形式、试卷结构、知识点及参考书目；具体以杭州医学院研究生招生网公布为准。
+- **复试安排**：初试占60%、复试占40%；复试内容为英语能力测试20%、专业能力测试40%、综合能力测试40%；复试形式目前以线下为主，具体以学校复试录取办法为准。
+## 各方立场与诉求
+1. **考生（经主持人代问）**：关注当前经济形势下医学技术专业研究生毕业后的就业前景，担心就业出口与竞争力。
+2. **宋宝峰**：回应称就业面宽广且具竞争力，毕业生可继续深造读博，也可进入三甲医院、疾控中心、医药企业与生物技术公司、医疗器械公司、保险公司、药监局、卫健委、海关、高校、研究所等单位；强调杭州高水平三甲医院及企业对研究生及以上学位者需求大，劝考生不必过度担心和焦虑。
+3. **考生（经主持人代问）**：询问硕士研究生入学考试初试科目有哪些，以及暑期如何备考。
+4. **宋宝峰**：回应称初试共三门，思想政治理论、英语为统考，专业课按报考方向自主命题（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合）；建议暑期重点复习，英语难度介于四级和六级之间，专业课可关注杭州医学院研究生招生网及研究生教育微信公众号获取大纲与参考教材。
+5. **考生（经主持人代问）**：关注跨专业报考问题，担心非本专业考生报考受限。
+6. **宋宝峰**：明确表示允许非本专业考生跨专业报考，如从事检验的可以报考检验方向，跨专业报考被录取概率会大大提高。
+7. **考生（经主持人代问）**：关注学校地理位置、交通条件及研究生参加学科竞赛的机会。
+8. **宋宝峰**：回应称学校有三个校区，主体在市中心黄路校区，交通便利；学校重视竞赛，设有资源提升改善、专门讲座与培训，研究生在竞赛中取得良好成绩，强调以赛促学、以赛促教、以赛促改。
+## 达成共识
+1. **招生口径已确认**：2026年医学技术专业硕士点计划招生34人，**实际招生人数以教育部2026年正式下达人数为准**，当前数字仅供考生参考。
+2. **初试科目与考试大纲已明确**：初试共三门，思想政治理论、英语为统考科目，专业课按报考方向自主命题（检验综合、医学影像技术综合、康复治疗综合、智能医学工程综合）；考试大纲含考试内容、形式、试卷结构、具体知识点及参考书目，以杭州医学院研究生招生网公布为准。
+3. **复试安排已确认**：复试目前以线下为主，初试成绩占60%、复试成绩占40%；复试内容分为英语能力测试（20%）、专业能力测试（40%）、综合能力测试（40%）三个环节，具体以学校复试录取办法为基础，可参考2025年复试办法。
+4. **跨专业报考政策已明确**：**允许非本专业考生跨专业报考**，如从事检验工作的考生可报考检验方向，宋宝峰书记明确表示跨专业报考被录取概率会大大提高。
+5. **就业前景判断已形成共识**：宋宝峰书记确认该专业就业面宽广，毕业生可进入医院相关科室、疾控中心、医药企业与生物技术公司、医疗器械公司、保险公司、药监局、卫健委、海关、高校、研究所等单位，也可继续深造读博；目前虽无毕业生，但**对高质量充分就业有信心**。
+6. **备考建议已给出**：英语考试难度介于四级和六级之间，暑期是备考关键期；专业课复习以学校研究生招生网及研究生教育微信公众号公布的方向、大纲、参考教材为准。
+## 待协调事项与后续
+### 待协调事项
+- [ ] **2026年实际招生人数确认**（杭州医学院研究生招生网 ｜ 教育部 ｜ 以教育部2026年正式下达人数为准）：目前计划招生34人，仅作参考
+- [ ] **初试考试大纲与参考书目确认**（杭州医学院研究生招生网 ｜ 考生 ｜ 以官网公布为准）：各方向专业综合课程为学校自主命题，具体考试内容、形式、试卷结构及参考书目需以官网发布为准
+- [ ] **复试具体形式与内容确认**（杭州医学院 ｜ 考生 ｜ 以2026年复试录取办法为准）：目前可参考2025年复试办法，复试以线下为主，具体安排届时公布
+### 后续安排与参与方式
+- **官方信息渠道**：杭州医学院研究生招生网（研究生招生.杭州医学院.education.cn），考生需经常关注；另可关注「杭州医学院研究生教育」微信公众号，可查看考试方向、大纲及参考教材书籍
 - **直播回看**：本场直播结束后24小时内上传至B站，考生可随时搜索回看
-- **信息发布渠道**：杭州医学院官网、杭州医学院研究生招生网（研究生招生.杭州医学院.教育.cn）、杭州医学院研究生教育微信公众号
-- **报考咨询**：考生可通过B站、微博、抖音弹幕区留言，嘉宾将进行点评答疑
-- **初试科目**：思想政治理论、英语（难度介于四级和六级之间）、专业综合（按方向考检验综合、医学影像技术综合、康复治疗综合或智能医学工程综合）
-- **专业综合考试**：分值300分，时长180分钟；检验综合中分子生物学检验占40%、生物化学检验占30%、微生物学检验占30%
-- **复试安排**：初试占60%、复试占40%；复试内容为英语能力测试占20%、专业能力测试占40%、综合能力测试占40%
-- **跨专业报考**：允许并鼓励非本专业考生跨专业报考医学技术专业硕士点
-- **备考建议**：暑期为关键备考期，英语可参照四级至六级之间难度准备，专业课聚焦学校公布的大纲与参考教材
-- **校区情况**：学校有三个校区，主校区位于市中心黄龙校区，交通便利
-- **学科竞赛**：学校重视研究生学科竞赛，设有资源提升改善、专门选手讲座与培训，研究生在竞赛中取得好成绩</t>
+- **报考咨询**：考生可通过B站、微博、抖音弹幕区留言，嘉宾将进行答疑解惑
+- **备考建议**：暑期为备考关键期，英语考试难度介于四级和六级之间，建议以研究生考试英语真题为参照；思想政治理论需与时俱进学习备考</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>73.40000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>23026/5597</t>
+          <t>23026/5588</t>
         </is>
       </c>
     </row>
@@ -11824,71 +11861,81 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t># 课程概况
-本次课程为历史小论文写作专题课，由主讲人围绕小论文写作的基本要求与四类题型（自命题、观点提示、图表信息等）的解题方法展开讲解。课程强调小论文必须亮明观点且具有凝聚力，论证部分以两到三条为宜，写作顺序为先交代背景学术报告，再亮出自己的观点，最后进行论述升华，论述需逻辑清晰，可用序号或时间脉络罗列，结尾须升华观点而非简单重复。自命题类题型解题步骤为先审题看要求，再读材料抓主要信息，最后罗列与材料相关的事实并控制篇幅；观点提示类题型需选择核心观点并明确表述，不能照抄材料观点；图表信息类题型需快速看题头、横向纵向信息，注意关系变化，提取有效信息后再分析。课程通过武汉长江大桥、1940年抗战时期材料等例题分析学生作答，指出观点不明确、论证条数过多、照抄材料观点、逻辑不清等常见问题并给出改进建议。
-# 核心知识点梳理
-## 小论文写作基本要求
-- **观点必须明确亮出**：不能只是简单陈述形式或罗列名词，要形成有凝聚力的观点，如「辉煌的中华文化」需表述自己的观点而非仅加名词。
-- **论证条数控制**：论证一般写**两到三条**，不宜过多；写一条难以支撑论点，太多则显冗长。
-- **写作顺序**：先打开背景的学术报告，再亮出自己的观点；最后进行论述升华，不能简单把观点抄一遍。
-- **逻辑呈现方式**：可用序号或时间脉络（如700时期、明清时期）罗列，也可按国内外、内政外交等维度分组，但必须让老师清楚看到你写了几条、各条内容。
-- **结尾论述要求**：最后论述要简便并升华观点，目的是提升观点高度，不能简单重复前文。
-## 自命题类题型解题方法
-- **审题步骤**：先阅读题目、慢点审题，看要求（如用世界史知识、限定范围），注意「小红帽」要求及形成标准。
-- **读材料方法**：先大概看材料抓主要信息，再细看材料之间的关系，提取有效信息。
-- **罗列事实**：题目先写好再罗列事实，不要直接写在答题卡上；罗列的事实要与材料有关系，避免乱罗列。
-- **武汉长江大桥例题**：背景可写新中国成立或改革开放以来；对内改革与对外开放按时间顺序，**先写对内改革再写对外开放**。
-- **常见问题**：学生作答时只看到屏幕写得好但未结合材料，或背景直接当成一个版本写，缺乏与材料的关联。
-## 观点提示类题型解题方法
-- **核心观点选择**：需选择核心观点并明确表述，判断观点正确或错误，不能照抄材料观点。
-- **例题材料背景**：1940年抗战时期材料，涉及国民对本国的历史应略有所知、了解本国历史对国家利益有威胁和利益、对本国历史有定义时不会偏激理解或推责于古人等四个观点。
-- **第二条观点阐述**：了解本国历史对国家利益有威胁和利益，需敬畏祖国意志；中华文化有很强优越性，如丝绸之路、四大发明对欧洲贡献、为东亚提供文化影响。
-- **第三条观点阐述**：对本国历史有定义时，不会偏激民族主义，也不会站在历史制高点推责于古人；需通达文化，连接历史与现在。
-- **写作要求**：不能照抄材料观点，需有自己的判断；结论需做出具体判断，不能重复材料观念。
-## 图表信息类题型解题方法
-- **读图方法**：快速看图表关键信息（题头、横向纵向），注意信息之间的关系变化，提取有效信息后再进行分析。
-- **例题类型**：涉及历史地图、数据等，需结合材料关系进行分析。
-- **历史地图题**：如707年、1900年等时间点，需在地图上画位置，注意修改补充（14年到现在每年修改）。
-- **建筑类题**：展现两三个图线，从建筑角度说明建筑与政治的关系，提取有效信息后结合材料与实践关系进行论述。
-- **共同体框架题**：涉及共同外交安全政策、司法和内部合作等大框架制度，提取三个信息后分析它们之间的关系再下结论。
-# 课堂互动与答疑
-**学生**：论证部分一般写几条比较合适？
-**教师**：写两到三条即可，不宜过多。写一条难以支撑论点，写太多又显得冗长，两三条既能充分论证又保持结构清晰。
-**学生**：自命题类题目解题时应该按什么步骤来？
-**教师**：先审题，看清题目要求，注意其中可能隐含的限定条件（如要求用世界史知识或限定在某一范围）；再读材料，先大致浏览抓主要信息，再细看材料之间的关系；最后罗列事实，先想好要写哪些与材料相关的事实再动笔，不要直接写在答题卡上。
-**学生**：武汉长江大桥这道题，背景部分可以怎么写？
-**教师**：可以写新中国成立，也可以写改革开放以来，关键是要有明确的时间定位。如果涉及对内改革和对外开放，按时间顺序应先写对内改革，再写对外开放。
-**学生**：观点提示类题目中，如何选择和处理观点？
-**教师**：要选择一个核心观点并明确表述自己的判断，不能照抄材料观点。需结合材料中的关键信息点，如历史背景、国家利益等，形成自己的独立见解，并在论述中详细展开。
-**学生**：图表信息类题目应该怎样快速把握材料？
-**教师**：先看题头、横向纵向信息，快速提取关键信息，注意信息之间的关系变化，再结合材料关系进行分析。图表可能涉及历史地图、数据等，要抓住主要信息点，不要被细节干扰。
-# 课后任务与学习建议
-## 课堂练习
-- **武汉长江大桥例题（自命题类）**：考点为新中国成立以来的重大国家建设成就，方法为审题后先写题目、再罗列与材料相关的事实；结论要点是背景可写新中国成立或改革开放以来，对内改革与对外开放须按时间顺序先写对内改革、再写对外开放。
-- **1940年抗战时期材料例题（观点提示类）**：考点为评析材料观点并任选两个事件融合论证，方法为选择核心观点、明确表述自己的判断、不重复材料观点；结论要点是国民应对本国历史略有所知、了解本国历史与国家利益相关、需敬畏祖国意志。
-- **历代民德等级变化图表例题（图表信息类）**：考点为从图表题头、横向纵向信息中提取关键信息并分析关系变化，方法为快速看图表关键信息、注意信息间关系、提取有效信息后再分析；结论要点是民德变化与制度改善、国家强盛的关系。
-- **梁启超观点例题（观点提示类）**：考点为评析梁启超关于中国某时期具有合理性的观点，方法为先亮明自己的观点再阐述论证；结论要点是突出「人人独善其身，人人相善其群」的中华传统精神，联系国家是否强盛、民德是否高尚与制度是否改善的关系。
-## 复习重点
-- **小论文写作基本要求**：观点必须明确亮出、具有凝聚力，不能只是简单陈述形式；论证部分写两到三条为宜，不宜过多；写作顺序为先写背景学术报告，再亮出自己的观点，最后进行论述升华。
-- **论述逻辑与结构**：论述需逻辑清晰，可用序号或时间脉络（如700时期、明清时期）罗列，也可按国内国外、内政外交等维度分类，但必须让阅卷者清楚看到所写内容；结尾论述要升华观点，不能简单重复观点。
-- **自命题类题型解题步骤**：先审题看要求（如小红帽要求及形成标准），再读材料抓主要信息，最后罗列与材料相关的事实并控制篇幅；题目先写好再罗列事实，避免直接写在答题卡上导致错乱。
-- **观点提示类题型解题方法**：需选择核心观点并明确表述自己的判断，不能照抄材料观点；不同观点需在论点中详细表述，关键时候还要注意对观点进行判断和升华。
-- **图表信息类题型解题方法**：需快速看图表关键信息（题头、横向纵向信息），注意信息之间的关系变化，提取有效信息后再进行分析；例题涉及历史地图、数据等，需结合材料关系进行解读。
-## 学习建议
-- **审题训练**：审题要慢，仔细看题目要求，注意「小红帽」等关键要求及形成标准；审题时注意题目是否限定用世界史知识或特定范围，避免答非所问。
-- **写作练习步骤**：先写题目，再罗列要使用的事实，确保事实与材料相关、不乱罗列；罗列好后先审题确认，再开始写作，最后进行结论升华。
-- **观点提炼练习**：练习从材料中提炼明确观点，避免只做简单陈述；可用「我认为……的观点是如何如何的」句式训练观点表述，注意观点需有凝聚力。
-- **论证条数控制**：论证部分写两到三条即可，不宜过多也不宜过少；写一条难以支撑论点，写太多则可能内容无法支撑，需根据材料合理取舍。
-- **时间脉络梳理**：写作时可用时间顺序（如700时期、明清时期）或国内外、内政外交等维度罗列内容，确保逻辑清晰、层次分明。
-- **例题复盘**：课后可复盘武汉长江大桥、1940年抗战时期材料、历代民德等级变化图表等例题，对照官方答案检查自己的观点表述、论证结构和结论升华是否到位。</t>
+          <t># 历史小论文写作方法与解题技巧讲解
+## 课程概况
+本次课程为历史小论文写作专题课，由老师主讲，围绕小论文写作要求与三类题型（自命题、观点提示、图表信息）的解题方法展开。老师强调小论文必须亮明观点，观点需有凝聚力，不能只是简单陈述形式；论证部分写两到三条，不宜过多；写作结构包括背景、观点、论证、总结，总结需升华观点，不能简单抄写观点。课程依次讲解三类题型的解题步骤：自命题类需先审题，注意要求（如用世界史知识、范围限制），再读材料抓主要信息，最后罗列与材料相关的事实并控制篇幅；观点提示类需先看观点，选择核心观点，明确表达判断，不能照抄材料；图表信息类需快速看图表关键信息（题头、横向纵向），注意信息之间的关系变化，提取有效信息进行分析。课程通过例题分析学生作答，如武汉长江大桥自命题、观点提示类材料评析、图表信息类题目等，指出学生作答中的问题，如观点不明确、照抄材料、未注意时间顺序等，并给出改进建议。
+## 核心知识点梳理
+### 小论文写作总体要求
+- **观点必须明确亮出**：不能只是简单陈述形式或罗列几个方面加个名词，观点要有凝聚力，必须把自己的观点表述清楚。
+- **论证条数控制**：论证部分一般写两到三条，不宜过多；写一条可能无法支撑论点，写太多则显得冗长。
+- **写作结构**：先打开背景的学术报告，再亮出自己的观点，然后进行论证，最后进行总结论述。
+- **总结需升华观点**：最后的总述或功效论述要简便，目的是升华观点，不能简单地把观点抄一遍。
+### 自命题类解题步骤
+- **审题**：先阅读题目、慢点审题，注意要求，如用世界史知识或限定在某个范围（如"在谁谁的范围"）；注意题目中的"小红帽"要求及形成标准。
+- **读材料**：认真读材料，先大概看一下抓主要信息，再细看材料之间的关系。
+- **罗列事实**：先写好题目，再罗列与材料相关的事实，不要乱罗列；最好先打草稿，不要直接写在答题卡上，避免写错又乱。
+- **控制篇幅**：注意控制字数，最后再进行总结升华。
+### 观点提示类解题方法
+- **选择核心观点**：先看有哪些观点，然后按照观点与材料的关系，选择一个核心观点，明确表达自己的判断（正确或错误）。
+- **不能照抄材料**：写的时候不能照抄材料观点，要详细表述自己的论点。
+- **总结升华**：最后要简单总结观点，并进行升华。
+### 图表信息类解题方法
+- **快速提取关键信息**：迅速看图表的关键信息，包括题头、横向纵向信息。
+- **分析信息关系**：注意信息之间的关系变化，提取有效信息后再进行分析。
+- **例题说明**：以图表信息类题目为例，需注意图表中不同时期的数据变化（如春秋、东汉、宋明等时期），结合时代背景（如儒家思想、社会状态）进行分析。
+### 例题分析：武汉长江大桥（自命题）
+- **学生作答思路**：学生从新中国成立、改革开放等背景切入，分析武汉长江大桥的意义，但老师指出其审题未注意要求，且未明确写出具体时间（如"新中国成立后""改革开放以来"）。
+- **老师点评**：写作应按时间顺序，先写对内改革再写对外开放；背景部分不能直接当成一个版本，要结合材料与观点。
+### 例题分析：观点提示类材料评析
+- **材料内容**：材料给出四个观点，如"国民对其本国历史应该略有所知""对本国历史有所知者必对我国利益有威胁和利益""对本国历史有悟空和定者不会偏激理解"等。
+- **学生作答**：学生选择第二条观点，从中华文化的优越性（如丝绸之路、四大发明对欧洲的贡献）进行论证。
+- **老师点评**：学生需注意写作背景（1940年抗战时期），说明为何在此时期写此内容；论证要结合具体史实，不能泛泛而谈。
+### 例题分析：图表信息类（历代民德等级变化）
+- **题目内容**：图表展示历代民德等级变化，涉及春秋、东汉、宋明等时期。
+- **学生作答**：学生从"古代民德的变化与文学"角度切入，选取春秋、东汉、宋明等时期进行分析。
+- **老师点评**：可结合时代背景（如儒家思想、社会状态）分析民德变化原因；官方答案引用梁启超观点"人人独善其身，人人相善其群"，并联系中华传统精神，说明国家是否强盛、民德是否高尚与制度是否改善的关系。
+## 课堂互动与答疑
+### Q1. 自命题小论文如何确定观点并展开论证？
+- **学生**：自命题小论文的观点应该怎么定？论证部分写几条合适？
+&gt; **教师**：观点必须明确亮出，不能只是简单陈述形式或罗列几个方面加个名词，要有凝聚力。论证部分写两到三条即可，一条难以支撑论点，太多则显得松散。写作结构为背景学术报告、观点、论证、总结，总结需升华观点，不能简单抄写观点。
+### Q2. 自命题类题目审题和读材料时要注意什么？
+- **学生**：自命题类题目解题时，审题和读材料有哪些要点？
+&gt; **教师**：先审题，注意要求，如用世界史知识或限定范围，留意“小红帽”要求和评分标准。读材料先抓主要信息，再细看材料间关系。先写题目，再罗列与材料相关的事实，避免直接写在答题卡上，控制篇幅，罗列要清晰，可按时间脉络或国内外等维度组织。
+### Q3. 观点提示类题目如何选择观点并避免照抄材料？
+- **学生**：观点提示类题目怎么选观点？能不能直接照抄材料里的观点？
+&gt; **教师**：需先看材料给出的观点，选择核心观点，明确表达自己的判断，如认为某观点正确或错误，并在论点中详细表述。不能照抄材料观点，要形成自己的看法。最后总结时需升华观点，不能简单重复。
+### Q4. 图表信息类题目如何提取有效信息？
+- **学生**：图表信息类题目怎么快速抓住关键信息？
+&gt; **教师**：先快速看图表关键信息，如题头、横向纵向内容，注意信息之间的关系变化，提取有效信息后再进行分析。例如历史地图题需关注位置关系，表格题需看数据变化趋势，再结合材料进行论述。
+### Q5. 评析材料观点时如何避免重复材料原话？
+- **学生**：评析材料观点时，结论部分怎么避免重复材料原话？
+&gt; **教师**：结论需自己做出具体判断，不能重复材料观点。例如评析钱穆《国史大纲》材料时，可结合抗战背景分析其写作目的，再提出自己的看法，如对本国历史应有所知、敬畏祖国历史等，结论要体现个人理解。
+### Q6. 图表题中历史时期选择如何与观点匹配？
+- **学生**：图表题中选历史时期时，怎么判断选哪个时期更合适？
+&gt; **教师**：选时期需与观点匹配，如写“古代人的变化与文学”可整体论述，也可选春秋、东汉、宋明等时期。选时期时需考虑典型事件支撑，如东汉可结合具体史实，若不确定可不选。注意图表中数据变化与时代背景的关系，如唐朝国力强盛但民德评价不高，需结合制度、社会状态分析。
+## 课后任务与学习建议
+### 课堂练习
+- [ ] **武汉长江大桥自命题练习**：围绕武汉长江大桥自拟题目，练习审题与观点提炼，注意材料中时间信息（如新中国成立、改革开放）与对内改革、对外开放的时间顺序，先写对内改革再写对外开放。
+- [ ] **观点提示类材料评析**：评析材料中关于国民了解本国历史的观点，任选材料中两个观点进行论证，结论需自己做出具体判断，不能重复材料观点。
+- [ ] **图表信息类练习**：快速提取图表题头、横向纵向信息，注意信息之间的关系变化，如历代民德等级变化图，结合时代背景（如唐朝国力强盛、宋明时期）分析民德与制度、国家强盛的关系。
+### 复习重点
+- **小论文写作结构**：背景学术报告→亮明观点→两到三条论证→总结升华，总结不能简单抄写观点，需升华观点。
+- **自命题类解题步骤**：先审题（注意用世界史知识或特定范围等要求），再读材料抓主要信息，先写题目再罗列与材料相关的事实，控制篇幅避免直接写在答题卡上。
+- **观点提示类解题方法**：先看观点，选择核心观点并明确表达判断（正确或错误），不能照抄材料，最后总结升华。
+- **图表信息类解题方法**：快速看图表关键信息（题头、横向纵向），注意信息之间的关系变化，提取有效信息进行分析。
+### 学习建议
+- **审题要慢**：注意题目要求中的"小红帽"（关键要求）及评分标准，如要求用世界史知识就不能用中国史内容。
+- **罗列事实先想好**：罗列的事实要与材料有关系，不要乱罗列，按时间脉络（如先秦、宋明、明清）或国内外等逻辑清晰排列。
+- **观点要亮明**：不能只是简单陈述形式或几个方面加个名词，观点需有凝聚力，可写一句诗作为观点但必须合适。
+- **总结要升华**：最后论述要升华观点，不能简单把观点抄一遍，要说明写这个东西是为了什么。</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>47.7</v>
+        <v>38.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12357/3523</t>
+          <t>12357/3595</t>
         </is>
       </c>
     </row>
@@ -12044,130 +12091,131 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t># 报告概况
-十四届全国人大三次会议于2025年开幕，出席代表2880人，符合法定人数。会议第一项议程为审议政府工作报告，国务院总理李强代表国务院作报告。报告回顾2024年工作，指出全年经济社会发展主要目标任务顺利完成，国内生产总值达134.9万亿元、增长5%；同时部署2025年经济社会发展总体要求、主要预期目标及政府工作任务，强调坚持稳中求进工作总基调，实施更加积极的财政政策和适度宽松的货币政策，大力提振消费、发展新质生产力、防范化解重点领域风险、保障和改善民生，确保“十四五”规划圆满收官。
-# 核心政策
-## 2025年经济社会发展总体要求与主要预期目标
-- **总体要求**：坚持稳中求进工作总基调，完整准确全面贯彻新发展理念，加快构建新发展格局，扎实推动高质量发展，进一步全面深化改革，扩大高水平对外开放，建设现代化产业体系，更好统筹发展和安全，实施更加积极有为的宏观政策，推动经济持续回升向好，高质量完成`十四五规划`目标任务。
-- **国内生产总值**：增长**5%左右**，既是稳就业、防风险、惠民生的需要，也有经济增长潜力和有利条件支撑，并与中长期发展目标相衔接。
-- **就业目标**：城镇调查失业率**5.5%左右**，城镇新增就业**1200万人以上**。
-- **物价目标**：居民消费价格涨幅**2%左右**。
-- **收入与收支**：居民收入增长和经济增长同步，国际收支保持基本平衡。
-- **粮食产量**：**1.4万亿斤左右**。
-- **能耗目标**：单位国内生产总值能耗降低**3%左右**，生态环境质量持续改善。
-## 宏观政策取向
-- **财政政策**：实施更加积极的财政政策，今年赤字率拟按**4%左右**安排，赤字规模**5.66万亿元**。
-- **政府债券**：拟发行超长期特别国债**1.3万亿元**；拟发行特别国债**5000亿元**支持国有大型商业银行补充资本；安排地方政府专项债券**4.4万亿元**；合计新增政府债务总规模**11.86万亿元**，比上一年增加**2.9万亿元**。
-- **支出结构**：加快各项资金下达，中央财政加大地方一般性转移支付力度，筑牢兜实基层`三保`底线；政府坚持过紧日子，腾出更多资金用于发展所需、民生所需。
-- **货币政策**：实施适度宽松的货币政策，适时降准降息，保持流动性充裕，使社会融资规模、货币供应量增长同经济增长、价格总水平预期目标相匹配。
-- **政策导向**：强化宏观政策民生导向，经济政策的着力点更多转向惠民生、促消费，推动更多资金资源`投资于人`、服务于民生；健全和用好宏观政策取向一致性评估工作机制，提升政策目标、工具、时机、力度、节奏的匹配度。
-## 2025年政府工作任务
-### 大力提振消费、扩大国内需求
-- **提振消费专项行动**：制定提升消费能力、增加优质供给、改善消费环境专项措施，释放多样化、差异化消费潜力。
-- **以旧换新**：安排超长期特别国债**3000亿元**支持消费品以旧换新。
-- **扩大服务消费**：扩大健康、养老、托幼、家政等多元化服务供给，加快数字、绿色、智能等新型消费发展，释放文化、旅游、体育等消费潜力。
-- **扩大有效投资**：今年中央预算内投资已安排**7350亿元**；用好超长期特别国债更大力度支持`两重建设`；优化地方政府专项债券管理机制，支持和鼓励民间投资发展。
-### 发展新质生产力、建设现代化产业体系
-- **培育新兴产业和未来产业**：深入推进战略性新兴产业融合集群发展，开展`新技术、新产品、新场景大规模应用示范行动`，培育生物制造、量子科技、具身智能、6G等未来产业。
-- **推动传统产业改造升级**：深入实施`制造业重大技术改造升级和大规模设备更新工程`，加快制造业数字化转型，开展`标准提升引领传统产业优化升级行动`。
-- **激发数字经济创新活力**：持续推进`人工智能+`行动，大力发展智能网联新能源汽车、人工智能手机和电脑、智能机器人等新一代智能终端，扩大5G规模化应用，优化全国算力资源布局，深化数据资源开发利用。
-### 实施科教兴国战略
-- **高质量教育体系**：制定实施`教育强国建设三年行动计划`，加强义务教育学校标准化建设，扩大高中阶段教育学位供给，逐步推行免费学前教育，加快`双一流`建设。
-- **高水平科技自立自强**：加快组织实施和超前布局重大科技项目，优化国家战略科技力量布局，推进科研院所改革，加强企业主导的产学研深度融合，从制度上保障企业参与国家科技创新决策、承担重大科技项目。
-- **人才队伍建设**：加快建设国家战略人才力量，大力支持和大胆使用青年科技人才，建设一流产业技术工程队伍，深化人才分类评价改革。
-### 推动标志性改革举措落地
-- **激发经营主体活力**：高质量完成`国有企业改革深化提升行动`，扎实落实促进民营经济发展的政策措施，加力推进清理拖欠企业账款工作，开展`规范涉企执法专项行动`。
-- **全国统一大市场**：破除地方保护和市场分割，综合整治`内卷式竞争`，修订出台新版市场准入负面清单，构建统一的信用修复制度，完善企业简易注销。
-- **财税金融改革**：开展中央部门`零基预算改革试点`，支持地方深化零基预算改革，加快推进部分品目消费税征收环节后移并下划地方；深化资本市场投融资综合改革，大力推动中长期资金入市。
-### 扩大高水平对外开放
-- **稳外贸**：优化融资结算、外汇等金融服务，扩大出口信用保险承保规模和覆盖面，促进跨境电商发展，加强海外仓建设，拓展境外经贸合作区功能，培育绿色贸易、数字贸易等新增长点。
-- **稳外资**：推进服务业扩大开放综合试点示范，扩大电信、医疗、教育等领域开放试点，推动自贸试验区提质增效和扩大改革任务授权。
-- **共建`一带一路`**：统筹推进重大标志性工程和`小而美`民生项目建设，强化法律、金融、物流等海外综合服务，优化产业链供应链国际合作布局。
-- **多双边合作**：持续扩大面向全球的高标准自由贸易区网络，坚定维护以世界贸易组织为核心的多边贸易机制。
+          <t># 十四届全国人大三次会议开幕 审议政府工作报告
+## 报告概况
+十四届全国人大三次会议于2025年开幕，出席代表2880人，符合法定人数。会议第一项议程为审议政府工作报告，国务院总理李强代表国务院作报告，回顾2024年工作并部署2025年任务。报告以“稳中求进”为总基调，强调高质量发展，提出2025年国内生产总值增长5%左右等主要预期目标，并部署大力提振消费、发展新质生产力、防范化解风险等十大任务，整体基调积极有为、迎难而上。
+## 核心政策
+1. **2025年经济社会发展主要预期目标**：国内生产总值增长**5%左右**；城镇调查失业率**5.5%左右**；城镇新增就业**1200万人以上**；居民消费价格涨幅**2%左右**；居民收入增长和经济增长同步；国际收支保持基本平衡；粮食产量**1.4万亿斤左右**；单位国内生产总值能耗降低**3%左右**；生态环境质量持续改善。
+2. **更加积极的财政政策**：今年赤字率拟按**4%左右**安排，赤字规模**5.66万亿元**；拟发行超长期特别国债**1.3万亿元**；拟发行特别国债**5000亿元**支持国有大型商业银行补充资本；安排地方政府专项债券**4.4万亿元**；今年合计新增政府债务总规模**11.86万亿元**，比上一年增加**2.9万亿元**；中央财政加大地方一般性转移支付力度，筑牢兜实基层`三保`底线。
+3. **适度宽松的货币政策**：适时降准降息，保持流动性充裕，使社会融资规模、货币供应量增长同经济增长、价格总水平预期目标相匹配；优化和创新结构性货币政策工具，更大力度促进楼市股市健康发展；进一步疏通货币政策传导渠道，推动社会综合融资成本下降。
+4. **全方位扩大国内需求**：实施`提振消费专项行动`，制定提升消费能力、增加优质供给、改善消费环境专项措施；安排超长期特别国债**3000亿元**支持消费品以旧换新；扩大健康、养老、托幼、家政等多元化服务供给；加快数字、绿色、智能等新型消费发展；今年中央预算内投资已安排**7350亿元**；用好超长期特别国债更大力度支持`两重`建设；优化地方政府专项债券管理机制，支持和鼓励民间投资发展。
+5. **因地制宜发展新质生产力**：培育壮大新兴产业、未来产业，开展`新技术、新产品、新场景大规模应用示范行动`；培育生物制造、量子科技、具身智能、6G等未来产业；深入实施`制造业重大技术改造升级和大规模设备更新工程`；持续推进`人工智能+`行动，大力发展智能网联新能源汽车、人工智能手机和电脑、智能机器人等新一代智能终端；扩大5G规模化应用，优化全国算力资源布局。
+6. **深入实施科教兴国战略**：制定实施`教育强国建设三年行动计划`，加强义务教育学校标准化建设，扩大高中阶段教育学位供给，逐步推行免费学前教育；加快组织实施和超前布局重大科技项目，加强企业主导的产学研深度融合；大力支持和大胆使用青年科技人才，深化人才分类评价改革。
+7. **推动标志性改革举措加快落地**：高质量完成`国有企业改革深化提升行动`；扎实落实促进民营经济发展的政策措施，加力推进清理拖欠企业账款工作，开展`规范涉企执法专项行动`；纵深推进全国统一大市场建设，综合整治`内卷式竞争`，修订出台新版市场准入负面清单；开展中央部门`零基预算改革试点`；深化资本市场投融资综合改革，大力推动中长期资金入市。
+8. **扩大高水平对外开放**：稳定对外贸易发展，扩大出口信用保险承保规模和覆盖面，促进跨境电商发展，加强海外仓建设；扩大电信、医疗、教育等领域开放试点；推动高质量共建`一带一路`走深走实；持续扩大面向全球的高标准自由贸易区网络，坚定维护以世界贸易组织为核心的多边贸易机制。
+9. **有效防范化解重点领域风险**：持续用力推动房地产市场止跌回稳，合理控制新增房地产用地供应，推进收购存量商品房，有效防范房企债务违约风险，加快构建房地产发展新模式；稳妥化解地方政府债务风险，完善和落实一揽子化债方案，做好地方政府隐性债务置换工作；一体推进地方中小金融机构风险处置和转型发展，健全金融监管体系，强化央地监管协同。
+10. **着力抓好三农工作**：稳定粮食播种面积，主攻单产和品质提升，严守耕地红线，高质量推进高标准农田建设，深入实施`种业振兴行动`；确保不发生规模性返贫致贫，统筹建立农村防止返贫致贫机制和低收入人口、欠发达地区分层分类帮扶制度；有序推进第二轮土地承包到期后再延长30年试点，扩大整省试点范围。
+11. **推进新型城镇化和区域协调发展**：深入实施`新型城镇化战略行动`，科学有序推进农业转移人口市民化，全面推进常住地提供基本公共服务，强化随迁子女义务教育保障；持续推进城市更新和城镇老旧小区改造；支持经济大省挑大梁，深化东中西东北地区产业协作。
+12. **加快经济社会发展全面绿色转型**：持续深入推进蓝天碧水净土保卫战，全面推进以国家公园为主体的自然保护地体系建设；深入实施`绿色低碳先进技术示范工程`，培育绿色建筑等新增长点；积极稳妥推进碳达峰碳中和，建立一批零碳园区、零碳工厂，建立产品碳足迹管理体系、碳标识认证制度，加快建设沙戈荒新能源基地。
+13. **加大保障和改善民生力度**：实施重点领域、重点行业、城乡基层和中小微企业就业支持计划；城乡居民基础养老金最低标准再提高**20元**，适当提高退休人员基本养老金；制定促进生育政策，发放育儿补贴，大力发展托幼一体服务；深化以公益性为导向的公立医院改革，优化药品集采政策，严格医保基金监管；深入实施`安全生产治本攻坚三年行动`，抓好校园学生餐饮、平台外卖安全监管。
+## 重点工作
+### 扩大国内需求
+1. **提振消费专项行动**：实施提振消费专项行动，制定提升消费能力、增加优质供给、改善消费环境专项措施，释放多样化、差异化消费潜力；多渠道促进居民增收。
+   - 安排超长期特别国债3000亿元支持消费品以旧换新。
+   - 扩大健康、养老、托幼、家政等多元化服务供给；加快数字、绿色、智能等新型消费发展，释放文化、旅游、体育等消费潜力。
+   - 强化消费者权益保护，营造安心放心消费环境。
+2. **扩大有效投资**：发挥好各类政府投资工具作用，加快实施一批重点项目，切实选准选好项目，管好用好资金，坚决防止低效无效投资。
+   - 今年中央预算内投资已安排7350亿元。
+   - 用好超长期特别国债，更大力度支持“两重”建设；优化地方政府专项债券管理机制。
+   - 支持和鼓励民间投资发展，让民间资本有更大发展空间。
+### 现代化产业体系建设
+1. **培育壮大新兴产业、未来产业**：深入推进战略性新兴产业融合集群发展，开展新技术、新产品、新场景大规模应用示范行动。
+   - 培育生物制造、量子科技、具身智能、6G等未来产业。
+   - 加强产业统筹布局和产能监测预警，梯度培育创新型企业。
+2. **推动传统产业改造升级**：深入实施制造业重大技术改造升级和大规模设备更新工程，加快制造业数字化转型，开展标准提升引领传统产业优化升级行动，打造名品精品经典产业。
+3. **激发数字经济创新活力**：持续推进“人工智能+”行动。
+   - 大力发展智能网联新能源汽车、人工智能手机和电脑、智能机器人等新一代智能终端；扩大5G规模化应用。
+   - 优化全国算力资源布局，深化数据资源开发利用，促进平台经济规范健康发展。
+### 科教兴国战略
+1. **加快建设高质量教育体系**：制定实施教育强国建设三年行动计划。
+   - 加强义务教育学校标准化建设，扩大高中阶段教育学位供给，逐步推行免费学前教育。
+   - 扎实推进优质本科扩容，加快“双一流”建设；建设高素质专业化教师队伍，加强师德师风建设。
+2. **推进高水平科技自立自强**：加快组织实施和超前布局重大科技项目，优化国家战略科技力量布局，推进科研院所改革。
+   - 加强企业主导的产学研深度融合，从制度上保障企业参与国家科技创新决策、承担重大科技项目。
+   - 健全科技成果转化支持政策和市场服务；加强科学普及工作，弘扬科学家精神，推动形成鼓励探索、宽容失败的创新环境。
+3. **全面提高人才队伍质量**：加快建设国家战略人才力量，大力支持和大胆使用青年科技人才，建设一流产业技术工人队伍，深化人才分类评价改革。
+### 标志性改革举措
+1. **激发各类经营主体活力**：坚持和落实“两个毫不动摇”。
+   - 高质量完成国有企业改革深化提升行动；扎实落实促进民营经济发展的政策措施。
+   - 加力推进清理拖欠企业账款工作，开展规范涉企执法专项行动。
+2. **纵深推进全国统一大市场建设**：破除地方保护和市场分割，综合整治“内卷式”竞争。
+   - 修订出台新版市场准入负面清单，优化新业态新领域市场准入环境。
+   - 构建统一的信用修复制度，完善企业简易注销程序，逐步推广经营主体活动发生地统计。
+3. **深化财税金融体制改革**：开展中央部门零基预算改革试点，支持地方深化零基预算改革；加快推进部分品目消费税征收环节后移并下划地方。
+   - 深化资本市场投融资综合改革，大力推动中长期资金入市，加强战略性力量储备和稳市机制建设。
+### 高水平对外开放
+1. **稳定对外贸易发展**：优化融资结算、外汇等金融服务，扩大出口信用保险承保规模和覆盖面。
+   - 促进跨境电商发展，加强海外仓建设，拓展境外经贸合作区功能。
+   - 支持内外贸一体化发展，推动服务贸易创新发展，培育绿色贸易、数字贸易等新增长点。
+2. **大力鼓励外商投资**：推进服务业扩大开放综合试点示范，扩大电信、医疗、教育等领域开放试点。
+   - 加强外资企业服务保障，推动自贸试验区提质增效和扩大改革任务授权。
+   - 持续营造市场化、法治化、国际化一流营商环境。
+3. **推动高质量共建“一带一路”走深走实**：统筹推进重大标志性工程和“小而美”民生项目建设，强化法律、金融、物流等海外综合服务，优化产业链供应链国际合作布局。
+4. **深化多双边和区域经济合作**：持续扩大面向全球的高标准自由贸易区网络，坚定维护以世界贸易组织为核心的多边贸易体制。
 ### 防范化解重点领域风险
-- **房地产市场**：持续用力推动房地产市场止跌回稳，合理控制新增房地产用地供应，盘活存量用地和商办用房，推进收购存量商品房，有效防范房企债务违约风险，加快构建房地产发展新模式，推动建设安全、舒适、绿色、智慧的好房子。
-- **地方政府债务**：完善和落实一揽子化债方案，优化考核和管控措施，动态调整债务高风险地区名单，做好地方政府隐性债务置换工作，坚决遏制违规举债行为。
-- **金融领域风险**：一体推进地方中小金融机构风险处置和转型发展，综合采取补充资本金、兼并重组、市场退出等方式分类化解风险，健全金融监管体系，强化央地监管协同，完善应对外部风险冲击预案。
-### 抓好三农工作、推进乡村全面振兴
-- **粮食稳产保供**：稳定粮食播种面积，主攻单产和品质提升，严守耕地红线，高质量推进高标准农田建设，深入实施`种业振兴行动`，加快先进适用农机装备研发应用和农业科技成果大面积推广。
-- **巩固脱贫攻坚成果**：提高监测帮扶效率，确保不发生规模性返贫致贫，加强异地搬迁后续扶持，分类推进帮扶产业提质增效，统筹建立农村防止返贫致贫机制和低收入人口、欠发达地区分类分层帮扶制度，完善过渡期后帮扶政策体系。
-- **农村改革**：有序推进第二轮土地承包到期后再延长30年试点，扩大整省试点范围，因地制宜推动兴业强县富民一体发展，拓宽农民增收渠道，建设宜居宜业和美乡村。
-### 推进新型城镇化和区域协调发展
-- **农业转移人口市民化**：科学有序推进农业转移人口市民化，全面推进常住地提供基本公共服务，强化随迁子女义务教育保障，推动将符合条件的农业转移人口纳入住房保障体系，畅通参加社会保险渠道。
-- **城市更新**：持续推进城市更新和城镇老旧小区改造，打造宜居、韧性、智慧城市。
-- **区域战略**：发挥区域协调发展战略、区域重大战略、主体功能区战略的叠加效应，支持经济大省挑大梁，深化东中西东北地区产业协作。
-### 绿色低碳转型
-- **污染防治和生态建设**：持续深入推进`蓝天碧水净土保卫战`，全面推进以国家公园为主体的自然保护地体系建设，实施生物多样性保护重大工程，积极推进美丽中国先行区建设。
-- **绿色低碳经济**：深入实施`绿色低碳先进技术示范工程`，培育绿色建筑等新增长点，有力有效管控高耗能项目，加强废弃物循环利用，健全绿色消费激励机制。
-- **碳达峰碳中和**：建立一批零碳园区、零碳工厂，开展碳排放统计核算，建立产品碳足迹管理体系和碳标识认证制度，加快建设`沙戈荒`新能源基地，开展煤电低碳化改造试点示范。
+1. **推动房地产市场止跌回稳**：合理控制新增房地产用地供应，盘活存量用地和商办用房，推进收购存量商品房，有效防范房企债务违约风险。
+   - 有序搭建相关基础性制度，加快构建房地产发展新模式，推动建设安全、舒适、绿色、智慧的“好房子”。
+2. **稳妥化解地方政府债务风险**：完善和落实一揽子化债方案，优化考核和管控措施，动态调整债务高风险地区名单。
+   - 做好地方政府隐性债务置换工作，完善政府债务管理机制，坚决遏制违规举债行为。
+3. **积极防范金融领域风险**：一体推进地方中小金融机构风险处置和转型发展，综合采取补充资本金、兼并重组、市场退出等方式分类化解风险。
+   - 健全金融监管体系，强化央地监管协同，完善应对外部风险冲击预案，有效维护金融安全稳定。
+### 乡村全面振兴
+1. **增强粮食等重要农产品稳产保供能力**：稳定粮食播种面积，主攻单产和品质提升，严守耕地红线，高质量推进高标准农田建设。
+   - 深入实施种业振兴行动，加快先进适用农机装备研发应用和农业科技成果大面积推广。
+2. **巩固拓展脱贫攻坚成果**：提高监测帮扶效率，确保不发生规模性返贫致贫。
+   - 加强异地搬迁后续扶持，分类推进帮扶产业提质增效，加大就业帮扶力度。
+   - 统筹建立农村防止返贫致贫机制和低收入人口、欠发达地区分类分层帮扶制度，完善过渡期后帮扶政策体系。
+3. **扎实推进农村改革发展**：有序推进第二轮土地承包到期后再延长30年试点，扩大整省试点范围。
+   - 因地制宜推动兴业、强县、富民一体发展，拓宽农民增收渠道。
+   - 持续改善农村基础设施、公共服务和人居环境，建设宜居宜业和美乡村。
+### 新型城镇化和区域协调发展
+1. **深入实施新型城镇化战略行动**：科学有序推进农业转移人口市民化，全面推进常住地提供基本公共服务。
+   - 强化随迁子女义务教育保障，推动将符合条件的农业转移人口纳入住房保障体系，畅通参加社会保险渠道。
+   - 持续推进城市更新和城镇老旧小区改造，打造宜居、韧性、智慧城市。
+2. **加大区域战略实施力度**：发挥区域协调发展战略、区域重大战略、主体功能区战略的叠加效应，积极培育新的增长极。
+   - 支持经济大省挑大梁，鼓励其他地区因地制宜、各展所长，深化东、中、西、东北地区产业协作。
+### 绿色低碳发展
+1. **加强污染防治和生态建设**：持续深入推进蓝天、碧水、净土保卫战。
+   - 全面推进以国家公园为主体的自然保护地体系建设，实施生物多样性保护重大工程。
+   - 积极推进美丽中国先行区建设。
+2. **加快发展绿色低碳经济**：深入实施绿色低碳先进技术示范工程，培育绿色建筑等新增长点。
+   - 有力有效管控高耗能项目，加强废弃物循环利用，健全绿色消费激励机制。
+3. **积极稳妥推进碳达峰碳中和**：建立一批零碳园区、零碳工厂。
+   - 开展碳排放统计核算，建立产品碳足迹管理体系、碳标识认证制度。
+   - 加快建设“沙戈荒”新能源基地，开展煤电低碳化改造试点示范，积极参与和引领全球环境和气候治理。
 ### 保障和改善民生
-- **稳定和扩大就业**：实施重点领域、重点行业、城乡基层和中小微企业就业支持计划，支持劳动密集型产业吸纳和稳定就业，拓宽高校毕业生等青年就业创业渠道，加强灵活就业和新就业形态劳动者权益保障，开展大规模职业技能提升培训。
-- **基本医疗卫生服务**：深化以公益性为导向的公立医院改革，实施`医疗卫生强基工程`，优化药品集采政策，健全药品价格形成机制，支持创新药发展，严格医保基金监管。
-- **社会保障**：城乡居民基础养老金最低标准再提高**20元**，适当提高退休人员基本养老金，推进社区支持的居家养老，强化失能老年人照护，加大对老年助餐服务、康复辅助器具购置和租赁支持力度。
-- **生育支持**：制定促进生育政策，发放育儿补贴，大力发展托幼一体服务。
-- **社会救助**：完善分层分类社会救助体系，保障困难群众基本生活。
-### 维护国家安全和社会稳定
-- **公共安全治理**：深入实施`安全生产治本攻坚三年行动`，抓好校园学生餐、平台外卖安全监管，做好自然灾害防范应对，推进基层综治中心规范化建设，提升公共法律服务均衡性和可及性，建设更高水平的平安中国。
-- **十五五规划编制**：今年将开展`十五五规划`编制工作，科学确定发展目标，谋划好重大战略任务、重大政策举措、重大工程项目。
-# 重点工作
-## 扩大国内需求
-- **提振消费专项行动**：制定提升消费能力、增加优质供给、改善消费环境专项措施，释放多样化、差异化消费潜力，多渠道促进居民增收。
-- **消费品以旧换新**：安排超长期特别国债3000亿元支持消费品以旧换新。
-- **扩大服务与新型消费**：扩大健康、养老、托幼、家政等多元化服务供给，加快数字、绿色、智能等新型消费发展，释放文化、旅游、体育等消费潜力，强化消费者权益保护。
-- **扩大有效投资**：发挥各类政府投资工具作用，加快实施一批重点项目，切实选准选好项目、管好用好资金，坚决防止低效无效投资。
-- **投资规模安排**：今年中央预算内投资已安排7350亿元；用好超长期特别国债更大力度支持"两重"建设；优化地方政府专项债券管理机制，支持和鼓励民间投资发展。
-## 发展新质生产力与建设现代化产业体系
-- **培育新兴产业和未来产业**：深入推进战略性新兴产业融合集群发展，开展新技术、新产品、新场景大规模应用示范行动，培育生物制造、量子科技、具身智能、6G等未来产业。
-- **产业统筹布局**：加强产业统筹布局和产能监测预警，梯度培育创新型企业。
-- **推动传统产业改造升级**：深入实施制造业重大技术改造升级和大规模设备更新工程，加快制造业数字化转型，开展标准提升引领传统产业优化升级行动，打造名品精品经典产业。
-- **激发数字经济创新活力**：持续推进"人工智能+"行动，大力发展智能网联新能源汽车、人工智能手机和电脑、智能机器人等新一代智能终端，扩大5G规模化应用，优化全国算力资源布局，深化数据资源开发利用，促进平台经济规范健康发展。
-## 实施科教兴国战略
-- **建设高质量教育体系**：制定实施教育强国建设三年行动计划，加强义务教育学校标准化建设，扩大高中阶段教育学位供给，逐步推行免费学前教育，扎实推进优质本科扩容，加快"双一流"建设。
-- **推进高水平科技自立自强**：加快组织实施和超前布局重大科技项目，优化国家战略科技力量布局，推进科研院所改革，加强企业主导的产学研深度融合，从制度上保障企业参与国家科技创新决策、承担重大科技项目。
-- **健全科技成果转化机制**：健全科技成果转化支持政策和市场服务，加强科学普及工作，弘扬科学家精神，推动形成鼓励探索、宽容失败的创新环境。
-- **提高人才队伍质量**：加快建设国家战略人才力量，大力支持和大胆使用青年科技人才，建设一流产业技术工人队伍，深化人才分类评价改革。
-## 推动标志性改革举措落地
-- **激发经营主体活力**：高质量完成国有企业改革深化提升行动，扎实落实促进民营经济发展的政策措施，加力推进清理拖欠企业账款工作，开展规范涉企执法专项行动。
-- **建设全国统一大市场**：破除地方保护和市场分割，综合整治"内卷式"竞争，修订出台新版市场准入负面清单，优化新业态新领域市场准入环境，构建统一的信用修复制度，完善企业简易注销程序。
-- **深化财税金融体制改革**：开展中央部门零基预算改革试点，支持地方深化零基预算改革，加快推进部分品目消费税征收环节后移并下划地方，深化资本市场投融资综合改革，大力推动中长期资金入市，加强战略性力量储备和稳市机制建设。
-## 扩大高水平对外开放
-- **稳定对外贸易发展**：优化融资结算、外汇等金融服务，扩大出口信用保险承保规模和覆盖面，促进跨境电商发展，加强海外仓建设，拓展境外经贸合作区功能，支持内外贸一体化发展，推动服务贸易创新发展，培育绿色贸易、数字贸易等新增长点。
-- **大力鼓励外商投资**：推进服务业扩大开放综合试点示范，扩大电信、医疗、教育等领域开放试点，加强外资企业服务保障，推动自贸试验区提质增效和扩大改革任务授权，持续营造市场化、法治化、国际化一流营商环境。
-- **推动共建"一带一路"走深走实**：统筹推进重大标志性工程和"小而美"民生项目建设，强化法律、金融、物流等海外综合服务，优化产业链供应链国际合作布局。
-- **深化多双边和区域经济合作**：持续扩大面向全球的高标准自由贸易区网络，坚定维护以世界贸易组织为核心的多边贸易体制，扩大同各国利益的汇合点。
-## 防范化解重点领域风险
-- **推动房地产市场止跌回稳**：合理控制新增房地产用地供应，盘活存量用地和商办用房，推进收购存量商品房，有效防范房企债务违约风险，有序搭建相关基础性制度，加快构建房地产发展新模式，推动建设安全、舒适、绿色、智慧的"好房子"。
-- **稳妥化解地方政府债务风险**：完善和落实一揽子化债方案，优化考核和管控措施，动态调整债务高风险地区名单，做好地方政府隐性债务置换工作，完善政府债务管理机制，坚决遏制违规举债行为。
-- **积极防范金融领域风险**：一体推进地方中小金融机构风险处置和转型发展，综合采取补充资本金、兼并重组、市场退出等方式分类化解风险，健全金融监管体系，强化央地监管协同，完善应对外部风险冲击预案。
-## 抓好"三农"工作与推进乡村全面振兴
-- **增强粮食稳产保供能力**：稳定粮食播种面积，主攻单产和品质提升，严守耕地红线，高质量推进高标准农田建设，深入实施种业振兴行动，加快先进适用农机装备研发应用和农业科技成果大面积推广。
-- **巩固拓展脱贫攻坚成果**：提高监测帮扶效率，确保不发生规模性返贫致贫，加强易地搬迁后续扶持，分类推进帮扶产业提质增效，加大就业帮扶力度，统筹建立农村防止返贫致贫机制和低收入人口、欠发达地区分层分类帮扶制度，完善过渡期后帮扶政策体系。
-- **扎实推进农村改革发展**：有序推进第二轮土地承包到期后再延长30年试点，扩大整省试点范围，因地制宜推动兴业、强县、富民一体发展，拓宽农民增收渠道，持续改善农村基础设施、公共服务和人居环境，建设宜居宜业和美乡村。
-## 推进新型城镇化和区域协调发展
-- **实施新型城镇化战略行动**：科学有序推进农业转移人口市民化，全面推进常住地提供基本公共服务，强化随迁子女义务教育保障，推动将符合条件的农业转移人口纳入住房保障体系，畅通参加社会保险渠道。
-- **推进城市更新**：持续推进城市更新和城镇老旧小区改造，打造宜居、韧性、智慧城市。
-- **加大区域战略实施力度**：发挥区域协调发展战略、区域重大战略、主体功能区战略的叠加效应，积极培育新的增长极，支持经济大省挑大梁，鼓励其他地区因地制宜、各展所长，深化东、中、西、东北地区产业协作。
-## 加快经济社会发展全面绿色转型
-- **加强污染防治和生态建设**：持续深入推进蓝天、碧水、净土保卫战，全面推进以国家公园为主体的自然保护地体系建设，实施生物多样性保护重大工程，积极推进美丽中国先行区建设。
-- **加快发展绿色低碳经济**：深入实施绿色低碳先进技术示范工程，培育绿色建筑等新增长点，有力有效管控高耗能项目，加强废弃物循环利用，健全绿色消费激励机制。
-- **积极稳妥推进碳达峰碳中和**：建立一批零碳园区、零碳工厂，开展碳排放统计核算，建立产品碳足迹管理体系和碳标识认证制度，加快建设"沙戈荒"新能源基地，开展煤电低碳化改造试点示范，积极参与和引领全球环境和气候治理。
-## 加大保障和改善民生力度
-- **稳定和扩大就业**：实施重点领域、重点行业、城乡基层和中小微企业就业支持计划，支持劳动密集型产业吸纳和稳定就业，统筹好新技术应用和岗位转换，拓宽高校毕业生等青年就业创业渠道，加强灵活就业和新就业形态劳动者权益保障，开展大规模职业技能提升培训行动。
-- **强化基本医疗卫生服务**：深化以公益性为导向的公立医院改革，完善薪酬制度，实施医疗卫生强基工程，优化药品集采政策，强化质量评估和监管，健全药品价格形成机制，支持创新药发展，完善中医药传承创新发展机制，加强疾病预防控制体系建设，严格医保基金监管。
-- **完善社会保障和服务政策**：城乡居民基础养老金最低标准再提高20元，适当提高退休人员基本养老金，推进社区支持的居家养老，强化失能老年人照护，加大对老年助餐服务、康复辅助器具购置和租赁支持力度。
-- **制定促进生育政策**：发放育儿补贴，大力发展托幼一体服务。
-- **完善社会救助体系**：完善分层分类社会救助体系，保障困难群众基本生活。
-## 维护国家安全和社会稳定
-- **加强公共安全治理**：深入实施安全生产治本攻坚三年行动，抓好校园学生餐、平台外卖安全监管，做好自然灾害防范应对，推进基层综治中心规范化建设，提升公共法律服务均衡性和可及性，建设更高水平的平安中国。
-&gt; 让广大干部把更多时间和精力用到干实事上，创造更多经得起历史和人民检验的发展业绩。</t>
+1. **更大力度稳定和扩大就业**：实施重点领域、重点行业、城乡基层和中小微企业就业支持计划。
+   - 支持劳动密集型产业吸纳和稳定就业，统筹好新技术应用和岗位转换。
+   - 优化就业创业服务，拓宽高校毕业生等青年就业创业渠道；加强灵活就业和新就业形态劳动者权益保障。
+   - 开展大规模职业技能提升培训行动，让多劳者多得、技高者多得、创新者多得。
+2. **强化基本医疗卫生服务**：深化以公益性为导向的公立医院改革，完善薪酬制度，实施医疗卫生强基工程。
+   - 优化药品集采政策，强化质量评估和监管；健全药品价格形成机制，支持创新药发展。
+   - 完善中医药传承创新发展机制，加强疾病预防控制体系建设。
+   - 严格医保基金监管，让每一分钱都用于增进人民健康福祉。
+3. **完善社会保障和服务政策**：城乡居民基础养老金最低标准再提高20元，适当提高退休人员基本养老金。
+   - 推进社区支持的居家养老，强化失能老年人照护，加大对老年助餐服务、康复辅助器具购置和租赁支持力度。
+   - 制定促进生育政策，发放育儿补贴，大力发展托幼一体服务。
+   - 完善分层分类社会救助体系，保障困难群众基本生活。
+4. **加强精神文明建设**：完善培育和践行社会主义核心价值观制度机制，发展哲学社会科学、新闻出版、广播影视、文学艺术和档案事业。
+   - 推动优质文化资源直达基层，健全文化产业体系和市场体系。
+   - 推进群众身边的运动场地设施建设，广泛开展全民健身活动；加强青少年科学健身和健康干预。
+### 国家安全和社会稳定
+1. **维护国家安全和社会稳定**：全面贯彻总体国家安全观，加强公共安全治理。
+   - 深入实施安全生产治本攻坚三年行动，抓好校园学生餐、平台外卖安全监管。
+   - 做好自然灾害防范应对，推进基层综治中心规范化建设，提升公共法律服务均衡性和可及性，建设更高水平的平安中国。
+### 政府自身建设
+1. **加强法治政府建设**：严格依照宪法法律履职尽责，自觉接受同级人大及其常委会监督、人民政协民主监督、社会和舆论监督，加强审计监督。
+2. **提升行政效能和水平**：把党中央决策部署和自身实际结合起来，提高创造性贯彻落实能力。
+   - 切实把面向基层的督查检查考核减下来，让广大干部把更多时间和精力用到干实事上。
+3. **推进政府党风廉政建设和反腐败斗争**：深入贯彻中央八项规定精神，坚定不移推进政府系统党风廉政建设和反腐败斗争，全面提升政府履职能力，确保党中央决策部署不折不扣落实到位。</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>53.2</v>
+        <v>53.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10273/7810</t>
+          <t>10273/6670</t>
         </is>
       </c>
     </row>
@@ -12379,73 +12427,66 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t># 全文摘要
-本次会议为景城苑小区物业招标答疑及评标会，由业委会组织，两家物业公司（富家物业、资平物业）分别应答业主提问，最终评标确定中标候选人。会议围绕改造计划与时间、停车管理、承接查验与交接、安管与监控、业主满意度与收费率、包干制经验与公益服务、楼层杂物与晾晒问题等板块展开。两家公司均承诺一年内完成主要改造；富家物业提出增设门禁系统、建设外围停车场、增设电动车停车场等停车管理措施，资平物业提出收集业主车辆信息、制定停车管理方案、升级道闸系统；针对承接查验，富家物业提出提前两周入场摸底、提前一周培训人员，资平物业提出分专业组验收并增派150%人员；资平物业对楼层杂物问题提出以疏导为主的解决方案。评标结果：长沙富佳物业72.91分、湖南恒居基居业物业60.73分、重庆新东源物业54.48分，第一名中标候选人为深圳市资平物业发展有限公司。
-# 分段速览
-## 00:00:10-00:09:36 富家物业答疑
-业主代表就改造计划、停车管理、承接查验、安管监控、满意度提升等五个方面提问，富家物业发言人逐一回应。改造方面，预计一年内完成标书所列12大改造项目；停车管理方面，提出先分析乱停原因再针对性施策，包括增加停车位、增设隔离墩、建设外围停车场并安装停车管理系统、增设电动车停车场；承接查验方面，提出提前两周项目负责人入场摸底、提前一周安排服务人员培训，交接不畅时先与现物业私下沟通，再请业委会或街道社区协调，必要时在许可下采取强制措施；安管监控方面，提出增设人行门禁系统、升级大堂报到系统、统一管理业主车辆信息；满意度方面，提出用心倾听、如实记录、马上处理、及时反馈的四句话方法。
-## 00:10:00-00:19:44 资平物业公司介绍与改造方案
-资平物业代表介绍公司情况：成立于2004年，总部在深圳，全国367个项目、127个业委会项目，公司创始人陈志平为万科物业创始人之一。针对景城苑项目，提出团队编制16人、薪酬福利高于周边同类项目、一线人员不外包；进场后分四步推进：第一个月集中整改环境绿化，半年内排查整改设备设施，八个月内完成重大改造，一年内保证小区有序运行。同时介绍将导入顾客管理系统集中处理业主投诉报事，形成大数据指导后续工作，并开展社区文化活动（每两个月一次）及适老化服务。
-## 00:19:52-00:25:55 资平物业答疑（改造、包干制与公益服务）
-业主代表就改造措施、包干制经验及公益服务提问。资平物业回应：改造方面，进场一个月集中整改环境绿化，半年内处理设备设施，八个月内完成主要改造，一年内保证小区有序；包干制方面，公司在湖南有11个项目，其中10个为包干制，强调财务透明、保证业主知情权，团队直招、管理干部30%从现有团队选拔、60%左右从现有物业优秀员工中招聘或重新招聘；公益服务方面，在长沙开展居家上门服务（员工免费、材料费由业主自买或物业购买）、家政、24小时业主护送等有偿与无偿业务。
-## 00:26:01-00:31:23 资平物业答疑（承接查验与安管监控）
-业主代表就承接查验、安管监控与停车管理提问。资平物业回应：承接查验方面，强调前期准备充足，与社区街道派出所沟通、与现物业和业委会明确设备设施及债务债权，按专业线分组验收并调动集团工程师协助，承接查验期间增派150%人员；安管监控方面，关键岗位（门岗、门勤岗、车务）由老员工担任，对来访人员和车辆进行管控登记核实；停车管理方面，提出收集业主车辆信息、制定停车管理方案（含禁停区域、动线规划），升级道闸系统识别外来车辆，通过技术手段加强关键部位监控。
-## 00:31:23-00:34:44 资平物业答疑（楼层杂物与晾晒）
-业主代表就楼层顶层堆放杂物和乱搭乱晒问题提问，要求在不激发矛盾的前提下解决。资平物业回应：以疏导为主而非强制，通过宣传引导（法律知识宣传、上门沟通、海报）提高业主意识，联合社区应急管理部门采取行动，给予业主处理杂物的时间期限；可设置临时堆放区供业主短期存放并限期解决；针对晾晒需求，在小区设置集中晾晒区，并可提供免费上门晾晒增值服务（业主提前预约，物业工作人员早上拉出、晚上收回）。
-## 00:35:00-00:35:33 评标与结果公布
-主持人宣布评标规则：打分环节全程保密，暂停网络直播，录像材料不予公开，总评委打分去掉一个最高分和最低分。公布各公司得分：长沙富佳物业管理有限公司72.91分，湖南恒居基居业物业管理有限公司60.73分，重庆新东源物业管理有限公司54.48分。第一名中标候选人为深圳市资平物业发展有限公司，招标活动圆满结束。
-# 要点梳理
-## 富家物业答疑
-- **改造计划**：富家物业预计改造项目在一年内完成，具体12大改造点详见标书第117页。
-- **停车管理**：先分析乱停原因（场地不足、距离远或业主不自觉），据此制定对策；停车位不够则增加停车位，业主不自觉则派保安、客服人员现场说服、劝阻、纠正。
-- **承接查验准备**：提前两周安排项目负责人入场摸底小区现场情况；提前一周将服务人员安排到位并培训，使其了解公司制度与操作流程。
-- **交接不畅应对**：先与现物业私下沟通了解诉求，公司间能解决则自行解决；不能解决则请业委会或街道社区组织现场协调会；仍无法解决时，在业委会、业主大会及街道社区许可下采取强制措施。
-- **安管监控改善**：大门口增设人行门禁系统，支持手机微信、卡、密码进出；升级大堂报到系统，将业主车辆信息统一录入管理，临时车辆由安保人员登记后放行。
-- **停车秩序改善**：地面增设隔离墩，禁止公共场所停车，保障消防通道与人行通道畅通；建设外围停车场并安装停车管理系统；小区内增设电动车停车场，解决电动车乱停乱放问题。
-- **业主满意度措施**：处理业主问题采取四句话方法——用心去倾听、如实记录、马上处理和及时反馈，处理完成后及时向业主反馈完成时间。
-## 资平物业公司介绍
-- **公司概况**：资平物业成立于2004年，总部在深圳，为全市场化物业公司，无开发背景；全国在管367个项目，其中127个为业委会项目。
-- **管理理念**：公司创始人陈志平先生原为万科物业创始人，曾协同建立中国第一个业委会；公司为中国物业管理协会副会长单位、全国百强企业。
-- **透明管理**：包干制项目每季度将物业管理费、停车费等财务情况向全体业主公示；电梯、消防等外包事务推进业主代表参与公共事务管理。
-- **团队配置**：景城苑项目人员编制16人，薪酬福利保证高于同类及周边项目；所有一线人员直招不外包。
-## 资平物业改造计划
-- **进场首月（洗理静音）**：调动湖南战队其他项目人员资源，对小区环境、绿化、杂物进行全面清扫，保证一个月内感官上干净整洁有序。
-- **半年内（疏金活选）**：调动集团设备公司水电、给排水、电梯、消防工程师，对小区设备设施全面排查诊断，在投资范围内集中改造。
-- **八个月内（疑难杂症）**：对消防、渗水等重大问题进行全面检查，形成意见后提交业委会或召开业主大会授权招投标，保证项目有效运作。
-- **品质提升**：将总部管理标准、前沿管理经验及与业主、业委会沟通经验延续至本项目。
-- **顾客管理系统**：全面导入顾客管理系统，将业主投诉、咨询、报事集中至系统，保证有人跟进、有人回访；根据每月投诉报事数据形成大数据库，指导下月工作方向。
-- **社区活动**：根据小区老龄化情况开展适老活动（如教老年人使用抖音），按不同团体开展社区文化活动，公司硬性标准为每两个月开展一次。
-## 资平物业答疑
-- **改造时间**：进场第一个月集中整改环境绿化；半年内处理设备设施；八个月内完成主要改造；一年内保证小区达到有序状态。
-- **改造措施**：进场后对环境绿化全面补种，清理园区、楼道杂物及牛皮癣；利用集团工程师资源全面排查设备设施，投资款内快速整改，需动用维修资金则启动业主大会授权；针对业主和业委会关注的问题进行优先整改。
-- **包干制经验**：公司在湖南有11个项目，其中10个为包干制、1个为酬金制；包干制下保证业主知情权、财务透明，增加与业委会和业主的互动，让业主参与物业管理。
-- **团队构成**：所有一线人员和管理干部直招，30%从集团现有人员选拔，60%左右吸纳现物业优秀员工或重新招聘。
-- **公益服务**：长沙项目开展居家上门服务，员工免费，材料费由业主自买或物业购买；开展家政服务及24小时业主护送服务，有偿与无偿业务结合。
-- **承接查验**：前期与社区街道、派出所沟通，与现物业和业委会明确设备设施、债务债权；按专业线分专业组验收，委派集团工程师协助查出问题；现有16人团队基础上增派150%人员参与承接查验。
-- **安管监控**：门岗、门勤岗、车务等关键岗位由老员工担任，对来访人员和车辆进行管控、登记、核实后放行；收集业主车辆信息，制定停车管理方案，升级道闸系统识别外来人员与业主亲戚来访；通过设备公司从技术层面解决监控问题。
-- **楼层杂物处理**：通过上门宣传、海报重复宣传法律知识，让业主认识堆放杂物的风险与法律责任；联合社区应急管理部门采取行动；上门沟通告知危害，给业主时间段处理杂物；设置临时堆放区供业主短期存放，限期解决，强调疏导而非强制。
-- **晾晒问题**：在小区寻找位置设置集中晾晒区供业主晾晒被子等；有项目可提供免费增值服务，太阳大时物业工作人员上门取送晾晒物品（早上拉出、晚上拉回）。
-## 评标结果
-- **评标规则**：打分环节全程保密，暂停会场网络直播，录像材料不予公开；总评委打分去掉一个最高分和一个最低分。
-- **得分情况**：长沙富佳物业管理有限公司72.91分；湖南恒居基居业物业管理有限公司60.73分；重庆新东源物业管理有限公司54.48分。
-- **中标候选人**：第一名中标候选人为深圳市资平物业发展有限公司。
-## 结论与决定
-- **中标候选人**：评标确定深圳市资平物业发展有限公司为第一名中标候选人。
-- **评标保密**：打分环节全程保密，暂停网络直播，录像材料不予公开。
-- **计分规则**：总评委打分去掉一个最高分和一个最低分。
-## 待确认与风险
-- **停车乱象**：小区存在车辆停放不规范、电动车乱停现象，卫生室周边同样存在此类问题。
-- **安管隐患**：小区监控门禁失效，导致人员车辆随意进出。
-- **停车管理混乱**：小区内停车管理比较混乱，消防通道停放车辆，含业主车辆及外来车辆。
-- **杂物堆放**：楼层顶层存在堆放杂物或乱搭乱晒问题。</t>
+          <t># 景城苑小区物业招标答疑及评标会
+## 全文摘要
+本次会议为景城苑小区物业招标答疑及评标会，由业委会组织，两家物业公司（富家物业、资平物业）分别应答业主提问，最终评标确定中标候选人。会议围绕改造计划与时间、停车管理、承接查验与交接、安防监控、业主满意度与收费率、包干制经验与公益服务、楼层杂物与晾晒问题等板块展开。富家物业承诺一年内完成改造，提出分析乱停原因、增加停车位、保安劝阻，提前两周入场摸底、提前一周培训人员，增设人行门禁、升级报到系统、增设隔离墩及电动车停车场，并以“用心倾听、如实记录、马上处理、及时反馈”提升满意度。资平物业计划进场一个月内集中整改环境绿化，半年内处理设备设施，八个月内完成主要改造，一年内达到有序状态；提出收集车辆信息、制定停车管理方案、升级道闸系统，关键岗位用老员工，承接查验时与社区街道派出所沟通、分专业组查验并增派150%人员；通过财务透明、每季度公示、管理透明、社区文化活动提升满意度，并提供居家上门等公益服务；对楼层杂物以宣传引导、联合社区、上门沟通、设置临时堆放区等疏导方式解决，设置集中晾晒区并提供免费上门晾晒服务。评标结果：第一名中标候选人为深圳市资平物业发展有限公司，第二名长沙富佳物业管理有限公司72.91分，第三名湖南恒居恒基居业物业管理有限公司60.73分，第四名重庆新东源新东源物业管理有限公司54.48分。打分环节全程保密，暂停网络直播，录像材料不予公开，总评委打分去掉一个最高分和最低分。
+## 分段速览
+### 00:00:10-00:09:36 富家物业答疑
+业主代表就改造计划、停车管理、承接查验、安防监控、满意度提升等五个方面提问，富家物业发言人逐一回应。改造方面承诺一年内完成标书所列12大改造项目；停车问题提出先分析乱停原因，再分别以增加停车位或保安客服现场劝阻纠正应对；承接查验强调提前两周项目负责人入场摸底、提前一周完成服务人员培训，交接不畅时依次采取私下沟通、请业委会或街道协调、经许可后强制措施；安防方面提出增设人行门禁、升级大堂报到系统、增设隔离墩、建设外围停车场及增设电动车停车场；满意度提升以"用心倾听、如实记录、马上处理、及时反馈"为原则。
+### 00:10:00-00:11:56 评标流程说明
+主持人宣布评标规则：抢标时间10分钟，每道题答题时间3分钟，并确认深圳市资平物业发展有限公司的题目编号为1213。现场进入下一家公司的答辩环节。
+### 00:12:22-00:19:44 资平物业公司介绍与改造计划
+资平物业代表介绍公司情况：成立于2004年，总部在深圳，全国367个项目、其中127个业委会项目，为中国物业管理协会副会长单位及全国百强企业。针对景城苑项目提出"四步走"计划：进场第一个月调动湖南战队资源集中整改环境绿化；半年内由集团设备公司工程师全面排查设备设施并在投资范围内集中改造；八个月内解决需业委会授权或业主大会决策的重大问题；随后导入公司管理标准。同时提出财务透明（包干制每季度公示）、管理透明（业主参与公共事务）、团队16人编制且一线人员不外包、导入顾客管理系统及开展社区文化活动等举措。
+### 00:19:52-00:22:45 资平物业回应改造时间与措施
+业主询问中标后改造着手方面及预计时间。资平物业回应：进场一个月集中整改环境绿化、清理楼道杂物；利用集团资源全面排查设备设施，投资款内快速整改，需动用维修资金的启动业主大会授权；针对业主和业委会关注问题优先整改。时间安排为一个月完成环境绿化、半年内处理设备设施、八个月集中整改，保证一年内小区达到有序状态。
+### 00:22:50-00:25:55 资平物业回应包干制经验与公益服务
+业主询问包干制经验及公益福利服务。资平物业介绍在湖南有11个项目，其中10个为包干制、1个为酬金制，强调包干制下同样保证财务透明和业主知情权，团队直招、管理干部30%从现有团队选拔、60%左右吸收原物业优秀员工或重新招聘。公益服务方面，长沙项目提供居家上门服务（员工免费、材料费由业主自付或公司购买）、家政服务及24小时业主护送服务等有偿与无偿业务。
+### 00:26:01-00:28:42 资平物业回应承接查验安排
+资平物业回应承接查验问题：前期与社区、街道、派出所沟通，与业委会及原物业明确设备设施和债务债权；按专业线分专业组查验，调动集团工程师协助查出问题，避免与物业形成对立局面；在现有16人团队基础上增派150%人员，依托成熟的承接查验小组和数字化手段，确保问题准确查出、不留隐患。
+### 00:28:42-00:31:23 资平物业回应安防与停车管理
+资平物业回应监控门禁失效及停车混乱问题：关键岗位（门岗、门勤岗、车务）由老员工担任，对外来人员车辆进行管控、登记、核实后放行；收集业主车辆信息，制定小区整体停车管理方案（含禁停区域），升级道闸系统识别外来人员与业主亲友；通过自身设备公司和平台在技术层面解决关键部位监控问题。
+### 00:31:23-00:34:44 资平物业回应楼层杂物与晾晒问题
+资平物业回应楼层顶层堆放杂物及乱搭乱晒问题：以宣传引导为主，通过上门宣传、海报等方式让业主认识法律风险；联合社区及应急管理部门采取行动；上门沟通并给予业主处理杂物的时间期限；利用闲置区域设置临时堆放点供业主限期存放。晾晒方面，计划在小区寻找位置设置集中晾晒区，并可在天气好时提供免费上门取送晾晒的增值服务，强调以疏导而非强制方式解决。
+### 00:35:00-00:35:33 评标结果公布
+评标委员会完成打分，主持人公布结果：第一名中标候选人为深圳市资平物业发展有限公司，第二名长沙富佳物业管理有限公司72.91分，第三名湖南恒居恒基居业物业管理有限公司60.73分，第四名重庆新东源物业管理有限公司54.48分。打分环节全程保密，暂停网络直播，录像材料不予公开，总评委打分去掉一个最高分和最低分。
+## 要点梳理
+### 富家物业答疑
+1. **改造计划与时间**：富家物业预计改造时间在一年内完成，具体改造项目已在标书第117页详细说明。
+2. **停车管理**：针对车辆停放不规范、电动车乱停问题，富家物业提出先分析原因（停车位不足或业主不自觉），若停车位不够则增加停车位，若业主不自觉则派保安、客服人员现场说服、劝阻、纠正。
+3. **承接查验与交接**：富家物业提出提前两周项目负责人入场摸底，提前一周安排服务人员到位并培训；交接不畅时先与原物业私下沟通，公司间无法解决则请业委会或街道社区组织协调会，仍无法解决时在业委会、业主大会及街道社区许可下采取强制措施。
+4. **安防与监控**：富家物业提出五项措施：大门口增设人行门禁系统（支持手机微信、卡、密码进出）；升级大堂报到系统，录入业主车辆信息统一管理，临时车辆由安保人员登记放行；地面增设隔离墩，禁止公共场所停车，保证消防通道和人行通道畅通；建设外围停车场并安装停车管理系统；小区内增设电动车停车场。
+5. **业主满意度与收费率**：富家物业提出四句话原则：用心去倾听、如实记录、马上处理和及时反馈，对业主投诉及时处理并反馈完成情况。
+### 资平物业答疑
+1. **公司概况**：资平物业成立于2004年，总部在深圳，为全市场化物业公司，无开发背景；全国有367个项目，其中127个为业委会项目；公司创始人陈志平为万科物业创始人，曾协同建立中国第一个业委会；公司为中国物业管理协会副会长单位、全国百强企业。
+2. **管理理念**：资平物业提出"让一线权利归还业主"，确保财务透明（包干制每季度公示物业管理费、停车费等财务信息）和管理透明（业委会授权项目推进业主代表参与公共事务管理）。
+3. **团队配置**：资平物业经勘察确定小区人员配置16人，薪酬福利保证高于同类及周边项目；所有一线人员直招不外包。
+4. **改造计划与时间**：资平物业提出四步举措：进场第一个月调动湖南战队其他项目资源，对环境绿化、清洁、杂物进行全面清扫；调动集团设备公司水电、给排水、电梯、消防工程师对设备设施全面排查诊断，合理范围内集中改造；涉及重大事项（消防、渗水等）检查后提供意见，经业委会授权或业主大会招投标；八个月以内完成设备设施和现场改造，保证项目有效运作，一年内达到有序状态。
+5. **停车管理**：资平物业提出收集小区业主车辆信息，制定整体停车管理方案（含禁区停放），升级道闸系统识别外来人员和业主亲戚来访，通过技术手段加强关键岗位和关键部位监控。
+6. **包干制经验**：资平物业在湖南有11个项目，其中10个为包干制、1个为酬金制；包干制下保证业主知情权、增加与业委会和业主的互动、团队直招，管理干部30%来自现有团队、60%左右为现有物业优秀员工或重新招聘。
+7. **公益服务**：资平物业在长沙开展居家上门服务，员工免费，材料费由业主自买或公司购买；提供家政、24小时业主护送服务等有偿和无偿业务。
+8. **承接查验与交接**：资平物业提出前期与社区、街道、派出所沟通，与原物业和业委会明确设备设施、债务债权；按专业线分专业组查验，调动集团工程师协助查出问题；在现有16人团队基础上增派150%人员，保证承接查验和数字化工作准确完成。
+9. **楼层杂物与晾晒问题**：资平物业提出以疏导为主、避免强制：通过上门宣传、海报、法律知识宣传引起业主重视；与社区、应急管理部门联合行动；上门沟通并给予业主处理杂物的时间段；设置临时堆放区供业主短期存放；设置集中晾晒区，可提供免费上门晾晒服务（早上拉出、晚上拉回）。
+### 结论与决定
+1. 评标确定深圳市资平物业发展有限公司为中标候选人。
+2. 第二名长沙富佳物业管理有限公司72.91分，第三名湖南恒居恒基居业物业管理有限公司60.73分，第四名重庆新东源新东源物业管理有限公司54.48分。
+3. 打分环节全程保密，暂停会场网络直播，录像材料不予公开。
+4. 总评委打分去掉一个最高分和一个最低分。
+### 行动项与分工
+- [ ] **评标结果提交**（主持人 ｜ 会议当场 ｜ 已完成）：公布中标候选人为深圳市资平物业发展有限公司。
+- [ ] **打分环节保密执行**（评标委员会 ｜ 会议当场 ｜ 已完成）：暂停网络直播，录像材料不予公开，除评委、监督员及必要会务人员外其余人员退场。
+### 待确认与风险
+1. 小区存在车辆停放不规范、电动车乱停现象。
+2. 小区监控门禁失效，导致人员车辆随意进出。
+3. 小区停车管理混乱。
+4. 楼层顶层存在堆放杂物或乱搭乱晒问题。</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>62</v>
+        <v>53.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11743/4376</t>
+          <t>11743/4375</t>
         </is>
       </c>
     </row>
@@ -12567,70 +12608,72 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t># 讲座概况
-本期视频由主讲人李正讲述康熙朝文渊阁大学士陈廷敬的一生，以澄清影视剧虚构功绩、还原历史真实为切入点，分「妈妈张氏的开蒙」「圣祖康熙的讲师」「至公无私的落幕」三个阶段展开。核心主张在于：陈廷敬虽无平三藩、收台湾、剿噶尔丹等显赫事功，却凭清廉正直、恪守初心赢得康熙终身信任——康熙临终前仍询问大臣中是否有「学问人品如大学士」可代理内廷事务者。关键锚点包括：陈廷敬1638年生于山西泽州府阳城县，6岁前由母亲张氏口授背完《论语》《孟子》《大学》《中庸》《诗经》，21岁中进士入翰林，75岁病逝谥号文贞。讲座面向历史爱好者，旨在通过陈廷敬一生说明「苟正其身矣，于从政乎何有」的为官之道，对理解清代官场生态与康熙朝政治具有参考意义。
-# 核心观点与论证
-## 母亲张氏开蒙奠定根基
-- **家学渊源**：陈廷敬本名陈敬，字子端，号午亭，1638年出生于山西泽州府阳城县，家中书香门第，往上数六代都是读书人且多在朝廷为官；父亲陈长七虽为管理家业未走仕途，但也是读书人，后入选顺治朝国子监。
-- **母亲张氏自幼饱读诗书**：张氏从小跟随父亲张弘毅认真读书，学过儒家经典与《资治通鉴》，陈廷敬形容“太夫人少儿颖慧特异”；嫁入陈家后每天干完家务即读书背诵，甚至半夜不睡，史载“太夫人于家政稍暇即出书籍，平几装诵，非秉夜不归寝”。
-- **6岁前背完四书与诗经**：陈廷敬出生后，母亲张氏即开始给他讲解儒家经典，史载“凡四子书毛诗皆太夫人口授以诵”，陈廷敬6岁外出上学前已背完《论语》《孟子》《大学》《中庸》和《诗经》。
-- **9岁作诗获母亲鼓励**：陈廷敬9岁作《咏牡丹》，其中“要使误接春”一句被母亲张氏夸为“天才”，童年学习大半在母亲关照与注视下展开。
-- **科举成绩优异**：顺治八年（1651年）陈廷敬14岁赴试潞安府，以童子第一入州学（全省第一考中秀才）；20岁中举人，21岁中进士，同年入选翰林院任庶吉士——对比天才李光地21岁尚未考上秀才。
-## 入翰林改名风波
-- **同届重名引发困扰**：顺治十五年四月，陈廷敬与直隶通州学子陈敬同被选为庶吉士，史载“山西泽州人陈敬、直隶通州人陈敬，32人俱为庶吉士”。
-- **直隶陈敬连累名声**：因清朝政府文件满汉双语，庶吉士须学满文；直隶陈敬学不下去、考试不及格，顺治点名批评并罚俸一年，原话“陈敬……清书俱未习熟，若不惩罚，何以立其将来，着各罚俸一年”，但因未带籍贯，翰林院风言风语不分山西还是直隶。
-- **主动上书改名**：陈廷敬22岁主动上书顺治请求更名，史载“庶吉士陈敬奏请更名廷敬，以与直隶庶吉士陈敬同名故也”；据李光地记载，“廷”字为顺治所赐，原话“陈文贞公初名敬，其家廷字文选日张皇帝所赐也”。
-- **与顺治同年且有渊源**：顺治与陈廷敬均为明崇祯十一年（1638年）出生，同年同岁；顺治欣赏陈廷敬，史载“陈文贞公时若冠祥祥玉堂所一席之夜往往蒙上赞许”。
-- **庶吉士毕业考同届第一**：顺治十八年，24岁的陈廷敬在庶吉士毕业考试中考取同届第一，获授秘书院检讨。
-## 为母请假三年仍获重用
-- **两场意外接连发生**：顺治十八年年初顺治感染天花驾崩；康熙元年老家来信母亲张氏病倒，陈廷敬在仕途起步关键期想都没想即请假归乡，史载“泽州陈文贞公，性至孝，时登极，闻太夫人病，即归省”，请假整整三年。
-- **重返官场迅速获评**：康熙六年陈廷敬考察一等称职；两年后32岁升任正六品国子监司业，到国家最高学府任副校长——其父陈长七15年前还只是国子监学生，陈廷敬已任国子监副校长。
-- **整顿国子监送礼风气**：当时国子监不成文规定学生拜见校长老师须带见面礼，史载“顾氏国子生入监，夜见祭酒以下官吏有志都得送礼”；陈廷敬坚持不收，史载“凡诸生以至献者悉秉去之”，学生越送礼越不见，不送礼才愿意见。
-- **两年连升三级**：整顿国子监后未受排挤，34岁升任从四品翰林院侍讲学士；康熙十一年十月，35岁被19岁的康熙亲自叫到身边担任日讲起居注官。
-## 康熙讲师与破例祭母
-- **升任经筵讲师**：陈廷敬在日讲官位置与康熙朝夕相处4年，康熙先后拔擢其为詹事府詹事与从二品内阁学士；康熙十五年九月，39岁充经筵讲官。
-- **教学风格外放狠辣**：陈廷敬讲评经史特别狠辣，对就骂错就骂，从不含糊其辞；曾指着史书上的孙权破口大骂，原话“无鼠相存，譬犹唇齿，不必智者而知之……全其屯权也哉”，批评孙权背刺关羽是“猪是狗”。
-- **执掌翰林院教习庶吉士**：康熙十六年正月，康熙让陈廷敬出任翰林院长院学士，给当届庶吉士上课，史载“以内阁学士陈廷敬为翰林院长院学士教习处学士”。
-- **母亲去世康熙破例祭奠**：陈廷敬母亲张氏去世终年59岁，康熙下令“满汉大臣俱系一体，汉大臣有丧，亦应遣大臣往祭”，派大学士明珠、喇沙里等携茶酒往祭；礼部反对称陈母封号按詹事三品“例不得祭奠”，康熙回应“以平靖世将握秦而恩福待，吾何以劝劳臣乎”，下令追封陈母按学士品级由官方祭奠。
-## 左都御史整顿吏治
-- **捐纳者上岗须追加考试**：康熙二十三年47岁升任从一品左都御史后，针对康熙十二年至二十二年十年战争期间开放捐纳、买官者众多的情况，上奏“自古未有不晓文艺之人可以为民父母者也……于选出之时仍行考试，文艺略小者给予录用，否则且令异业听其再试”。
-- **吏部反对康熙支持**：吏部以“以前补用人员从未考试，应不准行”反对；康熙支持陈廷敬并补充要求各地督抚详查已任命官员，原话“临民之官，若不识字义，何以办理民事而尽职掌？此事着一意不分捐纳与不捐纳，凡临民之官内有不识字义者，着该督府不时实行查参修治”。
-- **严查弹劾并给方案**：针对各省督府作风问题、地方政府赈灾懒政问题全部严查弹劾，一边指出问题一边给出解决方案——捐纳者不识字就追加考试，赈灾懒政则亲自拟定新的赈灾报批流程。
-- **连续出任三部尚书**：随后两年连续出任工部、户部、吏部三部尚书，他人到哪里就整顿到哪里；有人劝其“官场里不和光同尘是会落满怨的”，陈廷敬回应“我贤与虽折且怨，庸和尚说只要人是对的，事是好的，我陈廷敬即便遭受一点挫折和埋怨，也是无所谓的”。
-## 张谦案自证清白
-- **亲家攀咬受贿**：康熙二十六年陈廷敬50岁时，湖广巡抚张谦因贪污被抓，张谦既是陈廷敬老乡又是亲家（其子是陈廷敬二女婿）；张谦口供称曾出钱贿赂陈廷敬、徐乾学、高士奇，证据是三人曾给他写信劝其好好当官，张谦称这些信是索贿暗示。
-- **陈廷敬否认并辞官**：陈廷敬称“前楚府一案者，千随臣弃敬畏自分嫌疑之际……积疑成恨，羽射连染”，表示因张谦是亲戚尤其注意、从未特殊往来，张谦是因自己疏远而产生怨恨恶意攀咬；康熙传旨主审官马齐“此时需旧款需问，不可蔓延，若蔓延则千累者重”，只处理张谦、其他人密查。
-- **主动辞官留京修书**：51岁陈廷敬主动上书辞官，原话“臣自念无他才能报塞万一……唯当隐退田间，永衔恩于高厚”；康熙准许辞官但留其在京继续修书。
-- **三条理由证清白**：①据李光地说，陈廷敬后来吐槽张谦案从索贿到举报都是徐乾学一手策划，原话“陈泽周演，再破张骞做巡抚，要银子也是徐东海，后来银子不用手叫人参他又是徐东海，始终皆徐为之”；②徐乾学贪污事迹多且热衷结党；③徐乾学、高士奇后来均因贪污被罢官，唯独陈廷敬仅辞官一年即被康熙重新启用再任左都御史——康熙若无100%把握不会让其出任全国最高监察长官。
-## 晚年位高权重仍守初心
-- **历任尚书与大学士**：陈廷敬历任一年刑部尚书、六年户部尚书、四年吏部尚书，所到之处秩序井然；康熙四十二年66岁升任文渊阁大学士，同时总理南书房事务，一肩挑两门，位高权重一人之下。
-- **四次申请退休**：康熙四十六年70岁起逐渐上书申请退休，康熙以“机务重务，良难其人，不必求去”拒绝；70岁、71岁、72岁连续三年三次申请均被拒——陈廷敬是内阁中唯一既管南书房又当经筵讲师定期给康熙上课的大学士。
-- **第四次获准并获赐匾联**：康熙四十九年73岁第四次申请退休终获准，康熙亲写匾额“午亭山村”和楹联“春归乔木浓阴茂，秋到黄花晚节香”，并说“朕特殊匾联赐卿，自此不与人写字矣”。
-- **病逝获厚葬**：两年后陈廷敬病逝终年75岁，谥号文贞，史称陈文贞公；康熙包办所有治丧费用，从大内找紫砂碗做棺材，命皇三子允祉及大臣侍卫往祭，下令各部院满汉大臣往吊。
-- **一生清白恪守初心**：陈廷敬21岁入官场、75岁离世，宦海浮沉50余年依然声名清白；主讲人引用《论语》“苟正其身矣，于从政乎何有”总结——陈廷敬儿时学过的道理直到死都没有违背。
-# 金句总结
+          <t># 康熙朝陈廷敬生平事迹讲述
+## 讲座概况
+本期视频由主讲人李正讲述康熙朝文渊阁大学士陈廷敬的一生，以“妈妈张氏的开蒙”“圣祖康熙的讲师”“至公无私的落幕”三个阶段为骨架展开。陈廷敬本名陈敬，字子端，号午亭，1638年生于山西泽州府阳城县，21岁中进士入翰林院，因与直隶陈敬重名主动奏请改名，由顺治赐名“廷敬”。讲座核心判断有三：其一，影视剧中陈廷敬支持撤藩、招抚台湾、征剿噶尔丹等功绩均非史实，但其临终前仍被康熙问及“大臣中学问人品如大学士可代理内廷事务者为谁”，足见倚重；其二，陈廷敬由母亲张氏开蒙，6岁前已背完四书及诗经，14岁以全省第一考中秀才，其清廉品格深受母亲影响；其三，陈廷敬宦海浮沉50年声名清白，康熙49年第四次申请退休获准，两年后病逝，终年75岁，谥号文贞。讲座面向对清代历史、名臣生平及传统廉政文化感兴趣的观众，以史书记载与主讲人个人倾向（如张谦案中陈廷敬无辜的三点理由）相结合的方式呈现，适合希望了解陈廷敬真实历史形象、理解康熙朝官场生态与清官品格的听众。
+## 核心观点与论证
+### 母亲张氏的开蒙
+- **家学渊源**：陈廷敬本名陈敬，字子端，号午亭，1638年（崇祯11年）生于山西泽州府阳城县，家中书香门第，往上数六代都是读书人且多在朝廷为官；父亲陈长七虽为管理家业未走仕途，但入选过顺治朝国子监。
+- **母亲张氏自幼读书**：张氏从小随父张弘毅认真读书，通晓儒家经典与《资治通鉴》，陈廷敬形容其“少儿颖慧特异”；嫁人后每日干完家务便读书背诵，常半夜不睡，比许多考科举的书生还认真。
+- **6岁前背完四书与诗经**：陈廷敬出生后，母亲张氏即开始给他讲解儒家经典，史载“凡四子书毛诗皆太夫人口授以诵”，6岁外出上学前已背完《论语》《孟子》《大学》《中庸》和《诗经》。
+- **9岁作诗获母称赞**：陈廷敬9岁作《咏牡丹》，其中“要使误接春”一句被母亲张氏夸为“天才”，可见其童年学习大半在母亲关照与注视下展开。
+- **科举成绩优异**：顺治八年（1651年），陈廷敬14岁赴试潞安府，以全省第一考中秀才；20岁中举人，21岁中进士，同年入选翰林院任庶吉士——天才如李光地21岁连秀才还没考上。
+### 入翰林与改名风波
+- **与直隶陈敬重名**：顺治15年，陈廷敬入翰林时本名仍叫陈敬，同届中进士入翰林的还有一位直隶通州学子也叫陈敬，两人同被选为庶吉士。
+- **重名引发风波**：因清朝政府文件多为满汉双语，庶吉士需学满文；直隶陈敬学不下去、考试不及格，被顺治点名批评并罚俸一年，但因顺治未带籍贯，翰林院风言风语只说“新来的庶吉士中有个叫陈敬的不习清书被皇上骂了”。
+- **主动奏请改名**：陈廷敬坐不住，主动上书顺治请求改名，史载“庶吉士陈敬奏请更名廷敬，以与直隶庶吉士陈敬同名故也”，这一年他22岁。
+- **顺治赐名“廷敬”**：据李光地记载，陈廷敬的“廷”字是顺治所赐；改名后既与直隶陈敬撇清关系，又凭御赐名字与顺治拉近关系——顺治与陈廷敬同为崇祯11年出生，同年同岁且欣赏他。
+- **庶吉士毕业考第一**：顺治18年，24岁的陈廷敬在庶吉士毕业考试中考同届第一，获授秘书院检讨。
+### 为母守孝与重返官场
+- **为母病请假归乡三年**：康熙元年，老家来信说母亲张氏病倒，陈廷敬在仕途刚要起步时想都没想就请假归乡，史载“闻太夫人病，即归省”；母亲挺过来后，他这次请假整整三年，在最该积累工作经验的年纪履历出现空白。
+- **重返翰林院考评一等**：康熙六年，陈廷敬考察一等称职；两年后32岁升任正六品国子监司业，到国家最高学府当副校长——15年前他父亲陈长七还只是国子监学生，如今儿子已是副校长。
+- **整顿国子监送礼风气**：当时国子监有不成立规定，学生拜见校长老师须带见面礼；陈廷敬说“妈妈一直教育要做清官”，坚持不收，学生越送礼越不见，只有不送礼才愿意见，史载“凡诸生以至献者悉秉去之”。
+- **升任日讲官与经筵讲师**：整顿国子监后两年内连升三级，34岁官居从四品翰林院侍讲学士；康熙11年（35岁）被19岁的康熙亲自叫到身边任日讲起居注官，康熙15年（39岁）充经筵讲官，正式拜为康熙的经筵讲师。
+- **教学风格外放狠辣**：陈廷敬讲评经史特别狠辣，对就骂错就骂，从不含糊其辞；曾指着史书上的孙权破口大骂，原话称孙权背刺关羽“无鼠相存，譬犹唇齿，不必智者而知之……全其屯权也哉”，骂孙权是猪是狗。
+### 母亲去世与康熙恩典
+- **母亲病逝**：康熙16年，陈廷敬母亲张氏因病去世，终年59岁；陈廷敬立刻请假回老家奔丧。
+- **康熙打破满汉惯例**：康熙召集大臣表态，称“满汉大臣俱系一体，汉大臣有丧，亦应遣大臣往次”，下令派大学士明珠、翰林院长院学士喇沙里等携茶酒往祭——此前只有满洲大臣家里出丧朝廷才派人吊孝。
+- **礼部反对与康熙坚持**：礼部反对，理由是陈母封号是陈廷敬任詹事府詹事时朝廷授予的，按规定没资格得到官方祭奠；康熙表态“以平靖世将握秦而恩福待，吾何以劝劳臣乎”，即刻追封陈母按学士品级由官方派人祭奠。
+### 左都御史与整顿吏治
+- **捐纳者追加考试**：康熙23年，47岁的陈廷敬升任从一品左都御史；当时因三藩之乱到统一台湾连打十年仗，政府开放捐纳，不少人花钱买官，陈廷敬上奏“自古未有不晓文艺之人可以为民父母者也”，捐纳买官者正式上岗时须追加考试，考不上就别上岗。
+- **吏部反对与康熙支持**：吏部反对称“以前补用人员从未考试，应不准行”；但康熙支持陈廷敬，还补充要求各地督抚将已任命官员详查一遍，凡文化水平不过关的全被不靠，原话“临民之官，若不识字义，何以办理民事而尽职掌”。
+- **严查弹劾与拟定方案**：针对各省督府作风问题、地方政府赈灾懒政问题，陈廷敬全都严查弹劾，且一边指出问题一边给出解决方案——捐纳者不识字就追加考试，地方政府赈灾他亲自拟定新的赈灾报批流程。
+- **连续出任三部尚书**：随后两年，陈廷敬连续出任工部、户部、吏部三部尚书，他人到哪里就整顿到哪里；有人劝他“官场里不和光同尘是会落满怨的”，他表示“我贤与虽折且怨，庸和尚说”，只要人是对的、事是好的，遭受挫折和埋怨也无所谓。
+### 张谦案与辞官复出
+- **亲家张谦贪污攀咬**：康熙26年，50岁的陈廷敬遭遇湖广巡抚张谦贪污案——张谦既是陈廷敬老乡，又是其亲家（儿子是陈廷敬二女婿）；张谦口供称曾出钱贿赂陈廷敬、徐乾学、高士奇三人，并拿出三人曾给他写信劝他好好当官作为“索贿暗示”的证据。
+- **陈廷敬自辩与康熙处置**：陈廷敬称“臣所甚，以其败事遂疑及臣，积疑成恨”，因张谦是亲戚所以尤其注意、从未特殊往来，张谦是因自己过于疏远而恶意攀咬；康熙传旨主审官马齐“此时需旧款需问，不可蔓延”，只处理张谦一人，其他人一律事后密查。
+- **主动辞官**：康熙27年，51岁的陈廷敬主动上书奏请辞官以证清白，原话“唯当隐退田间，永衔恩于高厚”；康熙准许辞官，但留他在京继续修书。
+- **复出宣告清白**：康熙29年，53岁的陈廷敬仅辞官一年就被重新启用，再任左都御史监察外官——张谦案所涉徐乾学、高士奇后来都因贪污被罢官，唯独陈廷敬复出任全国最高监察长官，康熙以此正式宣告其清白。
+- **李光地证言**：据李光地记载，陈廷敬后来吐槽整个张谦案从索贿到举报都是徐乾学一手策划，原话“再破张骞做巡抚，要银子也是徐东海，后来银子不用手叫人参他又是徐东海，始终皆徐为之”。
+### 晚年与逝世
+- **历任尚书与大学士**：复出后陈廷敬历任一年刑部尚书、六年户部尚书、四年吏部尚书，所到之处秩序井然；康熙42年，66岁时一肩挑两门，既升任文渊阁大学士，又总理南书房事务，位高权重一人之下。
+- **四次申请退休**：陈廷敬不贪恋高位，从康熙46年70岁起逐渐上书申请退休，康熙始终表示“机务重地，良难其人，不必求去”；70岁、71岁、72岁连续三年三次申请均被拒绝，康熙49年73岁第四次申请才获准。
+- **康熙赐匾联**：康熙专门给陈廷敬写匾额“午亭山村”和楹联“春归乔木浓阴茂，秋到黄花晚”，并感慨“朕特殊匾联赐卿，自此不与人写字矣”。
+- **病逝与厚葬**：两年后陈廷敬病逝，终年75岁，谥号文贞，史称陈文贞公；康熙包办所有治丧费用，从大内找紫砂碗做棺材，下令中央各部大臣无论满汉都到丧礼吊孝祭奠，并派皇三子允祉及大臣侍卫往祭。
+- **一生总结**：陈廷敬21岁入官场，75岁病逝，宦海浮沉50年依然声名清白、恪守初心；主讲人引《论语》“苟正其身矣，于从政乎何有”作结，称陈廷敬儿时学过的道理直到死都没有违背。
+## 金句总结
 &gt; “朕日望大学士病体速愈，在佐朕料理机务几年。若事出意外，大臣中学问人品如大学士可代理内廷事务者为谁？”
-- 背景：康熙在陈廷敬临终前询问，还有谁可代理内廷事务，足见对其倚重之深。
-&gt; “自古未有不晓文艺之人可以为民父母者也。”
-- 背景：陈廷敬任左都御史时上奏，主张捐纳买官者上岗前必须追加考试，不识字义者不得为官。
-&gt; “我贤与虽折且怨，庸何伤？”
-- 背景：有人劝陈廷敬官场应和光同尘，他回应只要人是对的、事是好的，遭受挫折与埋怨也无所谓。
-&gt; “臣自念无他才能报塞万一，唯早夜兢兢私自淬砺，不徇亲党，不阿友朋，上恐负圣主之殊恩，下欲全微臣之孝节。”
-- 背景：张谦案中陈廷敬被攀咬受贿，主动上书辞官以证清白。
+&gt; —— **康熙帝** ｜ 针对陈廷敬临终前仍被倚重、询问可代理内廷事务之人的定调发言
+&gt; “自古未有不晓文艺之人可以为民父母者也，有未经考职遂行捐纳者，于选出之时仍行考试，文艺略小者给予录用，否则且令异业听其再试。”
+&gt; —— **陈廷敬（左都御史）** ｜ 针对捐纳买官者须经考试方能上岗的定调发言
+&gt; “临民之官，若不识字义，何以办理民事而尽职掌？”
+&gt; —— **康熙帝** ｜ 针对支持陈廷敬捐纳考试建议、要求详查已任命官员的定调发言
+&gt; “臣自念无他才能报塞万一，唯早夜静静私自淬砺，不寻亲党，不阿友朋，上恐负圣主之殊恩，下欲全微臣之孝节。”
+&gt; —— **陈廷敬（文渊阁大学士）** ｜ 针对张谦案被攀咬后主动辞官以证清白的定调发言
 &gt; “苟正其身矣，于从政乎何有？”
-- 背景：主讲人引《论语》总结陈廷敬一生——自身品行端正，治理政事便无困难。
+&gt; —— **主讲人李正引《论语》** ｜ 针对陈廷敬一生品行端正、恪守初心的总结发言
 &gt; “一个人只要自身品行端正，那么治理政事就没有什么是困难的。”
-- 背景：主讲人对陈廷敬一生的总结，强调其儿时所学道理直到去世都未曾违背。
-# Q&amp;A 环节
+&gt; —— **主讲人李正** ｜ 针对陈廷敬儿时所学道理终身未违背的定调发言
+## Q&amp;A 环节
 未提及</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>85.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>9132/4034</t>
+          <t>9132/4106</t>
         </is>
       </c>
     </row>
@@ -13250,72 +13293,74 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t># 访谈概述
-本期《锵锵三人行》由主持人（发言人1）与嘉宾当年明月（发言人3）、马先生（发言人2）围绕热播日剧《大奥》展开，探讨日本文化中的极端精神、忠诚与一丝不苟，并与中国的中庸文化作对比。嘉宾认为日本战后30年成为世界第二经济强国，源于全民族的极端精神；日本是忠诚文化的典型，如阿福25岁入大奥当奶妈、65岁去世、40年无私心；豆腐厂规定当天做当天卖，夜里12点整所有人开始干活，体现一丝不苟。随后话题转向明朝历史。当年明月解释为何写明史：因明史资料最多，但一个事件可能有七个不同说法，研究困难。他推崇朱元璋，因其从乞丐当上皇帝，是历史上最底层出身，明朝规章制度由他定下；朱元璋参加起义军是逼上梁山，因送信被告发不得不去。嘉宾持英雄史观，认为改变时势一定出现一个人。讨论明朝兴亡时，嘉宾认为明朝仁宣盛世不错，晚明市民生活轻松，江南工商业兴起；历史最大教训是从来没有从历史中得到过教训。明朝有趣在于宦官专政、文官专政、皇帝专政等，什么都能发生；1644年明朝首都北京可能发生瘟疫（疙瘩瘟），导致无人抵抗。关于明朝皇帝与审美，嘉宾谈到正德皇帝要去江南被大臣跪谏阻止，打死十几人仍坚持；天启皇帝爱当木匠，干完活拆大盆去卖，反映当时社会对家具的重视；明式家具在国际上地位高。正德皇帝被写坏，因明武宗实录由嘉靖指派杨廷和等人编，有偏颇。宋明是汉人政权，文人审美高，满族趣味表象化，如故宫大红大紫。
-# 访谈详细记录
-## 日本历史剧《大奥》与日本文化
-- **《大奥》剧情背景**：嘉宾（发言人2）介绍该剧三部，前两部相当于中国晚清到清初时段，后一部在明治维新之前，是一部有跨越性的历史剧。
-- **严谨精神与专业态度**：当年明月（发言人3）认为该剧吸引他的是严谨精神，演员人人认真、有专业精神；第一集将军出场时所有人呈45度鞠躬，场面华丽、色彩讲究，一看就不一样。
-- **“大奥”释义**：嘉宾（发言人2）解释“大奥”即后宫，日语中“奥”指很深的地方、屋子最里处，如“深奥”一词保留此痕迹；大奥规矩非常严谨，后宫不许进人。
-- **日本天皇与幕府关系**：当年明月（发言人3）指出日本天皇一直是摆设，实际权力在幕府将军手中；德川家康开创德川幕府后权力集于一人。他举例天皇想办活动没钱、找将军要钱被拒，活动没办成，天皇后来以退位抗议。
-- **日本极端精神**：当年明月（发言人3）认为日本文化从头到尾没变，是一种“极端精神”——所有事情要做到尽头；战后1945年起日本用30年成为世界第二经济强国（绝对量而非人均量），且是世界上强国里唯一没有资源的国家，这不是偶然而是必然。
-- **中国中庸与日本坚持原则的对比**：当年明月（发言人3）称中国文化精神是中庸，讲究“道”——不是对也不是错、不是黑也不是白，是一条最适合的路，像太极融合；日本精神恰恰相反，坚持一个原则，如炮手忘记一切只记得把这一炮开出去，就达到最高境界。
-- **日本忠诚文化**：嘉宾（发言人2）认为日本是忠诚文化的典型国家，多次去过日本未感到难过、无人非礼；文化差异从电视剧看得清清楚楚，如坚韧不拔、做到极致、忠诚。
-- **阿福的忠诚事例**：嘉宾（发言人2）举例阿福25岁进大奥当奶妈，65岁去世，40年无论做什么事不处于私心、完全是公心，甚至被伤害的对方都认为他出于公心，所有人都认为他是楷模。
-- **“慢慢来才是最快的方法”**：当年明月（发言人3）称有人跟他讲过“慢慢来才是最快的方法”；所有人按自己角度做自己的事、最节省成本，不会互相抵消，形成合力非常可怕。
-- **豆腐厂一丝不苟事例**：嘉宾（发言人2）讲述参观日本最底层豆腐厂：规定当天做当天卖，夜里11:45所有人做好不动手、坐着看表，12点整一到所有人开始干活，4点多干完上市，没人瞎聊胡侃。
-- **日本民族生存观**：当年明月（发言人3）认为日本没有资源、常火山地震，人对世界有极强求生欲望、对世界悲观，必须努力求生存，所以学会融入团体、按固定规则做事才能生存；日本人看樱花只看落的那一天，对死亡不是藐视而是有点向往、不惧怕，二战日军在华暴行源于藐视生命。
-- **嘉宾（发言人2）对“藐视生命”说的异议**：嘉宾（发言人2）认为日本民族不是藐视生命，而是重视、是翻着的；经济危机时日本很多身家万贯的人选择自杀，是重视生命资本的表现。
-- **日本聪明人无生存环境**：嘉宾（发言人2）称日本聪明人没有生存环境，社会文化抵制非常难过；他举例日本做绳子的人几年不赚钱，从产地批发出来给人送去1分钱不赚，铺平市场后拿单子给对方看，请求加2%，再对另一边加2%，全国市场4%就是不得了的利润。
-- **是否愿意做日本人**：嘉宾（发言人2）表示每个人在自己文化环境里愿意做，但“你做不成，你的文化是不允许这种现象生存的”；当年明月（发言人3）坦言很不愿意，因为很多时候像盲从，且日本人有寻死的潜在欲望。
-## 明朝历史与明史研究
-- **为何写明史**：当年明月（发言人3）称别人问他为何写明史，他诚实回答“明史我最熟”，因为明史资料最多；历史研究有两个难点，一是先秦春秋（如史记中孙武事迹只有一两篇、都是编的），二是明清——明实录几千万字、明通鉴、明纪事本末、明会典等堆得比山高，但一个事件可能有七个不同说法，像罗生门。
-- **明朝本身跌宕起伏**：嘉宾（发言人2）认为明朝260多年过程本身就跌宕起伏，几次要死没死了；如土木堡之变、夺门之变，皇上被瓦剌军抓起来、把弟弟扶起来，构成现代版电视剧才能捏造出的离奇情节。
-- **推崇朱元璋的原因**：当年明月（发言人3）认为朱元璋是历史上由最底层的人坐上皇位、独此一个——乞丐当上皇帝，刘邦好歹算村长或乡长；要过饭的人当上皇帝，每一层的猫腻全知道，所以疑心重；他从一起干到最后推翻元朝当上皇帝，明朝规章制度由他定下来、基本没有太大改动。
-- **英雄史观**：嘉宾（发言人2）认为人的因素最大，“改变时势一定是出现一个人”，持英雄史观；当年明月（发言人3）补充朱元璋天分相当高，像《亮剑》里的李云龙没上过军事院校但会打仗，是战场上死死生生积累下来的经验。
-- **朱元璋参加起义是逼上梁山**：当年明月（发言人3）讲述朱元璋好友汤和让他参加起义军，他在庙里犹豫、怕被杀头；后因送信被人听到告发，没办法只能去起义。他强调历史最重要的是明白“这事是真的”——旁观者觉得一跺脚就去参加起义很好玩，但那是要掉脑袋的。
-- **历史经验教训**：当年明月（发言人3）称“我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训”，因为历史事件发生时有背景，你不比前人聪明、甚至可能比前人笨，那种情况出现时你也得这么办；史书记载下来的是照片，而古人的生活是录像，你不知道那一幕之前和之后是什么。
-- **明朝各时期状况**：嘉宾（发言人2）认为明朝经验能体现在兴亡上，如仁宣盛世不错（时间太短不怎么提）；晚明尽管史书说政治黑暗、皇帝不上朝，但老百姓生活很好。
-- **晚明市民生活**：当年明月（发言人3）称明末很多真相被掩盖，市民生活特别轻松，想去哪去哪、皇册都不用了；江浙一带工商业兴起，给人当雇工活得很滋润，三言二拍这类市民小说是娱乐产品，说明有养活自己的资本；李时珍时期闹起义是因为陕西一带发生大规模灾荒。
-- **明末工艺与画派**：嘉宾（发言人2）称明末工艺品彻底改观、非常精细，有点像日本工艺，日本派大量工匠来中国交流；吴门画派文徵明、唐寅都是中后期人物，生活不好画不出小桥流水，而八大山人朱耷画的翻白眼鸟是因为对社会愤愤不平。
-- **明朝有趣之处**：当年明月（发言人3）称明朝什么都有——宦官专政（魏忠贤）、文官专政（张居正）、皇帝专政（朱元璋），皇帝出去了还能回来、回来了还能做皇帝；吴三桂与满清合作入关，除陈圆圆外还因崇祯死了，说法是“入关为崇祯皇帝复仇”。
-- **1644年北京瘟疫**：当年明月（发言人3）称有些史料记载1644年明朝首都北京发生瘟疫“疙瘩瘟”（很可能就是天花），导致李自成打到京城无人抵抗；他曾与老师交流说明朝亡得蹊跷，“什么坏事都让他赶上了”。
-- **王朝300年大限**：嘉宾（发言人2）认为中国历史王朝300年是大限，逼近300年自己就没了，和人到八九十岁大限快到了一样；严格讲超过300年大限的只有宋朝（南北宋接上、退让大半个国土），汉朝中间隔断14年、唐朝明朝清朝都没超过。
-- **明朝公司类比**：当年明月（发言人3）称王老师安慰他时说“一公司才200多年都玩了”，而明朝是多大的摊子、几千万人；今天数世界上超过200多年的公司没有几家。
-## 明朝皇帝与审美文化
-- **正德皇帝要去江南被阻**：当年明月（发言人3）讲述明武宗要去江南，大臣跪在金水桥前抗议、不让去，皇帝气坏了到锦衣卫打死了十几个人；到扬州后要东西没有、有也不给，皇帝不生气，让人准备酒席又说吃不了，把酒席折合的银两带回去，“皇帝打秋风”。
-- **正德皇帝有城府**：当年明月（发言人3）称正德从江南回来没进京城，在通州先停了一段时间，先派人打探京城里有没有人设埋伏、搞圈套，说明此人“非常有城府”，绝不是史料所写的那么蠢。
-- **正德被写坏的原因**：当年明月（发言人3）认为正德皇帝被写坏是因为明武宗实录是嘉靖时期编的，具体由嘉靖指派杨廷和等人编写，有偏颇——嘉靖不是正德的儿子而是堂兄弟，继位拐了个弯，不能把正德写得太好；嘉靖上台后搞大礼仪事件，为自己父亲（本是王）追封皇帝，为此死了很多人。
-- **正德不留种**：嘉宾（发言人2）称正德是明朝最荒淫的皇帝（清朝最荒淫的是咸丰），但正德没少找女人却不留种，没有正宗传下来，到嘉靖是拐弯；嘉宾（发言人3）补充“据说是去过（民间），但没有具体史料能够记载”，哪个史官也不敢记皇上出去嫖娼。
-- **天启皇帝当木匠**：嘉宾（发言人2）讲述天启皇帝爱当木匠，干完活拆大盆去卖，卖完回来还打听卖得怎么样，说卖得很好就特有成就感；嘉宾（发言人1）打趣“你要是再亲自去卖，那还好卖”。
-- **明式家具地位**：嘉宾（发言人2）认为天启皇帝当木匠从侧面反映当时社会时尚，家具在每个人心里地位高；明式家具在国际上地位高绝非偶然，“所有的偶然中一定有个必然的因素”，皇帝下那么大力气做，可见影响之深。
-- **宋明与满族审美差异**：嘉宾（发言人2）认为宋明是典型汉人政权、文人政权，文人审美比较高，对美的判断不是表象的；满族是异族，对美的判断都是表象的——今天凡是外在直观能看到的都卖得贵，而100年前晚清到民国初年值钱的一定是素雅的。
-- **明朝史官冒死求名**：嘉宾（发言人1）提到明朝有些史官把冒死进谏当成时尚，“我就是要跟皇帝说点难听的，让你砍我的头，这样我青史留名”；嘉宾（发言人2）认为这种文化的力量超出我们想象，过去常忽略这种力量。
-# 关键引语与金句
+          <t># 《大奥》与明朝文化对谈
+## 访谈概述
+本期《锵锵三人行》围绕日本历史剧《大奥》与明朝历史展开对谈，受访者为《明朝那些事》作者当年明月与收藏家马未都。访谈由主持人引出《大奥》热播话题，嘉宾借此讨论日本文化中的极端精神、忠诚文化与一丝不苟的作风，并延伸至中日文化差异；随后话题转向明朝历史，当年明月谈及写作缘由、朱元璋评价、明末市民生活及历史研究方法，马未都则分享对明代皇帝与明式家具的见解。受访者核心观点包括：日本文化强调“极端精神”，做事做到尽头，战后仅用30年成为世界第二经济强国；中国历史王朝“300年大限”，超过300年的只有宋朝；历史研究应理解当时背景，不能简单套用经验教训。访谈看点在于当年明月提出正德皇帝可能被嘉靖时期编写的实录抹黑，以及马未都指出明式家具地位高非偶然、皇帝亲自制作体现其影响。
+## 访谈详细记录
+### 议题一：日本历史剧《大奥》与日本文化
+- **访谈员**：最近刚播完的《大奥》引起很大反响，你们觉得怎么样？
+- **受访嘉宾**：我觉得是大长今以后更有影响的国外电视剧，确实是一部拍得非常好的作品。
+1. 《大奥》共三部，前两部对应中国晚清到清初时段，第三部在明治维新之前，是一部有跨越性的历史剧。
+2. 受访者认为《大奥》吸引他的是严谨精神——日本历史剧中每个群众演员都非常认真，有专业精神，将军出场时所有人呈45度鞠躬，场面华丽、色彩讲究。
+3. 受访者指出「大奥」即普通话的「后宫」，日语中「奥」指很深的地方，如「深奥」一词即保留此意。
+4. 受访者介绍日本历史背景：天皇一直是摆设，实际掌权的是幕府将军；德川家康开创德川幕府后权力集于一人，天皇曾因没钱办活动向将军要钱被拒，甚至以退位抗议。
+5. 受访者认为日本文化与中国文化存在极大不同：中国文化精神是中庸，日本精神是极端——所有事情要做到尽头。
+### 议题二：日本经济成功与民族精神
+1. 受访者认为日本战后1945年起用30年成为世界第二经济强国（以绝对量计），不是偶然而是必然，源于全民族的极端精神；日本是世界上强国中唯一没有资源的国家。
+2. 受访者举例说明日本人的一丝不苟：参观日本最底层豆腐厂时，规定当天做当天卖，所有人夜里11:45坐等，12点整准时开工，4点多干完上市，期间无人闲聊。
+3. 受访者提到日本终身雇佣制：按经济学原理缺乏竞争必致低效，但日本终身雇佣却效率极高，是西方经济学无法理解的奇迹。
+4. 受访者讲述日本绳子商人案例：为铺市场几年不赚钱，以进价批发给客户，等市场铺平后出示单据请求加价2%，再对另一边同样加价2%，最终全国获利4%。
+5. 受访者认为日本忠诚文化典型体现在《大奥》中的阿福：25岁入大奥当奶妈，65岁去世，40年无论做什么事不处私心、完全公心，连被伤害的对方都认为她出于公心。
+### 议题三：日本文化的两面性
+1. 受访者认为日本民族对世界有极强求生欲望，因岛国没有资源、常发生火山地震，人必须融入团体按固定规则做事才能生存。
+2. 受访者指出日本社会聪明人没有生存环境，文化抵制让偷奸耍滑者很难过；日本早期文化对商业的影响都建立在忠诚基础上。
+3. 受访者认为日本文化存在盲从倾向，且有寻死的潜在欲望——看樱花只看落的那天不看发芽，对死亡不是藐视而是有点向往或不惧怕，二战日军在华暴行即源于藐视生命。
+4. 另一位受访者不同意「藐视生命」的说法，认为日本民族不是藐视生命而是重视，是反过来重视生命这个资本。
+### 议题四：明朝历史与《明朝那些事》
+- **访谈员**：为什么周围很多人包括金庸晚年都说要研究明史，你对明史为什么特别感兴趣？
+- **受访嘉宾**：别人为什么看明史我真不知道，我看明史是因为明史我最熟，明史的资料最多。
+1. 受访者表示历史研究有两个难点：一是先秦春秋，史料少且多不可考（如孙武事迹仅《史记》一两篇）；二是明清，资料堆得比山还高但一个事件可能有七个不同说法，如同罗生门。
+2. 受访者认为明朝260多年过程本身跌宕起伏，几次濒临灭亡——土木堡之变、夺门之变等，皇上被瓦剌军抓走、扶弟弟即位，构成现代版电视剧才有的离奇情节。
+3. 受访者推崇朱元璋：一个乞丐当上皇帝，历史上由最底层坐上皇位独此一个（刘邦好歹算村长）；他因要过饭知道每一层猫腻，疑心重，但明朝规章制度由他定下，基本没有太大改动。
+4. 受访者认为历史最重要的是明白它是发生过的——朱元璋参加起义军是被逼的：好友汤和来信被知，被告发后没办法才去，旁观者觉得好玩，但当时是要掉脑袋的风险。
+5. 受访者认为历史研究不能套用经验教训：「我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训」，因为史书记载的只是照片，而古人的生活是录像，不知道那一幕之前和之后是什么。
+### 议题五：明末社会与明朝兴亡
+1. 受访者认为明朝经验能体现在兴亡上：仁宣盛世时期非常不错；晚明尽管史书说政治黑暗、皇帝不上朝，但老百姓生活很好。
+2. 受访者指出明末很多真相被掩盖：市民生活特别轻松，想去哪去哪，连皇册都不用了；江浙一带工商业兴起，给人当雇工活得很滋润，三言二拍这类市民小说出现说明有养活自己的资本。
+3. 受访者提到明末工艺品彻底改观、变得非常精细，日本派大量工匠来交流学习；吴门画派文征明、唐寅等画小桥流水、风雨归舟图，心态轻松，到八大山人朱耷时画的都是翻白眼，因对社会愤愤不平。
+4. 受访者提到1644年明朝灭亡时北京可能发生瘟疫——疙瘩瘟，可能是天花；受访者曾与老师交流认为明朝亡得蹊跷，什么坏事都赶上了。
+5. 受访者认为中国历史王朝300年是大限，超过300年的只有宋朝（南北宋接续，退让大半个国土保证延续），汉朝中间隔断14年，唐朝、明朝、清朝都没超过。
+### 议题六：明代皇帝与明式家具
+1. 受访者认为宋明两朝是典型汉人政权、文人政权，审美判断不是表象的；满族作为异族进来后对美的判断都是表象的——今天凡是外在直观能看到的都卖得贵，而100年前晚清到民国初年值钱的一定是素雅的。
+2. 受访者讲述明武宗正德皇帝要去江南，大臣跪在金水桥前抗议，皇帝气得去锦衣卫打人、打死了十几个；到扬州要东西没有，让人准备酒席又说吃不了，把酒席折合的银两带回去——皇帝打秋风。
+3. 受访者认为正德皇帝被写坏了：明武宗实录是嘉靖时期指派杨廷和等人编的，因嘉靖是堂兄弟接班（拐了个弯），不能把正德写得太好；正德从江南回来在通州先停半年，派人打探京城有没有埋伏，显示非常有城府。
+4. 受访者提到天启皇帝爱当木匠，干完活拆了大盆去卖，卖完还打听卖得怎么样，成就感特大；这从侧面反映明式家具在当时每个人心里地位高，明式家具在国际上地位高绝非偶然。
+5. 受访者提到正德皇帝被定为明朝最荒淫的皇帝（清朝最荒淫的是咸丰），但正德没少找女人却不留种，没有正宗传下来，到嘉靖是拐弯；他对宫内女人没兴趣，因女人被训练过、禁忌多太保守，而民女不知他是谁。
+## 关键引语与金句
 &gt; “慢慢来才是最快的方法。”
-- 背景：回应主持人关于日本文化中“小聪明”与走捷径的讨论，受访者引用他人观点说明专注本分、不投机取巧反而更有效率。
+&gt; —— **发言人3（嘉宾）** ｜ 针对日本文化中“不偷奸耍滑”的做事方式，回应主持人关于日本效率与忠诚文化的讨论
 &gt; “我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。”
-- 背景：回应主持人关于明朝兴亡经验教训的提问，受访者以此概括历史经验的局限性。
-&gt; “你站在一个历史的原点，你前后都看不见，你必须撤出来你才能看见。”
-- 背景：回应主持人关于朱元璋参加起义军是否“逼上梁山”的讨论，受访者解释后人评史常因脱离当时情境而误判。
+&gt; —— **发言人3（嘉宾）** ｜ 针对明朝兴亡经验教训的总结性发言
 &gt; “你要明白你不比前人聪明，你甚至可能比前人笨，就是当那种情况出现的时候，你也得这么办。”
-- 背景：承接“历史教训”话题，受访者说明历史事件发生时有特定背景，后人不应自以为比古人高明。
-&gt; “史书上记载下来的是什么？照片。而我们实际上我们的生活古人的生活都是录像。”
-- 背景：回应主持人关于历史经验能否套用的疑问，受访者用“照片”与“录像”比喻史书记载与真实生活的差异。
-&gt; “一个人到战场上死死生生多少年啊，没死，最后积累下来经验啊。然后我一上战场我就知道，唉敌人会往哪走，我该怎么打。”
-- 背景：回应主持人关于朱元璋是否“人才决定论”的提问，受访者以《亮剑》中李云龙为例，说明实战经验比书本更重要。
-&gt; “日本的文化跟中国的文化存在一个极大的不同。中国的文化精神是中庸。”
-- 背景：回应主持人关于日本战后经济崛起的讨论，受访者对比中日文化精神差异，引出“中庸”与“极端”之别。
-&gt; “他（朱元璋）因为知道每一层的猫腻，他就疑心重，这是肯定的，但他全知道，这种人才上。”
-- 背景：回应主持人关于朱元璋是否被推崇的提问，受访者解释朱元璋从乞丐到皇帝的经历使其洞悉底层各层弊端。</t>
+&gt; —— **发言人3（嘉宾）** ｜ 回应主持人关于历史经验能否套用于明朝兴亡的问题
+&gt; “史书上记载下来的是什么？照片。而我们实际上生活古人的生活都是录像。”
+&gt; —— **发言人3（嘉宾）** ｜ 解释为何不能简单从历史中套用经验教训
+&gt; “中国的文化精神是中庸。”
+&gt; —— **发言人3（嘉宾）** ｜ 对比中日文化差异时，概括中国文化核心精神
+&gt; “日本的文化跟中国的文化存在一个极大的不同。”
+&gt; —— **发言人3（嘉宾）** ｜ 引入中日文化对比话题时的定调发言
+&gt; “他是靠他不是靠说教，他是靠具体的事。”
+&gt; —— **发言人2（嘉宾）** ｜ 评价《大奥》中阿福形象所体现的日本忠诚文化
+&gt; “所有的偶然中一定有个必然的因素。”
+&gt; —— **发言人2（嘉宾）** ｜ 回应明式家具在国际上地位高的原因，强调其非偶然性</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>75.09999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17496/5227</t>
+          <t>17496/3448</t>
         </is>
       </c>
     </row>
@@ -13685,75 +13730,87 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t># 访谈概述
-本次访谈中，作家余华回顾了其文学创作历程与人生感悟。余华将文学创作分为1.0、2.0、3.0三个阶段：1.0强调逼自己坐下来写作，2.0受卡夫卡启发遭遇心理表现障碍，3.0受威廉·福克纳影响采用视觉描写，此后未再升级。他坦言最好的写作状态在40多岁到50岁（《兄弟》至《第七天》期间），但后悔浪费了这段时间，估计还能好好写作的时间约十年。访谈覆盖文学创作理念、写作状态与时间浪费、对批评的态度与自我调节、中年危机与人生感悟、文学理想与未来计划、网络热度与公众人物身份、人生姿态与历史长河等议题。核心观点包括：作家需要运气，写作需与时代相遇；不再追求写作高度，转而追求宽度，计划先写完一部喜剧；面对批评可选择不看负面消息来调节心态。关键锚点包括作品《兄弟》《第七天》《活着》及2006年开始未完成的长篇小说。看点在于余华亲述少年时在杭州湾被海流带至40里外、靠仰泳看星空获救的经历，以及澄清网上关于他说的话有一半不是他说的，并指莫言在莎士比亚故居发誓成为剧作家是「瞎扯」。
-# 访谈详细记录
-## 文学创作阶段与理念
-- **创作三阶段划分**：余华将文学创作分为1.0、2.0、3.0版本，3.0版本后未再升级；1.0版本强调逼自己坐下来写，让屁股和椅子建立友谊，2.0版本受卡夫卡启发，写作越写越难，遇到心理表现障碍。
-- **3.0版本受福克纳影响**：余华称3.0版本受威廉·福克纳启发，采用视觉描写而非心理描写，如写穷白人杀富白人时「让心脏停止跳动，让眼睛睁开」，通过视觉精确表达人物状态。
-- **《狂人日记》例证**：余华以《狂人日记》中「赵家的狗看了我一眼」为例，说明视觉描写能让人一下知道人物精神状态；他称去过精神病医院，精神病人说话逻辑清晰，只是方向不同。
-- **《活着》与写作成熟**：余华认为《活着》可能是4.0版本，但对他已不是难题，写作已成熟；写农民要用最朴素的语言，不能用华丽语言，3.0版本已够，已是「大海」。
-- **作家需要运气**：余华认为作家什么时候写什么作品很重要，写《十八岁》时一天写完6000字，对他这种写字慢的人已是奇迹。
-## 写作状态与时间浪费
-- **最佳写作状态**：余华认为最好的写作状态在40多岁到50岁，即《兄弟》到《第七天》期间，但那段时间「玩掉了」，只出了两部作品。
-- **未完成的长篇小说**：余华2006年开始写一部长篇小说，实践跨度与《兄弟》相同，但从个人角度出发，想用接近陀思妥耶夫斯基的激烈方式写，现在身体状态能维持激烈，但「那个感觉没了」。
-- **写作时间估计**：余华称剩下的能好好写作的时间可能只有十年左右，现在的工作很简单，就是写作、读书听音乐和锻炼。
-- **未来计划**：余华希望尽快找回感觉，开学时与学生见面，处理学校事务后回三亚继续写作。
-## 对批评的态度与自我调节
-- **《兄弟》出版遭遇**：余华称《兄弟》出版时带着「肯定是一片赞扬」的期待，结果一片骂声，他当时接受很多采访努力解释作品。
-- **《第七天》后的应对**：余华称《第七天》出版时只接受了一个采访，什么都不做，「就让他们去骂吧」；出版前告诉朋友做好挨骂准备，结果果然一片骂声。
-- **批评的区分**：余华认为有些批评没有道理，如批评宋凡平人物太完美——宋凡平是阶段性人物，只能写他在这个阶段的表现；有些批评有提醒作用，如有人说《第七天》中社会底层人未必都善良，这句话说得很好。
-- **自我调节方式**：余华称通过不看负面消息来调节心态，认为「我们可以选择什么让自己去知道，什么让自己去不知道」，负面消息太多就屏蔽掉。
-## 中年危机与人生感悟
-- **34岁的虚无感**：余华称34岁时在年终总结中感到虚无，认为成年人每到年底都会发现一种虚无，一年到头来「本来一个对生活充满信心的人变成一个面试者」。
-- **中年危机的本质**：余华认为中年危机是所有人都可能遇到的，现实世界每天都是重复，只有写作能带来新的东西，虚构的世界能带来新东西。
-- **应对不安的建议**：余华建议通过选择知道什么来隔离负面消息，有权利也有能力选择接收积极的信息。
-## 文学理想与未来计划
-- **从追求高度转向宽度**：余华表示对高度已经不追求了，现在追求宽度，知道自己能力在哪里、长处在哪里、还有多少潜力；「允许自己下滑一下，但再不要下滑得太多」。
-- **计划写喜剧**：余华称这次回来选择了一篇篇喜剧，想先写完一部喜剧，改变读者对他的印象，因为「把悲伤留给虚构，把欢乐留给现实」。
-- **对马尔克斯的反思**：余华认为这一代中国作家在很大程度上被马尔克斯误导，都想在一本书里写一个世纪的故事，但「没有能力在一个不到30万字的小说里面写出一个世界」。
-- **写作目标**：余华称现在知道要什么，就是把所处时代通过更多方式表现出来。
-## 网络热度与公众人物身份
-- **停一年活动**：余华称中间停了一年，任何活动、采访都不做，按过去经验一年就能在媒体上消失，但发现自媒体时代不是这样，会把几十年前的事情翻出来。
-- **澄清网络言论**：余华称互联网上关于他说的话有一半不是他说的，如「想要命好的」「精神内耗，心里的戏太多」都不是他说的。
-- **不担心热度消散**：余华称不担心网红一夜塌房，因为他的工作不是说话，是写作，「不说话其实也挺好」。
-## 人生姿态与历史长河
-- **遗忘的姿态**：余华被问及希望以什么姿态留在历史长河，回答是「遗忘的姿态」，因为那些能勉强被微风吹进耳朵的人也是勉强吹进来的。
-- **历史长河的主题**：余华认为假如历史的长河里有一个主题，这个主题就是「一个一个世界，一个一个的人」。
-## 童年游泳经历与人生感悟
-- **海流经历**：余华称小时候每年夏天在海盐游泳，有一天进入海流，知道不能挣扎只能跟着走，一直到了40里外才爬上来，赤脚沿海边走回来，天快亮了。
-- **从紧张到松弛**：余华称刚开始紧张害怕，后来放心，因为了解杭州湾的海流只会把他带回家，不会带到太平洋；「假如没有海流的话，我很可能游到一个让我游不回来的地方」。
-- **三亚星空与童年**：余华称在三亚看到小时候的天空，因为没污染，晚上和太太走路时常看天空和月亮，通过光晕发现「月光是金色的，不是银色的」。
-- **第一次看海的感受**：余华称童年第一次看到大海时感受到宽阔，认为「宽阔的能力就是人生」；小时候的人生感受是向前看的，现在的人生感受是往后看的，回忆占多了。
-## 与莫言、苏童的莎士比亚故居之行
-- **莫言发誓是「瞎扯」**：余华称与苏童、莫言一起去莎士比亚故居，莫言在雕塑前发誓要成为剧作家是「瞎扯」，他当时在挑选帽子，帽子钱还是余华付的。
-- **三顶帽子**：余华称买了三顶一模一样的黑蓝色帽子，上面有莎士比亚名字，在伦敦和牛津天天戴着，但「莎士比亚没有给予我们任何一点灵感」。
-- **对莫言写话剧的看法**：余华认为莫言小说对话很精彩，想表达写对话的「牛逼劲」就去写话剧，20多年前就开始写了，只是没拿出来；「再过几年他又会换一个说法」。
-# 关键引语与金句
+          <t># 余华访谈：创作理念与人生感悟
+## 访谈概述
+余华接受访谈，回顾其写作生涯与人生感悟。余华是当代作家，代表作包括《活着》《兄弟》《第七天》《文城》等。访谈围绕其文学创作理念、作品与时代的关系、对批评的态度、中年危机与自我调节、网络热度及未来计划展开。余华将文学创作分为1.0、2.0、3.0三个阶段，认为3.0版本后写作已成熟，不再追求高度而追求宽度；他坦言40多岁到50岁的最好写作时间被浪费，只出了两部作品，估计还能好好写作的时间约十年；他决定先写完一个喜剧，改变读者对他的印象。访谈锚点包括《兄弟》1996年开始创作、2003—2004年重写，《十八岁》一天写完6000字，以及在三亚看到童年星空。看点在于余华亲述童年被海流带走的经历，以及他指出的与流俗看法不同之处——他认为网上关于他的话有一半不是他说的，并称莫言在莎士比亚故居发誓要成为剧作家是“瞎扯”。
+## 访谈详细记录
+### 文学创作阶段与理念
+- **访谈员**：您把自学游泳的人设分成1.0、2.0、3.0，对应池塘、江河、大海，文学创作上是否也会分阶段？
+- **受访嘉宾**：文学上三个重要时刻：第一个是逼自己坐下来写，让屁股和椅子建立友谊；第二个是受卡夫卡启发；第三个是心理描写的视觉化。
+1. 余华将文学创作分为1.0、2.0、3.0三个阶段：1.0是逼自己坐下来写，2.0受卡夫卡启发，3.0通过视觉描写心理。
+2. 余华曾以托尔斯泰和陀思妥耶夫斯基为目标，现在知道距离不可逾越，但这种野心支撑他一篇篇写下来。
+3. 余华认为心理描写应通过视觉行为呈现，如福克纳写杀人者让心脏停止跳动、让眼睛睁开，用视觉精确表达内心状态。
+4. 余华认为3.0版本后无需再升级，写作已成熟，如《活着》虽可能被视为4.0版，但对他已不是难题。
+### 作品与时代的关系
+- **访谈员**：《兄弟》是对中国一段时期全景式的描写，是否会有更长远的规划？
+- **受访嘉宾**：中国始终处于大变化时代，《兄弟》创作始于1996年，2003-2004年重写时发现2004年的变化更大。
+1. 余华认为中国始终处于大变化时代，《兄弟》创作始于1996年，当时中国社会变化复杂。
+2. 余华庆幸《兄弟》1996年没有写完，因为2004年重写时发现，2004年的变化比1996年更大。
+### 写作状态与时间浪费
+- **访谈员**：您觉得最好的写作状态出现在什么时候？
+- **受访嘉宾**：最好的写作状态在40多岁到50岁，但那段时光被浪费了，只出了两部作品。
+1. 余华认为最好的写作状态在40多岁到50岁，但浪费了时间，只出了两部作品，现在非常可惜。
+2. 余华2006年开始写一部长篇小说，实践跨度与《兄弟》相同，从个人角度出发，想用接近陀思妥耶夫斯基的激烈方式写，但感觉已失去。
+3. 余华估计自己还能好好写作的时间约十年左右，在三亚的工作就是写作、读书听音乐和锻炼。
+### 未来计划
+- **访谈员**：您的长篇从《在细雨中呼喊》到《文城》间隔越来越长，下一步作品是否在2029年？
+- **受访嘉宾**：我希望快一点，开学时与学生见面，处理学校事务后回三亚继续写作。
+1. 余华计划开学时与学生见面，处理学校事务后回三亚继续写作，安安静静把感觉找回来。
+2. 余华希望下一部作品尽快完成，不一定要等到2029年。
+### 人生感悟与海流经历
+- **访谈员**：您在文章中说第一次看到大海时感受到的是人生，您当时感受到的人生是宽广的？
+- **受访嘉宾**：人生就是宽广，小时候的人生感受是向前看的，现在的人生感受是往后看的，回忆占多了。
+1. 余华童年游泳被海流带走，从紧张害怕到放心，最后在40里外上岸，赤脚沿海边走回来，天快亮了。
+2. 余华在三亚看到童年星空，因无污染，发现月光是金色的，不是银色的。
+3. 余华认为海流对很多人可能是坏事，但那一刻对他来说，没有海流可能就回不来了。
+### 对批评的态度
+- **访谈员**：《兄弟》出版时有很多批评家的声音，当时能听到这种声音时是什么感受？
+- **受访嘉宾**：《兄弟》出版时我期待一片赞扬，结果一片骂声，弄得我有点糊涂。
+1. 余华认为《兄弟》出版时遭遇一片骂声，当时还接受了很多采访努力解释作品。
+2. 余华对待批评的方式：不看无道理批评，重视有道理批评，如《第七天》中底层人物未必都善良的批评，将在以后作品中考虑。
+3. 余华认为宋凡平是阶段性出现的人物，只能写他在这个阶段的表现，批评他太完美是没有道理的。
+### 网络热度与自我调节
+- **访谈员**：您经历这种非常高的热度之后，再回归写作是会有更多灵感，还是会背负一些顾虑？
+- **受访嘉宾**：刚开始还是有一点，一个人怎么会在互联网上火起来，真的不是自己能够掌握的。
+1. 余华曾停一年活动，任何活动、采访都不做，但发现自媒体时代会把几十年前的事情翻出来。
+2. 余华认为互联网上关于他的话有一半不是他说的，如「想要命好的」「精神内耗」等都不是他说的。
+3. 余华不担心热度消散，因为他的工作是写作，不是说话，不说话也挺好。
+### 中年危机与排解
+- **访谈员**：您在年终总结时说一个成年人每到年底都会发现一种虚无，当时是如何面对这种不安？
+- **受访嘉宾**：当时感觉生活每天都在重复，只有写作能得到一些新的东西，这就是一种中年危机。
+1. 余华认为中年危机是普遍现象，只有写作能带来新东西，虚构的世界带来新的东西，现实世界每天都是重复。
+2. 余华建议通过选择知道什么来排解焦虑，如网上负面消息太多时就不看，屏蔽掉，我们有这个权利和能力选择。
+### 文学理想与姿态
+- **访谈员**：您之前跟莫言老师一起去莎士比亚的旧居，他在雕塑前说自己要成为一个剧作家，那您的文学理想是什么？
+- **受访嘉宾**：我们这一代作家在很大程度上都被马尔克斯误导了，都想在一本书里写一个世纪的故事，但其实没有必要。
+1. 余华认为一代作家被马尔克斯误导，想在不到30万字的小说里写出一个世界，但没有能力。
+2. 余华认为莫言在莎士比亚故居发誓是瞎扯，当时莫言在挑选帽子，帽子钱还是余华付的，三顶帽子一模一样。
+3. 余华希望以遗忘的姿态留在历史长河，因为那些能勉强被微风吹进耳朵的人，也是勉强吹进来的。
+## 关键引语与金句
 &gt; “我已经把那个40多岁到50岁最好的一段时间浪费掉了，就出了两部。”
-- 背景：谈到自己最好的写作状态出现在40多岁到50岁（《兄弟》到《第七天》期间），但那段时光被玩掉了，如今深感痛苦。
-&gt; “坐下来让屁股和椅子建立友谊，这是很重要的。”
-- 背景：回答文学创作1.0版本时，强调逼自己坐下来写作的重要性。
+&gt; —— **余华（受访者）** ｜ 谈及自己最好的写作状态出现在40多岁到50岁，却因玩掉时间只出版两部作品，深感痛苦
+&gt; “假如你不坐下来写写作，你那个躺在床上想我的作品怎么成功，那是没有用的，坐下来让屁股和椅子建立友谊，这是很重要的。”
+&gt; —— **余华（受访者）** ｜ 谈文学创作1.0阶段，强调逼自己坐下来写的重要性
+&gt; “当时我觉得我将可能我的目标是对着那个托尔斯泰和陀思妥耶夫斯基去的，现在我知道我离他们的距离是不可逾越的。”
+&gt; —— **余华（受访者）** ｜ 谈年轻时写作的野心与幻想，以及如今对自身能力的清醒认知
 &gt; “心理描写没有心理，它是视觉描写。”
-- 背景：谈到受威廉·福克纳启发，用视觉描写替代心理描写来呈现人物内心动荡。
-&gt; “兄弟出版的时候，我认为肯定是一片赞扬……结果一片骂声弄得我有点糊涂。”
-- 背景：回忆《兄弟》出版时带着期待却遭遇猛烈批评，当时还努力接受采访去解释作品。
+&gt; —— **余华（受访者）** ｜ 谈文学创作3.0版本，受威廉·福克纳启发，通过视觉行为精确表达人物内心状态
+&gt; “兄弟出版的时候，我认为肯定是一片赞扬，我是带着这样的一种期待去的，结果一片骂声弄得我有点糊涂。”
+&gt; —— **余华（受访者）** ｜ 谈《兄弟》出版时遭遇猛烈批评，与预期形成巨大反差
 &gt; “发生的事情我们是无法去选择什么让它发生，什么让它不发生，但是我们可以选择什么让自己去知道，什么让自己去不知道。”
-- 背景：回应年轻人如何排解巨大不安与焦虑，分享自己面对批评时的自我调节方式。
-&gt; “把悲伤留给虚构，把欢乐留给现实。”
-- 背景：谈到自己作品几乎都是悲剧，计划先写完一部喜剧来改变读者对他的悲观印象。
-&gt; “我现在追求的是宽度，不是高度。”
-- 背景：回应文学理想时表示不再追求写作高度，转而追求宽度，把所处时代通过更多方式表现出来。
-&gt; “假如那个历史的长河里边有一个主题的话，这个主题就是。一个一个世界，一个一个的人。”
-- 背景：被问及希望以什么姿态留在历史长河时，回答是遗忘的姿态，并认为历史长河的主题是一个世界、一个人。</t>
+&gt; —— **余华（受访者）** ｜ 谈面对中年危机与负面消息时的自我调节方式
+&gt; “现在在互联网上，起码我看到的啊，关于我说的话，有一半不是我说的。”
+&gt; —— **余华（受访者）** ｜ 谈网络热度非自己掌控，自媒体时代旧事被翻出，网上大量言论并非出自他本人
+&gt; “假如那个历史的长河里边有一个主题的话，这个主题就是遗忘。”
+&gt; —— **余华（受访者）** ｜ 谈希望以何种姿态留在历史长河，答案是遗忘的姿态</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>61.9</v>
+        <v>56.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>11212/3586</t>
+          <t>11212/3398</t>
         </is>
       </c>
     </row>
@@ -13863,74 +13920,95 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t># 讲座概况
-本次讲座由主讲人系统讲解柏林战役，以采访对话形式展开，面向对二战历史感兴趣的听众。内容围绕战役背景与兵力部署、战役过程与关键事件、英美未攻柏林的原因、战役细节与影视推荐、战役影响与后续历史五个板块展开。核心判断包括：柏林战役是二战欧洲战场最后一次大规模战役，也是人类历史上最大规模的城市作战；苏军以约250万兵力对德军约100万守军形成合围，于1945年4月16日至5月2日攻克柏林；战役奠定了冷战欧洲格局，直接导致德国分裂为东西两个德国直至1990年统一。关键锚点包括苏军距柏林60公里、希特勒于4月30日在地堡自杀、5月9日德国无条件投降。对听众而言，讲座有助于理解二战终结阶段的关键战役及其对战后世界格局的深远影响。
-# 核心观点与论证
-## 战役背景与双方态势
-- **苏军先发制人**：苏军进抵奥德河、尼斯河一线（今德波边境），距柏林仅60公里；英美联军才到易北河一带，距柏林100–120公里，苏联已获先发制人机会。
-- **苏军兵力部署**：白俄罗斯第一方面军（朱可夫元帅）从奥德河—法兰克福方向北部突击包围；乌克兰第一方面军（科涅夫元帅）由克拉科夫、德累斯顿方向前出，从南部绕至波茨坦地区实施西部包围。
-- **德军防守力量**：主要为从东线撤离的中央集团军群残部、柏林卫戍部队及国民掷弹兵部队（由老人和16岁以下孩子组成的民兵），总兵力约100万人，布防从柏林到桑多梅日桥头堡及奥德河一带。
-- **苏军合围态势**：苏军两个方面军总计约250万人，从北部什切青到南部德累斯顿形成合围网，对柏林实施合围。
-## 战役进程与关键节点
-- **第一阶段突击**：1945年4月16日，苏军以数以千计的火炮和喀秋莎火箭炮轰德军阵地，白俄罗斯第一方面军越过奥德河、乌克兰第一方面军越过尼斯河展开突击。
-- **进抵与突入城区**：因德军在桑多梅日桥头堡的防线修筑，苏军拖至4月20日左右才进抵柏林城区（今潘科区及帕卡洛镇一带），4月24日由白俄罗斯第一方面军突进柏林市区，科涅夫部队仍在向柏林边缘靠近。
-- **德军抵抗亮点**：德军温克第十二集团军与苏军一直进行周旋，是战役中表现突出的部队之一。
-- **战役结束**：4月30日夜间苏军占领德国国会大厦；5月2日柏林城防司令魏德林宣布柏林其余地区德军向苏军缴械投降，柏林战役结束；5月9日德国宣布无条件投降，将所属领空、领海、机械设备及仍控制的海外属地（荷兰、丹麦、挪威、波罗的海三国地区、捷克斯洛伐克）交与盟军，二战欧洲部分正式结束。
-## 希特勒之死与后续影响
-- **希特勒自杀**：1945年4月30日，柏林已被苏军围死、苏军距其地堡仅两条街，希特勒不甘被俘，与妻子爱娃·布劳恩在地堡举枪自尽；此前4月29日二人刚举行婚礼。
-- **尸体处理与争议**：希特勒死后部下用汽油焚烧其尸体，至今未见遗体全貌，仅获烧焦焦炭；因缺乏确切证据，外界说法不一，部分人坚信纳粹未覆灭而继续抵抗，导致谣言盛起。
-- **残余部队投降**：除第九集团军及温克第十二集团军残部在温克率领下渡过易北河向英美盟军投降外，柏林其余德军全部缴械。
-- **冷战格局奠定**：柏林战役胜利后德国分裂为东西两个德国，边界大致沿罗斯托克到图林根一线，直至1990年两德统一；日本于1945年9月2日在密苏里号军舰签署无条件投降书，二战彻底结束。
-## 英美未攻柏林的原因
-- **战后占领区协议**：盟国事先已达成协议，柏林战后属于苏联占领区，柏林会分出一半区域给西方盟国（即后来的西柏林）。
-- **艾森豪威尔的考量**：美军统帅艾森豪威尔认为美军攻占柏林会增加不必要伤亡，且占领后仍需撤出，得不偿失。
-- **优先占领精华地带**：西方盟军选择优先占领慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福等德国精华地带；且战后盟军还有求于苏联共同对日作战。
-## 战役细节与史料参考
-- **易北河会师为偶然**：西欧部队与东边苏联部队事先没有交流，双方在易北河会师只是偶然，事先高层未达成共识，实为各打各的。
-- **红旗插国会大厦细节**：著名历史照片中插上国会大厦的红旗并非标准苏军制式军旗，而是士兵临时用床单和颜料绘制；该士兵手上还带着三块从德国老百姓手里抢来的手表，摄影师为顾及国际观瞻让其重新摆拍。
-- **影视与传记推荐**：苏联拍摄有《柏林战役》，德国拍摄有《帝国的毁灭》（后者侧重希特勒最后生平及柏林防守人事任命，前者强调高层运筹帷幄与基层官兵舍生忘死）；另可参阅朱可夫自传、崔可夫自传及斯大林传记中关于柏林战役后苏俄与西方博弈的记载。
-# 金句总结
+          <t># 柏林战役历史讲解与问答
+## 讲座概况
+本次讲座由主讲人系统讲解柏林战役的历史背景、过程与影响，并现场解答听众疑问。讲座面向对二战历史感兴趣的听众，围绕战役背景与双方兵力、进攻阶段与关键事件、城市作战特点、英美未攻柏林的原因、战役细节与后续影响、相关影视与书籍推荐等板块展开。主讲人核心判断包括：柏林战役是人类历史上最大规模的城市作战，也是二战欧洲战场的最后一次大规模战斗；苏军以约250万兵力（白俄罗斯第一方面军、乌克兰第一方面军）对德军约100万守军发起进攻，战役始于1945年4月16日，5月2日柏林德军投降，5月9日德国无条件投降，二战欧洲部分正式结束。讲座以关键节点为锚点：4月30日希特勒与妻子爱娃·布劳恩在地堡自杀、4月30日夜间苏军占领国会大厦、易北河会师系偶然。对听众而言，本讲有助于理解柏林战役在二战欧洲战场的收官意义及其对战后冷战格局的奠基作用。
+## 核心观点与论证
+### 柏林战役的战略地位与苏军先机
+- 柏林战役是第二次世界大战欧洲战场的最后一次大规模战斗，也是苏德战争期间苏德进行的最后一场大规模战役。
+- 1945年同盟国与苏俄已从不同方向攻入德国本土，纳粹政权覆灭只是时间问题；对苏联而言，占领柏林可获得至高无上荣誉，故从上到下团结一致，不惜代价强攻。
+- 苏军进抵奥德河、尼斯河一线（今德波边境），距柏林仅60公里；英美联军刚到易北河一带，距柏林100–120公里，苏联已获先发制人机会。
+### 双方兵力与部署
+- 苏军参战部队为白俄罗斯第一方面军（指挥官朱可夫元帅）与乌克兰第一方面军（指挥官科涅夫元帅），总计约250万人，从北部什切青到南部德累斯顿形成合围网。
+- 白俄罗斯第一方面军从奥德河—法兰克福方向北部对柏林突击包围；乌克兰第一方面军由克拉科夫及德累斯顿方向前出，从南部绕至波茨坦地区实施西部包围。
+- 德军防守部队主要为从东线撤离的中央集团军群残部、柏林卫戍部队及国民掷弹兵部队（由老人及16岁以下孩子组成的民兵），总计约100万人，从柏林到桑多梅日桥头堡及奥德河一带布防。
+### 战役进程与关键节点
+- 第一阶段1945年4月16日，苏军以数以千计火炮和喀秋莎火箭炮轰德军阵地，白俄罗斯第一方面军越过奥德河、乌克兰第一方面军越过尼斯河展开突击。
+- 因德军在桑多梅日桥头堡防线修筑，苏军至4月20日左右才进抵柏林城区（今潘科区及帕卡洛镇一带），4月24日白俄罗斯第一方面军突入市区，科涅夫部队仍在向柏林边缘靠近。
+- 德军温克第十二集团军与苏军周旋，表现突出；4月30日夜间苏军占领德国国会大厦，5月2日柏林德军全部缴械投降，柏林战役结束。
+- 5月9日德国宣布无条件投降，将领空、领海、机械设备及仍控制的海外属地（荷兰、丹麦、挪威、波罗的海三国地区、捷克斯洛伐克）交与英美盟军及苏俄最高统帅，二战欧洲部分正式结束。
+### 希特勒自杀与后续影响
+- 1945年4月30日，柏林已被苏军围死，苏军距希特勒地堡仅两条街，希特勒不甘被俘，与妻子爱娃·布劳恩举枪自尽；此前4月29日二人举行婚礼。
+- 希特勒尸体被部下用汽油焚烧，至今未见遗体全貌，仅获烧焦焦炭，外界说法不一；除少数亲信外，多数人坚信纳粹未覆灭，以自欺欺人方式继续战斗，导致谣言盛行。
+- 柏林战役后德国分裂为东西两个德国，沿罗斯托克到图林根边界，奠定冷战欧洲基调，直至1990年两德统一。
+### 英美未攻柏林的原因
+- 盟国事先已达成协议，柏林战后属苏联，但会分出一半区域给西方盟国（即后来的西柏林）。
+- 美军统帅艾森豪威尔认为攻占柏林会增加不必要伤亡，且占领后还需撤出，得不偿失；西方盟军优先占领慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福等德国精华地带。
+- 打完德国后盟军还有求于苏联，需其协助对日作战。
+### 战役细节与史实补充
+- 易北河会师系偶然：西欧部队与东边苏联部队事先无交流，双方见到对方部队才知道合拢，高层未达成共识，各打各的。
+- 红旗插国会大厦的旗帜非标准苏制军旗，系士兵用床单和颜料临时绘制；插旗士兵手上戴有三块从德国百姓抢来的手表，摄影师为顾及国际观瞻要求重新摆拍。
+- 柏林城防司令魏德林宣布柏林其余地区德军向苏军投降；第九集团军及温克第十二集团军残部在温克率领下渡易北河向英美盟军投降。
+### 相关影视与书籍推荐
+- 影视推荐：苏联《柏林战役》、德国《帝国的毁灭》；德国视角侧重希特勒最后生平及柏林防守人事任命，苏联视角强调高层运筹帷幄与基层官兵舍生忘死。
+- 书籍推荐：朱可夫自传、崔可夫自传，以及斯大林传记中关于柏林战役后苏俄与西方博弈（西柏林划分、德国边境重新划定）的记载。
+## 金句总结
 &gt; “谁要是能占领了柏林，谁在二次世界大战结束之后，可以获得至高无上的一个地位。”
-- 背景：讲解战役背景时，说明苏联从上到下团结一致、不惜代价强攻柏林的原因。
-&gt; “此时对于纳粹德国来说可以说是丧钟敲响的开始。”
-- 背景：讲到苏军已进抵奥德河—尼斯河一线、距柏林仅60公里时，对德军处境的判断。
-&gt; “城市作战……非常困难，非常危险。”
-- 背景：回答听众关于城市作战与野外作战区别的提问，说明街道环境中敌军可从各处攻击、坦克和车辆受限。
-&gt; “大部分人都坚信纳粹没有覆灭，还在就是以自欺欺人的方式麻痹自己和苏军进行的就是不同程度的战斗。”
-- 背景：解释希特勒尸体被焚烧、遗体全貌未获证实后，外界传言纷起的原因。
-&gt; “与其这样，还不如说是尽可能去占领更多德国的精华地带……柏林就让给苏联吧。”
-- 背景：解释英美未攻柏林的原因，转述艾森豪威尔基于战后占领区协议与避免不必要伤亡的考量。
-&gt; “那个红旗其实不是一个标准的苏联制式军旗，它是士兵们临时用床单以及颜料临时绘制这么一面旗帜。”
-- 背景：补充“红旗插上国会大厦”著名照片的细节，说明旗帜为临时制作。
-&gt; “奠定了冷战欧洲部分的一个基调。”
-- 背景：回答柏林战役胜利后世界格局的提问，指出德国随后分裂为东西两个德国、直至1990年统一。
-# Q&amp;A 环节
-**听众**：城市作战跟野外作战有什么明显区别或定义吗？
-**主讲人**：城市作战中部队在街道上，敌人可能从任何方向攻击，坦克和车辆在街道上容易遭到来自建筑物或其他街道的火箭筒和机枪攻击，因此非常困难和危险。
-**听众**：是不是这个战役里面希特勒自杀了？
-**主讲人**：是的。1945年4月30日，柏林已被苏军围死，苏军距希特勒地堡仅两条街，希特勒不甘被俘，与妻子爱娃·布劳恩一起举枪自尽。
-**听众**：希特勒在地堡自杀的细节现在仍有争议，为什么这些细节这么受关注？
-**主讲人**：他自尽后部下用汽油焚烧其尸体，至今未见到遗体全貌，只获得烧焦的残骸，外界说法不一。除少数亲信外，大部分人坚信纳粹没有覆灭，以自欺欺人的方式继续战斗，导致谣言流传。
-**听众**：想更详细了解这场战役，有什么影视推荐吗？
-**主讲人**：苏联有《柏林战役》，德国有《帝国的毁灭》。德国角度更多描写希特勒最后生平及柏林防守人事任命；苏联方面强调从高层运筹帷幄到基层官兵舍生忘死的各方面描写。
-**听众**：主要进攻柏林的是苏联部队，为什么英美不打柏林？
-**主讲人**：丘吉尔曾想抢占柏林，但盟国事先已达成战后德国占领区协议，柏林战后属苏联，只分一半给西方盟国（后来的西柏林）。艾森豪威尔认为美军攻占柏林会增加不必要伤亡，且占领后还要撤出，得不偿失，不如占领慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福等精华地带。此外盟军还有求于苏联共同对日作战。
-**听众**：这场战役大概持续了多久？
-**主讲人**：从4月16日开始，一直进行到5月2日。
-**听众**：有什么书可以看吗？
-**主讲人**：可以看朱可夫自传、崔可夫自传，以及斯大林传记中关于柏林战役后苏俄与西方博弈、西柏林划分和德国边境重新划定的内容。
-**听众**：柏林战役胜利后，当时世界形成了怎样的格局？
-**主讲人**：奠定了冷战欧洲部分的基调，德国分裂为东西两个德国，边界大致沿罗斯托克到图林根，直到1990年两德才统一。
-**听众**：B站上比较火的鬼畜片段就是这场战役末期发生的吗？
-**主讲人**：对，那是电影《帝国的毁灭》里的片段，尤其是希特勒大骂温克丢下柏林逃跑那一段。</t>
+&gt; —— **主讲人** ｜ 针对苏联不惜代价强攻柏林动机的定调发言
+&gt; “城市作战……敌人可以从任何方向攻击你的部队，你的坦克和车辆就在街道上，敌人可能从建筑或其它街道用火箭筒和机枪攻击你，这非常困难和危险。”
+&gt; —— **主讲人** ｜ 针对城市作战与野外作战区别的定调发言
+&gt; “希特勒不甘于在兵败之后被苏联俘虏，所以说他举枪自尽了。”
+&gt; —— **主讲人** ｜ 针对希特勒自杀原因的定调发言
+&gt; “除了少数亲信以外，大部分人都坚信纳粹没有覆灭，还在以自欺欺人的方式麻痹自己和苏军进行不同程度的战斗。”
+&gt; —— **主讲人** ｜ 针对希特勒尸体被焚烧后谣言盛行的定调发言
+&gt; “你占领了柏林，你还是要只是把西柏林占在自己的手里，但是整个德国东部都是苏联的占领区，意味着西方盟军还要撤回去，所以说得不偿失。”
+&gt; —— **主讲人** ｜ 针对英美未攻柏林原因的定调发言
+&gt; “那个红旗其实不是一个标准的苏联制式军旗，它是士兵们临时用床单以及颜料临时绘制这么一面旗帜，但是这个非常具有代表性的意义。”
+&gt; —— **主讲人** ｜ 针对红旗插国会大厦标志性意义的定调发言
+&gt; “奠定了冷战欧洲部分的一个基调，就是差不多就是德国后来就分裂成了东西两个德国。”
+&gt; —— **主讲人** ｜ 针对柏林战役战后影响的定调发言
+## Q&amp;A 环节
+### Q1. 城市作战与野外作战的区别
+- **听众**：城市作战跟野外作战有什么明显的区别或定义吗？
+&gt; **主讲人**：城市作战中敌人可能从任何方向攻击你的部队，坦克和车辆在街道上容易遭到来自建筑物或其他街道的火箭筒和机枪攻击，非常困难和危险。
+### Q2. 希特勒是否在战役中自杀
+- **听众**：是不是这个战役里面希特勒自杀了？
+&gt; **主讲人**：是的。1945年4月30日，柏林已被苏军围死，红军距离希特勒地堡仅两条街，希特勒不甘被俘，与妻子爱娃·布劳恩一起举枪自尽。
+### Q3. 希特勒自杀细节为何争议不断
+- **听众**：希特勒在地堡自杀的细节现在仍有争议，为什么这些细节这么受关注？
+&gt; **主讲人**：他自尽后部下用汽油焚烧了尸体，至今未见遗体全貌，只有烧焦的焦炭，外界说法不一。除少数亲信外，大部分人坚信纳粹未覆灭，以自欺欺人的方式继续战斗，导致谣言盛行。
+### Q4. 相关影视作品推荐
+- **听众**：想更详细了解这场战役，有什么影视推荐吗？
+&gt; **主讲人**：苏联有《柏林战役》，德国有《帝国的毁灭》。德国视角侧重希特勒最后生平及柏林防守的人事任命；苏联视角强调从高层运筹帷幄到基层官兵舍生忘死的全面描写。
+### Q5. 英美为何不进攻柏林
+- **听众**：主要进攻柏林的是苏联部队，为什么英美不打柏林？
+&gt; **主讲人**：丘吉尔想抢占柏林，但盟国事先已达成协议，柏林战后属苏联，会分出一半给西方盟国（即后来的西柏林）。艾森豪威尔认为美军攻占柏林会增加不必要伤亡，且占领后还要撤出，得不偿失；不如占领慕尼黑、斯图加特、纽伦堡、汉堡、法兰克福等精华地带，且战后盟军还有求于苏联共同对日作战。
+### Q6. 易北河会师与红旗插国会大厦的细节
+- **听众**：补充两个细节——易北河会师是偶然，红旗插国会大厦是临时制作的。
+&gt; **主讲人**：易北河会师确实是双方事先无交流、各打各的偶然相遇。插旗士兵手上还戴着三块从德国老百姓抢来的手表，摄影师觉得有碍国际观瞻，要求重新摆拍，把表藏起来。
+### Q7. 战役持续时间
+- **听众**：这场战役大概持续了多久？
+&gt; **主讲人**：从4月16日开始，一直进行到5月2日。
+### Q8. 相关书籍推荐
+- **听众**：有什么书可以看吗？
+&gt; **主讲人**：可以看朱可夫自传、崔可夫自传，以及斯大林传记中关于柏林战役后苏俄与西方博弈、西柏林划分和德国边境重新划定的内容。
+### Q9. 战役胜利后的世界格局
+- **听众**：柏林战役胜利后，当时世界形成了怎样的格局？
+&gt; **主讲人**：奠定了冷战欧洲部分的基调，德国分裂为东西两个德国，大致沿罗斯托克到南部图林根的边界，直到1990年才统一。
+### Q10. 二战结束时间
+- **听众**：1945年后日本投降，二战紧接着结束了吗？
+&gt; **主讲人**：欧洲部分结束了；亚洲部分日本于9月2日在密苏里号军舰上签署无条件投降书，二战才彻底结束。
+### Q11. B站鬼畜片段出处
+- **听众**：B站上比较火的鬼畜片段是战役末期发生的吗？
+&gt; **主讲人**：对，那是电影《帝国的毁灭》里的片段，尤其是希特勒大骂温克丢下柏林逃跑那一段。</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>46</v>
+        <v>48.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4609/3412</t>
+          <t>4609/3940</t>
         </is>
       </c>
     </row>
@@ -14078,56 +14156,57 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t># 全文摘要
-本次为多人闲聊式讨论，参与方为发言人1至发言人5共五位，无明确主办方或机构背景。讨论围绕社会约定俗成规则的合理性、理想工作形态、AI与机器人承担苦活累活的可能性及其思想意识风险、以及语音分离标注测试等议题展开。关于社会规则，发言人1认为必须结婚、买房等规则不合理，经济不好时更不可行；发言人2认为结婚、买房、升职取决于遇到的人和自身经济能力；发言人3认为人必须工作是合理的。关于理想工作，发言人1希望按兴趣干活，发言人3举例宠物博主，发言人2提到游戏高手，并建议让AI做苦活累活而非创作。关于机器人风险，发言人2担忧机器人有独立思想后反抗并奴役人类，引用《终结者》剧情；发言人5认为机器人只需执行命令不必有思想；发言人3认为智能和思想可能无法分开。会议以分享为主，未形成明确结论。
-# 分段速览
-## 00:00:02-00:01:18 社会约定俗成规则的合理性讨论
-发言人1提出必须结婚、必须买房等约定俗成规则不合理，经济不好时更不可行；发言人2补充必须结婚生子，认为结婚、买房、升职都取决于遇到的人和自身经济能力；发言人3认为人必须工作是合理的，发言人1补充工作合理但状态应合理，应干自己想做的，不要与钱太保密。
-## 00:01:18-00:03:32 理想工作形态与AI承担苦活累活
-发言人1理想工作是每天按兴趣干活；发言人3举例宠物博主工作好，发宠物视频剪视频即可赚钱；发言人2提到游戏高手。发言人1指出总有脏活累活没人承担，发言人3建议让AI做苦活累活而非创作；发言人2联想到蔡明小品中机器人煮牛皮制品，认为机器人负责生产、人享受会提升幸福感。
-## 00:03:32-00:07:50 机器人思想意识与人类控制
-发言人2担忧机器人有独立思想后不甘压迫、反抗并奴役人类，引用终结者剧情；发言人3提到斯皮尔伯格人工智能电影结局类似；发言人5认为机器人只需接受命令执行命令，不必有思想；发言人3认为智能和思想可能无法分开。发言人2列举军队单兵装甲外骨骼、智能枪械、排雷机械狗等应用。
-## 00:07:50-00:09:54 影视作品中的机器人思想案例
-发言人2引用重返德军总部超级战士、数码宝贝中机械邪龙兽、安多路兽等案例，说明机器人有思想的构想；提到安多路兽在第二部被黑色魔轮控制后仍能通过人脸识别判断身份，主角嘉儿通过记忆唤醒其最终记忆。
-## 00:09:54-00:10:56 语音分离标注测试与结束
-发言人3提到语音分离测试，同时两人以上说话会有问题；发言人1认为标注的人需要认识他们的声音，并认为单人的麦至少自己的麦很强；随后结束讨论。
-# 要点梳理
-## 社会约定俗成规则的合理性
-- **发言人1**：必须结婚、必须买房等约定俗成规则不合理，经济好的时候可以，经济不好的时候不太可以。
-- **发言人2**：必须结婚生子也是不合理规则；结婚、买房、升职都取决于遇到什么样的人和自身经济能力，不能说得太绝对。
-- **发言人3**：人必须工作是合理的。
-- **发言人1**：工作可能是合理的，但工作状态应合理——干自己想做的，不要跟钱太保密。
-## 理想工作形态与AI承担苦活累活
-- **发言人1**：理想工作是每天起来想干啥就干啥，参考自己兴趣干活。
-- **发言人3**：宠物博主这类工作很好，每天发宠物日常、剪剪视频就能赚钱。
-- **发言人2**：游戏高手也是理想工作之一。
-- **发言人1**：指出总有脏活累活没人愿意承担。
-- **发言人3**：建议让AI去做苦活累活，而不是让它搞创作、艺术。
-- **发言人2**：提到蔡明小品中机器人把牛皮制品煮汤的情节，认为机器人负责生产、人负责享受会提升幸福感，前提是机器人脑袋不出毛病。
-- **发言人1**：质疑机器人负责生产、人享受的规则能否实现，认为这种规则不合理。
-## 机器人思想意识与人类控制
-- **发言人2**：担忧机器人有独立思想后不甘被压迫、奋起反抗并奴役人类，引用《终结者》剧情。
-- **发言人3**：提到斯皮尔伯格《人工智能》电影结局也是类似走向，归结为哲学问题。
-- **发言人5**：认为机器人只要能接受到命令、执行命令就行，不必有思想。
-- **发言人3**：认为机器人得有智能，但智能和思想可能没法分开。
-- **发言人5**：指出有思想才能执行指令，但思想可能带来不好影响，如让机器人往前走它却去打人。
-- **发言人2**：认为机器人有独立意识后可能成为犯罪代理人、职业杀手或超级战士，群体罢工反抗人类后果灾难性。
-- **发言人2**：列举军事应用——军队已有单兵装甲外骨骼、智能枪械、智能火箭发射器、排雷机械狗和机械车，若列装普及或不再需要单兵轻武器。
-- **发言人2**：引用《重返德军总部》超级战士、《数码宝贝》守卫兽和机械装甲兽进化成安多路兽、机械邪龙兽等案例，说明机器人有思想意识的构想。
-- **发言人2**：提到《数码宝贝》第二部第七集安多路兽被黑色魔轮控制后仍能通过人脸识别判断出人是谁，认为日本人九十年代就有此类思维构想。
-- **发言人4**：对《数码宝贝》中守卫兽和安多路兽的具体部数提出疑问，发言人2回应第一部和第二部都有。
-## 语音分离标注测试
-- **发言人3**：提到语音分离测试，同时两人以上说话时会有问题。
-- **发言人1**：询问两人一起说话时标注效果如何，认为标注的人需要认识他们的声音。
-- **发言人1**：认为单人的麦至少自己的麦很强，应该是单的。</t>
+          <t># 社会规则与AI机器人影响闲聊讨论
+## 全文摘要
+本次为多人闲聊式讨论，共5位发言人参与，无主办方与正式议程。讨论围绕社会约定俗成规则的合理性、理想工作形态、AI与机器人承担苦活累活的可能性及机器人拥有思想意识后的风险等议题展开，最后提及语音分离标注测试。关于社会规则，发言人认为必须结婚、买房等规则不合理，其可行性受经济条件与个人能力影响；关于理想工作，有观点认为按兴趣工作为佳，并建议由AI承担脏活累活而非创作；关于机器人风险，讨论聚焦于机器人具备独立思想后可能罢工反抗人类，并提及军队已有单兵装甲外骨骼等半机械人技术。讨论以分享为主，未形成明确结论。
+## 分段速览
+### 00:00:02-00:01:18 社会约定俗成规则的合理性
+发言人1提出必须结婚、必须买房等约定俗成规则不合理，认为经济好的时候可以，经济不好的时候不太可以；发言人2补充必须结婚生子也不合理，认为结婚、买房取决于遇到的人和自身经济能力；发言人3则认为历史对静辉来说都是合理的。发言人1还提到人不工作世界无法运转，工作可能合理，但理想状态是干自己想做的、不跟钱太保密。
+### 00:01:18-00:02:31 理想工作状态与脏活累活
+发言人2询问大家理想状态中的工作，发言人1表示每天起来想干啥就干啥、按兴趣干活很好；发言人4提出有没有可能不干活更好；发言人3举例宠物博主每天发宠物视频剪视频就能赚钱，发言人2提到游戏高手。发言人1指出总有一些脏活累活没人承担，发言人3建议让AI做苦活累活，而不是搞创作。
+### 00:02:31-00:05:53 机器人干苦活累活与思想意识风险
+发言人2联想到机器人干苦活累活，并回忆蔡明小品中机器人脑袋被敲后逆其道而反之的情节，讨论机器人负责生产、人负责享受能否实现。发言人2担心机器人有独立思想后罢工反抗人类，如终结者剧情；发言人3提到斯皮尔伯格的人工智能电影也是类似结局；发言人5认为机器人只要能接受到命令执行命令就行，不必有思想，发言人3认为智能和思想可能没法分开。
+### 00:05:53-00:08:05 机器人思想的风险与半机械人技术
+发言人5担心思想会带来不好影响，如机器人执行指令时打人；发言人2认为机器人有独立意识后罢工反抗人类后果灾难性，可能成为犯罪代理人、职业杀手或超级战士。发言人2提到军队已有单兵装甲外骨骼、智能枪械、智能火箭发射器等半机械人技术，排雷的机械狗和机械车已在用。
+### 00:08:05-00:10:56 数码宝贝联想与语音分离测试
+发言人2联想到重返德军总部的超级战士和数码宝贝中守卫兽、机械装甲兽进化成安多路兽，以及第一部最终boss机械邪龙兽是精密机械超级计算机形成生命体，并回忆第二部第七集安多路兽通过人脸识别判断人的片段。随后发言人3提到语音分离测试，同时两人以上说话会有影响，发言人1询问两人一起说话标注情况，认为标注的人需认识声音，并认为单人麦很强，最后发言人3提议结束，发言人4和发言人2同意停止。
+## 要点梳理
+### 社会约定俗成规则的合理性
+1. 发言人1认为必须结婚、必须买房等约定俗成规则不合理，经济好的时候可以，经济不好的时候不太可以。
+2. 发言人2补充必须结婚生子也是不合理规则，认为结婚、买房取决于遇到什么样的人及自身经济能力。
+3. 发言人3认为历史对静辉来说都是合理的。
+4. 发言人3提出人必须要工作是合理的；发言人2认为职业选择、进修学习等存在不确定性。
+### 理想工作与AI承担苦活累活
+1. 发言人1认为人不工作世界无法运转，工作可能合理，但理想状态是每天起来想干啥就干啥、按兴趣干活。
+2. 发言人4提出有没有可能不干活更好。
+3. 发言人3举例宠物博主工作好，每天发宠物视频剪视频就能赚钱；发言人2补充游戏高手。
+4. 发言人1指出总有一些脏活累活没人承担；发言人3建议让AI做苦活累活，而不是搞创作。
+5. 发言人2联想到机器人干苦活累活，并提及蔡明小品中机器人出故障的情节。
+### 机器人拥有思想意识的风险
+1. 发言人2担心机器人有独立思想后罢工反抗人类，如《终结者》剧情，后果灾难性。
+2. 发言人3提到斯皮尔伯格《人工智能》电影结局也是机器人反抗。
+3. 发言人5认为机器人只要能接受到命令执行命令就行，不必有思想；发言人3认为智能和思想可能没法分开。
+4. 发言人5担心思想带来不良影响，如机器人执行指令时打人；发言人2列举机器人成为犯罪代理人、职业杀手或超级战士等后果。
+5. 发言人2提到军队已有单兵装甲外骨骼、智能枪械、排雷机械狗等半机械人技术。
+6. 发言人2以《重返德军总部》超级战士、《数码宝贝》机械邪龙兽等为例，讨论机器人有思想意识的反派设定。
+### 语音分离标注测试
+1. 发言人3提到语音分离测试，同时两人以上说话会有影响。
+2. 发言人1询问两人一起说话标注情况，认为标注的人需认识声音，并认为单人麦很强。
+3. 发言人3提议结束，发言人4和发言人2同意停止。
+### 待确认与风险
+1. 机器人有独立思想后可能罢工反抗人类，后果灾难性。【高风险】
+2. 机器人有思想可能带来不良影响，如执行指令时打人。【高风险】
+3. 机器人可能成为犯罪代理人、职业杀手或超级战士。【高风险】
+4. 机器人有思想后是否会反抗人类、人类能否控制得当，未达成一致。
+5. AI普及后人类是否真的不用干苦活累活，尚属推测。</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>35.8</v>
+        <v>37.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3931/2278</t>
+          <t>3931/2244</t>
         </is>
       </c>
     </row>
@@ -14221,41 +14300,43 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t># 全文摘要
-本次为两人闲聊式会议，发言人1主导、发言人2插话提问，无主办方与正式议程。围绕哥斯拉系列电影剧情梳理与核废水现实影响两大板块展开：前者覆盖1954年首部至今日美各版本故事线、哥斯拉角色定位及怪兽设定；后者由电影题材引申至日本核废水排放对海产品与饮水安全的影响，并对比切尔诺贝利核事故处理方式。以分享为主，未形成明确结论。关键锚点：哥斯拉首部电影诞生于1954年；2014年美国版《哥斯拉》中哥斯拉与人类联手团灭雾托物种；2016年日本版《新哥斯拉》中哥斯拉最终被无人机投放炸弹耗尽能量并以冷冻剂封印；发言人2留学日本期间购买中国进口鱼类以规避核废水风险。
-# 分段速览
-## 00:00:00-00:09:48 哥斯拉系列电影剧情梳理
-发言人1主导梳理哥斯拉系列电影剧情，从1954年首部哥斯拉电影讲起，介绍哥斯拉起源为海底生物吸食核废料后变异，在日本神话中是大自然守护神，因人类核试验破坏生态而报复人类。随后展开美国版与日本版不同故事线的讨论，包括《哥斯拉大战金刚》中机械基多拉被金刚与哥斯拉联手打败、2014年美国版《哥斯拉》中哥斯拉与人类联手团灭雾托物种、2016年日本版《新哥斯拉》中哥斯拉被无人机投放炸弹耗尽能量并以冷冻剂封印等情节。发言人2偶尔插话提问，讨论围绕哥斯拉的角色定位、各版本剧情差异及怪兽设定展开。
-## 00:09:48-00:10:51 哥斯拉与奥特曼的关系讨论
-发言人1说明哥斯拉与奥特曼虽导演同为圆谷英二，但分属不同时间线，哥斯拉是地球本土物种，奥特曼来自奥特之星，两者均为正面形象，未直接战斗。同时提到翼龙拉顿在不同作品中分别与哥斯拉和奥特曼战斗过。
-## 00:10:51-00:15:17 核废水排放的现实影响与切尔诺贝利对比
-由哥斯拉题材引申到日本核废水排放的现实问题。发言人2提到留学日本期间购买中国进口鱼类以规避风险；发言人1指出日本国产产品因民族自信定价高昂但品质未必更优。讨论还涉及核废水对饮水安全的影响，以及切尔诺贝利核事故后反应堆被水泥封存、周边成为无人区的处理方式，被认为比日本更负责任。
-# 要点梳理
-## 哥斯拉系列电影剧情梳理
-- **起源设定**：哥斯拉首部电影诞生于1954年，迄今约70多年；起源为海底生物吸食核废料、核废水后变异成庞然大物，对人类世界展开报复。
-- **角色定位**：哥斯拉在日本神话中是大自然守护神，攻击人类是因人类无限制搞核试验、破坏自然生态；哥斯拉既有反派形象也有正面形象。
-- **美版《哥斯拉大战金刚》**：反派基多拉被哥斯拉打败后，人类反派势力将其仅存的一个头加装机械装甲复活为机械基多拉；金刚与哥斯拉不计前嫌联手，在香港九龙打败机械基多拉。
-- **2014年美国版《哥斯拉》**：两个以核弹、核废料为能源的蝙蝠变异物种「雾托」出现，哥斯拉为维护地球安全与人类携手将其团灭。
-- **美版第二部《哥斯拉怪兽之王》**：人类频繁核试验唤醒全球沉睡怪兽，基多拉降临地球；人类试图用水下子母弹形式让哥斯拉窒息，结果基多拉不受影响、哥斯拉差点溺死；人类重新喂核废料、核武器实爆唤醒哥斯拉打败基多拉。
-- **2016年日本版《新哥斯拉》**：海里蜥蜴类生物喝核废水后不断升级变大，人类武器攻击反而增强其战斗力；最终以无人机投放炸弹耗尽能量，再用冷冻剂封印。
-- **日本版其他剧情**：人类反派被做成外星人形象，外星人控制基多拉和其他怪兽，哥斯拉因基因不同反杀被外星人控制的怪兽、解放地球。
-- **哥斯拉与奥特曼关系**：两者导演最早都是圆谷英二，但分属不同时间线——哥斯拉是地球本土物种、奥特曼来自奥特之星，均为正面形象，未直接战斗；翼龙拉顿在哥斯拉和奥特曼作品中均与正派形象战斗过。
-- **系列延续原因**：哥斯拉每次都没被真正杀死，重新沉睡后形成不同版本续集；相关题材包括哥斯拉大战人类、机械哥斯拉、基多拉、哥斯拉最后的战斗等。
-## 核废水排放的现实影响
-- **日本核废水排放**：发言人1指出只要日本不停止排放核废水，哥斯拉题材就不会停；日本决定权不在自身，美国要求排不得不排。
-- **海产品与饮水担忧**：发言人1认为即使不吃日本海产品，日常饮水也会受影响；发言人2曾留学日本，当时购买中国进口到日本的鱼类以规避风险。
-- **日本国产食品价格**：发言人2称日本有民族自信，国产产品打上标签后价格非常贵，但品质未必更优。
-- **核废水健康影响**：发言人1表示目前未见变异案例，但白血病等病变肯定存在；不会出现像哥斯拉那样喝核废料马上变异成庞然大物的情况。
-- **切尔诺贝利对比**：切尔诺贝利核事故后反应堆被水泥封住，普里皮亚季和切尔诺贝利被称为鬼城、方圆百里无人区；发言人1认为相比日本，切尔诺贝利至少拦截封存了反应堆，处理更负责任。
-- **相关文艺作品**：游戏《使命召唤4》有切尔诺贝利关卡，反派车臣派军去挖核废料时被英国SAS特种部队主角狙杀、打断一条胳膊（双狙人关卡）。</t>
+          <t># 哥斯拉系列电影剧情与核废水话题讨论
+## 全文摘要
+本次为两人闲聊式讨论，由发言人1主导、发言人2参与，围绕哥斯拉系列电影剧情展开梳理，并延伸至核废水排放与核事故等现实话题。讨论覆盖哥斯拉起源与角色设定、日美不同版本故事线（含《哥斯拉怪兽之王》《哥斯拉大战金刚》《新哥斯拉》等）、哥斯拉与奥特曼的关系，以及日本核废水排放、切尔诺贝利核事故等现实议题。哥斯拉首部电影诞生于1954年，迄今已70余年；其设定为海底生物吸食核废料后变异，在日本神话中是大自然守护神，因人类破坏生态而攻击人类。讨论以分享为主，未形成明确结论。
+## 分段速览
+### 00:00:00-00:09:18 哥斯拉系列电影剧情梳理
+发言人1主导梳理哥斯拉系列电影剧情，从1954年首部电影讲起，介绍哥斯拉起源为海底生物吸食核废料后变异，在日本神话中是大自然守护神，因人类破坏生态而攻击人类。发言人1详细讲解了美国版《哥斯拉怪兽之王》中哥斯拉与人类携手打败外星生物基多拉，《哥斯拉大战金刚》中哥斯拉与金刚因地盘冲突战斗后联手打败机械基多拉，2014年美国版中哥斯拉与人类团灭以核废料为能源的雾托物种，以及2016年日本版《新哥斯拉》中哥斯拉吸收核废料不断升级，最终被无人机投放炸弹耗能后冷冻封印。发言人2偶尔插话提问，发言人1进行解答。
+### 00:09:18-00:12:01 哥斯拉与奥特曼关系及核废水题材延伸
+发言人1说明哥斯拉与奥特曼因导演同为圆谷英二，但属于不同时间线，未直接战斗。发言人2提及哪吒与变形金刚的中美合拍电影传闻。发言人1认为只要日本不停止排放核废水，相关题材电影就不会停，并指出日本排放核废水受美国影响。
+### 00:12:01-00:15:17 核废水排放现实讨论与切尔诺贝利核事故
+发言人2提到在日本留学期间因日本排放核废水，购买的是中国进口的鱼，并指出日本国产产品存在迷之民族自信导致价格偏高。发言人1提到切尔诺贝利核事故后反应堆被水泥封住，普里皮亚季和切尔诺贝利被称为鬼城，方圆百里是无人区，并提及游戏《使命召唤4》中有切尔诺贝利关卡，涉及车臣叛军和英国SAS特种部队。
+## 要点梳理
+### 哥斯拉系列电影剧情梳理
+1. 哥斯拉首部电影诞生于1954年，至今已有70多年历史，日本和美国翻拍出不同版本。
+2. 哥斯拉起源为海底生物吸食核废料、核废水后变异成庞然大物，对人类世界展开报复和攻击。
+3. 哥斯拉在日本神话中是大自然的守护神，攻击人类是因为人类无限制搞核试验、破坏自然生态。
+4. 《哥斯拉怪兽之王》中反派基多拉是外星生物，哥斯拉与人类携手将其打败。
+5. 《哥斯拉大战金刚》中哥斯拉与金刚因地盘冲突战斗，后联手打败机械基多拉——人类反派势力将基多拉仅存的一个头加装机械装甲复合升级而成。
+6. 2014年美国版哥斯拉电影中，哥斯拉与人类携手团灭以核弹、核废料为能源的雾托物种。
+7. 2016年日本版《新哥斯拉》中，哥斯拉吸收核废料不断升级变大，人类各种武器攻击反而增强其战斗力，最终以无人机投放炸弹耗光能量、再用冷冻剂封印。
+8. 日本版剧情将人类反派做成外星人形象，外星人控制基多拉和其他怪兽，哥斯拉因基因不同反杀外星人控制的怪兽、解放地球。
+9. 哥斯拉与奥特曼导演同为圆谷英二，但属于不同时间线——哥斯拉是地球本土物种，奥特曼来自奥特之星，两者均为正面形象，未直接战斗。
+10. 哥斯拉系列电影包括《哥斯拉大战人类》《哥斯拉大战机械哥斯拉》《哥斯拉大战基多拉》《哥斯拉最后的战斗》《新哥斯拉》《哥斯拉怪兽之王》《哥斯拉大战金刚》等。
+### 核废水排放与核事故现实讨论
+1. 发言人1认为只要日本不停止排放核废水，哥斯拉这类题材电影就不会停。
+2. 发言人2提到在日本留学期间，因日本开始排放核废水，购买的是中国进口到日本的鱼。
+3. 发言人1指出日本国产产品因「迷之民族自信」价格昂贵，进口虾鱼相对便宜。
+4. 发言人1提到切尔诺贝利核事故后反应堆被水泥封住，普里皮亚季和切尔诺贝利被称为鬼城，方圆百里是无人区，认为日本核废水排放比切尔诺贝利更不负责任。
+5. 发言人1提及游戏《使命召唤4》中有切尔诺贝利关卡，涉及车臣叛军挖核废料、英国SAS特种部队狙杀未成功的情节。
+6. 发言人1表示核废水对身体的损耗尚无明确说法，目前未见变异案例，但存在各种白血病等病变。</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>32.6</v>
+        <v>30.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5319/2062</t>
+          <t>5319/1809</t>
         </is>
       </c>
     </row>
@@ -14495,60 +14576,61 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t># 讨论议题与背景
-本次会议为6位发言人（发言人1至发言人6）围绕“18岁以前的深刻印象和记忆”展开的分享型讨论，由发言人1发起，引导大家回忆逃课、网吧游戏、追星、乐队等经历。议题范围涵盖：18岁前的逃课与走读生活、流行游戏（穿越火线、CS online、求生之路、仙剑、魔兽争霸等）、小说漫画与杂志（郭敬明小说、柯南、老夫子、意林等）、游戏暴力内容与年龄限制、求生之路剧情与现实关联、恐怖游戏与电影、游戏与电影先后关系、塔防游戏及使命召唤。讨论以分享观点为主，未形成统一结论，整体呈漫谈发散式推进，由发言人1不断抛出新话题引导，各发言人穿插分享个人经历与看法。关键锚点包括：穿越火线为08年游戏、求生之路第二部需18岁以上注册Steam账号、2020年新冠疫情后求生之路重新火爆。
-# 发言要点
-## 18岁前记忆分享
-- **发言人1**：初中走读，每周一下午4点放学后去游戏厅网吧，流行穿越火线（CF）、反恐精英online（CS online）等游戏；高中因高考压力不敢逃课，转而追星、搞乐队，偏好朋克金属音乐。
-- **发言人2**：18岁前未逃过课，大学逃过一次；喜欢看漫画，提及意林、读者、故事会等杂志。
-- **发言人5**：喜欢郭敬明的小说，提到萌化三国。
-- **发言人4**：班里流行看柯南和老夫子。
-## 电脑游戏与单机游戏回忆
-- **发言人4**：提到摩尔庄园、赛尔号。
-- **发言人2**：提到穿越火线、地下城与勇士；玩过魔兽争霸，区分其与魔兽世界（单机vs网游）。
-- **发言人5**：玩过仙剑四。
-- **发言人1**：单机最流行求生之路，联机局域玩。
-- **发言人4**：认为仙剑三最火，且有电视剧。
-## 第一人称射击游戏与暴力内容讨论
-- **发言人1**：因在贴吧和QQ空间写文章骂穿越火线被平台封禁，后成为CS反恐精英铁杆粉，喜欢僵尸模式，被说跳舞姿势像舞体僵尸。
-- **发言人5**：质疑游戏暴力内容无年龄限制，认为同龄人很少玩。
-- **发言人1**：解释求生之路第二部血腥暴力，未成年人不能注册Steam账号（需18岁以上）；穿越火线是08年游戏，国服开时比较血腥。
-## 求生之路游戏剧情与现实关联
-- **发言人1**：讲述求生之路剧情——美国政府默不作声导致病毒失控，军队强力介入但被感染，主角团不信政府自救；认为制作团队精准预测美国政府在新冠疫情中的表现，疫情后游戏重新火爆。
-- **发言人1**：解释求生之路中的敌人是病毒感染者，主角团是无症状感染者。
-- **发言人2**：提到欧美玩家爱玩打僵尸游戏，模式一上线欧洲玩家疯狂在线。
-## 恐怖游戏与电影讨论
-- **发言人1**：提到生化危机也是病毒泄露、政府反应迟钝导致失控，生化三用核武器夷平城市。
-- **发言人2**：认为生化危机游戏恐怖，不敢玩。
-- **发言人5**：分享过年与表姐表弟看恐怖片，大家都跑了。
-- **发言人6**：提到表哥每年过年放恐怖片。
-## 游戏与电影先后关系及变形金刚
-- **发言人1**：认为生化危机先有游戏后有电影；求生之路是在惊变48小时和生化危机基础上，先有电影后有游戏。
-- **发言人1**：认为变形金刚先有玩具，后有MV和电影，并认为其有点抄袭日本题材，电影有翻拍盗版感觉。
-## 塔防游戏与使命召唤讨论
-- **发言人3**：经常玩塔防游戏，如植物大战僵尸、Kindle rush。
-- **发言人2**：提到植物大战僵尸有变态版，后期满屏子弹导致电脑卡顿；认为使命召唤等游戏太男性化。
-- **发言人1**：介绍使命召唤黑色行动基于冷战时期美苏真实历史，现代战争虚构，后期剧情高估俄罗斯。
-# 共识形成
-- **一致意见**：与会者普遍认同18岁前的记忆以游戏、漫画、小说等娱乐活动为主，且对**穿越火线（CF）、反恐精英（CS）、求生之路、生化危机**等游戏有共同记忆；多数人认为这些游戏存在暴力内容，且**未成年人不能注册Steam账号（需18岁以上）**是普遍认知。
-- **倾向性认识**：发言人1认为求生之路制作团队精准预测了美国政府在新冠疫情中的表现，导致疫情后游戏重新火爆；发言人2补充欧美玩家热衷打僵尸类游戏，欧洲年轻人都在玩；发言人6以「艺术源于生活」表示认同。
-  - **游戏与电影先后关系**：发言人1认为生化危机先有游戏后有电影，求生之路先有电影后有游戏；发言人2对此未明确表态，仅提问「先有游戏还是先有电影」。
-  - **游戏暴力与年龄限制**：发言人5质疑游戏暴力内容无年龄限制，认为同龄人很少玩；发言人1解释求生之路第二部血腥暴力，导致未成年人不能注册Steam账号，并提到穿越火线是08年游戏，国服开时比较血腥。
-  - **游戏评价**：发言人2认为使命召唤等游戏「太男性化」；发言人1介绍使命召唤黑色行动基于冷战时期美苏真实历史，现代战争虚构，后期剧情高估俄罗斯，发言人6认为「感觉都挺歪的」。
-# 待探讨问题与后续
-- **未确认**：发言人2对反恐精英、穿越火线、地下城与勇士等游戏的先后顺序记不清，表示「有点记不清是先后了」。
-- **未确认**：发言人5不确定自己玩过的是《仙剑奇侠传》还是《古剑奇谭》，表述为「我忘记是仙元剑还是古剑四长我也玩过」。
-- **未确认**：发言人2对《求生之路》中最怕的角色表示「我没想玩，我这都忘了，有点忘了」，未给出明确答案。
-- **未定论**：关于《求生之路》主角团的最终结局，发言人1表示「最后反正也不知道怎么样，四生四死我们也不知道」，游戏未给出明确交代。
-- **未定论**：发言人1认为《变形金刚》电影「有点抄袭小日本的当时的一些个题材」，此观点未获其他成员回应或讨论，属单方看法。</t>
+          <t># 18岁前记忆分享与游戏文化讨论
+## 讨论议题与背景
+本次会议为一场围绕18岁前记忆的分享讨论，由主持人发起，共6位成员（发言人1至发言人6）参与，以漫谈回忆的方式展开。讨论由主持人提议分享18岁前印象深刻的事（如逃课、网吧游戏、追星、音乐会等）切入，随后话题自然发散。议题范围涵盖：18岁前的逃课与游戏经历、流行文化（郭敬明小说、柯南、《老夫子》、《意林》等杂志）、电脑与单机游戏（摩尔庄园、穿越火线、求生之路、仙剑四、魔兽争霸等）、第一人称射击游戏的暴力内容与年龄限制、求生之路剧情与现实关联、游戏与电影的先后关系及变形金刚起源、塔防游戏与使命召唤剧情。讨论以分享观点为主，未形成统一结论，整体呈漫谈发散式推进，由主持人引导话题逐块转换，成员间穿插补充与追问。关键锚点包括：发言人1初中走读时每周一下午4点放学后去游戏厅网吧、穿越火线为08年国服上线、求生之路因暴力内容要求18岁以上才能注册Steam账号。
+## 发言要点
+### 18岁前的逃课与游戏经历
+1. **【逃课经历】初中走读放学后去网吧**（发言人1）：初中走读，每周一下午4点放学（因老师、校领导集中学习座谈），大家聚集在游戏厅、网吧，玩穿越火线（CF）、反恐精英online（CS online）、使命召唤、战地、魔兽等游戏。
+  - **观点碰撞**：发言人2表示18岁前没逃过课，大学才逃过一次；发言人3认为逃课是正常现象；发言人4补充上大学不算。
+2. **【高中转变】因高考压力不敢逃课**（发言人1）：高中因高考心理压力不敢逃课，转而追星、搞乐队，玩架子鼓、电吉他、贝斯，追求朋克金属主题音乐。
+### 18岁前的流行文化（小说、漫画、杂志）
+1. **【小说】郭敬明作品**（发言人5）：特别喜欢郭敬明的小说。
+  - **观点碰撞**：发言人2认为郭敬明的小说看着难受、扭曲，提到《梦里花落知多少》。
+2. **【漫画】柯南与老夫子**（发言人4、发言人1）：发言人4提到班里流行看柯南；发言人1补充当时流行看名侦探柯南漫画版和香港漫画《老夫子》，并惊讶发言人5不知道老夫子。
+3. **【杂志】意林、读者、故事会**（发言人2）：当时看《意林》《读者》《故事会》等杂志，觉得《意林》讲得好，但现在内容反转了。
+### 18岁前的电脑游戏与单机游戏
+1. **【网页游戏】摩尔庄园、赛尔号**（发言人4）：小学和初中玩摩尔庄园、赛尔号。
+2. **【网游】穿越火线、地下城与勇士**（发言人2）：初中玩穿越火线、地下城与勇士，但记不清先后顺序。
+3. **【单机游戏】求生之路、仙剑系列**（发言人1、发言人5）：发言人1提到单机最流行求生之路，可联机局域玩；发言人5玩过仙剑四，还玩过仙辕剑或古剑四（记不清具体是哪个）。
+4. **【魔兽】魔兽争霸与魔兽世界**（发言人2）：初中玩魔兽争霸（单机），区别于魔兽世界（网游）。
+5. **【MOBA】英雄联盟与DOTA的鄙视链**（发言人5、发言人2）：英雄联盟和DOTA存在鄙视链，发言人2认为王者荣耀处于鄙视链最底端。
+### 第一人称射击游戏与暴力内容
+1. **【穿越火线】被封禁后转投CS**（发言人1）：因在贴吧和QQ空间写文章骂穿越火线抄袭，被穿越火线平台封禁，后成为CS反恐精英铁杆热衷粉，最喜欢僵尸模式；学校舞蹈队说他跳舞姿势像舞体僵尸。
+2. **【求生之路】暴力内容与年龄限制**（发言人1）：求生之路第二部可拿东洋刀、电锯、砍刀砍丧尸群，能把脑袋和四肢砍飞、血喷一脸，很暴力；因此未成年人不能注册Steam账号，需18岁以上才能玩。
+  - **观点碰撞**：发言人5质疑暴力游戏对小孩的影响，认为同龄人很少玩这类游戏，感觉是姑父、叔叔那辈人玩的。
+3. **【CS版本】1.5与1.6**（发言人1、发言人4）：发言人1询问更喜欢CS 1.5还是1.6的皮肤，发言人4表示现在看穿越火线像像素游戏。
+### 求生之路的剧情与现实关联
+1. **【剧情预测】美国政府表现**（发言人1）：求生之路制作团队精准预测了美国政府在面对大灾难时的表现——一开始对病毒传播默不作声，导致国家失控，军队强力介入以暴力清理方式处理（不管是否感染一律枪毙），结果军队也被感染失控；主角团不相信政府承诺，自己拿起枪自救，去荒岛开辟新住处，游戏名称由此而来。
+  - **支撑论据**：2020年新冠疫情爆发后，美国政府的表现与游戏预测一致，疫情之后全世界重新玩起这个游戏。
+2. **【玩家反应】欧美玩家热衷打僵尸**（发言人2）：打僵尸游戏模式一上线，欧洲玩家就疯狂在线，整个欧洲年轻人都在打僵尸。
+3. **【相关游戏】最后生还者**（发言人6）：最近看视频介绍最后生还者，那游戏挺火；发言人1补充主角团差点被军队物理消灭，后来对军队反杀杀出血路。
+### 游戏与电影的先后关系及变形金刚
+1. **【先后关系】生化危机与求生之路**（发言人1、发言人2）：生化危机是先有游戏后有电影；求生之路是在惊变48小时和生化危机基础上，先有电影后有游戏。
+2. **【变形金刚】先有玩具**（发言人4、发言人1）：发言人4提问变形金刚先有的啥，发言人1认为是先有玩具，后有MV和电影（绿日乐队出过介绍变形金刚的MV）。
+### 塔防游戏与使命召唤
+1. **【塔防游戏】植物大战僵尸**（发言人3、发言人2）：发言人3喜欢玩塔防游戏，如植物大战僵尸和Kindle rush；发言人2提到植物大战僵尸有特别变态的版，后期满屏全是子弹，电脑都卡得扛不住。
+2. **【使命召唤】黑色行动与现代战争**（发言人1）：黑色行动以冷战时期美国和苏联结合真实历史进行明争暗斗的军事秘密行动；现代战争第一部贴合车臣战争、伊拉克战争、海湾战争，但后期美国挑衅俄罗斯、俄罗斯反杀到美国本土、吊打北约的剧情，结合当前俄罗斯军队在乌克兰的表现，有点高估俄罗斯了。
+  - **观点碰撞**：发言人2认为使命召唤这类游戏太男性化；发言人6感觉剧情都挺歪的。
+## 共识形成
+1. **【达成共识】18岁前记忆以游戏与流行文化为主**：全场一致认可18岁前印象最深的记忆集中在网吧游戏、漫画小说与追星乐队等流行文化领域；关键产出为**梳理出穿越火线（CF）、反恐精英online（CS online）、求生之路、生化危机、魔兽争霸、仙剑系列、摩尔庄园、赛尔号、植物大战僵尸等代表性游戏**，以及**柯南、老夫子、郭敬明小说、《意林》《读者》《故事会》等流行读物**。
+2. **【核心分歧/待定取舍】游戏暴力内容与年龄限制的争议**：发言人5质疑求生之路等游戏暴力血腥、同龄人很少玩，认为小孩不宜接触；发言人1则解释求生之路因暴力内容已设置年龄限制（未成年人不能注册Steam账号，需18岁以上），并认为游戏制作团队精准预测了美国政府在疫情中的表现。另一分歧点为游戏与电影的先后关系：发言人1指出生化危机先有游戏后有电影、求生之路先有电影后有游戏，发言人4则提问变形金刚的起源，发言人1认为是先有玩具后有MV和电影，未形成统一意见。
+## 待探讨问题与后续
+1. **未确认：游戏与电影先后关系的判断依据**：发言人1指出生化危机先有游戏后有电影、求生之路先有电影后有游戏、变形金刚先有玩具后有MV和电影，但未给出具体时间线或出处，该判断有待核实。
+2. **未定论：求生之路剧情与美国政府疫情表现的关联性**：发言人1认为游戏制作团队精准预测了美国政府在新冠疫情中的表现，并称疫情后游戏重新火爆，但未提供数据支撑，该观点属个人解读。
+3. **未确认：游戏年龄限制的实际执行情况**：发言人1称求生之路因暴力内容要求18岁以上才能注册Steam账号，发言人5质疑暴力游戏对小孩的影响，但未讨论限制措施的实际落地效果。
+4. **未定论：使命召唤现代战争剧情对俄罗斯军力的评价**：发言人1认为后期剧情高估俄罗斯，结合当前俄乌冲突表现，但未展开论证，属个人看法。
+5. **未确认：植物大战僵尸变态版的来源与版本**：发言人2提到后期满屏子弹导致电脑卡顿，但未说明具体版本或获取渠道。
+6. **未确认：魔兽争霸与魔兽世界的区别说明**：发言人2指出一个是单机一个是网游，但未深入解释两者关系，话题被搁置。
+7. **未定论：英雄联盟与DOTA的鄙视链**：发言人5提出存在鄙视链，发言人2补充王者荣耀处于最底端，但未讨论该现象的形成原因或影响。</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>49.4</v>
+        <v>64.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6453/2395</t>
+          <t>6453/3493</t>
         </is>
       </c>
     </row>
@@ -14822,59 +14904,78 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t># 讨论议题与背景
-本次为四人（发言人1至发言人4）围绕古典小说的闲谈式讨论，无明确会议目的与正式议程。讨论由发言人2提议继续此前未说完的《红楼梦》话题而起，随后在《红楼梦》《金瓶梅》《水浒传》《西游记》等作品间自然流转。议题范围包括：《红楼梦》的官场暗线与四大家族兴衰、护官符诗句、薛宝钗结局版本差异、吃螃蟹与冷香丸等细节描写；《金瓶梅》与《水浒传》的关联、武松报仇线差异、西门庆结局及妻妾群像；《西游记》中佛教虚伪的体现；以及《红楼梦》是否映射曹雪芹个人经历、有无明确朝代等历史背景问题。讨论以分享观点为主，未形成统一结论，整体呈漫谈发散式推进，各议题间无明确边界，由发言者自由接续。讨论中提及护官符「丰年好大雪，珍珠如土金如铁」、冷香丸需雨水日雨水与各节气花蕊、如来佛祖「区区收了300两黄金」等具体细节作为锚点。
-# 发言要点
-## 《红楼梦》讨论
-- **发言人3**：提出《红楼梦》存在官场暗线，四大家族兴衰与朝堂变化相关，如王熙凤前期地位高、结局惨，与其兄长的官场地位及先死相关。
-- **发言人4**：质疑四大家族人物稀少，每家仅两三人，如王家、史家、薛家，只知典型人物，感觉没什么厉害人家。
-- **发言人1**：背诵护官符诗句——「贾不假，白玉为堂金作马；阿房宫三百里，住不下金陵一个史；东海缺少白玉床，龙王来请金陵王；丰年好大雪，珍珠如土金如铁」。
-- **发言人3**：指出四大家族整体走在下坡路，对应王朝家族的衰败。
-- **发言人4**：提到《红楼梦》中江南吃螃蟹非常讲究，需卸钱卸身等工具，小时候看没看明白但对此印象深刻。
-- **发言人3**：提到冷香丸需雨水那一日的雨水、小雪那一日的雪，且要正好碰上每个节气，配春天的白牡丹、夏天的白荷花、秋天的白芙蓉、冬天的白梅花。
-- **发言人3**：提到薛宝钗结局版本差异——120回版本中嫁给贾宝玉后为无性婚姻，贾宝玉不久出家；另一版本中她后来怀了孩子。
-- **发言人2**：追问怀的孩子是否为贾宝玉的，发言人3回应那是狗血版本，发言人1认为不至于弄这么狗血。
-- **发言人4**：提到《红楼梦》映射曹雪芹经历，作者以前是大家族出身，否则写不出吃螃蟹技巧、冷香丸等细节。
-- **发言人3**：指出《红楼梦》没有明确朝代，是写得很虚的虚构故事，映射作者时代；发言人1补充当时已是禁书，更不敢写明朝代。
-## 《金瓶梅》与《水浒传》讨论
-- **发言人1**：指出《金瓶梅》中武松报仇未成功，因西门庆被高官权势压制；与水浒传不同，西门庆在楼上喝茶时得仆人报信翻窗逃脱，武松后被发配，故事转向西门庆线。
-- **发言人3**：认为《金瓶梅》是西门庆这个小人物的发展史，不涉及《水浒传》起义章节；西门庆这样一个无赖能爬到较高位置且过得舒服，体现官场黑暗。
-- **发言人2**：询问西门庆与宋江等人有无交集，发言人3回应应该不会写，但丞相是同一个丞相。
-- **发言人2**：询问西门庆结局在两个版本中的差异，发言人3提到金瓶梅版本中西门庆最终过度而死，而非水浒中被武松砍头。
-- **发言人3**：提到西门庆有十个老婆，有的老婆特别懦弱，潘金莲属于很有心机、比较强势的类型。
-- **发言人3**：提到西门庆一个老婆生病后去看和尚、不信治病，因迷信而死；书中佛教也很黑，收灯油钱。
-- **发言人4**：提到金瓶梅里吃的也写得好，西门庆摆宴的饮食描写细致。
-- **发言人2**：将金瓶梅中潘金莲的心机与孙权二宫之争中王夫人、孙鲁班搅乱东吴政局作类比，询问大家对二宫之争的了解。
-## 《西游记》及其他讨论
-- **发言人1**：提到《西游记》中如来佛祖说「区区收了300两黄金」，体现佛教虚伪。
-- **发言人2**：补充《西游记》佛教虚伪情节——狮驼岭，以及寺院住持觊觎唐僧袈裟、引火自焚。
-- **发言人4**：提到黑神话游戏中也有相关boss，发言人1补充金齿蟑螂。
-- **发言人2**：询问《红楼梦》是否有真实历史事件，发言人3回应开头即虚构，与三国、水浒有明确历史人物和时间线不同。
-- **发言人4**：提到《红楼梦》很明显映射当时时代，也有说法认为演的是曹雪芹本人经历。
-# 共识形成
-- **一致意见**：与会者普遍认可《红楼梦》中存在官场暗线，四大家族兴衰与朝堂变化相关，如王熙凤地位与其兄长官场地位相关；同时一致认为四大家族整体走在下坡路，对应王朝衰败。
-- **倾向性认识**：多数发言倾向认为《金瓶梅》是西门庆这个小人物的发展史，不涉及《水浒传》起义章节；武松报仇线在《金瓶梅》中被高官权势压制，与《水浒传》结局不同。
-- **主要分歧点**：发言人3与发言人4对四大家族人物数量存在分歧——发言人4质疑四大家族人物稀少，每家仅两三人，发言人3认为可能是未细读书中人物所致；发言人3与发言人1对薛宝钗结局版本存在分歧——发言人3提到120回版本中薛宝钗嫁给贾宝玉后无性婚姻，贾宝玉出家，另一版本中她怀了孩子，发言人1认为该版本过于狗血。
-- **结论口径**：发言人3指出《红楼梦》没有明确朝代，是虚构故事，映射作者时代；发言人4提到《红楼梦》映射曹雪芹经历，作者是大家族出身，否则写不出吃螃蟹技巧、冷香丸等细节。
-# 待探讨问题与后续
-- **未确认**：《红楼梦》中四大家族是否真的只有少数人物，发言人4质疑每家仅两三人，发言人3回应称可能是没看书、书里人挺多，但未进一步核实。
-- **未确认**：《金瓶梅》中西门庆的结局在不同版本中是否一致，发言人3提到金瓶梅版本中西门庆最终过度而死，而非《水浒传》中被武松砍头，但未查阅确认。
-- **未确认**：《红楼梦》是否映射曹雪芹个人经历，发言人4提到有这种说法，发言人3认为作者若非大家族出身写不出那么多细节，但未定论。
-- **待核实**：《西游记》中如来佛祖收300两黄金的情节出自哪一章节，发言人1称「好像是最后一集」，但记不清具体出处。
-- **未定论**：《红楼梦》中薛宝钗在贾宝玉出家后是否怀有孩子，发言人3提到120回版本与另一版本说法不同，发言人1认为「不至于弄这么狗血」，未达成一致。
-- **待核实**：《金瓶梅》中西门庆是否与宋江等水浒人物有交集，发言人2提问，发言人3称「应该不会写」，但未确认。
-- **未确认**：《金瓶梅》中西门庆一个老婆因迷信和尚而病死、佛教收灯油钱的情节，发言人3提及但发言人4表示「细节记不清」。
-- **未确认**：《西游记》中寺院住持觊觎袈裟引火自焚的情节，发言人2提及但称「记不清了」，发言人3表示可能看的是电视剧。
-- **未定论**：《金瓶梅》中潘金莲是否属于西门庆十个老婆中最有心机、最强势者，发言人3称「印象中是这样」，但未进一步核实。
-- **未确认**：孙权二宫之争中王夫人与孙鲁班搅乱东吴政局的说法，发言人2提出后询问大家了解程度，无人回应，话题随即被终止。</t>
+          <t># 古典小说闲聊讨论会
+## 讨论议题与背景
+本次会议为四人（发言人1、发言人2、发言人3、发言人4）围绕《红楼梦》《金瓶梅》《水浒传》《西游记》等古典小说的闲聊式讨论，由发言人1提议继续此前未说完的《红楼梦》话题开场。讨论议题包括：《红楼梦》的官场暗线与四大家族兴衰、护官符诗句、薛宝钗结局版本差异、吃螃蟹与冷香丸等细节描写；《金瓶梅》与《水浒传》的武松报仇线差异、西门庆的小人物发展史及其结局；《西游记》中佛教虚伪的情节；以及《红楼梦》有无明确朝代、是否映射曹雪芹经历等历史背景问题。讨论以分享观点为主，未形成统一结论，整体呈漫谈发散式推进，各议题间自然流转，穿插成员间的提问与补充。
+## 发言要点
+### 《红楼梦》讨论
+1. **【官场暗线】四大家族兴衰与朝堂变化相关**（发言人：发言人3）
+   - **核心主张**：《红楼梦》存在一条官场暗线，四大家族兴衰与朝堂变化相关。
+   - **支撑论据/案例**：王熙凤前期地位高、后期结局惨，与其兄长在官场上的地位相关，兄长先死导致其失势。
+   - **观点碰撞/互动**：发言人4质疑四大家族人物稀少，每家仅两三人，只知典型人物；发言人3回应薛宝钗家为经商有钱，发言人1补充护官符诗句佐证四大家族声势。
+2. **【护官符诗句】四大家族声势描述**（发言人：发言人1）
+   - **核心主张**：护官符诗句概括四大家族权势。
+   - **支撑论据/案例**：贾不假，白玉为堂金作马；阿房宫三百里，住不下金陵一个史；东海缺少白玉床，龙王来请金陵王；丰年好大雪，珍珠如土金如铁。
+   - **观点碰撞/互动**：发言人4认为四大家族「说都很牛逼，就感觉没什么厉害人家」，发言人3回应「他们整体都在走一个下坡路」，发言人1认同「说的就是王朝家族的衰败」。
+3. **【薛宝钗结局】版本差异与争议**（发言人：发言人3）
+   - **核心主张**：薛宝钗嫁给贾宝玉后，贾宝玉不久出家，有版本称薛宝钗后来怀孕。
+   - **观点碰撞/互动**：发言人2追问「那是贾宝玉的还是」，发言人3回应「那肯定是狗血版本」，发言人1认同「这个应该不至于弄这么狗血」。
+4. **【生活细节】吃螃蟹与冷香丸的讲究**（发言人：发言人4、发言人3）
+   - **核心主张**：《红楼梦》生活细节描写丰富，体现作者阅历。
+   - **支撑论据/案例**：发言人4提到吃螃蟹需卸钳卸身等工具，第一次听说吃螃蟹需这么多工具；发言人3提到冷香丸需雨水日的雨水、小雪日的雪，与每个节气正好碰上，发言人1补充需春天的白牡丹、夏天的白荷花、秋天的白芙蓉、冬天的白梅花。
+   - **观点碰撞/互动**：发言人4认为「写不出都吃螃蟹的技巧」，佐证作者为大家族出身。
+5. **【历史背景】朝代模糊与映射曹雪芹经历**（发言人：发言人3、发言人4）
+   - **核心主张**：《红楼梦》没有明确朝代，是虚构故事，但映射作者所处时代。
+   - **支撑论据/案例**：发言人4提到有说法称《红楼梦》演的是曹雪芹经历，其以前是大家族；发言人3回应「要不然他写不出来那那么多的细节」。
+   - **观点碰撞/互动**：发言人2询问《红楼梦》历史上是否有真实事件对应，发言人3回应「开头他就是说，他就是那个湖边漫步」，发言人1补充「红楼梦当时不是禁书吗？都已经不说朝代已经是禁书了，那说朝代更禁」。
+### 《金瓶梅》与《水浒传》讨论
+1. **【武松报仇线】金瓶梅与水浒传的差异**（发言人：发言人1）
+   - **核心主张**：《金瓶梅》中武松报仇未成，与《水浒传》直接砍头不同。
+   - **支撑论据/案例**：武松找西门庆时，西门庆在楼上喝茶，得仆人报信后从楼上翻下逃脱，武松后被发配，之后开始讲西门庆的线。
+   - **观点碰撞/互动**：发言人4追问「他最后死是因为啊重病昏过去了」，发言人1回应「就是被这种高官还有大家族，对，就权势给摁压下来」，发言人2总结「就是西门庆霸凌武大郎」。
+2. **【西门庆结局】纵欲过度而死**（发言人：发言人3）
+   - **核心主张**：《金瓶梅》中西门庆最终纵欲过度而死。
+   - **观点碰撞/互动**：发言人2询问西门庆在水浒与金瓶梅两个版本中的结局，发言人3回应「不是说这个版本里面新闻是终于过度死」，发言人2确认「在金庸没的版本是吧」。
+3. **【西门庆与宋江交集】未确认**（发言人：发言人2、发言人1、发言人3）
+   - **核心主张**：西门庆与宋江是否有交集未确认。
+   - **支撑论据/案例**：发言人1表示「理亏不知道了」，发言人3认为「应该应该不会写。他们他他那个丞相是同一个丞相」，发言人4提到西门庆「跟这个中央这个攀上线，老老厉害了」。
+4. **【西门庆妻妾】潘金莲有心机**（发言人：发言人3）
+   - **核心主张**：西门庆有十个老婆，潘金莲属于有心机的一类。
+   - **支撑论据/案例**：西门庆有的老婆特别懦弱，潘金莲属于很有心机那一种，比较强势。
+   - **观点碰撞/互动**：发言人4追问潘金莲是否杀死武大郎，发言人3未直接回应，转而提到西门庆有一个老婆因迷信看和尚、不去治病而死。
+5. **【金瓶梅定位】小人物发展史**（发言人：发言人3）
+   - **核心主张**：《金瓶梅》是西门庆这个小人物的发展史。
+   - **支撑论据/案例**：西门庆这样一个无赖能爬到比较高、过得比较舒服，体现官场黑暗。
+   - **观点碰撞/互动**：发言人2询问金瓶梅是否讲水浒中起义章节，发言人3回应「没有，他就是从这个人物，西门庆，他这个算是一个小人物，他的一个发展史」。
+### 《西游记》及其他
+1. **【佛教虚伪】如来收黄金与寺院住持自焚**（发言人：发言人1、发言人2）
+   - **核心主张**：《西游记》体现佛教虚伪。
+   - **支撑论据/案例**：发言人1提到如来佛祖说「区区收了300两黄金」；发言人2提到寺院住持觊觎唐僧袈裟，引火自焚。
+   - **观点碰撞/互动**：发言人2追问「那是哪一集啊」，发言人1回应「忘了忘了，好像是最后一集吧」。
+2. **【朝代对比】红楼梦与金瓶梅水浒的朝代差异**（发言人：发言人2、发言人3、发言人4）
+   - **核心主张**：金瓶梅与水浒是北宋时期，红楼梦是明末清初、无明确朝代。
+   - **支撑论据/案例**：发言人4提到红楼梦是明清的、明末清初，与郑成功同时代；发言人3回应「红楼梦其实没有明确的朝代。它就是一个写的很虚的一个故事」。
+   - **观点碰撞/互动**：发言人2询问红楼梦历史上是否有真实事件对应，发言人3回应无明确朝代，发言人4补充「作者是那个时代的，他就是映射那个时代」。
+## 共识形成
+1. **【达成共识】《红楼梦》存在官场暗线**：发言人3提出《红楼梦》有一条官场暗线，四大家族兴衰与朝堂变化相关，如王熙凤地位与其兄长在官场的地位相关，其结局悲惨也因兄长先死；发言人1补充护官符诗句印证四大家族（贾、史、王、薛）的权势描述，**护官符诗句**被全场引用确认。
+2. **【核心分歧/待定取舍】《红楼梦》薛宝钗结局版本**：发言人3提到120回版本中薛宝钗嫁给贾宝玉后，贾宝玉不久出家，有版本称薛宝钗后来怀孕；发言人1认为这是狗血版本，发言人2质疑孩子是否为贾宝玉的，发言人3回应那是狗血版本，未达成一致。另**《金瓶梅》与《水浒传》武松报仇线差异**：发言人1讲述《金瓶梅》中武松报仇未成、西门庆从楼上翻下逃脱、武松被发配，与《水浒传》中直接砍头不同，发言人3认为《金瓶梅》是西门庆这个小人物的发展史，西门庆最终纵欲过度而死，此差异被全场认可。
+## 待探讨问题与后续
+1. **未确认：《金瓶梅》中西门庆与宋江是否有交集**：发言人2提出疑问，发言人1表示不清楚，发言人3认为应该不会写，但提到丞相是同一个。
+2. **待核实：《金瓶梅》中潘金莲是否杀死武大郎**：发言人4询问潘金莲是否杀死武大郎，发言人3未直接确认，仅提及潘金莲属于有心机的一类。
+3. **未定论：《红楼梦》中薛宝钗是否怀孕**：发言人3提到有版本称薛宝钗嫁给贾宝玉后怀孕，但发言人1认为是狗血版本，未达成一致。
+4. **未确认：《金瓶梅》中武松报仇线细节**：发言人1讲述武松报仇未成、西门庆从楼上翻下逃脱、武松被发配，但发言人4对西门庆最终死因（重病昏过去）与发言人3（纵欲过度而死）说法不一致。
+5. **待核实：《红楼梦》四大家族人物稀少问题**：发言人4质疑四大家族每家仅两三人，发言人3回应薛宝钗家为经商有钱，但未深入核实书中人物数量。
+6. **未确认：《西游记》如来佛祖收300两黄金的章节**：发言人1提到该情节，但表示忘了具体是哪一集，发言人2询问后未获明确答复。
+7. **待核实：《红楼梦》是否映射曹雪芹经历**：发言人4提到有说法称《红楼梦》映射曹雪芹经历，作者为大家族出身，发言人3表示否则写不出细节，但未进一步考证。
+8. **未确认：《金瓶梅》中潘金莲是否强势**：发言人3认为潘金莲属于有心机的一类，发言人4表示认同，但未深入讨论其具体行为。</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>45.8</v>
+        <v>50.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>5893/2850</t>
+          <t>5893/3827</t>
         </is>
       </c>
     </row>
@@ -15160,45 +15261,41 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t># 全文摘要
-本次录音为多人闲聊，参与者共6位发言人，话题从个人阅读习惯、综艺喜好延伸到专业背景与生活琐事。围绕阅读与综艺喜好、专业背景与生活闲聊、日本现代化转型讨论准备三个板块展开：发言人1反复阅读《红楼梦》，发言人2和4表示不怎么看小说、更常刷短剧和综艺；发言人1介绍综艺《种地吧》，提到节目有十个男孩子，录制周期约半年、几乎24小时录制，成员成立农业公司并种植小月季和水培蔬菜，有收益但有的项目亏钱、有的盈利，成员是实际股东但个人主要收益来自综艺；专业背景方面，发言人2是俄语专业但未从事相关工作，发言人1学数学后学统计，发言人4学软件工程；录音后半段，发言人6提议讨论日本的现代化转型，涉及明治维新与和平宪法，发言人5表示不太懂但准备进行录音。以分享为主，未形成明确结论。
-# 分段速览
-## 00:00:02-00:05:32 阅读习惯与综艺讨论
-开场闲聊从阅读习惯切入，发言人1提到自己反复阅读《红楼梦》，高中时开始读，最初不太懂，反复读后发现有意思；发言人2和4表示不怎么看小说，更常刷短剧和综艺。随后话题转向综艺喜好，发言人1介绍《种地吧》节目，提到节目有十个男孩子，大部分搞音乐，后来组成组合并开演唱会；录制周期约半年，几乎24小时录制，视频素材多。发言人1还提到英国综艺《克拉克森的农场》。
-## 00:05:32-00:08:15 专业背景交流
-发言人1继续介绍《种地吧》成员成立农业公司、尝试创业的情况，提到种植小月季和水培蔬菜，有收益但有的项目亏钱、有的盈利，成员是实际股东，每人掏钱，但个人主要收益来自综艺。随后话题转向专业背景，发言人2提到自己是俄语专业但就业时未从事相关工作，因长时间不用已遗忘；发言人1之前学数学，后来学统计；发言人4是理科生，学软件工程。
-## 00:08:15-00:10:28 生活闲聊与录音收尾
-发言人1提到三人音色不太像，录音应该容易区分。随后话题转向头发护理，发言人4分享自己换用洗发水的经验，目前囤有三种，感觉头发没那么容易油了；发言人2询问是否有推荐，发言人4表示记不清牌子，答应之后找订单告知。发言人1宣布录音结束，发言人2表示时间过得很快。
-## 00:10:29-00:13:02 日本现代化转型讨论准备
-发言人5接手录音，提到下一个话题是日本现代化转型，涉及明治维新与和平宪法。发言人6提议讨论日本的现代化转型，发言人5表示自己不太懂，但准备进行录音。期间穿插关于录音安排、会议室使用等事务性对话，发言人1去三楼找会议室，讨论涉及八爪鱼、金融等录音安排事项。
-# 要点梳理
-## 阅读与综艺喜好
-- **发言人1**：反复阅读《红楼梦》，高中时开始读，最初不太能读懂，反复读后发现有意思。
-- **发言人2**：不怎么看小说，更常刷短剧，看电视剧和综艺较多。
-- **发言人4**：不怎么看小说，看综艺较多，偏好娱乐类、旅游类、户外类综艺。
-- **《种地吧》**：发言人1看过，节目有十个男孩子，大部分搞音乐，走偶像路线但选择小众路径，后来组成组合并开演唱会。
-- **《种地吧》录制**：录制周期约半年，几乎24小时录制，视频素材多；成员种植小月季和水培蔬菜，有收益，有的项目亏钱、有的盈利。
-- **《种地吧》经营**：成员成立农业公司尝试创业、发展新型农业，是实际股东、每人掏钱，但个人主要收益来自综艺；种月季需请专人看水看土，农业门槛较高。
-- **《克拉克森的农场》**：发言人1提到英国种地题材综艺，认为也挺好看。
-## 专业背景与生活闲聊
-- **发言人2**：俄语专业，就业时未从事俄语相关工作，因五六年不用已遗忘。
-- **发言人2**：提到康鹏曾科普俄罗斯人贸易相关信息，称其生意内部消化较多、对外营销较少，信息不怎么外传。
-- **发言人1**：之前学数学，后来学统计，一直是理科生。
-- **发言人4**：理科生，学软件工程，属工科。
-- **发言人4**：换用洗发水，目前囤有三种轮着用，感觉头发没那么容易油了；称洗发水换着用对头发好一些。
-- **发言人4**：所用洗发水品牌不认识、叫不上名字，答应之后找订单告诉发言人2。
-## 日本现代化转型讨论准备
-- **发言人6**：提议讨论日本的现代化转型，涉及明治维新与和平宪法。
-- **发言人5**：表示自己不太懂日本现代化转型，但准备进行录音。
-- **发言人6**：称发言人5在日本上学，认为该话题是发言人5的主场。</t>
+          <t># 闲聊与日本现代化转型讨论准备
+## 全文摘要
+会议为多人闲聊式交流，共六位发言人参与，前半段围绕个人阅读、观影偏好与专业背景展开，后半段转入日本现代化转型讨论的准备。话题覆盖个人阅读与观影偏好、专业背景与职业、日本现代化转型讨论准备三个板块。发言人1反复阅读《红楼梦》多遍，并介绍《种地吧》综艺：十个男孩组成组合并成立农业公司，录制周期约半年、24小时录制，项目有亏有盈，成员为实际股东；还提及英国综艺《克拉克森的农场》。发言人2和发言人4平时看电视剧和综艺较多。专业背景方面，发言人2为俄语专业但未从事相关工作，发言人1学数学后学统计，发言人4学软件工程。后半段发言人6提出讨论日本现代化转型，涉及明治维新与和平宪法，发言人5表示不熟悉并安排录音事宜，发言人1前往三楼寻找会议室。以分享为主，未形成明确结论。
+## 分段速览
+### 00:00:02-00:06:06 闲聊：阅读与观影偏好
+开场闲聊围绕个人阅读与观影习惯展开。发言人1提到反复阅读《红楼梦》多遍，最初高中时读不太懂，反复读才发现趣味；发言人2与发言人4表示平时看电视剧和综艺较多，烧脑类内容看得少。发言人1介绍《种地吧》综艺：十个男孩因节目组成组合，成立农业公司尝试创业，录制周期约半年、几乎24小时录制，项目有亏有盈，成员为实际股东；还提及英国综艺《克拉克森的农场》。期间穿插讨论种地内容、收益来源及三农主题流行等话题。
+### 00:06:23-00:08:15 专业背景交流
+话题转向专业背景。发言人2为俄语专业，但就业未从事俄语相关工作，因多年不用已逐渐遗忘；提及俄罗斯人做贸易生意内部消化较多、对外营销较少。发言人1学数学、后学统计，一直是理科生；发言人4学软件工程，属工科。发言人1顺带提到其姐也是软件工程专业。
+### 00:08:17-00:10:19 洗发水与发质闲聊
+发言人2称赞发言人3头发多，引发洗发水话题。发言人4表示洗发水换着用、家中囤有三种，称换用后头发不易油；发言人2听说换着用对头发好，询问推荐品牌，发言人4记不清所用牌子，答应稍后找订单告知。
+### 00:10:22-00:13:02 日本现代化转型讨论准备
+发言人5接手安排后续录音事宜，提及中英混播、八爪鱼等录制安排，并协调会议室。发言人6提出讨论日本现代化转型，涉及明治维新与和平宪法；发言人5表示对此话题不熟悉。发言人1前往三楼寻找会议室，发言人6称在日本上学的“彪子”是主场，讨论准备尚在进行中。
+## 要点梳理
+### 个人阅读与观影偏好
+1. 发言人1反复阅读《红楼梦》多遍，高中初读时不太能读懂，反复读后才觉得有意思。
+2. 发言人2和发言人4平时看电视剧和娱乐综艺较多，发言人2表示烧脑类内容读着读着就不想再读。
+3. 发言人1介绍《种地吧》综艺：十个男孩原多走偶像路线，因该综艺组成组合，录制周期约半年、几乎24小时录制，视频素材量很大。
+4. 《种地吧》成员成立农业公司尝试创业，发展新型农业；项目有亏有盈，成员为实际股东、每人掏钱参与。
+5. 《种地吧》种植内容包括小月季和水培蔬菜，月季种植需请专人看水看土，外行人难以操作；另有一个鱼塘但未认真经营。
+6. 发言人1提及英国种地综艺《克拉克森的农场》。
+### 专业背景与职业
+1. 发言人2为俄语专业，就业时未从事俄语相关工作，因五六年未用已逐渐遗忘。
+2. 发言人2提到俄罗斯人贸易相关生意内部消化较多，对外营销较少，相关信息来自康鹏的科普。
+3. 发言人1本科为数学，后学统计；发言人4为软件工程专业，属工科。
+### 日本现代化转型讨论准备
+1. 发言人6提出讨论日本现代化转型，涉及明治维新与和平宪法。
+2. 发言人5表示对日本现代化转型话题不熟悉，并安排录音事宜；发言人1前往三楼寻找会议室。</t>
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>29.6</v>
+        <v>26.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5310/1845</t>
+          <t>5310/1579</t>
         </is>
       </c>
     </row>
@@ -15354,94 +15451,115 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t># 讲座概况
-本次研讨会由主讲人系统讲解朝鲜半岛从分裂到统一再到分裂的历史脉络，重点围绕朝鲜战争的爆发背景、主要进程、各方称谓及战后影响展开，并面向听众解答朝韩现状、旅游、军队战斗力、中美关系等延伸问题。讲座覆盖朝鲜战争背景与进程、战争影响与意义、朝韩现状与旅游、朝韩分裂原因与统一展望、朝鲜战争中的韩军表现、抗美援朝决策与中美关系、当前朝韩关系与大国博弈等板块。核心判断包括：朝鲜战争奠定中国强国地位，美国不敢再小瞧中国；朝韩分裂源于美苏冷战建立缓冲区，若统一大概率韩国兼并朝鲜，但北方有核武器和导弹，对东北亚是不稳定因素；韩军1952年前战斗力弱，之后不可小视。关键锚点：1950年6月北朝鲜军队越过三八线、1950年10月19日志愿军跨过鸭绿江、1953年7月27日停战协定。对听众而言，讲座有助于理解朝鲜半岛历史渊源及当前朝韩对立的深层逻辑。
-# 核心观点与论证
-## 朝鲜战争爆发背景与进程
-- **三八线形成**：1945年日本投降后，美苏军队以北纬38度为基准分别进驻朝鲜南北，形成三八线；此前朝鲜半岛经历高丽、百济与新罗从分裂到统一，二战后再次分裂。
-- **苏联鼓动朝鲜进攻**：1949年新中国宣布废除列强在华一切租界及特权，包括苏联在东北的中长铁路及大连旅顺特区，苏联不甘心，鼓动朝鲜进攻韩国，希望以仁川或釜山代替旅顺大连地位，继续在亚洲发挥影响力。
-- **战争爆发与各方称谓**：1950年6月北朝鲜军队率先越过三八线南攻，朝鲜战争爆发；朝鲜称“祖国统一解放战争”，中国称“抗美援朝”，韩国称“625事件”，美国及西方国家称“朝鲜战争”或“韩战”（台湾地区称谓）。
-- **仁川登陆与战局逆转**：朝鲜人民军初期从三八线打到洛东江环形防御圈（大邱至釜山一带）；1950年9月15日美军仁川登陆成功，将深入韩国境内的朝鲜人民军分割包围、逐次歼灭，收复三八线以南领土。
-- **中国出兵与主要战役**：美军以联合国军身份参战（16国共同出兵），总司令麦克阿瑟欲吞并整个北朝鲜，中国以“唇亡齿寒”为由决定以志愿军形式出兵；1950年10月19日跨过鸭绿江，10月25日与韩军首次交火，11月5日第一次战役结束；第二次战役为长津湖战役，第三次战役越过三八线占领汉城（今首尔）、仁川、水原，推进至三七线。
-- **停战协定与今日边界**：第五次战役（最后一次大规模战役）后双方在三八线互有攻防；西部中朝方面占领开城、延安半岛和瓮津半岛，东部美军占领襄阳地区和金刚山地区；1953年7月27日双方达成停战协定，朝韩仅名义停战，未实现真正和平。
-## 朝鲜战争的影响与意义
-- **奠定中国强国地位**：朝鲜战争从中国角度奠定强国地位，美国再不敢小瞧中国；1967年越南战争时期，中国警告美国不得越过北纬十七度线（南越北越边境线），否则中国必将出兵越南，美国未敢越线。
-- **美国“被遗忘的战争”**：美国称朝鲜战争为“被遗忘的战争”；联合国军最后一任司令官马克·克拉克承认，他是美国历史上第一次在未取得胜利的情况下签署停战协议的司令官。
-- **对朝韩伤害最深**：朝鲜和韩国本是一脉相承的血肉同胞，却分裂成两个国家，三八线悲剧延续至今。
-## 朝韩分裂原因与统一展望
-- **美苏冷战布局**：美国在分出三八线以南领土单独建立韩国，是为保护日本免遭苏联及共产主义势力影响，形成缓冲区；苏联也需要在亚洲建立卫星附属国，故扶植北朝鲜独立建国，奉行对苏联马首是瞻的政策。
-- **统一民选政府设想落空**：最初设想在不同占领区受降后，像奥地利那样形成普选、建立统一民选政府；但美苏关系恶化急转直下，所扶植领导人各有心思，意识形态不同最终建立两个国家，成为朝鲜战争爆发缘由。
-- **统一大概率韩国兼并朝鲜**：若朝韩统一，大概率是韩国兼并朝鲜，因经济影响和综合实力摆在那儿；但北方有充足优质兵源及核武器、导弹等尖端武器，统一后对东北亚地区都是不稳定的定时炸弹。
-- **越南统一类比**：越南统一时宣布继承法国在中南半岛所有地盘和疆域，统一第二年进攻柬埔寨和泰国，被中国1979年出兵发动自卫反击战；越南尚且如此，朝鲜半岛统一后局势更加不可控。
-## 韩军战斗力评价
-- **1952年前战斗力弱**：战争初期韩军瞎指挥，差点被朝鲜团灭；6月25日战争爆发后，从7月10日起朝鲜南部地面战斗主要由美军和朝鲜人民军进行，韩军一开始只负责“冲人头”角色。
-- **1952年后形成战斗力**：1952年之后美国重新整军训练韩军，韩军才形成基本战斗力；此前对美军来说类似“猪队友”，志愿军与美军占不到便宜时都从韩军战线突击，美军每次兵败都由韩军战线崩溃引起。
-- **第五次战役韩军崩溃**：第五次战役（朝鲜战争最大运动战）中，志愿军从朝鲜半岛东部韩军战线形成反包围突击，打崩整个韩军前线，美国在韩国领土上撤销了韩国第三军团。
-- **韩军体制渊源**：韩军军官主体是二战时期日本扶植的伪军和傀儡部队骨干，士兵类似国民党时期抓壮丁形式强征农村青年；从成军至今贯彻昭和日军武士道精神管理体制，关西兵、老兵欺负新兵，军队霸凌事件延续至今，是充满昭和军国主义思想余孽的旧日军部队延伸。
-## 抗美援朝决策与中美关系
-- **海军实力不足无法解放台湾**：台湾与大陆间海峡距离约100公里，当时中共刚建国没有相应海军实力；美国出兵朝鲜半岛同时，海军第七舰队进驻台湾，既防解放军解放台湾，也防国民党反攻大陆。
-- **唇亡齿寒决定出兵**：美军越过三八线向朝鲜及中朝边境进发，触动中国敏感神经，“唇亡齿寒”概念深入人心；即便不愿与美国爆发全面战争，但不得不进行，既然海上无法战斗，就在陆地上争取战略主动。
-- **长津湖与上甘岭**：长津湖和上甘岭两场战役接连让美军惨败，至今是美国人挥之不去的梦魇。
-## 当前朝韩关系与大国博弈
-- **美国忌惮中俄**：美国惧怕朝鲜背后的中国和俄罗斯——朝鲜战争时中国出动志愿军帮朝鲜打回美国，苏联提供空军掩护和武器后勤支持，中苏联手把美国打回三八线以南；故美国未主动进攻朝鲜，也未再次挑起半岛武装冲突。
-- **朝鲜不敢贸然动武**：金家担心江山在贸然发动战争后被颠覆，故也不敢贸然发动战争；当前朝韩对立是微妙平衡，有西方国家在背后支撑。
-- **图们江出海口问题**：中俄朝关系“各怀鬼胎”，图们江出海口问题至今未解决；图们江是俄罗斯和朝鲜界江，国际水域航道可通行，但俄朝建了一座小桥，大船无法通过，俄朝都不希望中国过分强大，不想把出海口让给中国。
-# 金句总结
-&gt; “唇亡齿寒这么一个概念，就是深入人心。”
-- 背景：主讲人解释美军越过三八线进犯中朝边境后，中国决定以志愿军形式出兵朝鲜的原因。
-&gt; “美国再也不敢小瞧我们了。”
-- 背景：主讲人回答朝鲜战争对中国国际地位的影响，指出战争奠定了中国的强国地位。
+          <t># 朝鲜战争历史讲解与问答研讨会
+## 讲座概况
+本次研讨会由主讲人系统讲解朝鲜战争历史，以问答形式展开，面向对朝鲜战争及朝韩关系感兴趣的听众。内容围绕朝鲜战争背景与起因、战争过程与重要战役、战后影响与意义三大板块展开，并延伸至朝鲜旅游现状、朝鲜半岛分裂渊源、当前朝韩关系、中俄朝关系及韩国军队作用等议题。主讲人指出，战争源于美苏冷战对峙及朝鲜半岛分裂状态，1950年6月北朝鲜军队越过三八线南进引发战争，中国以志愿军形式于1950年10月19日跨过鸭绿江参战，历经多次战役后，双方于1953年7月27日达成停战协定，但朝韩仅名义上停战，未实现真正和平。主讲人评价朝鲜战争奠定了中国强国地位，美国在越南战争中未敢越过北纬十七度线；美军最后一任司令官克拉克承认是首位在未取胜情况下签署停战协议的司令官。战争加深了朝鲜半岛分裂，三八线悲剧延续至今。针对听众提问，主讲人分析了当前朝韩关系处于微妙平衡，若朝韩统一大概率是韩国兼并朝鲜，但可能成为东北亚不稳定因素。
+## 核心观点与论证
+### 朝鲜战争爆发源于美苏冷战对峙与半岛分裂
+- **分裂起点**：1945年日本投降后，美苏军队以北纬38度为界分别进驻朝鲜南北，形成三八线。
+- **苏联动机**：1949年新中国宣布废除列强在华特权，包括收回苏联在东北的中长铁路及大连旅顺特权；苏联鼓动朝鲜进攻韩国，希望以仁川或釜山替代旅顺、大连的远东地位。
+- **战争爆发**：1950年6月，北朝鲜军队率先越过三八线南进，朝鲜战争爆发；各方称谓不同——朝鲜称“祖国统一解放战争”，中国称“抗美援朝”，韩国称“625事件”，美西方称“朝鲜战争”或“韩战”。
+### 战争进程与重要战役
+- **初期推进**：朝鲜人民军从三八线一路推进至洛东江环形防御圈（大邱至釜山一带）。
+- **仁川登陆**：1950年9月15日美军仁川登陆成功，将深入韩境的朝鲜人民军分割包围、逐次歼灭，收复三八线以南领土。
+- **中国参战**：美军越过三八线后，中国以志愿军形式出兵，1950年10月19日跨过鸭绿江，10月25日与韩军首次交火，11月5日第一次战役结束。
+- **后续战役**：第二次战役含长津湖战役；第三次战役志愿军越过三八线，占领汉城（今首尔）、仁川、水原，推进至三七线；第五次战役为最后一次大规模战役。
+- **停战协定**：1953年7月27日双方达成停战协定，朝韩仅名义上停战，未实现真正和平；西部中朝方占领开城、延安半岛、望京半岛，东部美军占领襄阳、金刚山地区。
+### 朝鲜战争奠定中国强国地位
+- **国际地位**：战争奠定中国强国地位，美国再不敢小瞧中国；1967年越南战争时期，中国警告美军不得越过北纬十七度线，否则中国必出兵越南，美军未敢越线。
+- **美方评价**：美军最后一任司令官克拉克承认，他是美国历史上第一位在未取得胜利的情况下签署停战协议的司令官；此战在美国被称为“被遗忘的战争”。
+- **半岛悲剧**：朝韩本是血肉同胞却分裂为两国，三八线悲剧延续至今。
+### 朝鲜半岛分裂源于美苏各自建立缓冲区
+- **美国意图**：在韩国建立缓冲区，保护日本免遭苏联及共产主义势力影响。
+- **苏联意图**：在朝鲜北部建立卫星附属国，奉行对苏联马首是瞻的指示。
+- **统一失败**：原本计划在不同占领区受降后，像奥地利那样普选建立统一民选政府；但美苏关系急转直下，所扶植领导人各有心思，意识形态不同最终建立两个国家，成为朝鲜战争爆发的缘由。
+### 当前朝韩关系处于微妙平衡
+- **美国忌惮**：美国因惧怕朝鲜背后的中国和俄罗斯，未主动进攻朝鲜，也未再次挑起半岛武装冲突。
+- **朝鲜顾虑**：金家担心贸然发动战争后政权被颠覆，故不敢轻举妄动。
+- **统一风险**：若朝韩统一，大概率是韩国兼并朝鲜（经济与综合实力占优）；但北方拥有优质兵源及核武器、导弹等尖端武器，统一后对东北亚地区是“不稳定的定时炸弹”——参照越南统一后次年进攻柬埔寨、泰国，中国1979年被迫发动自卫反击战。
+### 韩国军队战斗力前后差异显著
+- **初期表现**：战争爆发时韩军瞎指挥，差点被朝鲜团灭；1950年7月10日后南部地面战斗主要由美军与朝鲜人民军进行，韩军仅“冲人头”。
+- **后期整训**：1952年后美军重新整军训练，韩军才形成基本战斗力；此前韩军战线常被志愿军突击，导致美军每次兵败皆因韩军战线崩溃。
+- **第五次战役**：志愿军从韩军东部战线反包围突击，打崩韩军前线，美国在韩国领土上撤销了韩国第三军团。
+- **军队渊源**：韩军军官主体为二战时期日本扶植的伪军和傀儡部队骨干，士兵为强征农村青年；延续昭和日军武士道精神管理体制，老兵欺负新兵、军队霸凌事件延续至今。
+### 抗美援朝而非解放台湾的战略选择
+- **海军短板**：台湾海峡约100公里，中共刚建国缺乏海军实力，无法进行渡海作战。
+- **美国介入**：美国将台湾和韩国共同纳入亚太保护圈，陆军出兵朝鲜半岛，海军第七舰队进驻台湾海峡，既防解放军解放台湾，也防国民党反攻大陆。
+- **唇亡齿寒**：美军越过三八线向中朝边境进发，触动中国敏感神经；既然海上无法作战，就在陆地上作战——长津湖、上甘岭两场战役接连让美军惨败，成为美国人挥之不去的梦魇。
+## 金句总结
+&gt; “唇亡齿寒这个概念，就是深入人心。所以说导致了就是即便不愿意和美国爆发全面战争，但是又不得不进行一个全面战争。”
+&gt; —— **发言人1（主讲人）** ｜ 针对中国为何在美军越过三八线后决定出兵朝鲜的定调发言
 &gt; “他是美国历史上第一次在未取得胜利的情况下签署停战协议的司令官。”
-- 背景：主讲人引述美军最后一任司令官克拉克的自我评价，说明美国称朝鲜战争为“被遗忘的战争”。
-&gt; “伤害最深的其实还是朝鲜和韩国。毕竟大家都是就是一脉相承嘛，都是血肉同胞，却分裂成了两个国家。”
-- 背景：主讲人总结朝鲜战争对朝韩两国的长期伤害，指出三八线悲剧延续至今。
-&gt; “如果说是朝韩要是统一，大概率应该是韩国兼并朝鲜。”
-- 背景：主讲人展望朝韩统一前景，依据经济影响与综合实力判断统一方向。
+&gt; —— **发言人1（主讲人）** ｜ 针对朝鲜战争对美国历史意义的评价
+&gt; “伤害最深的其实还是朝鲜和韩国。毕竟大家都是就是一脉相承嘛，都是血肉同胞，却分裂成了两个国家，并且这样的三八线的悲剧延续至今。”
+&gt; —— **发言人1（主讲人）** ｜ 针对朝鲜战争对朝鲜半岛人民影响的总结
+&gt; “美国再也不敢小瞧我们了，导致在一九六七年的越南战争时期，中国这边向美国发出的警告，绝对不允许越过北纬十七度线。”
+&gt; —— **发言人1（主讲人）** ｜ 针对朝鲜战争奠定中国强国地位的论证
+&gt; “如果说是朝韩要是统一，大概率应该是韩国兼并朝鲜。毕竟经济影响和综合实力摆在这儿。”
+&gt; —— **发言人1（主讲人）** ｜ 针对朝韩统一可能走向的判断
 &gt; “今日朝韩如果统一的话，那对于整个东北亚地区来说，都是一颗不稳定的定时炸弹。”
-- 背景：主讲人分析朝韩统一后北方拥有核武器与导弹，类比越南统一后进攻柬埔寨、泰国，指出局势更不可控。
-&gt; “咱们和朝鲜的问题，还有俄罗斯的问题，主要就是图们江出海口的那个问题，到现在今天还拖着这个事没有着落。”
-- 背景：主讲人回答中俄朝关系现状，指出图们江出海口被俄朝封死、大船无法通行的问题至今未解决。
-&gt; “既然海上没办法进行战斗，那就只能在陆地上进行战斗。”
-- 背景：主讲人解释抗美援朝决策逻辑——解放军陆军强而海军弱，故选择在陆地争取战略主动。
-# Q&amp;A 环节
-**发言人4**：这场战争开始和结束时，韩国和朝鲜的势力差别大吗？战争的改变大吗？
-**主讲人**：从中国角度说，奠定了我们强国地位，美国再不敢小瞧我们。1967年越南战争时，中国警告美国不得越过北纬十七度线，美国未敢越线。这场战争在美国被称为“被遗忘的战争”，最后一任司令官克拉克承认自己是美国历史上首位未取得胜利就签署停战协议的司令官。伤害最深的还是朝鲜和韩国，本是血肉同胞却分裂成两个国家，三八线的悲剧延续至今。
-**发言人2**：现在越南还分南北吗？
-**主讲人**：越南是统一的，美国最终放弃了南越，北越趁机统一了南越。
-**发言人2**：三八线定了之后，现在韩国跟朝鲜哪边好玩一点？
-**主讲人**：当然是韩国更好玩。朝鲜旅游没有人身自由，入境先搜手机检查，没有无线网，只有平壤有自己的网络运营商，类似咱们国家八九十年代的状态，手机很落后，国际漫游和网络非常贵。那几天就是参观主体思想和社会主义辉煌建设成就，类似以前文革时期那种无产阶级高于一切的思想，活在异次元世界当中。
-**发言人4**：他们普通人可以上网吗？
-**主讲人**：普通人不能上网，局域网都很有限，普通人连电脑和5G手机都用不起。主要是外部有韩国，韩国用韩剧作意识形态宣传武器，老百姓知道真相后会颠覆政权，所以那么多朝鲜老百姓往韩国跑，鲜有韩国人去朝鲜，这就是脱北者。
-**发言人3**：他们有拿飞机往朝鲜发传单，发韩国文化那种图，文化入侵？
-**主讲人**：有的，朝鲜严防，谁家被发现私藏肯定要追究连带责任。
-**发言人2**：朝鲜那边有啥好玩的？
-**主讲人**：也就平壤看看志愿军抗美援朝的功绩，还有开城，毕竟是朝鲜半岛三千年古都，特产小人参。
-**发言人3**：朝鲜有他们古代的文化吗？高丽，还有韩剧里讲朝鲜古代将军什么的。
-**主讲人**：朝鲜半岛文明是中华文明的衍生物，有3500年历史，最早是商周时期形成初步文明，一直是中华文化圈中原的附属国，直到甲午战争清朝战败后，朝鲜才脱离与中国隶属关系，成立大韩帝国，后来与日本合并，二战后复国又被分裂成朝鲜和韩国。
-**发言人6**：朝鲜是不是有像北京或俄罗斯那样很大的广场？平壤的金日成广场，是以领导人命名？
-**主讲人**：对，以领导人来命名，他们大将军、大元帅这样的。
-**发言人4**：南北之间的割裂有什么历史渊源？为什么会成为两个政权？
-**主讲人**：一开始美苏都希望在朝鲜半岛建缓冲区。美国在南方单独建韩国，是为保护日本免遭苏联及共产主义势力影响；苏联也需要在亚洲建卫星附属国，所以在朝鲜北部宣布北朝鲜独立。本来设想像奥地利那样普选建立统一民选政府，但美苏关系恶化极快，所扶植的领导人也各有心思，意识形态不同，最终建立两个国家，这也是朝鲜战争爆发的缘由。
-**发言人4**：当时美国没有打败朝鲜，你觉得现在美国对朝鲜的态度是怎样的？
-**主讲人**：美国惧怕朝鲜背后的中国和俄罗斯。朝鲜战争时中国出动志愿军帮朝鲜把美国打回去，苏联提供空军掩护和武器后勤支持，中苏联手把美国打回三八线以南，所以美国忌惮，没有主动进攻朝鲜，也没再挑起朝鲜半岛武装冲突。朝鲜金家也担心贸然发动战争后江山被颠覆，所以也不敢动武。
-**发言人7**：现在的朝韩对立可以认为是韩国和西方国家在背后支撑，是微妙平衡。如果当时没有形成冷战布局、互相争夺半岛控制权，大一统的朝鲜半岛会是什么形态？大号朝鲜还是平衡的韩朝？
-**主讲人**：如果当时美国没下场救援韩国，今日朝鲜可能是苏联卫星国，是牵制咱们国家的钉子，也是威胁美国在亚洲尤其是日本的定时炸弹。现在朝韩若统一，大概率是韩国兼并朝鲜，毕竟经济和综合实力摆在那儿，但北方有充足优质兵源以及核武器和导弹，统一后对整个东北亚都是不稳定定时炸弹。当年越南统一后第二年就进攻柬埔寨和泰国，被逼到79年我们出兵对越自卫反击战，越南尚且如此，朝鲜半岛统一后局势更不可控。
-**发言人3**：你感觉现在中国、俄罗斯和朝鲜之间关系怎么样？
-**主讲人**：各怀鬼胎。咱们和朝鲜、俄罗斯的问题主要是图们江出海口，到现在还拖着没着落。
-**发言人4**：什么出海口？
-**主讲人**：图们江是俄罗斯和朝鲜的界江，那个地方是日本海的出海口，在中朝俄边境那块，国际水域航道可以通行，但俄罗斯和朝鲜建了一座小桥，大船没法过去。俄朝都不希望咱们过分强大，不想过多依附于我们，所以把图们江出海口封死了。
-**发言人6**：朝鲜战争中朝鲜军队和韩国军队有没有发挥什么作用？
-**主讲人**：一开始韩国军队瞎指挥，差点被朝鲜团灭。6月25日战争爆发，7月10日以后南部地面战斗主要是美军和朝鲜人民军打，韩军一开始就是冲人头角色。1952年之后美国把韩国重新整军训练，韩军才形成基本战斗力。此前韩军对美军像猪队友，志愿军跟美军占不到便宜时都从韩军战线突击，美军每次兵败都是韩军战线崩溃引起。第五次战役中志愿军从朝鲜半岛东部反包围突击，把韩军前线打崩，美国把韩国第三军团全部撤销——美国人在韩国领土上把韩国军队撤销了。韩军1952年前战斗力我不敢恭维，之后不可小视。韩军军官主体是二战时日本人扶植的伪军和傀儡部队骨干，士兵类似国民党抓壮丁强征农村青年，一直贯彻昭和日军武士道精神，老兵欺负新兵，军队霸凌事件延续至今，是充满昭和军国主义思想余孽的旧日军部队延伸。
-**发言人5**：1950年援朝时中国刚成立，实力不强，为什么选择抗美援朝而不是收复台湾？
-**主讲人**：台湾和大陆之间海峡约100公里，当时中共刚建国没有海军实力。50年朝鲜战争爆发，美国参众两院认为是共产主义世界对自由世界的全面进攻，把台湾和韩国共同纳入美国亚太保护圈，美军陆军出兵朝鲜半岛，海军第七舰队进驻台湾，既防解放军解放台湾，也防国民党反攻大陆。但美军越过三八线向中朝边境进发，触动咱们敏感神经，“唇亡齿寒”深入人心，即便不愿和美国爆发全面战争也不得不打。台湾的事已经让咱们很被动，朝鲜半岛既然要争取战略主动，解放军陆军很强，海上没法打就在陆地上打。这也是后来战斗意志的体现，长津湖和上甘岭接连让美军惨败，到今天也是美国人挥之不去的梦魇。</t>
+&gt; —— **发言人1（主讲人）** ｜ 针对朝韩统一潜在风险的警示
+&gt; “俄罗斯和朝鲜都不希望咱们过分强大，然后不想过多依附于我们，所以说在那个图们江出海口给封死了。”
+&gt; —— **发言人1（主讲人）** ｜ 针对图们江出海口问题长期未决的原因分析
+&gt; “他就是一支充满着昭和军国主义时期那种思想余孽的，就是旧日军部队的一种延伸。”
+&gt; —— **发言人1（主讲人）** ｜ 针对韩国军队历史沿革与管理体制的定性评价
+## Q&amp;A 环节
+### Q1. 金刚山的位置归属
+- **听众**：金刚山是在韩国还是在朝鲜？
+&gt; **主讲人**：金刚山是跨朝韩边界的一座山脉，类似国内华山那种主峰加附属峰的形式，双方各有一部分。
+### Q2. 朝鲜战争对各方的影响
+- **听众**：战争开始和结束时，韩国和朝鲜的势力有很大差别吗？这场战争改变大吗？
+&gt; **主讲人**：从中国角度，战争奠定了强国地位，美国再不敢小瞧我们，1967年越南战争时中国警告美国不得越过北纬十七度线，美国未敢越线。这场战争在美国被称为“被遗忘的战争”，美军最后一任司令官克拉克承认是首位在未取得胜利情况下签署停战协议的司令官。伤害最深的还是朝鲜和韩国，本是血肉同胞却分裂成两个国家，三八线悲剧延续至今。
+### Q3. 越南是否还分南北
+- **听众**：现在越南还分南北吗？
+&gt; **主讲人**：没有，越南是统一的。美国最终放弃了南越，北越趁机会把南越统一了。
+### Q4. 朝鲜旅游体验与限制
+- **听众**：三八线定了之后，韩国跟朝鲜哪边好玩一点？
+&gt; **主讲人**：韩国更好玩。朝鲜旅游没有人身自由，入境第一件事是搜手机检查，没有无线网，只有平壤有自己的网络运营商，类似国内八九十年代状态，手机落后、国际漫游和网络非常贵。参观内容主要是主体思想和社会主义辉煌建设成就，类似文革时期那种无产阶级高于一切的思想，像活在异次元世界。
+### Q5. 朝鲜普通人能否上网
+- **听众**：他们普通人可以上网吗？
+&gt; **主讲人**：普通人不能上网，局域网都很有限，连电脑和5G手机都用不起。外部有韩国用韩剧作意识形态宣传武器，老百姓知道真相后会颠覆政权，所以朝鲜严防外部信息。这也是为什么那么多朝鲜老百姓往韩国跑，即脱北者，鲜有韩国人去朝鲜。
+### Q6. 朝鲜对韩国文化入侵的防范
+- **听众**：他们有用飞机往朝鲜发传单或韩国文化内容吗？
+&gt; **主讲人**：有的。朝鲜严防这类内容，只要被发现谁家私藏，肯定要追究连带责任。
+### Q7. 朝鲜旅游景点推荐
+- **听众**：朝鲜那边有啥好玩的？
+&gt; **主讲人**：也就平壤看看志愿军抗美援朝的功绩，还有开城——朝鲜半岛三千年古都，特产小人参。整个朝鲜半岛都盛产人参。
+### Q8. 朝鲜古代文化与中华文明的关系
+- **听众**：朝鲜有他们古代的文化吗？比如高丽，还有韩剧里讲的朝鲜古代将军什么的。
+&gt; **主讲人**：朝鲜半岛文明是中华文明的一个衍生物，约有3500年历史，最早可追溯到商周时期形成初步文明。高丽半岛一直是中华文化圈中中原的附属国，直到甲午战争清朝战败后，朝鲜才彻底脱离与中国的关系，成立大韩帝国，后与日本合并，二战后复国又被分裂成朝鲜和韩国。
+### Q9. 平壤金日成广场的命名
+- **听众**：朝鲜是不是有类似北京或俄罗斯那样的大广场？平壤的金日成广场是以领导人命名的吗？
+&gt; **主讲人**：对，以领导人来命名，他们的大将军、大元帅这样的。
+### Q10. 朝鲜半岛分裂的历史渊源
+- **听众**：南北之间的割裂有什么历史渊源？为什么会成为两个政权？
+&gt; **主讲人**：一开始美苏都希望在朝鲜半岛建立缓冲区。美国在分出三八线以南单独建韩国，是为保护日本免遭苏联及共产主义势力影响；苏联也需要在亚洲建立卫星附属国，所以在朝鲜北部宣布独立，奉行对苏联马首是瞻。最初计划像奥地利那样在不同占领区受降后普选建立统一民选政府，但美苏关系恶化极快，扶植的领导人也各有心思，因意识形态不同最终建立两个国家，这也是朝鲜战争爆发的缘由。
+### Q11. 当前美国对朝鲜的态度
+- **听众**：当时美国没有打败朝鲜，你觉得现在美国对朝鲜的态度是怎样的？
+&gt; **主讲人**：美国惧怕朝鲜背后的中国和俄罗斯。朝鲜战争时朝鲜快被美国完全占领，中国出动志愿军帮朝鲜把美国打回去，苏联也提供空军掩护和武器后勤支持，中苏联手把美国打回三八线以南。美国忌惮这些因素，所以没有主动进攻朝鲜，也没再挑起朝鲜半岛武装冲突。朝鲜金家也担心贸然发动战争后江山被颠覆，所以也不敢贸然发动战争。
+### Q12. 若没有冷战布局，朝鲜半岛会是什么形态
+- **听众**：现在的朝韩对立可以认为是韩国和西方国家在背后支撑的微妙平衡。如果当时没有形成冷战布局、互相争夺半岛控制权，大一统的朝鲜半岛会是什么形态？大号朝鲜还是平衡的韩朝？
+&gt; **主讲人**：如果当时美国没下场救援韩国，今日朝鲜可能是苏联卫星国，用来牵制中国、威胁美国在亚洲尤其是日本的定时炸弹。现在朝韩若统一，大概率是韩国兼并朝鲜，毕竟经济影响和综合实力摆在那儿，北方有充足优质兵源及核武器和导弹尖端武器，统一后对整个东北亚都是不稳定定时炸弹。当年越南统一后宣布继承法国在中南半岛所有地盘，第二年就进攻柬埔寨和泰国，被逼得中国79年出兵对越南自卫反击战。越南尚且如此，朝鲜半岛统一后局势更不可控。
+### Q13. 中国、俄罗斯与朝鲜的关系
+- **听众**：你感觉现在中国、俄罗斯和朝鲜之间关系怎么样？
+&gt; **主讲人**：各怀鬼胎。咱们和朝鲜、俄罗斯的问题主要是图们江出海口问题，到今天还拖着没着落。
+### Q14. 图们江出海口问题
+- **听众**：什么出海口？
+&gt; **主讲人**：图们江是俄罗斯和朝鲜的界江，那个地方是日本海的出海口。中朝俄边境那块图们江国际水域航道可以通行，但俄罗斯和朝鲜建了一座小桥，大船没法过去。俄罗斯和朝鲜都不希望咱们过分强大，不想过多依附于我们，所以把图们江出海口封死了，都不想把出海口让给我们。
+### Q15. 朝鲜和韩国军队在战争中的作用
+- **听众**：朝鲜战争中朝鲜军队和韩国军队有没有发挥什么作用？
+&gt; **主讲人**：一开始韩军瞎指挥，差点被朝鲜团灭。6月25日战争爆发，7月10日以后朝鲜南部地面战斗主要是美军和朝鲜人民军进行，韩军一开始负责冲人头。1952年之后美国把韩国重新整军训练备战，韩军才形成基本战斗力。此前韩军对美军像猪队友，志愿军跟美军占不到便宜时都从韩军战线突击，美军每次兵败都是韩军战线崩溃引起。第五次战役中志愿军从朝鲜半岛东部对韩军形成反包围突击，把整个韩军前线打崩，美国把韩国第三军团全部撤销——是美国人在韩国领土上把韩国军队给撤销了。韩军战斗力1952年前不敢恭维，1952年后不可小视。韩军军官主体是二战时期日本人扶植的伪军和傀儡部队骨干，士兵像国民党抓壮丁形式强征的农村青年，从成军至今一直贯彻昭和日军武士道精神管理体制，关西兵、老兵欺负新兵、军队霸凌事件蔓延至今，是充满昭和军国主义思想余孽的旧日军部队延伸。
+### Q16. 为何选择抗美援朝而非解放台湾
+- **听众**：1950年抗美援朝时中国刚成立，实力不强，为什么选择抗美援朝而不是收复台湾？
+&gt; **主讲人**：台湾和大陆之间有漫长海峡，距离约100公里，中共刚建国没有相应海军实力。1950年朝鲜战争爆发，美国参众两院普遍认为这是共产主义世界对自由世界的全面进攻，把台湾和韩国共同纳入美国亚太保护圈，美军陆军出兵朝鲜半岛，海军第七舰队进驻台湾，一来防止解放军解放台湾，二来防止国民党反攻大陆。解放军建军时没有海军实力，没办法进行解放台湾的战斗。但美军越过三八线向朝鲜及中朝边境进发，触动敏感神经，唇亡齿寒概念深入人心，即便不愿和美国爆发全面战争又不得不打。台湾的事已让中国很被动，朝鲜半岛这场既然要争取战略主动，解放军陆军很强，海上没办法战斗就只能在陆地上战斗。这也是后来在长津湖和上甘岭接连让美军惨败的战斗意志体现，这两场战役到今天仍是美国人挥之不去的梦魇。</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>69</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7464/5912</t>
+          <t>7464/6116</t>
         </is>
       </c>
     </row>
@@ -15629,48 +15747,61 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t># 对话概况
-本次为多人闲聊，无明确身份线索，仅以发言人编号区分。发言人2率先抛出“出门必带的三样东西”话题，各人分享随身物品习惯，随后话题自然延伸至头发打理与个人形象，再因提及下雨而转到天气与居住安全。主要话题包括：出门必带物品、头发打理与个人形象、下雨天气与居住安全。以分享为主，未形成明确结论；各人习惯差异明显，如发言人2必带手机、充电宝、指甲刀，上班另带刮胡刀（平均每三天一次，因胡子一天长几毫米），发言人1强调必须带钥匙，发言人4必带皮圈绑头发，发言人5每天带手机、耳机和工卡；对绑发与披发的审美偏好亦不同，发言人2认为披发显头小，发言人1觉得散头发更好看。可记锚点：发言人2胡子一天长几毫米、平均每三天带一次刮胡刀、曾留胡子被误认为新疆少数民族。
-# 交流内容
-- **出门必带物品**：发言人2发起“出门必带三样东西”话题，自述带`手机`、`充电宝`、`指甲刀`，并解释指甲刀为`多重指甲刀`，可刮指甲、磨手掌；发言人1强调必须带`钥匙`，因家门为`指纹锁`，不带钥匙不行；发言人4表示必带`皮圈`绑头发；发言人5称每天带`手机`、`耳机`和`工卡`。
-  - 发言人2补充上班必带`充电宝`、`手机`、`刮胡刀`，平均`每三天`带一次刮胡刀，因胡子`一天能长几毫米`，不带会痒；并称已用`电子锁`多年，用指甲刀“平替”钥匙。
-  - 发言人1提到出差不带`手机卡`，上班几乎只带手机；发言人3提到出门带`纸巾`、下雨带`伞`；发言人2建议带`一块砖重量`的充电宝，既能充电也能防身。
-- **头发打理与个人形象**：发言人2好奇初中男生为何薅女生`头发圈`，并认为绑头发显`脑袋大`、披发显`头小`；发言人1觉得`散头发`比绑着好看，不想让女生绑；发言人3建议弄`公分`两边补点小点。
-  - 发言人2称高中时梦想留`长发`和`大胡子`，因不好打理放弃；尝试留胡子时去学校报道，被误认为`新疆少数民族`。
-- **下雨天气与居住安全**：发言人1提到`秋天`容易下雨，发言人2好奇为何不是`春天`；发言人4认为`北京``夏天`易下雨，发言人1补充夏天易下`暴雨`。
-  - 发言人3回忆每年下雨`园区门口`都是水，`李博`家因`地势`低被淹；发言人2据此建议住`三楼以上`，远离低楼层。
-# 关键原话
+          <t># 出门必带物品闲聊会
+## 对话概况
+本次为多人闲聊场合，五位发言人围绕“出门必带的三样东西”展开分享，由发言人2起头提问，各人依次报出手机、充电宝、指甲刀、钥匙、皮圈、耳机、工卡等随身物品，随后话题自然流转至头发打理与个人形象（由皮圈引出绑发与披发偏好），再经带伞话题转入下雨天气与居住安全（园区积水、李博家被淹）。主要话题包括：出门必带物品、头发打理与个人形象、下雨天气与居住安全。倾向与差异对照：以分享个人习惯为主，未形成明确结论；差异主要体现在随身物品选择（如发言人2带刮胡刀、发言人4带皮圈、发言人5带耳机工卡）及审美偏好（发言人2认为绑发显脑袋大、若为女生会披发，发言人1认为散发更好看），属习惯与审美差异。值得记的锚点：发言人2称胡子一天能长几毫米、上班平均每三天带一次刮胡刀；发言人3提到每年下雨园区门口积水、李博家曾被淹。
+## 交流内容
+### 出门必带物品讨论
+1. **出门必带三样**：发言人2发起话题，称必带手机、充电宝、指甲刀，并解释指甲刀为多功能款，可刮指甲、磨手掌。
+  - **发言人1**：必须带钥匙，因家门为指纹锁；出差必带手机卡。
+  - **发言人3**：带钥匙；另补充出门带纸巾、下雨带伞。
+  - **发言人4**：必带皮圈绑头发；认为钥匙破坏性强，倾向套起来或挂起来。
+  - **发言人5**：每天必带手机、耳机和工卡，工卡用于刷脸进单位及领夜宵。
+2. **上班三件套**：发言人2称上班必带充电宝、手机、刮胡刀，平均每三天带一次刮胡刀，因胡子一天能长几毫米，不带会痒。
+  - **发言人1**：上班只带手机，不背包不带伞；出差才带手机卡。
+  - **发言人5**：耳机和工卡直接放单位，不随身带。
+3. **工卡佩戴习惯**：发言人1提到有人把工卡挂脖，发言人2认为仅政府系统或外企商务场合有必要，平时不必挂；发言人5提及字节员工不录出来会有小惩罚，发言人2质疑此举属剥削员工。
+### 头发打理与个人形象
+1. **绑发与披发偏好**：由皮圈话题延伸，发言人2认为绑头发显得脑袋大，若自己是女生会选择披发；发言人1认为散头发比绑着好看，不希望女生绑发；发言人3建议弄个中分、两边补点小点缀。
+2. **长发与胡子经历**：发言人2称高中时梦想上大学留长发、大胡子，后因不好打理放弃；曾留胡子去学校报到，被误认为新疆少数民族；发言人1提及看到男生留长披发搞艺术，发言人2回应不好打理。
+### 下雨天气与居住安全
+1. **下雨季节讨论**：发言人1称北京下雨少且无季节性，夏天易下暴雨；发言人4认为北京夏天容易下雨；发言人2好奇为何说秋天易下雨。
+2. **积水与居住建议**：发言人3提到每年下雨园区门口都是水，李博家因地势低曾被淹；发言人2建议住三楼以上以防水淹。
+## 关键原话
 &gt; “手机充电宝指甲刀。指甲刀得对呀，因为那个指甲刀是多重指甲刀，比如说还有那个刮刮指甲呀，然后磨摸手掌啊什么的。”
-- 背景：发言人2回答“出门必带的三样东西是什么”时列举自己的随身物品。
+&gt; —— **发言人2** ｜ 针对出门必带三样东西的表态
 &gt; “对呀，我必须带钥匙，不带钥匙就行。”
-- 背景：发言人1回应出门必带物品话题，强调钥匙是必带项。
+&gt; —— **发言人1** ｜ 针对出门必带物品的表态
 &gt; “我我已经好多年的电子锁了，我都没什么钥匙的概念了都。然后所以说拿指甲刀来平替钥匙了。”
-- 背景：发言人2回应发言人1带钥匙的习惯，说明自己用电子锁多年、以指甲刀替代钥匙。
+&gt; —— **发言人2** ｜ 针对钥匙与电子锁话题的表态
 &gt; “对，所以说我上班必带三件套，充电宝、手机、刮胡刀。”
-- 背景：发言人2总结自己上班出门的必带物品，此前提到胡子一天能长几毫米、平均每三天带一次刮胡刀。
+&gt; —— **发言人2** ｜ 针对上班必带物品的表态
 &gt; “我现在每天就是手机、耳机和工卡。”
-- 背景：发言人5回应“上班带什么”时列举自己的日常随身物品。
-&gt; “反正要是我是女的，我肯定不绑。要一绑的话，我自个的角度就觉得显得自己脑袋很大，对不对？”
-- 背景：发言人2讨论女生绑头发话题，表达披发显头小的个人看法。
-&gt; “那个时候的梦想的形象是这样的。但后来发现啊留胡子不太好打理还是算的，然后那个头发更不好打理，我就打消这样的想法和念头了。”
-- 背景：发言人2回忆高中时想留长发大胡子的梦想，因打理困难而放弃。
-&gt; “就他那个地势吧，然后就是家里，然后他那个地势。”
-- 背景：发言人3回应下雨话题，说明李博家因地势低被淹的情况。
-# 共识与分歧
-**共识**：在场多数人认同**出门必带物品以实用、应急为导向**，如手机、充电宝、钥匙、刮胡刀等，均服务于日常通勤或突发需求（如充电、开门、打理形象），这一共识源于对便利性和安全感的共同需求。此外，大家普遍认为**电子锁和手机打卡已弱化钥匙、工卡的随身必要性**，发言人2、发言人1均以自身经历佐证，反映出对技术替代传统物件的普遍接受。
-**分歧**：一是**随身物品取舍**存在习惯差异，如发言人2坚持带指甲刀、刮胡刀（因胡子生长快），发言人4必带皮圈（因长发需绑扎），发言人5带耳机和工卡，分歧性质属**个人习惯与生活场景差异**，非价值对立。二是**头发打理偏好**上，发言人2认为绑发显头大、披发更佳，发言人1觉得散发更好看，分歧属**审美差异**，依据各自对形象效果的直观判断。三是**下雨季节认知**不同，发言人1称秋天易雨，发言人4认为北京夏天多雨，属**经验性认知差异**，未深入论证。
-**倾向**：本场以分享漫谈为主，未形成明确结论或决策，整体倾向是**尊重个体习惯、轻松交流**，无对抗性立场。
-# 延伸话题与后续
-- **字节员工不录出来会有什么惩罚？**：发言人1提到“现在有可能字节员工哦，要录出来”，发言人5回应“有点小的惩罚吧”，发言人2追问“比如说什么样的惩罚”，发言人5答“那就得问他们了”，发言人2评价“那这不成了剥削员工了吗”，话题未深入即被带过。
-- **为什么秋天容易下雨？**：发言人1称“我觉得包里有秋天就容易下雨呀”，发言人2追问“不是说春天容易下雨吗？为什么说秋天容易下雨？”，发言人4提出“我觉得北京是夏天容易下雨的”，发言人1补充“北京倒是下雨很少，也没个季节性”，未形成明确解释。</t>
+&gt; —— **发言人5** ｜ 针对上班必带物品的表态
+&gt; “反正要是我是女的，我肯定不绑。要一绑的话，我自个的角度就觉得显得自己脑袋很大。”
+&gt; —— **发言人2** ｜ 针对头发绑与不绑话题的表态
+&gt; “他住的一楼吗？是被淹了的时候。”
+&gt; —— **发言人2** ｜ 针对李博家被淹话题的追问
+&gt; “那个妹子好像没买大雨，她一大早就早上可能就送给孩子，然后就去。”
+&gt; —— **发言人3** ｜ 针对下雨积水与李博家被淹话题的补充
+## 共识与分歧
+**共识与分歧**
+- **共识**：在出门必带物品上，多数人认同**手机是必备品**，且普遍接受电子锁替代传统钥匙的趋势——发言人1家门为指纹锁、发言人2多年使用电子锁，均因此弱化了钥匙的携带需求。这一共识源于技术便利带来的生活习惯改变。
+- **分歧一（习惯差异）**：必带物品因人而异，发言人2强调指甲刀、刮胡刀等个人护理工具，发言人4必带皮圈，发言人5必带耳机和工卡。分歧性质为**个人习惯差异**，源于各自生活需求不同，而非价值判断。
+- **分歧二（审美差异）**：关于头发绑与不绑，发言人1认为散头发更好看，发言人2认为绑发显脑袋大、若自己是女生会选择披发。分歧性质为**审美差异**，双方均基于个人视觉偏好，无对错之分。
+- **分歧三（事实认知）**：关于下雨季节，发言人1称北京下雨无季节性，发言人4认为北京夏天易下雨，发言人3则提到园区门口每年下雨积水。分歧性质为**经验观察差异**，依据各自对北京天气的切身感受。
+- **本场倾向**：以分享个人习惯为主，未形成明确结论或统一立场；讨论氛围轻松，参与者对他人习惯多持好奇与理解态度，未出现激烈对立。
+## 延伸话题与后续
+- [ ] 字节员工不录出来会有什么惩罚？（发言人5 表示“有点小的惩罚”，但未说明具体内容，发言人2 追问后未获答复）
+- [ ] 秋天为什么容易下雨？（发言人2 提出疑问，发言人1 未解释，发言人4 认为北京夏天容易下雨，话题未深入）</t>
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>28.5</v>
+        <v>31.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3851/2312</t>
+          <t>3851/2333</t>
         </is>
       </c>
     </row>
@@ -15866,50 +15997,46 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t># 讨论议题与背景
-本次会议为多人闲聊，围绕各自最常用的手机APP、视频播放器、音乐APP及歌手偏好展开讨论，无明确结论。参会者为发言人1至发言人5共五人，原文未给出具体姓名或职务。讨论由发言人1发起「手机里最常用的三个APP」话题，随后自然延伸至AI助手使用、视频观看方式、音乐平台选择及歌手乐队偏好等议题。手机APP方面，发言人2常用知乎、小红书、谷歌，发言人3常用微信、抖音、淘宝、京东，发言人4常用微信、小红书并提及小布AI助手，发言人5常用B站，发言人1提及百度千问、吉米等AI助手；发言人3认为AI小助手回答更精准、总结性强，发言人2则表示仍停留在浏览器、纸质地图和尺子铅笔标注的思维模式，不太信任AI软件。视频观看方面，发言人3常用腾讯视频、爱奇艺、优酷、芒果TV，发言人2因广告时间长不愿等待而直接用B站，并指出国内付费电视剧在YouTube上免费但部分内容仍需付费，大平台有版权纠纷需付费、小网站无版权纠纷可免费观看，发言人4提及YouTube手机翻墙困难及单框架手机无法下载YouTube。音乐APP方面，发言人5常用网易云音乐但单框架手机不适配需用卓翼通，发言人2以前常用酷狗、酷我并提及欧美平台虾扎，认为欧美平台有更多演唱会版本音乐、国内网易云因版权纠纷播不出大牌歌曲；发言人1、发言人2、发言人4分别在上班时、随时、通勤路上听音乐，发言人2在柏林坐地铁时听音乐代入感强。歌手偏好方面，发言人3提到谢霆锋翻唱Taylor Swift并讨论其歌曲如Love Story，发言人2对Taylor Swift重新火起来表示疑惑，认为其对九零后和零零后影响都深。讨论以漫谈发散方式推进，由发言人2多次引导话题转换，未形成统一结论。
-# 发言要点
-## 最常用的手机APP
-- **发言人2**：常用知乎、小红书、谷歌，自述仍停留在浏览器加纸质地图、尺子圆规铅笔标注的思维模式，不太信任AI软件，不确定其回答是否正确。
-- **发言人3**：常用微信、抖音、淘宝、京东等购物平台，也下载了豆包；认为AI小助手回答更精准、总结性更强、更全面。
-- **发言人4**：常用微信、小红书，现在不用浏览器，直接用手机自带的小布AI助手搜索。
-- **发言人5**：常用B站，也使用YouTube，希望AI能识别中英混杂的表述。
-- **发言人1**：手机里装有百度千问、吉米等多个AI助手，未装腾讯元宝。
-## 视频观看与播放器APP
-- **发言人3**：常用腾讯视频、爱奇艺、优酷、芒果TV等播放器，会点进去看有没有想看的，也接受看广告换VIP时长的模式。
-- **发言人2**：因广告时间太长等不起，直接用B站观看；指出国内付费电视剧在YouTube上免费，但部分内容仍需付费，自己反而找到一些小网站不用花钱。
-- **发言人2**：解释大平台因版权纠纷需付费，小网站没有版权纠纷所以免费。
-- **发言人4**：指出YouTube手机一般翻不了墙；**发言人5**补充单框架手机现在连YouTube都下载不了。
-## 音乐APP与收听场景
-- **发言人5**：常用网易云音乐，但单框架手机不适配，目前全靠卓翼通使用。
-- **发言人2**：以前常用酷狗、酷我，也使用欧美音乐平台虾扎；认为欧美平台有更多演唱会版本，国内网易云因版权纠纷播不出大牌歌曲。
-- **发言人1**：认为虾扎上唱的多是小众歌手；**发言人2**补充主要是小众翻唱多一些。
-- **发言人1**：上班时听音乐；**发言人4**：通勤路上听，需用降噪耳机；**发言人2**：说不准什么时候都有，在柏林坐地铁时因地铁安静，听音乐代入感强。
-## 歌手偏好与Taylor Swift讨论
-- **发言人3**：最近刷到谢霆锋翻唱Taylor Swift，开始喜欢谢霆锋，提到《玉蝴蝶》等老歌。
-- **发言人2**：对Taylor Swift重新火起来表示疑惑——中学时（2010年代开头）她就火过，后因绯闻消沉，现在对九零后和零零后影响都很深。
-- **发言人2**：回忆Taylor Swift与猫头鹰之城主角亚当·杨传过绯闻，当时从东南卫视台湾节目看到报道；**发言人4**表示没有很关注。
-- **发言人1**：认为五月天以前挺好，新发的还行但唱不上去了。
-# 共识形成
-- **一致意见**：多数成员认可AI助手在回答精准度与总结性上优于传统浏览器搜索，发言人3明确表示AI小助手「回答的更精准一点，总结性比较强」，发言人4、发言人5亦已实际使用小布、豆包等AI工具。
-- **倾向性认识**：视频观看方面，发言人2主张因广告时间过长而倾向使用B站直接观看，并指出国内付费电视剧在YouTube上可免费观看，但部分内容仍需付费；其解释为大平台存在版权纠纷故需付费，小网站无版权纠纷可免费观看。
-- **主要分歧点**：发言人2与发言人3、发言人4、发言人5在AI工具信任度上不一致——发言人2表示「不太确定它是否说的是对的」，仍停留在浏览器、纸质地图和尺子铅笔标注的思维模式，自认「比大家落后了一代」；其余成员则已接受并日常使用AI助手。
-- **音乐平台分歧**：发言人2认为欧美音乐平台（虾扎）拥有更多演唱会版本音乐，国内网易云因版权纠纷播不出大牌歌曲；发言人5则反映网易云在单框架手机上不适配，需借助卓翼通使用。
-- **歌手偏好分歧**：发言人2对Taylor Swift重新走红表示疑惑，认为其对九零后和零零后影响均深；发言人3则从演唱会感染力角度认可其表现，称「虽然听不懂，但氛围特别好」。
-# 待探讨问题与后续
-- **未确认**：发言人2对Taylor Swift（梅梅）中学时期走红、后因绯闻消沉、近期又重新火起来的原因表示疑惑，询问大家看法，发言人3认为其演唱有感染力、氛围好，但未形成定论。
-- **待核实**：发言人5提到单框架手机网易云音乐不适配，需用卓翼通解决，其他APP已适配，具体适配问题未展开讨论。
-- **未定论**：发言人2表示不太信任AI软件，不确定其回答是否正确，仍停留在浏览器、纸质地图和尺子铅笔标注的思维模式，与发言人3认为AI小助手回答更精准、总结性强的观点存在分歧，未达成一致。
-- **未确认**：发言人2提及欧美音乐平台虾扎有更多演唱会版本音乐，国内网易云因版权纠纷播不出大牌歌曲，该说法未获其他成员验证或讨论。
-- **未定论**：发言人2指出国内付费电视剧在YouTube上免费，但部分内容仍需付费，小网站因无版权纠纷可免费观看，相关版权问题未深入探讨。</t>
+          <t># 常用APP与音乐偏好闲聊会
+## 讨论议题与背景
+本次会议为多人闲聊，共5位发言人参与，围绕各自最常用的手机APP、视频播放器、音乐APP及对AI助手和Taylor Swift等话题展开讨论。话题由发言人1发起，从手机里最常用的三个APP切入，随后自然延伸到AI助手使用偏好、视频播放器广告问题、音乐APP选择及听歌习惯，最后聚焦于喜欢的歌手与Taylor Swift为何重新走红。讨论以分享观点为主，未形成统一结论，整体呈漫谈发散式推进，各议题间无明确边界，由发言者自由引出新话题。会议提及小布、豆包等AI助手，以及网易云、酷狗、虾扎等音乐平台，发言人2以「浏览器加地图测绘，用尺子标识的年代」自喻，表达对AI软件准确性的不确定。
+## 发言要点
+### 最常用的手机APP
+1. **常用APP分享**（发言人2）：常用知乎、小红书、谷歌。
+2. **常用APP分享**（发言人3）：常用微信、抖音、淘宝、京东等购物平台。
+3. **常用APP分享**（发言人4）：常用微信、小红书，并提及用手机自带的小布AI助手替代浏览器搜索。
+4. **常用APP分享**（发言人5）：B站和YouTube用得较多，希望工具能识别中英混杂内容。
+5. **AI助手与浏览器之争**（发言人3、发言人2）：发言人3认为AI助手回答更全面、精准、总结性强；发言人2表示仍停留在浏览器、纸质地图加尺子圆规铅笔标注的思维模式，不太确定AI软件是否说得对。
+### 视频播放器与广告问题
+1. **常用播放器**（发言人3）：常用腾讯视频、爱奇艺、优酷、芒果TV，会点进去看有没有想看的。
+2. **广告时长争议**（发言人2、发言人3、发言人5）：发言人2抱怨广告时间太长不愿等，用B站直接看；发言人3提到现在可看广告换取VIP时长；发言人5认为APP太多，不知道开哪个VIP。
+### 音乐APP与听歌习惯
+1. **音乐APP选择**（发言人5、发言人2）：发言人5常用网易云音乐，并提到单框架手机网易云不适配，需用卓翼通；发言人2以前用酷狗、酷我。
+2. **国外音乐平台**（发言人2）：提及国外平台虾扎，欧美演唱会版本比国内网易云更多，但大牌版权有纠纷播不出来，小众翻唱多一些。
+3. **听歌场景**（发言人4、发言人2）：发言人4在通勤路上听，需降噪耳机；发言人2觉得在柏林坐地铁听音乐代入感强，因地铁比较安静。
+### 喜欢的歌手与Taylor Swift
+1. **近期关注歌手**（发言人3）：刷到谢霆锋演Taylor Swift，喜欢谢霆锋，提到《玉蝴蝶》等老歌。
+2. **Taylor Swift重新走红之惑**（发言人2）：中学时（2010年代开头）Taylor Swift已火，后因绯闻消沉，最近又火，疑惑为何对九零后和零零后影响都深；提及《Speak Now》《Back To December》《Love Story》等歌及与猫头鹰之城主角亚当杨的绯闻。
+3. **全球影响力**（发言人4）：认为Taylor Swift确有全球影响力。
+## 共识形成
+1. **【达成共识】AI助手在回答全面性、精准度与总结性上优于浏览器**：发言人3提出AI小助手「更全面一点，回答的更精准一点，然后总结性比较强」，发言人1、发言人4、发言人5均表示已下载或使用豆包、小布等AI助手，发言人2虽持保留态度但未反驳该判断。
+2. **【核心分歧/待定取舍】对AI软件可靠性的信任程度**：发言人2明确表示「不太喜欢用这些AI软件，不太确定它是否说的是对的」，自述仍停留在「浏览器加地图测绘、用尺子标识的年代」，用「大家在用GPS，我还在用纸质地图加尺子、圆规和铅笔标注」作比；发言人3则认为AI助手回答更全面精准，双方在是否以AI助手替代传统搜索工具上立场不一。
+3. **【达成共识】大型视频平台广告过长是普遍痛点**：发言人2抱怨「广告时间太长了，我不愿意等」，倾向用B站直接观看；发言人3补充可通过看广告换取VIP时长，发言人5认为「APP太多了，都不知道开哪个」，对广告与会员机制均持负面态度。
+4. **【核心分歧/待定取舍】音乐平台选择与适配问题**：发言人5常用网易云音乐，但指出「单框架手机网易云一直不适配，现在全用卓翼通」；发言人2以前用酷狗、酷我，并提及国外平台虾扎有更多欧美演唱会版本，因版权纠纷部分内容播不出来；发言人1认为虾扎「唱的都是一些小众歌手」。
+## 待探讨问题与后续
+1. **未确认：AI助手回答的准确性**——发言人2表示不确定AI软件是否说得对，仍停留在浏览器、纸质地图和尺子铅笔标注的思维模式；发言人3则认为AI助手回答更全面、精准、总结性强，双方未就此达成一致。
+2. **未定论：Taylor Swift重新火起来的原因**——发言人2疑惑其为何在消沉后重新火起来，认为对九零后和零零后影响都很深；发言人3认为其演唱有感染力、氛围好，发言人4认为其有全球影响力，未形成统一解释。
+3. **待核实：单框架手机网易云不适配问题**——发言人5提到单框架手机网易云一直不适配，需用卓翼通，其他APP已适配，原因未展开讨论。
+4. **未确认：国外音乐平台虾扎的可用性**——发言人2提及虾扎有更多欧美演唱会版本，但发言人4指出YouTube手机一般翻不了墙，虾扎在国内是否可用未明确。
+5. **未定论：付费与免费观看渠道的取舍**——发言人1发现国内付费电视剧在YouTube上免费，发言人2认为大平台有版权纠纷需付费、小网站反而免费，但小网站有广告风险，未达成一致。</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>34.3</v>
+        <v>31.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4259/2708</t>
+          <t>4259/2322</t>
         </is>
       </c>
     </row>
@@ -16085,69 +16212,74 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t># 讲座概况
-本次讨论由主持人（发言人1）发起，围绕2022年俄乌战争爆发后俄军在战场上的实际表现展开，以多人自由座谈的形式进行，旨在探讨俄军表现是否为其真实状态，并交流对俄军及俄罗斯的认知。讨论覆盖四个板块：俄军在俄乌战争中的表现、游戏与媒体中的俄军形象、俄罗斯的地缘政治与欧洲认知、俄罗斯旅游与文化。核心判断包括：俄军单兵素质强但后勤和指挥拉垮，整体呈“矮脚巨人”状态；俄乌战争从闪电战演变为持久战，双方重装备耗光后变成“菜鸡互啄”；欧洲将乌克兰视为“欧洲之门”，支援乌克兰意在将俄罗斯挡在亚洲之外。讨论以2022年俄军进攻乌克兰、2014年克里米亚事件、圣彼得堡东宫等为锚点。对关注俄乌战局、俄罗斯地缘角色及文化认知的听众具有参考价值。
-# 核心观点与论证
-## 俄军表现与预期严重不符
-- **战前预期**：2022年俄乌战争爆发时，全世界认为战争天平会向俄罗斯一边倒，基辅会很快被占领，乌克兰会被消灭，泽连斯基会流亡。
-- **实际战况**：泽连斯基扛住俄罗斯进攻，反而把俄军从基辅打回白俄罗斯和乌克兰边境，剧情超出各方反转和认知。
-- **闪电战变持久战**：俄军第一批部队进入乌克兰时遭遇民兵自发抵抗而非军队有组织进攻，一来二去从闪电战变成持久战。
-- **战场形态退化**：双方重装备耗光，只能隔着战壕互相扔手雷或用无人机互炸，从钢铁洪流变成“菜鸡互啄”状态。
-## 俄军失利的深层原因
-- **普京信息茧房**：发言人1认为普京活在自己的信息茧房里，对战场真实情况缺乏准确认知。
-- **情报经费被贪污**：情报官员把用于策反乌克兰官员的经费全部贪污瓜分，普京真要进攻乌克兰时，乌克兰高官并未收到策反经费。
-- **乌克兰民族仇恨**：2014年俄罗斯占领克里米亚后，乌克兰上下迸发出民族仇恨，类似九一八事变“一枪不发丢掉整个克里米亚”的耻辱感，当权者的无能与腐败引发民众不满。
-- **基层官兵不知情**：俄军基层官兵不知道2022年会进攻乌克兰，许多部队收到命令以为是去演习，演着演着就进入了乌克兰。
-## 俄军单兵强而整体拉垮
-- **矮脚巨人比喻**：发言人1认为俄军单兵素质很厉害，但总体很拉垮，主要在后勤和指挥上，像柯基一样腿短支撑不起庞大身躯。
-- **战场进步有限**：发言人4认为俄乌战场打得跟二战时没啥进步，多了点无人机，但还是扔手雷互炸，不太先进。
-- **防守反击特点**：发言人4认为俄罗斯打仗得被打到要家破国亡才能迸发战斗力打防反，主动进攻感觉不行。
-## 游戏与媒体中的俄军形象被抹黑
-- **西方游戏塑造反派**：发言人2和4认为《红警》是美国为黑苏联而制作，游戏里苏联形象都是反派，很猛很变态，研究邪乎武器，规模非常夸张。
-- **心灵控制器隐喻**：发言人1举例《红警》中的心灵控制器，认为共产主义解放世界的思想被抹黑成心灵控制。
-- **形象360度反差**：发言人1指出《战地风云》《使命召唤》《红警》等游戏中的俄军或苏联红军形象，与现实俄军表现有360度反差。
-## 乌克兰的地缘战略价值
-- **欧洲之门**：乌克兰在欧洲人认知中被称为“欧洲之门”，欧洲人认为欧亚分界线在乌克兰而非乌拉尔山脉，因为白俄罗斯大部分是沼泽地，无法形成大规模运输通道走廊。
-- **俄罗斯立国依赖乌克兰**：乌克兰军队前身是苏联红军重要组成部分，俄罗斯立国靠乌克兰成为立国资本，没有乌克兰的俄罗斯帝国终究只是边缘亚洲国家。
-- **唇亡齿寒**：欧洲把乌克兰看得很重，明白唇亡齿寒的道理，要武装并守好乌克兰，把俄罗斯挡在亚洲之外。
-## 欧洲将俄罗斯视为“半兽人”
-- **蒙古统治历史**：俄罗斯人被蒙古人统治二百年，不被欧洲人认可接纳，被当成长着欧洲人面孔的亚洲游牧民族。
-- **冰封王座类比**：发言人1用《冰封王座》中贝加尔湖半兽人形象类比欧洲对俄罗斯的认知，指俄罗斯被当成亚洲野蛮人看待。
-- **东欧国家敌视**：在美国人认知中俄罗斯既非朋友也非敌人，但在波兰、乌克兰、波罗的海三国等东欧国家眼中，俄罗斯就是敌人、蛮子、半兽人。
-## 俄罗斯历史掠夺与文化艺术
-- **东宫藏品丰富**：发言人1推荐圣彼得堡东宫，称其为世界四大艺术博物馆之一，连续三次参观不同区域都没逛完馆藏珍宝。
-- **全球掠夺藏品**：俄罗斯以探险队名义从全球掠夺藏品，包括德国、法国、荷兰、朝鲜半岛、蒙古、西藏、西夏王陵、敦煌、阿富汗、中亚、埃及、北非、奥斯曼帝国土耳其等地。
-- **掠夺方式差异**：发言人1指出俄罗斯没像英法那样圆明园式掠夺，但二战结束后打进德国，把纳粹产品运回国内。
-# 金句总结
-&gt; “俄军单兵素质很厉害，但是总体就很拉垮，主要后勤和指挥上，就是矮脚巨人的感觉，是不是就有点像柯基的感觉，就是腿特别短，支撑不起他庞大的身子的那种感觉。”
-- 背景：总结俄军在俄乌战争中的整体表现，对比其单兵能力与后勤指挥短板。
+          <t># 俄乌战争俄军表现与俄罗斯认知探讨
+## 讲座概况
+本次讨论由主持人（发言人1）发起，围绕2022年俄罗斯进攻乌克兰后俄军在战场上的实际表现展开，旨在探讨俄军表现是否为其真实应有状态，并交流对俄军及俄罗斯的认知。讨论覆盖四个板块：俄军在俄乌战争中的表现、游戏与媒体中的俄军形象、俄罗斯的地缘政治与欧洲认知、俄罗斯文化与旅游印象。核心判断包括：俄军单兵素质强但整体拉垮，主要问题在后勤与指挥，被形容为“矮脚巨人”；普京活在自己的信息茧房里，情报官员贪污了策反乌克兰官员的经费；欧洲将乌克兰视为“欧洲之门”，因蒙古统治历史将俄罗斯视为“长着欧洲人面孔的亚洲游牧民族”，故自发支援乌克兰以阻挡俄罗斯。讨论以《红警》《战地风云》等游戏中的俄军形象、2014年克里米亚事件、圣彼得堡东宫等为锚点。对关注俄乌局势及俄罗斯认知的听众具有参考意义。
+## 核心观点与论证
+### 俄军表现与“钢铁洪流”印象的反差
+- 2022年俄乌战争爆发时，全世界普遍预期战争天平向俄罗斯一边倒、基辅很快被占领、泽连斯基流亡；实际泽连斯基扛住进攻，并将俄军从基辅打回白俄罗斯与乌克兰边境。
+- 发言人1总结：俄军单兵素质很厉害，但总体拉垮，主要问题在后勤和指挥，形容为“矮脚巨人”，像柯基一样腿短撑不起庞大身躯。
+- 发言人4认为俄乌战场与二战相比没多大进步，只多了无人机，双方重装备耗光后隔着战壕互相扔手雷、用无人机互炸，从“钢铁洪流”变成“菜鸡互啄”。
+- 俄罗斯无人机依赖伊朗提供，乌克兰由北约持续输血，发言人1类比为越战形式：乌克兰相当于北约，俄罗斯相当于越战时期的美国。
+### 俄军表现拉垮的原因
+- **信息茧房与腐败**：发言人1认为普京活在自己的信息茧房里；情报官员将用于策反乌克兰官员的经费全部贪污瓜分，普京却真去进攻乌克兰，导致乌克兰高官未收到策反经费。
+- **民族仇恨积累**：2014年俄罗斯占领克里米亚后，乌克兰上下迸发民族仇恨，发言人1类比为“九一八事变”式耻辱——一枪不发丢掉整个克里米亚，民众对政府无能与腐败不满。
+- **基层官兵不知情**：俄军基层官兵不知道2022年会进攻乌克兰，许多部队收到命令以为是演习，“演着演着就进乌克兰了”；第一批部队遭遇的是民兵自发抵抗，而非军队有组织进攻，闪电战由此变成持久战。
+- **防守反击强于主动进攻**：发言人4认为俄罗斯打仗要被打到“家破国亡”才能迸发战斗力、打防守反击；主动进攻表现差。
+### 游戏与媒体中的俄军形象
+- 游戏如《战地风云》《战地三》《使命召唤》《红警》中俄军或苏联红军形象，与现实中俄军表现有“360度”反差。
+- 发言人2认为《红警》是美国为黑苏联而做；发言人4指出这些游戏多由西方主导，苏联形象几乎都是反面、很猛很变态，研究邪乎武器、规模夸张。
+- 发言人1提到游戏把共产主义解放世界思想抹黑成“心灵控制器”，把苏联形容为暴力美学的形象代言。
+### 欧洲对俄罗斯的地缘认知
+- 乌克兰在欧洲人认知中被称为“欧洲之门”；欧洲人认为欧亚分界线在乌克兰，因白俄罗斯多为沼泽地、缺乏大规模运输通道，故把俄罗斯人当亚洲人看待。
+- 俄罗斯人被蒙古人统治过二百年，不被欧洲认可接纳，被视为“长着欧洲人面孔的亚洲游牧民族”，类似《冰封王座》中半兽人式反派角色。
+- 欧洲自发支援乌克兰、不让俄罗斯打赢，因为若俄罗斯握紧乌克兰，欧洲会“再一次生活在曾经的阴影之下”；这也是乌克兰死活不向俄罗斯妥协的根本原因。
+- 乌克兰军队前身是苏联红军重要组成部分，俄罗斯立国靠乌克兰为立国资本，因此俄罗斯必须把乌克兰握在手里；没有乌克兰的俄罗斯帝国“终究只是沦为边缘亚洲国家”。
+### 俄罗斯文化与旅游印象
+- 发言人1推荐圣彼得堡东宫，称其为世界四大艺术博物馆之一，连续去三次、分不同区域仍未逛完馆藏珍宝，建议夏天去圣彼得堡。
+- 东宫藏品来源多样：列强殖民战争掠夺、王室联姻赠送、二战打进德国后运回纳粹产品；往东涉及朝鲜半岛、蒙古、西藏、西夏王陵、敦煌，往南涉及阿富汗、中亚、埃及、北非、奥斯曼帝国与土耳其藏品。
+- 俄罗斯以俄罗斯族为主，其东扩类似美国西进运动，源源不断淘金移民；境内有多个共和国，但总体上仍是俄罗斯族主导。
+## 金句总结
+&gt; “俄军单兵素质很厉害，但是总体就很拉垮，主要后勤和指挥上，然后就是矮脚巨人的感觉，是不是就有点像柯基的感觉，就是腿特别短，支撑不起他庞大的身子的那种感觉。”
+&gt; —— **发言人1（主持人）** ｜ 针对俄军在俄乌战争中整体表现与单兵能力反差的定调发言
 &gt; “因为双方都把重装备给耗光了，所以说就只能隔着战壕互相扔手雷，或者是互相用无人机互炸，现在就是就是从一种钢铁洪流变成了最后的菜鸡互啄。”
-- 背景：描述俄乌战争从闪电战演变为持久战后的战场形态。
-&gt; “普京飘了，他活在他自己的一个信息茧房里边。”
-- 背景：分析俄军进攻乌克兰决策失误的根源，指出其情报与决策链条的失灵。
+&gt; —— **发言人1（主持人）** ｜ 针对俄乌战场当前作战形态的总结
+&gt; “普京飘了，他活在他自己的一个信息茧房里边，因为一开始的时候，他底下的情报官员把那个用于策反乌克兰官员的那些经费全部都给贪污瓜分了。”
+&gt; —— **发言人1（主持人）** ｜ 针对俄军进攻受挫背后原因的分析
+&gt; “乌克兰在欧洲人的认知里面是被称为欧洲之门……在欧洲人的认知里面，欧亚分界线在乌克兰那边。”
+&gt; —— **发言人1（主持人）** ｜ 针对欧洲地缘认知与乌克兰战略地位的阐释
+&gt; “终究是把俄罗斯人当成亚洲人来看待，就亚洲野蛮人……就是长着欧洲人面孔的亚洲游牧民族。”
+&gt; —— **发言人1（主持人）** ｜ 针对欧洲对俄罗斯身份认知的定调发言
 &gt; “没有乌克兰的俄罗斯帝国终究只是沦为边缘亚洲国家，这样不会被欧洲所待见的一个状态。”
-- 背景：解释俄罗斯必须控制乌克兰的地缘政治逻辑，以及欧洲支援乌克兰的动因。
-&gt; “在欧洲人的认知里面，欧亚分界线在乌克兰那边……他们终究是把俄罗斯人当成亚洲人来看待，就亚洲野蛮人。”
-- 背景：说明欧洲将乌克兰视为“欧洲之门”、将俄罗斯视为“半兽人”的历史与地理认知根源。
-&gt; “俄罗斯被蒙古人统治过二百年，所以就是他们不被欧洲人所认可、接纳，终究就是被当成是亚洲游牧民族来看待，就是长着欧洲人面孔的亚洲游牧民族。”
-- 背景：追溯欧洲对俄罗斯身份认知的历史成因，解释其被排斥于欧洲之外的原因。
-&gt; “乌克兰就相当于是北约，然后俄罗斯就相当于是越战时期的美国跟乌克兰就这么耗着。”
-- 背景：类比俄乌战争的消耗战性质，说明北约持续输血乌克兰的对抗格局。
-# Q&amp;A 环节
-**发言人4**：俄罗斯打仗是不是得被打到快家破国亡才能迸发战斗力，主动进攻感觉不行？
-**发言人1**：只能说是普京飘了，活在自己的信息茧房里。一开始情报官员把用于策反乌克兰官员的经费全部贪污瓜分了，没想到普京真会进攻乌克兰；加上2014年丢掉克里米亚后乌克兰上下有类似九一八的耻辱感，基层官兵还以为去演习，结果遭遇民兵自发抵抗，闪电战就拖成了持久战。
-**发言人4**：感觉俄乌战场跟二战比没啥进步，就多了点无人机，还是不太先进。
-**发言人1**：双方重装备都耗光了，只能隔着战壕扔手雷、用无人机互炸，从钢铁洪流变成菜鸡互啄；俄罗斯的无人机还靠伊朗给，乌克兰则有北约持续输血，类似越战形式。
-**发言人2**：去俄罗斯旅游后办美签会不会被拒？
-**发言人1**：会受影响。我上次去美国，在边境入口因为去过好几次俄罗斯被拦下来盘问，差点被怀疑是间谍；美国对咱们入境卡得严，欧洲尤其是波兰、乌克兰、波利海三国则把俄罗斯当敌人和蛮子看。</t>
+&gt; —— **发言人1（主持人）** ｜ 针对俄罗斯必须控制乌克兰的地缘逻辑
+&gt; “俄罗斯的无人机都是靠伊朗给他的……乌克兰它是由北约给它持续不断的输血，然后可以说是一种越战的那种形式。”
+&gt; —— **发言人1（主持人）** ｜ 针对俄乌双方外部支撑格局的类比
+&gt; “俄乌战场打的跟二战时候也没啥进步，多了点无人机，但还是欠好战。什么扔手雷的，在这打就是不太先进。”
+&gt; —— **发言人4（参与者）** ｜ 针对俄乌战场技术水平的评价
+## Q&amp;A 环节
+### Q1. 俄军表现是否是其真实状态
+- **听众**：俄军在俄乌战争中的表现，是否是其真正应有的状态？
+&gt; **发言人1**：不是。俄军单兵素质很厉害，但总体拉垮，主要问题在后勤和指挥上，像矮脚巨人——腿特别短，支撑不起庞大的身子，有点像柯基的感觉。
+### Q2. 俄军主动进攻为何表现差
+- **听众**：俄罗斯打仗感觉主动进攻时表现很差，这是为什么？
+&gt; **发言人1**：只能说是普京飘了，活在他自己的信息茧房里。一开始情报官员把用于策反乌克兰官员的经费全部贪污瓜分了，没想到普京真会进攻乌克兰，结果经费被贪后，乌克兰高官没收到策反款。加上2014年俄罗斯占领克里米亚后，乌克兰上下迸发出民族仇恨，类似九一八事变的耻辱感，一枪不发丢掉整个克里米亚，民众对政府无能与腐败非常不满。俄军基层官兵也不知道2022年会进攻乌克兰，好多部队收到命令以为是去演习，结果演着演着就进了乌克兰，第一批部队遭遇的是民兵自发抵抗，而不是军队有组织的进攻，一来二去从闪电战变成了持久战。
+### Q3. 俄乌战场为何像二战水平
+- **听众**：感觉俄乌战场打的跟二战时候也没啥进步，多了点无人机，还是扔手雷，不太先进？
+&gt; **发言人1**：因为双方都把重装备给耗光了，只能隔着战壕互相扔手雷，或者互相用无人机互炸，从钢铁洪流变成了菜鸡互啄。俄罗斯的无人机都是靠伊朗给的，乌克兰则是由北约持续输血，类似越战形式——乌克兰相当于北约，俄罗斯相当于越战时期的美国，就这么耗着。
+### Q4. 欧洲为何把俄罗斯当半兽人
+- **听众**：欧洲为什么把俄罗斯当成半兽人那种反派角色来看待？
+&gt; **发言人1**：因为俄罗斯人被蒙古人统治过二百年，不被欧洲人认可接纳，终究被当成亚洲游牧民族——长着欧洲人面孔的亚洲游牧民族。在欧洲人的认知里，欧亚分界线在乌克兰那边，白俄罗斯大部分是沼泽地，没法形成大规模运输通道走廊，所以欧洲和亚洲的边界始终在乌克兰这一块过渡地带。乌克兰在欧洲人认知中被称为欧洲之门，欧洲一定要守住乌克兰，把俄罗斯挡在亚洲之外，不让它涉足欧洲。如果俄罗斯握紧乌克兰，欧洲会再一次生活在曾经的阴影之下，这也是乌克兰死活不能向俄罗斯妥协的根本原因。
+### Q5. 俄罗斯东西部差异是否很大
+- **听众**：俄罗斯地域那么宽阔，远东地区和欧洲那头风格差别大吗？
+&gt; **发言人1**：总的来说还是以俄罗斯族为主，毕竟俄国东扩也像美国西进似的，源源不断地淘金移民。</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>48.6</v>
+        <v>45</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6103/3017</t>
+          <t>6103/3607</t>
         </is>
       </c>
     </row>
@@ -16249,50 +16381,58 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t># 讲座概况
-会议围绕电影《南京照相馆》展开，由主持人贝姐（发言人1）组织，与会者交流观影印象并探讨影片背后的南京大屠杀历史。讨论先由各发言人分享观感，随后主持人系统介绍1937年八一三淞沪抗战至南京沦陷的历史脉络，并澄清影片中虚构与真实的成分：主要人物为虚构，但照片拍摄真实，实际由两位美国传教士记录日军暴行，中国照片冲洗人员偷偷拷贝后于战后提交国民政府军事法庭作为审判证据。讨论还延伸至相关纪念馆参观经历，涉及沈阳伪满洲国博物馆、唐山大地震纪念馆、上海淞沪会战纪念馆及南京大屠杀纪念馆的参观热度。核心判断包括：八一三淞沪抗战是日军自九一八事变以来首次遭遇的迎头痛击；日军指挥官松井石根曾下令约束军纪，但因病被替换，接任的朝香宫鸠彦亲王发布“不留俘虏”命令，最终导致军纪失控与南京大屠杀。影片中中华门城墙战斗、挹江门撤退惨案及战后谷寿夫等日军军官被枪决均为真实历史。本场讨论面向对影片及抗战历史感兴趣的听众，有助于区分艺术虚构与史实依据。
-# 核心观点与论证
-## 电影主要人物虚构，照片拍摄真实
-- **照片来源**：真实历史中，日军暴行照片由两位美国传教士拍摄，而非电影中主角拍摄；同期中国照片冲洗人员无意间发现日军所摄暴行照片（当时在日本属禁文），偷偷拷贝藏起，抗战后递交国民政府军事法庭作为审判日本战犯的证据。
-- **人物设定**：电影中主角与日本军官建立友谊等情节属虚构，真实历史并非以电影所描述方式进行拍摄。
-## 日军攻破南京后军纪失控
-- **战前态势**：1937年8月13日国民党军队在上海与日军激战（八一三淞沪抗战），因实力原因撤退，日军从上海一路追击至南京；自1931年九一八事变以来，日军占领东北、华北均未遭遇成规模抵抗，八一三淞沪抗战是其首次迎头痛击。
-- **战场状态**：日军从上海打到南京历时约四个月，伤亡惨重、已“杀红眼”，缺乏纪律与军纪约束，攻破南京后无人性约束，导致南京大屠杀发生。
-- **指挥官更替**：原指挥官松井石根因生病被临时替换，他曾发布命令要求避免在上海至南京沿线烧杀抢掠，以防增强中国军民抵抗意志；接任者为裕仁亲王的叔叔朝香宫鸠彦亲王，是脱亚入欧思想的狂热追随者，认为亚洲除日本外皆低贱。
-- **屠杀命令**：朝香宫鸠彦亲王上任后发布第一道命令“不留俘虏”，日军从格杀俘虏蔓延至对老百姓施暴，最终导致南京大屠杀、日军军纪失控。
-## 电影中真实历史细节
-- **中华门战斗**：电影开头中华门城墙战斗是真实历史细节，反映日军进攻南京所遭受的抵抗。
-- **挹江门惨案**：电影中军队和平民撤退时，宪兵未让撤出，因守挹江门部队未收到撤退命令，两边信息差导致惨案发生。
-- **战后审判**：电影尾声审判为真实历史，打进南京的谷寿夫（第六师团师团长）等几名南京大屠杀主犯（基层日军军官）当时被枪决。
-## 国人对抗战历史关注度高
-- **沈阳伪满洲国博物馆**：发言人2上午前往，下午排队排不上，整个广场全是人，必须预约。
-- **唐山大地震纪念馆**：发言人2参观时情况类似，人很多。
-- **上海抗战纪念馆**：发言人3提到上海淞沪会战、四行仓库等纪念馆人很多，去的那天下大雨里面仍全是人，大人小孩都很多，认为上海宣传做得好。
-- **南京大屠杀纪念馆**：发言人3认为难抢票，发言人4表示多年前去过，当时还可以。
-# 金句总结
-&gt; “在战场上长达四个月的一个状态，然后已经杀红眼了，就是可以说是在战争底下那种就是人性的泯灭吧。”
-- 背景：解释日军从上海追击至南京后发生大屠杀的心理动因。
-&gt; “从他们当时那样的一个心态来说，就觉得自己遭受了一种前所未有的侮辱，以及在战场上的一种应激创伤反应。”
-- 背景：分析日军视角下对遭遇顽强抵抗后的心理反应。
-&gt; “攻破了敌方的城镇，都要以屠城来进行自己那种狂欢与麻痹。”
-- 背景：结合日本历史传统，解释攻破南京后屠城行为的文化根源。
-&gt; “从上到下那种高压武士道的精神那种，哦，就是欺凌与霸凌的这种背景之下，更想找一种宣泄口这种方式来发泄。”
-- 背景：剖析日军内部高压体制下士兵寻求发泄渠道导致暴行蔓延。
-&gt; “在他的眼里，就是整个亚洲国家除了日本以外，其他国家都是低贱的。”
-- 背景：描述接任指挥官朝香宫鸠彦亲王的立场，解释其“不留俘虏”命令的思想根源。
+          <t># 《南京照相馆》观影讨论与历史背景辨析
+## 讲座概况
+本次讨论由主持人贝姐（发言人1）发起，围绕电影《南京照相馆》展开，先交流观影印象，再介绍南京大屠杀的历史背景，并辨析影片中虚构与真实的历史细节。与会者包括发言人2、发言人3、发言人4、发言人5，各自分享了观影感受：有人通过抖音切片了解影片，有人认为其属灾难电影且结局老弱妇孺存活，也有人因题材沉重而未观看。主持人随后梳理了从1937年八一三淞沪抗战、国军撤退、日军追击至南京，到因军纪失控、战场应激及武士道精神等因素导致南京大屠杀的完整脉络。核心判断包括：影片主要人物为虚构，但照片拍摄真实——实为两位美国传教士拍摄日军暴行，另有中国照片冲洗人员偷偷拷贝日军禁文照片，战后提交国民政府军事法庭作为审判证据；影片中中华门城墙战斗、挹江门撤退信息差惨案、尾声谷寿夫等主犯被枪决均为真实历史。讨论还延伸至相关纪念馆参观经历，如沈阳伪满洲国博物馆、上海淞沪会战纪念馆及南京大屠杀纪念馆的预约与参观情况。本场讨论面向对历史题材电影及抗战史感兴趣的听众，有助于区分艺术创作与史实，增进对南京大屠杀历史细节的认知。
+## 核心观点与论证
+### 电影主要人物虚构，但照片拍摄真实
+- 电影中主角与日本军官建立友谊等情节为虚构，但照片拍摄本身真实，只是方式与电影描述不同。
+- 真实历史中，两位美国传教士拍摄了日军暴行照片。
+- 同时期，一名负责为日本人冲洗照片的中国后期人员，无意间发现日军拍摄的暴行照片（当时属日本禁文），偷偷拷贝并藏匿，抗战后提交给国民政府军事法庭，作为审判日本战犯的证据。
+### 日军攻破南京后军纪失控导致大屠杀
+- 1937年8月13日，国民党军队在上海与日军激战（八一三淞沪抗战），后因实力原因撤退，日军从上海一路追击至南京。
+- 自1931年九一八事变占领东北、七七事变占领华北以来，日军均未遭遇成规模抵抗；八一三淞沪抗战是日军入侵中国以来首次遭受迎头痛击，战场伤亡惨重、长达四个月，日军已“杀红眼”。
+- 日军攻破南京后，缺乏法律与军纪约束，导致惨无人道的南京大屠杀事件发生。
+### 日军指挥更替与“不留俘虏”命令
+- 原日军指挥官松井石根（老牌皇道派军人、了解中国）曾接连发布命令，要求避免在上海至南京沿线烧杀抢掠，因其认为此举会招致中国军民反感、增强抵抗意志。
+- 松井石根因生病被临时替换，接任者为裕仁亲王的叔叔朝香宫鸠彦亲王，此人极度追随日本“脱亚入欧”思想，认为亚洲国家除日本外皆低贱。
+- 朝香宫鸠彦上任后发布第一道命令“不留俘虏”，导致日军第一时间格杀勿论，随后蔓延至对老百姓的暴行，最终酿成南京大屠杀。
+### 电影中的真实历史细节
+- 电影开头中华门城墙的战斗为真实历史细节，反映日军进攻南京所遭受的抵抗。
+- 挹江门撤退时，守军未收到撤退命令，与撤退部队信息差造成惨案。
+- 电影尾声审判中，打进南京的部队主犯（如第六师团师团长谷寿夫及多名基层日军军官）被枪决，属真实历史。
+### 日军暴行心理动因
+- 日军自九一八事变以来未遭像样抵抗，在上海遭受迎头痛击后，从自身角度感到“前所未有的侮辱”及战场应激创伤反应。
+- 结合日本自古攻破敌方城镇即屠城的传统，日军以屠城进行狂欢与麻痹，心态为“兴许活不到战争结束，趁活着放纵自己”。
+- 日本从上到下高压武士道精神与欺凌霸凌背景，使日军更想寻找宣泄口发泄。
+## 金句总结
+&gt; “在战场上长达四个月的一个状态，然后已经杀红眼了，就是可以说是在战争底下那种人性的泯灭吧。”
+&gt; —— **发言人1（主持人）** ｜ 针对日军攻破南京后暴行成因的定调发言
+&gt; “从他们当时那样的一个心态来说，觉得遭受了一种前所未有的侮辱，以及在战场上的一种应激创伤反应。”
+&gt; —— **发言人1（主持人）** ｜ 分析日军在南京实施暴行的心理动因
 &gt; “果然他上任之后发布的第一道命令就是不留俘虏，月后祭坟。”
-- 背景：指出朝香宫鸠彦亲王接替松井石根后下达的导致大屠杀的直接命令。
-# Q&amp;A 环节
-**发言人4**：电影里面虚构的部分，是不是包括主角和一位日本军官建立友谊的情节？这个日本军官是否真实存在？
-**发言人1**：电影里的主要人物是虚构的，但照片的拍摄是真实的，只是方式与电影描述不同。真实历史中，两位美国传教士拍摄了日军暴行；同时，一位负责给日本人冲洗照片的中国后期人员无意间发现这些暴行照片，偷偷拷贝并藏起，战后提交给国民政府军事法庭作为审判日本战犯的证据。</t>
+&gt; —— **发言人1（主持人）** ｜ 针对朝香宫鸠彦亲王接任日军统帅后军纪失控的定调发言
+&gt; “真实的一个历史是，当时是两个美国的传教士，然后当时是拍摄的当时日军的这一块相关的一个暴行。”
+&gt; —— **发言人1（主持人）** ｜ 辨析电影虚构与真实历史时对照片来源的澄清
+&gt; “他偷偷拷贝了下来，藏起来了之后，然后是于抗战之后然后把这个递交给当时国民政府的军事法庭，就是作为审判日本战犯的一个证据。”
+&gt; —— **发言人1（主持人）** ｜ 说明中国照片冲洗人员保存日军暴行证据的真实经过
+&gt; “就是守义江门的部队没有收到撤退命令，然后导致的就是两边的部队互相，就是得到的情况和信息差不一样，最造成了最终最后的一个惨案。”
+&gt; —— **发言人1（主持人）** ｜ 针对电影中挹江门撤退惨案真实历史细节的说明
+## Q&amp;A 环节
+### Q1. 电影中虚构与真实内容的辨析
+- **听众**：电影里主角与一名日本军官建立友谊，这个情节是虚构的吗？有没有真实的日本军官原型？
+&gt; **主讲人**：电影主要人物是虚构的，但照片拍摄是真实的，只是并非以电影描述的方式进行。真实历史是两位美国传教士拍摄了日军暴行；同时期，一位负责给日本人冲洗照片的中国人员无意间发现这些日军拍摄的暴行照片（当时属日本禁文），偷偷拷贝藏起，抗战后提交给国民政府军事法庭，作为审判日本战犯的证据。
+### Q2. 电影中还有哪些细节是真实历史？
+- **听众**：除了照片，电影里还有哪些细节是历史上真实发生的？
+&gt; **主讲人**：电影开头中华门城墙的战斗是真实历史细节；挹江门撤退时，守军未收到撤退命令，与撤退部队信息差导致惨案，也是真实事件；电影尾声关于审判的部分，打进南京的几支部队主犯如谷寿夫（第六师团师团长）等被枪决，同样是真实历史。</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>39.5</v>
+        <v>39.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>4228/2063</t>
+          <t>4228/2397</t>
         </is>
       </c>
     </row>
@@ -16380,49 +16520,44 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t># 讨论议题与背景
-本次会议为自由讨论型，由发言人1主持，发言人2参与，共两人围绕日本国家概况展开漫谈式交流。讨论由主持人提出「谈一谈日本这个国家的一个概况，还有大家对日本的一个印象」开场，随后话题自然发散，先后涉及日本文化的历史阶段与本土化转型、天皇制度与君主立宪制比较、日本旅游与购物体验等议题。讨论以分享个人印象与知识为主，未形成统一结论。发言中提及日本文化经历大化改新、明治维新、和平宪法三次转折，以及1945年二战后麦克阿瑟进驻日本推动社会转型等关键时间点。讨论整体呈发散推进，由文化历史延伸至政治体制，再转入旅游购物话题，未按固定议程逐块展开。
-# 发言要点
-## 日本文化历史与印象
-- **发言人2**：读研时上过日本文化课，读过老舍《四世同堂》后，认为民族仇恨还是应该有一定影响；同时日本文化对中国影响很多。
-- **发言人1**：日本文化没有原创，是外来接收后本土化改进的转型；追问发言人2所指的日本文化具体是哪个历史阶段。
-- **发言人2**：指传统文化与现代文化艺术，如漆艺、茶艺等。
-- **发言人1**：漆器和茶艺源自唐朝吴越文化，日本在此基础上本土化转型。
-- **发言人1**：日本经历三次转折——古代大化改新、近代明治维新、二战后和平宪法转型；大化改新后向中国和朝鲜半岛学习，形成和服、制茶、漆器等传统。
-- **发言人1**：明治维新后日本向欧美列强看齐，引入英国和德国的法度；二战后美国制定和平宪法，社会结构大规模转型，向美国看齐，形成动漫、二次元、汽车工业和铁道工业等印象。
-- **发言人2**：听过一种评论——日本是岛国、气候不稳定，农业可能因海啸等灾害毁于一旦，所以民族性格容易极端。
-- **发言人1**：古代日本天皇对各地封建领主而言更像吉祥物，类似东汉末年、战国时期的天子；天皇不能退位，被当作神灵供奉，以精神层面控制老百姓。
-- **发言人1**：1945年二战结束后，美军统帅麦克阿瑟进驻日本，公开要求天皇在媒体和众人面前露面，让平民知道天皇是真人而非神灵，从精神上打破固有认知，推动社会转型。
-- **发言人2**：询问日本民众现在对天皇是否还有崇拜。
-- **发言人1**：现在没有了，类似英国和西班牙的君主立宪制，天皇是象征性存在，不能参与政治和国家事务；政治由国会和内阁选出首相执政。
-- **发言人1**：美国把日本改造成英美海洋法系的国家结构；天皇存在感不如英国国王，因为英国国王还是整个英联邦国家的名义元首，而日本只有本州岛范围，天皇无实权、靠政府养着。
-- **发言人1**：除日本、英国外，欧洲西班牙也有皇室，东南亚泰国也有；体制上与日本相近的是英国和西班牙。
-## 日本旅游与购物
-- **发言人1**：推荐日本城市长崎、东京、大阪；自己曾去过长崎，认为该城市融合了东方文化和中国文化的元素。
-- **发言人1**：东京有很多美食、购物、博物馆，秋叶原是动漫周边和手办的发源地，数码宝贝玩偶、铁甲小宝原装玩具、黑暗战路暴龙兽合金版都是秋叶原最早发行的。
-- **发言人1**：日本购物值得买奢侈品，价格便宜，还有Vintage Shop中古店（二手奢侈品商店）。
-- **发言人1**：中古店源于广场协议后日本泡沫经济一夜崩溃，失业上班族将高档大衣、西装、皮具、皮鞋等奢侈品二手寄卖，催生新产业；上海有很多中古店，能买到LV、Burberry、古奇等上个世纪知名大牌，女性款式多、男性款式相对少。
-- **发言人2**：买手办等不一定只去日本，法国、意大利、韩国也很多。
-- **发言人1**：法国、意大利、韩国都是女生买化妆品、名牌，男生买巧克力；感觉欧洲和日韩的巧克力都比国内好。
-- **发言人1**：个人在日本最喜欢爬山，去爬富士山、看古城、逛博物馆，如镰仓、京都、名古屋；偏爱镰仓夏天的气候，比较舒服。
-# 共识形成
-- **一致意见**：双方均认可日本文化对当代影响深远，且日本文化缺乏原创性，属于外来接收后的本土化改进；发言人1与发言人2对日本文化中漆器、茶道等传统标志性内容无异议。
-- **倾向性认识**：发言人1系统梳理日本文化三次转折——大化改新（向中国、朝鲜半岛学习，形成和服、制茶、漆器等传统）、明治维新（向欧美学习，引入英德法度）、二战后和平宪法转型（向美国看齐，形成动漫、汽车工业等当代印象）；发言人2对此未提出反对，并补充岛国气候不稳定导致民族性格易极端的观点，发言人1未反驳。
-- **主要分歧点**：发言人2认为民族仇恨应对日本印象「还是应该要有一点影响」；发言人1则认为中日民族仇恨「还没那么严重」，不及欧洲中亚地区民族仇恨之深，双方未就此统一。
-- **天皇制度认知**：发言人1明确天皇在历史上被视为「吉祥物」，二战后麦克阿瑟迫使其公开露面打破神格认知，现为无实权的君主立宪象征；发言人2以「他们现在的民众对天皇没有那种崇拜了，还是有吧？」表达疑问，发言人1以「没有了」回应并解释体制与英国、西班牙相近，双方就此达成一致。
-# 待探讨问题与后续
-- **未确认**：日本民众对天皇的崇拜是否还存在，发言人2提出此疑问，发言人1回应称已不存在，天皇现为象征性存在，但未提供调查数据或民意依据。
-- **待核实**：二次元一词的英文翻译，发言人1现场提问但无人给出答案，讨论未继续。
-- **未定论**：日本文化具体指哪一个历史阶段的日本文化，发言人1提出此问题，发言人2回应涵盖传统文化与现代文化艺术，但未明确界定具体时期。
-- **未定论**：日本民族性格是否因岛国气候不稳定而趋于极端，发言人2提出此观点，发言人1未明确赞同或反对，话题未深入展开。</t>
+          <t># 日本文化历史与旅游购物体验讨论会
+## 讨论议题与背景
+本次讨论由主持人（发言人1）发起，围绕日本国家概况、文化历史、社会结构及旅游购物体验展开自由交流，参与者为发言人2。讨论由主持人提出“谈一谈日本这个国家概况及大家印象”作为由头，随后逐块推进：先探讨日本文化的历史阶段与三次转折（大化改新、明治维新、二战后和平宪法转型），再论及天皇制度演变与君主立宪制比较，最后转向日本旅游与购物体验（含中古店产业由来）。整体以分享观点为主，未形成统一结论；讨论中穿插英语表达与自由联想，属漫谈发散型推进。原文涉及的关键锚点包括：日本文化三次转折、1945年二战后麦克阿瑟进驻日本、广场协议后泡沫经济崩溃催生中古店产业。
+## 发言要点
+### 日本文化历史与印象
+1. **【日本文化缺乏原创性，属外来文化本土化转型】**（发言人：发言人1）
+   - **核心主张**：日本文化没有自身原创，均为外来接收后的本土化改进。
+   - **支撑论据/案例**：日本文化经历三次转折——古代大化改新时期向中国和朝鲜半岛学习，形成和服、制茶、漆器等传统；近代明治维新时期向欧美列强看齐，引入英国和德国的法度；二战后美国制定和平宪法，推动社会结构转型。
+   - **观点碰撞/互动**：发言人2提及个人对日本文化的喜爱，包括读研时上过日本文化课程、读过老舍《四世同堂》，认为民族仇恨仍应有一定影响；发言人1回应称民族仇恨程度不及欧洲中亚地区严重。
+2. **【天皇制度演变与象征性存在】**（发言人：发言人1）
+   - **核心主张**：古代天皇对各地封建领主而言类似吉祥物，被供奉以在精神层面控制百姓。
+   - **支撑论据/案例**：1945年二战结束后，美军统帅麦克阿瑟进驻日本，公开要求天皇在媒体和众人面前露面，打破其神格认知，推动社会转型。
+   - **观点碰撞/互动**：发言人2询问民众现在对天皇是否还有崇拜；发言人1回应称已无崇拜，天皇为君主立宪制下的象征性存在，无实权，由国会和内阁选出首相执政，与英国、西班牙体制相近，但天皇存在感弱于英国国王（因英国国王还是英联邦国家名义元首）。
+### 日本旅游与购物体验
+1. **【日本旅游偏好：登山、古城与博物馆】**（发言人：发言人1）
+   - **核心主张**：个人喜欢去日本爬山、看古城和逛博物馆。
+   - **支撑论据/案例**：具体偏好包括爬富士山、去镰仓（Kamakura）、京都（Kyoto）等关西地区古城，喜欢镰仓夏天的气候。
+2. **【日本购物推荐与中古店产业起源】**（发言人：发言人1）
+   - **核心主张**：日本购物推荐包括奢侈品、中古店（Vintage shop）、手办、化妆品等。
+   - **支撑论据/案例**：中古店产业源于广场协议后泡沫经济一夜崩溃，失业上班族将原先购买的高档大衣、西装、皮具等通过二手回收方式寄卖，催生新产业；上海也有此类商店，可买到LV、Burberry、古奇等品牌。
+   - **观点碰撞/互动**：发言人2补充购物可买化妆品、美妆、玩具等；发言人1提及秋叶原曾发行数码宝贝、铁甲小宝等动漫玩偶合金版，但称秋叶原现在不太行。
+## 共识形成
+1. **【达成共识】日本文化属外来文化本土化转型**：发言人1与发言人2均认可日本文化缺乏原创性，系在吸收外来文化基础上进行本土化改进，并一致认同日本文化对中国影响较深。发言人1系统梳理日本文化三次关键转折：古代大化改新时期向中国和朝鲜半岛学习，形成和服、制茶、漆器等传统；近代明治维新时期向欧美列强看齐，引入英国和德国的法度；二战后美国制定和平宪法，推动社会结构转型。**天皇制度在二战后由神格化转为象征性存在**，当前日本为君主立宪制，天皇无实权，由国会和内阁选出首相执政，与英国、西班牙体制相近，但天皇存在感弱于英国国王。
+2. **【核心分歧/待定取舍】民族仇恨对日本文化态度的影响程度**：发言人2表示读《四世同堂》后认为民族仇恨应对日本文化态度有所影响；发言人1回应称民族仇恨影响没那么严重，并对比欧洲、中亚民族仇恨更为严峻。双方未就此达成统一意见，仅形成倾向性认识——民族仇恨存在但程度判断不一。另就日本民众当前对天皇是否仍有崇拜，发言人2提出疑问，发言人1明确回应称已无崇拜，天皇仅为象征性存在。
+## 待探讨问题与后续
+1. **未确认：日本民众现在对天皇是否还有崇拜**——发言人2提出此疑问，发言人1回应称已无崇拜，天皇为象征性存在，但此判断仅为个人观点，未提供调查或数据支撑。
+2. **未确认：二次元用英语怎么说**——发言人1在讨论中提出此问题，现场无人给出明确答案，话题随即转向其他内容。
+3. **未定论：日本文化具体指哪个历史阶段**——发言人1追问发言人2所指日本文化属于哪个时期，发言人2回应涵盖传统文化与现代文化艺术，但未明确界定具体阶段。
+4. **未定论：日本民族性格与岛国地理环境的关系**——发言人2提出日本因岛国气候不稳定导致民族性格易极端的观点，发言人1未明确赞同或反驳，该观点未获进一步论证。
+5. **未确认：中古店产业与广场协议的直接关联**——发言人1称中古店源于广场协议后泡沫经济崩溃、失业者寄卖奢侈品，但未提供具体数据或史料佐证。</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>33.9</v>
+        <v>31.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>4892/2339</t>
+          <t>4892/2193</t>
         </is>
       </c>
     </row>
@@ -16634,51 +16769,69 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t># 讨论议题与背景
-本次会议为五人参与的文学延伸讨论（发言人1至发言人5），由主持人发言人1提议，在先前聊过《西游记》的基础上继续展开，先围绕《三国演义》与三国正史进行讨论，随后转向《红楼梦》的解读与续书问题。三国部分涉及诸葛亮去世后的正史脉络（姜维北伐、孙权二宫之争、邓艾偷渡阴平、刘禅投降、西晋灭吴）、阵营偏好、借荆州与湘水划界、白衣渡江、东吴大都督结局、姜维与魏延评价、三顾茅庐与隆中对等议题；红楼梦部分涉及前八十回与后四十回作者差异、第五回判词、晴雯与袭人的人物对应、反清复明解读及高鹗续书为何成为官方结尾等问题。整体以分享观点为主，未形成统一结论；讨论按三国、红楼梦两大议题逐块推进，穿插成员间的补充与追问，最后因时间关系由主持人暂停，计划继续下一个话题。
-# 发言要点
-## 三国演义与正史讨论
-- **发言人2**：三国到诸葛亮去世基本就结束了，后面没意思，也没看完；受《三国演义》影响，偏好蜀汉刘备阵营，认为刘备算白手起家。
-- **发言人1**：正史后续还有姜维北伐、孙权二宫之争（晚年昏庸害死两个儿子致东吴大乱）、邓艾偷渡阴平、姜维反间计自爆、刘禅投降、西晋灭吴。
-- **发言人1**：刘备称汉中王在封建礼治时期不妥，引发连锁反应——吕蒙白衣渡江、刘备伐吴失败（夷陵惨败）。
-- **发言人1**：借荆州事件中，孙权只要求归还部分地区，刘备不乐意；孙权派兵强夺荆南三郡，后因曹操攻汉中，双方签湘水划界（湘水之盟）。
-- **发言人1**：鲁肃与关羽各带随从在中立区谈判，被罗贯中美化为「关云长单刀赴会」；刘备此举耗尽孙刘联盟信任。
-- **发言人2**：白衣渡江伪装商人突破底线，开了坏头，吕蒙口碑差；**发言人1**补充后世将「小偷鼠辈」与吕蒙画等号。
-- **发言人1**：东吴大都督结局——周瑜被曹军射毒箭阵亡、鲁肃瘟疫病故、吕蒙病故、陆逊在二宫之争时因问责孙权被活活逼死。
-- **发言人1**：姜维是魏国降将，若非诸葛亮提拔在蜀汉缺乏说服力；刘禅轻信黄皓谗言，姜维后期无力回天。
-- **发言人1**：魏延正史无谋反之心，只是不甘大军撤退，烧毁栈道；若非姜维断后挡住司马懿，后果严重，行为与谋反无异。
-- **发言人5**：三顾茅庐——刘备中原屡战屡败，经推荐得知诸葛亮，携关羽、张飞三次拜访，诸葛亮提出隆中对战略（联合孙权），同意辅佐。
-- **发言人1**：隆中对「横跨荆益、外结好孙权」在白衣渡江后自相矛盾；北伐目标转向关中、陇西，第一次北伐因马谡失街亭破产，此后北伐只是绝望中的抗争。
-## 红楼梦解读与续书讨论
-- **发言人4**：红楼梦可当爱情小说看，讲贾宝玉、薛宝钗、林黛玉爱情故事，巧在是没有解开的谜底。
-- **发言人3**：只写了前八十回，后四十回是别人续的；**发言人2**提及有「反清复明」版本解读。
-- **发言人4**：初读高鹗续本觉得合理，后知后四十回非同一作者；反复读前八十回后，发现林黛玉性格和贾母态度变化明显。
-- **发言人3**：第五回贾宝玉梦游太虚幻境，判词已交代结局；**发言人4**补充判词未点明，探春、史湘云结局都是猜的。
-- **发言人4**：晴雯是林黛玉的替身，袭人性格像薛宝钗；晴雯之死是曹雪芹原作所写，映照后续。
-- **发言人2**：有解读称林黛玉代表明朝、薛宝钗代表清朝；**发言人4**补充还有人解读秦可卿是前朝公主。
-- **发言人4**：判词在第五回，分正钗和副钗，正钗对应小姐、副钗对应丫鬟，对应每个人命运。
-- **发言人2**：询问为何选高鹗后四十回作为官方结尾；**发言人4**解释官方说法是其在残稿上梳理完善，未违背作者原意，但诗词能力不及曹雪芹。
-- **发言人2**：提及植物园附近有曹雪芹小道；**发言人3**补充在北苑所旁边村子，之前爬山看到过。
-# 共识形成
-- **一致意见**：三国部分，发言人2与发言人1均认为诸葛亮去世后三国故事基本结束，后续内容无太大意义；对吕蒙白衣渡江，发言人1与发言人2一致认为其伪装商人偷袭盟友突破底线、开了坏头，导致吕蒙后世口碑差。红楼梦部分，发言人3与发言人4一致确认**红楼梦前八十回为曹雪芹原作，后四十回为他人续写**；发言人4与发言人3均认可第五回判词已预示人物结局，但探春、史湘云等具体结局仍属猜测。
-- **倾向性认识**：发言人1认为刘备称汉中王是引发孙刘决裂的连锁反应起点，导致白衣渡江与夷陵惨败；发言人2受演义影响倾向蜀汉阵营，未对此提出异议。发言人4认为晴雯是林黛玉的替身、袭人性格似薛宝钗，晴雯之死为曹雪芹原作所写，发言人3未表异议。
-- **主要分歧点**：关于魏延，发言人1主张其无谋反之心，但烧毁栈道的行为与谋反无异；发言人2仅提及魏延被砍，未展开反驳。关于红楼梦结局，发言人2提出林黛玉代表明朝、薛宝钗代表清朝的解读，发言人4未明确认同，仅提及秦可卿为前朝公主的解读。关于高鹗续书，发言人2质疑其为何成为官方结尾，发言人4解释官方说法为未违背作者原意，双方未就此达成一致。
-# 待探讨问题与后续
+          <t># 三国演义与红楼梦文学讨论会
+## 讨论议题与背景
+本次讨论由主持人（发言人1）发起，延续此前《西游记》话题，将文学讨论延伸至《三国演义》与《红楼梦》。参会成员共5人（发言人1至发言人5），以漫谈分享形式展开。讨论围绕两大议题推进：其一为《三国演义》及正史人物，涉及赤壁之战、蜀汉阵营偏好、刘备称汉中王引发的连锁反应（吕蒙白衣渡江、夷陵惨败）、借荆州与湘水之盟、鲁肃关羽单刀赴会、白衣渡江的争议、东吴大都督结局、姜维北伐困境及魏延烧栈道事件；其二为《红楼梦》解读，涉及前八十回与后四十回作者差异、林黛玉性格变化、第五回判词预示结局、晴雯之死映照黛玉命运、金陵十二钗判词体系及高鹗续书作为官方结尾的合理性。整体以分享观点为主，未形成统一结论；讨论按议题逐块推进，先三国后红楼，由主持人引导话题转换。
+## 发言要点
+### 三国演义与正史讨论
+1. **【三国整体印象】讨论核心**（发言人：发言人2）
+   - **核心主张**：三国到诸葛亮去世就基本结束，后面没意思，自己没看完。
+   - **支撑论据/案例**：诸葛亮去世时故事已进行到八九成，后面内容缺乏吸引力。
+2. **【正史刘备评价】讨论核心**（发言人：发言人1）
+   - **核心主张**：刘备贸然称汉中王引发连锁反应，导致孙刘联盟破裂。
+   - **支撑论据/案例**：称王后孙权不再信任刘备，引发吕蒙白衣渡江、刘备伐吴失败即夷陵惨败；刘备借南郡不还，孙权派兵夺荆南三郡，后双方签订湘水之盟（湘水划界）。
+3. **【单刀赴会史实】讨论核心**（发言人：发言人1）
+   - **核心主张**：正史中鲁肃与关羽各自不带兵士、带随从在中立区谈判，被罗贯中美化为关云长只身赴险单刀赴会。
+   - **观点碰撞/互动**：发言人2表示认同，未提出异议。
+4. **【白衣渡江评价】讨论核心**（发言人：发言人2）
+   - **核心主张**：白衣渡江伪装成商人偷袭盟友，突破古代战争道德底线，开了坏头。
+   - **支撑论据/案例**：吕蒙此举使后世将「小偷鼠辈」与吕蒙画等号；发言人1补充当时双方仍是盟友，偷盟友之家口碑极差。
+5. **【东吴大都督结局】讨论核心**（发言人：发言人1）
+   - **核心主张**：东吴四位大都督结局均不佳。
+   - **支撑论据/案例**：周瑜正史中被曹军射毒箭阵亡；鲁肃因瘟疫病故；吕蒙病故；陆逊在二宫之争时因问责孙权立太子问题被活活逼死。
+6. **【蜀汉内部矛盾】讨论核心**（发言人：发言人1）
+   - **核心主张**：姜维作为魏国降将，在蜀汉内部缺乏说服力，诸葛亮去世后难以力挽狂澜。
+   - **支撑论据/案例**：刘禅轻信黄皓谗言；姜维若非诸葛亮提拔，在阵营内没有威信，众人不服。
+7. **【魏延之死辨析】讨论核心**（发言人：发言人1）
+   - **核心主张**：魏延没有反心，但其行为与谋反无异。
+   - **支撑论据/案例**：魏延因与杨仪个人矛盾，不甘心大军撤退，烧毁悬崖栈道；若非姜维断后挡住司马懿军队，后果不堪设想，最终众人对其产生反心。
+8. **【三顾茅庐与隆中对】讨论核心**（发言人：发言人5）
+   - **核心主张**：刘备三顾茅庐请出诸葛亮，诸葛亮提出隆中对战略。
+   - **支撑论据/案例**：刘备中原屡战屡败，经人推荐得知诸葛亮有卧龙之才，携关羽、张飞三次拜访，前两次未遇，第三次打动诸葛亮，提出联合孙权的隆中对战略。
+9. **【隆中对破产分析】讨论核心**（发言人：发言人1）
+   - **核心主张**：白衣渡江后蜀汉失去荆州全境，隆中对「横跨荆益、外结好孙权」战略自相矛盾。
+   - **支撑论据/案例**：结好孙权则荆州要不回来；诸葛亮北伐目标转向关中平原和陇西，第一次北伐因马谡兵败街亭而破产，后期北伐沦为绝望中的抗争，只能拖延魏国灭蜀时间。
+### 红楼梦解读与续书讨论
+1. **【红楼梦版本问题】讨论核心**（发言人：发言人3）
+   - **核心主张**：红楼梦只写了前八十回，后四十回为他人续写。
+   - **观点碰撞/互动**：发言人2补充有版本解读涉及反清复明，但真正意义与当时社会有关；发言人4表示第一遍读高鹗续书版本时觉得合理，知道作者不同后反复读前八十回，发现林黛玉性格变化很大。
+2. **【判词与结局预示】讨论核心**（发言人：发言人3）
+   - **核心主张**：第五回贾宝玉梦游太虚幻境已用判词形式交代结局。
+   - **支撑论据/案例**：发言人4补充判词未点明具体结局，探春、史湘云结局及最终谁与贾宝玉在一起均为猜测；金陵十二钗正钗对应小姐、副钗对应丫鬟，判词对应每个人命运。
+3. **【晴雯之死与黛玉映照】讨论核心**（发言人：发言人4）
+   - **核心主张**：晴雯之死是曹雪芹原作所写，映照林黛玉命运。
+   - **支撑论据/案例**：晴雯性格像林黛玉，袭人性格像薛宝钗；发言人2提到有解读认为林黛玉代表明朝、薛宝钗代表清朝，发言人4补充有人解读秦可卿为前朝公主。
+4. **【高鹗续书官方地位】讨论核心**（发言人：发言人2）
+   - **核心主张**：询问为何选高鹗后四十回作为四大名著官方结尾。
+   - **支撑论据/案例**：发言人4回应官方说法是高鹗在残稿基础上梳理完善，未违背作者原意，但写作细节与诗词能力不及曹雪芹。
+## 共识形成
+1. **【达成共识】三国部分以正史与演义对照为讨论主线**：发言人1多次补充正史细节（刘备称汉中王引发连锁反应、湘水之盟、鲁肃与关羽单刀赴会、东吴大都督结局、姜维降将身份、魏延烧栈道），发言人2、发言人5以演义印象回应（赤壁之战、蜀汉阵营、三顾茅庐），双方在「演义与正史存在差异」这一方向上形成一致认识，未出现对立主张。关键产出：**发言人1系统梳理了刘备称王→孙刘联盟破裂→白衣渡江→夷陵惨败的因果链**，并指出鲁肃与关羽单刀赴会被罗贯中美化为关云长单刀赴会。
+2. **【核心分歧/待定取舍】红楼梦后四十回续书是否合理**：发言人4认为高鹗续书「总体来说还是比较合理」，官方说法是「没有违背作者原意」，但承认其诗词能力不及曹雪芹；发言人2则质疑「为啥最终选高鹗的后四十回作为官方结尾」，并提到有解读认为林黛玉代表明朝、薛宝钗代表清朝。分歧本质在于：续书是否忠实于原作意图——发言人4以「前八十回反复读后再接触续书，林黛玉性格变化很大」为据，发言人2以「后四十回照着判词写但看不太明白」为疑，双方未达成统一意见。
 ## 待探讨问题与后续
-- **未定论**：红楼梦后四十回为何选高鹗版本作为官方结尾？发言人2提出疑问，发言人4解释官方说法是未违背作者原意，但未形成定论。
-- **未确认**：红楼梦结局中谁与贾宝玉在一起？发言人4指出探春、史湘云结局及最终婚配对象均为猜测，判词未点明。
-- **未确认**：红楼梦是否存在反清复明寓意？发言人2提及解读称林黛玉代表明朝、薛宝钗代表清朝，发言人4补充有人解读秦可卿为前朝公主，均属民间解读，未获确认。
-- **未定论**：三国中刘备称汉中王是否直接导致孙刘联盟破裂？发言人1提出此观点并分析连锁反应，发言人2未明确回应，讨论未深入。
-- **待核实**：曹雪芹小道及故居位置。发言人2提及植物园附近有曹雪芹小道，发言人3称在北苑所旁边村子见过，发言人4提到北京植物园内有其故居，具体位置未核实。
-因时间关系，主持人发言人1暂停讨论，计划下一个话题继续，未约定具体时间与内容。</t>
+1. **未定论：红楼梦后四十回为何选高鹗续书作为官方结尾**——发言人2提出疑问，发言人4回应称官方说法是其在残稿基础上梳理完善、未违背作者原意，但诗词能力不及曹雪芹，此解释是否成立仍属开放讨论。
+2. **未定论：探春、史湘云的结局及最终谁与贾宝玉在一起**——发言人4指出判词未点明具体结局，这些人物归宿均系猜测，无定论。
+3. **未确认：林黛玉是否代表明朝、薛宝钗是否代表清朝**——发言人2提到有解读持此说，发言人1补充为「明清」对应，但未获与会者确认或展开论证。
+4. **未确认：秦可卿为前朝公主的解读**——发言人4提及有人作此解读，未展开讨论，亦无结论。
+5. **待核实：曹雪芹小道及故居位置**——发言人2提到曾去过一处有曹雪芹小道的地方，发言人3称在北京植物园北苑所旁村子见过，发言人4表示植物园内有其故居，具体位置与史实待核实。
+6. **未定论：三国正史中刘备称汉中王是否引发孙刘决裂的连锁反应**——发言人1主张刘备贸然称王不妥，导致吕蒙白衣渡江、夷陵惨败；此因果判断属个人分析，未获其他成员明确认同或反驳。</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>46.3</v>
+        <v>44.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6453/2502</t>
+          <t>6453/3207</t>
         </is>
       </c>
     </row>
@@ -16794,53 +16947,61 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t># 讨论议题与背景
-本次讨论由发言人1主持，从兵法和战法角度切入，围绕三国经典战役的影响及人物评价展开漫谈式交流，发言人2、发言人3参与。议题依次涉及赤壁之战曹军失利原因、东吴北伐路线与合肥之战、火烧连营与陆逊、孙权与刘备等人物评价、武将战力比较，以及诸葛亮北伐中魏延守街亭的假设性讨论。整体以分享观点为主，未形成统一结论；发言人多以讲述史实细节和提出个人判断推进，偶有相互追问与补充。讨论中提及公元215年合肥之战、张辽率800死士大破孙权、火烧连营七百里等关键节点，并以“孙十万”“生子当如孙仲谋”等典故作为评价锚点。
-# 发言要点
-## 赤壁之战的影响
-- **发言人1**：赤壁之战曹军失败主要因主力虎豹骑擅长陆战，刚收服荆州没有像样水军，不敌以水军为主的东吴，类比为渡海攻坚战、两栖登陆打海战的规格。
-- **发言人2**：对赤壁之战影响表示「不好说」，未展开具体观点。
-## 合肥之战与东吴北伐
-- **发言人1**：东吴北伐必须经过合肥——从建业（今南京）过长江到江北，走小河到巢湖，上岸打下合肥后才能靠近淮河，进而连接徐州、鲁西南直至海河一带；孙权一生多次攻打合肥未果。
-- **发言人1**：公元215年合肥之战，孙权动员所有武将从巢湖进攻合肥；当时曹军主力在攻汉中，合肥仅有张辽、李典、乐进三将镇守，且三人矛盾深重——张辽原为吕布部下，与乐进、李典不和。
-- **发言人1**：张辽率800死士骑马向吴军冲锋，孙权大败而归，由此产生「张八百大破孙十万」的段子；孙权差点被俘——张辽、李典不认识孙权，战后问被俘吴军「马骑得好、箭射得准、上半身长下半身短、长小胡子的人是谁」，得知是孙权后后悔没抓住。
-- **发言人1**：张辽威震合肥，城内小孩不敢啼哭；后人吐槽孙权「正面打敌人打不过，偷盟友的家」，称其为「合肥战神孙十万」。
-- **发言人1**：今南京紫金山孙权墓确切位置已找不着，只立碑写「此地可能就是孙权墓的大概位置」，碑前堆满张辽的影视海报和游戏卡片。
-- **发言人3**：孙权在「孙十万」之前也打过败仗——孙策刚死时，孙权率几万人打刘繇（原文未确认具体人名），被对方几千人追着打。
-- **发言人1**：赤壁之战后曹军以骑兵为主遇大江大河打不了水战，吴军擅长划船、摇橹、游泳但上岸没法打，双方僵持不下——不是曹军实力不行，而是骑兵没法打水战。
-## 火烧连营与陆逊
-- **发言人1**：刘备体恤下属，不忍士兵在酷暑中受折磨，让士兵在密林扎营避暑；陆逊抓住秋季干燥、树叶飘落的时机，在秋老虎时期一口气放火，连营七百里被烧得子虚乌有，刘备只身逃回白帝城。
-- **发言人2**：提出「陆逊和孙家有仇」的说法，但表示「陆家和孙家没听过」。
-- **发言人1**：陆逊为江东四杰之一；孙策、孙坚是外来户，孙策被称为小霸王、太冒失，后来被刺杀。
-## 三国人物评价
-- **发言人1**：曹操说「生子当如孙仲谋」，因孙策把位置传给弟弟孙权——孙权开疆拓土能力不行，但能守住家业，对比曹操的几个儿子是最争气的一个。
-- **发言人3**：从南往北打不好找先例，除了朱元璋打过去，剩下能守住首都就不错了；孙权打仗打得挺颓，刘备至少汉中之战打得挺好。
-- **发言人1**：刘备在夷陵之战（火烧连营）被仇恨冲昏头脑、冒进；汉中之战靠法正和黄权辅佐，凭地势地利把曹操耗出汉中，勉强打赢。
-- **发言人1**：关羽很厉害，曾水淹七军、阵中斩将（历史第一个阵中斩将直接改变战场局势的人），失败是阵营内队友不争气，不是能力不行。
-- **发言人3**：关羽打过啥只知道水淹七军；斩颜良诛文丑是个人战力，不算部队打仗；黄忠阵斩夏侯渊与关羽不同——关羽是摆好阵后斩将，黄忠可能是从山上冲下来。
-- **发言人3**：张飞不知道有什么经典战役，只知道长坂坡。
-- **发言人1**：张飞在演义里与马超在成都城下大战五百回合。
-- **发言人1**：曹魏五子良将包括张辽（从吕布降过来）、曹仁、夏侯渊、张郃、徐晃、于禁（后被关羽生擒）；曹操底下人多血厚，比较能耗得起。
-## 北伐策略讨论
-- **发言人1**：若诸葛亮第一次北伐用魏延守街亭，大概率能把张郃反杀回去，不会像马谡那样轻易丢掉街亭，第一次北伐可能就成功；魏延想法大胆，但不符合蜀汉当时的实际支撑。
-- **发言人3**：蜀汉地盘太小。
-# 共识形成
-- **一致意见**：赤壁之战曹军失败主要因其主力虎豹骑擅长陆战、不擅水战，东吴以水军为主，曹军无法渡江，类比为渡海攻坚战；东吴北伐必须经过合肥、从巢湖上岸，孙权一生多次攻打合肥未果，公元215年合肥之战张辽率800死士大破孙权大军，孙权差点被俘，后人称其为“孙十万”。
-- **倾向性认识**：对蜀汉和曹魏印象更好，孙权因“偷家”行为被吐槽；刘备在夷陵之战中因仇恨冒进，汉中之战靠法正、黄权辅佐获胜；关羽战力强，曾水淹七军、阵中斩将，但队友不争气；张飞无经典战役，仅知长坂坡；五子良将包括张辽、曹仁、夏侯渊、张郃、徐晃、于禁。
-- **主要分歧点**：发言人1认为若诸葛亮第一次北伐用魏延守街亭，可能反杀张郃，但魏延想法大胆不符合蜀汉实际支撑；发言人3补充蜀汉地盘太小，未对魏延方案明确表态。
-# 待探讨问题与后续
-- **未确认**：发言人3提到的孙权早期败绩的具体对手是谁，其本人未能回忆出名字，仅记得是孙策刚死时期、赤壁之战前，孙权率数万人被对方几千人追打；发言人1先后猜测刘表、张辽、曹仁、刘琦等，均未获发言人3确认。
-- **未定论**：关羽与黄忠阵中斩将的含金量比较——发言人3认为关羽是摆好阵后阵中斩将、直接改变战场局势，黄忠斩夏侯渊可能是从山上冲下，两者不完全一样，未进一步展开。
-- **未定论**：张飞是否有经典战役——发言人3表示只知长坂坡，未想到其他战例，讨论未继续深入。
-- **未定论**：若诸葛亮第一次北伐用魏延守街亭能否成功——发言人1认为大概率能反杀张郃、北伐可能成功，但魏延想法大胆不符合蜀汉实际支撑；发言人3补充蜀汉地盘太小，未形成一致结论。</t>
+          <t># 三国经典战役与将领能力讨论
+## 讨论议题与背景
+本次会议为三国经典战役与将领能力的漫谈式讨论，由发言人1主持，发言人2、发言人3参与，共3人。讨论由此前《红楼梦》《三国》《水浒》《西游记》《金瓶梅》的延伸话题引入，聚焦从兵法和战法角度分析赤壁之战、合肥之战、火烧连营等战役，并延伸至孙权、刘备、关羽、张飞及曹魏五子良将等人物评价。议题范围包括：赤壁之战与合肥之战分析、火烧连营与陆逊评价、孙权与刘备军事能力评价、曹魏将领与诸葛亮北伐讨论。整体以分享观点为主，未形成统一结论；讨论按议题逐块推进，由发言人1主导讲述史实并引导提问，发言人2、发言人3穿插补充与质疑。关键锚点包括公元215年合肥之战、张辽率800死士大破孙权军队（“张八百大破孙十万”）、火烧连营七百里。
+## 发言要点
+### 赤壁之战与合肥之战分析
+1. **【赤壁之战败因】曹军不擅水战**（发言人：发言人1）
+   - **核心主张**：赤壁之战曹军失败非实力不济，而是以虎豹骑为主的骑兵不擅水战。
+   - **支撑论据/案例**：曹操刚收服荆州，无像样水军；江东以水军为主，双方各擅其长，长江天险形成僵持。
+2. **【合肥之战】张八百大破孙十万**（发言人：发言人1）
+   - **核心主张**：孙权一生多次北伐合肥均未成功，公元215年合肥之战最出名。
+   - **支撑论据/案例**：曹军主力攻汉中，合肥仅张辽、李典、乐进镇守且三人有矛盾；张辽率800死士骑马冲击吴军，大败孙权军队，孙权差点被俘，吴军被俘将士描述孙权特征后张辽后悔未抓住他。
+   - **观点碰撞/互动**：发言人2回应称小时候认为孙权厉害，长大后观感反转。
+3. **【北伐路线】合肥为东吴北伐必经之地**（发言人：发言人1）
+   - **支撑论据/案例**：东吴从建业（今南京）出发，过长江经巢湖上岸，打下合肥才能靠近淮河，进而连接徐州、鲁西南乃至海河一带；孙权一生致力于打合肥未果。
+### 火烧连营与陆逊评价
+1. **【火烧连营】刘备冒进致惨败**（发言人：发言人1）
+   - **核心主张**：刘备因体恤士兵在密林扎营避暑，被陆逊抓住秋季干燥时机火攻。
+   - **支撑论据/案例**：连营七百里被一把火烧毁，刘备只身逃回白帝城；陆逊为江东四杰之一。
+2. **【陆逊与孙家关系】陆逊为江东四杰**（发言人：发言人1、发言人2）
+   - **观点碰撞/互动**：发言人2提出陆逊与孙家有仇的说法，发言人1回应陆逊为江东四杰，并提及孙策因冒失被刺杀。
+### 孙权与刘备军事能力评价
+1. **【孙权早期败绩】数万人败给数千人**（发言人：发言人3）
+   - **核心主张**：孙权在孙策刚死时曾以数万人败给数千人，被追着打。
+   - **观点碰撞/互动**：发言人1追问具体对手，发言人3未能确认姓名，排除刘表、张辽、曹仁后仍未定论。
+2. **【刘备军事能力】夷陵冒进、汉中尚可**（发言人：发言人1、发言人3）
+   - **核心主张**：刘备在夷陵之战因仇恨冲昏头脑而冒进；汉中之战靠法正、黄权辅佐，利用地势耗退曹操。
+   - **观点碰撞/互动**：发言人3认为刘备汉中之战打得挺好，发言人1补充夷陵之战是冒失所致。
+3. **【关羽能力】个人战力突出**（发言人：发言人1、发言人3）
+   - **核心主张**：关羽水淹七军，且阵中斩将改变战局，是历史第一人。
+   - **观点碰撞/互动**：发言人3质疑关羽除水淹七军外无其他战绩，发言人1补充斩颜良、诛文丑；发言人3认为那是个人战力而非部队作战，与黄忠斩夏侯渊不同。
+4. **【张飞评价】无经典战役**（发言人：发言人3）
+   - **支撑论据/案例**：张飞无经典战役，仅知长坂坡；发言人1补充演义中与马超大战五百回合。
+### 曹魏将领与诸葛亮北伐讨论
+1. **【五子良将】曹魏兵多将广能耗**（发言人：发言人1、发言人3）
+   - **核心主张**：五子良将包括张辽、曹仁、夏侯渊、张郃、徐晃、于禁，于禁被关羽生擒。
+   - **支撑论据/案例**：曹魏血厚人多，能持久消耗。
+2. **【街亭假设】魏延守街亭或可反杀**（发言人：发言人1）
+   - **核心主张**：诸葛亮第一次北伐若用魏延守街亭，大概率能反杀张郃，避免街亭丢失，北伐可能成功。
+   - **观点碰撞/互动**：发言人3回应蜀汉地盘太小；发言人1承认魏延想法大胆但不符合蜀汉实际支撑。
+## 共识形成
+1. **【达成共识】赤壁之战与合肥之战均体现双方擅长领域差异**：赤壁之战曹军因以骑兵为主、不擅水战而败，吴军以水军为主、不擅陆战；合肥之战中吴军上岸后无法与曹军骑兵抗衡，双方僵持不下。发言人1明确表述「赤壁之战不是曹军实力不行，而是毕竟骑兵没法打水战」，「张八百大破孙十万也是毕竟长期划船、游泳的人让他上，在陆地上像骑兵那样去冲锋打仗，他也不擅长」。
+2. **【核心分歧/待定取舍】孙权军事能力评价**：发言人2表示「小时候老觉得孙权比较厉害，长大以后感觉公平反转的比较厉害」，发言人1与发言人3均认同孙权打仗表现不佳，但发言人3补充孙权早期也曾以数万人败给数千人，具体对手未确认，发言人1追问后未能确定该对手身份。**对刘备军事能力评价存在分歧**：发言人3认为「刘备至少到最后汉中之战打得还挺好的」，发言人1则指出夷陵之战中刘备「被仇恨冲昏头脑了，所以说开始冒失，有点冒进了」，但认可汉中之战靠法正、黄权辅佐及地势优势耗退曹操。
+## 待探讨问题与后续
+1. **未确认：孙权早期败给的具体人物是谁**——发言人3提到孙权在孙策刚死时期曾以数万人败给数千人，但无法确认对手姓名，先后猜测刘油、刘表、曹仁、刘琦等均未获确认，最终未定论。
+2. **待核实：张飞是否有经典战役**——发言人3表示只知长坂坡，未想到其他经典战役，发言人1提及演义中与马超大战五百回合，但未进一步展开核实。
+3. **未定论：魏延守街亭能否改变诸葛亮第一次北伐结果**——发言人1提出若用魏延守街亭大概率能反杀张郃、北伐可能成功，但认为魏延想法大胆、不符合蜀汉实际支撑，发言人3仅回应「地盘太小了」，未形成定论。
+4. **未确认：关羽阵中斩将是否为历史第一人**——发言人3提出关羽阵中斩将可能是历史第一人做到直接改变战场局势，发言人1对比黄忠阵斩夏侯渊，发言人3认为两者情况可能不同，未进一步核实。</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>47.4</v>
+        <v>41.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>4899/2512</t>
+          <t>4899/2686</t>
         </is>
       </c>
     </row>
@@ -16902,72 +17063,74 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t># 讲座概况
-本次研讨会由主讲人讲解1979年至1989年苏联入侵阿富汗战争（苏阿战争）的历史背景、过程及影响，面向对冷战史与地缘政治感兴趣的听众。讲座围绕阿富汗的地理位置与历史地位、苏联出兵原因、战争过程与各方援助、以及阿富汗被称为“帝国坟场”的原因等板块展开。核心判断包括：阿富汗地处亚洲中间走廊地带，是兵家必争之地；其国土纵深百分之九十为高原山地，易守难攻，使任何列强难以有效控制；苏联因担心阿富汗倒向美国而于1979年12月24日平安夜以兵变形式突袭喀布尔，处决阿明、扶植卡尔迈勒，却陷入长达十年的游击战争消耗，最终于1989年撤军。讲座以阿富汗东接中国、北邻塔吉克斯坦等地理锚点，以及中国援助五六式冲锋枪、美国提供毒刺导弹压制苏联武装直升机等案例为支撑。对听众而言，本讲有助于理解冷战时期大国博弈与地区冲突的互动逻辑，以及非对称战争在复杂地形中的制胜机理。
-# 核心观点与论证
-## 阿富汗地处亚洲咽喉，战略位置决定列强觊觎
-- 阿富汗东接中国，北邻塔吉克斯坦，南接巴基斯坦、锡林、伊朗，被称为亚洲的中间走廊地带，是名副其实的兵家必争之地。
-- 谁控制了阿富汗，谁就控制住了亚洲的咽喉。
-- 阿富汗是贫油国，但周边国家都是富油国，如西边的伊朗、北边的土库曼斯坦和塔吉克斯坦。
-## 阿富汗易守难攻，素有帝国坟场之称
-- 阿富汗国土纵深百分之九十为高原山地地带，是天然的游击战地区，易守难攻。
-- 除喀布尔和坎大哈等主要城市外，大部分地区实行乡村部落长老制，政府没有控制力，各村落部落各自为政，列强与城市政府均无法有力控制广大高原山地。
-- 历史上大英帝国入侵后，曾被阿富汗短暂反推回巴基斯坦地区，阿富汗因此多次获得帝国坟场的称号。
-## 苏联出兵源于地缘与冷战双重考量
-- 20世纪50年代，阿富汗同时与苏联及西方国家保持友好交往，实行君主立宪制，国内精英阶层奉行亲英与亲苏两头政策：文化上师从英国，国家建设和工业方面向苏联看齐。
-- 基辛格评价阿富汗国王阿明是用的苏联的火柴在点的美国的香烟，两边一起要好处，获得墙头草的称号。
-- 阿明对苏联日益干涉内政不满并过度导向美国，苏联担心阿富汗脱离掌控后对其中亚地区造成被动，高层政治局决定在阿富汗彻底导向美国之前武力介入。
-- 发言人3补充：按勃列日涅夫逻辑，阿富汗被视为苏联大家庭成员，不允许任何成员外出，类似此前出兵捷克；同时期处于苏攻美守阶段，苏联进行意识形态扩张与军事霸权恐吓，共同导致出兵。
-## 苏联以兵变形式突袭，一夜控制喀布尔
-- 1979年12月24日平安夜，苏联趁阿富汗高层与军队被先前释放的清散信号麻痹，以阿富汗请求苏联救援的说法，从东部、中部及西部（塔吉克斯坦、土库曼斯坦方向）分路推进。
-- 一个晚上彻底控制喀布尔政府高层，处决阿明一家，扶植苏联代理人卡尔迈勒上台，将阿富汗重新纳入苏联阵营。
-## 国际合力援助，阿富汗展开十年游击战
-- 苏联出兵招致众多阿拉伯国家、中国和西方盟国共同不满，各方合力援助阿富汗；由阿富汗和穆斯林国家出动兵源，中国和西方盟国出动武器与情报资源。
-- 中国提供与AK47同型号的五六式冲锋枪和五六式半自动步枪，通过援助形式稀释国内饱和的军工业，并与西方盟国达成秘而不宣的默契。
-- 中国只提供军火、未派人，专家主要教授地道战、地雷战等抗战时期战法。
-- 美国援助先进单兵武器如毒刺防空导弹（类似火箭筒），有效压制苏联最先进的雌鹿武装直升机；坦克和步兵战车在高原山地无法形成有效战斗力，需以步兵加武装直升机作战。
-## 苏联军力难以发挥，士气低落终致撤军
-- 苏联军事实力看似庞大，但武器在阿富汗高原山地发挥不了作用，基层官兵普遍厌战，不明白为何来此战斗，士气一落千丈。
-- 阿富汗圣战者具备狂烈激进的伊斯兰圣战思想，从上到下宗教式洗脑，抱着同归于尽的思想进行圣战，类似二战时期日本军国主义荼毒下的日本军民。
-- 苏联扛不住阿富汗人民战争的消耗，最终于1989年从阿富汗撤军。
-# 金句总结
+          <t># 苏阿战争历史讲解与讨论
+## 讲座概况
+本次研讨会由主讲人系统讲解1979年至1989年苏联入侵阿富汗战争（苏阿战争）的历史背景、过程与影响，并回答听众提问。讲座围绕阿富汗的地理战略位置、战前与苏西方关系、苏联入侵决策与过程、多国援助及十年游击战、最终撤军等板块展开。核心判断包括：阿富汗地处亚洲中部，东接中国，北邻塔吉克斯坦，南接巴基斯坦、锡林、伊朗，被称为亚洲的中间走廊地带，谁控制了阿富汗谁就控制住亚洲咽喉；其国土百分之九十为高原山地，易守难攻，历史上多次被称为帝国坟场；1979年12月24日平安夜，苏联以兵变政变形式借口阿富汗请求救援，一夜控制喀布尔，处决阿明一家，扶植卡尔迈勒上台，此举招致阿拉伯国家、中国及西方盟国共同不满，各方合力援助阿富汗抵抗组织，展开长达十年的游击战争，苏联最终于1989年撤军。讲座面向对冷战史与地缘政治感兴趣的听众，有助于理解阿富汗问题的历史根源及大国博弈逻辑。
+## 核心观点与论证
+### 阿富汗的战略位置与帝国坟场成因
+- **地理枢纽**：阿富汗东接中国，北邻塔吉克斯坦，南接巴基斯坦、锡林、伊朗，被称为亚洲的中间走廊地带，谁控制了阿富汗，谁就控制住了亚洲的咽喉。
+- **易守难攻的地形**：国土纵深百分之九十为高原山地地带，是天然的游击战地区，历史上多次获得帝国坟场称号，第一次大英帝国入侵后曾被阿富汗反推回巴基斯坦地区。
+- **部落长老制**：除喀布尔和坎大哈等主要城市外，百分之九十地区由乡村部落长老制控制，政府无控制力，各村落部落各自为政，列强与城市政府均无法形成有力控制。
+- **资源状况**：阿富汗是贫油国，但周边国家均为富油国——西边伊朗、北边土库曼斯坦和塔吉克斯坦。
+### 苏联入侵的决策与过程
+- **战前平衡外交**：20世纪50年代，阿富汗同时与苏联及西方国家保持友好交往，实行君主立宪制，精英阶层奉行亲英与亲苏两头政策，文化上师从英国（议会制度、君主立宪制度、大学现代科学），国家建设和工业方面向苏联看齐。
+- **基辛格评价**：基辛格评价阿富汗国王阿明“用苏联的火柴点美国的香烟”，指其两边要好处、获得墙头草称号。
+- **入侵动因**：阿明对苏联日益干涉内政不满并过度导向美国，苏联高层政治局担心阿富汗脱离掌控、导向美国会使中亚地区陷入被动，决定在阿富汗彻底导向美国之前以兵变和武力介入。
+- **入侵过程**：1979年12月24日平安夜，苏联趁阿富汗高层和军队被清散信号麻痹，以阿富汗请求救援为借口，从东部、中部、西部（塔吉克斯坦、土库曼斯坦方向）分路推进，一夜控制喀布尔，处决阿明一家，扶植代理人卡尔迈勒上台。
+- **冷战背景**：同时期处于苏攻美守时期，苏联咄咄逼人进行意识形态扩张和军事霸权恐吓，共同导致出兵阿富汗；发言人3补充，根据勃列日涅夫逻辑，苏联不允许势力范围内成员外出，类似出兵捷克，阿富汗必须下场，加上战略要地特殊性，构成苏联的战略性失误。
+### 多国援助与十年游击战
+- **国际反应**：苏联入侵招致阿拉伯国家、中国及西方盟国共同不满抵触，各方合力援助阿富汗，由阿富汗和穆斯林国家出兵源，中国和西方盟国出武器与情报资源。
+- **中国援助**：中国提供与AK47同型号的五六式冲锋枪和五六式半自动步枪，通过援助稀释已饱和的军工业产能，并与西方盟国达成秘而不宣的默契共同抵抗苏联霸权主义。
+- **军事专家**：中国主要派遣专家教授兵法、地道战、地雷战等战法，未派作战人员。
+- **美国援助**：美国援助毒刺导弹（类似防空导弹的火箭筒），可有效压制苏联最先进的雌鹿武装直升机；坦克和步兵战车在高原山地无法形成有效战斗力，需以步兵加武装直升机作战。
+- **圣战者特性**：阿富汗圣战者受狂烈激进的伊斯兰圣战思想及宗教式洗脑影响，具备类似二战日本军国主义荼毒下军民不顾一切同归于尽的战斗意志。
+- **苏联撤军**：苏联军事实力看似庞大但武器在阿富汗无法发挥作用，基层官兵普遍厌战、士气一落千丈，最终扛不住阿富汗人民战争的消耗，于1989年撤军。
+## 金句总结
 &gt; “谁控制了阿富汗，谁就控制住了亚洲的咽喉。”
-- 背景：回答听众关于阿富汗战略价值的提问，解释其地理位置的重要性。
+&gt; —— **发言人1（主讲人）** ｜ 针对阿富汗战略地理位置关键性的定调发言
+&gt; “用苏联的火柴在点的美国的香烟。”
+&gt; —— **发言人1（主讲人）** ｜ 转述基辛格对阿富汗国王阿明两头讨好外交政策的评价
+&gt; “阿富汗多次获得其帝国坟场的称号。”
+&gt; —— **发言人1（主讲人）** ｜ 针对阿富汗易守难攻、列强入侵屡遭失败的历史定调
 &gt; “它这个国家相对来说是个贫油国，但它周边的国家都是富油国。”
-- 背景：回应听众关于阿富汗是否有石油的疑问，说明其资源状况及周边环境。
-&gt; “根据这个勃列日涅夫的这个逻辑来说，是不允许任何一个成员外出的。”
-- 背景：发言人3以冷战思维分析苏联出兵原因，类比此前出兵捷克。
-&gt; “就是狂烈的激进的伊斯兰圣战思想。以及从上到下那种宗教式那种洗脑。”
-- 背景：解释阿富汗圣战者的含义及其战斗意志的来源。
+&gt; —— **发言人1（主讲人）** ｜ 回应阿富汗是否因石油被觊觎的提问
+&gt; “阿富汗是一个非常重要的战略要地，所以加上苏联这个错判，导致苏联的大大的战略性失误。”
+&gt; —— **发言人3（听众）** ｜ 针对苏联出兵阿富汗决策失误的补充判断
 &gt; “任何一个列强以及阿富汗的城市政府对于广大的阿富汗高原山地地区无法形成一个有力的控制。”
-- 背景：说明阿富汗被称为“帝国坟场”的原因，即其高原山地地形与部落长老制使外部势力难以有效控制。
+&gt; —— **发言人1（主讲人）** ｜ 解释阿富汗被称为帝国坟场的地形与部落制根源
 &gt; “苏联的军事实力看似庞大，但实际上它的武器发挥不了任何的作用。”
-- 背景：总结苏联在阿富汗战争中军事装备难以适应高原山地作战，导致战斗力受限。
-&gt; “大家都不明白为什么要来这里进行战斗。所以说，苏军的士气也是一落千丈。”
-- 背景：说明苏联基层官兵普遍厌战，士气低落，最终促使苏联于1989年撤军。
-# Q&amp;A 环节
-**听众**：阿富汗到底有啥好呀？为啥都想打它？
-**主讲人**：地理位置的原因，谁控制了阿富汗，谁就控制住了亚洲的咽喉。
-**听众**：是不是阿富汗有石油啊？
-**主讲人**：它相对来说是个贫油国，但周边国家都是富油国，比如西边的伊朗，北边的土库曼斯坦和塔吉克斯坦。
-**听众**：其实这个我感觉得用当时的冷战思维来看，阿富汗当时被苏联化为是苏联势力、苏联大家庭中的一员。根据勃列日涅夫的逻辑，不允许任何一个成员外出，所以就像之前出兵捷克一样，这次阿富汗是必须要下场的，而阿富汗又是一个非常特殊的战略要地，加上苏联的错判，导致苏联大大的战略性失误。
-**主讲人**：对的，同时期冷战的状态也是苏攻美守时期，苏联咄咄逼人地进行意识形态扩张以及军事霸权的恐吓，共同导致了苏联出兵阿富汗。
-**听众**：之前看阿富汗那边把部队叫什么圣战者，这个是什么意思？
-**主讲人**：就是狂烈的激进的伊斯兰圣战思想，以及从上到下那种宗教式洗脑，导致阿富汗圣战者具备像二战时期日本军国主义荼毒之下的日本军民那样不顾一切、抱着同归于尽的思想进行圣战。
-**听众**：这次苏阿战争之前，已经有三次英阿战争，阿富汗被称为帝国坟场，可以简单说一下为什么这个位置这么难打吗？虽然它的国土面积没有那么大，经济实力又没有那么好。
-**主讲人**：因为这个国家百分之九十都是高原山地地带，是天然的游击战地区。除了喀布尔和坎大哈那几个主要城市以外，剩下大部分百分之九十的地区都是乡村部落长老制，政府没有任何控制力，由部落长老控制，各个村落与部落各自为政，导致任何列强以及阿富汗城市政府都无法对广大高原山地形成有力控制。同时期咱们国家帮助阿富汗圣战抵抗者，教他们地道战、地雷战等抗战时期的战法，美国也援助了比较先进的单兵武器，比如毒刺防空导弹，可以有效压制苏联最先进的雌鹿武装直升机。坦克和步兵战车在阿富汗无法形成有效战斗力，因为这些装备主要用于平原地带，高原山地还是要以步兵加武装直升机才能形成有效战斗力。苏联军事实力看似庞大，但武器发挥不了作用，加上基层官兵普遍厌战，士气一落千丈，最终1989年扛不住压力撤军。
-**听众**：咱们男生基本都说完了，都说过一遍了。
-**主讲人**：也是给了一些枪炮，比如咱们给的与AK47同型号的五六式冲锋枪和五六式半自动步枪，通过援助形式把咱们国家已经饱和的军工业产业稀释掉，同时也是为了抵抗苏联霸权主义，和西方盟国达成了一种秘而不宣的默契。
-**听众**：只提供军火，但是没有派人。
-**主讲人**：专家派的主要就教一些兵法、地道战、地雷战这一块的。</t>
+&gt; —— **发言人1（主讲人）** ｜ 针对苏联重装部队在阿富汗高原山地失效的论证
+&gt; “大家为了抵抗苏联的霸权主义和西方盟国达成了一种就是呃秘而不宣的默契。”
+&gt; —— **发言人1（主讲人）** ｜ 说明中国与西方盟国共同援助阿富汗抵抗组织时的协作状态
+## Q&amp;A 环节
+### Q1. 阿富汗为何被多国觊觎
+- **听众**：男生阿富汗到底有啥好呀？为啥都想打它？
+&gt; **主讲人**：地理位置的原因，谁控制了阿富汗，谁就控制住了亚洲的咽喉。
+### Q2. 阿富汗是否有石油
+- **听众**：哎，是不是阿富汗有石油啊？
+&gt; **主讲人**：它这个国家相对来说是个贫油国，但它周边的国家都是富油国，比如说是西边的伊朗，北边的土库曼斯坦和塔吉克斯坦。
+### Q3. 苏联为何必须出兵阿富汗
+- **听众**：其实这个我感觉得用当时的冷战思维来看，因为阿富汗当时被苏联化为是苏联势力，就是苏联大家庭中的一员。根据这个勃列日涅夫的这个逻辑来说，是不允许任何一个成员外出的。所以就像之前出兵捷克一样，这次阿富汗他是必须要下场的，而阿富汗是一个非常特殊的战略要地，所以加上苏联这个错判，导致苏联的大大的战略性失误。
+&gt; **主讲人**：对的，同时期冷战的状态也是苏攻美守时期，然后苏联咄咄逼人的进行意识形态的扩张以及军事霸权的恐吓，然后共同导致了苏联出兵阿富汗。
+### Q4. 圣战者的含义
+- **听众**：嗯，之前看那个阿富汗那边把那个部队叫什么圣战者，这个是什么意思？
+&gt; **主讲人**：就是狂烈的激进的伊斯兰圣战思想，以及从上到下那种宗教式那种洗脑，然后导致了其阿富汗圣战者具备像二战时期日本军国主义荼毒之下的日本军民的那样一样，不顾一切的就是抱着一种同归于尽的思想进行一种圣战的方式。
+### Q5. 阿富汗为何被称为帝国坟场
+- **听众**：其实这次苏阿战争之前，已经有三次这个英阿战争，这个阿富汗这个这个被称为叫做帝国坟场，这个可以，就是简单说一下为什么这个阿富汗这个位置这么难打？虽然它的国土面积没有那么大，然后经济实力又没有那么好。
+&gt; **主讲人**：因为这个国家百分之九十都是处于高原山地地带，就是一个天然的游击战地区。它除了以喀布尔和坎大哈那几个主要城市为首的城市地区以外，剩下大部分百分之九十的地区都是乡村部落长老制的那种制度。你到乡村就是政府没有任何的控制力，都是由部落的长老，也就是咱们以前国内宗族的，像什么族长、村长这样的一个形式，然后控制的该部落，然后各个村落与部落各自为政，然后导致了，就任何一个列强以及阿富汗的城市政府对于广大的阿富汗高原山地地区无法形成一个有力的控制。同时期，咱们国家当时也是帮助那个阿富汗圣战抵抗者，教他们兵法，就比如说咱们以前抗战时期所用的，比如地道战、地雷战这样的一个战法，然后和苏联持续进行了就是游击战争。然后美国同时期也援助了比较先进的单兵武器吧，然后从而有效的对苏联的重装部队实行有效的压制，比如说毒刺，它是一个就是类似于就是防空导弹的一个火箭筒，然后可以有效压制苏联的最新最先进的当时的这武装直升机，也就是雌鹿的一个武装直升机，因为坦克和步兵战车在阿富汗没有办法形成有效的战斗力，那是因为这些装备主要是用在平原地带的，在高原山地还是要以步兵加那个武装直升机才能形成有效的战斗力。所以说，苏联的军事实力看似庞大，但实际上它的武器发挥不了任何的作用。再加上苏联的基层官兵普遍也厌战，大家都不明白为什么要来这里进行战斗。所以说，苏军的士气也是一落千丈。就最终八九年的时候，苏联从上到下也扛不住这个压力，然后最终撤军。
+### Q6. 中国对阿富汗的援助细节
+- **听众**：哎，咱们男生基本都说完了，都说过一遍了。
+&gt; **主讲人**：呃，也是给了一些枪炮，比如说像咱们给的和AK四十七同样型号的五六式冲锋枪和五六式半自动步枪，也是通过这个援助的一个形式。然后我把咱们国家就是已经饱和的军工业，这个就是产业给它稀释掉，然后同时也为了抵抗苏联的霸权主义和西方盟国达成了一种就是呃秘而不宣的默契。
+- **听众**：呃，只提供军火，但是没有派人。
+&gt; **主讲人**：呃，专家派的主要就教一些兵法、地道战、地雷战这一块的。</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>41.7</v>
+        <v>40.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>3129/3279</t>
+          <t>3129/3957</t>
         </is>
       </c>
     </row>
@@ -17159,74 +17322,53 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t># 讨论议题与背景
-本次讨论由发言人2以《白夜行》为引子发起，四位发言人（编号1至4）围绕各国文学特点与底层民众描写展开漫谈式交流。讨论从日本文学切入，先后比较法国、英国、俄国、美国文学的主题差异，延伸至中国底层文学受限现状、台湾电影《假如我是真的》的改编背景、欧洲人口膨胀与移民北美的原因、历史饥荒与文学批判的关系，最后以《西游记》狮驼岭章节的黑暗解读收尾。整体以分享观点为主，未形成统一结论，讨论按议题逐块推进，由发言人2多次引导话题转向。讨论中提及《菊与刀》《悲惨世界》《古拉格群岛》《平凡的世界》《一九四二》等作品，以及契诃夫、托尔斯泰、高尔基、格罗斯曼等作家，并涉及狮驼岭距灵山约500公里、电影拍摄于上世纪七十年代末八十年代初等具体信息。
-# 发言要点
-## 日本文学《白夜行》讨论
-- **发言人1**：《白夜行》是悬疑小说，叙事手法新颖，结局阴暗，阅读时猜不到真相，每个人都有嫌疑。
-- **发言人2**：美国作家本尼迪克特《菊与刀》生动描绘日本人性格特点，《白夜行》中也能体现，由此引出各国文学偏好比较。
-## 各国文学特点比较
-- **发言人1**：法国文学体现抗争精神，法国历史上革命多。
-- **发言人4**：法国小说比英国小说更多描绘底层民众，英国文学多写贵族生活。
-- **发言人2**：法国文学具有浪漫理想主义精神与奉献，在《悲惨世界》中体现生动。
-- **发言人2**：比较法国与俄国对底层民众的描绘，俄国更生动，如契诃夫、列夫·托尔斯泰的作品。
-- **发言人4**：俄国文学戏剧性更明显、曲折更多。
-- **发言人2**：《古拉格群岛》真正批判人性黑暗面，最早出版法语版，俄语版等到苏联解体后才发行。
-- **发言人1**：国内底层文学如《平凡的世界》写得深刻，但因政策原因受限，相关电影也不让看。
-## 中国底层文学与历史事件
-- **发言人2**：台湾电影《假如我是真的》改编自俄国小说，结合文革真实事件，上世纪七十年代末、八十年代初拍摄，讲述知青上山下乡时期真实体现。
-- **发言人2**：电影结合果戈里《钦差大臣》故事背景，是台湾对大陆的舆论宣传战，批判上山下乡时期的不公。
-- **发言人1**：台湾批判自己，也批判平衡，台湾总会拍电影。
-## 俄国文学与苏联时期作品
-- **发言人2**：个人喜欢契诃夫，如《变色龙》《装在套子里的人》《凡卡》。
-- **发言人2**：苏联时期喜欢格罗斯曼，他是红军战地记者，写《命运与生活》，揭露红军后期进入欧洲后看似不公的问题，从平民视角呈现苏联红军基层真实形象。
-- **发言人1**：苏联时期作者虽多，但自己看得很少。
-- **发言人2**：高尔基因正面宣传而更广为人知。
-- **发言人2**：高尔基《海燕》体现老百姓被压迫后走投无路的奋起反抗。
-## 英国文学与移民原因
-- **发言人1**：英国文学如《圣诞欢歌》《雾都孤儿》也描写底层人，查尔斯·狄更斯很多作品如此。
-- **发言人1**：英国文学写贵族与穷人之间的鸿沟，穷人把希望寄托在宗教或虚无的东西上。
-- **发言人2**：欧洲土地无法承载人口膨胀，以英国、爱尔兰为主移民北美新大陆，这是根本原因。
-## 美国文学与历史背景
-- **发言人2**：美国文学侧重现代社会，与欧洲理想主义精神图腾不同。
-- **发言人1**：美国历史短，美洲大陆未发生欧洲、亚洲大陆那么多悲惨事件，相对幸福。
-- **发言人2**：北美大平原农业资源广阔，美国经济不好也永远不缺粮食。
-- **发言人2**：黑死病、天花、饥荒、旱灾、蝗灾等在美国从未发生过，美国人无法真正理解饥荒为何物。
-## 历史饥荒与文学批判
-- **发言人1**：电影《一九四二》讲大饥荒和战乱。
-- **发言人2**：日本人给灾民发放粮食，国民党对灾区漠视，导致日本人占领河南省大部地区。
-- **发言人1**：有人为换取粮食给日本人送情报，这是人性，被利用了没办法。
-- **发言人2**：列夫·托尔斯泰是前线俄军，把百姓疾苦与贵族奢华进行讽刺对比，因沙俄新闻管制严厉而以小说方式发表。
-- **发言人2**：俄国文学与法国文学有相似也有不同，更侧重对人性丑恶的揭露与批判，更为讽刺。
-## 《西游记》狮驼岭解读
-- **发言人2**：狮驼岭章节中，佛门三大圣兽青狮、白象、大鹏偷离佛门到下界作妖，把城池所有人吃掉，扶植小妖成为公民，尸骸遍地，孙悟空不战而弃。
-- **发言人2**：原著描写人皮当地毯、骷髅头骨当装饰物和器具，此地距灵山不过500公里，与佛教普度众生理念大相径庭。
-- **发言人2**：吴承恩在古代就预测并批判揭露佛教被上层王公大臣用来迷惑、高压奴役底层民众，而非真正众生平等，这是汉传佛教与藏传佛教的本质不同。
-- **发言人2**：古代藏族王公大臣就是这种状态，若共产党未解放西藏，悲剧会延续到今天。
-- **发言人1**：狮驼岭章节太血腥，黑神话悟空游戏未设计该章节，估计不好过审，剧情既要委婉又要深刻很难。
-- **发言人2**：狮驼岭章节中若非佛祖出手，孙悟空会被大鹏精打败，大鹏精是《西游记》全剧中唯一能遛猴子的反派角色。
-- **发言人4**：狮驼岭章节电视剧有拍，但未把那些惨状细节拍得生动。
-# 共识形成
-- **一致意见**：与会者普遍认同《白夜行》叙事手法新颖、结局阴暗，符合日本文学特点；法国文学具有抗争精神与浪漫理想主义，英国文学多描写贵族生活，俄国文学在描绘底层民众方面更为生动、讽刺性更强。
-- **倾向性认识**：发言人2认为俄国文学对人性丑恶的揭露与批判比法国文学更为讽刺，并以《古拉格群岛》为例，指出其最早出版法语版、俄语版在苏联解体后才发行；发言人1补充国内底层文学如《平凡的世界》因政策原因受限，台湾电影《假如我是真的》结合文革真实事件批判上山下乡时期的不公。
-- **主要分歧点**：在底层民众描写生动性上，发言人2倾向俄国文学更胜一筹，发言人4则认为法国文学比英国文学更多描绘底层民众；发言人1提出英国文学如《圣诞欢歌》《雾都孤儿》同样描写底层人，与发言人2「英国多贵族生活」的判断不完全一致。
-- **关键结论口径**：发言人2指出狮驼岭距灵山约500公里，原著描写佛门圣兽吃人、尸骸遍地，与佛教「普度众生」理念相悖，认为吴承恩借此批判佛教被上层利用奴役民众；电视剧和游戏未充分展现该章节黑暗细节。
-# 待探讨问题与后续
-- **未确认**：发言人1提到国内底层文学如《平凡的世界》因政策原因受限，但未展开具体政策依据与受限范围。
-- **未确认**：发言人2称《古拉格群岛》最早出版版本为法语版、俄语版在苏联解体后发行，未核实出版时间与版本细节。
-- **未确认**：发言人2称电影《假如我是真的》改编自俄国小说并结合文革真实事件，未核实具体改编来源与拍摄年份。
-- **未确认**：发言人2称日本人给灾民发放粮食导致国民党失去河南大部，未核实该历史叙述的具体史料依据。
-- **未确认**：发言人2称狮驼岭距离灵山约500公里，未核实原著中该距离表述。
-- **未确认**：发言人2称吴承恩在《西游记》中预测并批判佛教被上层利用奴役民众，未展开论证依据。
-- **未确认**：发言人2称汉传佛教与藏传佛教本质截然不同，未展开具体比较依据。</t>
+          <t># 各国文学特点闲聊与《西游记》狮驼岭寓意探讨
+## 讨论议题与背景
+本次讨论为一场围绕各国文学特点的闲聊式漫谈，由发言人2主导话题推进，发言人1、3、4参与分享。讨论由《白夜行》的悬疑叙事与阴暗结局切入，引出对日本文学性格特征的探讨，随后依次对比法国、英国、俄国、美国文学在底层描写、理想主义、讽刺性等方面的差异，穿插个人阅读体验与作品推荐，最后转向《西游记》狮驼岭章节的黑暗寓意及其对佛教虚伪性的批判。整体以分享观点为主，未形成统一结论；讨论按话题逐块推进，从日本文学自然过渡至多国文学对比，再聚焦于具体章节解读。关键锚点包括美国作家本尼迪克特的《菊与刀》、台湾电影《假如我是真的》结合俄国《钦差大臣》与文革知青上山下乡背景，以及狮驼岭距灵山约500公里却发生人伦惨剧的细节。
+## 发言要点
+### 日本文学《白夜行》讨论
+1. **《白夜行》叙事与结局**（发言人1）：悬疑小说，叙事手法新颖，上来都是隐藏线索，让人猜不到真相，每个人都有嫌疑，但结局非常阴暗。
+2. **《菊与刀》佐证日本性格**（发言人2）：美国作家本尼迪克特所著《菊与刀》生动描绘日本人性格特点，可从《白夜行》中体现，并引出各国文学偏好话题。
+### 各国文学特点对比
+1. **法国文学：抗争精神与浪漫理想主义**（发言人1、2、4）
+  - **核心主张**：法国文学体现抗争精神，描绘底层民众较多，具有浪漫理想主义与奉献精神。
+  - **支撑论据/案例**：发言人1认为法国「挺爱革命，有点抗争精神」；发言人4指出法国小说比英国更多描绘底层民众，英国多写贵族生活；发言人2以《悲惨世界》为例说明其浪漫理想主义与奉献精神。
+2. **英国文学：贵族生活与底层鸿沟**（发言人1、4）
+  - **核心主张**：英国文学多写贵族生活，底层描写较少。
+  - **支撑论据/案例**：发言人1提到《圣诞欢歌》《雾都孤儿》等狄更斯作品讲底层人，但突出贵族与穷人间的鸿沟，穷人把希望寄托于宗教等虚无之物；发言人4表示只看过《简爱》。
+3. **俄国文学：讽刺性与人性丑恶揭露**（发言人2）
+  - **核心主张**：俄国文学比法国更讽刺，过多揭露人性丑恶。
+  - **支撑论据/案例**：发言人2举《古拉格群岛》为例，称其真正批判人性黑暗面，且该书法语版早于俄语版出版（俄语版待苏联解体后发行）；还提到契诃夫的《变色龙》《装在套子里的人》《凡卡》，以及苏联作家格罗斯曼（红军战地记者）所著《命运与生活》，从平民视角写红军进入欧洲后的不公问题。
+4. **美国文学：历史短、关注现代社会**（发言人2、1）
+  - **核心主张**：美国文学历史短，叙事风格不同于欧洲，更关注现代社会，与欧洲理想主义精神图腾不同。
+  - **支撑论据/案例**：发言人2提到马克·吐温、海明威；发言人1提到《了不起的盖茨比》，并认为美洲大陆未发生欧亚大陆那么多悲惨事件，相对幸福；发言人2补充北美大平原农业资源广阔，美国永远不缺粮食，未经历过饥荒。
+5. **国内底层文学受限**（发言人1）：国内写底层的作品其实很深刻，如《平凡的世界》，但因政策原因很多小说和电影不让看。
+6. **《假如我是真的》电影**（发言人2）：台湾拍摄，改编自俄国果戈里《钦差大臣》故事，结合文革知青上山下乡时期真实事件，上世纪七十年代末、八十年代初拍摄，是当时台湾与大陆舆论宣传战、意识形态攻势的一部分，批判大陆上山下乡及文革时期的不公。
+### 《西游记》狮驼岭章节讨论
+1. **狮驼岭黑暗情节描述**（发言人2）：佛门三大圣兽青狮、白象、大鹏偷离佛门到下界作妖，吃光城池所有人，扶植小妖成为国家公民；唐僧师徒路过时尸骸遍地，孙悟空不战而弃、发抖；原著描写人皮当地毯、骷髅头骨作装饰物和器具。
+2. **狮驼岭与佛教理念相悖**（发言人2）：此地距灵山仅约500公里，却发生人伦惨剧，与佛教普度众生、众生平等理念大相径庭；认为吴承恩在古代就已预测并批判揭露佛教在部分地区成为上层王公大臣迷惑底层民众、进行高压奴役的统治工具，并对比汉传佛教与藏传佛教的本质差异。
+3. **影视与游戏未充分呈现**（发言人1、2、4）：电视剧有拍但未把惨案讲得生动，只拍几个妖精被收服；发言人1提到《黑神话：悟空》未设计狮驼岭章节，因过于血腥、意义深刻，剧情既要委婉又要表现深刻，很难设计且不好过审。
+4. **大鹏精实力**（发言人2）：整个《西游记》中唯一能遛猴子的反派角色是大鹏精，若非佛祖出手，孙悟空终将被大鹏精打败。
+## 共识形成
+1. **【达成共识】各国文学特点的倾向性认识**：与会者普遍认可法国文学具有抗争精神与浪漫理想主义（如《悲惨世界》），英国文学多描写贵族生活、底层描写较少，俄国文学更侧重揭露人性丑恶与讽刺（如《古拉格群岛》），美国文学历史较短、叙事风格不同于欧洲、更关注现代社会。发言人1认为国内底层文学也很深刻，但因政策原因受限；发言人2补充《假如我是真的》电影结合俄国《钦差大臣》与文革知青上山下乡背景。
+2. **【核心分歧/待定取舍】底层描写生动性之争**：发言人2提问法国与俄国哪个描绘底层民众更生动，发言人4认为俄国文学戏剧性更明显、更曲折；发言人1则指出英国文学如《圣诞欢歌》《雾都孤儿》也大量描写底层，与发言人2认为英国文学多写贵族生活的观点存在分歧。发言人2还提出《西游记》狮驼岭章节批判佛教虚伪、对比汉传与藏传佛教本质差异，发言人1认为该章节过于血腥且意义深刻，难以在《黑神话：悟空》中设计呈现。
+## 待探讨问题与后续
+1. **未确认：各国文学偏好是否形成统一结论**——讨论中发言人2多次引导比较法国、英国、俄国、美国文学特点，各成员分别表达看法（如发言人4认为法国文学比英国文学更多描绘底层民众、发言人1认为英国文学多写贵族生活），但未就偏好达成一致，属开放式漫谈。
+2. **待核实：《假如我是真的》电影改编来源**——发言人2称该片由俄国小说改编并结合文革知青上山下乡时期真实事件拍摄，但未说明具体改编自哪部俄国作品，仅提及与果戈里《钦差大臣》故事背景有结合。
+3. **未定论：《古拉格群岛》作者归属**——发言人2发言中将《古拉格群岛》与陀思妥耶夫斯基关联，但该书实际作者为索尔仁尼琴，原文未就此澄清，存在表述混淆。
+4. **待核实：《白夜行》叙事手法评价**——发言人1称其「上来就都是隐藏的」「每个人都有嫌疑」，但未展开具体叙事技巧分析，该评价停留在个人感受层面。
+5. **未确认：国内底层文学受限程度**——发言人1提出国内底层文学「写的挺深刻」但因政策原因「不让你看了」，并举电影改编受限为例，但未给出具体作品或政策依据，属个人判断。
+6. **未定论：美国文学是否缺乏苦难主题**——发言人1认为美洲大陆未经历欧洲、亚洲大陆的瘟疫与饥荒，美国人「无法真正理解饥荒为何物」；发言人2补充北美大平原农业资源广阔，但未就此展开深入论证。
+7. **待核实：狮驼岭章节与藏传佛教的关联性**——发言人2将《西游记》狮驼岭情节与旧社会西藏状况、汉传佛教与藏传佛教本质差异相联系，该类比属个人解读，未获其他成员确认或反驳。
+8. **未确认：《黑神话：悟空》未设计狮驼岭章节的原因**——发言人1推测因「太血腥」「不太好过审」「意义深刻」而未被设计，但未提供游戏开发方的官方说明，属推测性判断。</t>
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>50.7</v>
+        <v>40.3</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5886/3022</t>
+          <t>5886/3055</t>
         </is>
       </c>
     </row>
@@ -17298,88 +17440,92 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t># 全文摘要
-本次例会由主持人召集，产品、开发1、开发2等团队成员参与，围绕手机图库项目整体进展、排期与风险进行对齐。会议覆盖智能分类与相册推荐改版、AI智能标签接口与模型部署、云同步模块断点续传与OOM问题、缩略图渲染优化与性能压测、时间轴视图加载速度优化、AI修图功能预留与插件化架构、项目里程碑与内测包排期等板块。关键结论包括：隐私相册入口提到首部顶部二级菜单；AI标签接口采用本地缓存策略与端侧预过滤方案；云同步采用分片加载方案；时间轴采用本地索引预加载；AI修图本次不实现、预留插件化架构；项目月底封版、下周三发内测包。关键数字锚点：AI识别准确率提升约88%、单次请求耗时从800ms涨至约1.5s、内存占用降约30%、主流机型帧率稳定60帧、内测包暂定下周三发布。
-# 分段速览
-## 00:00:00-00:01:23 开场与产品侧进展同步
-主持人开场说明会议目的为对齐手机图库项目整体进展、排期与潜在风险。产品侧同步智能分类和相册推荐改版进展：高保真原型已出V1.5版，调整网格视图交互逻辑并优化长按微动效；低端机上滑列表偶发掉帧，已与开发2沟通通过降低预览图缩放级别换帧；用户调研反馈隐私相册入口太深，建议下一版提到首部顶部二级菜单。主持人确认入口改动不算大，要求产品出交互方案评审，并强调掉帧问题需抓紧，因下周将进入性能压测。
-## 00:01:51-00:03:19 AI标签接口与模型部署讨论
-开发1汇报后端V2识别模型已跑起来，准确率较上一代提升约88%，但视频帧提取功能使单次请求耗时从800毫秒涨至约1.5秒。产品否决异步推送方案，提出本地缓存策略：首次识别慢、之后本地读库秒出。开发1确认可行，下午拉分支改逻辑，预计三天联调完，但提示缓存命中率低时需回溯。开发1同时提出云同步模块断点续传在弱网下状态机紊乱的问题。
-## 00:03:19-00:05:03 同步模块OOM与缩略图渲染优化
-开发2确认同步队列积压超一千张时部分机型出现OOM崩溃，尤其iOS，已加分片加载机制（每次拉五十张），但拖慢同步进度。主持人否决后台静默同步权限申请，同意分片加载方案但要求进度不拖。开发2汇报缩略图渲染优化：JPEG硬解换软解，内存占用降约30%、CPU占用上升，主流三款机型灰度帧率稳定60帧、低端机50帧；另发现批量删除照片时数据库锁死Bug，已用消息队列临时规避，正式修复排到下下周版本。
-## 00:05:03-00:07:01 端侧预过滤与时间轴加载优化
-主持人提出端侧预过滤思路：先用轻量级模型过滤gif或截图，再走全量云端识别，平均耗时压一半。开发1评估需申请200MB本地缓存空间，产品确认安装包加两三百兆问题不大，同意按需加载方案（约两天搞定）。开发1提出时间轴视图滑动到老照片时卡死三秒以上，原因是EXIF解析耗时和磁盘IO瓶颈，准备加本地索引预加载（最近三个月建树状结构），主持人同意但提醒别与云同步模块抢资源。
-## 00:07:25-00:09:42 预加载资源协调与AI修图预留
-开发2确认预加载放主线程IO池、同步放子线程后台服务互不冲突，但需用户授权媒体和存储权限，产品设计引导弹窗。产品提出运营希望下版本加AI修图快捷入口，主持人决定本次不硬塞，在PRD预留接口和UI占位，开发侧做插件化架构。开发2提出趁重构把渲染层抽成插件化、用GLSL写统一接口，工作量多一周，需调整优先级。
-## 00:09:42-00:12:18 排期确认与收尾
-主持人调整优先级：非核心UI微调往后排，资源给到管线重构和AI标签优化，要求开发2今天下班前发精确工作量、开发1排联调时间赶在周五前跑通主干流程。确认里程碑按原定计划月底封版，内测包暂定下周三发，拉体验官群重点跑AI分类和同步模块。开发1提出与DBA对齐索引策略，主持人同意拉群配合。开发2建议性能报告将iOS和安卓对比数据分开列，主持人同意合并成一份总览。
-# 要点梳理
-## 智能分类与相册推荐改版
-- **原型进展**：高保真原型已出V1.5版，调整网格视图交互逻辑，长按手势增加微动效反馈。
-- **掉帧问题**：低端机上滑列表偶尔掉帧，已与开发2沟通，拟通过降低预览图缩放级别换帧。
-- **隐私相册入口**：用户调研反馈入口太深，产品建议下一版提到首部顶部二级菜单；产品经理确认改动不大，要求产品出交互方案评审。
-## AI智能标签接口与模型部署
-- **模型进展**：后端V2版识别模型已跑起来，准确率比上一代提升约88%。
-- **耗时问题**：因增加视频帧提取功能，单次请求耗时从800毫秒涨至约1.5秒。
-- **方案决策**：异步推送方案被否决，改为本地缓存策略；开发1下午拉分支改逻辑，预计三天联调完，但缓存命中率低时需回溯。
-- **端侧预过滤**：产品经理提出先用轻量级模型过滤gif或截图，再走全量云端识别，平均耗时可压一半；开发1评估模型体积和端侧推理开销，需申请200MB本地缓存空间。
-- **按需加载**：产品确认安装包加两三百兆问题不大，采用按需加载方案，用现有资源下发模块，约两天搞定。
-## 云同步模块与OOM问题
-- **断点续传**：云同步模块在弱网环境下出现状态机紊乱。
-- **OOM崩溃**：同步队列积压到一千张以上时部分机型崩溃，尤其iOS内存回收机制激进。
-- **分片加载**：开发2已加机制，每次拉五十张处理完再拉下一批；后台静默同步权限申请被否决，先按分片方案走但进度不能拖。
-## 缩略图渲染优化与性能压测
-- **解码优化**：JPEG硬解换软解，内存占用降约30%，CPU占用上升。
-- **灰度数据**：主流三款机型帧率稳定60帧，低端机约50帧；周四性能报告今晚出初稿。
-- **数据库锁死Bug**：批量删除照片时若同时触发回收站重建索引，数据库偶尔锁死；已用消息队列排队临时规避，正式修复排进V1.2迭代。
-## 时间轴视图加载优化
-- **卡顿问题**：滑动到二十年前老照片时页面卡死三秒以上，测试提了三个优高优Bug；原因为历史图片EXIF解析耗时太长加磁盘IO瓶颈。
-- **预加载方案**：加本地索引预加载，最近三个月照片建树状结构，滑到底部动态加载旧数据；预加载放主线程IO池，同步放子线程后台服务，互不冲突。
-- **权限引导**：预加载需用户授权媒体和存储权限，产品设计引导弹窗，明天出稿走柔和提示路线。
-## AI修图预留与插件化架构
-- **需求预留**：运营希望下个版本加AI修图快捷入口（一键去背景、智能调色），本次主线是性能和分类不硬塞，在PRD预留接口和UI占位。
-- **插件化架构**：开发2提出把渲染层抽成插件化、用GLSL写统一接口，工作量多一周；产品经理调整优先级，非核心UI微调往后排，资源给到管线重构和AI标签优化。
-- **后端接口**：开发1确认新接口按微服务规范出标准RESTful加Swagger文档。
-## 里程碑与内测排期
-- **封版时间**：项目里程碑按原定计划，月底封版。
-- **内测安排**：内测包暂定下周三发，拉体验官群重点跑AI分类和同步模块；产品做好反馈收集表，开发准备日志抓取。
-## 结论与决定
-- 隐私相册入口提到首部顶部二级菜单，产品出交互方案评审。
-- AI标签接口采用本地缓存策略，开发1下午拉分支改逻辑，预计三天联调完。
-- 端侧预过滤方案采用，开发1评估模型体积和端侧推理开销，申请200MB本地缓存空间。
-- 按需加载方案采用，用现有资源下发模块，约两天搞定。
-- 云同步模块采用分片加载方案，不申请后台静默同步权限。
-- 缩略图渲染优化临时规避方案先稳住，正式修复排进V1.2迭代。
-- 时间轴视图采用本地索引预加载方案，产品设计引导弹窗。
-- AI修图功能本次不实现，在PRD预留接口和UI占位，开发侧做插件化架构。
-- 非核心UI微调往后排，资源给到管线重构和AI标签优化。
-- 项目里程碑按原定计划，月底封版；内测包暂定下周三发。
-## 行动项与分工
-- **产品（发言人2）**：下午定稿隐私相册入口和引导弹窗稿子，明天上午拉UI走查，并制作AI修图占位图；十一点半前将UI走查稿发给产品经理。
-- **开发1（发言人3）**：下午拉分支改本地缓存逻辑，预计三天联调完；评估端侧预过滤模型体积和推理开销；按需加载约两天搞定；今晚搭好接口联调环境，明天与测试过一遍；拉群与DBA对齐索引策略。
-- **开发2（发言人4）**：继续跑分片加载和渲染优化压测数据，明天同步；评估管线重构精确工作量，今天下班前发给产品经理；让测试组将iOS和安卓性能对比数据合并成一份总览报告。
-## 待确认与风险
-- 端侧预过滤的模型体积和端侧推理开销待评估。
-- 缓存命中率低时需回溯，产品需心里有底。
-- 分片加载拖慢同步进度，需产品商量是否允许用户手动设置同步频率。
-- 预加载需用户授权媒体和存储权限，引导弹窗交互设计待产品出稿。
-- 管线重构工作量多一周，需产品经理确认能否把非核心Bug修复往后挪。
-- 低端机上滑列表掉帧，影响用户体验。
-- AI标签接口单次请求耗时从800ms涨到1.5s，可能影响用户等待体验。
-- 云同步模块弱网环境下状态机紊乱，可能导致同步异常。
-- 同步队列积压到一千张以上时部分机型OOM崩溃，尤其iOS。
-- 批量删除照片时数据库锁死，影响数据一致性。
-- 时间轴视图滑动到老照片时卡死三秒以上，影响核心功能体验。
-- 预加载需用户授权，若用户拒绝可能影响功能使用。
-- AI修图功能本次不实现，运营需求可能后续带来压力。</t>
+          <t># 手机图库项目进展对齐与排期确认会
+## 全文摘要
+本次例会由产品经理（发言人1）主持，产品（发言人2）、开发1（发言人3）、开发2（发言人4）参与，围绕手机图库项目进展、排期与风险对齐。会议覆盖智能分类与相册推荐改版、AI智能标签接口与模型部署、云同步模块问题、缩略图渲染优化与性能压测、时间轴视图加载优化、AI修图功能预留及项目里程碑与内测安排等议题。关键结论包括：隐私相册入口提升至首部顶部二级菜单；AI标签采用本地缓存与端侧预过滤方案；云同步采用分片加载、不申请后台静默同步权限；AI修图本次不纳入、预留插件化架构；月底封版、下周三发内测包。关键数字锚点：AI识别准确率提升约88%、单次请求耗时增至约1.5秒、内存占用降约30%、主流机型帧率稳定60帧。
+## 分段速览
+### 00:00:00-00:01:23 开场与产品侧进展同步
+会议开场，主持人明确本次短会目标为对齐手机图库项目进展、排期与风险，按产品侧交互迭代、开发侧技术实现与性能优化、总结重点工作的顺序进行。产品侧同步智能分类与相册推荐改版进展：高保真原型已出V1.5版，调整网格视图交互逻辑并优化长按手势微动效；测试反馈低端机上滑列表偶发掉帧，已与开发2沟通考虑降低预览图缩放级别；用户调研反映隐私相册入口过深，建议下版提升至首部顶部二级菜单。主持人认可入口调整不算大改动，要求产品出交互方案评审，并强调掉帧问题需抓紧，因下周将进入性能压测。
+### 00:01:51-00:03:19 AI标签接口与云同步问题同步
+开发1汇报后端V2识别模型已跑通，准确率较上代提升约88%，但视频帧提取功能使单次请求耗时从800毫秒增至约1.5秒，提出异步推送方案。产品否决异步推送，建议采用本地缓存策略——首次识别慢、之后本地读库秒出，开发1确认可行并计划加CQLite缓存层，预计三天联调完，同时提示缓存命中率低时需回溯。开发1另提出云相册同步断点续传在弱网下出现状态机紊乱，开发2反馈同步队列积压超一千张时部分机型出现OOM崩溃，尤其iOS严重，已采用分片加载机制每次拉取五十张，但拖慢整体同步进度。
+### 00:03:57-00:05:03 同步方案定调与缩略图渲染优化
+主持人否决后台静默同步权限申请（审核严、大概率下不了），确定先按分片加载方案走但进度不能拖。开发2汇报缩略图渲染优化：改用新图片解码库，JPEG硬解换软解，内存占用降约30%但CPU占用上升；已在主流三款机型灰度，帧率稳定60帧、低端机约50帧，周四性能报告初稿今晚可出。同时提出批量删除照片触发回收站重建索引时数据库偶发锁死，已写临时规避方案用消息队列排队处理，正式修复预计排到下下周版本。主持人要求临时规避先稳住，正式修复排进V1.2迭代。
+### 00:05:03-00:07:01 端侧预过滤方案与时间轴卡顿问题
+主持人提出端侧轻量级预过滤思路——先用轻量模型过滤gif或截图，剩余走全量云端识别，可平均压一半耗时。开发1评估需申请200兆本地缓存空间，产品确认安装包加两三百兆问题不大，建议按需加载（首次进智能标签时触发下载），开发1确认可用现有资源下发模块实现，约两天搞定。开发1另提出时间轴视图滑动到二十年前老照片时页面卡死三秒以上（测试提三个优高优Bug），根因是历史图片EXIF解析耗时过长加磁盘IO瓶颈，计划加本地索引预加载，最近三个月照片建树状结构、滑到底部动态加载旧数据。主持人同意改动，但提醒勿与云同步抢资源。
+### 00:07:25-00:09:15 资源隔离确认与AI修图功能预留
+开发2确认预加载放主线程IO池、同步放子线程后台服务，互不影响，但预加载需用户授权媒体和存储权限，若首次拒绝需引导弹窗，产品表示明天出稿走柔和提示路线。产品同步运营希望下版本加AI修图快捷入口（一键去背景、智能调色），主持人决定本次不硬塞（主线为性能和分类），要求在PRD写好接口逻辑和UI占位，开发侧做插件化架构预留扩展性。开发2提出趁重构将图片处理管线抽成插件化、用GLSL写统一接口，工作量多一周左右，需确认能否将非核心Bug修复往后挪。
+### 00:09:42-00:12:18 优先级调整与里程碑确认
+主持人调整优先级：非核心UI微调往后排，资源给到管线重构和AI标签优化；要求开发2今天下班前评估精确工作量，开发1排模型部署和端侧预过滤联调时间、尽量周五前跑通主干流程，周四性能压测需拿达标数据。产品确认下午定稿隐私相册入口和引导弹窗稿子、明天上午拉UI走查，并制作AI修图占位图。里程碑按原定计划月底封版，内测包暂定下周三发，拉体验官群重点跑AI分类和同步模块，产品做好反馈收集表、开发准备日志抓取。开发1提出需与数据库组对齐索引策略，主持人同意拉群让DBA配合优化建表；开发2确认今晚继续跑压测数据、明天同步，性能报告将iOS和安卓对比数据分开列，测试组合并成一份总览。
+## 要点梳理
+### 智能分类与相册推荐改版
+1. 高保真原型已出V1.5版，调整网格视图交互逻辑，长按手势增加微动效反馈。
+2. 测试反馈部分低端机上滑列表偶发掉帧，已与开发2沟通，考虑通过降低预览图缩放级别换取帧率。
+3. 用户调研反馈“隐私相册”入口太深，产品建议下一版提升至首部顶部二级菜单；产品经理确认改动不大，要求产品出交互方案供评审。
+### AI智能标签接口与模型部署
+1. 后端V2识别模型已跑通，准确率较上一代提升约88%。
+2. 因新增视频帧提取功能，单次请求耗时从800毫秒增至约1.5秒；产品提出本地缓存策略，开发1确认加CQLite缓存层可行，预计三天联调完，但缓存命中率低时需回溯。
+3. 产品经理提出端侧轻量级预过滤方案（先过滤gif/截图，再走云端识别），可平均压一半耗时；开发1评估模型体积与端侧推理开销，需申请200兆本地缓存空间。
+4. 产品同意安装包增加两三百兆，建议按需加载（首次进入智能标签时触发下载），开发1确认可用现有资源下发模块，约两天搞定。
+### 云同步模块问题
+1. 云相册同步断点续传在弱网环境下出现状态机紊乱。
+2. 同步队列积压至一千张以上时部分机型出现OOM崩溃，iOS内存回收机制较激进；开发2已加分片加载机制（每次拉五十张），但拖慢整体同步进度。
+3. 产品经理否决后台静默同步权限申请（审核严），同意先按分片加载方案走，但进度不能拖。
+### 缩略图渲染优化与性能压测
+1. 改用新图片解码库，JPEG硬解换软解，内存占用降约30%，CPU占用上升。
+2. 已在主流三款机型灰度，帧率稳定60帧，低端机约50帧；周四性能评审，性能报告初稿今晚出。
+3. 批量删除照片时若同时触发回收站重建索引，数据库偶尔锁死；已写临时规避方案（消息队列排队处理），正式修复排进V1.2迭代。
+### 时间轴视图加载速度优化
+1. 测试提三个优高优Bug：滑动到二十年前老照片时页面卡死三秒以上，原因为历史图片EXIF解析耗时太长加磁盘IO瓶颈。
+2. 开发1计划加本地索引预加载（最近三个月照片建树状结构，滑到底部动态加载旧数据）；产品经理同意，但提醒勿与云同步抢资源。
+3. 开发2确认预加载放主线程IO池、同步放子线程后台服务，互不影响；预加载需用户授权“媒体”和“存储”权限，产品明天出引导弹窗稿（柔和提示路线，不用强制遮罩）。
+### AI修图功能预留
+1. 运营反馈希望下版本加“AI修图”快捷入口（一键去背景、智能调色）；产品经理决定本次不纳入，在PRD写好接口逻辑和UI占位，开发侧做成插件化架构。
+2. 开发2提出趁重构将图片处理管线抽成插件化，用GLSL写统一接口，工作量多一周左右；产品经理同意调整优先级，非核心UI微调往后排，资源给到管线重构和AI标签优化。
+3. 开发2需今天下班前评估精确工作量发产品经理；开发1确认后端接口按标准RESTful加Swagger文档输出。
+### 项目里程碑与内测安排
+1. 项目里程碑按原定计划月底封版；内测包暂定下周三发，拉体验官群，重点跑AI分类和同步模块。
+2. 产品做好反馈收集表，开发准备日志抓取工作；开发1今晚搭好接口联调环境，明天与测试过一遍，并拉群与DBA对齐索引策略。
+### 结论与决定
+1. 隐私相册入口提升至首部顶部二级菜单，产品出交互方案供评审。
+2. AI标签采用本地缓存策略（CQLite缓存层）与端侧预过滤方案，开发1负责实施，产品评估安装包影响。
+3. 云同步采用分片加载方案，不申请后台静默同步权限。
+4. 批量删除数据库锁死Bug：临时规避方案先稳住，正式修复排进V1.2迭代。
+5. 时间轴视图采用本地索引预加载方案，注意与云同步资源隔离。
+6. AI修图功能本次不纳入，预留接口和插件化架构。
+7. 非核心UI微调往后排，资源给到管线重构和AI标签优化。
+8. 月底封版，下周三发内测包。
+### 行动项与分工
+- [ ] **出隐私相册入口交互方案**（产品 ｜ 下午定稿 ｜ 待评审）
+- [ ] **出引导弹窗稿**（产品 ｜ 明天出稿，明天上午拉UI走查 ｜ 待开始）
+- [ ] **制作AI修图占位图**（产品 ｜ 保持视觉一致性 ｜ 待开始）
+- [ ] **UI走查稿发产品经理**（产品 ｜ 十一点半前 ｜ 待完成）
+- [ ] **加CQLite缓存层**（开发1 ｜ 下午拉分支，预计三天联调完 ｜ 进行中）
+- [ ] **评估端侧预过滤模型体积与推理开销**（开发1 ｜ 待评估）
+- [ ] **按需加载实现**（开发1 ｜ 约两天 ｜ 待开始）
+- [ ] **排模型部署和端侧预过滤联调时间，周五前跑通主干流程**（开发1 ｜ 周五前 ｜ 待开始）
+- [ ] **搭接口联调环境，明天与测试过一遍**（开发1 ｜ 今晚搭好 ｜ 待完成）
+- [ ] **拉群与DBA对齐索引策略**（开发1 ｜ 待开始）
+- [ ] **继续分片加载和渲染优化，跑压测数据**（开发2 ｜ 今晚继续，明天同步 ｜ 进行中）
+- [ ] **评估管线重构精确工作量并发产品经理**（开发2 ｜ 今天下班前 ｜ 待完成）
+- [ ] **配合开发1做端侧推理联调**（开发2 ｜ 待开始）
+- [ ] **让测试组将iOS和安卓性能报告合并成一份总览**（开发2 ｜ 周四评审前 ｜ 待完成）
+### 待确认与风险
+1. 低端机掉帧问题可能影响周四性能压测达标【高风险】。
+2. AI标签单次请求耗时1.5秒，用户可能无法接受；缓存命中率低时需回溯，可能影响体验。
+3. 云同步弱网下状态机紊乱，可能导致同步失败；同步队列积压导致OOM崩溃，分片加载拖慢进度。
+4. 批量删除时数据库锁死，临时规避方案可能不够稳定。
+5. 时间轴视图卡死问题，预加载方案可能影响其他模块。
+6. 端侧预过滤的模型体积和推理开销待评估。
+7. AI修图插件化架构的具体工作量待开发2评估。
+8. 预加载权限引导弹窗的交互设计待产品出稿。</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>76.90000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>3605/3974</t>
+          <t>3605/4540</t>
         </is>
       </c>
     </row>
@@ -17465,87 +17611,101 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t># 全文摘要
-总监主持月度研讨会，组长、销冠及销售A、销售B参与，围绕上月案场转化率下滑复盘与下月攻坚展开。会议覆盖数据复盘、工地开放日标准化、价格抗性与逼定策略、跟进节奏与渠道带看质量、老带新政策、目标分解与周末答谢会、专项培训与销控纪律等板块。判定量够但转化不足，卡在逼定与转化环节，客户流失集中于价格预期与交付信心两大抗性。最终确定工地开放日定于每周三、逼定权益可视化、渠道带看实名制、周末业主答谢会联动去化、专项演练与销控实时同步等动作，并分解下月总去化120套目标。关键锚点：上月成交76套、转化率23%、下月目标120套、老带新奖励2万元、渠道带看占比65%。
-# 分段速览
-## 00:00:00–00:01:17 数据复盘与问题定性
-总监开场定下会议时长四十分钟，要求组长先过核心指标。组长汇报上月案场总到访三百二十组、环比增百分之十五，成交七十六套、转化率百分之二十三，较上月下降四个百分点；渠道带看占比百分之六十五、自然来访百分之三十五，蓄客量约三千二百组，认购到成交流失率约百分之十八。总监判定量够但转化不足，指出渠道占比过高反映自主拓客与案场拦截能力退化，要求销冠从一线角度分析客户流失原因。
-## 00:01:53–00:03:36 客户流失两大抗性与工地开放日标准化
-销冠复盘流失客户集中在价格预期与交付信心两大抗性：竞品推特价房、首付分期、送物业费等玩法造成价格落差，客户对园林选材、车库层高、外墙保温层等细节追问细致，光靠话语背书不够。销售A补充交付信心案例，并反映工地开放日频率不足、流程繁琐、报备审批需半天。组长提议固定每周三下午开放、提前在客户群和朋友圈预告，总监拍板标准化并指定组长出方案，提前两天在CRM系统推送意向客户。
-## 00:03:36–00:05:40 价格抗性应对与逼定策略
-总监明确价格抗性不能硬扛，下月政策调整后可在装修包和车位上做文章，并询问销冠送三年物业费的逼定手法。销冠介绍算总账方法：不直接降价，而是把物业费、车位管理费、装修损耗拉表对比竞品，说明单价高两千但十年省物业和维修费，再递限时权益逼定函，本周定可申请多送三年、过周失效。销售B提出客户对限时权益不买账，需把权益具象化，如打印三年缴费明细放在合同旁；同时反映案场物料更新慢、逼定函常是上月版本。
-## 00:05:40–00:08:27 跟进提速、渠道实名制与老带新政策
-组长记录物料问题，本周出新版并计划做权益可视化台卡，同时指出跟进节奏慢、客户晚上问政策回复慢导致热度下降。总监要求客户不过夜、分片包干：组长带销售A和销售B回访上周未成交的三百多组客户，销冠梳理二十几个高意向客户周末集中逼定；渠道带看下月起必须实名登记并标注需求标签，否则扣减渠道积分。销售A提出中介可能抵触，总监表示亲自与渠道部沟通。销售B汇报老带新奖励政策：成功一套奖两万现金或等值车位券，本月推四组、两组在谈，老业主需话术和礼品支持。
-## 00:08:27–00:10:08 业主推荐官方案与下月目标分解
-组长准备定制伴手礼（高端茶叶礼盒、定制保温杯）支持老带新。销冠建议搞业主推荐官活动，成功推荐可升级物业服务等级，如优先预约维修、免费家政清洗一次，软硬结合更易在小区群传播。总监要求组长把方案加入执行表、下周前出详细执行表。随后公布集团下月指标总去化一百二十套、比上月多百分之五十，组长按人员配置拆分：销冠二十八套，组长加销售A、销售B共五十套，剩余十二套作机动和渠道攻坚储备。
-## 00:10:08–00:12:10 目标认领与周末答谢会分工
-总监确认拆分合理但压力在销售A和销售B身上，两人表态能扛：销售A手头十五个准客户等认筹通知，希望渠道带看质量再筛一筛；销售B计划周末办小型业主答谢会，邀请成交业主分享并推老带新政策。销冠支持并提议联动，其改善型客户与答谢会客群重合度高，可把高意向客户拢到一起周末集中去化。总监明确分工：销售B主抓流程，销售A负责客户邀约和逼定记录，销冠带人协助。另安排本周两次专项演练（竞品对比与抗性化解、逼定时机与谈判心理学），每人必须参加、课后抽考，组长盯进度并挂钩绩效系数。
-## 00:12:10–00:15:07 销控纪律、补充建议与散会
-组长反映销控表更新延迟导致重复推房、易引客诉，总监定性为底线问题，要求销控实时同步、CRM系统锁房、群里喊话，下月再因销控不同步丢单或客诉直接问责，组长设专人每小时刷新销控大屏。销售A建议答谢会邀约话术统一为老业主专属品鉴宴、避开促销字眼，销售B随即修改邀约模板；销冠补充财务和法务在洽谈区待命、现场出数出收据可提升成交率至少两成，总监协调周六日轮流值班。散会前总监要求组长半小时内发会议纪要和任务分解表，销冠下周晨会分享逼定案例。
-# 要点梳理
-## 上月数据复盘与转化率问题
-- **整体数据**：上月案场总到访320组，环比增加15%，达标；成交76套，转化率23%，较上月27%下降4个百分点。
-- **来访结构**：渠道带看占比65%，自然来访35%；蓄客量约3200组，认购到成交流失率约18%。
-- **销冠业绩**：上月成交19套，为组内最高。
-- **客户流失两大抗性**：价格预期（竞品推特价房、首付分期、送物业费）和交付信心（客户细问园林选材、车库层高、外墙保温层）。
-- **总监判断**：渠道带看占比过高，反映自主拓客能力和案场拦截能力退化。
-## 工地开放日标准化
-- **现状问题**：工地开放日频率不够，客户自行看房不便，陪看占用销售时间；流程繁琐，报备审批需半天。
-- **决策**：工地开放日定于每周三下午固定开放，提前两天在CRM系统推送意向客户，客户直接对接专属顾问。
-- **责任分工**：组长负责出标准化方案。
-## 价格抗性与逼定策略
-- **销冠逼定手法**：不直接降价，算总账对比竞品——单价虽高2000元，但十年省物业费和品质维修维护费；配合“限时权益”逼定函，本周定可申请多送三年物业费，过周失效。
-- **销售B补充**：客户对“限时权益”不买账，需将权益具象化，如把三年缴费明细打印出来放在合同旁。
-- **物料问题**：案场逼定函更新慢，常为上月版本；组长记录并联系设计，本周出新版，写清权益条款。
-## 跟进节奏与渠道带看质量
-- **跟进问题**：客户晚上问政策回复慢，热度下降；总监强调“客户不过夜”，分片包干。
-- **回访安排**：组长带销售A和销售B回访上周未成交的300多组客户，重点盯“再考虑考虑”的。
-- **高意向梳理**：销冠梳理手头20多个高意向客户，周末集中逼定。
-- **渠道实名制**：下月起带看必须实名登记并标注需求标签，否则扣减渠道积分；总监亲自与渠道部沟通，质量大于数量，不行直接换备选。
-## 老带新政策与业主推荐官
-- **奖励政策**：老带新成功一套奖励2万现金或等值车位券；销售B本月推4组，2组在谈。
-- **伴手礼支持**：组长准备定制高端茶叶礼盒和定制保温杯，老业主转介绍时直接送。
-- **业主推荐官活动**：销冠建议每成功推荐一套，除现金外升级物业服务等级（优先预约维修、免费家政清洗一次）；组长将方案加入执行表，下周前出详细执行表。
-## 下月目标分解与周末答谢会
-- **目标**：下月集团指标总去化120套，较上月增加50%。
-- **目标拆分**：销冠28套；组长+销售A+销售B共50套；剩余12套作为机动和渠道攻坚储备。
-- **销售A表态**：手头15个准客户等下周认筹通知，希望渠道带看质量再筛一筛。
-- **周末答谢会**：销售B主抓流程，销售A负责客户邀约和逼定记录，销冠带人协助盯两桌；与改善型客户联动，集中去化。
-- **邀约话术**：统一为“老业主专属品鉴宴”，避开“促销”字眼；销售B修改邀约短信和电话模板。
-## 专项培训与销控纪律
-- **专项演练**：本周安排两次——竞品对比与抗性化解、逼定时机与谈判心理学；每人必须参加，课后现场抽考，不过加练。
-- **考核挂钩**：组长安排签到和考核表，结果挂钩下周绩效系数。
-- **销控纪律**：销控必须实时同步，谁推哪套在群里喊一声，CRM系统同步锁房；下月再因销控不同步丢单或客诉直接问责。
-- **销控刷新**：组长设置专人每小时刷新销控大屏。
-- **财务法务待命**：总监协调财务和法务周六日轮流值班，在案场外围待命，现场能签当场出数出收据，成交率可提升至少两成。
-## 结论与决定
-- 工地开放日标准化，定于每周三下午固定开放，提前两天在CRM系统推送意向客户。
-- 逼定权益可视化，本周内更新案场物料，替换旧版逼定函。
-- 渠道带看下月起实名登记并标注需求标签，否则扣减渠道积分。
-- 下月总去化目标120套，拆分：销冠28套，组长+销售A+销售B共50套，剩余12套机动。
-- 周末举办业主答谢会，邀约话术统一为“老业主专属品鉴宴”。
-- 销控必须实时同步，CRM系统锁房，下月再出现因销控不同步丢单或客诉直接问责。
-- 财务和法务周六日轮流值班，在案场外围待命。
-## 行动项与分工
-- **组长**：散会后半小时内将会议纪要和任务分解表发到工作群；制定工地开放日标准化方案；准备定制伴手礼；将业主推荐官方案加入执行表，下周前出详细执行表；安排签到考核表，挂钩下周绩效系数；设置专人每小时刷新销控大屏。
-- **销冠**：梳理20多个高意向客户，周末集中逼定；周末答谢会带人协助盯两桌；下周晨会分享逼定案例。
-- **销售A**：与组长、销售B合计完成50套目标；周末答谢会负责客户邀约和逼定记录。
-- **销售B**：与组长、销售A合计完成50套目标；周末答谢会主抓流程；修改邀约短信和电话模板。
-- **总监**：与渠道部沟通带看实名制；协调财务和法务周六日轮流值班；盯渠道和工程对接。
-## 待确认与风险
-- 渠道带看实名制可能引发中介抵触，影响渠道推盘意愿，需与渠道部沟通确认。
-- 案场物料更新慢，逼定函版本滞后可能影响逼定效果。
-- 销控表更新延迟可能导致重复推房，引发客诉。
-- 下月目标120套较上月增加50%，压力较大。
-- 周末答谢会的具体流程和邀约名单尚未最终确定。</t>
+          <t># 案场转化率提升与下月去化目标研讨会
+## 全文摘要
+上月月度研讨会由总监主持，组长、销冠、销售A、销售B等案场团队参与，围绕案场转化率下滑问题展开约四十分钟的专项讨论。会议覆盖上月数据复盘、客户流失抗性分析、工地开放日标准化、逼定策略优化、渠道带看质量管控、老带新政策、下月目标拆分、专项培训与销控纪律等议题。核心结论是量够但转化不足，问题集中在逼定和转化环节，据此确定工地开放日每周三固定开放、逼定权益可视化、渠道带看实名制、周末业主答谢会联动去化、销控实时同步等动作，并拆分下月总去化120套目标。关键数字锚点：上月到访320组、转化率23%、渠道带看占比65%、下月目标120套。
+## 分段速览
+### 00:00:00-00:01:17 数据复盘与转化率问题
+总监开场定下会议时长四十分钟，要求组长过核心指标。组长汇报上月案场总到访三百二十组、环比增百分之十五，成交七十六套、转化率百分之二十三，较上月下降四个百分点；渠道带看占比百分之六十五，蓄客量约三千二百组，认购到成交流失率约百分之十八。总监定性为量够转化不够，渠道占比过高反映自主拓客与案场拦截能力退化，问题卡在逼定和转化环节。
+### 00:01:53-00:03:36 客户流失抗性与工地开放日
+销冠复盘流失客户集中在价格预期与交付信心两大抗性，建议把工地实时进展和材料样板直接呈现给客户。销售A以改善型夫妻档案例印证工程透明可促成成交，同时指出工地开放日频率不够、流程繁琐。组长提议每周三下午固定开放、提前预告并直接对接专属顾问，总监认可并要求组长出标准化方案，提前两天在CRM系统推送意向客户。
+### 00:04:22-00:06:12 逼定策略与物料更新
+销冠分享“算总账”逼定手法，不直接降价而是对比单价高两千但十年省物业和维修费，配合“限时权益”逼定函承诺多送三年物业费。销售B指出客户对“限时权益”有套路感，需将权益具象化，如打印三年缴费明细；同时反映案场逼定函常为上月旧版。组长记录物料问题，承诺本周联系设计出新版，并计划下月制作“权益可视化”台卡。
+### 00:06:12-00:08:27 跟进节奏、渠道质量与老带新
+总监要求客户不过夜，安排组长带销售A、销售B回访上周未成交的三百多组，销冠梳理二十几个高意向客户周末逼定；渠道带看下月起实名登记并带需求标签，否则扣减渠道积分。销售A担忧渠道抵触，总监表示亲自与渠道部沟通。销售B汇报老带新奖励政策已下，本月推四组、两组在谈，组长准备定制伴手礼支持。
+### 00:08:43-00:11:20 业主推荐官与目标拆分
+销冠提议“业主推荐官”活动，成功推荐可升级物业服务等级，组长承诺下周前出执行表。总监宣布下月总去化一百二十套，组长按产出权重拆分：销冠二十八套，组长、销售A、销售B三人一组五十套，剩余十二套作机动储备。销售A、销售B表态能扛，销售B计划周末办业主答谢会，销冠协助联动高意向客户集中去化。
+### 00:11:20-00:15:07 培训、销控纪律与收尾
+总监安排本周两次专项演练并现场抽考，组长负责签到考核、挂钩绩效系数。销售A提出销控表更新延迟易致客诉，总监要求实时同步、CRM锁房，再出现直接问责，组长设专人每小时刷新销控大屏。销售A建议邀约话术用“老业主专属品鉴宴”避开“促销”字眼，销冠建议财务法务现场待命，总监协调周末值班。组长总结五项核心议题后散会。
+## 要点梳理
+### 上月数据复盘与转化率问题
+1. 上月案场总到访320组，环比增加15%，达标；成交76套，转化率23%，较上月27%下降4个百分点。
+2. 渠道带看占比65%，自然来访35%；蓄客量约3200组，认购到成交流失率约18%。
+3. 销冠上月成交19套，为组内最高；总监指出量够但转化不足，渠道占比过高反映自主拓客能力和案场拦截能力退化。
+4. 客户流失两大抗性：价格预期（竞品推特价房、首付分期、送物业费）和交付信心（关注园林选材、车库层高、外墙保温层）。
+5. 销售A通过带客户直接问工人成功转化改善型客户，但工地开放日频率不够、流程繁琐（报备审批需半天），陪看占时间影响转化。
+### 工地开放日标准化
+1. 组长提议每周三下午固定开放，提前在客户群和朋友圈发预告，客户直接对接专属顾问，不走复杂流程。
+2. 总监认可并要求组长出方案：工地开放日定于每周三，提前两天在CRM系统推送给意向客户。
+### 价格抗性与逼定策略
+1. 销冠采用“算总账”方式：对比竞品，单价虽高2000元，但十年省物业和品质维修维护费；配合“限时权益”逼定函，承诺本周定可申请多送三年物业费。
+2. 销售B发现客户对“限时权益”不买账，需将权益具象化——打印三年缴费明细放在合同旁；案场物料更新慢，逼定函常为上月版本。
+3. 组长联系设计本周出新版逼定函，把权益条款写清楚；下月制作“权益可视化”台卡放在洽谈区。
+4. 总监明确不能硬扛价格，可在装修包和车位上做文章。
+### 跟进节奏与渠道带看质量
+1. 组长指出跟进节奏慢，客户晚上问政策回复慢导致热度下降；总监要求“客户不过夜”，分片包干。
+2. 组长带销售A和销售B回访上周未成交的300多组客户，重点盯“再考虑考虑”的。
+3. 销冠梳理手头二十几个高意向客户，周末一波逼定。
+4. 渠道无效带看多，中介随便拉人凑数；下月起带看必须实名登记并有明确需求标签，否则扣减渠道积分。
+5. 销售A担忧渠道抵触，总监表示亲自与渠道部沟通，质量大于数量，底线不破。
+### 老带新政策与业主推荐官
+1. 老带新成功一套奖励两万现金或等值车位券；销售B本月推四组，两组在谈。
+2. 组长准备定制伴手礼（高端茶叶礼盒、定制保温杯），老业主转介绍时直接送。
+3. 销冠提议“业主推荐官”活动：成功推荐一套可升级物业服务等级（优先预约维修、免费家政清洗一次），软性权益更易在小区群传播。
+4. 组长将方案加入执行表，下周前出详细执行表。
+### 下月目标拆分与团队分工
+1. 下月总去化目标120套，比上月多50%；销冠目标28套，组长、销售A、销售B三人一组目标50套，剩余12套作为机动和渠道攻坚储备。
+2. 销售A手头15个准客户等下周认筹通知，表态三人能扛50套，希望渠道带看质量再筛一筛。
+3. 销售B计划周末举办业主答谢会，邀请成交业主分享并推老带新政策；销冠协助盯两桌，联动高意向客户集中去化。
+4. 答谢会分工：销冠带人协助，销售B主抓流程，销售A负责客户邀约和逼定记录。
+### 专项培训与销控纪律
+1. 本周安排两次专项演练：“竞品对比与抗性化解”“逼定时机与谈判心理学”；每人必须参加，课后现场抽考，不过加练。
+2. 组长安排签到和考核表，结果挂钩下周绩效系数。
+3. 案场销控表更新延迟，客户定后销售仍推同套房易引起客诉；销控必须实时同步，CRM系统锁房，群里喊一声。
+4. 下月再出现销控不同步丢单或客诉直接问责；组长在晨会强调纪律，设置专人每小时刷新销控大屏。
+### 周末答谢会与现场服务
+1. 销售A建议邀约话术统一为“老业主专属品鉴宴”，避开“促销”字眼；销售B改邀约短信和电话模板。
+2. 销冠建议财务和法务在洽谈区待命，现场签单出收据，客户安全感强，成交率可提升至少两成。
+3. 总监协调财务和法务周六日轮流值班，在案场外围待命，服务前置。
+### 结论与决定
+1. 工地开放日标准化，定于每周三，提前两天在CRM系统推送意向客户。
+2. 逼定权益可视化，下月制作“权益可视化”台卡，替换旧版物料。
+3. 渠道带看实名制与质量考核，下月起执行，否则扣减渠道积分。
+4. 周末业主答谢会联动去化，销冠带人协助，销售B主抓流程，销售A负责邀约和逼定记录。
+5. 专项培训本周安排两次演练，每人必须参加，课后抽考，不过加练。
+6. 销控实时同步，CRM系统锁房，下月再出现销控不同步丢单或客诉直接问责。
+7. 邀约话术统一为“老业主专属品鉴宴”，避开“促销”字眼。
+8. 财务和法务周六日轮流值班，在案场外围待命。
+### 行动项与分工
+- [ ] **出工地开放日标准化方案**（组长 ｜ 定于每周三，提前两天CRM推送 ｜ 待执行）
+- [ ] **更新逼定函物料，本周出新版**（组长联系设计 ｜ 本周 ｜ 待执行）
+- [ ] **制作“权益可视化”台卡**（组长 ｜ 下月 ｜ 待执行）
+- [ ] **准备定制伴手礼（茶叶礼盒、保温杯）**（组长 ｜ 未明确时限 ｜ 待执行）
+- [ ] **“业主推荐官”方案加入执行表，出详细执行表**（组长 ｜ 下周前 ｜ 待执行）
+- [ ] **安排专项培训签到和考核表，挂钩下周绩效系数**（组长 ｜ 本周 ｜ 待执行）
+- [ ] **晨会强调销控纪律，设置专人每小时刷新销控大屏**（组长 ｜ 散会后晨会 ｜ 待执行）
+- [ ] **散会后半小时内发会议纪要和任务分解表到工作群**（组长 ｜ 散会后半小时内 ｜ 待执行）
+- [ ] **梳理二十几个高意向客户，周末一波逼定**（销冠 ｜ 周末 ｜ 待执行）
+- [ ] **协助周末答谢会，盯两桌，联动高意向客户**（销冠 ｜ 周末 ｜ 待执行）
+- [ ] **下周晨会分享逼定案例**（销冠 ｜ 下周晨会 ｜ 待执行）
+- [ ] **回访上周未成交300多组客户，重点盯“再考虑考虑”的**（组长、销售A、销售B ｜ 未明确时限 ｜ 待执行）
+- [ ] **负责周末答谢会客户邀约和逼定记录**（销售A ｜ 周末 ｜ 待执行）
+- [ ] **主抓周末答谢会流程，改邀约短信和电话模板为“老业主专属品鉴宴”**（销售B ｜ 周末前 ｜ 待执行）
+- [ ] **与渠道部沟通渠道带看实名制事宜**（总监 ｜ 未明确时限 ｜ 待执行）
+- [ ] **协调财务和法务周六日轮流值班，在案场外围待命**（总监 ｜ 周六日 ｜ 待执行）
+- [ ] **盯渠道和工程对接**（总监 ｜ 未明确时限 ｜ 待执行）
+### 待确认与风险
+1. 渠道带看实名制可能引起渠道抵触，影响推盘意愿【高风险】。
+2. 案场物料更新慢，逼定函版本滞后，影响逼定效果。
+3. 销控表更新延迟，可能导致丢单或客诉【阻塞】。</t>
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>69.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>4211/4213</t>
+          <t>4211/4232</t>
         </is>
       </c>
     </row>
@@ -17621,76 +17781,80 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t># 全文摘要
-本次例会由组长主持，A、B两位成员参与，围绕ASR模型迭代进度、线上推理延迟及长音频解码卡死问题展开。会议覆盖数据清洗与模型训练、推理延迟优化、长音频卡死修复、前端采样率升级、监控面板与CI自动评估流水线等板块。关键结论为：确认流式RNN-T混合架构与2秒切分方案，稳定性优先、精度次之，下周先出热修复版本上灰度。关键数字锚点：有效语音时长占比提升至94%、WER下降0.8个点、首字延迟目标控制在80ms以内、热修复版本周四提测。
-# 分段速览
-## 00:00:00-00:01:21 数据清洗与模型训练进展
-会议开场后，A汇报数据清洗流水线已完成第二轮，有效语音时长占比从89%提升至94%，并重新校对了CTC的blank token分布。B反馈验证集WER下降0.8个点，但指出低资源语言混合边界场景下中英文切换时模型易吞音或重复解码。A确认问题源于CTC对齐阶段对跨语言边界和轻声尾音处理不够平滑。
-## 00:01:21-00:04:35 架构调整与推理延迟优化讨论
-A提出将全纯Transformer架构更换为流式RNN-T与Transformer混合形态，先在20小时核心数据上训练，并计划引入MixUp和Cut增强策略。B认可方向但提醒RNN-T缓存机制和显存占用在并发量高时可能导致OOM，A回应已评估INT8量化和动态缓存释放策略。B随后提出动态Batching导致首字延迟波动在150ms至300ms之间，计划改为静态分段加流式解码方案，音频按2秒切块，VAD预过滤，目标首字延迟控制在80ms以内、吞吐量稳定在120路并发。
-## 00:04:35-00:06:43 组长指示与CI评估流水线
-组长提出三点要求：流式架构切换不能影响非流式离线批处理、VAD阈值需做消融实验找最优解、下周一划拨三块A100做增量训练但需错峰调度。A回应会分开离线和流式验证集，并补充提出用GitLab CI跑自动评估流水线，代码合入即触发数据拉取、模型加载、测试集解码、结果对比，预计三天落地、周四前出V1版本。B配合将压测数据输出为标准JSON格式。
-## 00:06:43-00:08:49 长音频解码卡死问题与热修复
-B报告线上出现超长连续带方言口音音频导致解码器陷入无效循环、服务器节点重启的问题，默认max steps为2048个token、超时5秒，RNN-T的attention权重震荡未收敛导致OOM。A建议加early stopping机制，连续30步置信度低于0.2时强制截断并返回当前序列。组长决定稳定性优先、精度次之，下周先出热修复版本上灰度，B负责改解码逻辑，A配合长序列数据配比和边界用例验证，热修复版本周四提测。
-## 00:08:49-00:11:06 监控面板与前端采样率升级
-B提出接Prometheus和Grafana监控面板，可视化QPS、延迟、显存利用率、解码步数、VAD误切率，告警分P0（服务不可用或延迟超500ms）和P1（显存超85%或WER突增）两级。另提出前端SDK采样率16k与新模型32k输入不匹配，上采样引入高频伪影，32k模型在长尾词上WER比16k好0.5%，前端排期推至下月。A建议B先写轻量级重采样插件用libresample实测CPU占用和延迟影响，CPU开销控制在5%以内再提方案。
-## 00:11:06-00:11:57 总结与收尾
-组长总结四项要点：流式RNN-T混合架构和2秒切分方案本周五前出详细设计和压测数据；VAD阈值和长序列解码卡死问题B周四出消融报告和热修复方案；前端32k采样率升级B出对比文档和重采样插件实测；监控面板和CI流水线本周内定稿并开始对接运维和测试环境。A确认周三前发CI脚本和测试用例评审，B确认负责推理优化、VAD消融、热修复和监控文档，会议结束。
-# 要点梳理
-## 数据清洗与模型训练进展
-- **数据清洗**：流水线完成第二轮，长尾噪音、极端口音、背景人声重叠片段已分流，有效语音时长占比从89%提升至94%。
-- **WER表现**：验证集WER下降0.8个点；低资源语言混合边界场景下，中英文切换时模型易吞音或重复解码。
-- **架构调整**：A计划将全纯Transformer架构换成流式RNN-T与Transformer混合形态，先在20小时核心数据上训练。
-- **数据增强**：已加时间偏移，对背景白噪声和混响鲁棒性不足，准备引入MixUp和Cut再迭代一轮。
-- **CTC对齐问题**：跨语言边界和轻声尾音处理不够平滑，导致切分点偏移。
-## 推理延迟与动态Batching优化
-- **现状问题**：动态Batching在长短音频混排时抖动，首字延迟波动在150ms至300ms之间，产品反馈体验不连贯。
-- **优化方案**：B计划改为静态分段加流式解码组合方案，音频按2秒切块，前端VAD预过滤，后端RNN-T增量解码。
-- **性能目标**：首字延迟控制在80ms以内，整体吞吐量稳定在120路并发。
-- **VAD阈值**：暂定-25dB，结合能量和谱熵双模型判断；A提醒需平衡误切率和漏切率，阈值过高切掉轻声尾音致缺字，过低产生多余切分增加无效推理。
-- **验证计划**：B下周拉线上流量回放做端到端对比，前后帧特征打点日志供A排查切分点对齐影响。
-## 长音频解码卡死问题
-- **问题现象**：用户输入超长连续带方言口音音频，解码器陷入无效循环，直接导致服务器节点重启。
-- **参数现状**：解码器默认max steps为2048个token，超时时间5秒；实际序列长度超阈值时未做优雅降级，直接报OOM。
-- **根因分析**：RNN-T的attention权重一直震荡未收敛。
-- **解决方案**：A建议加early stopping机制，连续30步置信度低于0.2时强制截断并返回当前序列，可解决90%以上卡死问题；B负责实施并补充超时熔断和降级返回。
-- **决策口径**：组长明确稳定性优先、精度次之，专业术语后续通过词表扩展和热词注入解决，下周先出热修复版本上灰度。
-## 前端采样率升级与兼容方案
-- **问题**：前端SDK音频采样率16k，新模型为32k输入，上采样会引入高频伪影影响识别率。
-- **数据对比**：32k模型在长尾词上WER比16k好0.5%。
-- **排期冲突**：前端对接人称排期推到下个月，组长计划拉产品和技术总监过会优先插队。
-- **备选方案**：A建议B先写轻量级重采样插件，用libresample实测CPU占用和延迟影响再决策，避免盲目加中间环节拖慢主流程；CPU开销控制在5%以内再提方案。
-## 监控面板与CI自动评估流水线
-- **监控需求**：B计划接Prometheus和Grafana，可视化QPS、延迟、显存利用率、解码步数、VAD误切率。
-- **告警分级**：P0为服务不可用或延迟超500ms，P1为显存超85%或WER突增；指标定义文档明早发出，组长转发运维负责人。
-- **CI流水线**：A用GitLab CI跑自动评估，代码合入触发数据拉取、模型加载、测试集解码、结果对比；WER未下降或RTF超标直接打回。
-- **落地时间**：A预计三天完成，周四前出V1版本；B配合将压测数据输出为标准JSON格式供流水线读取。
-## 结论与决定
-- **稳定性优先，精度次之**：长序列解码卡死问题先保稳定性，下周出热修复版本上灰度。
-- **流式RNN-T混合架构方向确认**：流式解码适合实时转写业务，但不能影响现有非流式离线批处理，双线都要保。
-- **2秒切分方案确认合理**：VAD阈值需做消融实验画误切/漏切曲线找最优解，不只看延迟。
-- **前端32k升级需推进**：为0.5%的WER精度损失不值得，组长拉会插队推进。
-## 行动项与分工
-- **A**：本周五前出流式RNN-T混合架构和2秒切分方案详细设计及压测数据。
-- **A**：周四前出CI自动评估流水线V1版本，周三前把CI脚本和测试用例发群里评审。
-- **A**：配合长序列数据配比和边界用例验证，调整启动脚本错峰跑训练（NLP组有四个job在排队）。
-- **B**：周四出VAD阈值消融报告和热修复方案，热修复版本今晚改完、周四提测。
-- **B**：明早发出监控指标定义文档，本周内定稿监控面板并开始对接运维。
-- **B**：出前端32k采样率升级对比文档和重采样插件实测数据，CPU开销控制在5%以内。
-- **组长**：协调三块A100算力下周一开始划拨，注意与NLP组项目错峰；拉会推进前端32k升级插队。
-## 待确认与风险
-- **显存压降未验证**：RNN-T的prefix LM缓存INT8量化配合动态缓存释放，预计压降30%显存占用，压测数据明天下午发群确认阈值。
-- **VAD阈值线上表现未知**：真实线上环境底噪更复杂，需线上流量回放验证误切/漏切平衡。
-- **前端32k升级排期未定**：前端排期推至下月，需组长拉会推进；服务端加重采样模块会增加CPU开销和推理链路延迟。
-- **RNN-T显存风险**：并发量高时KV Cache显存峰值易飙高，可能导致线上服务OOM。</t>
+          <t># ASR模型迭代与线上稳定性优化例会
+## 全文摘要
+本次例会由组长主持，A与B两位成员参与，围绕ASR模型迭代进度、线上推理延迟及长音频解码卡死问题展开同步与讨论。会议覆盖数据清洗与模型训练、推理延迟优化与动态Batching调整、长音频解码卡死、监控系统与CI自动评估流水线、前端32k采样率升级等板块。关键结论为：确认流式RNN-T混合架构与2秒切块方案，稳定性优先、精度次之，下周先出热修复版本上灰度；VAD阈值需消融实验确定最优解；监控面板与CI流水线本周内定稿并对接运维和测试环境。关键数字锚点：有效语音时长占比从89%提升至94%，验证集WER下降0.8个点，目标首字延迟控制在80ms以内、吞吐量稳定在120路并发，前端32k模型在长尾词上WER比16k好0.5%。
+## 分段速览
+### 00:00:00-00:04:35 数据清洗与模型训练进展
+会议开场后，A汇报数据清洗流水线已完成第二轮，有效语音时长占比从89%提升至94%，并计划将全纯Transformer架构切换为流式RNN-T与Transformer混合形态，先在20小时核心数据上训练。B反馈验证集WER下降0.8个点，但指出低资源语言混合边界场景下中英文切换时模型易吞音或重复解码。A回应称问题源于CTC对齐阶段对跨语言边界和轻声尾音处理不够平滑，并计划引入MixUp和Cut增强策略。B提醒RNN-T的KV Cache显存峰值在并发量高时可能飙高导致OOM，A表示已评估INT8量化配合动态缓存释放策略，预计降低30%显存占用，压测数据明天下午发布。
+### 00:04:35-00:06:43 推理延迟优化与CI流水线
+B提出动态Batching导致首字延迟波动在150ms到300ms之间，计划改为静态分段加流式解码：音频按2秒切块，前端VAD预过滤，后端RNN-T增量解码，目标首字延迟控制在80ms以内、吞吐量稳定在120路并发。A建议VAD阈值需平衡误切率和漏切率，并拉线上流量回放验证。组长提出三点要求：流式架构切换不能影响非流式离线批处理、VAD阈值做消融实验、下周划拨三块A100做增量训练。A补充提出用GitLab CI实现自动评估流水线，代码合入触发数据拉取、模型加载、测试集解码、结果对比，预计三天落地，周四前出V1版本。
+### 00:06:43-00:08:49 长音频解码卡死与热修复
+B报告线上出现超长连续带方言口音音频，解码器陷入无效循环导致服务器节点重启。解码器默认max steps为2048个token，超时时间5秒，RNN-T的attention权重震荡未收敛导致OOM。A建议增加early stopping机制：连续30步置信度低于0.2时强制截断并返回当前序列，可解决90%以上卡死问题。B将实施该逻辑并补充超时熔断和降级返回。组长决定稳定性优先、精度次之，下周先出热修复版本上灰度，B负责改解码逻辑，A配合长序列数据配比和边界用例验证，周四提测。
+### 00:08:49-00:11:06 监控系统与前端采样率升级
+B提出日志系统简陋，计划接入Prometheus和Grafana，可视化QPS、延迟、显存利用率、解码步数、VAD误切率，告警分P0/P1两级，明天下班前发指标定义文档。前端SDK采样率16k与新模型32k不匹配，上采样引入高频伪影，前端排期推至下月。组长计划拉产品和技术总监优先插队，备选方案为服务端加实时重采样模块。A建议先做轻量级重采样插件实测，B将出压测对比数据，CPU开销控制在5%以内再提方案。
+### 00:11:06-00:11:57 总结与行动项确认
+组长总结四项行动：流式RNN-T混合架构和2秒切分方案周五前出详细设计和压测数据；VAD阈值和长序列解码卡死问题周四出消融报告和热修复方案；前端32k采样率升级由组长拉会推进；监控面板和CI流水线本周内定稿并对接运维和测试环境。A确认周三前把CI脚本和测试用例发群里评审，B确认负责推理优化、VAD消融、热修复和监控文档，会议结束。
+## 要点梳理
+### 数据清洗与模型训练进展
+1. 数据清洗流水线第二轮完成，有效语音时长占比从89%提升至94%，长尾噪音、极端口音和背景人声重叠片段已单独分流。
+2. 重新校对CTC的blank token分布，发现多音字和连读场景的切分点存在偏移，计划用新基准跑一轮消融。
+3. 验证集WER下降0.8个点；低资源语言混合边界场景下，中英文切换时模型易吞音或重复解码。
+4. 计划将全纯Transformer架构切换为流式RNN-T与Transformer混合形态，先在20小时核心数据上训练。
+5. 数据增强已加时间偏移，但背景白噪声和混响鲁棒性不足，准备引入MixUp和Cut再迭代一轮。
+6. RNN-T的prefix LM缓存计划做INT8量化，配合动态缓存释放策略，预计降低30%显存占用；压测数据未跑完，明天下午发日志和截图。
+### 推理延迟优化与动态Batching调整
+1. 动态Batching在长短音频混排时首字延迟波动在150ms至300ms之间，产品反馈体验不连贯。
+2. 计划改为静态分段加流式解码：音频按2秒切块，前端VAD预过滤，后端RNN-T增量解码；目标首字延迟控制在80ms以内，吞吐量稳定在120路并发。
+3. VAD阈值当前为-25dB，结合能量和谱熵双模型判断；组长要求做消融实验，画误切率和漏切率曲线找最优解。
+4. 计划下周拉线上流量回放做端到端对比，前后帧特征打点日志以便排查切分点对齐影响。
+5. 流式解码和静态切分的衔接是否影响热词注入实时生效，待验证。
+### 长音频解码卡死问题
+1. 线上出现超长连续带方言口音音频，解码器陷入无效循环，直接导致服务器节点重启。
+2. 解码器默认max steps为2048个token，超时时间5秒；实际序列长度超阈值时未做优雅降级，直接报OOM，根因是RNN-T的attention权重震荡未收敛。
+3. 计划增加early stopping机制：连续30步置信度低于0.2时强制截断并返回当前序列，预计解决90%以上卡死问题；同时补充超时熔断和降级返回。
+4. 组长定调：稳定性优先，精度次之，下周先出热修复版本上灰度；专业术语后续通过词表扩展和热词注入解决。
+### 监控系统与CI自动评估流水线
+1. 计划接入Prometheus和Grafana，可视化QPS、延迟、显存利用率、解码步数、VAD误切率。
+2. 告警阈值分两级：P0为服务不可用或延迟超500ms，P1为显存超85%或WER突增；监控指标定义文档明天下班前发组长。
+3. 计划用GitLab CI实现自动评估流水线：代码合入触发数据拉取、模型加载、测试集解码、结果对比；WER未下降或RTF超标直接打回。
+4. CI流水线预计三天落地，周四前出V1版本；B配合将压测数据输出为标准JSON格式。
+### 前端32k采样率升级
+1. 前端SDK采样率仍为16k，新模型为32k输入，上采样会引入高频伪影影响识别率；前端排期推至下个月。
+2. 32k模型在长尾词上WER比16k好0.5%，组长决定拉产品和技术总监优先插队推进。
+3. 备选方案为服务端加实时重采样模块，但会增加CPU开销和推理链路延迟；B先出压测对比数据，CPU开销控制在5%以内再提方案。
+### 结论与决定
+1. 流式RNN-T混合架构和2秒切分方案确认可行，A和B分头推进，本周五前出详细设计和压测数据。
+2. 稳定性优先，精度次之，下周先出热修复版本上灰度。
+3. 监控面板和CI自动评估流水线本周内定稿，并开始对接运维和测试环境。
+4. 前端32k采样率升级由组长拉会推进，B出对比文档和重采样插件实测。
+### 行动项与分工
+- [ ] **流式RNN-T混合架构与2秒切分方案详细设计及压测数据**（A、B ｜ 本周五前 ｜ 进行中）
+- [ ] **VAD阈值消融实验，画误切率和漏切率曲线**（B ｜ 周四出消融报告 ｜ 进行中）
+- [ ] **长序列解码卡死热修复：early stopping机制、超时熔断和降级返回**（B ｜ 今晚改完，周四提测 ｜ 进行中）
+- [ ] **长序列数据配比和边界用例验证**（A ｜ 配合B热修复版本 ｜ 进行中）
+- [ ] **CI自动评估流水线V1版本：评估脚本和流水线配置**（A ｜ 周四前 ｜ 进行中）
+- [ ] **压测数据输出标准JSON格式**（B ｜ 配合CI流水线 ｜ 进行中）
+- [ ] **监控指标定义文档**（B ｜ 明天下班前发组长 ｜ 进行中）
+- [ ] **前端32k采样率升级对比文档和重采样插件实测，CPU开销控制在5%以内**（B ｜ 未明确时限 ｜ 进行中）
+- [ ] **协调算力：下周一开始划拨三块A100做增量训练，与NLP组错峰跑**（组长 ｜ 下周一 ｜ 未开始）
+- [ ] **拉产品和技术总监推进前端32k采样率升级排期**（组长 ｜ 未明确时限 ｜ 未开始）
+- [ ] **CI脚本和测试用例发群评审**（A ｜ 周三前 ｜ 进行中）
+### 待确认与风险
+1. RNN-T的KV Cache显存峰值在并发量高时可能飙高，导致服务OOM【高风险】。
+2. RNN-T的prefix LM缓存INT8量化后显存占用具体压降幅度，压测数据未跑完，待确认。
+3. VAD阈值在真实线上环境底噪下的表现，需线上流量回放验证。
+4. 流式解码和静态切分的衔接是否影响热词注入实时生效，待验证。
+5. 前端不升级32k采样率，上采样引入高频伪影影响识别率【阻塞】。
+6. 服务端加重采样模块可能增加推理链路延迟，需压测数据支撑决策。</t>
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>65.40000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3912/3833</t>
+          <t>3912/4049</t>
         </is>
       </c>
     </row>
